--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/EN/EN_DAWUD.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/EN/EN_DAWUD.xlsx
@@ -60,8 +60,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -488,7 +492,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Privacy When Relieving Oneself","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم went far away to relieve himself, teaching privacy, modesty, and care in personal matters."},"heading":{"title":"Hadith About Privacy When Relieving Oneself","description":"This hadith gives a clear lesson in toilet etiquette and personal privacy. Mughirah ibn Shu'bah narrates that when the Prophet صلى الله عليه وسلم went outside to relieve himself, he went to a far-off place. The main point is simple: a private matter should be kept private. The wording does not add extra details, so the explanation should stay focused on what is said. The Prophet صلى الله عليه وسلم chose distance when relieving himself, showing modesty in action. For readers searching for a hadith about privacy in Islam, this narration shows that Islamic manners cover daily habits too. Even a basic human need is handled with care, dignity, and respect for others."},"teachings":["Personal privacy is part of good manners.","Relieving oneself should be done away from people when possible.","Modesty can be shown through simple daily actions."],"related_hadiths":[{"id":"2","book_id":"4","label":"Sunan Abu Dawud"},{"id":"14","book_id":"4","label":"Sunan Abu Dawud"},{"id":"15","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Privacy When Relieving Oneself","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم went far away to relieve himself, teaching privacy, modesty, and care in personal matters."},"heading":{"title":"Hadith About Privacy When Relieving Oneself","description":"This hadith gives a clear lesson in toilet etiquette and personal privacy. Mughirah ibn Shu'bah narrates that when the Prophet صلى الله عليه وسلم went outside to relieve himself, he went to a far-off place. The main point is simple: a private matter should be kept private. The wording does not add extra details, so the explanation should stay focused on what is said. The Prophet صلى الله عليه وسلم chose distance when relieving himself, showing modesty in action. For readers searching for a hadith about privacy in Islam, this narration shows that Islamic manners cover daily habits too. Even a basic human need is handled with care, dignity, and respect for others."},"teachings":["Personal privacy is part of good manners.","Relieving oneself should be done away from people when possible.","Modesty can be shown through simple daily actions."],"related_hadiths":[{"id":"2","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"14","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"15","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E2" s="4" t="n"/>
@@ -511,7 +515,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoid Facing the Two Qiblahs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم forbade facing the two qiblahs during urination or excretion, teaching respect in private acts."},"heading":{"title":"Hadith About Facing the Two Qiblahs While Relieving Oneself","description":"This hadith gives a short but serious rule about direction. Ma'qil ibn AbuMa'qil al-Asadi narrates that the Messenger of Allah صلى الله عليه وسلم forbade them from facing the two qiblahs at the time of urination or excretion. The text does not explain the phrase in detail, so the safest explanation is to keep it as the narration gives it. The core topic is qiblah respect in toilet etiquette. For people searching for hadith about facing qiblah in bathroom, this report adds another wording about avoiding a sacred direction while relieving oneself. It also shows that even when a matter is private, a believer is taught to act with respect."},"teachings":["The narration forbids facing the two qiblahs while urinating or excreting.","Respect for sacred direction is linked to private conduct.","Short hadiths can still give clear daily guidance."],"related_hadiths":[{"id":"9","book_id":"4","label":"Sunan Abu Dawud"},{"id":"144","book_id":"1","label":"Sahih Bukhari"},{"id":"11","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoid Facing the Two Qiblahs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم forbade facing the two qiblahs during urination or excretion, teaching respect in private acts."},"heading":{"title":"Hadith About Facing the Two Qiblahs While Relieving Oneself","description":"This hadith gives a short but serious rule about direction. Ma'qil ibn AbuMa'qil al-Asadi narrates that the Messenger of Allah صلى الله عليه وسلم forbade them from facing the two qiblahs at the time of urination or excretion. The text does not explain the phrase in detail, so the safest explanation is to keep it as the narration gives it. The core topic is qiblah respect in toilet etiquette. For people searching for hadith about facing qiblah in bathroom, this report adds another wording about avoiding a sacred direction while relieving oneself. It also shows that even when a matter is private, a believer is taught to act with respect."},"teachings":["The narration forbids facing the two qiblahs while urinating or excreting.","Respect for sacred direction is linked to private conduct.","Short hadiths can still give clear daily guidance."],"related_hadiths":[{"id":"9","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"144","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"11","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E3" s="4" t="n"/>
@@ -534,7 +538,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ablution from a Brass Vessel","description":"$book_name$ $hadith_number$ - $chapter_name$. Abdullah ibn Zayd reports the Prophet performed ablution from a brass vessel."},"heading":{"title":"Hadith About Performing Wudu from a Brass Vessel","description":"This hadith about performing wudu from a brass vessel is narrated by Abdullah ibn Zayd. He said that the Messenger of Allah (صلى الله عليه وسلم) came to them, and they brought water for him in a brass vessel. The Prophet (صلى الله عليه وسلم) then performed ablution. The report is simple and focused. It mentions the visit, the water, the brass vessel, and the act of wudu. It does not add extra rulings beyond what is stated. People searching for this narration often use phrases like brass vessel wudu hadith, Abdullah ibn Zayd wudu, and Prophet performed ablution from a vessel. The hadith gives a clear example of purification using that vessel."},"teachings":["Water was brought to the Prophet (صلى الله عليه وسلم) in a brass vessel.","The Prophet (صلى الله عليه وسلم) performed ablution from that water.","The narration records a clear and simple detail about wudu practice."],"related_hadiths":[{"id":"197","book_id":"1","label":"Sahih Bukhari"},{"id":"471","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ablution from a Brass Vessel","description":"$book_name$ $hadith_number$ - $chapter_name$. Abdullah ibn Zayd reports the Prophet performed ablution from a brass vessel."},"heading":{"title":"Hadith About Performing Wudu from a Brass Vessel","description":"This hadith about performing wudu from a brass vessel is narrated by Abdullah ibn Zayd. He said that the Messenger of Allah (صلى الله عليه وسلم) came to them, and they brought water for him in a brass vessel. The Prophet (صلى الله عليه وسلم) then performed ablution. The report is simple and focused. It mentions the visit, the water, the brass vessel, and the act of wudu. It does not add extra rulings beyond what is stated. People searching for this narration often use phrases like brass vessel wudu hadith, Abdullah ibn Zayd wudu, and Prophet performed ablution from a vessel. The hadith gives a clear example of purification using that vessel."},"teachings":["Water was brought to the Prophet (صلى الله عليه وسلم) in a brass vessel.","The Prophet (صلى الله عليه وسلم) performed ablution from that water.","The narration records a clear and simple detail about wudu practice."],"related_hadiths":[{"id":"197","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"471","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E4" s="4" t="n"/>
@@ -557,7 +561,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Prostrations for Forgetfulness in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. When forgetfulness happens in salah, this hadith points to two prostrations as a simple way to correct the prayer."},"heading":{"title":"Sujood as-Sahw: Two Prostrations for Forgetfulness in Prayer","description":"This hadith focuses on sujood as-sahw, the two prostrations linked to forgetfulness in prayer. The wording is short, but the lesson is clear: when a worshipper forgets something in salah, he should make two prostrations. The report also mentions that the narrator turned away and then performed two prostrations because of forgetfulness. For someone searching for a hadith about forgetting in prayer, this gives a direct action rather than leaving the person confused. It does not describe every possible case of prayer mistakes. It simply gives a clear rule from the text: forgetfulness in salah is answered with two prostrations. This keeps the prayer connected to certainty and humble correction."},"teachings":["Forgetfulness in prayer is treated with a clear action, not panic.","The text points to two prostrations when a person forgets in salah.","A worshipper should correct a prayer mistake in the way taught in the report."],"related_hadiths":[{"id":"1022","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1024","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1030","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Prostrations for Forgetfulness in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. When forgetfulness happens in salah, this hadith points to two prostrations as a simple way to correct the prayer."},"heading":{"title":"Sujood as-Sahw: Two Prostrations for Forgetfulness in Prayer","description":"This hadith focuses on sujood as-sahw, the two prostrations linked to forgetfulness in prayer. The wording is short, but the lesson is clear: when a worshipper forgets something in salah, he should make two prostrations. The report also mentions that the narrator turned away and then performed two prostrations because of forgetfulness. For someone searching for a hadith about forgetting in prayer, this gives a direct action rather than leaving the person confused. It does not describe every possible case of prayer mistakes. It simply gives a clear rule from the text: forgetfulness in salah is answered with two prostrations. This keeps the prayer connected to certainty and humble correction."},"teachings":["Forgetfulness in prayer is treated with a clear action, not panic.","The text points to two prostrations when a person forgets in salah.","A worshipper should correct a prayer mistake in the way taught in the report."],"related_hadiths":[{"id":"1022","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1024","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1030","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E5" s="4" t="n"/>
@@ -580,7 +584,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet Forgot in Prayer and Corrected It","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet prayed five rak'ahs, then made two prostrations and taught that he could forget as people forget."},"heading":{"title":"Hadith About Forgetfulness in Prayer and Sujood as-Sahw","description":"This hadith gives a very human lesson about forgetfulness in prayer. The Messenger of Allah led the people in five rak'ahs. After the prayer, the people spoke among themselves, and he asked what had happened. They asked whether the prayer had been increased. When they told him that he had prayed five, he turned and made two prostrations, then gave salutation. He also said that he was a human being and forgot as they forgot. For readers searching for sujood as-sahw hadith or hadith about forgetting rak'ahs, the main message is simple: a prayer mistake can be corrected. The report teaches calm correction and honesty when an error is noticed."},"teachings":["Even a prayer mistake should be handled calmly and clearly.","The Prophet corrected the extra rak'ah with two prostrations.","The text teaches that forgetfulness can happen and should be addressed properly."],"related_hadiths":[{"id":"1021","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1034","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1038","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet Forgot in Prayer and Corrected It","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet prayed five rak'ahs, then made two prostrations and taught that he could forget as people forget."},"heading":{"title":"Hadith About Forgetfulness in Prayer and Sujood as-Sahw","description":"This hadith gives a very human lesson about forgetfulness in prayer. The Messenger of Allah led the people in five rak'ahs. After the prayer, the people spoke among themselves, and he asked what had happened. They asked whether the prayer had been increased. When they told him that he had prayed five, he turned and made two prostrations, then gave salutation. He also said that he was a human being and forgot as they forgot. For readers searching for sujood as-sahw hadith or hadith about forgetting rak'ahs, the main message is simple: a prayer mistake can be corrected. The report teaches calm correction and honesty when an error is noticed."},"teachings":["Even a prayer mistake should be handled calmly and clearly.","The Prophet corrected the extra rak'ah with two prostrations.","The text teaches that forgetfulness can happen and should be addressed properly."],"related_hadiths":[{"id":"1021","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1034","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1038","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E6" s="4" t="n"/>
@@ -603,7 +607,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Completing a Missed Rak'ah After Salutation","description":"$book_name$ $hadith_number$ - $chapter_name$. When one rak'ah remained, the Prophet returned, had the iqamah called, and led the people in the missed rak'ah."},"heading":{"title":"Hadith About a Missed Rak'ah and Completing the Prayer","description":"This hadith deals with a missed rak'ah in prayer. The Messenger of Allah gave salutation while one rak'ah still remained. A man came and told him that he had forgotten one rak'ah. The Prophet returned to the mosque, ordered Bilal to call the iqamah, and then led the people in that remaining rak'ah. The report later identifies the man as Talhah ibn Ubaydullah. For a person searching for hadith about missing a rak'ah or correcting prayer after salam, the text shows that the missed part of the prayer was completed. It also shows that speaking up about a prayer error can help the congregation correct what was left."},"teachings":["A missed part of prayer should be completed when it is known.","A respectful reminder can help correct a congregation's prayer.","The report shows action after salutation when a rak'ah remained."],"related_hadiths":[{"id":"1022","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1024","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1028","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Completing a Missed Rak'ah After Salutation","description":"$book_name$ $hadith_number$ - $chapter_name$. When one rak'ah remained, the Prophet returned, had the iqamah called, and led the people in the missed rak'ah."},"heading":{"title":"Hadith About a Missed Rak'ah and Completing the Prayer","description":"This hadith deals with a missed rak'ah in prayer. The Messenger of Allah gave salutation while one rak'ah still remained. A man came and told him that he had forgotten one rak'ah. The Prophet returned to the mosque, ordered Bilal to call the iqamah, and then led the people in that remaining rak'ah. The report later identifies the man as Talhah ibn Ubaydullah. For a person searching for hadith about missing a rak'ah or correcting prayer after salam, the text shows that the missed part of the prayer was completed. It also shows that speaking up about a prayer error can help the congregation correct what was left."},"teachings":["A missed part of prayer should be completed when it is known.","A respectful reminder can help correct a congregation's prayer.","The report shows action after salutation when a rak'ah remained."],"related_hadiths":[{"id":"1022","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1024","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1028","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
@@ -626,7 +630,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Build Prayer on Certainty and Leave Doubt","description":"$book_name$ $hadith_number$ - $chapter_name$. When doubt enters salah, this hadith teaches building on what is certain and ending with two prostrations."},"heading":{"title":"Hadith About Doubt in Prayer: Build on Certainty","description":"This hadith is a clear guide for doubt in prayer. The Prophet said that when a person is unsure how much he has prayed, he should throw away the doubt and base the prayer on what he is sure of. After completing the prayer with certainty, he should make two prostrations. The text explains the result in both cases. If the prayer was already complete, the extra rak'ah and prostrations count as extra prayer. If it was incomplete, the added rak'ah completes it, and the two prostrations are a disgrace for the devil. For searchers asking what to do when unsure in salah, this hadith gives a careful and steady answer."},"teachings":["Doubt in prayer should be set aside in favor of what is certain.","Two prostrations are made after the prayer is completed with certainty.","The added rak'ah either completes the prayer or counts as extra prayer, as stated in the hadith."],"related_hadiths":[{"id":"1026","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1027","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1029","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Build Prayer on Certainty and Leave Doubt","description":"$book_name$ $hadith_number$ - $chapter_name$. When doubt enters salah, this hadith teaches building on what is certain and ending with two prostrations."},"heading":{"title":"Hadith About Doubt in Prayer: Build on Certainty","description":"This hadith is a clear guide for doubt in prayer. The Prophet said that when a person is unsure how much he has prayed, he should throw away the doubt and base the prayer on what he is sure of. After completing the prayer with certainty, he should make two prostrations. The text explains the result in both cases. If the prayer was already complete, the extra rak'ah and prostrations count as extra prayer. If it was incomplete, the added rak'ah completes it, and the two prostrations are a disgrace for the devil. For searchers asking what to do when unsure in salah, this hadith gives a careful and steady answer."},"teachings":["Doubt in prayer should be set aside in favor of what is certain.","Two prostrations are made after the prayer is completed with certainty.","The added rak'ah either completes the prayer or counts as extra prayer, as stated in the hadith."],"related_hadiths":[{"id":"1026","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1027","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1029","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Prostrations That Disgrace the Devil","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet named the two prostrations of forgetfulness a disgrace for the devil in prayer correction."},"heading":{"title":"Sajdah Sahw Hadith: The Two Prostrations Against the Devil","description":"This short hadith gives a strong name to the two prostrations of forgetfulness. Ibn Abbas narrated that the Prophet called them disgraceful for the devil. The text does not give a long case or step-by-step detail here. It points to the meaning of sujood as-sahw: it is not only a prayer correction, but also a response to the confusion linked to forgetfulness. For people searching for sajdah sahw hadith or the two prostrations of forgetfulness, this report highlights the spiritual side of the act. The hadith stays focused on one phrase, so the explanation should stay focused too: these two prostrations answer forgetfulness and turn the mistake into correction."},"teachings":["The two prostrations of forgetfulness carry a clear name in this report.","The hadith links sujood as-sahw with pushing back confusion from the devil.","A short text can still teach a strong meaning about prayer correction."],"related_hadiths":[{"id":"1024","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1026","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1030","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Prostrations That Disgrace the Devil","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet named the two prostrations of forgetfulness a disgrace for the devil in prayer correction."},"heading":{"title":"Sajdah Sahw Hadith: The Two Prostrations Against the Devil","description":"This short hadith gives a strong name to the two prostrations of forgetfulness. Ibn Abbas narrated that the Prophet called them disgraceful for the devil. The text does not give a long case or step-by-step detail here. It points to the meaning of sujood as-sahw: it is not only a prayer correction, but also a response to the confusion linked to forgetfulness. For people searching for sajdah sahw hadith or the two prostrations of forgetfulness, this report highlights the spiritual side of the act. The hadith stays focused on one phrase, so the explanation should stay focused too: these two prostrations answer forgetfulness and turn the mistake into correction."},"teachings":["The two prostrations of forgetfulness carry a clear name in this report.","The hadith links sujood as-sahw with pushing back confusion from the devil.","A short text can still teach a strong meaning about prayer correction."],"related_hadiths":[{"id":"1024","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1026","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1030","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E9" s="4" t="n"/>
@@ -672,7 +676,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | What to Do When Unsure About Three or Four Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. When unsure between three and four rak'ahs, add one rak'ah and make two seated prostrations before salam."},"heading":{"title":"Hadith About Three or Four Rak'ahs Doubt in Salah","description":"This hadith speaks to a common prayer doubt: not knowing whether three or four rak'ahs have been prayed. The Prophet said that the person should pray one additional rak'ah and make two prostrations while sitting before giving salutation. The text explains two possible outcomes. If the added rak'ah becomes a fifth, the two prostrations make it even. If it is the fourth, the two prostrations are a disgrace for the devil. For anyone searching what to do if confused in salah, this narration gives a direct path. It does not ask the worshipper to guess endlessly. It teaches a set action when the doubt is between three and four."},"teachings":["When unsure between three and four rak'ahs, the text gives a clear action.","The two prostrations are made while sitting before the salutation.","The hadith explains both possible results of the added rak'ah."],"related_hadiths":[{"id":"1024","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1027","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1032","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | What to Do When Unsure About Three or Four Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. When unsure between three and four rak'ahs, add one rak'ah and make two seated prostrations before salam."},"heading":{"title":"Hadith About Three or Four Rak'ahs Doubt in Salah","description":"This hadith speaks to a common prayer doubt: not knowing whether three or four rak'ahs have been prayed. The Prophet said that the person should pray one additional rak'ah and make two prostrations while sitting before giving salutation. The text explains two possible outcomes. If the added rak'ah becomes a fifth, the two prostrations make it even. If it is the fourth, the two prostrations are a disgrace for the devil. For anyone searching what to do if confused in salah, this narration gives a direct path. It does not ask the worshipper to guess endlessly. It teaches a set action when the doubt is between three and four."},"teachings":["When unsure between three and four rak'ahs, the text gives a clear action.","The two prostrations are made while sitting before the salutation.","The hadith explains both possible results of the added rak'ah."],"related_hadiths":[{"id":"1024","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1027","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1032","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E10" s="4" t="n"/>
@@ -695,7 +699,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Complete the Fourth Rak'ah When Certain of Three","description":"$book_name$ $hadith_number$ - $chapter_name$. If certain that three rak'ahs were prayed, complete one more, recite tashahhud, prostrate twice, then give salam."},"heading":{"title":"Hadith About Being Sure of Three Rak'ahs in Prayer","description":"This hadith gives a detailed step for doubt in prayer when the person is sure that three rak'ahs have been prayed. The Prophet said that he should stand and complete one rak'ah with its prostrations. Then he should sit, recite the tashahhud, and when nothing remains except the salutation, make two prostrations while sitting. After that, he gives salutation. For search terms like sure of three rak'ahs hadith or sujood as-sahw before salam, this narration is very direct. It shows that the prayer is built on what is certain. It also places the two prostrations near the end, before the final salutation described in the text."},"teachings":["When certainty is three rak'ahs, the person completes one more rak'ah.","The hadith includes tashahhud before the two prostrations.","The two prostrations are made while sitting before giving salutation."],"related_hadiths":[{"id":"1024","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1026","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1028","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Complete the Fourth Rak'ah When Certain of Three","description":"$book_name$ $hadith_number$ - $chapter_name$. If certain that three rak'ahs were prayed, complete one more, recite tashahhud, prostrate twice, then give salam."},"heading":{"title":"Hadith About Being Sure of Three Rak'ahs in Prayer","description":"This hadith gives a detailed step for doubt in prayer when the person is sure that three rak'ahs have been prayed. The Prophet said that he should stand and complete one rak'ah with its prostrations. Then he should sit, recite the tashahhud, and when nothing remains except the salutation, make two prostrations while sitting. After that, he gives salutation. For search terms like sure of three rak'ahs hadith or sujood as-sahw before salam, this narration is very direct. It shows that the prayer is built on what is certain. It also places the two prostrations near the end, before the final salutation described in the text."},"teachings":["When certainty is three rak'ahs, the person completes one more rak'ah.","The hadith includes tashahhud before the two prostrations.","The two prostrations are made while sitting before giving salutation."],"related_hadiths":[{"id":"1024","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1026","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1028","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E11" s="4" t="n"/>
@@ -718,7 +722,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Strong Opinion of Four Rak'ahs and Sajdah Sahw","description":"$book_name$ $hadith_number$ - $chapter_name$. When the stronger thought is four rak'ahs, the hadith gives tashahhud, two seated prostrations, then salam."},"heading":{"title":"Hadith About Stronger Opinion in Prayer Doubt","description":"This hadith describes a case where a person is praying and doubts whether he prayed three or four rak'ahs, while his stronger opinion is that he prayed four. The wording says he should recite tashahhud, then make two prostrations while sitting before salutation. After that, he should recite tashahhud again and give salutation, clearly. For people searching sajdah sahw when most likely four rak'ahs were prayed, the text gives a specific order. Abu Dawud also notes differences in how the report was transmitted, but the main wording in the translation remains focused on prayer doubt, tashahhud, two prostrations, and salutation."},"teachings":["The report addresses doubt when the stronger thought is four rak'ahs.","It mentions tashahhud before the two prostrations and tashahhud again after them.","The two prostrations are made while sitting before the salutation mentioned in the text."],"related_hadiths":[{"id":"1024","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1026","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1033","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Strong Opinion of Four Rak'ahs and Sajdah Sahw","description":"$book_name$ $hadith_number$ - $chapter_name$. When the stronger thought is four rak'ahs, the hadith gives tashahhud, two seated prostrations, then salam."},"heading":{"title":"Hadith About Stronger Opinion in Prayer Doubt","description":"This hadith describes a case where a person is praying and doubts whether he prayed three or four rak'ahs, while his stronger opinion is that he prayed four. The wording says he should recite tashahhud, then make two prostrations while sitting before salutation. After that, he should recite tashahhud again and give salutation, clearly. For people searching sajdah sahw when most likely four rak'ahs were prayed, the text gives a specific order. Abu Dawud also notes differences in how the report was transmitted, but the main wording in the translation remains focused on prayer doubt, tashahhud, two prostrations, and salutation."},"teachings":["The report addresses doubt when the stronger thought is four rak'ahs.","It mentions tashahhud before the two prostrations and tashahhud again after them.","The two prostrations are made while sitting before the salutation mentioned in the text."],"related_hadiths":[{"id":"1024","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1026","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1033","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
@@ -741,7 +745,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | When Unsure About More or Less Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. When unsure about more or less rak'ahs, make two seated prostrations and reject false whispers without clear signs."},"heading":{"title":"Hadith About More or Less Rak'ahs and Prayer Whispers","description":"This hadith joins two related issues in prayer: uncertainty about the number of rak'ahs and whispers about purity. The Prophet said that if one prays and does not know whether he prayed more or less, he should perform two prostrations while sitting. Then the text mentions a whisper from the devil saying that the person has been defiled. The reply is to reject that claim unless there is a smell by the nose or a sound by the ears. For searchers looking for hadith about waswas in salah, this report keeps the worshipper from acting on empty doubt. It teaches correction for prayer count and care with claims about broken ablution."},"teachings":["Uncertainty about more or less rak'ahs is answered with two seated prostrations.","A mere whisper about being defiled is not accepted in this text.","The report links certainty to clear signs such as smell or sound."],"related_hadiths":[{"id":"1024","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1030","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1031","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | When Unsure About More or Less Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. When unsure about more or less rak'ahs, make two seated prostrations and reject false whispers without clear signs."},"heading":{"title":"Hadith About More or Less Rak'ahs and Prayer Whispers","description":"This hadith joins two related issues in prayer: uncertainty about the number of rak'ahs and whispers about purity. The Prophet said that if one prays and does not know whether he prayed more or less, he should perform two prostrations while sitting. Then the text mentions a whisper from the devil saying that the person has been defiled. The reply is to reject that claim unless there is a smell by the nose or a sound by the ears. For searchers looking for hadith about waswas in salah, this report keeps the worshipper from acting on empty doubt. It teaches correction for prayer count and care with claims about broken ablution."},"teachings":["Uncertainty about more or less rak'ahs is answered with two seated prostrations.","A mere whisper about being defiled is not accepted in this text.","The report links certainty to clear signs such as smell or sound."],"related_hadiths":[{"id":"1024","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1030","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1031","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
@@ -764,7 +768,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Devil Confuses a Person in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. When the devil confuses a person about how much he prayed, the hadith teaches two seated prostrations."},"heading":{"title":"Hadith About the Devil Confusing a Person in Prayer","description":"This hadith explains why a worshipper may suddenly feel lost about the number of rak'ahs. The Prophet said that when one stands to pray, the devil comes and confuses him until he does not know how much he has prayed. If a person finds this happening, he should perform two prostrations while sitting. For people searching hadith about confusion in salah or sujood as-sahw for not knowing rak'ahs, this narration gives comfort and a practical action. It does not tell the person to become upset or stop the prayer. It points to two seated prostrations when that confusion happens. The focus is steady worship and correction."},"teachings":["Confusion about the number of rak'ahs can happen during prayer.","The hadith names the devil as a cause of this confusion.","The given response is two prostrations while sitting."],"related_hadiths":[{"id":"1029","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1031","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1032","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Devil Confuses a Person in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. When the devil confuses a person about how much he prayed, the hadith teaches two seated prostrations."},"heading":{"title":"Hadith About the Devil Confusing a Person in Prayer","description":"This hadith explains why a worshipper may suddenly feel lost about the number of rak'ahs. The Prophet said that when one stands to pray, the devil comes and confuses him until he does not know how much he has prayed. If a person finds this happening, he should perform two prostrations while sitting. For people searching hadith about confusion in salah or sujood as-sahw for not knowing rak'ahs, this narration gives comfort and a practical action. It does not tell the person to become upset or stop the prayer. It points to two seated prostrations when that confusion happens. The focus is steady worship and correction."},"teachings":["Confusion about the number of rak'ahs can happen during prayer.","The hadith names the devil as a cause of this confusion.","The given response is two prostrations while sitting."],"related_hadiths":[{"id":"1029","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1031","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1032","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E14" s="4" t="n"/>
@@ -787,7 +791,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Seated Prostrations Before Salutation","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that the two prostrations of forgetfulness are made while sitting before salutation in prayer."},"heading":{"title":"Sujood as-Sahw Before Salam While Sitting","description":"This hadith is a version of the previous report, and its added wording matters. It says that the two prostrations are made while the person is sitting before he gives the salutation. Since the report is connected to confusion about how much one has prayed, the added detail helps readers searching for sujood as-sahw before salam. The text does not add a new story or a new cause. It simply gives a placement: sitting, before the salutation. That makes it useful for understanding the order mentioned in this narration. The teaching stays narrow and clear. When this kind of prayer confusion occurs, the two prostrations are not left vague in this version."},"teachings":["This version adds that the two prostrations are done while sitting.","The placement mentioned here is before the salutation.","The report helps clarify the order in a case of prayer confusion."],"related_hadiths":[{"id":"1030","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1032","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1029","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Seated Prostrations Before Salutation","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that the two prostrations of forgetfulness are made while sitting before salutation in prayer."},"heading":{"title":"Sujood as-Sahw Before Salam While Sitting","description":"This hadith is a version of the previous report, and its added wording matters. It says that the two prostrations are made while the person is sitting before he gives the salutation. Since the report is connected to confusion about how much one has prayed, the added detail helps readers searching for sujood as-sahw before salam. The text does not add a new story or a new cause. It simply gives a placement: sitting, before the salutation. That makes it useful for understanding the order mentioned in this narration. The teaching stays narrow and clear. When this kind of prayer confusion occurs, the two prostrations are not left vague in this version."},"teachings":["This version adds that the two prostrations are done while sitting.","The placement mentioned here is before the salutation.","The report helps clarify the order in a case of prayer confusion."],"related_hadiths":[{"id":"1030","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1032","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1029","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E15" s="4" t="n"/>
@@ -810,7 +814,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostrate Twice Before Salam, Then Give Salam","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that the two prostrations are made before salutation, after which the worshipper gives salutation."},"heading":{"title":"Hadith About Sajdah Sahw Before Taslim","description":"This hadith is another version of the report about prayer confusion. Its added phrase says that the person should perform two prostrations before giving the salutation, then give the salutation. For readers asking whether sajdah sahw is before salam in this narration, the answer from this text is direct. It gives a short order: two prostrations first, then salutation. The report does not list every prayer mistake, so the explanation should not stretch beyond the wording. Its value is in the simple detail it adds to the wider topic of sujood as-sahw. It keeps the worshipper focused on a taught correction when confusion enters the prayer."},"teachings":["This version places the two prostrations before the salutation.","The salutation is given after the two prostrations.","The wording adds order and timing to the prayer correction."],"related_hadiths":[{"id":"1030","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1031","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1026","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostrate Twice Before Salam, Then Give Salam","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that the two prostrations are made before salutation, after which the worshipper gives salutation."},"heading":{"title":"Hadith About Sajdah Sahw Before Taslim","description":"This hadith is another version of the report about prayer confusion. Its added phrase says that the person should perform two prostrations before giving the salutation, then give the salutation. For readers asking whether sajdah sahw is before salam in this narration, the answer from this text is direct. It gives a short order: two prostrations first, then salutation. The report does not list every prayer mistake, so the explanation should not stretch beyond the wording. Its value is in the simple detail it adds to the wider topic of sujood as-sahw. It keeps the worshipper focused on a taught correction when confusion enters the prayer."},"teachings":["This version places the two prostrations before the salutation.","The salutation is given after the two prostrations.","The wording adds order and timing to the prayer correction."],"related_hadiths":[{"id":"1030","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1031","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1026","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E16" s="4" t="n"/>
@@ -833,7 +837,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Prostrations After Salutation for Doubt","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith states that whoever doubts in prayer should make two prostrations after giving the salutation."},"heading":{"title":"Hadith About Sujood as-Sahw After Salam for Prayer Doubt","description":"This hadith gives a brief ruling-style statement about doubt in prayer. The Prophet said that anyone who is in doubt in his prayer should make two prostrations after giving the salutation. For people searching sujood as-sahw after salam hadith, this narration is short and clear. It does not describe the exact doubt, the number of rak'ahs, or a full story. It focuses on the timing mentioned here: after the salutation. Since other reports in this batch mention before salutation in other cases, this hadith should be explained on its own terms. Its direct message is that doubt in prayer can be followed by two prostrations after salam."},"teachings":["The hadith connects doubt in prayer with two prostrations.","This narration places those prostrations after the salutation.","The text is general and does not describe a specific rak'ah count."],"related_hadiths":[{"id":"1024","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1038","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1028","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Prostrations After Salutation for Doubt","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith states that whoever doubts in prayer should make two prostrations after giving the salutation."},"heading":{"title":"Hadith About Sujood as-Sahw After Salam for Prayer Doubt","description":"This hadith gives a brief ruling-style statement about doubt in prayer. The Prophet said that anyone who is in doubt in his prayer should make two prostrations after giving the salutation. For people searching sujood as-sahw after salam hadith, this narration is short and clear. It does not describe the exact doubt, the number of rak'ahs, or a full story. It focuses on the timing mentioned here: after the salutation. Since other reports in this batch mention before salutation in other cases, this hadith should be explained on its own terms. Its direct message is that doubt in prayer can be followed by two prostrations after salam."},"teachings":["The hadith connects doubt in prayer with two prostrations.","This narration places those prostrations after the salutation.","The text is general and does not describe a specific rak'ah count."],"related_hadiths":[{"id":"1024","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1038","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1028","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E17" s="4" t="n"/>
@@ -856,7 +860,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forgetting the Sitting After Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet stood after two rak'ahs without sitting, then made two prostrations before salutation and gave salam."},"heading":{"title":"Hadith About Forgetting the First Sitting in Prayer","description":"This hadith describes a prayer led by the Messenger of Allah in which he prayed two rak'ahs, then stood without sitting. The people also stood with him. When the prayer was finished and they expected him to give the salutation, he said Allah is most great, then made two prostrations while sitting before the salutation. After that, he gave the salutation. For people searching hadith about forgetting tashahhud or first sitting in salah, this report gives the event and the correction. It does not mention a speech or a long explanation. The lesson is seen through the action: the prayer continued, and the missed sitting was answered with two prostrations before salam."},"teachings":["When the sitting after two rak'ahs was missed, the prayer continued.","The Prophet made two seated prostrations before salutation.","The congregation followed the imam when he stood."],"related_hadiths":[{"id":"1035","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1036","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1037","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forgetting the Sitting After Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet stood after two rak'ahs without sitting, then made two prostrations before salutation and gave salam."},"heading":{"title":"Hadith About Forgetting the First Sitting in Prayer","description":"This hadith describes a prayer led by the Messenger of Allah in which he prayed two rak'ahs, then stood without sitting. The people also stood with him. When the prayer was finished and they expected him to give the salutation, he said Allah is most great, then made two prostrations while sitting before the salutation. After that, he gave the salutation. For people searching hadith about forgetting tashahhud or first sitting in salah, this report gives the event and the correction. It does not mention a speech or a long explanation. The lesson is seen through the action: the prayer continued, and the missed sitting was answered with two prostrations before salam."},"teachings":["When the sitting after two rak'ahs was missed, the prayer continued.","The Prophet made two seated prostrations before salutation.","The congregation followed the imam when he stood."],"related_hadiths":[{"id":"1035","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1036","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1037","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E18" s="4" t="n"/>
@@ -879,7 +883,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing After Two Rak'ahs and Reciting Tashahhud","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that some people recited tashahhud while standing after the imam had stood from two rak'ahs."},"heading":{"title":"Hadith About Standing After Two Rak'ahs and Sujood Sahw","description":"This hadith is a follow-up version of the report about standing after two rak'ahs without sitting. It adds that some of the people recited the tashahhud while standing. Abu Dawud also mentions that Ibn al-Zubair made two prostrations before salutation in a similar case, and that this was the view of al-Zuhri. The safest explanation is to stay with the text: the issue is a missed sitting after two rak'ahs, and the related action is two prostrations before salam. For searchers asking about forgotten tashahhud in prayer, this narration adds a detail about what some worshippers did while standing, without changing the main event described in the previous report."},"teachings":["The report is tied to standing after two rak'ahs without sitting.","Some people recited tashahhud while standing, as the version states.","The related correction mentioned is two prostrations before salutation."],"related_hadiths":[{"id":"1034","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1036","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1037","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing After Two Rak'ahs and Reciting Tashahhud","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that some people recited tashahhud while standing after the imam had stood from two rak'ahs."},"heading":{"title":"Hadith About Standing After Two Rak'ahs and Sujood Sahw","description":"This hadith is a follow-up version of the report about standing after two rak'ahs without sitting. It adds that some of the people recited the tashahhud while standing. Abu Dawud also mentions that Ibn al-Zubair made two prostrations before salutation in a similar case, and that this was the view of al-Zuhri. The safest explanation is to stay with the text: the issue is a missed sitting after two rak'ahs, and the related action is two prostrations before salam. For searchers asking about forgotten tashahhud in prayer, this narration adds a detail about what some worshippers did while standing, without changing the main event described in the previous report."},"teachings":["The report is tied to standing after two rak'ahs without sitting.","Some people recited tashahhud while standing, as the version states.","The related correction mentioned is two prostrations before salutation."],"related_hadiths":[{"id":"1034","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1036","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1037","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E19" s="4" t="n"/>
@@ -902,7 +906,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | If the Imam Stands After Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. If an imam stands after two rak'ahs, he sits if not fully upright; if upright, he continues and makes sujood sahw."},"heading":{"title":"Hadith About Imam Standing After Two Rak'ahs","description":"This hadith gives a clear case about an imam who stands at the end of two rak'ahs. The Prophet said that if the imam remembers before standing straight up, he should sit down. But if he has already stood straight up, he should not sit down; instead, he performs the two prostrations of forgetfulness. For users searching what if the imam forgets first tashahhud, this text is direct. It separates the case into two moments: before fully standing and after fully standing. The report also includes Abu Dawud's note about one narrator, but the teaching in the translated wording is focused on the imam's action and sujood as-sahw."},"teachings":["If the imam remembers before fully standing, he sits down.","If he is already upright, the text says he does not sit back down.","The correction in that case is two prostrations of forgetfulness."],"related_hadiths":[{"id":"1034","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1037","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1038","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | If the Imam Stands After Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. If an imam stands after two rak'ahs, he sits if not fully upright; if upright, he continues and makes sujood sahw."},"heading":{"title":"Hadith About Imam Standing After Two Rak'ahs","description":"This hadith gives a clear case about an imam who stands at the end of two rak'ahs. The Prophet said that if the imam remembers before standing straight up, he should sit down. But if he has already stood straight up, he should not sit down; instead, he performs the two prostrations of forgetfulness. For users searching what if the imam forgets first tashahhud, this text is direct. It separates the case into two moments: before fully standing and after fully standing. The report also includes Abu Dawud's note about one narrator, but the teaching in the translated wording is focused on the imam's action and sujood as-sahw."},"teachings":["If the imam remembers before fully standing, he sits down.","If he is already upright, the text says he does not sit back down.","The correction in that case is two prostrations of forgetfulness."],"related_hadiths":[{"id":"1034","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1037","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1038","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E20" s="4" t="n"/>
@@ -925,7 +929,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Following the Imam Who Stood After Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Al-Mughirah continued after standing from two rak'ahs, then made two prostrations after salam."},"heading":{"title":"Hadith About Imam Mistake and Sujood Sahw After Salam","description":"This hadith gives a lived example from al-Mughirah ibn Shu'bah. He led the people in prayer and stood after two rak'ahs. They said Subhan Allah to alert him, and he also said Subhan Allah, but he continued. When he completed the prayer and gave salutation, he made two prostrations of forgetfulness. Then he said that he saw the Messenger of Allah doing as he had done. For people searching about following an imam who forgets tashahhud, this report shows the imam continuing after standing, then making sujood as-sahw after salam. Abu Dawud also mentions several Companions and later figures connected to this practice, but the main report is the action in prayer."},"teachings":["The people reminded the imam by saying Subhan Allah.","After standing, al-Mughirah continued the prayer and did not sit back down.","He made two prostrations of forgetfulness after salutation."],"related_hadiths":[{"id":"1034","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1036","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1038","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Following the Imam Who Stood After Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Al-Mughirah continued after standing from two rak'ahs, then made two prostrations after salam."},"heading":{"title":"Hadith About Imam Mistake and Sujood Sahw After Salam","description":"This hadith gives a lived example from al-Mughirah ibn Shu'bah. He led the people in prayer and stood after two rak'ahs. They said Subhan Allah to alert him, and he also said Subhan Allah, but he continued. When he completed the prayer and gave salutation, he made two prostrations of forgetfulness. Then he said that he saw the Messenger of Allah doing as he had done. For people searching about following an imam who forgets tashahhud, this report shows the imam continuing after standing, then making sujood as-sahw after salam. Abu Dawud also mentions several Companions and later figures connected to this practice, but the main report is the action in prayer."},"teachings":["The people reminded the imam by saying Subhan Allah.","After standing, al-Mughirah continued the prayer and did not sit back down.","He made two prostrations of forgetfulness after salutation."],"related_hadiths":[{"id":"1034","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1036","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1038","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E21" s="4" t="n"/>
@@ -948,7 +952,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | For Each Forgetfulness, Two Prostrations After Salam","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith says that for each forgetfulness there are two prostrations after giving the salutation."},"heading":{"title":"Hadith: For Each Forgetfulness There Are Two Prostrations","description":"This hadith states a broad phrase about forgetfulness in prayer. The Prophet said that for each forgetfulness there are two prostrations after giving the salutation. The wording is brief, but it is useful for readers searching sujood as-sahw after salam or two prostrations for every forgetfulness. The report does not list examples, so it should not be used here to invent cases not mentioned in the text. Its message is general: forgetfulness has a prayer correction, and this narration places the two prostrations after salutation. Abu Dawud also notes wording differences in the chain, but the translated statement remains focused on the link between forgetfulness, two prostrations, and salam."},"teachings":["Forgetfulness in prayer is linked with two prostrations in this report.","This narration places the prostrations after the salutation.","The statement is general and does not list separate types of mistakes."],"related_hadiths":[{"id":"1033","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1036","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1037","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | For Each Forgetfulness, Two Prostrations After Salam","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith says that for each forgetfulness there are two prostrations after giving the salutation."},"heading":{"title":"Hadith: For Each Forgetfulness There Are Two Prostrations","description":"This hadith states a broad phrase about forgetfulness in prayer. The Prophet said that for each forgetfulness there are two prostrations after giving the salutation. The wording is brief, but it is useful for readers searching sujood as-sahw after salam or two prostrations for every forgetfulness. The report does not list examples, so it should not be used here to invent cases not mentioned in the text. Its message is general: forgetfulness has a prayer correction, and this narration places the two prostrations after salutation. Abu Dawud also notes wording differences in the chain, but the translated statement remains focused on the link between forgetfulness, two prostrations, and salam."},"teachings":["Forgetfulness in prayer is linked with two prostrations in this report.","This narration places the prostrations after the salutation.","The statement is general and does not list separate types of mistakes."],"related_hadiths":[{"id":"1033","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1036","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1037","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E22" s="4" t="n"/>
@@ -971,7 +975,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostrations, Tashahhud, Then Salutation","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet forgot something in prayer, made two prostrations, recited tashahhud, and then gave salutation."},"heading":{"title":"Hadith About Sujood Sahw With Tashahhud Before Salam","description":"This hadith reports that the Prophet led the people in prayer and forgot something. He then made two prostrations, recited the tashahhud, and gave the salutation. The text does not say exactly what was forgotten, so a careful explanation should not add a specific mistake. The value of this narration is in the order it gives: prostrations, tashahhud, then salam. For readers searching for tashahhud after sujood as-sahw, this hadith is useful because the wording mentions it clearly. It also shows that a forgotten matter in prayer can be followed by a taught correction. The report is simple and focused, and the explanation should stay that way."},"teachings":["The hadith does not name the exact forgotten matter.","The order mentioned is two prostrations, tashahhud, then salutation.","The prayer mistake was corrected within the prayer practice described."],"related_hadiths":[{"id":"1030","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1038","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1034","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostrations, Tashahhud, Then Salutation","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet forgot something in prayer, made two prostrations, recited tashahhud, and then gave salutation."},"heading":{"title":"Hadith About Sujood Sahw With Tashahhud Before Salam","description":"This hadith reports that the Prophet led the people in prayer and forgot something. He then made two prostrations, recited the tashahhud, and gave the salutation. The text does not say exactly what was forgotten, so a careful explanation should not add a specific mistake. The value of this narration is in the order it gives: prostrations, tashahhud, then salam. For readers searching for tashahhud after sujood as-sahw, this hadith is useful because the wording mentions it clearly. It also shows that a forgotten matter in prayer can be followed by a taught correction. The report is simple and focused, and the explanation should stay that way."},"teachings":["The hadith does not name the exact forgotten matter.","The order mentioned is two prostrations, tashahhud, then salutation.","The prayer mistake was corrected within the prayer practice described."],"related_hadiths":[{"id":"1030","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1038","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1034","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E23" s="4" t="n"/>
@@ -994,7 +998,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Waiting After Salam So Women Could Leave","description":"$book_name$ $hadith_number$ - $chapter_name$. After salutation, the Prophet stayed briefly; people understood this as allowing women to leave before men."},"heading":{"title":"Hadith About Women Leaving After Prayer Before Men","description":"This hadith is about prayer etiquette after the salutation. Umm Salamah said that when the Messenger of Allah gave salutation, he stayed for a while. The people understood that this was so women could leave earlier than men. The report is short, so the lesson should remain simple. It shows calm order after congregational prayer and care in how people leave. For readers searching hadith about women leaving mosque after prayer or Prophet stayed after salam, this narration gives the core picture: he did not rush away immediately after salutation, and the people saw wisdom in that pause. The hadith does not add a long legal discussion, so the explanation stays with the wording."},"teachings":["The Prophet stayed briefly after giving salutation.","People understood the pause as allowing women to leave before men.","The report points to calm order after congregational prayer."],"related_hadiths":[{"id":"837","book_id":"1","label":"Sahih Bukhari"},{"id":"875","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Waiting After Salam So Women Could Leave","description":"$book_name$ $hadith_number$ - $chapter_name$. After salutation, the Prophet stayed briefly; people understood this as allowing women to leave before men."},"heading":{"title":"Hadith About Women Leaving After Prayer Before Men","description":"This hadith is about prayer etiquette after the salutation. Umm Salamah said that when the Messenger of Allah gave salutation, he stayed for a while. The people understood that this was so women could leave earlier than men. The report is short, so the lesson should remain simple. It shows calm order after congregational prayer and care in how people leave. For readers searching hadith about women leaving mosque after prayer or Prophet stayed after salam, this narration gives the core picture: he did not rush away immediately after salutation, and the people saw wisdom in that pause. The hadith does not add a long legal discussion, so the explanation stays with the wording."},"teachings":["The Prophet stayed briefly after giving salutation.","People understood the pause as allowing women to leave before men.","The report points to calm order after congregational prayer."],"related_hadiths":[{"id":"837","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"875","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E24" s="4" t="n"/>
@@ -1017,7 +1021,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray in Your Dwellings During Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear teaching on praying in dwellings during cold or rainy travel nights."},"heading":{"title":"Hadith About Pray in Your Dwellings and Prayer Ease","description":"This Hadith teaches prayer ease during travel when the weather is hard. Ibn Umar made the call to prayer at Dajnan and then told people to offer prayer in their dwellings. He connected this action to the Messenger of Allah (صلى الله عليه وسلم), who used to command the caller to announce prayer and then say, “Pray in your dwellings” on a cold or rainy night during a journey. The main point is simple: worship remains important, but hardship is recognized. The Hadith about praying at home in rain shows care for people who may struggle with cold, rain, and travel. It is not about leaving prayer. It is about praying in a safer and easier place when the stated condition exists."},"teachings":["Prayer should still be offered, even when weather makes travel difficult.","Cold and rain during a journey can be a reason for praying in one’s dwelling.","Religious instruction should consider real hardship faced by people.","The announcement was made clearly so people knew what to do."],"related_hadiths":[{"id":"1062","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1063","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1065","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray in Your Dwellings During Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear teaching on praying in dwellings during cold or rainy travel nights."},"heading":{"title":"Hadith About Pray in Your Dwellings and Prayer Ease","description":"This Hadith teaches prayer ease during travel when the weather is hard. Ibn Umar made the call to prayer at Dajnan and then told people to offer prayer in their dwellings. He connected this action to the Messenger of Allah (صلى الله عليه وسلم), who used to command the caller to announce prayer and then say, “Pray in your dwellings” on a cold or rainy night during a journey. The main point is simple: worship remains important, but hardship is recognized. The Hadith about praying at home in rain shows care for people who may struggle with cold, rain, and travel. It is not about leaving prayer. It is about praying in a safer and easier place when the stated condition exists."},"teachings":["Prayer should still be offered, even when weather makes travel difficult.","Cold and rain during a journey can be a reason for praying in one’s dwelling.","Religious instruction should consider real hardship faced by people.","The announcement was made clearly so people knew what to do."],"related_hadiths":[{"id":"1062","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1063","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1065","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E25" s="4" t="n"/>
@@ -1040,7 +1044,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer at Home on Cold Windy Nights","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith showing the call to pray in dwellings on cold, windy, or rainy travel nights."},"heading":{"title":"Pray in Your Dwellings Hadith for Cold and Windy Nights","description":"This Hadith gives another clear report about prayer ease in hard weather. Ibn Umar made the call to prayer at Dajnan on a cold and windy night. At the end of the call, he announced, “Pray in your dwellings.” He then explained that the Messenger of Allah (صلى الله عليه وسلم) used to command the mu’adhdhin to make this announcement when it was a cold or rainy night during travel. The Hadith about prayer in rain and wind shows that the call to prayer could include guidance for the situation people were facing. It does not remove the prayer. It tells people where they may pray under these conditions. The teaching is practical, direct, and caring."},"teachings":["The call to prayer may include guidance when people face hardship.","Cold, wind, and rain during travel are mentioned as reasons for praying in dwellings.","The Prophet’s practice was followed and explained by Ibn Umar.","Ease in worship does not mean neglecting prayer."],"related_hadiths":[{"id":"1061","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1063","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1064","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer at Home on Cold Windy Nights","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith showing the call to pray in dwellings on cold, windy, or rainy travel nights."},"heading":{"title":"Pray in Your Dwellings Hadith for Cold and Windy Nights","description":"This Hadith gives another clear report about prayer ease in hard weather. Ibn Umar made the call to prayer at Dajnan on a cold and windy night. At the end of the call, he announced, “Pray in your dwellings.” He then explained that the Messenger of Allah (صلى الله عليه وسلم) used to command the mu’adhdhin to make this announcement when it was a cold or rainy night during travel. The Hadith about prayer in rain and wind shows that the call to prayer could include guidance for the situation people were facing. It does not remove the prayer. It tells people where they may pray under these conditions. The teaching is practical, direct, and caring."},"teachings":["The call to prayer may include guidance when people face hardship.","Cold, wind, and rain during travel are mentioned as reasons for praying in dwellings.","The Prophet’s practice was followed and explained by Ibn Umar.","Ease in worship does not mean neglecting prayer."],"related_hadiths":[{"id":"1061","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1063","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1064","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E26" s="4" t="n"/>
@@ -1063,7 +1067,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray in Dwellings During Bad Weather","description":"$book_name$ $hadith_number$ - $chapter_name$. A simple report on announcing prayer in dwellings during cold, windy, or rainy weather."},"heading":{"title":"Hadith About Praying in Dwellings During Cold and Rain","description":"This Hadith focuses on the phrase “Pray in the dwellings.” Nafi reports that Ibn Umar made the call to prayer on a cold and windy night, then gave this instruction. He explained that when there was a cold or rainy night, the Messenger of Allah (صلى الله عليه وسلم) used to command the mu’adhdhin to announce the same message. The Hadith about praying in dwellings helps readers see that Islamic practice includes mercy in difficult conditions. The weather mentioned in the text is specific: cold, wind, or rain. The point is not to treat prayer lightly. Rather, people are guided to pray without being forced into avoidable hardship. The message is short, clear, and easy to follow."},"teachings":["The instruction to pray in dwellings was linked to cold or rainy nights.","The mu’adhdhin could announce a practical change for the worshippers.","Following the Prophet’s example includes care for people’s hardship.","Prayer remains part of the day even when the place of prayer changes."],"related_hadiths":[{"id":"1061","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1062","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1065","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray in Dwellings During Bad Weather","description":"$book_name$ $hadith_number$ - $chapter_name$. A simple report on announcing prayer in dwellings during cold, windy, or rainy weather."},"heading":{"title":"Hadith About Praying in Dwellings During Cold and Rain","description":"This Hadith focuses on the phrase “Pray in the dwellings.” Nafi reports that Ibn Umar made the call to prayer on a cold and windy night, then gave this instruction. He explained that when there was a cold or rainy night, the Messenger of Allah (صلى الله عليه وسلم) used to command the mu’adhdhin to announce the same message. The Hadith about praying in dwellings helps readers see that Islamic practice includes mercy in difficult conditions. The weather mentioned in the text is specific: cold, wind, or rain. The point is not to treat prayer lightly. Rather, people are guided to pray without being forced into avoidable hardship. The message is short, clear, and easy to follow."},"teachings":["The instruction to pray in dwellings was linked to cold or rainy nights.","The mu’adhdhin could announce a practical change for the worshippers.","Following the Prophet’s example includes care for people’s hardship.","Prayer remains part of the day even when the place of prayer changes."],"related_hadiths":[{"id":"1061","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1062","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1065","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E27" s="4" t="n"/>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rainy Night Prayer at Home","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith on announcing prayer at homes in Medina during rainy nights or cold mornings."},"heading":{"title":"Rainy Night Prayer at Home Hadith and Prayer Ease","description":"This Hadith mentions that the announcer of the Messenger of Allah (صلى الله عليه وسلم) announced for people to pray at homes in Medina on a rainy night or a cold morning. The wording is brief, but the meaning is easy to understand. The people were not told to ignore prayer. They were given a way to pray while avoiding hardship from rain or cold. This Hadith about praying at home in bad weather is closely connected to reports about “Pray in your dwellings.” It shows that the guidance was not only spoken as a general idea; it was announced to people when the weather called for it. The focus is mercy, clarity, and keeping prayer within people’s ability."},"teachings":["Rainy nights and cold mornings are mentioned as times of hardship.","The announcement helped people know that praying at home was allowed in that situation.","Prayer was still expected, even when people did not gather as usual.","Clear public guidance helps remove confusion during difficult weather."],"related_hadiths":[{"id":"1061","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1062","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1066","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rainy Night Prayer at Home","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith on announcing prayer at homes in Medina during rainy nights or cold mornings."},"heading":{"title":"Rainy Night Prayer at Home Hadith and Prayer Ease","description":"This Hadith mentions that the announcer of the Messenger of Allah (صلى الله عليه وسلم) announced for people to pray at homes in Medina on a rainy night or a cold morning. The wording is brief, but the meaning is easy to understand. The people were not told to ignore prayer. They were given a way to pray while avoiding hardship from rain or cold. This Hadith about praying at home in bad weather is closely connected to reports about “Pray in your dwellings.” It shows that the guidance was not only spoken as a general idea; it was announced to people when the weather called for it. The focus is mercy, clarity, and keeping prayer within people’s ability."},"teachings":["Rainy nights and cold mornings are mentioned as times of hardship.","The announcement helped people know that praying at home was allowed in that situation.","Prayer was still expected, even when people did not gather as usual.","Clear public guidance helps remove confusion during difficult weather."],"related_hadiths":[{"id":"1061","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1062","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1066","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E28" s="4" t="n"/>
@@ -1109,7 +1113,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rain During Travel and Prayer Ease","description":"$book_name$ $hadith_number$ - $chapter_name$. A concise Hadith showing permission to pray in one’s dwelling during rain on a journey."},"heading":{"title":"Hadith About Rain During Travel and Praying in Your Dwelling","description":"This Hadith is very direct. Jabir said that they were with the Messenger of Allah (صلى الله عليه وسلم) during a journey, and rain fell upon them. The Messenger of Allah (صلى الله عليه وسلم) then said that anyone who wanted to pray in his dwelling may pray. The Hadith about rain during travel shows a clear case of prayer ease. The condition in the text is rain while travelling. The wording also shows choice: “Anyone who wants.” It does not present prayer as something to leave. It gives room for people to pray in their own place when rain makes gathering harder. This is a simple teaching about care, ease, and practical worship under real weather conditions."},"teachings":["Rain during a journey can bring ease in where a person prays.","The Prophet (صلى الله عليه وسلم) allowed those who wished to pray in their dwelling.","Prayer remains part of worship even when people do not gather in the usual place.","The Hadith shows concern for people facing wet and difficult travel conditions."],"related_hadiths":[{"id":"1061","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1062","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1063","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rain During Travel and Prayer Ease","description":"$book_name$ $hadith_number$ - $chapter_name$. A concise Hadith showing permission to pray in one’s dwelling during rain on a journey."},"heading":{"title":"Hadith About Rain During Travel and Praying in Your Dwelling","description":"This Hadith is very direct. Jabir said that they were with the Messenger of Allah (صلى الله عليه وسلم) during a journey, and rain fell upon them. The Messenger of Allah (صلى الله عليه وسلم) then said that anyone who wanted to pray in his dwelling may pray. The Hadith about rain during travel shows a clear case of prayer ease. The condition in the text is rain while travelling. The wording also shows choice: “Anyone who wants.” It does not present prayer as something to leave. It gives room for people to pray in their own place when rain makes gathering harder. This is a simple teaching about care, ease, and practical worship under real weather conditions."},"teachings":["Rain during a journey can bring ease in where a person prays.","The Prophet (صلى الله عليه وسلم) allowed those who wished to pray in their dwelling.","Prayer remains part of worship even when people do not gather in the usual place.","The Hadith shows concern for people facing wet and difficult travel conditions."],"related_hadiths":[{"id":"1061","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1062","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1063","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E29" s="4" t="n"/>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Jumuah Prayer in Rain and Mud","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith showing ease for Jumuah when rain and mud would cause hardship for worshippers."},"heading":{"title":"Jumuah Prayer in Rain Hadith and Ease from Hardship","description":"This Hadith gives a strong example of care for people on a rainy day. Ibn Abbas told his mu’adhdhin not to say “Come to prayer” after the testimony that Muhammad is the Messenger of Allah. Instead, he told him to say, “Pray at your homes.” Some people were surprised, so Ibn Abbas explained that someone better than him had done it. He also said that Friday prayer is an obligatory duty, but he disliked putting people into hardship so they would have to walk through mud and rain. This Hadith about Jumuah in rain keeps two points together: Friday prayer has weight, and hardship is not ignored."},"teachings":["Friday prayer is described as an obligatory duty in the Hadith.","Rain and mud were treated as real hardship for people walking to prayer.","Ibn Abbas wanted to avoid causing people difficulty.","People may be surprised by ease, so clear explanation is helpful."],"related_hadiths":[{"id":"1064","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1067","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1065","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Jumuah Prayer in Rain and Mud","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith showing ease for Jumuah when rain and mud would cause hardship for worshippers."},"heading":{"title":"Jumuah Prayer in Rain Hadith and Ease from Hardship","description":"This Hadith gives a strong example of care for people on a rainy day. Ibn Abbas told his mu’adhdhin not to say “Come to prayer” after the testimony that Muhammad is the Messenger of Allah. Instead, he told him to say, “Pray at your homes.” Some people were surprised, so Ibn Abbas explained that someone better than him had done it. He also said that Friday prayer is an obligatory duty, but he disliked putting people into hardship so they would have to walk through mud and rain. This Hadith about Jumuah in rain keeps two points together: Friday prayer has weight, and hardship is not ignored."},"teachings":["Friday prayer is described as an obligatory duty in the Hadith.","Rain and mud were treated as real hardship for people walking to prayer.","Ibn Abbas wanted to avoid causing people difficulty.","People may be surprised by ease, so clear explanation is helpful."],"related_hadiths":[{"id":"1064","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1067","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1065","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E30" s="4" t="n"/>
@@ -1155,7 +1159,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Friday Prayer Duty and Exceptions","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith stating Jumuah in congregation as a duty, with four named exceptions."},"heading":{"title":"Friday Prayer Duty Hadith with Four Exceptions","description":"This Hadith speaks about the duty of Friday prayer in congregation. The Prophet (صلى الله عليه وسلم) is reported to have said that the Friday prayer in congregation is a necessary duty for every Muslim, with four exceptions: a slave, a woman, a boy, and a sick person. The Hadith about Friday prayer duty is short, but it gives a clear rule within the wording provided. It also names the exceptions directly, so the explanation should not add other groups or conditions not found in the text. Abu Dawud also notes that Tariq ibn Shihab had seen the Prophet (صلى الله عليه وسلم) but had not heard anything from him. The main message is the importance of Jumuah, while also noting the stated exceptions."},"teachings":["Friday prayer in congregation is described as a necessary duty.","The Hadith names four exceptions: a slave, a woman, a boy, and a sick person.","The text should be understood with care and without adding extra exceptions here.","Abu Dawud’s note reminds readers to notice details about narration."],"related_hadiths":[{"id":"1066","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1068","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1069","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Friday Prayer Duty and Exceptions","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith stating Jumuah in congregation as a duty, with four named exceptions."},"heading":{"title":"Friday Prayer Duty Hadith with Four Exceptions","description":"This Hadith speaks about the duty of Friday prayer in congregation. The Prophet (صلى الله عليه وسلم) is reported to have said that the Friday prayer in congregation is a necessary duty for every Muslim, with four exceptions: a slave, a woman, a boy, and a sick person. The Hadith about Friday prayer duty is short, but it gives a clear rule within the wording provided. It also names the exceptions directly, so the explanation should not add other groups or conditions not found in the text. Abu Dawud also notes that Tariq ibn Shihab had seen the Prophet (صلى الله عليه وسلم) but had not heard anything from him. The main message is the importance of Jumuah, while also noting the stated exceptions."},"teachings":["Friday prayer in congregation is described as a necessary duty.","The Hadith names four exceptions: a slave, a woman, a boy, and a sick person.","The text should be understood with care and without adding extra exceptions here.","Abu Dawud’s note reminds readers to notice details about narration."],"related_hadiths":[{"id":"1066","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1068","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1069","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E31" s="4" t="n"/>
@@ -1178,7 +1182,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | First Friday Prayer After Medina","description":"$book_name$ $hadith_number$ - $chapter_name$. A report naming Juwatha as the first Friday prayer after the Prophet’s mosque in Medina."},"heading":{"title":"First Friday Prayer After Medina Hadith and Jumuah History","description":"This Hadith records a point from the early history of Friday prayer. Ibn Abbas said that the first Friday prayer offered in Islam after the Friday prayer in the mosque of the Messenger of Allah (صلى الله عليه وسلم) was the Friday prayer offered at Juwatha, a village from the villages of al-Bahrain. The narrator Uthman added that it was a village from the villages of the tribe of Abd al-Qais. The Hadith about the first Friday prayer after Medina is not giving a long story or legal detail. It simply preserves a named place and event. Its main value is in showing that Jumuah was held beyond the Prophet’s mosque and remembered by the companions."},"teachings":["The Hadith identifies Juwatha as an early place where Friday prayer was offered.","It connects the spread of Jumuah to a named village in al-Bahrain.","The report preserves a specific historical memory about Friday prayer.","The wording should be kept to the place and detail mentioned in the text."],"related_hadiths":[{"id":"1069","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1067","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | First Friday Prayer After Medina","description":"$book_name$ $hadith_number$ - $chapter_name$. A report naming Juwatha as the first Friday prayer after the Prophet’s mosque in Medina."},"heading":{"title":"First Friday Prayer After Medina Hadith and Jumuah History","description":"This Hadith records a point from the early history of Friday prayer. Ibn Abbas said that the first Friday prayer offered in Islam after the Friday prayer in the mosque of the Messenger of Allah (صلى الله عليه وسلم) was the Friday prayer offered at Juwatha, a village from the villages of al-Bahrain. The narrator Uthman added that it was a village from the villages of the tribe of Abd al-Qais. The Hadith about the first Friday prayer after Medina is not giving a long story or legal detail. It simply preserves a named place and event. Its main value is in showing that Jumuah was held beyond the Prophet’s mosque and remembered by the companions."},"teachings":["The Hadith identifies Juwatha as an early place where Friday prayer was offered.","It connects the spread of Jumuah to a named village in al-Bahrain.","The report preserves a specific historical memory about Friday prayer.","The wording should be kept to the place and detail mentioned in the text."],"related_hadiths":[{"id":"1069","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1067","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E32" s="4" t="n"/>
@@ -1201,7 +1205,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | First Jumuah Led for Forty People","description":"$book_name$ $hadith_number$ - $chapter_name$. A report about As'ad ibn Zurarah leading an early Friday prayer with forty people."},"heading":{"title":"First Jumuah with Forty People Hadith and Early Friday Prayer","description":"This Hadith shares a remembered event about early Friday prayer. When Ka'b ibn Malik heard the call to prayer on Friday, he would pray for mercy for As'ad ibn Zurarah. His son asked why he did this. Ka'b explained that As'ad was the first to hold the Friday prayer for them at Hazm an-Nabit, in the area mentioned in the narration. When asked how many people were present, he said they were forty. The Hadith about first Jumuah with forty people is focused on memory, gratitude, and a specific early gathering. It does not give extra details beyond the place, the person, and the number. The lesson is to remember those who helped establish good acts."},"teachings":["Ka'b remembered As'ad ibn Zurarah when hearing the Friday call.","The Hadith records an early Friday prayer gathering with forty people.","It shows gratitude for someone connected to a good religious act.","The narration gives specific details without adding a long explanation."],"related_hadiths":[{"id":"1068","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1067","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | First Jumuah Led for Forty People","description":"$book_name$ $hadith_number$ - $chapter_name$. A report about As'ad ibn Zurarah leading an early Friday prayer with forty people."},"heading":{"title":"First Jumuah with Forty People Hadith and Early Friday Prayer","description":"This Hadith shares a remembered event about early Friday prayer. When Ka'b ibn Malik heard the call to prayer on Friday, he would pray for mercy for As'ad ibn Zurarah. His son asked why he did this. Ka'b explained that As'ad was the first to hold the Friday prayer for them at Hazm an-Nabit, in the area mentioned in the narration. When asked how many people were present, he said they were forty. The Hadith about first Jumuah with forty people is focused on memory, gratitude, and a specific early gathering. It does not give extra details beyond the place, the person, and the number. The lesson is to remember those who helped establish good acts."},"teachings":["Ka'b remembered As'ad ibn Zurarah when hearing the Friday call.","The Hadith records an early Friday prayer gathering with forty people.","It shows gratitude for someone connected to a good religious act.","The narration gives specific details without adding a long explanation."],"related_hadiths":[{"id":"1068","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1067","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E33" s="4" t="n"/>
@@ -1224,7 +1228,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid and Friday Prayer Same Day","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith showing the Prophet gave a concession when Eid and Friday came on the same day."},"heading":{"title":"Eid and Friday Prayer Same Day Hadith with Concession","description":"This Hadith discusses what happened when Eid prayer and Friday prayer came on the same day. Mu'awiyah asked Zayd ibn Arqam if he had witnessed this with the Messenger of Allah (صلى الله عليه وسلم). Zayd said yes. When asked what the Prophet (صلى الله عليه وسلم) did, he said that the Prophet offered the Eid prayer, then granted a concession regarding Friday prayer and said, “If anyone wants to offer it, he may offer.” The Hadith about Eid and Jumuah on the same day is clear in its wording. It mentions Eid being prayed first and then a concession for Friday prayer. It does not cancel the value of Jumuah, but it reports the permission given in that case."},"teachings":["Eid prayer and Friday prayer can fall on the same day.","The Prophet (صلى الله عليه وسلم) offered the Eid prayer first in this report.","A concession was given for the Friday prayer in that situation.","The wording leaves room for whoever wanted to offer Friday prayer to do so."],"related_hadiths":[{"id":"1071","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1073","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid and Friday Prayer Same Day","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith showing the Prophet gave a concession when Eid and Friday came on the same day."},"heading":{"title":"Eid and Friday Prayer Same Day Hadith with Concession","description":"This Hadith discusses what happened when Eid prayer and Friday prayer came on the same day. Mu'awiyah asked Zayd ibn Arqam if he had witnessed this with the Messenger of Allah (صلى الله عليه وسلم). Zayd said yes. When asked what the Prophet (صلى الله عليه وسلم) did, he said that the Prophet offered the Eid prayer, then granted a concession regarding Friday prayer and said, “If anyone wants to offer it, he may offer.” The Hadith about Eid and Jumuah on the same day is clear in its wording. It mentions Eid being prayed first and then a concession for Friday prayer. It does not cancel the value of Jumuah, but it reports the permission given in that case."},"teachings":["Eid prayer and Friday prayer can fall on the same day.","The Prophet (صلى الله عليه وسلم) offered the Eid prayer first in this report.","A concession was given for the Friday prayer in that situation.","The wording leaves room for whoever wanted to offer Friday prayer to do so."],"related_hadiths":[{"id":"1071","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1073","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E34" s="4" t="n"/>
@@ -1247,7 +1251,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn al-Zubayr and Eid on Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. A report where Ibn Abbas said Ibn al-Zubayr followed the Sunnah on Eid and Friday."},"heading":{"title":"Ibn al-Zubayr Eid on Friday Hadith and the Sunnah","description":"This Hadith reports an event during the time of Ibn al-Zubayr. Ata said that Ibn al-Zubayr led them in the Eid prayer on a Friday early in the morning. Later, when they went for Friday prayer, he did not come out to them, so they prayed by themselves alone. When Ibn Abbas later came and they mentioned the matter to him, he said, “He followed the sunnah.” The Hadith about Eid and Friday on the same day is tied to a real action and Ibn Abbas’s response. The text does not give a long ruling, but it clearly connects the action to the Sunnah. The focus is the overlap of Eid and Jumuah and the ease shown in that case."},"teachings":["Eid prayer was held early on a Friday in this report.","Ibn al-Zubayr did not come out later for Friday prayer.","Ibn Abbas described the action as following the Sunnah.","The Hadith shows a practical example connected to Eid and Friday falling together."],"related_hadiths":[{"id":"1070","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1073","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn al-Zubayr and Eid on Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. A report where Ibn Abbas said Ibn al-Zubayr followed the Sunnah on Eid and Friday."},"heading":{"title":"Ibn al-Zubayr Eid on Friday Hadith and the Sunnah","description":"This Hadith reports an event during the time of Ibn al-Zubayr. Ata said that Ibn al-Zubayr led them in the Eid prayer on a Friday early in the morning. Later, when they went for Friday prayer, he did not come out to them, so they prayed by themselves alone. When Ibn Abbas later came and they mentioned the matter to him, he said, “He followed the sunnah.” The Hadith about Eid and Friday on the same day is tied to a real action and Ibn Abbas’s response. The text does not give a long ruling, but it clearly connects the action to the Sunnah. The focus is the overlap of Eid and Jumuah and the ease shown in that case."},"teachings":["Eid prayer was held early on a Friday in this report.","Ibn al-Zubayr did not come out later for Friday prayer.","Ibn Abbas described the action as following the Sunnah.","The Hadith shows a practical example connected to Eid and Friday falling together."],"related_hadiths":[{"id":"1070","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1073","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E35" s="4" t="n"/>
@@ -1270,7 +1274,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Festivals on One Day","description":"$book_name$ $hadith_number$ - $chapter_name$. A report about Eid and Friday joining on one day during the time of Ibn al-Zubayr."},"heading":{"title":"Two Festivals on One Day Hadith: Eid and Friday Together","description":"This Hadith speaks about a day when Friday and Eid al-Fitr came together during the time of Ibn al-Zubayr. Ata reports that Ibn al-Zubayr said, “Two festivals have come together on one day.” He combined them and offered two rak'ahs in the morning, then did not add anything to them until he offered the afternoon prayer. The Hadith about two festivals on one day is closely tied to the topic of Eid and Jumuah on the same day. The narration reports what happened and how the prayer was handled in that situation. It should be explained with care, without adding details that are not in the text. The main point is the joined occasion and the action reported."},"teachings":["The report calls Eid and Friday two festivals on one day.","Ibn al-Zubayr offered two rak'ahs in the morning.","The narration says he did not add anything until the afternoon prayer.","The Hadith records a specific practice in a specific situation."],"related_hadiths":[{"id":"1070","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1071","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1073","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Festivals on One Day","description":"$book_name$ $hadith_number$ - $chapter_name$. A report about Eid and Friday joining on one day during the time of Ibn al-Zubayr."},"heading":{"title":"Two Festivals on One Day Hadith: Eid and Friday Together","description":"This Hadith speaks about a day when Friday and Eid al-Fitr came together during the time of Ibn al-Zubayr. Ata reports that Ibn al-Zubayr said, “Two festivals have come together on one day.” He combined them and offered two rak'ahs in the morning, then did not add anything to them until he offered the afternoon prayer. The Hadith about two festivals on one day is closely tied to the topic of Eid and Jumuah on the same day. The narration reports what happened and how the prayer was handled in that situation. It should be explained with care, without adding details that are not in the text. The main point is the joined occasion and the action reported."},"teachings":["The report calls Eid and Friday two festivals on one day.","Ibn al-Zubayr offered two rak'ahs in the morning.","The narration says he did not add anything until the afternoon prayer.","The Hadith records a specific practice in a specific situation."],"related_hadiths":[{"id":"1070","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1071","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1073","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E36" s="4" t="n"/>
@@ -1293,7 +1297,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Suffices for Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith saying Eid may suffice for Friday, while the Prophet still offered Jumuah."},"heading":{"title":"Eid Prayer Suffices for Friday Hadith and Jumuah Choice","description":"This Hadith reports the Prophet (صلى الله عليه وسلم) saying that two festivals had come together on that day. He said that if anyone did not want to offer the Friday prayer, the Eid prayer was sufficient for him. He also said, “But we shall offer the Friday prayer.” The Hadith about Eid prayer sufficing for Friday is clear in both parts. It gives ease to those who do not want to attend Friday prayer in that situation, while also showing that Friday prayer was still offered by the Prophet (صلى الله عليه وسلم) and those with him. The wording should be kept balanced. It is not a general statement about every Friday. It is about the day when Eid and Friday came together."},"teachings":["The Hadith describes Eid and Friday as two festivals joined on one day.","It mentions ease for one who does not want to offer Friday prayer then.","The Prophet (صلى الله عليه وسلم) still said that they would offer the Friday prayer.","The text keeps both concession and continued Jumuah together."],"related_hadiths":[{"id":"1070","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1071","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Suffices for Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith saying Eid may suffice for Friday, while the Prophet still offered Jumuah."},"heading":{"title":"Eid Prayer Suffices for Friday Hadith and Jumuah Choice","description":"This Hadith reports the Prophet (صلى الله عليه وسلم) saying that two festivals had come together on that day. He said that if anyone did not want to offer the Friday prayer, the Eid prayer was sufficient for him. He also said, “But we shall offer the Friday prayer.” The Hadith about Eid prayer sufficing for Friday is clear in both parts. It gives ease to those who do not want to attend Friday prayer in that situation, while also showing that Friday prayer was still offered by the Prophet (صلى الله عليه وسلم) and those with him. The wording should be kept balanced. It is not a general statement about every Friday. It is about the day when Eid and Friday came together."},"teachings":["The Hadith describes Eid and Friday as two festivals joined on one day.","It mentions ease for one who does not want to offer Friday prayer then.","The Prophet (صلى الله عليه وسلم) still said that they would offer the Friday prayer.","The text keeps both concession and continued Jumuah together."],"related_hadiths":[{"id":"1070","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1071","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E37" s="4" t="n"/>
@@ -1316,7 +1320,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Friday Fajr Recitation Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith naming the surahs recited by the Prophet in Fajr prayer on Friday."},"heading":{"title":"Friday Fajr Recitation Hadith: Surah Sajdah and Al-Insan","description":"This Hadith tells us what the Messenger of Allah (صلى الله عليه وسلم) used to recite in the morning prayer on Friday. Ibn Abbas said that he recited Surah Tanzil al-Sajdah and Surah al-Dahr, also known from the wording as “Has there come upon man a time from the period.” The Hadith about Friday Fajr recitation is simple and focused. It does not discuss a sermon, the Friday prayer itself, or other parts of the day. It only mentions the Fajr prayer on Friday and the two surahs recited. This makes it useful for anyone searching for the Sunnah recitation in Friday morning prayer. The teaching is to notice and preserve the Prophet’s prayer practice."},"teachings":["The Prophet (صلى الله عليه وسلم) recited Surah al-Sajdah in Friday Fajr prayer.","He also recited Surah al-Dahr in the Friday morning prayer.","The Hadith is limited to the Fajr prayer on Friday.","Specific recitations from the Prophet’s practice were carefully remembered."],"related_hadiths":[{"id":"1075","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1067","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1080","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Friday Fajr Recitation Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith naming the surahs recited by the Prophet in Fajr prayer on Friday."},"heading":{"title":"Friday Fajr Recitation Hadith: Surah Sajdah and Al-Insan","description":"This Hadith tells us what the Messenger of Allah (صلى الله عليه وسلم) used to recite in the morning prayer on Friday. Ibn Abbas said that he recited Surah Tanzil al-Sajdah and Surah al-Dahr, also known from the wording as “Has there come upon man a time from the period.” The Hadith about Friday Fajr recitation is simple and focused. It does not discuss a sermon, the Friday prayer itself, or other parts of the day. It only mentions the Fajr prayer on Friday and the two surahs recited. This makes it useful for anyone searching for the Sunnah recitation in Friday morning prayer. The teaching is to notice and preserve the Prophet’s prayer practice."},"teachings":["The Prophet (صلى الله عليه وسلم) recited Surah al-Sajdah in Friday Fajr prayer.","He also recited Surah al-Dahr in the Friday morning prayer.","The Hadith is limited to the Fajr prayer on Friday.","Specific recitations from the Prophet’s practice were carefully remembered."],"related_hadiths":[{"id":"1075","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1067","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1080","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E38" s="4" t="n"/>
@@ -1339,7 +1343,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Silk Suit and Friday Dress","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith about a silk suit, Friday appearance, and not wearing what the Prophet forbade."},"heading":{"title":"Silk Suit Hadith and Friday Dress Guidance","description":"This Hadith reports that Umar saw a silken suit being sold near the mosque gate. He suggested that the Messenger of Allah (صلى الله عليه وسلم) buy it and wear it on Friday and when delegations came. The Messenger of Allah (صلى الله عليه وسلم) replied that one who has no share in the afterlife wears this suit. Later, similar suits came to the Messenger of Allah (صلى الله عليه وسلم), and he gave one to Umar. Umar asked about this because of the earlier statement. The Prophet (صلى الله عليه وسلم) clarified, “I did not give it to you that you should wear it.” Umar then gave it to his brother in Mecca, who was a disbeliever. The Hadith about silk and Friday dress shows the difference between owning, gifting, and wearing in this report."},"teachings":["Umar wanted the Prophet (صلى الله عليه وسلم) to dress well for Friday and delegations.","The Prophet (صلى الله عليه وسلم) objected to wearing that silken suit.","Giving the suit did not mean permission for Umar to wear it.","The Hadith shows the need to ask when an action seems unclear."],"related_hadiths":[{"id":"1077","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1078","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1079","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Silk Suit and Friday Dress","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith about a silk suit, Friday appearance, and not wearing what the Prophet forbade."},"heading":{"title":"Silk Suit Hadith and Friday Dress Guidance","description":"This Hadith reports that Umar saw a silken suit being sold near the mosque gate. He suggested that the Messenger of Allah (صلى الله عليه وسلم) buy it and wear it on Friday and when delegations came. The Messenger of Allah (صلى الله عليه وسلم) replied that one who has no share in the afterlife wears this suit. Later, similar suits came to the Messenger of Allah (صلى الله عليه وسلم), and he gave one to Umar. Umar asked about this because of the earlier statement. The Prophet (صلى الله عليه وسلم) clarified, “I did not give it to you that you should wear it.” Umar then gave it to his brother in Mecca, who was a disbeliever. The Hadith about silk and Friday dress shows the difference between owning, gifting, and wearing in this report."},"teachings":["Umar wanted the Prophet (صلى الله عليه وسلم) to dress well for Friday and delegations.","The Prophet (صلى الله عليه وسلم) objected to wearing that silken suit.","Giving the suit did not mean permission for Umar to wear it.","The Hadith shows the need to ask when an action seems unclear."],"related_hadiths":[{"id":"1077","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1078","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1079","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E39" s="4" t="n"/>
@@ -1362,7 +1366,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dressing for Eid and Delegations","description":"$book_name$ $hadith_number$ - $chapter_name$. A shorter version about Umar suggesting a silken suit for Eid and delegations."},"heading":{"title":"Dressing for Eid and Delegations Hadith with Silk Suit Context","description":"This Hadith is a shorter report connected to the fuller narration before it. Abdullah ibn Umar said that Umar ibn al-Khattab found a suit of silken cloth being sold in the market. He took it to the Messenger of Allah (صلى الله عليه وسلم) and suggested that he purchase it and beautify himself with it for Eid and for the arrival of delegations. The narrator then says the Hadith continued, and that the former version is more complete. The Hadith about dressing for Eid and delegations shows Umar’s suggestion about outward appearance on special public occasions. Since this report is brief and points back to the fuller version, the explanation should not go beyond what is included here."},"teachings":["Umar suggested dressing well for Eid and visiting delegations.","The garment mentioned was a silken suit.","This version is shorter and points to a fuller narration.","The Hadith shows how companions asked the Prophet (صلى الله عليه وسلم) about public appearance."],"related_hadiths":[{"id":"1076","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1078","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1079","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dressing for Eid and Delegations","description":"$book_name$ $hadith_number$ - $chapter_name$. A shorter version about Umar suggesting a silken suit for Eid and delegations."},"heading":{"title":"Dressing for Eid and Delegations Hadith with Silk Suit Context","description":"This Hadith is a shorter report connected to the fuller narration before it. Abdullah ibn Umar said that Umar ibn al-Khattab found a suit of silken cloth being sold in the market. He took it to the Messenger of Allah (صلى الله عليه وسلم) and suggested that he purchase it and beautify himself with it for Eid and for the arrival of delegations. The narrator then says the Hadith continued, and that the former version is more complete. The Hadith about dressing for Eid and delegations shows Umar’s suggestion about outward appearance on special public occasions. Since this report is brief and points back to the fuller version, the explanation should not go beyond what is included here."},"teachings":["Umar suggested dressing well for Eid and visiting delegations.","The garment mentioned was a silken suit.","This version is shorter and points to a fuller narration.","The Hadith shows how companions asked the Prophet (صلى الله عليه وسلم) about public appearance."],"related_hadiths":[{"id":"1076","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1078","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1079","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E40" s="4" t="n"/>
@@ -1385,7 +1389,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Garments for Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith encouraging two Friday garments for one who can afford them."},"heading":{"title":"Two Garments for Friday Prayer Hadith and Clean Appearance","description":"This Hadith gives simple guidance about Friday clothing. The Messenger of Allah (صلى الله عليه وسلم) said, in meaning, that there is no harm if a person who can provide them has two garments for Friday, other than the two garments used for daily work. The Hadith about two garments for Friday prayer is practical and easy to understand. It links Friday with a better set of clothing when a person has the means. The text does not say everyone must own extra garments, because the wording includes “if he can provide them.” It also does not speak about luxury. It points to having clothes for Friday separate from work clothes when possible."},"teachings":["A person who can afford it may keep separate garments for Friday.","The Hadith distinguishes Friday clothing from daily work clothing.","The wording considers ability and does not burden one who cannot provide them.","Friday prayer is treated as a time worth preparing for."],"related_hadiths":[{"id":"1076","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1077","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1079","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Garments for Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith encouraging two Friday garments for one who can afford them."},"heading":{"title":"Two Garments for Friday Prayer Hadith and Clean Appearance","description":"This Hadith gives simple guidance about Friday clothing. The Messenger of Allah (صلى الله عليه وسلم) said, in meaning, that there is no harm if a person who can provide them has two garments for Friday, other than the two garments used for daily work. The Hadith about two garments for Friday prayer is practical and easy to understand. It links Friday with a better set of clothing when a person has the means. The text does not say everyone must own extra garments, because the wording includes “if he can provide them.” It also does not speak about luxury. It points to having clothes for Friday separate from work clothes when possible."},"teachings":["A person who can afford it may keep separate garments for Friday.","The Hadith distinguishes Friday clothing from daily work clothing.","The wording considers ability and does not burden one who cannot provide them.","Friday prayer is treated as a time worth preparing for."],"related_hadiths":[{"id":"1076","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1077","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1079","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E41" s="4" t="n"/>
@@ -1408,7 +1412,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mosque Manners Before Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith prohibiting buying, selling, lost-item calls, poetry, and circles before Jumuah."},"heading":{"title":"Mosque Manners Hadith Before Friday Prayer","description":"This Hadith teaches several manners connected to the mosque and Friday prayer. The Messenger of Allah (صلى الله عليه وسلم) prohibited buying and selling in the mosque. He also prohibited announcing aloud about a lost thing and reciting a poem in it. The Hadith also mentions that he prohibited sitting in a circle in the mosque on Friday before the prayer. The Hadith about mosque manners before Friday prayer keeps the mosque focused on worship and order. It lists specific actions, so the explanation should stay close to those actions. The main message is not about rejecting all speech, but about avoiding the stated activities in the mosque, especially before Jumuah as mentioned."},"teachings":["Buying and selling in the mosque are prohibited in this Hadith.","Calling out about a lost item in the mosque is also prohibited.","The text mentions poetry recitation in the mosque as prohibited.","Sitting in circles before Friday prayer is specifically mentioned."],"related_hadiths":[{"id":"1078","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1080","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1067","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mosque Manners Before Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith prohibiting buying, selling, lost-item calls, poetry, and circles before Jumuah."},"heading":{"title":"Mosque Manners Hadith Before Friday Prayer","description":"This Hadith teaches several manners connected to the mosque and Friday prayer. The Messenger of Allah (صلى الله عليه وسلم) prohibited buying and selling in the mosque. He also prohibited announcing aloud about a lost thing and reciting a poem in it. The Hadith also mentions that he prohibited sitting in a circle in the mosque on Friday before the prayer. The Hadith about mosque manners before Friday prayer keeps the mosque focused on worship and order. It lists specific actions, so the explanation should stay close to those actions. The main message is not about rejecting all speech, but about avoiding the stated activities in the mosque, especially before Jumuah as mentioned."},"teachings":["Buying and selling in the mosque are prohibited in this Hadith.","Calling out about a lost item in the mosque is also prohibited.","The text mentions poetry recitation in the mosque as prohibited.","Sitting in circles before Friday prayer is specifically mentioned."],"related_hadiths":[{"id":"1078","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1080","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1067","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E42" s="4" t="n"/>
@@ -1431,7 +1435,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet Teaching Prayer from the Pulpit","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith showing the Prophet praying on the pulpit so people could follow and learn."},"heading":{"title":"Prophet Teaching Prayer from the Pulpit Hadith","description":"This Hadith describes the pulpit of the Messenger of Allah (صلى الله عليه وسلم) and how he used it to teach people. Sahl ibn Sa'd explained that the Prophet (صلى الله عليه وسلم) asked for a wooden pulpit to be made so he could sit on it when speaking to the people. He also saw the Messenger of Allah (صلى الله عليه وسلم) pray on it: saying “Allah is most great,” bowing while on it, then stepping back down to prostrate at the base of the pulpit. After finishing, the Prophet (صلى الله عليه وسلم) turned to the people and said he did this so they could follow him and learn his prayer. The Hadith about teaching prayer shows that the Prophet used visible action to help people learn clearly."},"teachings":["The pulpit was made so the Prophet (صلى الله عليه وسلم) could address people.","The Prophet (صلى الله عليه وسلم) prayed in a visible way so people could follow him.","He explained the purpose of the action after finishing the prayer.","Teaching can be done through clear example, not only words."],"related_hadiths":[{"id":"1079","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1074","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1075","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet Teaching Prayer from the Pulpit","description":"$book_name$ $hadith_number$ - $chapter_name$. A Hadith showing the Prophet praying on the pulpit so people could follow and learn."},"heading":{"title":"Prophet Teaching Prayer from the Pulpit Hadith","description":"This Hadith describes the pulpit of the Messenger of Allah (صلى الله عليه وسلم) and how he used it to teach people. Sahl ibn Sa'd explained that the Prophet (صلى الله عليه وسلم) asked for a wooden pulpit to be made so he could sit on it when speaking to the people. He also saw the Messenger of Allah (صلى الله عليه وسلم) pray on it: saying “Allah is most great,” bowing while on it, then stepping back down to prostrate at the base of the pulpit. After finishing, the Prophet (صلى الله عليه وسلم) turned to the people and said he did this so they could follow him and learn his prayer. The Hadith about teaching prayer shows that the Prophet used visible action to help people learn clearly."},"teachings":["The pulpit was made so the Prophet (صلى الله عليه وسلم) could address people.","The Prophet (صلى الله عليه وسلم) prayed in a visible way so people could follow him.","He explained the purpose of the action after finishing the prayer.","Teaching can be done through clear example, not only words."],"related_hadiths":[{"id":"1079","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1074","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1075","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E43" s="4" t="n"/>
@@ -1454,7 +1458,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Pulpit and Friday Khutbah","description":"$book_name$ $hadith_number$ - $chapter_name$. Tamim al-Dari offered to make a pulpit for the Prophet, showing care for the Friday khutbah setting."},"heading":{"title":"Hadith About the Prophet's Pulpit and the Friday Khutbah","description":"This Hadith focuses on the Prophet's pulpit, also called the minbar, and how it was made for him when he became heavier. Tamim al-Dari noticed the Prophet's need and asked if he could make a pulpit that would support him. The Prophet صلى الله عليه وسلم agreed, and a pulpit with two steps was made. The main lesson is simple: useful help in religious service has value. The Hadith does not give a long ruling; it only describes a real event around the Friday khutbah and the mosque setting. It also shows that the Companions paid attention to the Prophet's comfort and the needs of public teaching."},"teachings":["Useful support for Islamic teaching can be a good service.","The Companions cared about the Prophet's comfort during public worship.","The mosque setting was arranged in a practical way for the khutbah.","A simple tool like a pulpit can help people hear and benefit from reminders."],"related_hadiths":[{"id":"918","book_id":"1","label":"Sahih Bukhari"},{"id":"3584","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Pulpit and Friday Khutbah","description":"$book_name$ $hadith_number$ - $chapter_name$. Tamim al-Dari offered to make a pulpit for the Prophet, showing care for the Friday khutbah setting."},"heading":{"title":"Hadith About the Prophet's Pulpit and the Friday Khutbah","description":"This Hadith focuses on the Prophet's pulpit, also called the minbar, and how it was made for him when he became heavier. Tamim al-Dari noticed the Prophet's need and asked if he could make a pulpit that would support him. The Prophet صلى الله عليه وسلم agreed, and a pulpit with two steps was made. The main lesson is simple: useful help in religious service has value. The Hadith does not give a long ruling; it only describes a real event around the Friday khutbah and the mosque setting. It also shows that the Companions paid attention to the Prophet's comfort and the needs of public teaching."},"teachings":["Useful support for Islamic teaching can be a good service.","The Companions cared about the Prophet's comfort during public worship.","The mosque setting was arranged in a practical way for the khutbah.","A simple tool like a pulpit can help people hear and benefit from reminders."],"related_hadiths":[{"id":"918","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3584","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E44" s="4" t="n"/>
@@ -1477,7 +1481,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Space Around the Prophet's Pulpit","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes the small space between the Prophet's pulpit and mosque wall."},"heading":{"title":"Hadith About the Space Between the Minbar and Mosque Wall","description":"This Hadith gives a clear picture of the Prophet's mosque layout. Salamah b. al-Akwa' said the space between the pulpit of the Messenger of Allah صلى الله عليه وسلم and the wall was only wide enough for a goat to pass. The core topic is the Prophet's minbar and the physical space around it. The Hadith is brief, but it helps readers searching for a hadith about the Prophet's pulpit, mosque wall, or minbar location. It does not discuss a broad legal ruling in this text. It simply records a measured detail from the mosque, showing how closely the Companions observed and preserved even small matters linked to the Prophet's worship space."},"teachings":["The Companions preserved even small details about the Prophet's mosque.","The minbar had a known place near the wall of the mosque.","Simple descriptions in Hadith can help us picture early mosque life.","Careful observation was part of how the Sunnah was transmitted."],"related_hadiths":[{"id":"497","book_id":"1","label":"Sahih Bukhari"},{"id":"509a","book_id":"2","label":"Sahih Muslim"},{"id":"7334","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Space Around the Prophet's Pulpit","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes the small space between the Prophet's pulpit and mosque wall."},"heading":{"title":"Hadith About the Space Between the Minbar and Mosque Wall","description":"This Hadith gives a clear picture of the Prophet's mosque layout. Salamah b. al-Akwa' said the space between the pulpit of the Messenger of Allah صلى الله عليه وسلم and the wall was only wide enough for a goat to pass. The core topic is the Prophet's minbar and the physical space around it. The Hadith is brief, but it helps readers searching for a hadith about the Prophet's pulpit, mosque wall, or minbar location. It does not discuss a broad legal ruling in this text. It simply records a measured detail from the mosque, showing how closely the Companions observed and preserved even small matters linked to the Prophet's worship space."},"teachings":["The Companions preserved even small details about the Prophet's mosque.","The minbar had a known place near the wall of the mosque.","Simple descriptions in Hadith can help us picture early mosque life.","Careful observation was part of how the Sunnah was transmitted."],"related_hadiths":[{"id":"497","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"509a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"7334","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E45" s="4" t="n"/>
@@ -1500,7 +1504,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer at Meridian on Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions prayer at midday and the special exception stated for Friday."},"heading":{"title":"Hadith About Prayer at Meridian Except on Friday","description":"This Hadith speaks about offering prayer at the meridian, meaning the middle part of the day when the sun is at its height. The Prophet صلى الله عليه وسلم is reported to have disliked prayer at that time except on Friday. The narration also mentions that Hell-fire is kindled except on Friday. The text includes Abu Dawud's note about the chain, saying it is mursal and explaining the hearing issue between narrators. So the safest explanation stays close to the wording: this report connects Friday with a special exception from the usual disliked time. It is mainly searched as a hadith about prayer at meridian, zawal time prayer, and Friday prayer time."},"teachings":["The Hadith mentions a disliked time for prayer at midday, with Friday named as an exception.","Abu Dawud included a note about the chain, so the narration should be read with care.","Friday is treated distinctly in this report.","Hadith study includes both the wording and the condition of the narration."],"related_hadiths":[{"id":"831","book_id":"2","label":"Sahih Muslim"},{"id":"565","book_id":"3","label":"Sunan an-Nasai"},{"id":"1519","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer at Meridian on Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions prayer at midday and the special exception stated for Friday."},"heading":{"title":"Hadith About Prayer at Meridian Except on Friday","description":"This Hadith speaks about offering prayer at the meridian, meaning the middle part of the day when the sun is at its height. The Prophet صلى الله عليه وسلم is reported to have disliked prayer at that time except on Friday. The narration also mentions that Hell-fire is kindled except on Friday. The text includes Abu Dawud's note about the chain, saying it is mursal and explaining the hearing issue between narrators. So the safest explanation stays close to the wording: this report connects Friday with a special exception from the usual disliked time. It is mainly searched as a hadith about prayer at meridian, zawal time prayer, and Friday prayer time."},"teachings":["The Hadith mentions a disliked time for prayer at midday, with Friday named as an exception.","Abu Dawud included a note about the chain, so the narration should be read with care.","Friday is treated distinctly in this report.","Hadith study includes both the wording and the condition of the narration."],"related_hadiths":[{"id":"831","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"565","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"1519","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E46" s="4" t="n"/>
@@ -1523,7 +1527,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lunch and Siesta After Jumuah","description":"$book_name$ $hadith_number$ - $chapter_name$. Sahl reports that they took lunch or a siesta after the Friday prayer."},"heading":{"title":"Hadith About Lunch and Siesta After Jumuah Prayer","description":"This Hadith gives a simple glimpse into the Friday routine of the Companions. Sahl b. Sa'd said they would have a siesta or lunch after the Friday prayer. The core topic is Jumuah routine, especially what happened after the prayer. The text does not mention a command, a fixed meal, or a required nap. It only describes their practice. That makes the explanation balanced: the Hadith shows that after Jumuah, people returned to normal rest and food. Users often search for hadith about nap after Jumuah, lunch after Friday prayer, or siesta after Jumuah. This report is short, friendly, and easy to understand because it speaks about daily life around worship."},"teachings":["The Companions sometimes took lunch or rest after Jumuah.","Worship and normal daily needs can fit together in a simple routine.","The Hadith describes a practice without turning it into an absolute demand.","Friday prayer shaped the timing of their rest and meal."],"related_hadiths":[{"id":"941","book_id":"1","label":"Sahih Bukhari"},{"id":"940","book_id":"1","label":"Sahih Bukhari"},{"id":"6279","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lunch and Siesta After Jumuah","description":"$book_name$ $hadith_number$ - $chapter_name$. Sahl reports that they took lunch or a siesta after the Friday prayer."},"heading":{"title":"Hadith About Lunch and Siesta After Jumuah Prayer","description":"This Hadith gives a simple glimpse into the Friday routine of the Companions. Sahl b. Sa'd said they would have a siesta or lunch after the Friday prayer. The core topic is Jumuah routine, especially what happened after the prayer. The text does not mention a command, a fixed meal, or a required nap. It only describes their practice. That makes the explanation balanced: the Hadith shows that after Jumuah, people returned to normal rest and food. Users often search for hadith about nap after Jumuah, lunch after Friday prayer, or siesta after Jumuah. This report is short, friendly, and easy to understand because it speaks about daily life around worship."},"teachings":["The Companions sometimes took lunch or rest after Jumuah.","Worship and normal daily needs can fit together in a simple routine.","The Hadith describes a practice without turning it into an absolute demand.","Friday prayer shaped the timing of their rest and meal."],"related_hadiths":[{"id":"941","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"940","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6279","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E47" s="4" t="n"/>
@@ -1546,7 +1550,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Call to Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains the Friday adhan during the Prophet's time and the later call ordered by Uthman."},"heading":{"title":"Hadith About the Jumuah Adhan and Uthman's Added Call","description":"This Hadith is about the call to Friday prayer. Al-Sa'ib b. Yazid said that during the time of the Prophet صلى الله عليه وسلم, Abu Bakr, and Umar, the call to Jumuah was first made when the imam sat on the pulpit. Later, when the people became many during the time of Uthman, he ordered a third call, which was made on al-Zaura. The narration then says the practice continued. The key phrase users search for is Jumuah adhan hadith, along with first adhan on Friday and Uthman third adhan. The text is mainly a report of how the call was made and how it changed when the number of people increased."},"teachings":["The early Friday call was made when the imam sat on the pulpit.","The report mentions a later added call during Uthman's time because people increased.","The Hadith records both the Prophet's time and later practice.","Community size affected how people were alerted for Jumuah."],"related_hadiths":[{"id":"912","book_id":"1","label":"Sahih Bukhari"},{"id":"916","book_id":"1","label":"Sahih Bukhari"},{"id":"1393","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Call to Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains the Friday adhan during the Prophet's time and the later call ordered by Uthman."},"heading":{"title":"Hadith About the Jumuah Adhan and Uthman's Added Call","description":"This Hadith is about the call to Friday prayer. Al-Sa'ib b. Yazid said that during the time of the Prophet صلى الله عليه وسلم, Abu Bakr, and Umar, the call to Jumuah was first made when the imam sat on the pulpit. Later, when the people became many during the time of Uthman, he ordered a third call, which was made on al-Zaura. The narration then says the practice continued. The key phrase users search for is Jumuah adhan hadith, along with first adhan on Friday and Uthman third adhan. The text is mainly a report of how the call was made and how it changed when the number of people increased."},"teachings":["The early Friday call was made when the imam sat on the pulpit.","The report mentions a later added call during Uthman's time because people increased.","The Hadith records both the Prophet's time and later practice.","Community size affected how people were alerted for Jumuah."],"related_hadiths":[{"id":"912","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"916","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1393","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E48" s="4" t="n"/>
@@ -1569,7 +1573,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Adhan at the Mosque Gate","description":"$book_name$ $hadith_number$ - $chapter_name$. Sa'id reports the Friday adhan at the mosque gate when the Prophet sat on the pulpit."},"heading":{"title":"Hadith About the Friday Adhan at the Mosque Gate","description":"This Hadith continues the topic of the Jumuah adhan. Sa'id b. Yazid reported that the call to Friday prayer was made at the gate of the mosque in front of the Messenger of Allah صلى الله عليه وسلم when he sat on the pulpit. The report also mentions Abu Bakr and Umar, then points to the same meaning as the previous narration. The main search idea is adhan on Friday, especially the call when the imam sits on the minbar. The Hadith does not discuss every later practice in detail here; it records where and when the call was made. It is useful for readers who want a clear report about the Friday adhan at the mosque gate."},"teachings":["The Friday adhan was connected to the imam sitting on the pulpit.","The mosque gate is mentioned as the place of the call in this report.","The practice is linked to the time of the Prophet صلى الله عليه وسلم, Abu Bakr, and Umar.","The narration preserves a public detail of Jumuah worship."],"related_hadiths":[{"id":"912","book_id":"1","label":"Sahih Bukhari"},{"id":"916","book_id":"1","label":"Sahih Bukhari"},{"id":"1393","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Adhan at the Mosque Gate","description":"$book_name$ $hadith_number$ - $chapter_name$. Sa'id reports the Friday adhan at the mosque gate when the Prophet sat on the pulpit."},"heading":{"title":"Hadith About the Friday Adhan at the Mosque Gate","description":"This Hadith continues the topic of the Jumuah adhan. Sa'id b. Yazid reported that the call to Friday prayer was made at the gate of the mosque in front of the Messenger of Allah صلى الله عليه وسلم when he sat on the pulpit. The report also mentions Abu Bakr and Umar, then points to the same meaning as the previous narration. The main search idea is adhan on Friday, especially the call when the imam sits on the minbar. The Hadith does not discuss every later practice in detail here; it records where and when the call was made. It is useful for readers who want a clear report about the Friday adhan at the mosque gate."},"teachings":["The Friday adhan was connected to the imam sitting on the pulpit.","The mosque gate is mentioned as the place of the call in this report.","The practice is linked to the time of the Prophet صلى الله عليه وسلم, Abu Bakr, and Umar.","The narration preserves a public detail of Jumuah worship."],"related_hadiths":[{"id":"912","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"916","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1393","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E49" s="4" t="n"/>
@@ -1592,7 +1596,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bilal as the Prophet's Muadhdhin","description":"$book_name$ $hadith_number$ - $chapter_name$. Sa'ib reports that the Prophet had no other muadhdhin except Bilal."},"heading":{"title":"Hadith About Bilal as the Muadhdhin of the Prophet","description":"This Hadith focuses on Bilal and the role of the muadhdhin. Sa'ib said there was no other muadhdhin of the Messenger of Allah صلى الله عليه وسلم except Bilal, then the narrator reported the rest to the same effect. The wording is short, so the explanation should stay short in meaning but full in clarity. The Hadith points to Bilal's known place in making the call connected with the Prophet صلى الله عليه وسلم. It also sits within the broader topic of the Jumuah adhan, since the surrounding narrations speak about the Friday call. People searching for Bilal muadhdhin hadith, Prophet's muadhdhin, or Friday adhan Bilal can find this report useful."},"teachings":["Bilal is named as the muadhdhin of the Messenger of Allah صلى الله عليه وسلم in this report.","The Hadith connects the adhan with a known Companion.","Short narrations can still preserve an important public role.","The call to prayer had trusted people assigned to it."],"related_hadiths":[{"id":"912","book_id":"1","label":"Sahih Bukhari"},{"id":"916","book_id":"1","label":"Sahih Bukhari"},{"id":"1092b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bilal as the Prophet's Muadhdhin","description":"$book_name$ $hadith_number$ - $chapter_name$. Sa'ib reports that the Prophet had no other muadhdhin except Bilal."},"heading":{"title":"Hadith About Bilal as the Muadhdhin of the Prophet","description":"This Hadith focuses on Bilal and the role of the muadhdhin. Sa'ib said there was no other muadhdhin of the Messenger of Allah صلى الله عليه وسلم except Bilal, then the narrator reported the rest to the same effect. The wording is short, so the explanation should stay short in meaning but full in clarity. The Hadith points to Bilal's known place in making the call connected with the Prophet صلى الله عليه وسلم. It also sits within the broader topic of the Jumuah adhan, since the surrounding narrations speak about the Friday call. People searching for Bilal muadhdhin hadith, Prophet's muadhdhin, or Friday adhan Bilal can find this report useful."},"teachings":["Bilal is named as the muadhdhin of the Messenger of Allah صلى الله عليه وسلم in this report.","The Hadith connects the adhan with a known Companion.","Short narrations can still preserve an important public role.","The call to prayer had trusted people assigned to it."],"related_hadiths":[{"id":"912","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"916","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1092b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E50" s="4" t="n"/>
@@ -1615,7 +1619,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sitting for the Friday Khutbah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Mas'ud sat when he heard the Prophet say sit down, showing quick response to instruction."},"heading":{"title":"Hadith About Sitting When the Prophet Gave the Friday Khutbah","description":"This Hadith is about listening and responding during the Friday khutbah. Jabir reported that when the Messenger of Allah صلى الله عليه وسلم seated himself on the pulpit on Friday, he said, sit down. Ibn Mas'ud heard this while he was at the door of the mosque and sat down there. When the Prophet صلى الله عليه وسلم saw him, he called him forward. The report also includes Abu Dawud's note that the tradition is known as mursal. The key idea is khutbah etiquette and quick obedience to the Prophet's instruction. The Hadith does not say more than this event, so the explanation should not add extra claims. It simply shows a Companion responding right away to what he heard."},"teachings":["Ibn Mas'ud responded quickly when he heard the Prophet's instruction.","The Hadith highlights attentiveness during the Friday khutbah setting.","The Prophet صلى الله عليه وسلم noticed Ibn Mas'ud and called him closer.","Abu Dawud's note reminds readers to consider the chain of narration."],"related_hadiths":[{"id":"934","book_id":"1","label":"Sahih Bukhari"},{"id":"929","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sitting for the Friday Khutbah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Mas'ud sat when he heard the Prophet say sit down, showing quick response to instruction."},"heading":{"title":"Hadith About Sitting When the Prophet Gave the Friday Khutbah","description":"This Hadith is about listening and responding during the Friday khutbah. Jabir reported that when the Messenger of Allah صلى الله عليه وسلم seated himself on the pulpit on Friday, he said, sit down. Ibn Mas'ud heard this while he was at the door of the mosque and sat down there. When the Prophet صلى الله عليه وسلم saw him, he called him forward. The report also includes Abu Dawud's note that the tradition is known as mursal. The key idea is khutbah etiquette and quick obedience to the Prophet's instruction. The Hadith does not say more than this event, so the explanation should not add extra claims. It simply shows a Companion responding right away to what he heard."},"teachings":["Ibn Mas'ud responded quickly when he heard the Prophet's instruction.","The Hadith highlights attentiveness during the Friday khutbah setting.","The Prophet صلى الله عليه وسلم noticed Ibn Mas'ud and called him closer.","Abu Dawud's note reminds readers to consider the chain of narration."],"related_hadiths":[{"id":"934","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"929","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E51" s="4" t="n"/>
@@ -1638,7 +1642,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing During Friday Khutbah","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir b. Samurah strongly reports that the Prophet preached standing, sat, then stood again."},"heading":{"title":"Hadith About the Prophet Standing for the Friday Khutbah","description":"This Hadith gives a strong eyewitness statement about the Prophet's Friday khutbah. Jabir b. Samurah said the Messenger of Allah صلى الله عليه وسلم used to deliver the sermon standing, then sit down, then stand and preach standing again. He rejected the claim that the Prophet preached sitting and said he had prayed with him more than two thousand prayers. The core topic is khutbah standing, and the main search phrase is Prophet gave khutbah standing. The Hadith is focused on the posture and order of the sermon. It does not add details about the content of the khutbah here. It mainly protects an observed practice from being misreported."},"teachings":["The Prophet صلى الله عليه وسلم is described as giving the khutbah while standing.","The khutbah included sitting between two standing parts.","Jabir b. Samurah spoke from repeated personal observation.","The Hadith warns against wrongly reporting the Prophet's practice."],"related_hadiths":[{"id":"862b","book_id":"2","label":"Sahih Muslim"},{"id":"920","book_id":"1","label":"Sahih Bukhari"},{"id":"861","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing During Friday Khutbah","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir b. Samurah strongly reports that the Prophet preached standing, sat, then stood again."},"heading":{"title":"Hadith About the Prophet Standing for the Friday Khutbah","description":"This Hadith gives a strong eyewitness statement about the Prophet's Friday khutbah. Jabir b. Samurah said the Messenger of Allah صلى الله عليه وسلم used to deliver the sermon standing, then sit down, then stand and preach standing again. He rejected the claim that the Prophet preached sitting and said he had prayed with him more than two thousand prayers. The core topic is khutbah standing, and the main search phrase is Prophet gave khutbah standing. The Hadith is focused on the posture and order of the sermon. It does not add details about the content of the khutbah here. It mainly protects an observed practice from being misreported."},"teachings":["The Prophet صلى الله عليه وسلم is described as giving the khutbah while standing.","The khutbah included sitting between two standing parts.","Jabir b. Samurah spoke from repeated personal observation.","The Hadith warns against wrongly reporting the Prophet's practice."],"related_hadiths":[{"id":"862b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"920","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"861","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E52" s="4" t="n"/>
@@ -1661,7 +1665,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praise, Guidance, and Obedience","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet's address began with praise, seeking help, testimony, and a call to obey Allah and His Messenger."},"heading":{"title":"Hadith About the Prophet's Khutbah Opening and Obedience","description":"This Hadith records words the Messenger of Allah صلى الله عليه وسلم would say when addressing people. He began by praising Allah, seeking His help and pardon, and seeking refuge in Allah from the evils of the soul. He affirmed that whoever Allah guides cannot be led astray, and whoever He leaves astray has no guide. He then bore witness that there is no god but Allah and that Muhammad is His servant and Messenger. The address also says that the Prophet was sent with truth, giving good tidings and warning before the Hour. The core message is clear: guidance comes from Allah, testimony is central, and obeying Allah and His Messenger is the path of right conduct."},"teachings":["The khutbah began with praise of Allah and seeking His help.","The text points to Allah as the giver of guidance.","The testimony of faith is placed at the heart of the address.","Obedience to Allah and His Messenger is linked with right guidance."],"related_hadiths":[{"id":"1404","book_id":"3","label":"Sunan an-Nasai"},{"id":"3277","book_id":"3","label":"Sunan an-Nasai"},{"id":"3278","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praise, Guidance, and Obedience","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet's address began with praise, seeking help, testimony, and a call to obey Allah and His Messenger."},"heading":{"title":"Hadith About the Prophet's Khutbah Opening and Obedience","description":"This Hadith records words the Messenger of Allah صلى الله عليه وسلم would say when addressing people. He began by praising Allah, seeking His help and pardon, and seeking refuge in Allah from the evils of the soul. He affirmed that whoever Allah guides cannot be led astray, and whoever He leaves astray has no guide. He then bore witness that there is no god but Allah and that Muhammad is His servant and Messenger. The address also says that the Prophet was sent with truth, giving good tidings and warning before the Hour. The core message is clear: guidance comes from Allah, testimony is central, and obeying Allah and His Messenger is the path of right conduct."},"teachings":["The khutbah began with praise of Allah and seeking His help.","The text points to Allah as the giver of guidance.","The testimony of faith is placed at the heart of the address.","Obedience to Allah and His Messenger is linked with right guidance."],"related_hadiths":[{"id":"1404","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"3277","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"3278","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E53" s="4" t="n"/>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Obey Allah and His Messenger","description":"$book_name$ $hadith_number$ - $chapter_name$. This report adds a prayer to be among those who obey Allah, obey His Messenger, and avoid His anger."},"heading":{"title":"Hadith About Obeying Allah and His Messenger in the Friday Address","description":"This Hadith is a report from Ibn Shihab about the Friday address of the Messenger of Allah صلى الله عليه وسلم. It follows the same meaning as the previous address and adds that whoever disobeys Allah and His Apostle goes astray. It then includes a supplication asking Allah to make us among those who obey Him, obey His Messenger, follow what He likes, and stay away from His anger. The core topic is obedience. The main search phrase is obey Allah and His Messenger hadith. The wording is direct and personal. It turns the khutbah from a statement of truth into a prayer for practical faith, right action, and distance from what brings Allah's anger."},"teachings":["Disobedience to Allah and His Messenger is described as misguidance.","The report includes a prayer for obedience and Allah's pleasure.","Following what Allah likes is named as a desired path.","The address reminds people that they belong to Allah."],"related_hadiths":[{"id":"1404","book_id":"3","label":"Sunan an-Nasai"},{"id":"3277","book_id":"3","label":"Sunan an-Nasai"},{"id":"3278","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Obey Allah and His Messenger","description":"$book_name$ $hadith_number$ - $chapter_name$. This report adds a prayer to be among those who obey Allah, obey His Messenger, and avoid His anger."},"heading":{"title":"Hadith About Obeying Allah and His Messenger in the Friday Address","description":"This Hadith is a report from Ibn Shihab about the Friday address of the Messenger of Allah صلى الله عليه وسلم. It follows the same meaning as the previous address and adds that whoever disobeys Allah and His Apostle goes astray. It then includes a supplication asking Allah to make us among those who obey Him, obey His Messenger, follow what He likes, and stay away from His anger. The core topic is obedience. The main search phrase is obey Allah and His Messenger hadith. The wording is direct and personal. It turns the khutbah from a statement of truth into a prayer for practical faith, right action, and distance from what brings Allah's anger."},"teachings":["Disobedience to Allah and His Messenger is described as misguidance.","The report includes a prayer for obedience and Allah's pleasure.","Following what Allah likes is named as a desired path.","The address reminds people that they belong to Allah."],"related_hadiths":[{"id":"1404","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"3277","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"3278","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E54" s="4" t="n"/>
@@ -1707,7 +1711,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Careful Wording in a Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet corrected a speaker for poor wording about obedience and disobedience."},"heading":{"title":"Hadith About Careful Wording in Islamic Speech","description":"This Hadith teaches care in public speech. Adi b. Hatim said a speaker delivered a speech in the presence of the Prophet صلى الله عليه وسلم. The speaker said, anyone who obeys Allah and His Apostle, and one who disobeys them. The Prophet صلى الله عليه وسلم responded by telling him to go away, calling him a bad speaker. The Hadith is short, but the message is strong: words in a khutbah or public address matter. The text does not give a long explanation of the mistake, so we should not add more than needed. It shows that religious speech should be clear, respectful, and careful when speaking about Allah and His Messenger."},"teachings":["Public religious speech should be worded with care.","The Prophet صلى الله عليه وسلم corrected poor wording in a sermon setting.","Speaking about Allah and His Messenger requires respect and clarity.","A short mistake in wording can matter when addressing people."],"related_hadiths":[{"id":"870","book_id":"2","label":"Sahih Muslim"},{"id":"3281","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Careful Wording in a Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet corrected a speaker for poor wording about obedience and disobedience."},"heading":{"title":"Hadith About Careful Wording in Islamic Speech","description":"This Hadith teaches care in public speech. Adi b. Hatim said a speaker delivered a speech in the presence of the Prophet صلى الله عليه وسلم. The speaker said, anyone who obeys Allah and His Apostle, and one who disobeys them. The Prophet صلى الله عليه وسلم responded by telling him to go away, calling him a bad speaker. The Hadith is short, but the message is strong: words in a khutbah or public address matter. The text does not give a long explanation of the mistake, so we should not add more than needed. It shows that religious speech should be clear, respectful, and careful when speaking about Allah and His Messenger."},"teachings":["Public religious speech should be worded with care.","The Prophet صلى الله عليه وسلم corrected poor wording in a sermon setting.","Speaking about Allah and His Messenger requires respect and clarity.","A short mistake in wording can matter when addressing people."],"related_hadiths":[{"id":"870","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"3281","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E55" s="4" t="n"/>
@@ -1730,7 +1734,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Catching a Rak'ah in Salah","description":"$book_name$ $hadith_number$ - $chapter_name$. Catching one rak'ah with the imam is counted as reaching the prayer, showing the value of joining salah on time."},"heading":{"title":"Hadith About Catching One Rak'ah in Prayer","description":"This hadith about catching one rak'ah in prayer gives a clear and comforting rule for someone who reaches the congregation late. Abu Hurairah reports that the Messenger of Allah صلى الله عليه وسلم said that whoever obtains a rak'ah in the prayer along with the imam has obtained the whole prayer. The main point is not to be careless, but to understand the value of joining salah with the imam when one still catches a full rak'ah. For people searching for “hadith about catching one rakah” or “joining prayer late with imam,” this narration speaks directly to that case. It teaches that the rak'ah matters in reaching the prayer, and it keeps the focus on joining the imam properly."},"teachings":["Catching a rak'ah with the imam is counted as reaching the prayer.","A latecomer should still join the prayer when a rak'ah can be obtained.","The hadith highlights the value of praying with the imam.","The ruling is tied to obtaining a rak'ah, not merely arriving near the end."],"related_hadiths":[{"id":"608c","book_id":"2","label":"Sahih Muslim"},{"id":"580","book_id":"1","label":"Sahih Bukhari"},{"id":"556","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Catching a Rak'ah in Salah","description":"$book_name$ $hadith_number$ - $chapter_name$. Catching one rak'ah with the imam is counted as reaching the prayer, showing the value of joining salah on time."},"heading":{"title":"Hadith About Catching One Rak'ah in Prayer","description":"This hadith about catching one rak'ah in prayer gives a clear and comforting rule for someone who reaches the congregation late. Abu Hurairah reports that the Messenger of Allah صلى الله عليه وسلم said that whoever obtains a rak'ah in the prayer along with the imam has obtained the whole prayer. The main point is not to be careless, but to understand the value of joining salah with the imam when one still catches a full rak'ah. For people searching for “hadith about catching one rakah” or “joining prayer late with imam,” this narration speaks directly to that case. It teaches that the rak'ah matters in reaching the prayer, and it keeps the focus on joining the imam properly."},"teachings":["Catching a rak'ah with the imam is counted as reaching the prayer.","A latecomer should still join the prayer when a rak'ah can be obtained.","The hadith highlights the value of praying with the imam.","The ruling is tied to obtaining a rak'ah, not merely arriving near the end."],"related_hadiths":[{"id":"608c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"580","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"556","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E56" s="4" t="n"/>
@@ -1753,7 +1757,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surahs Recited on Eid and Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم recited Surah Al-A'la and Surah Al-Ghashiyah in Eid and Friday prayers, even when both met."},"heading":{"title":"Surahs Recited in Eid and Friday Prayer","description":"This hadith about Surahs recited in Eid prayer and Friday prayer shows a repeated practice of the Messenger of Allah صلى الله عليه وسلم. Al-Nu'man b. Bashir said that the Prophet صلى الله عليه وسلم used to recite Surah Al-A'la and Surah Al-Ghashiyah in the two Eid prayers and on Friday. The report also says that when Eid and Friday came on the same day, he recited those same two Surahs in both prayers. For anyone searching “what surah to recite in Eid prayer” or “Friday prayer recitation hadith,” this narration gives a direct answer from the text. It shows steadiness in recitation and keeps both Eid salah and Jumu'ah linked to Qur'an recitation known from the Prophet صلى الله عليه وسلم."},"teachings":["Surah Al-A'la and Surah Al-Ghashiyah were recited in Eid prayers.","The same two Surahs were also recited on Friday.","When Eid and Friday coincided, the Prophet صلى الله عليه وسلم recited them in both prayers.","The hadith shows a known pattern of Qur'an recitation in these prayers."],"related_hadiths":[{"id":"878a","book_id":"2","label":"Sahih Muslim"},{"id":"533","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"877a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surahs Recited on Eid and Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم recited Surah Al-A'la and Surah Al-Ghashiyah in Eid and Friday prayers, even when both met."},"heading":{"title":"Surahs Recited in Eid and Friday Prayer","description":"This hadith about Surahs recited in Eid prayer and Friday prayer shows a repeated practice of the Messenger of Allah صلى الله عليه وسلم. Al-Nu'man b. Bashir said that the Prophet صلى الله عليه وسلم used to recite Surah Al-A'la and Surah Al-Ghashiyah in the two Eid prayers and on Friday. The report also says that when Eid and Friday came on the same day, he recited those same two Surahs in both prayers. For anyone searching “what surah to recite in Eid prayer” or “Friday prayer recitation hadith,” this narration gives a direct answer from the text. It shows steadiness in recitation and keeps both Eid salah and Jumu'ah linked to Qur'an recitation known from the Prophet صلى الله عليه وسلم."},"teachings":["Surah Al-A'la and Surah Al-Ghashiyah were recited in Eid prayers.","The same two Surahs were also recited on Friday.","When Eid and Friday coincided, the Prophet صلى الله عليه وسلم recited them in both prayers.","The hadith shows a known pattern of Qur'an recitation in these prayers."],"related_hadiths":[{"id":"878a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"533","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"877a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E57" s="4" t="n"/>
@@ -1776,7 +1780,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah Al-Ghashiyah in Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet صلى الله عليه وسلم recited Surah Al-Ghashiyah after Surah Al-Jumu'ah in the Friday prayer."},"heading":{"title":"Hadith About Surah Al-Ghashiyah in Jumu'ah Prayer","description":"This hadith about Surah Al-Ghashiyah in Friday prayer focuses on what the Messenger of Allah صلى الله عليه وسلم recited after Surah Al-Jumu'ah. Al-Dahhak b. Qais asked al-Nu'man b. Bashir about the Prophet's recitation on Friday after Surah Al-Jumu'ah. The answer was simple: he used to recite Surah Al-Ghashiyah. This makes the hadith very useful for people searching “Surah Jumuah and Ghashiyah hadith” or “what to recite in Jumuah prayer.” The text does not give a long ruling or many options. It reports a specific recitation practice. The lesson is to value what is clearly narrated and to keep the Friday prayer connected to Qur'an recitation as taught in the hadith."},"teachings":["Surah Al-Ghashiyah was recited after Surah Al-Jumu'ah in Friday prayer.","The companion asked directly about the Prophet's Friday recitation.","The answer gives a clear report without extra detail.","The hadith points to care in preserving the Prophet's prayer practice."],"related_hadiths":[{"id":"878a","book_id":"2","label":"Sahih Muslim"},{"id":"877a","book_id":"2","label":"Sahih Muslim"},{"id":"533","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah Al-Ghashiyah in Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet صلى الله عليه وسلم recited Surah Al-Ghashiyah after Surah Al-Jumu'ah in the Friday prayer."},"heading":{"title":"Hadith About Surah Al-Ghashiyah in Jumu'ah Prayer","description":"This hadith about Surah Al-Ghashiyah in Friday prayer focuses on what the Messenger of Allah صلى الله عليه وسلم recited after Surah Al-Jumu'ah. Al-Dahhak b. Qais asked al-Nu'man b. Bashir about the Prophet's recitation on Friday after Surah Al-Jumu'ah. The answer was simple: he used to recite Surah Al-Ghashiyah. This makes the hadith very useful for people searching “Surah Jumuah and Ghashiyah hadith” or “what to recite in Jumuah prayer.” The text does not give a long ruling or many options. It reports a specific recitation practice. The lesson is to value what is clearly narrated and to keep the Friday prayer connected to Qur'an recitation as taught in the hadith."},"teachings":["Surah Al-Ghashiyah was recited after Surah Al-Jumu'ah in Friday prayer.","The companion asked directly about the Prophet's Friday recitation.","The answer gives a clear report without extra detail.","The hadith points to care in preserving the Prophet's prayer practice."],"related_hadiths":[{"id":"878a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"877a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"533","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E58" s="4" t="n"/>
@@ -1799,7 +1803,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah Al-Jumu'ah and Al-Munafiqun","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah heard the Prophet صلى الله عليه وسلم recite Surah Al-Jumu'ah and Surah Al-Munafiqun in the Friday prayer."},"heading":{"title":"Hadith About Surah Al-Jumu'ah and Al-Munafiqun in Friday Prayer","description":"This hadith about Surah Al-Jumu'ah and Surah Al-Munafiqun in Friday prayer gives another report of the Prophet's صلى الله عليه وسلم recitation. Ibn Abi Rafi' said that Abu Hurairah led the Friday prayer and recited Surah Al-Jumu'ah and then “When the hypocrites come to you,” meaning Surah Al-Munafiqun, in the last rak'ah. When he was told that Ali used to recite those two Surahs in Kufah, Abu Hurairah answered that he heard the Messenger of Allah صلى الله عليه وسلم recite them on Friday. For people searching “Surah Jumuah and Munafiqun hadith,” this narration is direct. It shows that Abu Hurairah based his recitation on what he personally heard from the Prophet صلى الله عليه وسلم."},"teachings":["Surah Al-Jumu'ah and Surah Al-Munafiqun were recited in Friday prayer.","Abu Hurairah linked this practice to what he heard from the Prophet صلى الله عليه وسلم.","The report shows care in following known Prophetic recitation.","It also shows that companions recognized shared practices in different places."],"related_hadiths":[{"id":"877a","book_id":"2","label":"Sahih Muslim"},{"id":"879a","book_id":"2","label":"Sahih Muslim"},{"id":"878a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah Al-Jumu'ah and Al-Munafiqun","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah heard the Prophet صلى الله عليه وسلم recite Surah Al-Jumu'ah and Surah Al-Munafiqun in the Friday prayer."},"heading":{"title":"Hadith About Surah Al-Jumu'ah and Al-Munafiqun in Friday Prayer","description":"This hadith about Surah Al-Jumu'ah and Surah Al-Munafiqun in Friday prayer gives another report of the Prophet's صلى الله عليه وسلم recitation. Ibn Abi Rafi' said that Abu Hurairah led the Friday prayer and recited Surah Al-Jumu'ah and then “When the hypocrites come to you,” meaning Surah Al-Munafiqun, in the last rak'ah. When he was told that Ali used to recite those two Surahs in Kufah, Abu Hurairah answered that he heard the Messenger of Allah صلى الله عليه وسلم recite them on Friday. For people searching “Surah Jumuah and Munafiqun hadith,” this narration is direct. It shows that Abu Hurairah based his recitation on what he personally heard from the Prophet صلى الله عليه وسلم."},"teachings":["Surah Al-Jumu'ah and Surah Al-Munafiqun were recited in Friday prayer.","Abu Hurairah linked this practice to what he heard from the Prophet صلى الله عليه وسلم.","The report shows care in following known Prophetic recitation.","It also shows that companions recognized shared practices in different places."],"related_hadiths":[{"id":"877a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"879a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"878a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E59" s="4" t="n"/>
@@ -1822,7 +1826,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Al-A'la and Al-Ghashiyah in Jumu'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم recited Surah Al-A'la and Surah Al-Ghashiyah in the Friday prayer as part of his practice."},"heading":{"title":"Hadith About Al-A'la and Al-Ghashiyah in Friday Prayer","description":"This hadith about Al-A'la and Al-Ghashiyah in Friday prayer is short, but it carries a clear practice. Samurah ibn Jundub narrated that the Messenger of Allah صلى الله عليه وسلم used to recite “Glorify the name of your most high Lord,” which is Surah Al-A'la, and “Has the story of the overwhelming event reached you?” which is Surah Al-Ghashiyah, in the Friday prayer. For readers searching “Friday prayer recitation hadith” or “Surah Ala and Ghashiyah Jumuah,” this report gives a simple answer. It does not add details about a one-time event. It says he used to recite these Surahs, showing a repeated practice in Jumu'ah salah."},"teachings":["Surah Al-A'la was recited in the Friday prayer.","Surah Al-Ghashiyah was also recited in the Friday prayer.","The wording points to a repeated practice of the Prophet صلى الله عليه وسلم.","The hadith keeps the focus on Qur'an recitation within Jumu'ah salah."],"related_hadiths":[{"id":"878a","book_id":"2","label":"Sahih Muslim"},{"id":"533","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"879a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Al-A'la and Al-Ghashiyah in Jumu'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم recited Surah Al-A'la and Surah Al-Ghashiyah in the Friday prayer as part of his practice."},"heading":{"title":"Hadith About Al-A'la and Al-Ghashiyah in Friday Prayer","description":"This hadith about Al-A'la and Al-Ghashiyah in Friday prayer is short, but it carries a clear practice. Samurah ibn Jundub narrated that the Messenger of Allah صلى الله عليه وسلم used to recite “Glorify the name of your most high Lord,” which is Surah Al-A'la, and “Has the story of the overwhelming event reached you?” which is Surah Al-Ghashiyah, in the Friday prayer. For readers searching “Friday prayer recitation hadith” or “Surah Ala and Ghashiyah Jumuah,” this report gives a simple answer. It does not add details about a one-time event. It says he used to recite these Surahs, showing a repeated practice in Jumu'ah salah."},"teachings":["Surah Al-A'la was recited in the Friday prayer.","Surah Al-Ghashiyah was also recited in the Friday prayer.","The wording points to a repeated practice of the Prophet صلى الله عليه وسلم.","The hadith keeps the focus on Qur'an recitation within Jumu'ah salah."],"related_hadiths":[{"id":"878a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"533","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"879a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E60" s="4" t="n"/>
@@ -1845,7 +1849,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Following the Imam from Behind a Barrier","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed in his apartment while people followed him from behind, showing valid following of the imam."},"heading":{"title":"Hadith About Following the Imam in Congregational Prayer","description":"This hadith about following the imam in congregational prayer tells us that the Messenger of Allah صلى الله عليه وسلم prayed in his apartment while people followed him from behind the apartment. The text is brief, so we should keep the meaning brief too. It shows people taking him as imam even though he was inside his room and they were behind it. For someone searching “following imam behind barrier hadith” or “praying behind imam from another place,” this narration is linked to that topic. The hadith does not mention a full legal discussion, distance, or modern building layouts. It simply reports that the Prophet صلى الله عليه وسلم prayed in his apartment and the people followed him from behind it."},"teachings":["People followed the Prophet صلى الله عليه وسلم in prayer while he was in his apartment.","The report shows congregational following in the situation described.","The text does not add details beyond this specific setting.","The hadith teaches careful attention to how the imam is followed."],"related_hadiths":[{"id":"419a","book_id":"2","label":"Sahih Muslim"},{"id":"688","book_id":"1","label":"Sahih Bukhari"},{"id":"424","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Following the Imam from Behind a Barrier","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed in his apartment while people followed him from behind, showing valid following of the imam."},"heading":{"title":"Hadith About Following the Imam in Congregational Prayer","description":"This hadith about following the imam in congregational prayer tells us that the Messenger of Allah صلى الله عليه وسلم prayed in his apartment while people followed him from behind the apartment. The text is brief, so we should keep the meaning brief too. It shows people taking him as imam even though he was inside his room and they were behind it. For someone searching “following imam behind barrier hadith” or “praying behind imam from another place,” this narration is linked to that topic. The hadith does not mention a full legal discussion, distance, or modern building layouts. It simply reports that the Prophet صلى الله عليه وسلم prayed in his apartment and the people followed him from behind it."},"teachings":["People followed the Prophet صلى الله عليه وسلم in prayer while he was in his apartment.","The report shows congregational following in the situation described.","The text does not add details beyond this specific setting.","The hadith teaches careful attention to how the imam is followed."],"related_hadiths":[{"id":"419a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"688","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"424","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E61" s="4" t="n"/>
@@ -1868,7 +1872,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs After Friday Prayer at Home","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar prayed two rak'ahs at home after Friday prayer and linked this practice to the Prophet صلى الله عليه وسلم."},"heading":{"title":"Hadith About Two Rak'ahs After Jumu'ah at Home","description":"This hadith about two rak'ahs after Jumu'ah at home shows how Ibn Umar understood and practiced the Sunnah. Nafi' said Ibn Umar saw a man praying two rak'ahs in the same place after the Friday prayer. Ibn Umar pushed him and asked if he was making Friday four rak'ahs. The narration then says Ibn Umar used to pray two rak'ahs in his house after Friday prayer and said that the Messenger of Allah صلى الله عليه وسلم did this. For people searching “two rakah after Jumuah at home hadith,” this report is direct. It also shows that Ibn Umar did not like joining those two rak'ahs to the Friday prayer in the same place in that way."},"teachings":["Ibn Umar prayed two rak'ahs at home after Friday prayer.","He linked this practice to the Messenger of Allah صلى الله عليه وسلم.","He objected to making it look like Friday prayer was four rak'ahs.","The hadith points to separating the obligatory Jumu'ah from prayer after it."],"related_hadiths":[{"id":"882a","book_id":"2","label":"Sahih Muslim"},{"id":"937","book_id":"1","label":"Sahih Bukhari"},{"id":"522","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs After Friday Prayer at Home","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar prayed two rak'ahs at home after Friday prayer and linked this practice to the Prophet صلى الله عليه وسلم."},"heading":{"title":"Hadith About Two Rak'ahs After Jumu'ah at Home","description":"This hadith about two rak'ahs after Jumu'ah at home shows how Ibn Umar understood and practiced the Sunnah. Nafi' said Ibn Umar saw a man praying two rak'ahs in the same place after the Friday prayer. Ibn Umar pushed him and asked if he was making Friday four rak'ahs. The narration then says Ibn Umar used to pray two rak'ahs in his house after Friday prayer and said that the Messenger of Allah صلى الله عليه وسلم did this. For people searching “two rakah after Jumuah at home hadith,” this report is direct. It also shows that Ibn Umar did not like joining those two rak'ahs to the Friday prayer in the same place in that way."},"teachings":["Ibn Umar prayed two rak'ahs at home after Friday prayer.","He linked this practice to the Messenger of Allah صلى الله عليه وسلم.","He objected to making it look like Friday prayer was four rak'ahs.","The hadith points to separating the obligatory Jumu'ah from prayer after it."],"related_hadiths":[{"id":"882a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"937","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"522","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E62" s="4" t="n"/>
@@ -1891,7 +1895,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Before and After Jumu'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar lengthened prayer before Jumu'ah and prayed two rak'ahs at home after it, reporting the Prophet's practice."},"heading":{"title":"Hadith About Prayer Before and After Friday Prayer","description":"This hadith about prayer before and after Friday prayer reports what Ibn Umar used to do and what he said about the Prophet صلى الله عليه وسلم. Nafi' said Ibn Umar would lengthen his prayer before Jumu'ah and then offer two rak'ahs after it in his house. He would say that the Messenger of Allah صلى الله عليه وسلم used to do that. For people searching “prayer before Jumuah hadith” or “two rakah after Friday prayer at home,” this narration joins both points in one report. The text does not explain how long the prayer before Jumu'ah was or give a fixed number for it here. It simply reports lengthening prayer before Friday and praying two rak'ahs at home afterward."},"teachings":["Ibn Umar lengthened prayer before the Friday prayer.","He prayed two rak'ahs at home after Jumu'ah.","He reported that the Prophet صلى الله عليه وسلم used to do that.","The hadith keeps the before and after practices distinct."],"related_hadiths":[{"id":"882a","book_id":"2","label":"Sahih Muslim"},{"id":"937","book_id":"1","label":"Sahih Bukhari"},{"id":"522","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Before and After Jumu'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar lengthened prayer before Jumu'ah and prayed two rak'ahs at home after it, reporting the Prophet's practice."},"heading":{"title":"Hadith About Prayer Before and After Friday Prayer","description":"This hadith about prayer before and after Friday prayer reports what Ibn Umar used to do and what he said about the Prophet صلى الله عليه وسلم. Nafi' said Ibn Umar would lengthen his prayer before Jumu'ah and then offer two rak'ahs after it in his house. He would say that the Messenger of Allah صلى الله عليه وسلم used to do that. For people searching “prayer before Jumuah hadith” or “two rakah after Friday prayer at home,” this narration joins both points in one report. The text does not explain how long the prayer before Jumu'ah was or give a fixed number for it here. It simply reports lengthening prayer before Friday and praying two rak'ahs at home afterward."},"teachings":["Ibn Umar lengthened prayer before the Friday prayer.","He prayed two rak'ahs at home after Jumu'ah.","He reported that the Prophet صلى الله عليه وسلم used to do that.","The hadith keeps the before and after practices distinct."],"related_hadiths":[{"id":"882a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"937","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"522","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E63" s="4" t="n"/>
@@ -1914,7 +1918,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Separating One Prayer from Another","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches not to connect one prayer to another until speaking or moving out after Friday prayer."},"heading":{"title":"Hadith About Not Joining One Prayer to Another","description":"This hadith about not joining one prayer to another gives clear guidance after Friday prayer. Al-Sa'ib b. Yazid said that after praying Jumu'ah with Mu'awiyah, he stood in the same place and prayed. Mu'awiyah later told him not to do that again. He said that after Friday prayer, one should not connect another prayer to it until speaking or going out, because the Prophet صلى الله عليه وسلم commanded that one prayer should not be joined to another until a person speaks or goes out. For people searching “do not join one prayer to another hadith” or “change place after fard prayer hadith,” this narration is directly about separation between prayers."},"teachings":["A prayer should not be connected to another without a break described in the hadith.","Speaking or going out is mentioned as a way to separate prayers.","Mu'awiyah corrected the action by citing the Prophet's صلى الله عليه وسلم command.","The teaching is given in the setting after Friday prayer."],"related_hadiths":[{"id":"883a","book_id":"2","label":"Sahih Muslim"},{"id":"881a","book_id":"2","label":"Sahih Muslim"},{"id":"882a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Separating One Prayer from Another","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches not to connect one prayer to another until speaking or moving out after Friday prayer."},"heading":{"title":"Hadith About Not Joining One Prayer to Another","description":"This hadith about not joining one prayer to another gives clear guidance after Friday prayer. Al-Sa'ib b. Yazid said that after praying Jumu'ah with Mu'awiyah, he stood in the same place and prayed. Mu'awiyah later told him not to do that again. He said that after Friday prayer, one should not connect another prayer to it until speaking or going out, because the Prophet صلى الله عليه وسلم commanded that one prayer should not be joined to another until a person speaks or goes out. For people searching “do not join one prayer to another hadith” or “change place after fard prayer hadith,” this narration is directly about separation between prayers."},"teachings":["A prayer should not be connected to another without a break described in the hadith.","Speaking or going out is mentioned as a way to separate prayers.","Mu'awiyah corrected the action by citing the Prophet's صلى الله عليه وسلم command.","The teaching is given in the setting after Friday prayer."],"related_hadiths":[{"id":"883a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"881a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"882a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E64" s="4" t="n"/>
@@ -1937,7 +1941,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Umar's Prayer After Jumu'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar prayed after Jumu'ah differently in Mecca and Medina, and mentioned the Prophet's practice."},"heading":{"title":"Hadith About Prayer After Jumu'ah in Mecca and Medina","description":"This hadith about prayer after Jumu'ah describes what Ibn Umar did in two places. Ata said that when Ibn Umar prayed Friday prayer in Mecca, he would move forward and pray two rak'ahs, then move forward and pray four rak'ahs. When he was in Medina, he prayed Jumu'ah, returned to his house, and prayed two rak'ahs, not praying them in the mosque. When this was mentioned to him, he replied that the Messenger of Allah صلى الله عليه وسلم used to do it. For people searching “Ibn Umar prayer after Jumuah” or “two and four rakah after Friday prayer,” this report shows the practice described in the text without adding more than it says."},"teachings":["Ibn Umar did not keep the same pattern in every place mentioned.","In Medina, he prayed two rak'ahs at home after Jumu'ah.","In Mecca, he moved and prayed two, then moved and prayed four.","He connected the practice to the Messenger of Allah صلى الله عليه وسلم."],"related_hadiths":[{"id":"882a","book_id":"2","label":"Sahih Muslim"},{"id":"881a","book_id":"2","label":"Sahih Muslim"},{"id":"937","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Umar's Prayer After Jumu'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar prayed after Jumu'ah differently in Mecca and Medina, and mentioned the Prophet's practice."},"heading":{"title":"Hadith About Prayer After Jumu'ah in Mecca and Medina","description":"This hadith about prayer after Jumu'ah describes what Ibn Umar did in two places. Ata said that when Ibn Umar prayed Friday prayer in Mecca, he would move forward and pray two rak'ahs, then move forward and pray four rak'ahs. When he was in Medina, he prayed Jumu'ah, returned to his house, and prayed two rak'ahs, not praying them in the mosque. When this was mentioned to him, he replied that the Messenger of Allah صلى الله عليه وسلم used to do it. For people searching “Ibn Umar prayer after Jumuah” or “two and four rakah after Friday prayer,” this report shows the practice described in the text without adding more than it says."},"teachings":["Ibn Umar did not keep the same pattern in every place mentioned.","In Medina, he prayed two rak'ahs at home after Jumu'ah.","In Mecca, he moved and prayed two, then moved and prayed four.","He connected the practice to the Messenger of Allah صلى الله عليه وسلم."],"related_hadiths":[{"id":"882a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"881a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"937","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E65" s="4" t="n"/>
@@ -1960,7 +1964,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Rak'ahs After Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم instructed anyone praying after Jumu'ah to pray four rak'ahs, with mention of completing them at home."},"heading":{"title":"Hadith About Four Rak'ahs After Jumu'ah Prayer","description":"This hadith about four rak'ahs after Jumu'ah prayer gives a direct instruction from the Messenger of Allah صلى الله عليه وسلم. Abu Hurairah reported that if anyone prays after Friday prayer, he should pray four rak'ahs. Another wording says: when you have offered the Friday prayer, pray four rak'ahs after it. The report then adds that if someone prayed two rak'ahs in the mosque and then came home, he should pray two more. For people searching “four rakah after Jumuah hadith” or “Sunnah after Friday prayer,” this narration answers the question from the wording itself. It focuses on the number four and also mentions completing the count between mosque and home."},"teachings":["The hadith instructs four rak'ahs after Friday prayer for one who prays after it.","Another wording gives the same meaning after Jumu'ah is offered.","Two rak'ahs in the mosque may be followed by two more at home in the report.","The text centers on prayer after Jumu'ah, not before it."],"related_hadiths":[{"id":"881a","book_id":"2","label":"Sahih Muslim"},{"id":"881b","book_id":"2","label":"Sahih Muslim"},{"id":"523","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Rak'ahs After Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم instructed anyone praying after Jumu'ah to pray four rak'ahs, with mention of completing them at home."},"heading":{"title":"Hadith About Four Rak'ahs After Jumu'ah Prayer","description":"This hadith about four rak'ahs after Jumu'ah prayer gives a direct instruction from the Messenger of Allah صلى الله عليه وسلم. Abu Hurairah reported that if anyone prays after Friday prayer, he should pray four rak'ahs. Another wording says: when you have offered the Friday prayer, pray four rak'ahs after it. The report then adds that if someone prayed two rak'ahs in the mosque and then came home, he should pray two more. For people searching “four rakah after Jumuah hadith” or “Sunnah after Friday prayer,” this narration answers the question from the wording itself. It focuses on the number four and also mentions completing the count between mosque and home."},"teachings":["The hadith instructs four rak'ahs after Friday prayer for one who prays after it.","Another wording gives the same meaning after Jumu'ah is offered.","Two rak'ahs in the mosque may be followed by two more at home in the report.","The text centers on prayer after Jumu'ah, not before it."],"related_hadiths":[{"id":"881a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"881b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"523","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E66" s="4" t="n"/>
@@ -1983,7 +1987,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs at Home After Jumu'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used to pray two rak'ahs in his house after the Friday prayer, showing a home Sunnah practice."},"heading":{"title":"Hadith About the Prophet Praying Two Rak'ahs After Friday Prayer","description":"This hadith about the Prophet صلى الله عليه وسلم praying two rak'ahs after Friday prayer is simple and clear. Abdullah ibn Umar narrated that the Messenger of Allah صلى الله عليه وسلم used to pray two rak'ahs in his house after the Friday prayer. Abu Dawud also notes that a similar report came from Abdullah b. Dinar from Ibn Umar. For people searching “two rakah after Jumuah hadith” or “Prophet prayed Sunnah after Friday at home,” this narration gives the main wording they need. The hadith does not say these two rak'ahs were prayed in the mosque. It says they were prayed in his house, so the explanation should stay with that point."},"teachings":["The Prophet صلى الله عليه وسلم prayed two rak'ahs after Friday prayer.","The report states that he prayed them in his house.","Ibn Umar is the narrator of this practice.","The hadith supports keeping the after-Jumu'ah prayer distinct from the Friday prayer itself."],"related_hadiths":[{"id":"882a","book_id":"2","label":"Sahih Muslim"},{"id":"937","book_id":"1","label":"Sahih Bukhari"},{"id":"522","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs at Home After Jumu'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used to pray two rak'ahs in his house after the Friday prayer, showing a home Sunnah practice."},"heading":{"title":"Hadith About the Prophet Praying Two Rak'ahs After Friday Prayer","description":"This hadith about the Prophet صلى الله عليه وسلم praying two rak'ahs after Friday prayer is simple and clear. Abdullah ibn Umar narrated that the Messenger of Allah صلى الله عليه وسلم used to pray two rak'ahs in his house after the Friday prayer. Abu Dawud also notes that a similar report came from Abdullah b. Dinar from Ibn Umar. For people searching “two rakah after Jumuah hadith” or “Prophet prayed Sunnah after Friday at home,” this narration gives the main wording they need. The hadith does not say these two rak'ahs were prayed in the mosque. It says they were prayed in his house, so the explanation should stay with that point."},"teachings":["The Prophet صلى الله عليه وسلم prayed two rak'ahs after Friday prayer.","The report states that he prayed them in his house.","Ibn Umar is the narrator of this practice.","The hadith supports keeping the after-Jumu'ah prayer distinct from the Friday prayer itself."],"related_hadiths":[{"id":"882a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"937","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"522","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E67" s="4" t="n"/>
@@ -2006,7 +2010,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Moving Place After Jumu'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar moved from his Friday prayer place before praying two and then four rak'ahs after Jumu'ah."},"heading":{"title":"Hadith About Moving Before Praying After Friday Prayer","description":"This hadith about moving place after Jumu'ah reports what Ata saw from Ibn Umar many times. Ibn Umar would move a little away from the place where he had offered the Friday prayer, then pray two rak'ahs. After that, he would walk farther away and pray four rak'ahs. When Ibn Jurayj asked Ata how often he saw Ibn Umar do this, Ata said he saw it many times. For people searching “move place after Jumuah prayer hadith” or “Ibn Umar two and four rakah after Friday,” this narration is focused on action after the Friday prayer. It shows movement before the extra prayers and mentions both two rak'ahs and four rak'ahs."},"teachings":["Ibn Umar moved from his Friday prayer spot before praying after it.","He prayed two rak'ahs after moving a little.","He then moved farther and prayed four rak'ahs.","Ata reported seeing Ibn Umar do this many times."],"related_hadiths":[{"id":"883a","book_id":"2","label":"Sahih Muslim"},{"id":"882a","book_id":"2","label":"Sahih Muslim"},{"id":"881a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Moving Place After Jumu'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar moved from his Friday prayer place before praying two and then four rak'ahs after Jumu'ah."},"heading":{"title":"Hadith About Moving Before Praying After Friday Prayer","description":"This hadith about moving place after Jumu'ah reports what Ata saw from Ibn Umar many times. Ibn Umar would move a little away from the place where he had offered the Friday prayer, then pray two rak'ahs. After that, he would walk farther away and pray four rak'ahs. When Ibn Jurayj asked Ata how often he saw Ibn Umar do this, Ata said he saw it many times. For people searching “move place after Jumuah prayer hadith” or “Ibn Umar two and four rakah after Friday,” this narration is focused on action after the Friday prayer. It shows movement before the extra prayers and mentions both two rak'ahs and four rak'ahs."},"teachings":["Ibn Umar moved from his Friday prayer spot before praying after it.","He prayed two rak'ahs after moving a little.","He then moved farther and prayed four rak'ahs.","Ata reported seeing Ibn Umar do this many times."],"related_hadiths":[{"id":"883a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"882a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"881a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E68" s="4" t="n"/>
@@ -2029,7 +2033,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid al-Fitr and Eid al-Adha","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah replaced the two old days of games with Eid al-Adha and Eid al-Fitr, giving Muslims better days."},"heading":{"title":"Hadith About Eid al-Fitr and Eid al-Adha Replacing Old Days","description":"This hadith about Eid al-Fitr and Eid al-Adha shows how the two Muslim festival days were named in the text. Anas ibn Malik narrated that when the Messenger of Allah صلى الله عليه وسلم came to Medina, the people had two days on which they played games. He asked what those days were, and they said they used to play on them in the pre-Islamic period. The Prophet صلى الله عليه وسلم then said that Allah had substituted for them something better: the day of sacrifice and the day of breaking the fast. For people searching “Allah replaced two days with Eid hadith” or “Eid al-Fitr and Eid al-Adha hadith,” this narration gives the main wording."},"teachings":["Allah replaced the two old days with Eid al-Adha and Eid al-Fitr.","The hadith names the day of sacrifice and the day of breaking the fast.","The Prophet صلى الله عليه وسلم asked about the meaning of the two earlier days.","The report connects Muslim celebration to the two Eid days mentioned."],"related_hadiths":[{"id":"1556","book_id":"3","label":"Sunan an-Nasai"},{"id":"964","book_id":"1","label":"Sahih Bukhari"},{"id":"979","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid al-Fitr and Eid al-Adha","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah replaced the two old days of games with Eid al-Adha and Eid al-Fitr, giving Muslims better days."},"heading":{"title":"Hadith About Eid al-Fitr and Eid al-Adha Replacing Old Days","description":"This hadith about Eid al-Fitr and Eid al-Adha shows how the two Muslim festival days were named in the text. Anas ibn Malik narrated that when the Messenger of Allah صلى الله عليه وسلم came to Medina, the people had two days on which they played games. He asked what those days were, and they said they used to play on them in the pre-Islamic period. The Prophet صلى الله عليه وسلم then said that Allah had substituted for them something better: the day of sacrifice and the day of breaking the fast. For people searching “Allah replaced two days with Eid hadith” or “Eid al-Fitr and Eid al-Adha hadith,” this narration gives the main wording."},"teachings":["Allah replaced the two old days with Eid al-Adha and Eid al-Fitr.","The hadith names the day of sacrifice and the day of breaking the fast.","The Prophet صلى الله عليه وسلم asked about the meaning of the two earlier days.","The report connects Muslim celebration to the two Eid days mentioned."],"related_hadiths":[{"id":"1556","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"964","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"979","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E69" s="4" t="n"/>
@@ -2052,7 +2056,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Time","description":"$book_name$ $hadith_number$ - $chapter_name$. Abdullah ibn Busr disliked a delayed Eid prayer and recalled that they used to finish by forenoon time."},"heading":{"title":"Hadith About Eid Prayer Time in the Forenoon","description":"This hadith about Eid prayer time gives a scene from Abdullah ibn Busr, a companion of the Messenger of Allah صلى الله عليه وسلم. He came out with the people on Eid al-Fitr or Eid al-Adha and disliked the delay of the imam. He said that they used to finish their Eid prayer at that moment, and the narration explains that it was the time of forenoon. For people searching “Eid prayer time hadith” or “when did companions finish Eid prayer,” this report is useful because it links Eid prayer to an early time in the day. The hadith does not give a clock time. It gives a remembered practice tied to the forenoon."},"teachings":["Abdullah ibn Busr disliked the imam delaying the Eid prayer.","He recalled that they used to finish at that time.","The narration identifies that time as the forenoon.","The report is about Eid al-Fitr or Eid al-Adha prayer timing."],"related_hadiths":[{"id":"964","book_id":"1","label":"Sahih Bukhari"},{"id":"885a","book_id":"2","label":"Sahih Muslim"},{"id":"885b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Time","description":"$book_name$ $hadith_number$ - $chapter_name$. Abdullah ibn Busr disliked a delayed Eid prayer and recalled that they used to finish by forenoon time."},"heading":{"title":"Hadith About Eid Prayer Time in the Forenoon","description":"This hadith about Eid prayer time gives a scene from Abdullah ibn Busr, a companion of the Messenger of Allah صلى الله عليه وسلم. He came out with the people on Eid al-Fitr or Eid al-Adha and disliked the delay of the imam. He said that they used to finish their Eid prayer at that moment, and the narration explains that it was the time of forenoon. For people searching “Eid prayer time hadith” or “when did companions finish Eid prayer,” this report is useful because it links Eid prayer to an early time in the day. The hadith does not give a clock time. It gives a remembered practice tied to the forenoon."},"teachings":["Abdullah ibn Busr disliked the imam delaying the Eid prayer.","He recalled that they used to finish at that time.","The narration identifies that time as the forenoon.","The report is about Eid al-Fitr or Eid al-Adha prayer timing."],"related_hadiths":[{"id":"964","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"885a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"885b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E70" s="4" t="n"/>
@@ -2075,7 +2079,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women Attending Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Women were told to attend Eid goodness and Muslim supplication, with help given to those lacking outer garments."},"heading":{"title":"Hadith About Women Attending Eid Prayer and Supplication","description":"This hadith about women attending Eid prayer shows the wide call to be present for Eid goodness. Umm Atiyyah said that the Messenger of Allah صلى الله عليه وسلم commanded them to bring out secluded women on the day of Eid. When menstruating women were mentioned, he said they should be present at the place of virtue and the supplications of the Muslims. A woman then asked what should be done if one of them did not have an outer garment, and the Prophet صلى الله عليه وسلم said her friend should lend part of her garment. For people searching “women attending Eid prayer hadith” or “menstruating women Eid hadith,” this narration gives the direct wording and shows care for participation and help."},"teachings":["Women were commanded to come out on the day of Eid.","Menstruating women were to be present for goodness and Muslim supplication.","A woman without an outer garment could be helped by her friend.","The hadith shows practical support so women could attend."],"related_hadiths":[{"id":"890c","book_id":"2","label":"Sahih Muslim"},{"id":"981","book_id":"1","label":"Sahih Bukhari"},{"id":"539","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women Attending Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Women were told to attend Eid goodness and Muslim supplication, with help given to those lacking outer garments."},"heading":{"title":"Hadith About Women Attending Eid Prayer and Supplication","description":"This hadith about women attending Eid prayer shows the wide call to be present for Eid goodness. Umm Atiyyah said that the Messenger of Allah صلى الله عليه وسلم commanded them to bring out secluded women on the day of Eid. When menstruating women were mentioned, he said they should be present at the place of virtue and the supplications of the Muslims. A woman then asked what should be done if one of them did not have an outer garment, and the Prophet صلى الله عليه وسلم said her friend should lend part of her garment. For people searching “women attending Eid prayer hadith” or “menstruating women Eid hadith,” this narration gives the direct wording and shows care for participation and help."},"teachings":["Women were commanded to come out on the day of Eid.","Menstruating women were to be present for goodness and Muslim supplication.","A woman without an outer garment could be helped by her friend.","The hadith shows practical support so women could attend."],"related_hadiths":[{"id":"890c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"981","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"539","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E71" s="4" t="n"/>
@@ -2098,7 +2102,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Menstruating Women at Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. Menstruating women were to attend Eid goodness while keeping away from the prayer place of Muslims."},"heading":{"title":"Hadith About Menstruating Women Keeping Away from the Prayer Place","description":"This hadith about menstruating women at Eid adds a detail to the report from Umm Atiyyah. It says the menstruating women should keep themselves away from the place of prayer of the Muslims. In another part, the report also carries the meaning of the earlier narration about the outer garment. For people searching “menstruating women Eid prayer hadith” or “keep away from musalla Eid hadith,” this text is specific. It does not say they were absent from Eid gathering altogether. It says they stayed away from the prayer place while the wider meaning of attending the good and supplication is found in the connected report. The explanation should not go beyond that wording."},"teachings":["Menstruating women were told to keep away from the prayer place.","The report is connected to the command for women to go out for Eid.","The garment detail is mentioned through another route in the narration.","The hadith separates presence at Eid goodness from the prayer place itself."],"related_hadiths":[{"id":"890c","book_id":"2","label":"Sahih Muslim"},{"id":"981","book_id":"1","label":"Sahih Bukhari"},{"id":"1652","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Menstruating Women at Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. Menstruating women were to attend Eid goodness while keeping away from the prayer place of Muslims."},"heading":{"title":"Hadith About Menstruating Women Keeping Away from the Prayer Place","description":"This hadith about menstruating women at Eid adds a detail to the report from Umm Atiyyah. It says the menstruating women should keep themselves away from the place of prayer of the Muslims. In another part, the report also carries the meaning of the earlier narration about the outer garment. For people searching “menstruating women Eid prayer hadith” or “keep away from musalla Eid hadith,” this text is specific. It does not say they were absent from Eid gathering altogether. It says they stayed away from the prayer place while the wider meaning of attending the good and supplication is found in the connected report. The explanation should not go beyond that wording."},"teachings":["Menstruating women were told to keep away from the prayer place.","The report is connected to the command for women to go out for Eid.","The garment detail is mentioned through another route in the narration.","The hadith separates presence at Eid goodness from the prayer place itself."],"related_hadiths":[{"id":"890c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"981","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1652","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E72" s="4" t="n"/>
@@ -2121,7 +2125,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women Saying Takbir at Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. Women were commanded to go out for Eid, and menstruating women joined the takbir from behind the people."},"heading":{"title":"Hadith About Women Joining Takbir on Eid","description":"This hadith about women saying takbir at Eid gives a clear picture from Umm Atiyyah's report. She said they were commanded to go out for Eid. She added that the menstruating women stood behind the people and uttered the takbir along with them. For people searching “women saying takbir on Eid hadith” or “menstruating women takbir Eid,” this narration is direct and easy to understand. It shows that even those not praying stood behind the people and joined in the takbir. The text does not add a long list of other acts. It focuses on going out, standing behind the people, and saying Allahu Akbar with them."},"teachings":["Women were commanded to go out for Eid.","Menstruating women stood behind the people.","They joined the people in saying takbir.","The hadith shows participation in Eid remembrance even while not in the prayer rows."],"related_hadiths":[{"id":"890c","book_id":"2","label":"Sahih Muslim"},{"id":"971","book_id":"1","label":"Sahih Bukhari"},{"id":"539","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women Saying Takbir at Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. Women were commanded to go out for Eid, and menstruating women joined the takbir from behind the people."},"heading":{"title":"Hadith About Women Joining Takbir on Eid","description":"This hadith about women saying takbir at Eid gives a clear picture from Umm Atiyyah's report. She said they were commanded to go out for Eid. She added that the menstruating women stood behind the people and uttered the takbir along with them. For people searching “women saying takbir on Eid hadith” or “menstruating women takbir Eid,” this narration is direct and easy to understand. It shows that even those not praying stood behind the people and joined in the takbir. The text does not add a long list of other acts. It focuses on going out, standing behind the people, and saying Allahu Akbar with them."},"teachings":["Women were commanded to go out for Eid.","Menstruating women stood behind the people.","They joined the people in saying takbir.","The hadith shows participation in Eid remembrance even while not in the prayer rows."],"related_hadiths":[{"id":"890c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"971","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"539","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E73" s="4" t="n"/>
@@ -2144,7 +2148,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women, Eid Prayer, and Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Women were told to attend both Eid prayers, while Friday prayer was not made obligatory on them."},"heading":{"title":"Hadith About Women Attending Eid and No Jumu'ah Obligation","description":"This hadith about women, Eid prayer, and Friday prayer reports a message sent by the Messenger of Allah صلى الله عليه وسلم through Umar b. al-Khattab. Umm Atiyyah said that the women of the Ansar were gathered, Umar stood at the door, greeted them, and conveyed the message. The command was to bring out menstruating women and virgins for both Eid prayers. The report also says that Friday prayer was not obligatory on them and that they were prohibited from following funeral processions. For people searching “women Eid prayer hadith” or “is Jumuah obligatory on women hadith,” this narration gives the exact points found in the text."},"teachings":["Women were commanded to come out for both Eid prayers.","The report mentions menstruating women and virgins.","Friday prayer was not made obligatory on the women in this narration.","The narration also mentions a prohibition from accompanying funeral processions."],"related_hadiths":[{"id":"890c","book_id":"2","label":"Sahih Muslim"},{"id":"981","book_id":"1","label":"Sahih Bukhari"},{"id":"539","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women, Eid Prayer, and Friday Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Women were told to attend both Eid prayers, while Friday prayer was not made obligatory on them."},"heading":{"title":"Hadith About Women Attending Eid and No Jumu'ah Obligation","description":"This hadith about women, Eid prayer, and Friday prayer reports a message sent by the Messenger of Allah صلى الله عليه وسلم through Umar b. al-Khattab. Umm Atiyyah said that the women of the Ansar were gathered, Umar stood at the door, greeted them, and conveyed the message. The command was to bring out menstruating women and virgins for both Eid prayers. The report also says that Friday prayer was not obligatory on them and that they were prohibited from following funeral processions. For people searching “women Eid prayer hadith” or “is Jumuah obligatory on women hadith,” this narration gives the exact points found in the text."},"teachings":["Women were commanded to come out for both Eid prayers.","The report mentions menstruating women and virgins.","Friday prayer was not made obligatory on the women in this narration.","The narration also mentions a prohibition from accompanying funeral processions."],"related_hadiths":[{"id":"890c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"981","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"539","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E74" s="4" t="n"/>
@@ -2167,7 +2171,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Changing Wrong with Hand, Tongue, or Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. When a wrong was seen in Eid practice, a man spoke up, and the Prophet's صلى الله عليه وسلم guidance on changing wrong was cited."},"heading":{"title":"Hadith About Changing Wrong with Hand Tongue or Heart","description":"This hadith about changing wrong with the hand, tongue, or heart begins with an Eid event. Marwan brought out the pulpit on Eid and started the sermon before the prayer. A man stood up and said that this went against the Sunnah: the pulpit had not been brought out before, and the sermon had begun before the prayer. Abu Sa'id al-Khudri then said the man had done his duty. He reported hearing the Messenger of Allah صلى الله عليه وسلم say that whoever sees an evil should change it with his hand if able, then with his tongue if unable, then with his heart if unable, and that this is the weakest degree of faith. This is why people search “whoever sees evil hadith” and “change evil with hand tongue heart hadith.”"},"teachings":["The man spoke when he saw an Eid practice opposed to the Sunnah described in the report.","Abu Sa'id said he had fulfilled what was upon him.","The hadith gives levels of response: hand, tongue, then heart.","The response is tied to ability, as stated in the wording."],"related_hadiths":[{"id":"49a","book_id":"2","label":"Sahih Muslim"},{"id":"5008","book_id":"3","label":"Sunan an-Nasai"},{"id":"2169","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Changing Wrong with Hand, Tongue, or Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. When a wrong was seen in Eid practice, a man spoke up, and the Prophet's صلى الله عليه وسلم guidance on changing wrong was cited."},"heading":{"title":"Hadith About Changing Wrong with Hand Tongue or Heart","description":"This hadith about changing wrong with the hand, tongue, or heart begins with an Eid event. Marwan brought out the pulpit on Eid and started the sermon before the prayer. A man stood up and said that this went against the Sunnah: the pulpit had not been brought out before, and the sermon had begun before the prayer. Abu Sa'id al-Khudri then said the man had done his duty. He reported hearing the Messenger of Allah صلى الله عليه وسلم say that whoever sees an evil should change it with his hand if able, then with his tongue if unable, then with his heart if unable, and that this is the weakest degree of faith. This is why people search “whoever sees evil hadith” and “change evil with hand tongue heart hadith.”"},"teachings":["The man spoke when he saw an Eid practice opposed to the Sunnah described in the report.","Abu Sa'id said he had fulfilled what was upon him.","The hadith gives levels of response: hand, tongue, then heart.","The response is tied to ability, as stated in the wording."],"related_hadiths":[{"id":"49a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"5008","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"2169","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E75" s="4" t="n"/>
@@ -2190,7 +2194,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Before Khutbah and Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Eid prayer came before the sermon, followed by advice to women and their charity."},"heading":{"title":"Eid Prayer Hadith: Prayer Before Khutbah and Giving Charity","description":"This Eid prayer hadith shows a clear order in the Prophet’s practice on the day of breaking the fast. He first offered the prayer, then gave the sermon to the people. After finishing the khutbah, he went to the women and reminded them as well. The report also shows Bilal holding out his garment while women gave alms, including rings and other items. The main lesson is simple: the Eid prayer came first, then the Eid khutbah, and charity had a visible place on that day. The hadith about Eid charity also shows that reminders should reach all listeners, not only the main crowd."},"teachings":["The Eid prayer was offered before the sermon in this narration.","The Prophet addressed the people and then gave a reminder to the women.","The women responded by giving alms from what they had, including jewelry."],"related_hadiths":[{"id":"885b","book_id":"2","label":"Sahih Muslim"},{"id":"958","book_id":"1","label":"Sahih Bukhari"},{"id":"979","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Before Khutbah and Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Eid prayer came before the sermon, followed by advice to women and their charity."},"heading":{"title":"Eid Prayer Hadith: Prayer Before Khutbah and Giving Charity","description":"This Eid prayer hadith shows a clear order in the Prophet’s practice on the day of breaking the fast. He first offered the prayer, then gave the sermon to the people. After finishing the khutbah, he went to the women and reminded them as well. The report also shows Bilal holding out his garment while women gave alms, including rings and other items. The main lesson is simple: the Eid prayer came first, then the Eid khutbah, and charity had a visible place on that day. The hadith about Eid charity also shows that reminders should reach all listeners, not only the main crowd."},"teachings":["The Eid prayer was offered before the sermon in this narration.","The Prophet addressed the people and then gave a reminder to the women.","The women responded by giving alms from what they had, including jewelry."],"related_hadiths":[{"id":"885b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"958","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"979","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E76" s="4" t="n"/>
@@ -2213,7 +2217,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer and Giving Alms","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration highlights Eid prayer before the sermon and the women giving alms after being advised."},"heading":{"title":"Eid Prayer and Charity Hadith: Prayer First, Sermon After","description":"This narration gives another report of the Eid prayer hadith from Ibn Abbas. The Messenger of Allah came out on Eid, prayed first, and then delivered the sermon. After that, he went to the women with Bilal. The narrator mentions the probable wording that he commanded them to give alms, and the women began placing their jewelry. The core topic is Eid charity after the Eid khutbah. The text keeps the order clear: prayer, sermon, then advice to the women. It is a short report, but it gives a strong picture of worship, teaching, and giving all taking place on Eid day."},"teachings":["The Prophet offered the Eid prayer before giving the sermon.","He made a separate effort to reach the women with advice.","The women gave from their jewelry after being urged to give alms."],"related_hadiths":[{"id":"884d","book_id":"2","label":"Sahih Muslim"},{"id":"964","book_id":"1","label":"Sahih Bukhari"},{"id":"885b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer and Giving Alms","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration highlights Eid prayer before the sermon and the women giving alms after being advised."},"heading":{"title":"Eid Prayer and Charity Hadith: Prayer First, Sermon After","description":"This narration gives another report of the Eid prayer hadith from Ibn Abbas. The Messenger of Allah came out on Eid, prayed first, and then delivered the sermon. After that, he went to the women with Bilal. The narrator mentions the probable wording that he commanded them to give alms, and the women began placing their jewelry. The core topic is Eid charity after the Eid khutbah. The text keeps the order clear: prayer, sermon, then advice to the women. It is a short report, but it gives a strong picture of worship, teaching, and giving all taking place on Eid day."},"teachings":["The Prophet offered the Eid prayer before giving the sermon.","He made a separate effort to reach the women with advice.","The women gave from their jewelry after being urged to give alms."],"related_hadiths":[{"id":"884d","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"964","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"885b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E77" s="4" t="n"/>
@@ -2236,7 +2240,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women’s Reminder and Alms on Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet went to the women when he thought they had not heard and urged them to give alms."},"heading":{"title":"Hadith About Women Giving Charity on Eid After the Reminder","description":"This hadith about women giving charity on Eid adds an important detail. The Prophet thought the women could not hear the sermon, so he walked over to them with Bilal. He gave them an exhortation and commanded them to give alms. The women then placed earrings and rings in Bilal’s garment. The core topic is not only charity, but also making sure the message is heard. The report does not add a long speech or extra ruling. It simply shows care in communication, a direct reminder, and a quick response through giving. It is a clear Eid charity hadith with a focus on women’s participation."},"teachings":["The Prophet went to the women when he thought they had not heard.","He gave them a direct reminder and urged them to give alms.","The women gave items they owned, such as earrings and rings."],"related_hadiths":[{"id":"884b","book_id":"2","label":"Sahih Muslim"},{"id":"979","book_id":"1","label":"Sahih Bukhari"},{"id":"964","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women’s Reminder and Alms on Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet went to the women when he thought they had not heard and urged them to give alms."},"heading":{"title":"Hadith About Women Giving Charity on Eid After the Reminder","description":"This hadith about women giving charity on Eid adds an important detail. The Prophet thought the women could not hear the sermon, so he walked over to them with Bilal. He gave them an exhortation and commanded them to give alms. The women then placed earrings and rings in Bilal’s garment. The core topic is not only charity, but also making sure the message is heard. The report does not add a long speech or extra ruling. It simply shows care in communication, a direct reminder, and a quick response through giving. It is a clear Eid charity hadith with a focus on women’s participation."},"teachings":["The Prophet went to the women when he thought they had not heard.","He gave them a direct reminder and urged them to give alms.","The women gave items they owned, such as earrings and rings."],"related_hadiths":[{"id":"884b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"979","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"964","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E78" s="4" t="n"/>
@@ -2259,7 +2263,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Alms for Poor Muslims","description":"$book_name$ $hadith_number$ - $chapter_name$. Women gave rings and earrings in alms, and the Prophet distributed them among poor Muslims."},"heading":{"title":"Eid Charity Distribution Hadith: Alms Given to Poor Muslims","description":"This Eid charity distribution hadith gives a final detail about what happened to the alms collected on Eid. Women gave earrings and rings, and Bilal placed them in his garment. The report then says the Prophet distributed them among the poor Muslims. The core message is very direct: charity was collected and then passed on to people in need. The hadith does not describe a long system or extra conditions. It shows a simple act of giving and a clear use for the donated items. For anyone searching for a hadith about Eid charity for the poor, this narration is highly focused."},"teachings":["The women gave jewelry as alms during the Eid gathering.","Bilal collected the alms in his garment.","The collected items were distributed among poor Muslims."],"related_hadiths":[{"id":"884d","book_id":"2","label":"Sahih Muslim"},{"id":"964","book_id":"1","label":"Sahih Bukhari"},{"id":"979","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Alms for Poor Muslims","description":"$book_name$ $hadith_number$ - $chapter_name$. Women gave rings and earrings in alms, and the Prophet distributed them among poor Muslims."},"heading":{"title":"Eid Charity Distribution Hadith: Alms Given to Poor Muslims","description":"This Eid charity distribution hadith gives a final detail about what happened to the alms collected on Eid. Women gave earrings and rings, and Bilal placed them in his garment. The report then says the Prophet distributed them among the poor Muslims. The core message is very direct: charity was collected and then passed on to people in need. The hadith does not describe a long system or extra conditions. It shows a simple act of giving and a clear use for the donated items. For anyone searching for a hadith about Eid charity for the poor, this narration is highly focused."},"teachings":["The women gave jewelry as alms during the Eid gathering.","Bilal collected the alms in his garment.","The collected items were distributed among poor Muslims."],"related_hadiths":[{"id":"884d","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"964","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"979","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E79" s="4" t="n"/>
@@ -2282,7 +2286,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer, Sermon, and Alms","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas describes the Eid prayer, sermon, no adhan or iqamah, and women giving jewelry in alms."},"heading":{"title":"Eid Prayer Hadith: No Adhan, Sermon After Prayer, and Charity","description":"This Eid prayer hadith brings several points together in one report. Ibn Abbas said he attended Eid with the Messenger of Allah when he was young. The Prophet came to the marked place near the house of Kathir b. al-Salt, prayed, and then preached. The narrator does not mention adhan or iqamah. After the sermon, the Prophet commanded charity, and the women began pointing to their ears and throats, showing jewelry they could give. Bilal was then sent to them and returned to the Prophet. The report gives a clear scene of Eid worship, public teaching, and alms in one gathering."},"teachings":["The Eid prayer was followed by the sermon.","The narration does not mention adhan or iqamah for the Eid prayer.","The women indicated jewelry from their ears and throats for charity."],"related_hadiths":[{"id":"886a","book_id":"2","label":"Sahih Muslim"},{"id":"887","book_id":"2","label":"Sahih Muslim"},{"id":"959","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer, Sermon, and Alms","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas describes the Eid prayer, sermon, no adhan or iqamah, and women giving jewelry in alms."},"heading":{"title":"Eid Prayer Hadith: No Adhan, Sermon After Prayer, and Charity","description":"This Eid prayer hadith brings several points together in one report. Ibn Abbas said he attended Eid with the Messenger of Allah when he was young. The Prophet came to the marked place near the house of Kathir b. al-Salt, prayed, and then preached. The narrator does not mention adhan or iqamah. After the sermon, the Prophet commanded charity, and the women began pointing to their ears and throats, showing jewelry they could give. Bilal was then sent to them and returned to the Prophet. The report gives a clear scene of Eid worship, public teaching, and alms in one gathering."},"teachings":["The Eid prayer was followed by the sermon.","The narration does not mention adhan or iqamah for the Eid prayer.","The women indicated jewelry from their ears and throats for charity."],"related_hadiths":[{"id":"886a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"887","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"959","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E80" s="4" t="n"/>
@@ -2305,7 +2309,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Adhan or Iqamah for Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration states that Eid prayer was offered without adhan and iqamah by the Prophet and caliphs."},"heading":{"title":"No Adhan for Eid Prayer Hadith: A Clear Report from Ibn Abbas","description":"This hadith is focused on one clear point: the Eid prayer was offered without adhan and without iqamah. Ibn Abbas reports this from the Messenger of Allah. He also mentions that Abu Bakr and Umar, or Uthman according to the narrator’s doubt, did the same. The core topic is no adhan for Eid prayer. The wording is brief, so the explanation should stay brief as well. It does not discuss the full method of Eid prayer, the khutbah, or charity. It simply records the absence of the regular prayer calls in this Eid setting and connects that practice to the Prophet and early leaders."},"teachings":["The Prophet offered the Eid prayer without adhan.","The Eid prayer was also without iqamah in this report.","The narrator mentions that early caliphs followed this practice."],"related_hadiths":[{"id":"887","book_id":"2","label":"Sahih Muslim"},{"id":"886a","book_id":"2","label":"Sahih Muslim"},{"id":"959","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Adhan or Iqamah for Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration states that Eid prayer was offered without adhan and iqamah by the Prophet and caliphs."},"heading":{"title":"No Adhan for Eid Prayer Hadith: A Clear Report from Ibn Abbas","description":"This hadith is focused on one clear point: the Eid prayer was offered without adhan and without iqamah. Ibn Abbas reports this from the Messenger of Allah. He also mentions that Abu Bakr and Umar, or Uthman according to the narrator’s doubt, did the same. The core topic is no adhan for Eid prayer. The wording is brief, so the explanation should stay brief as well. It does not discuss the full method of Eid prayer, the khutbah, or charity. It simply records the absence of the regular prayer calls in this Eid setting and connects that practice to the Prophet and early leaders."},"teachings":["The Prophet offered the Eid prayer without adhan.","The Eid prayer was also without iqamah in this report.","The narrator mentions that early caliphs followed this practice."],"related_hadiths":[{"id":"887","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"886a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"959","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E81" s="4" t="n"/>
@@ -2328,7 +2332,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Without Adhan and Iqamah","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir b. Samurah says he prayed Eid with the Prophet many times without adhan or iqamah."},"heading":{"title":"Eid Prayer Without Adhan and Iqamah: Hadith from Jabir b. Samurah","description":"This narration is a direct hadith about Eid prayer without adhan and iqamah. Jabir b. Samurah says he prayed the Eid prayer with the Prophet not once or twice, but many times. Each time, there was no adhan and no iqamah. The phrase “not once or twice” gives weight to the repeated nature of what he saw. The report does not describe the takbir, recitation, sermon, or charity. It keeps the focus on the calls before prayer. For readers searching “Eid prayer no adhan no iqamah hadith,” this narration is one of the clearest reports because it is simple and repeated."},"teachings":["Jabir b. Samurah prayed Eid with the Prophet many times.","He reports that those Eid prayers had no adhan.","He also reports that those Eid prayers had no iqamah."],"related_hadiths":[{"id":"887","book_id":"2","label":"Sahih Muslim"},{"id":"959","book_id":"1","label":"Sahih Bukhari"},{"id":"886a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer Without Adhan and Iqamah","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir b. Samurah says he prayed Eid with the Prophet many times without adhan or iqamah."},"heading":{"title":"Eid Prayer Without Adhan and Iqamah: Hadith from Jabir b. Samurah","description":"This narration is a direct hadith about Eid prayer without adhan and iqamah. Jabir b. Samurah says he prayed the Eid prayer with the Prophet not once or twice, but many times. Each time, there was no adhan and no iqamah. The phrase “not once or twice” gives weight to the repeated nature of what he saw. The report does not describe the takbir, recitation, sermon, or charity. It keeps the focus on the calls before prayer. For readers searching “Eid prayer no adhan no iqamah hadith,” this narration is one of the clearest reports because it is simple and repeated."},"teachings":["Jabir b. Samurah prayed Eid with the Prophet many times.","He reports that those Eid prayers had no adhan.","He also reports that those Eid prayers had no iqamah."],"related_hadiths":[{"id":"887","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"959","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"886a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E82" s="4" t="n"/>
@@ -2351,7 +2355,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Takbirs Apart from Ruku","description":"$book_name$ $hadith_number$ - $chapter_name$. This version clarifies the Eid takbir count is apart from the two takbirs said at bowing."},"heading":{"title":"Eid Takbir Count Hadith: Seven and Five Apart from Ruku Takbirs","description":"This narration continues the same Eid takbir hadith through another chain and adds a helpful detail. It says the count is apart from the two takbirs pronounced at the time of bowing. This means the report is speaking about the extra takbirs of the Eid prayer, not every takbir used while moving through the prayer. The core topic is Eid takbir count. The text itself does not explain the whole prayer from beginning to end, so the explanation should not go beyond that. It simply makes the count clearer for readers looking for the hadith about seven and five takbirs in Eid prayer."},"teachings":["The narration repeats the Eid takbir count through another chain.","It adds that the count excludes the takbirs of bowing.","The added wording helps separate extra Eid takbirs from movement takbirs."],"related_hadiths":[{"id":"1280","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1277","book_id":"6","label":"Sunan Ibn Majah"},{"id":"536","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Takbirs Apart from Ruku","description":"$book_name$ $hadith_number$ - $chapter_name$. This version clarifies the Eid takbir count is apart from the two takbirs said at bowing."},"heading":{"title":"Eid Takbir Count Hadith: Seven and Five Apart from Ruku Takbirs","description":"This narration continues the same Eid takbir hadith through another chain and adds a helpful detail. It says the count is apart from the two takbirs pronounced at the time of bowing. This means the report is speaking about the extra takbirs of the Eid prayer, not every takbir used while moving through the prayer. The core topic is Eid takbir count. The text itself does not explain the whole prayer from beginning to end, so the explanation should not go beyond that. It simply makes the count clearer for readers looking for the hadith about seven and five takbirs in Eid prayer."},"teachings":["The narration repeats the Eid takbir count through another chain.","It adds that the count excludes the takbirs of bowing.","The added wording helps separate extra Eid takbirs from movement takbirs."],"related_hadiths":[{"id":"1280","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1277","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"536","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E83" s="4" t="n"/>
@@ -2374,7 +2378,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid al-Fitr Takbir and Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith states seven takbirs in the first rak'ah, five in the second, with recitation after them."},"heading":{"title":"Eid al-Fitr Takbir Hadith: Seven, Five, Then Recitation","description":"This Eid al-Fitr takbir hadith gives both the number and the place of recitation. Abdullah b. Amr b. al-As reports that the Prophet said there are seven takbirs in the first rak'ah and five in the second rak'ah of the prayer on the day of breaking the fast. The report also says the recitation comes after the takbirs in both rak'ahs. That is the main point of this narration. It does not mention the khutbah, charity, or the place of prayer. For a reader searching how many takbirs in Eid al-Fitr prayer, this hadith is focused and easy to follow."},"teachings":["The first rak'ah of Eid al-Fitr prayer has seven takbirs in this report.","The second rak'ah has five takbirs in this report.","The Qur'an recitation is mentioned after the takbirs in both rak'ahs."],"related_hadiths":[{"id":"1278","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1277","book_id":"6","label":"Sunan Ibn Majah"},{"id":"536","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid al-Fitr Takbir and Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith states seven takbirs in the first rak'ah, five in the second, with recitation after them."},"heading":{"title":"Eid al-Fitr Takbir Hadith: Seven, Five, Then Recitation","description":"This Eid al-Fitr takbir hadith gives both the number and the place of recitation. Abdullah b. Amr b. al-As reports that the Prophet said there are seven takbirs in the first rak'ah and five in the second rak'ah of the prayer on the day of breaking the fast. The report also says the recitation comes after the takbirs in both rak'ahs. That is the main point of this narration. It does not mention the khutbah, charity, or the place of prayer. For a reader searching how many takbirs in Eid al-Fitr prayer, this hadith is focused and easy to follow."},"teachings":["The first rak'ah of Eid al-Fitr prayer has seven takbirs in this report.","The second rak'ah has five takbirs in this report.","The Qur'an recitation is mentioned after the takbirs in both rak'ahs."],"related_hadiths":[{"id":"1278","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1277","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"536","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E84" s="4" t="n"/>
@@ -2397,7 +2401,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Takbir Sequence and Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. This report describes takbir and recitation in the Eid al-Fitr prayer, with a note on seven and five."},"heading":{"title":"Eid Prayer Takbir Sequence Hadith: Takbir, Recitation, and Bowing","description":"This Eid prayer takbir sequence hadith reports how the Prophet prayed on the day of breaking the fast. It mentions seven takbirs in the first rak'ah, then recitation. It then describes standing for the next rak'ah, saying takbir four times in this wording, then reciting and bowing. Abu Dawud adds that Waki' and Ibn al-Mubarak narrated it as seven in the first and five in the second. The core topic is the takbir sequence in Eid prayer. Since the report itself includes a note about different wording, the explanation should keep that detail clear without trying to settle more than the text states."},"teachings":["The narration describes takbir before recitation in the first rak'ah.","It also describes takbir before recitation in the second rak'ah.","Abu Dawud notes another version with seven and five takbirs."],"related_hadiths":[{"id":"1278","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1277","book_id":"6","label":"Sunan Ibn Majah"},{"id":"536","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Takbir Sequence and Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. This report describes takbir and recitation in the Eid al-Fitr prayer, with a note on seven and five."},"heading":{"title":"Eid Prayer Takbir Sequence Hadith: Takbir, Recitation, and Bowing","description":"This Eid prayer takbir sequence hadith reports how the Prophet prayed on the day of breaking the fast. It mentions seven takbirs in the first rak'ah, then recitation. It then describes standing for the next rak'ah, saying takbir four times in this wording, then reciting and bowing. Abu Dawud adds that Waki' and Ibn al-Mubarak narrated it as seven in the first and five in the second. The core topic is the takbir sequence in Eid prayer. Since the report itself includes a note about different wording, the explanation should keep that detail clear without trying to settle more than the text states."},"teachings":["The narration describes takbir before recitation in the first rak'ah.","It also describes takbir before recitation in the second rak'ah.","Abu Dawud notes another version with seven and five takbirs."],"related_hadiths":[{"id":"1278","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1277","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"536","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E85" s="4" t="n"/>
@@ -2420,7 +2424,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Takbirs Report in Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Musa reports four takbirs in Eid prayer, and Hudhaifah confirms his answer."},"heading":{"title":"Eid Takbir Hadith: Abu Musa’s Report of Four Takbirs","description":"This narration records a question about the Eid takbir. Sa'id b. al-As asked Abu Musa al-Ash'ari and Hudhaifah b. al-Yaman how the Messenger of Allah would say takbir in the prayers of Eid al-Adha and Eid al-Fitr. Abu Musa answered that he said takbir four times, like the takbir for funerals. Hudhaifah said that Abu Musa was correct. Abu Musa also said he used to say the takbir in the same way when he was governor of Basrah. The report is clear about what these Companions stated. It should not be mixed with other narrations unless those are named separately."},"teachings":["Sa'id b. al-As asked senior Companions about Eid takbir.","Abu Musa answered that it was four takbirs, like funeral prayer.","Hudhaifah confirmed Abu Musa’s answer in this report."],"related_hadiths":[{"id":"536","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1278","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1280","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Takbirs Report in Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Musa reports four takbirs in Eid prayer, and Hudhaifah confirms his answer."},"heading":{"title":"Eid Takbir Hadith: Abu Musa’s Report of Four Takbirs","description":"This narration records a question about the Eid takbir. Sa'id b. al-As asked Abu Musa al-Ash'ari and Hudhaifah b. al-Yaman how the Messenger of Allah would say takbir in the prayers of Eid al-Adha and Eid al-Fitr. Abu Musa answered that he said takbir four times, like the takbir for funerals. Hudhaifah said that Abu Musa was correct. Abu Musa also said he used to say the takbir in the same way when he was governor of Basrah. The report is clear about what these Companions stated. It should not be mixed with other narrations unless those are named separately."},"teachings":["Sa'id b. al-As asked senior Companions about Eid takbir.","Abu Musa answered that it was four takbirs, like funeral prayer.","Hudhaifah confirmed Abu Musa’s answer in this report."],"related_hadiths":[{"id":"536","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1278","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1280","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E86" s="4" t="n"/>
@@ -2443,7 +2447,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surahs Recited in Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Waqid reports that the Prophet recited Surah Qaf and Surah Al-Qamar in both Eid prayers."},"heading":{"title":"Eid Prayer Recitation Hadith: Surah Qaf and Surah Al-Qamar","description":"This Eid prayer recitation hadith answers a direct question from Umar b. al-Khattab. He asked Abu Waqid al-Laithi what the Messenger of Allah recited in the prayers of Eid al-Adha and Eid al-Fitr. Abu Waqid replied that he recited Surah Qaf, beginning “By the Glorious Quran,” and Surah Al-Qamar, beginning “The Hour is nigh.” The core topic is recitation in the Eid prayer. The report does not discuss the number of takbirs or the sermon. It only names the surahs used in both Eid prayers, making it useful for anyone searching for hadith about what to recite in Eid salah."},"teachings":["Umar asked Abu Waqid what was recited in the Eid prayers.","The Prophet recited Surah Qaf in both Eid prayers in this report.","He also recited Surah Al-Qamar in both Eid prayers in this report."],"related_hadiths":[{"id":"891a","book_id":"2","label":"Sahih Muslim"},{"id":"891b","book_id":"2","label":"Sahih Muslim"},{"id":"1282","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surahs Recited in Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Waqid reports that the Prophet recited Surah Qaf and Surah Al-Qamar in both Eid prayers."},"heading":{"title":"Eid Prayer Recitation Hadith: Surah Qaf and Surah Al-Qamar","description":"This Eid prayer recitation hadith answers a direct question from Umar b. al-Khattab. He asked Abu Waqid al-Laithi what the Messenger of Allah recited in the prayers of Eid al-Adha and Eid al-Fitr. Abu Waqid replied that he recited Surah Qaf, beginning “By the Glorious Quran,” and Surah Al-Qamar, beginning “The Hour is nigh.” The core topic is recitation in the Eid prayer. The report does not discuss the number of takbirs or the sermon. It only names the surahs used in both Eid prayers, making it useful for anyone searching for hadith about what to recite in Eid salah."},"teachings":["Umar asked Abu Waqid what was recited in the Eid prayers.","The Prophet recited Surah Qaf in both Eid prayers in this report.","He also recited Surah Al-Qamar in both Eid prayers in this report."],"related_hadiths":[{"id":"891a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"891b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1282","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E87" s="4" t="n"/>
@@ -2466,7 +2470,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sitting for the Eid Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. After the Eid prayer, the Prophet said whoever wished could sit for the sermon or leave."},"heading":{"title":"Eid Khutbah Hadith: Sitting for the Sermon After Prayer","description":"This Eid khutbah hadith reports what happened after the Eid prayer. Abdullah ibn as-Sa'ib says he attended the Eid prayer with the Messenger of Allah. When the prayer was finished, the Prophet said they would deliver the sermon. He then said that whoever liked to sit and listen could sit, and whoever liked to go could go. Abu Dawud adds that this is a mursal tradition from Ata reporting from the Prophet. The core message from the text is the choice mentioned after the prayer. The explanation should stay with that wording and not add wider rulings beyond what the narration itself says."},"teachings":["The sermon came after the Eid prayer in this narration.","The Prophet announced that the sermon would be delivered.","The wording gives people the choice to sit for it or leave."],"related_hadiths":[{"id":"889","book_id":"2","label":"Sahih Muslim"},{"id":"956","book_id":"1","label":"Sahih Bukhari"},{"id":"888","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sitting for the Eid Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. After the Eid prayer, the Prophet said whoever wished could sit for the sermon or leave."},"heading":{"title":"Eid Khutbah Hadith: Sitting for the Sermon After Prayer","description":"This Eid khutbah hadith reports what happened after the Eid prayer. Abdullah ibn as-Sa'ib says he attended the Eid prayer with the Messenger of Allah. When the prayer was finished, the Prophet said they would deliver the sermon. He then said that whoever liked to sit and listen could sit, and whoever liked to go could go. Abu Dawud adds that this is a mursal tradition from Ata reporting from the Prophet. The core message from the text is the choice mentioned after the prayer. The explanation should stay with that wording and not add wider rulings beyond what the narration itself says."},"teachings":["The sermon came after the Eid prayer in this narration.","The Prophet announced that the sermon would be delivered.","The wording gives people the choice to sit for it or leave."],"related_hadiths":[{"id":"889","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"956","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"888","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E88" s="4" t="n"/>
@@ -2489,7 +2493,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Returning by Another Route on Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports that the Prophet went out by one road on Eid and returned by another road."},"heading":{"title":"Eid Route Hadith: Going One Way and Returning Another","description":"This Eid route hadith is short and easy to understand. Abdullah ibn Umar reports that the Messenger of Allah went out by one road on the day of Eid and returned by another road. The narration does not give the reason for changing the route, so the safe explanation is simply that this action is reported from the Prophet on Eid day. It is often searched as “different route on Eid hadith” or “return by another road on Eid.” The core topic is the Prophet’s route to and from the Eid prayer. The text gives the action, not a long reason or extra detail."},"teachings":["The Prophet went out by one route on Eid day.","He returned by a different route.","The narration records a practical detail of the Prophet’s Eid outing."],"related_hadiths":[{"id":"986","book_id":"1","label":"Sahih Bukhari"},{"id":"1300","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1297","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Returning by Another Route on Eid","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports that the Prophet went out by one road on Eid and returned by another road."},"heading":{"title":"Eid Route Hadith: Going One Way and Returning Another","description":"This Eid route hadith is short and easy to understand. Abdullah ibn Umar reports that the Messenger of Allah went out by one road on the day of Eid and returned by another road. The narration does not give the reason for changing the route, so the safe explanation is simply that this action is reported from the Prophet on Eid day. It is often searched as “different route on Eid hadith” or “return by another road on Eid.” The core topic is the Prophet’s route to and from the Eid prayer. The text gives the action, not a long reason or extra detail."},"teachings":["The Prophet went out by one route on Eid day.","He returned by a different route.","The narration records a practical detail of the Prophet’s Eid outing."],"related_hadiths":[{"id":"986","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1300","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1297","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E89" s="4" t="n"/>
@@ -2512,7 +2516,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shawwal Moon Sighting and Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Riders testified to seeing the moon, so the Prophet told people to break the fast and pray next morning."},"heading":{"title":"Moon Sighting Hadith for Eid: Break the Fast and Go to Prayer","description":"This moon sighting hadith for Eid describes a case where some riders came to the Prophet and testified that they had seen the new moon the previous day. The Prophet then commanded the people to break the fast and to go out to their place of prayer in the morning. The core topic is the link between the sighting of the new moon and Eid al-Fitr. The report does not discuss calendars, calculations, or different lands. It only states what happened in this case: testimony was given, the fast was ended, and the people were told to attend the prayer place the next morning."},"teachings":["Men came and testified that they had seen the new moon the previous day.","The Prophet commanded the people to break the fast.","He told them to go out to the prayer place in the morning."],"related_hadiths":[{"id":"2333","book_id":"4","label":"Sunan Abu Dawud"},{"id":"2111","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shawwal Moon Sighting and Eid Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Riders testified to seeing the moon, so the Prophet told people to break the fast and pray next morning."},"heading":{"title":"Moon Sighting Hadith for Eid: Break the Fast and Go to Prayer","description":"This moon sighting hadith for Eid describes a case where some riders came to the Prophet and testified that they had seen the new moon the previous day. The Prophet then commanded the people to break the fast and to go out to their place of prayer in the morning. The core topic is the link between the sighting of the new moon and Eid al-Fitr. The report does not discuss calendars, calculations, or different lands. It only states what happened in this case: testimony was given, the fast was ended, and the people were told to attend the prayer place the next morning."},"teachings":["Men came and testified that they had seen the new moon the previous day.","The Prophet commanded the people to break the fast.","He told them to go out to the prayer place in the morning."],"related_hadiths":[{"id":"2333","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"2111","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -2539,7 +2543,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Walking to the Eid Prayer Place","description":"$book_name$ $hadith_number$ - $chapter_name$. Bakr ibn Mubashshir describes walking with Companions to the Eid prayer place and returning home."},"heading":{"title":"Eid Prayer Place Hadith: Walking to the Musalla with the Companions","description":"This Eid prayer place hadith describes how Bakr ibn Mubashshir al-Ansari used to go with the Companions of the Messenger of Allah to the musalla on Eid al-Fitr and Eid al-Adha. They would pass through a valley called Batn Bathan until they reached the prayer place. Then they prayed with the Messenger of Allah and returned through Batn Bathan to their homes. The core topic is going to the Eid musalla. The report is mainly a description of movement and place. It does not mention the sermon, takbir count, or charity. Its strength is the clear picture of attending Eid prayer with the Companions."},"teachings":["The Companions went to the Eid prayer place on both Eid days.","They walked through Batn Bathan on the way to the musalla.","They prayed with the Prophet and then returned to their homes."],"related_hadiths":[{"id":"956","book_id":"1","label":"Sahih Bukhari"},{"id":"889","book_id":"2","label":"Sahih Muslim"},{"id":"986","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Walking to the Eid Prayer Place","description":"$book_name$ $hadith_number$ - $chapter_name$. Bakr ibn Mubashshir describes walking with Companions to the Eid prayer place and returning home."},"heading":{"title":"Eid Prayer Place Hadith: Walking to the Musalla with the Companions","description":"This Eid prayer place hadith describes how Bakr ibn Mubashshir al-Ansari used to go with the Companions of the Messenger of Allah to the musalla on Eid al-Fitr and Eid al-Adha. They would pass through a valley called Batn Bathan until they reached the prayer place. Then they prayed with the Messenger of Allah and returned through Batn Bathan to their homes. The core topic is going to the Eid musalla. The report is mainly a description of movement and place. It does not mention the sermon, takbir count, or charity. Its strength is the clear picture of attending Eid prayer with the Companions."},"teachings":["The Companions went to the Eid prayer place on both Eid days.","They walked through Batn Bathan on the way to the musalla.","They prayed with the Prophet and then returned to their homes."],"related_hadiths":[{"id":"956","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"889","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"986","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E91" s="4" t="n"/>
@@ -2562,7 +2566,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs and No Prayer Before or After","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports two rak'ahs on Eid al-Fitr with no prayer before or after, followed by charity."},"heading":{"title":"Eid Prayer Two Rak'ahs Hadith: No Prayer Before or After","description":"This Eid prayer two rak'ahs hadith reports that the Messenger of Allah came out on the day of breaking the fast and prayed two rak'ahs. Ibn Abbas adds that he did not pray before them or after them. The Prophet then went to the women with Bilal and commanded them to give alms. The women began placing items such as earrings and necklaces. The core topic is the Eid al-Fitr prayer and the charity that followed. The narration is useful for readers searching for no prayer before or after Eid prayer hadith, while also showing the same Eid charity scene found in other reports."},"teachings":["The Prophet prayed two rak'ahs on Eid al-Fitr.","He did not pray before or after those two rak'ahs in this report.","He then went to the women with Bilal and commanded charity."],"related_hadiths":[{"id":"964","book_id":"1","label":"Sahih Bukhari"},{"id":"884d","book_id":"2","label":"Sahih Muslim"},{"id":"884e","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs and No Prayer Before or After","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports two rak'ahs on Eid al-Fitr with no prayer before or after, followed by charity."},"heading":{"title":"Eid Prayer Two Rak'ahs Hadith: No Prayer Before or After","description":"This Eid prayer two rak'ahs hadith reports that the Messenger of Allah came out on the day of breaking the fast and prayed two rak'ahs. Ibn Abbas adds that he did not pray before them or after them. The Prophet then went to the women with Bilal and commanded them to give alms. The women began placing items such as earrings and necklaces. The core topic is the Eid al-Fitr prayer and the charity that followed. The narration is useful for readers searching for no prayer before or after Eid prayer hadith, while also showing the same Eid charity scene found in other reports."},"teachings":["The Prophet prayed two rak'ahs on Eid al-Fitr.","He did not pray before or after those two rak'ahs in this report.","He then went to the women with Bilal and commanded charity."],"related_hadiths":[{"id":"964","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"884d","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"884e","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E92" s="4" t="n"/>
@@ -2585,7 +2589,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer in the Mosque During Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurayrah reports that rain fell on Eid, so the Prophet led the Eid prayer in the mosque."},"heading":{"title":"Eid Prayer in the Mosque Hadith: When Rain Fell on Eid","description":"This hadith about Eid prayer in the mosque mentions a simple situation. Abu Hurayrah reports that rain fell on the day of Eid, so the Prophet led the people in the Eid prayer in the mosque. The core topic is Eid prayer during rain. The narration does not describe the sermon, the number of takbirs, or the reason in legal terms. It only tells us that rain happened on Eid and the prayer was led inside the mosque. For readers searching for Eid prayer in mosque due to rain hadith, this report is direct. The explanation should stay with the stated event and avoid adding more than the text says."},"teachings":["Rain fell on the day of Eid in this narration.","The Prophet led the people in the Eid prayer.","The prayer was held in the mosque on that rainy Eid day."],"related_hadiths":[{"id":"1313","book_id":"6","label":"Sunan Ibn Majah"},{"id":"889","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eid Prayer in the Mosque During Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurayrah reports that rain fell on Eid, so the Prophet led the Eid prayer in the mosque."},"heading":{"title":"Eid Prayer in the Mosque Hadith: When Rain Fell on Eid","description":"This hadith about Eid prayer in the mosque mentions a simple situation. Abu Hurayrah reports that rain fell on the day of Eid, so the Prophet led the people in the Eid prayer in the mosque. The core topic is Eid prayer during rain. The narration does not describe the sermon, the number of takbirs, or the reason in legal terms. It only tells us that rain happened on Eid and the prayer was led inside the mosque. For readers searching for Eid prayer in mosque due to rain hadith, this report is direct. The explanation should stay with the stated event and avoid adding more than the text says."},"teachings":["Rain fell on the day of Eid in this narration.","The Prophet led the people in the Eid prayer.","The prayer was held in the mosque on that rainy Eid day."],"related_hadiths":[{"id":"1313","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"889","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -2612,7 +2616,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer for Rain with Humble Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم prayed for rain with two rak'ahs, loud recitation, raised hands, and facing the qiblah."},"heading":{"title":"Prayer for Rain Hadith: Two Rak'ahs, Raised Hands, and Qiblah","description":"This istisqa prayer hadith gives a clear picture of how the Messenger of Allah صلى الله عليه وسلم led the people when they needed rain. He took them out to the place of prayer, led two rak'ahs, recited the Qur'an aloud, turned his cloak, raised his hands, made dua for rain, and faced the qiblah. The main lesson is simple: when people face hardship, they turn to Allah with prayer and supplication. The hadith about prayer for rain also shows that the act was public and organized, not only a private request. It joins Salah, Qur'an recitation, dua, and humble body language in one act of worship."},"teachings":["The Prophet صلى الله عليه وسلم led the people in two rak'ahs when praying for rain.","He recited aloud in the prayer, as stated in the report.","He raised his hands and faced the qiblah while making supplication.","Turning the cloak is mentioned as part of this rain prayer report."],"related_hadiths":[{"id":"894a","book_id":"2","label":"Sahih Muslim"},{"id":"1023","book_id":"1","label":"Sahih Bukhari"},{"id":"1027","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer for Rain with Humble Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم prayed for rain with two rak'ahs, loud recitation, raised hands, and facing the qiblah."},"heading":{"title":"Prayer for Rain Hadith: Two Rak'ahs, Raised Hands, and Qiblah","description":"This istisqa prayer hadith gives a clear picture of how the Messenger of Allah صلى الله عليه وسلم led the people when they needed rain. He took them out to the place of prayer, led two rak'ahs, recited the Qur'an aloud, turned his cloak, raised his hands, made dua for rain, and faced the qiblah. The main lesson is simple: when people face hardship, they turn to Allah with prayer and supplication. The hadith about prayer for rain also shows that the act was public and organized, not only a private request. It joins Salah, Qur'an recitation, dua, and humble body language in one act of worship."},"teachings":["The Prophet صلى الله عليه وسلم led the people in two rak'ahs when praying for rain.","He recited aloud in the prayer, as stated in the report.","He raised his hands and faced the qiblah while making supplication.","Turning the cloak is mentioned as part of this rain prayer report."],"related_hadiths":[{"id":"894a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1023","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E94" s="4" t="n"/>
@@ -2635,7 +2639,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Facing Qiblah in Rain Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. See how the Prophet صلى الله عليه وسلم prayed for rain by facing the qiblah, turning his cloak, praying two rak'ahs, and reciting aloud."},"heading":{"title":"Istisqa Prayer Hadith: Facing the Qiblah and Turning the Cloak","description":"This istisqa hadith focuses on the Prophet صلى الله عليه وسلم going out to ask Allah for rain. He turned his back to the people while praying to Allah, faced the qiblah, turned his cloak, and then offered two rak'ahs. The report also mentions Qur'an recitation in the two rak'ahs, with one version explaining that it was done aloud. For anyone searching for a hadith about prayer for rain, this narration shows that the request for rain was tied to clear acts of worship: facing Allah's direction in prayer, making dua, and praying with the people. It also teaches calm order during a time of need."},"teachings":["The Prophet صلى الله عليه وسلم faced the qiblah while making supplication for rain.","He turned his cloak during the rain prayer.","He offered two rak'ahs after the supplication details mentioned in the report.","The recitation in the prayer is described as aloud in one version."],"related_hadiths":[{"id":"894b","book_id":"2","label":"Sahih Muslim"},{"id":"894c","book_id":"2","label":"Sahih Muslim"},{"id":"1023","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Facing Qiblah in Rain Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. See how the Prophet صلى الله عليه وسلم prayed for rain by facing the qiblah, turning his cloak, praying two rak'ahs, and reciting aloud."},"heading":{"title":"Istisqa Prayer Hadith: Facing the Qiblah and Turning the Cloak","description":"This istisqa hadith focuses on the Prophet صلى الله عليه وسلم going out to ask Allah for rain. He turned his back to the people while praying to Allah, faced the qiblah, turned his cloak, and then offered two rak'ahs. The report also mentions Qur'an recitation in the two rak'ahs, with one version explaining that it was done aloud. For anyone searching for a hadith about prayer for rain, this narration shows that the request for rain was tied to clear acts of worship: facing Allah's direction in prayer, making dua, and praying with the people. It also teaches calm order during a time of need."},"teachings":["The Prophet صلى الله عليه وسلم faced the qiblah while making supplication for rain.","He turned his cloak during the rain prayer.","He offered two rak'ahs after the supplication details mentioned in the report.","The recitation in the prayer is described as aloud in one version."],"related_hadiths":[{"id":"894b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"894c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1023","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E95" s="4" t="n"/>
@@ -2658,7 +2662,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Cloak Reversal in Istisqa","description":"$book_name$ $hadith_number$ - $chapter_name$. Understand the report on turning the cloak during rain supplication, placing each side on the opposite shoulder before dua."},"heading":{"title":"Rain Dua Hadith: Turning the Cloak Before Supplication","description":"This hadith about rain dua is a shorter version of the earlier report. It does not mention the prayer in this version, so the focus stays on the cloak and the supplication. The Prophet صلى الله عليه وسلم turned his cloak by placing the right side on his left shoulder and the left side on his right shoulder. After that, he made supplication to Allah, the Exalted. For people searching for turning cloak in istisqa, this narration gives a specific detail about how the cloak was changed. It reminds us to read each report carefully: some narrations mention the prayer, while this one highlights the cloak reversal and dua."},"teachings":["This version does not mention the prayer, so its main detail is the cloak reversal.","The right side of the cloak was placed on the left shoulder.","The left side of the cloak was placed on the right shoulder.","The supplication to Allah came after the cloak was turned."],"related_hadiths":[{"id":"894a","book_id":"2","label":"Sahih Muslim"},{"id":"894c","book_id":"2","label":"Sahih Muslim"},{"id":"1027","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Cloak Reversal in Istisqa","description":"$book_name$ $hadith_number$ - $chapter_name$. Understand the report on turning the cloak during rain supplication, placing each side on the opposite shoulder before dua."},"heading":{"title":"Rain Dua Hadith: Turning the Cloak Before Supplication","description":"This hadith about rain dua is a shorter version of the earlier report. It does not mention the prayer in this version, so the focus stays on the cloak and the supplication. The Prophet صلى الله عليه وسلم turned his cloak by placing the right side on his left shoulder and the left side on his right shoulder. After that, he made supplication to Allah, the Exalted. For people searching for turning cloak in istisqa, this narration gives a specific detail about how the cloak was changed. It reminds us to read each report carefully: some narrations mention the prayer, while this one highlights the cloak reversal and dua."},"teachings":["This version does not mention the prayer, so its main detail is the cloak reversal.","The right side of the cloak was placed on the left shoulder.","The left side of the cloak was placed on the right shoulder.","The supplication to Allah came after the cloak was turned."],"related_hadiths":[{"id":"894a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"894c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E96" s="4" t="n"/>
@@ -2681,7 +2685,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Cloak in Istisqa","description":"$book_name$ $hadith_number$ - $chapter_name$. Explore how the Prophet صلى الله عليه وسلم prayed for rain wearing a black robe and turned it on his shoulders when it was too heavy."},"heading":{"title":"Istisqa Prayer Hadith: The Black Cloak and Rain Supplication","description":"This prayer for rain hadith gives a small but vivid detail from the istisqa prayer. The Messenger of Allah صلى الله عليه وسلم prayed for rain while wearing a black robe with an ornamented border. He wanted to reverse it from bottom to top by holding the lower part, but it was too heavy. So he turned it around on his shoulders instead. The narration is about a real action during the rain prayer, not a long speech or ruling. It shows the Prophet صلى الله عليه وسلم making an effort to turn the garment, then doing what was possible when the robe was heavy. The focus remains on humble supplication for rain."},"teachings":["The Prophet صلى الله عليه وسلم prayed for rain while wearing a black robe with a border.","He intended to reverse the robe from bottom to top.","When the robe was too heavy, he turned it on his shoulders.","The report connects the cloak movement with the rain prayer."],"related_hadiths":[{"id":"894a","book_id":"2","label":"Sahih Muslim"},{"id":"1027","book_id":"1","label":"Sahih Bukhari"},{"id":"1023","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Cloak in Istisqa","description":"$book_name$ $hadith_number$ - $chapter_name$. Explore how the Prophet صلى الله عليه وسلم prayed for rain wearing a black robe and turned it on his shoulders when it was too heavy."},"heading":{"title":"Istisqa Prayer Hadith: The Black Cloak and Rain Supplication","description":"This prayer for rain hadith gives a small but vivid detail from the istisqa prayer. The Messenger of Allah صلى الله عليه وسلم prayed for rain while wearing a black robe with an ornamented border. He wanted to reverse it from bottom to top by holding the lower part, but it was too heavy. So he turned it around on his shoulders instead. The narration is about a real action during the rain prayer, not a long speech or ruling. It shows the Prophet صلى الله عليه وسلم making an effort to turn the garment, then doing what was possible when the robe was heavy. The focus remains on humble supplication for rain."},"teachings":["The Prophet صلى الله عليه وسلم prayed for rain while wearing a black robe with a border.","He intended to reverse the robe from bottom to top.","When the robe was too heavy, he turned it on his shoulders.","The report connects the cloak movement with the rain prayer."],"related_hadiths":[{"id":"894a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1023","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E97" s="4" t="n"/>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Humility in Prayer for Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم went out humbly for rain prayer, made dua, said takbir, and prayed two rak'ahs like Eid prayer."},"heading":{"title":"Istisqa Prayer Hadith: Humility, Dua, Takbir, and Two Rak'ahs","description":"This istisqa prayer hadith centers on humility before Allah. Ibn Abbas described that the Messenger of Allah صلى الله عليه وسلم went out wearing old clothes, in a humble and lowly manner, until he reached the place of prayer. He ascended the pulpit, but the report says he did not deliver the usual kind of sermon. Instead, he kept making dua, showing humbleness to Allah, and saying takbir. Then he prayed two rak'ahs as done on Eid. For anyone searching how to pray istisqa, this narration gives simple markers from the text: humility, supplication, takbir, and two rak'ahs. The mood is need, not display."},"teachings":["The Prophet صلى الله عليه وسلم went out in a humble and lowly manner.","He remained engaged in dua, humbleness, and takbir.","The report says he did not give the usual form of sermon.","He prayed two rak'ahs like the Eid prayer."],"related_hadiths":[{"id":"894a","book_id":"2","label":"Sahih Muslim"},{"id":"1023","book_id":"1","label":"Sahih Bukhari"},{"id":"1027","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Humility in Prayer for Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم went out humbly for rain prayer, made dua, said takbir, and prayed two rak'ahs like Eid prayer."},"heading":{"title":"Istisqa Prayer Hadith: Humility, Dua, Takbir, and Two Rak'ahs","description":"This istisqa prayer hadith centers on humility before Allah. Ibn Abbas described that the Messenger of Allah صلى الله عليه وسلم went out wearing old clothes, in a humble and lowly manner, until he reached the place of prayer. He ascended the pulpit, but the report says he did not deliver the usual kind of sermon. Instead, he kept making dua, showing humbleness to Allah, and saying takbir. Then he prayed two rak'ahs as done on Eid. For anyone searching how to pray istisqa, this narration gives simple markers from the text: humility, supplication, takbir, and two rak'ahs. The mood is need, not display."},"teachings":["The Prophet صلى الله عليه وسلم went out in a humble and lowly manner.","He remained engaged in dua, humbleness, and takbir.","The report says he did not give the usual form of sermon.","He prayed two rak'ahs like the Eid prayer."],"related_hadiths":[{"id":"894a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1023","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E98" s="4" t="n"/>
@@ -2727,7 +2731,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Turning the Cloak While Facing Qiblah","description":"$book_name$ $hadith_number$ - $chapter_name$. Read how the Prophet صلى الله عليه وسلم went to the prayer place, asked for rain, faced the qiblah, and turned his cloak."},"heading":{"title":"Istisqa Hadith: Turning the Cloak When Facing the Qiblah","description":"This istisqa hadith gives a short report from Abdullah b. Zaid al-Mazini. The Messenger of Allah صلى الله عليه وسلم went out to the place of prayer, made supplication for rain, and turned his cloak when he faced the qiblah. The hadith about rain prayer is not long, but it ties together three clear actions: going out, asking Allah for rain, and turning the cloak while facing the qiblah. It is a useful narration for readers who want a simple text on the rain prayer practice. The meaning is easy to understand: in need, the Prophet صلى الله عليه وسلم turned to Allah with a visible act of supplication."},"teachings":["The Prophet صلى الله عليه وسلم went out to the place of prayer.","He made supplication for rain.","He faced the qiblah during the act mentioned in the report.","He turned his cloak when facing the qiblah."],"related_hadiths":[{"id":"894a","book_id":"2","label":"Sahih Muslim"},{"id":"894c","book_id":"2","label":"Sahih Muslim"},{"id":"1027","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Turning the Cloak While Facing Qiblah","description":"$book_name$ $hadith_number$ - $chapter_name$. Read how the Prophet صلى الله عليه وسلم went to the prayer place, asked for rain, faced the qiblah, and turned his cloak."},"heading":{"title":"Istisqa Hadith: Turning the Cloak When Facing the Qiblah","description":"This istisqa hadith gives a short report from Abdullah b. Zaid al-Mazini. The Messenger of Allah صلى الله عليه وسلم went out to the place of prayer, made supplication for rain, and turned his cloak when he faced the qiblah. The hadith about rain prayer is not long, but it ties together three clear actions: going out, asking Allah for rain, and turning the cloak while facing the qiblah. It is a useful narration for readers who want a simple text on the rain prayer practice. The meaning is easy to understand: in need, the Prophet صلى الله عليه وسلم turned to Allah with a visible act of supplication."},"teachings":["The Prophet صلى الله عليه وسلم went out to the place of prayer.","He made supplication for rain.","He faced the qiblah during the act mentioned in the report.","He turned his cloak when facing the qiblah."],"related_hadiths":[{"id":"894a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"894c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E99" s="4" t="n"/>
@@ -2750,7 +2754,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Raising Hands in Dua for Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم prayed for rain standing at Ahjar az-Zayt, raising his hands before his face without exceeding his head."},"heading":{"title":"Dua for Rain Hadith: Raising the Hands Before the Face","description":"This dua for rain hadith reports what Umayr saw at Ahjar az-Zayt near az-Zawra'. The Prophet صلى الله عليه وسلم was standing, making supplication, praying for rain, and raising his hands in front of his face. The report adds that he did not lift them above his head. For readers searching raising hands in dua for rain, this narration gives a clear physical description from one sighting. It does not speak about every form of dua; it only describes this scene of istisqa. The teaching is focused and simple: the Prophet صلى الله عليه وسلم asked Allah for rain while standing and raising his hands with a measured posture."},"teachings":["The Prophet صلى الله عليه وسلم was seen standing while making supplication for rain.","He raised his hands in front of his face.","In this report, his hands did not go above his head.","The location mentioned is Ahjar az-Zayt near az-Zawra'."],"related_hadiths":[{"id":"1023","book_id":"1","label":"Sahih Bukhari"},{"id":"894a","book_id":"2","label":"Sahih Muslim"},{"id":"894b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Raising Hands in Dua for Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم prayed for rain standing at Ahjar az-Zayt, raising his hands before his face without exceeding his head."},"heading":{"title":"Dua for Rain Hadith: Raising the Hands Before the Face","description":"This dua for rain hadith reports what Umayr saw at Ahjar az-Zayt near az-Zawra'. The Prophet صلى الله عليه وسلم was standing, making supplication, praying for rain, and raising his hands in front of his face. The report adds that he did not lift them above his head. For readers searching raising hands in dua for rain, this narration gives a clear physical description from one sighting. It does not speak about every form of dua; it only describes this scene of istisqa. The teaching is focused and simple: the Prophet صلى الله عليه وسلم asked Allah for rain while standing and raising his hands with a measured posture."},"teachings":["The Prophet صلى الله عليه وسلم was seen standing while making supplication for rain.","He raised his hands in front of his face.","In this report, his hands did not go above his head.","The location mentioned is Ahjar az-Zayt near az-Zawra'."],"related_hadiths":[{"id":"1023","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"894a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"894b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E100" s="4" t="n"/>
@@ -2773,7 +2777,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Beautiful Dua for Beneficial Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the Prophet's صلى الله عليه وسلم supplication asking Allah for replenishing, abundant, useful rain that comes without harm or delay."},"heading":{"title":"Dua for Rain Hadith: Asking Allah for Beneficial Rain","description":"This dua for rain hadith carries a moving scene. The people came to the Prophet صلى الله عليه وسلم weeping because of drought. He asked Allah for rain that would replenish them, be abundant, fertilising, profitable, not harmful, and come without delay. The report then says the sky became overcast. For someone searching for beneficial rain dua, this narration teaches us to ask not only for rain, but for rain that helps and does not harm. The words in the hadith are balanced: they ask for need, benefit, and safety together. It is a strong reminder that even natural relief is sought from Allah with care and humility."},"teachings":["The people came weeping due to drought.","The Prophet صلى الله عليه وسلم asked Allah for rain that would benefit them.","The supplication asked for rain that was not injurious.","The report says the sky became overcast after the dua."],"related_hadiths":[{"id":"1017","book_id":"1","label":"Sahih Bukhari"},{"id":"1020","book_id":"1","label":"Sahih Bukhari"},{"id":"897b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Beautiful Dua for Beneficial Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the Prophet's صلى الله عليه وسلم supplication asking Allah for replenishing, abundant, useful rain that comes without harm or delay."},"heading":{"title":"Dua for Rain Hadith: Asking Allah for Beneficial Rain","description":"This dua for rain hadith carries a moving scene. The people came to the Prophet صلى الله عليه وسلم weeping because of drought. He asked Allah for rain that would replenish them, be abundant, fertilising, profitable, not harmful, and come without delay. The report then says the sky became overcast. For someone searching for beneficial rain dua, this narration teaches us to ask not only for rain, but for rain that helps and does not harm. The words in the hadith are balanced: they ask for need, benefit, and safety together. It is a strong reminder that even natural relief is sought from Allah with care and humility."},"teachings":["The people came weeping due to drought.","The Prophet صلى الله عليه وسلم asked Allah for rain that would benefit them.","The supplication asked for rain that was not injurious.","The report says the sky became overcast after the dua."],"related_hadiths":[{"id":"1017","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1020","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"897b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E101" s="4" t="n"/>
@@ -2796,7 +2800,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | High Raising of Hands in Istisqa","description":"$book_name$ $hadith_number$ - $chapter_name$. Discover how the Prophet صلى الله عليه وسلم raised his hands high in supplication specifically when praying for rain."},"heading":{"title":"Raising Hands in Dua for Rain: A Hadith on Istisqa","description":"This hadith about raising hands in dua for rain gives a clear statement from Anas. He reported that the Prophet صلى الله عليه وسلم was not accustomed to raise his hands in any supplication he made except when praying for rain. In istisqa, he would raise them high enough that the whiteness of his armpits was visible. The wording is about the Prophet's practice as Anas saw and described it. For readers searching istisqa prayer hadith, this narration shows that rain supplication had a special visible form in this report. It also reminds us that asking Allah for rain was done with deep need and open, raised hands."},"teachings":["Anas reported a special raising of hands during prayer for rain.","The Prophet صلى الله عليه وسلم raised his hands high in istisqa.","The report describes the whiteness of his armpits becoming visible.","The narration focuses on the manner of supplication."],"related_hadiths":[{"id":"1023","book_id":"1","label":"Sahih Bukhari"},{"id":"894a","book_id":"2","label":"Sahih Muslim"},{"id":"894b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | High Raising of Hands in Istisqa","description":"$book_name$ $hadith_number$ - $chapter_name$. Discover how the Prophet صلى الله عليه وسلم raised his hands high in supplication specifically when praying for rain."},"heading":{"title":"Raising Hands in Dua for Rain: A Hadith on Istisqa","description":"This hadith about raising hands in dua for rain gives a clear statement from Anas. He reported that the Prophet صلى الله عليه وسلم was not accustomed to raise his hands in any supplication he made except when praying for rain. In istisqa, he would raise them high enough that the whiteness of his armpits was visible. The wording is about the Prophet's practice as Anas saw and described it. For readers searching istisqa prayer hadith, this narration shows that rain supplication had a special visible form in this report. It also reminds us that asking Allah for rain was done with deep need and open, raised hands."},"teachings":["Anas reported a special raising of hands during prayer for rain.","The Prophet صلى الله عليه وسلم raised his hands high in istisqa.","The report describes the whiteness of his armpits becoming visible.","The narration focuses on the manner of supplication."],"related_hadiths":[{"id":"1023","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"894a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"894b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E102" s="4" t="n"/>
@@ -2819,7 +2823,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Spreading Hands During Rain Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم made rain supplication by spreading his hands with the inner sides toward the earth."},"heading":{"title":"Dua for Rain Hadith: Spreading the Hands Toward the Earth","description":"This dua for rain hadith adds another description from Anas. He said the Prophet صلى الله عليه وسلم used to make supplication for rain in this manner: he spread his hands and kept the inner side of the hands toward the earth, until Anas saw the whiteness of his armpits. The report is very specific about the hand position during istisqa. It is not a general lesson about every dua; it is about this manner of asking Allah for rain. For readers looking for how the Prophet made dua for rain, this narration highlights the physical form of the supplication: hands spread, palms directed downward, and raised with need."},"teachings":["The Prophet صلى الله عليه وسلم spread his hands while making rain supplication.","The inner sides of the hands were toward the earth.","Anas saw the whiteness of his armpits during the raising.","The report describes the manner of istisqa dua."],"related_hadiths":[{"id":"1023","book_id":"1","label":"Sahih Bukhari"},{"id":"894a","book_id":"2","label":"Sahih Muslim"},{"id":"894c","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Spreading Hands During Rain Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم made rain supplication by spreading his hands with the inner sides toward the earth."},"heading":{"title":"Dua for Rain Hadith: Spreading the Hands Toward the Earth","description":"This dua for rain hadith adds another description from Anas. He said the Prophet صلى الله عليه وسلم used to make supplication for rain in this manner: he spread his hands and kept the inner side of the hands toward the earth, until Anas saw the whiteness of his armpits. The report is very specific about the hand position during istisqa. It is not a general lesson about every dua; it is about this manner of asking Allah for rain. For readers looking for how the Prophet made dua for rain, this narration highlights the physical form of the supplication: hands spread, palms directed downward, and raised with need."},"teachings":["The Prophet صلى الله عليه وسلم spread his hands while making rain supplication.","The inner sides of the hands were toward the earth.","Anas saw the whiteness of his armpits during the raising.","The report describes the manner of istisqa dua."],"related_hadiths":[{"id":"1023","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"894a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"894c","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E103" s="4" t="n"/>
@@ -2842,7 +2846,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Open Palms in Supplication","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the report of the Prophet صلى الله عليه وسلم praying at Ahjar al-Zait while spreading his hands in supplication."},"heading":{"title":"Rain Supplication Hadith: The Prophet صلى الله عليه وسلم Spreading His Hands","description":"This rain supplication hadith is short, but it gives a clear scene. Muhammad b. Ibrahim reported from a man who witnessed the Prophet صلى الله عليه وسلم that he saw him praying at Ahjar al-Zait while spreading his hands. The report does not give a long sermon, a full prayer format, or a detailed dua. It simply records what was seen: the Prophet صلى الله عليه وسلم in prayer and supplication with his hands spread. For people searching dua for rain hadith, this narration supports the idea that raised or spread hands were part of the visible manner in these reports. It is best read as a focused witness statement."},"teachings":["A witness saw the Prophet صلى الله عليه وسلم praying at Ahjar al-Zait.","The Prophet صلى الله عليه وسلم was spreading his hands.","The report is brief and limited to what the witness saw.","The narration connects supplication with an open-handed posture."],"related_hadiths":[{"id":"1023","book_id":"1","label":"Sahih Bukhari"},{"id":"894a","book_id":"2","label":"Sahih Muslim"},{"id":"894b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Open Palms in Supplication","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the report of the Prophet صلى الله عليه وسلم praying at Ahjar al-Zait while spreading his hands in supplication."},"heading":{"title":"Rain Supplication Hadith: The Prophet صلى الله عليه وسلم Spreading His Hands","description":"This rain supplication hadith is short, but it gives a clear scene. Muhammad b. Ibrahim reported from a man who witnessed the Prophet صلى الله عليه وسلم that he saw him praying at Ahjar al-Zait while spreading his hands. The report does not give a long sermon, a full prayer format, or a detailed dua. It simply records what was seen: the Prophet صلى الله عليه وسلم in prayer and supplication with his hands spread. For people searching dua for rain hadith, this narration supports the idea that raised or spread hands were part of the visible manner in these reports. It is best read as a focused witness statement."},"teachings":["A witness saw the Prophet صلى الله عليه وسلم praying at Ahjar al-Zait.","The Prophet صلى الله عليه وسلم was spreading his hands.","The report is brief and limited to what the witness saw.","The narration connects supplication with an open-handed posture."],"related_hadiths":[{"id":"1023","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"894a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"894b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E104" s="4" t="n"/>
@@ -2865,7 +2869,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Complete Rain Prayer Scene","description":"$book_name$ $hadith_number$ - $chapter_name$. Study the Prophet's صلى الله عليه وسلم rain prayer: public gathering, praise of Allah, dua, raised hands, turned cloak, two rak'ahs, and rainfall."},"heading":{"title":"Istisqa Prayer Hadith: Public Dua, Two Rak'ahs, and Rain","description":"This istisqa prayer hadith gives a fuller scene of the prayer for rain. The people complained of lack of rain, so the Prophet صلى الله عليه وسلم fixed a day for them to come out. He sat on the pulpit, said takbir, praised Allah, and reminded them that Allah ordered them to supplicate Him and promised to answer. He made dua, raised his hands until the whiteness under his armpits was visible, turned his back to the people, turned his cloak while keeping his hands raised, then prayed two rak'ahs. The report says Allah produced a cloud, thunder and lightning came, and rain fell by Allah's permission. The core message is need, worship, and reliance on Allah."},"teachings":["The people brought their complaint of drought to the Prophet صلى الله عليه وسلم.","He praised Allah, made dua, raised his hands, and turned his cloak.","He prayed two rak'ahs after descending from the pulpit.","The report says rain came by Allah's permission."],"related_hadiths":[{"id":"894a","book_id":"2","label":"Sahih Muslim"},{"id":"1023","book_id":"1","label":"Sahih Bukhari"},{"id":"1027","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Complete Rain Prayer Scene","description":"$book_name$ $hadith_number$ - $chapter_name$. Study the Prophet's صلى الله عليه وسلم rain prayer: public gathering, praise of Allah, dua, raised hands, turned cloak, two rak'ahs, and rainfall."},"heading":{"title":"Istisqa Prayer Hadith: Public Dua, Two Rak'ahs, and Rain","description":"This istisqa prayer hadith gives a fuller scene of the prayer for rain. The people complained of lack of rain, so the Prophet صلى الله عليه وسلم fixed a day for them to come out. He sat on the pulpit, said takbir, praised Allah, and reminded them that Allah ordered them to supplicate Him and promised to answer. He made dua, raised his hands until the whiteness under his armpits was visible, turned his back to the people, turned his cloak while keeping his hands raised, then prayed two rak'ahs. The report says Allah produced a cloud, thunder and lightning came, and rain fell by Allah's permission. The core message is need, worship, and reliance on Allah."},"teachings":["The people brought their complaint of drought to the Prophet صلى الله عليه وسلم.","He praised Allah, made dua, raised his hands, and turned his cloak.","He prayed two rak'ahs after descending from the pulpit.","The report says rain came by Allah's permission."],"related_hadiths":[{"id":"894a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1023","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E105" s="4" t="n"/>
@@ -2888,7 +2892,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Rain and Relief from Excess Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم prayed for rain during drought, then asked Allah to move the rain around Medina when harm was feared."},"heading":{"title":"Dua for Rain Hadith: Around Us and Not Upon Us","description":"This hadith about dua for rain begins with drought in Medina. While the Prophet صلى الله عليه وسلم was preaching on Friday, a man stood and asked him to pray to Allah for water because livestock had perished. The Prophet صلى الله عليه وسلم spread his hands and prayed. The sky had been clear, then wind and clouds came, and rain poured until people walked through water to their homes. The rain continued until the next Friday. When harm to houses was mentioned, the Prophet صلى الله عليه وسلم smiled and said, \"Around us and not upon us.\" The cloud then dispersed around Medina like a crown. The hadith teaches asking Allah for help and also asking for relief when rain becomes harmful."},"teachings":["The people asked the Prophet صلى الله عليه وسلم to pray for rain during drought.","He spread his hands and made dua.","When damage was feared, he asked for rain around them, not upon them.","The report describes the clouds dispersing around Medina."],"related_hadiths":[{"id":"1020","book_id":"1","label":"Sahih Bukhari"},{"id":"1017","book_id":"1","label":"Sahih Bukhari"},{"id":"897b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Rain and Relief from Excess Rain","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم prayed for rain during drought, then asked Allah to move the rain around Medina when harm was feared."},"heading":{"title":"Dua for Rain Hadith: Around Us and Not Upon Us","description":"This hadith about dua for rain begins with drought in Medina. While the Prophet صلى الله عليه وسلم was preaching on Friday, a man stood and asked him to pray to Allah for water because livestock had perished. The Prophet صلى الله عليه وسلم spread his hands and prayed. The sky had been clear, then wind and clouds came, and rain poured until people walked through water to their homes. The rain continued until the next Friday. When harm to houses was mentioned, the Prophet صلى الله عليه وسلم smiled and said, \"Around us and not upon us.\" The cloud then dispersed around Medina like a crown. The hadith teaches asking Allah for help and also asking for relief when rain becomes harmful."},"teachings":["The people asked the Prophet صلى الله عليه وسلم to pray for rain during drought.","He spread his hands and made dua.","When damage was feared, he asked for rain around them, not upon them.","The report describes the clouds dispersing around Medina."],"related_hadiths":[{"id":"1020","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1017","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"897b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E106" s="4" t="n"/>
@@ -2911,7 +2915,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allahumma Asqina in Rain Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the narration where the Prophet صلى الله عليه وسلم raised his hands before his face and said: O Allah, give us water."},"heading":{"title":"Dua for Rain Hadith: Allahumma Asqina and Raised Hands","description":"This rain dua hadith is a shorter route for the same general event reported from Anas. It says the Messenger of Allah صلى الله عليه وسلم raised his hands in front of his face and said, \"O Allah! Give us water.\" The narrator then continued with wording like the previous report. For people searching Allahumma asqina hadith, this narration is easy to remember because the dua is short and direct. The Prophet صلى الله عليه وسلم asked Allah for water in a time of need. The report also mentions the hand position: raised in front of his face. The lesson stays simple: turn to Allah, ask clearly, and seek relief through supplication."},"teachings":["The Prophet صلى الله عليه وسلم raised his hands in front of his face.","He said, \"O Allah! Give us water.\"","The report is connected to the earlier rain event narrated by Anas.","The wording shows a short and direct supplication."],"related_hadiths":[{"id":"1017","book_id":"1","label":"Sahih Bukhari"},{"id":"1020","book_id":"1","label":"Sahih Bukhari"},{"id":"897b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allahumma Asqina in Rain Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the narration where the Prophet صلى الله عليه وسلم raised his hands before his face and said: O Allah, give us water."},"heading":{"title":"Dua for Rain Hadith: Allahumma Asqina and Raised Hands","description":"This rain dua hadith is a shorter route for the same general event reported from Anas. It says the Messenger of Allah صلى الله عليه وسلم raised his hands in front of his face and said, \"O Allah! Give us water.\" The narrator then continued with wording like the previous report. For people searching Allahumma asqina hadith, this narration is easy to remember because the dua is short and direct. The Prophet صلى الله عليه وسلم asked Allah for water in a time of need. The report also mentions the hand position: raised in front of his face. The lesson stays simple: turn to Allah, ask clearly, and seek relief through supplication."},"teachings":["The Prophet صلى الله عليه وسلم raised his hands in front of his face.","He said, \"O Allah! Give us water.\"","The report is connected to the earlier rain event narrated by Anas.","The wording shows a short and direct supplication."],"related_hadiths":[{"id":"1017","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1020","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"897b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E107" s="4" t="n"/>
@@ -2934,7 +2938,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mercy for Servants, Animals, and Land","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the Prophet's صلى الله عليه وسلم rain supplication asking Allah to water servants and cattle, spread mercy, and revive dead land."},"heading":{"title":"Dua for Rain Hadith: Mercy for People, Animals, and Dead Land","description":"This dua for rain hadith gives a beautiful wording from the Prophet صلى الله عليه وسلم when he prayed for rain. He said, \"O Allah! Provide water for Your servants and Your cattle, display Your mercy and give life to Your dead land.\" The wording is broad and caring. It asks Allah for water not only for people, but also for animals and the land. For readers searching Islamic dua for rain, this narration shows how rain is linked with mercy, life, and provision. The hadith does not add a long event around the dua; its focus is the supplication itself. It teaches us to ask Allah for benefit that reaches creation around us."},"teachings":["The supplication asks Allah to provide water for His servants.","It also mentions cattle, showing concern for animals.","The dua asks Allah to display His mercy.","It asks for dead land to be given life."],"related_hadiths":[{"id":"1017","book_id":"1","label":"Sahih Bukhari"},{"id":"894a","book_id":"2","label":"Sahih Muslim"},{"id":"1023","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mercy for Servants, Animals, and Land","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the Prophet's صلى الله عليه وسلم rain supplication asking Allah to water servants and cattle, spread mercy, and revive dead land."},"heading":{"title":"Dua for Rain Hadith: Mercy for People, Animals, and Dead Land","description":"This dua for rain hadith gives a beautiful wording from the Prophet صلى الله عليه وسلم when he prayed for rain. He said, \"O Allah! Provide water for Your servants and Your cattle, display Your mercy and give life to Your dead land.\" The wording is broad and caring. It asks Allah for water not only for people, but also for animals and the land. For readers searching Islamic dua for rain, this narration shows how rain is linked with mercy, life, and provision. The hadith does not add a long event around the dua; its focus is the supplication itself. It teaches us to ask Allah for benefit that reaches creation around us."},"teachings":["The supplication asks Allah to provide water for His servants.","It also mentions cattle, showing concern for animals.","The dua asks Allah to display His mercy.","It asks for dead land to be given life."],"related_hadiths":[{"id":"1017","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"894a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1023","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E108" s="4" t="n"/>
@@ -2957,7 +2961,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hasten to Prayer During Eclipse","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم prayed during a solar eclipse and taught that the sun and moon are signs of Allah, not tied to birth or death."},"heading":{"title":"Eclipse Prayer Hadith: The Sun and Moon Are Signs of Allah","description":"This eclipse prayer hadith reports a solar eclipse during the time of the Prophet صلى الله عليه وسلم. He stood with the people for a long time, bowed, rose, bowed again, rose again, and bowed again in each rak'ah before prostrating. The standing was so long that some people became unconscious and water was poured on them. After the sun became bright, he taught that the sun and moon are not eclipsed because of anyone's death or birth. They are two signs of Allah, and when they are eclipsed, people should hasten to prayer. For readers searching sun eclipse hadith, the main teaching is to respond with prayer, not superstition."},"teachings":["The Prophet صلى الله عليه وسلم led a long prayer during the solar eclipse.","The report describes three bowings in each rak'ah.","He rejected linking eclipses to anyone's death or birth.","He taught people to hasten to prayer during an eclipse."],"related_hadiths":[{"id":"1057","book_id":"1","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hasten to Prayer During Eclipse","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم prayed during a solar eclipse and taught that the sun and moon are signs of Allah, not tied to birth or death."},"heading":{"title":"Eclipse Prayer Hadith: The Sun and Moon Are Signs of Allah","description":"This eclipse prayer hadith reports a solar eclipse during the time of the Prophet صلى الله عليه وسلم. He stood with the people for a long time, bowed, rose, bowed again, rose again, and bowed again in each rak'ah before prostrating. The standing was so long that some people became unconscious and water was poured on them. After the sun became bright, he taught that the sun and moon are not eclipsed because of anyone's death or birth. They are two signs of Allah, and when they are eclipsed, people should hasten to prayer. For readers searching sun eclipse hadith, the main teaching is to respond with prayer, not superstition."},"teachings":["The Prophet صلى الله عليه وسلم led a long prayer during the solar eclipse.","The report describes three bowings in each rak'ah.","He rejected linking eclipses to anyone's death or birth.","He taught people to hasten to prayer during an eclipse."],"related_hadiths":[{"id":"1057","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E109" s="4" t="n"/>
@@ -2980,7 +2984,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Until the Eclipse Clears","description":"$book_name$ $hadith_number$ - $chapter_name$. See how the Prophet صلى الله عليه وسلم corrected the idea that an eclipse happened because of death and told people to pray until it clears."},"heading":{"title":"Sun Eclipse Hadith: Pray Until the Eclipse Becomes Clear","description":"This sun eclipse hadith reports that an eclipse happened on the day Ibrahim, the son of the Prophet صلى الله عليه وسلم, died. Some people said the eclipse was because of Ibrahim's death. The Prophet صلى الله عليه وسلم then led the people in a long eclipse prayer with repeated recitation, bowing, and prostration. After the prayer, when the sun had become bright, he said that the sun and moon are two signs of Allah and are not eclipsed because of a person's death. He told the people to pray until the eclipse clears. The key message is clear: a believer answers an eclipse with prayer and remembrance, not false explanations."},"teachings":["The eclipse happened on the day Ibrahim died, according to the report.","The Prophet صلى الله عليه وسلم corrected the claim that the eclipse was caused by a death.","He led the people in a long prayer with repeated bowings and prostrations.","He told people to pray until the eclipse clears."],"related_hadiths":[{"id":"1060","book_id":"1","label":"Sahih Bukhari"},{"id":"1063","book_id":"1","label":"Sahih Bukhari"},{"id":"911a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Until the Eclipse Clears","description":"$book_name$ $hadith_number$ - $chapter_name$. See how the Prophet صلى الله عليه وسلم corrected the idea that an eclipse happened because of death and told people to pray until it clears."},"heading":{"title":"Sun Eclipse Hadith: Pray Until the Eclipse Becomes Clear","description":"This sun eclipse hadith reports that an eclipse happened on the day Ibrahim, the son of the Prophet صلى الله عليه وسلم, died. Some people said the eclipse was because of Ibrahim's death. The Prophet صلى الله عليه وسلم then led the people in a long eclipse prayer with repeated recitation, bowing, and prostration. After the prayer, when the sun had become bright, he said that the sun and moon are two signs of Allah and are not eclipsed because of a person's death. He told the people to pray until the eclipse clears. The key message is clear: a believer answers an eclipse with prayer and remembrance, not false explanations."},"teachings":["The eclipse happened on the day Ibrahim died, according to the report.","The Prophet صلى الله عليه وسلم corrected the claim that the eclipse was caused by a death.","He led the people in a long prayer with repeated bowings and prostrations.","He told people to pray until the eclipse clears."],"related_hadiths":[{"id":"1060","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1063","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"911a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E110" s="4" t="n"/>
@@ -3003,7 +3007,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Long Standing in Eclipse Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Read how the Prophet صلى الله عليه وسلم led a long eclipse prayer on a hot day with extended standing, bowing, and prostration."},"heading":{"title":"Eclipse Prayer Hadith: Long Standing, Bowing, and Prostration","description":"This eclipse prayer hadith from Jabir describes a solar eclipse on a very hot day. The Messenger of Allah صلى الله عليه وسلم led his Companions in prayer and made the standing long until people began to fall down. He then bowed for a long time, rose and remained standing, bowed again for a long time, rose again, then made two prostrations. He stood and did in the same manner again, making four bowings and four prostrations in total. For readers searching how eclipse prayer is prayed, this report highlights length, seriousness, and repeated bowing. It shows that the eclipse prayer was treated as a serious act of worship."},"teachings":["The eclipse prayer happened on a very hot day.","The Prophet صلى الله عليه وسلم prolonged the standing and bowing.","The report describes four bowings and four prostrations.","The Companions prayed behind him during the eclipse."],"related_hadiths":[{"id":"1057","book_id":"1","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","label":"Sahih Muslim"},{"id":"1060","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Long Standing in Eclipse Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Read how the Prophet صلى الله عليه وسلم led a long eclipse prayer on a hot day with extended standing, bowing, and prostration."},"heading":{"title":"Eclipse Prayer Hadith: Long Standing, Bowing, and Prostration","description":"This eclipse prayer hadith from Jabir describes a solar eclipse on a very hot day. The Messenger of Allah صلى الله عليه وسلم led his Companions in prayer and made the standing long until people began to fall down. He then bowed for a long time, rose and remained standing, bowed again for a long time, rose again, then made two prostrations. He stood and did in the same manner again, making four bowings and four prostrations in total. For readers searching how eclipse prayer is prayed, this report highlights length, seriousness, and repeated bowing. It shows that the eclipse prayer was treated as a serious act of worship."},"teachings":["The eclipse prayer happened on a very hot day.","The Prophet صلى الله عليه وسلم prolonged the standing and bowing.","The report describes four bowings and four prostrations.","The Companions prayed behind him during the eclipse."],"related_hadiths":[{"id":"1057","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1060","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E111" s="4" t="n"/>
@@ -3026,7 +3030,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu Method","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes Abdullah bin Zaid showing the Messenger’s wudu, including wiping the head front and back."},"heading":{"title":"Abdullah bin Zaid Wudu Hadith: How the Prophet Performed Ablution","description":"This Hadith is a key match for “Abdullah bin Zaid wudu hadith.” A person asked whether ‘Abd Allah b. Zaid could show how the Messenger of Allah صلى الله عليه وسلم performed ablution. He agreed and called for water. He washed the hands, rinsed the mouth and snuffed water three times, washed the face three times, washed the forearms up to the elbows twice, wiped the head with both hands from front to back and back to the starting place, then washed the feet. The Hadith is valuable because it is a direct demonstration. It gives searchers of “how to perform wudu step by step” a clear sequence from the narration itself."},"teachings":["Abdullah bin Zaid taught wudu by showing it.","The report mentions mouth and nose cleansing three times.","The forearms are mentioned as washed twice in this narration.","The head wipe is described from front to back and back again."],"related_hadiths":[{"id":"186","book_id":"1","label":"Sahih Bukhari"},{"id":"192","book_id":"1","label":"Sahih Bukhari"},{"id":"235a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu Method","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes Abdullah bin Zaid showing the Messenger’s wudu, including wiping the head front and back."},"heading":{"title":"Abdullah bin Zaid Wudu Hadith: How the Prophet Performed Ablution","description":"This Hadith is a key match for “Abdullah bin Zaid wudu hadith.” A person asked whether ‘Abd Allah b. Zaid could show how the Messenger of Allah صلى الله عليه وسلم performed ablution. He agreed and called for water. He washed the hands, rinsed the mouth and snuffed water three times, washed the face three times, washed the forearms up to the elbows twice, wiped the head with both hands from front to back and back to the starting place, then washed the feet. The Hadith is valuable because it is a direct demonstration. It gives searchers of “how to perform wudu step by step” a clear sequence from the narration itself."},"teachings":["Abdullah bin Zaid taught wudu by showing it.","The report mentions mouth and nose cleansing three times.","The forearms are mentioned as washed twice in this narration.","The head wipe is described from front to back and back again."],"related_hadiths":[{"id":"186","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"192","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"235a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E112" s="4" t="n"/>
@@ -3049,7 +3053,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Bowings and Four Prostrations","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the eclipse prayer description from A'ishah: long recitation, long bowing, four bowings, and four prostrations."},"heading":{"title":"Eclipse Prayer Hadith: Four Bowings, Four Prostrations, and Long Recitation","description":"This eclipse prayer hadith from A'ishah gives a careful description of the prayer. During a solar eclipse, the Messenger of Allah صلى الله عليه وسلم came to the mosque, stood, said takbir, and the people lined up behind him. He recited for a long time, bowed for a long time, then rose and said, \"Allah listens to him who praises Him; our Lord, and to Thee be praise.\" He then recited again for a long time, though less than the first, and bowed again, though less than the first bowing. He did the same in the second rak'ah, completing four bowings and four prostrations before the sun became bright."},"teachings":["The Prophet صلى الله عليه وسلم came to the mosque during the eclipse.","The people stood in rows behind him.","The prayer included long recitation and long bowing.","The report states four bowings and four prostrations."],"related_hadiths":[{"id":"1057","book_id":"1","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Bowings and Four Prostrations","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the eclipse prayer description from A'ishah: long recitation, long bowing, four bowings, and four prostrations."},"heading":{"title":"Eclipse Prayer Hadith: Four Bowings, Four Prostrations, and Long Recitation","description":"This eclipse prayer hadith from A'ishah gives a careful description of the prayer. During a solar eclipse, the Messenger of Allah صلى الله عليه وسلم came to the mosque, stood, said takbir, and the people lined up behind him. He recited for a long time, bowed for a long time, then rose and said, \"Allah listens to him who praises Him; our Lord, and to Thee be praise.\" He then recited again for a long time, though less than the first, and bowed again, though less than the first bowing. He did the same in the second rak'ah, completing four bowings and four prostrations before the sun became bright."},"teachings":["The Prophet صلى الله عليه وسلم came to the mosque during the eclipse.","The people stood in rows behind him.","The prayer included long recitation and long bowing.","The report states four bowings and four prostrations."],"related_hadiths":[{"id":"1057","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E113" s="4" t="n"/>
@@ -3072,7 +3076,7 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eclipse Prayer with Two Bowings","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how this hadith describes the Prophet’s solar eclipse prayer with two rak'ahs and two bowings in each rak'ah."},"heading":{"title":"Solar Eclipse Prayer Hadith: Two Bowings in Each Rak'ah","description":"This hadith about eclipse prayer gives a short but clear picture of how the Messenger of Allah صلى الله عليه وسلم prayed during a solar eclipse. Ibn Abbas reports that the prayer matched the narration from Aishah: it was two rak'ahs, and in each rak'ah there were two bowings. The main lesson is simple: when the sun was eclipsed, the Prophet صلى الله عليه وسلم turned to salah. The wording does not add a sermon, charity, or other acts here. It focuses on the form of Salat al-Kusuf, especially the repeated bowing. For anyone searching for solar eclipse prayer hadith, this report shows that the eclipse prayer was not treated like a normal short prayer."},"teachings":["The Prophet صلى الله عليه وسلم prayed during a solar eclipse.","This report describes two rak'ahs in the eclipse prayer.","Each rak'ah included two bowings according to this narration.","The hadith highlights salah as the response mentioned here."],"related_hadiths":[{"id":"1064","book_id":"1","label":"Sahih Bukhari"},{"id":"1065","book_id":"1","label":"Sahih Bukhari"},{"id":"901e","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eclipse Prayer with Two Bowings","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how this hadith describes the Prophet’s solar eclipse prayer with two rak'ahs and two bowings in each rak'ah."},"heading":{"title":"Solar Eclipse Prayer Hadith: Two Bowings in Each Rak'ah","description":"This hadith about eclipse prayer gives a short but clear picture of how the Messenger of Allah صلى الله عليه وسلم prayed during a solar eclipse. Ibn Abbas reports that the prayer matched the narration from Aishah: it was two rak'ahs, and in each rak'ah there were two bowings. The main lesson is simple: when the sun was eclipsed, the Prophet صلى الله عليه وسلم turned to salah. The wording does not add a sermon, charity, or other acts here. It focuses on the form of Salat al-Kusuf, especially the repeated bowing. For anyone searching for solar eclipse prayer hadith, this report shows that the eclipse prayer was not treated like a normal short prayer."},"teachings":["The Prophet صلى الله عليه وسلم prayed during a solar eclipse.","This report describes two rak'ahs in the eclipse prayer.","Each rak'ah included two bowings according to this narration.","The hadith highlights salah as the response mentioned here."],"related_hadiths":[{"id":"1064","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1065","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"901e","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E114" s="4" t="n"/>
@@ -3095,7 +3099,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Long Eclipse Prayer and Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. See how the Prophet صلى الله عليه وسلم led a long eclipse prayer, faced the qiblah, and made supplication until the eclipse ended."},"heading":{"title":"Solar Eclipse Prayer Hadith: Long Recitation, Bowing, and Dua","description":"This solar eclipse prayer hadith shows a long act of worship during the eclipse. Ubayy b. Ka'b says the Prophet صلى الله عليه وسلم led the people in prayer. He recited from one of the long surahs, bowed five times, and made two prostrations. Then he stood for the second rak'ah and did the same: a long recitation, five bowings, and two prostrations. After that, he sat facing the qiblah and made dua until the eclipse was over. The focus of this narration is not a short response, but steady prayer and supplication. It teaches that the sight of an eclipse moved the Prophet صلى الله عليه وسلم and the people toward worship until the sign passed."},"teachings":["The Prophet صلى الله عليه وسلم led the people in prayer during the eclipse.","The narration mentions long Qur'an recitation in both rak'ahs.","He faced the qiblah and made supplication until the eclipse ended.","The hadith connects eclipse prayer with patient worship."],"related_hadiths":[{"id":"1059","book_id":"1","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Long Eclipse Prayer and Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. See how the Prophet صلى الله عليه وسلم led a long eclipse prayer, faced the qiblah, and made supplication until the eclipse ended."},"heading":{"title":"Solar Eclipse Prayer Hadith: Long Recitation, Bowing, and Dua","description":"This solar eclipse prayer hadith shows a long act of worship during the eclipse. Ubayy b. Ka'b says the Prophet صلى الله عليه وسلم led the people in prayer. He recited from one of the long surahs, bowed five times, and made two prostrations. Then he stood for the second rak'ah and did the same: a long recitation, five bowings, and two prostrations. After that, he sat facing the qiblah and made dua until the eclipse was over. The focus of this narration is not a short response, but steady prayer and supplication. It teaches that the sight of an eclipse moved the Prophet صلى الله عليه وسلم and the people toward worship until the sign passed."},"teachings":["The Prophet صلى الله عليه وسلم led the people in prayer during the eclipse.","The narration mentions long Qur'an recitation in both rak'ahs.","He faced the qiblah and made supplication until the eclipse ended.","The hadith connects eclipse prayer with patient worship."],"related_hadiths":[{"id":"1059","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E115" s="4" t="n"/>
@@ -3118,7 +3122,7 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Repeated Recitation and Bowing","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes Qur'an recitation and repeated bowing in the Prophet’s solar eclipse prayer."},"heading":{"title":"Solar Eclipse Prayer Hadith: Recitation Before Each Bowing","description":"This hadith about Salat al-Kusuf gives a clear sequence from the Prophet’s صلى الله عليه وسلم solar eclipse prayer. Ibn Abbas reports that the Prophet صلى الله عليه وسلم recited from the Qur'an, then bowed. He repeated this pattern: recitation, bowing; recitation, bowing; recitation, bowing; then he prostrated. The second rak'ah was performed in a similar way. The wording keeps our attention on recitation and bowing, not on extra details outside the report. For readers looking for how to pray eclipse prayer, this narration shows that Qur'an recitation had a clear place before the bowings. It also shows that the prayer during an eclipse was marked by repeated standing, recitation, and humility."},"teachings":["The Prophet صلى الله عليه وسلم recited Qur'an during the eclipse prayer.","This narration mentions repeated bowing in the first rak'ah.","The second rak'ah was similar to the first.","The hadith keeps the focus on worship during the solar eclipse."],"related_hadiths":[{"id":"1065","book_id":"1","label":"Sahih Bukhari"},{"id":"901e","book_id":"2","label":"Sahih Muslim"},{"id":"1046","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Repeated Recitation and Bowing","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes Qur'an recitation and repeated bowing in the Prophet’s solar eclipse prayer."},"heading":{"title":"Solar Eclipse Prayer Hadith: Recitation Before Each Bowing","description":"This hadith about Salat al-Kusuf gives a clear sequence from the Prophet’s صلى الله عليه وسلم solar eclipse prayer. Ibn Abbas reports that the Prophet صلى الله عليه وسلم recited from the Qur'an, then bowed. He repeated this pattern: recitation, bowing; recitation, bowing; recitation, bowing; then he prostrated. The second rak'ah was performed in a similar way. The wording keeps our attention on recitation and bowing, not on extra details outside the report. For readers looking for how to pray eclipse prayer, this narration shows that Qur'an recitation had a clear place before the bowings. It also shows that the prayer during an eclipse was marked by repeated standing, recitation, and humility."},"teachings":["The Prophet صلى الله عليه وسلم recited Qur'an during the eclipse prayer.","This narration mentions repeated bowing in the first rak'ah.","The second rak'ah was similar to the first.","The hadith keeps the focus on worship during the solar eclipse."],"related_hadiths":[{"id":"1065","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"901e","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1046","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E116" s="4" t="n"/>
@@ -3141,7 +3145,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Silent Long Eclipse Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. A report of the Prophet صلى الله عليه وسلم praying long during a dark solar eclipse, then praising Allah after the sun became clear."},"heading":{"title":"Eclipse Prayer Hadith: Long Silent Standing and Praise of Allah","description":"This eclipse prayer hadith describes a strong scene. Samurah ibn Jundub says he and another boy were shooting arrows when the sun darkened and looked black. They went to the mosque and found the Prophet صلى الله عليه وسلم already out. He led a very long prayer. The narrator says they did not hear his voice during the standing, bowing, or prostration. He did the same in the second rak'ah. The sun became bright when he sat after the second rak'ah. After the salutation, he stood, praised Allah, extolled Him, and testified to Allah’s oneness and to his own mission as Allah’s servant and Messenger. The report highlights prayer, patience, and praise."},"teachings":["The Companions went to the mosque when the sun darkened.","The Prophet صلى الله عليه وسلم prayed with very long standing, bowing, and prostration.","The narrator says they did not hear his voice in that prayer.","After the prayer, the Prophet صلى الله عليه وسلم praised Allah and testified to faith."],"related_hadiths":[{"id":"1061","book_id":"1","label":"Sahih Bukhari"},{"id":"1059","book_id":"1","label":"Sahih Bukhari"},{"id":"1063","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Silent Long Eclipse Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. A report of the Prophet صلى الله عليه وسلم praying long during a dark solar eclipse, then praising Allah after the sun became clear."},"heading":{"title":"Eclipse Prayer Hadith: Long Silent Standing and Praise of Allah","description":"This eclipse prayer hadith describes a strong scene. Samurah ibn Jundub says he and another boy were shooting arrows when the sun darkened and looked black. They went to the mosque and found the Prophet صلى الله عليه وسلم already out. He led a very long prayer. The narrator says they did not hear his voice during the standing, bowing, or prostration. He did the same in the second rak'ah. The sun became bright when he sat after the second rak'ah. After the salutation, he stood, praised Allah, extolled Him, and testified to Allah’s oneness and to his own mission as Allah’s servant and Messenger. The report highlights prayer, patience, and praise."},"teachings":["The Companions went to the mosque when the sun darkened.","The Prophet صلى الله عليه وسلم prayed with very long standing, bowing, and prostration.","The narrator says they did not hear his voice in that prayer.","After the prayer, the Prophet صلى الله عليه وسلم praised Allah and testified to faith."],"related_hadiths":[{"id":"1061","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1059","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1063","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E117" s="4" t="n"/>
@@ -3164,7 +3168,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray When Signs Appear","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that Allah’s signs should move believers to prayer when they witness events like an eclipse."},"heading":{"title":"Solar Eclipse Prayer Hadith: Pray When You See Allah’s Signs","description":"This hadith about eclipse prayer gives both an action and a clear teaching. Qabisah al-Hilali says a solar eclipse happened in the time of the Messenger of Allah صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم came out in a startled state, pulling his garment, and prayed two rak'ahs with long standing. When he finished, the sun became bright. Then he explained that these are signs by which Allah, the Exalted, creates fear in His servants. He told the people that when they see anything like this, they should pray as they would pray a newly performed obligatory prayer. The message is direct: a frightening sign should turn the heart toward salah, not careless talk or delay."},"teachings":["The Prophet صلى الله عليه وسلم responded to the eclipse by prayer.","The prayer included two rak'ahs with long standing.","The hadith calls such events signs from Allah.","The instruction given here is to pray when such signs are seen."],"related_hadiths":[{"id":"1059","book_id":"1","label":"Sahih Bukhari"},{"id":"1048","book_id":"1","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray When Signs Appear","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that Allah’s signs should move believers to prayer when they witness events like an eclipse."},"heading":{"title":"Solar Eclipse Prayer Hadith: Pray When You See Allah’s Signs","description":"This hadith about eclipse prayer gives both an action and a clear teaching. Qabisah al-Hilali says a solar eclipse happened in the time of the Messenger of Allah صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم came out in a startled state, pulling his garment, and prayed two rak'ahs with long standing. When he finished, the sun became bright. Then he explained that these are signs by which Allah, the Exalted, creates fear in His servants. He told the people that when they see anything like this, they should pray as they would pray a newly performed obligatory prayer. The message is direct: a frightening sign should turn the heart toward salah, not careless talk or delay."},"teachings":["The Prophet صلى الله عليه وسلم responded to the eclipse by prayer.","The prayer included two rak'ahs with long standing.","The hadith calls such events signs from Allah.","The instruction given here is to pray when such signs are seen."],"related_hadiths":[{"id":"1059","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1048","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E118" s="4" t="n"/>
@@ -3187,7 +3191,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eclipse Until Stars Appeared","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration follows the report of Qabisah and adds that the eclipse lasted until the stars appeared."},"heading":{"title":"Solar Eclipse Hadith: Darkness Until the Stars Appeared","description":"This narration is closely tied to the previous report from Qabisah al-Hilali. It says that the solar eclipse took place, and the narrator related it with the same meaning as the narration of Musa. The added wording says that it continued until the stars appeared. Because the text is brief, the explanation should stay brief and careful. The main point is that the eclipse was not treated as a normal passing sight. It was linked with the Prophet’s صلى الله عليه وسلم response of prayer in the connected report. For a person searching for solar eclipse hadith, this narration adds a vivid detail about how dark the event became while still keeping the same message: respond to signs with worship."},"teachings":["The narration reports a solar eclipse.","It follows the meaning of the earlier Qabisah report.","It adds that the stars appeared during the event.","The related report connects the eclipse with prayer."],"related_hadiths":[{"id":"1059","book_id":"1","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","label":"Sahih Bukhari"},{"id":"1063","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eclipse Until Stars Appeared","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration follows the report of Qabisah and adds that the eclipse lasted until the stars appeared."},"heading":{"title":"Solar Eclipse Hadith: Darkness Until the Stars Appeared","description":"This narration is closely tied to the previous report from Qabisah al-Hilali. It says that the solar eclipse took place, and the narrator related it with the same meaning as the narration of Musa. The added wording says that it continued until the stars appeared. Because the text is brief, the explanation should stay brief and careful. The main point is that the eclipse was not treated as a normal passing sight. It was linked with the Prophet’s صلى الله عليه وسلم response of prayer in the connected report. For a person searching for solar eclipse hadith, this narration adds a vivid detail about how dark the event became while still keeping the same message: respond to signs with worship."},"teachings":["The narration reports a solar eclipse.","It follows the meaning of the earlier Qabisah report.","It adds that the stars appeared during the event.","The related report connects the eclipse with prayer."],"related_hadiths":[{"id":"1059","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1063","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E119" s="4" t="n"/>
@@ -3210,7 +3214,7 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Long Qur'an Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet صلى الله عليه وسلم leading eclipse prayer with long recitation, estimated near Al-Baqarah and Al-i-Imran."},"heading":{"title":"Eclipse Prayer Hadith: Long Qur'an Recitation in Salat al-Kusuf","description":"This eclipse prayer hadith focuses on long Qur'an recitation. Aishah says a solar eclipse happened in the time of the Messenger of Allah صلى الله عليه وسلم. He came out and led the people in prayer. She estimated that his first recitation was like Surah al-Baqarah. The narration then says he prostrated twice, stood again, and prolonged the recitation. Aishah estimated that this recitation was like Surah Al-i-Imran. The report does not give a short formula for the prayer. Instead, it shows the weight and length of worship during the eclipse. For anyone searching for Salat al-Kusuf recitation, this hadith points to long standing with Qur'an."},"teachings":["The Prophet صلى الله عليه وسلم led the people in prayer during a solar eclipse.","Aishah estimated the first recitation near Surah al-Baqarah.","The later recitation was also long, estimated near Surah Al-i-Imran.","The hadith highlights long Qur'an recitation in eclipse prayer."],"related_hadiths":[{"id":"1046","book_id":"1","label":"Sahih Bukhari"},{"id":"1065","book_id":"1","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Long Qur'an Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet صلى الله عليه وسلم leading eclipse prayer with long recitation, estimated near Al-Baqarah and Al-i-Imran."},"heading":{"title":"Eclipse Prayer Hadith: Long Qur'an Recitation in Salat al-Kusuf","description":"This eclipse prayer hadith focuses on long Qur'an recitation. Aishah says a solar eclipse happened in the time of the Messenger of Allah صلى الله عليه وسلم. He came out and led the people in prayer. She estimated that his first recitation was like Surah al-Baqarah. The narration then says he prostrated twice, stood again, and prolonged the recitation. Aishah estimated that this recitation was like Surah Al-i-Imran. The report does not give a short formula for the prayer. Instead, it shows the weight and length of worship during the eclipse. For anyone searching for Salat al-Kusuf recitation, this hadith points to long standing with Qur'an."},"teachings":["The Prophet صلى الله عليه وسلم led the people in prayer during a solar eclipse.","Aishah estimated the first recitation near Surah al-Baqarah.","The later recitation was also long, estimated near Surah Al-i-Imran.","The hadith highlights long Qur'an recitation in eclipse prayer."],"related_hadiths":[{"id":"1046","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1065","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E120" s="4" t="n"/>
@@ -3233,7 +3237,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Loud Recitation in Eclipse Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith states that the Prophet صلى الله عليه وسلم recited the Qur'an aloud during the eclipse prayer."},"heading":{"title":"Eclipse Prayer Hadith: Loud Recitation in Salat al-Kusuf","description":"This short hadith gives one clear point: the Messenger of Allah صلى الله عليه وسلم recited from the Qur'an in a loud voice during the eclipse prayer. Aishah reports it directly. The narration does not discuss the number of bowings, the length of the prayer, or the sermon afterward. Its focus is the sound of the recitation in Salat al-Kusuf. That makes it useful for people searching for whether eclipse prayer is recited aloud. The wording shows that, in this report, Qur'an was recited loudly in the eclipse prayer. It also fits with the larger pattern in these narrations, where the eclipse is met with prayer and Qur'an, not with fear alone."},"teachings":["The Prophet صلى الله عليه وسلم recited Qur'an in the eclipse prayer.","This report states that the recitation was loud.","The hadith is focused on recitation, not other details.","It supports learning the form of Salat al-Kusuf from the narrated practice."],"related_hadiths":[{"id":"1065","book_id":"1","label":"Sahih Bukhari"},{"id":"901e","book_id":"2","label":"Sahih Muslim"},{"id":"1046","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Loud Recitation in Eclipse Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith states that the Prophet صلى الله عليه وسلم recited the Qur'an aloud during the eclipse prayer."},"heading":{"title":"Eclipse Prayer Hadith: Loud Recitation in Salat al-Kusuf","description":"This short hadith gives one clear point: the Messenger of Allah صلى الله عليه وسلم recited from the Qur'an in a loud voice during the eclipse prayer. Aishah reports it directly. The narration does not discuss the number of bowings, the length of the prayer, or the sermon afterward. Its focus is the sound of the recitation in Salat al-Kusuf. That makes it useful for people searching for whether eclipse prayer is recited aloud. The wording shows that, in this report, Qur'an was recited loudly in the eclipse prayer. It also fits with the larger pattern in these narrations, where the eclipse is met with prayer and Qur'an, not with fear alone."},"teachings":["The Prophet صلى الله عليه وسلم recited Qur'an in the eclipse prayer.","This report states that the recitation was loud.","The hadith is focused on recitation, not other details.","It supports learning the form of Salat al-Kusuf from the narrated practice."],"related_hadiths":[{"id":"1065","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"901e","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1046","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E121" s="4" t="n"/>
@@ -3256,7 +3260,7 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing Like Al-Baqarah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم stood for a long time during the eclipse prayer, nearly like Surah al-Baqarah."},"heading":{"title":"Solar Eclipse Prayer Hadith: Standing Nearly as Long as Al-Baqarah","description":"This narration gives a strong sense of the length of the Prophet’s صلى الله عليه وسلم eclipse prayer. Ibn Abbas reports that a solar eclipse took place and the Messenger of Allah صلى الله عليه وسلم prayed with the people. He stood for a long time, nearly equal to the recitation of Surah al-Baqarah, and then bowed. The rest of the tradition is referred to without being fully repeated in the provided text. Because of that, the explanation should stay with what is stated: the prayer was in congregation, the standing was very long, and the bowing came after that long standing. For readers looking for solar eclipse prayer hadith, this report shows the seriousness and length of that worship."},"teachings":["The Prophet صلى الله عليه وسلم prayed with the people during a solar eclipse.","The standing was long, nearly like the recitation of Surah al-Baqarah.","The narration mentions bowing after the long standing.","The hadith shows that the eclipse prayer was not rushed."],"related_hadiths":[{"id":"1046","book_id":"1","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","label":"Sahih Muslim"},{"id":"1064","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing Like Al-Baqarah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم stood for a long time during the eclipse prayer, nearly like Surah al-Baqarah."},"heading":{"title":"Solar Eclipse Prayer Hadith: Standing Nearly as Long as Al-Baqarah","description":"This narration gives a strong sense of the length of the Prophet’s صلى الله عليه وسلم eclipse prayer. Ibn Abbas reports that a solar eclipse took place and the Messenger of Allah صلى الله عليه وسلم prayed with the people. He stood for a long time, nearly equal to the recitation of Surah al-Baqarah, and then bowed. The rest of the tradition is referred to without being fully repeated in the provided text. Because of that, the explanation should stay with what is stated: the prayer was in congregation, the standing was very long, and the bowing came after that long standing. For readers looking for solar eclipse prayer hadith, this report shows the seriousness and length of that worship."},"teachings":["The Prophet صلى الله عليه وسلم prayed with the people during a solar eclipse.","The standing was long, nearly like the recitation of Surah al-Baqarah.","The narration mentions bowing after the long standing.","The hadith shows that the eclipse prayer was not rushed."],"related_hadiths":[{"id":"1046","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"901a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1064","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E122" s="4" t="n"/>
@@ -3279,7 +3283,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eclipse Is Not for Birth or Death","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that eclipses are not caused by anyone’s birth or death, and calls believers to dua, takbir, and charity."},"heading":{"title":"Hadith About Eclipse: Dua, Takbir, and Charity During an Eclipse","description":"This hadith gives one of the clearest teachings about an eclipse in Islam. Aishah reports that the Prophet صلى الله عليه وسلم said the sun and the moon are not eclipsed because of anyone’s death or birth. This corrects the idea that an eclipse is tied to a human life event. Then he gives the response: when you see it, supplicate Allah, declare His greatness, and give alms. The core message is not fear of people or stories about people. It is turning to Allah through dua, takbir, and charity. For users searching for hadith about eclipse, this narration is easy to understand and very direct."},"teachings":["Eclipses are not linked to someone’s death or birth.","The Prophet صلى الله عليه وسلم told people to supplicate Allah when they see it.","The hadith mentions declaring Allah’s greatness during the eclipse.","Giving alms is also named as a response in this report."],"related_hadiths":[{"id":"1043","book_id":"1","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","label":"Sahih Bukhari"},{"id":"1044","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eclipse Is Not for Birth or Death","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that eclipses are not caused by anyone’s birth or death, and calls believers to dua, takbir, and charity."},"heading":{"title":"Hadith About Eclipse: Dua, Takbir, and Charity During an Eclipse","description":"This hadith gives one of the clearest teachings about an eclipse in Islam. Aishah reports that the Prophet صلى الله عليه وسلم said the sun and the moon are not eclipsed because of anyone’s death or birth. This corrects the idea that an eclipse is tied to a human life event. Then he gives the response: when you see it, supplicate Allah, declare His greatness, and give alms. The core message is not fear of people or stories about people. It is turning to Allah through dua, takbir, and charity. For users searching for hadith about eclipse, this narration is easy to understand and very direct."},"teachings":["Eclipses are not linked to someone’s death or birth.","The Prophet صلى الله عليه وسلم told people to supplicate Allah when they see it.","The hadith mentions declaring Allah’s greatness during the eclipse.","Giving alms is also named as a response in this report."],"related_hadiths":[{"id":"1043","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1044","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E123" s="4" t="n"/>
@@ -3302,7 +3306,7 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pairs of Rak'ahs Until Clear","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the Prophet صلى الله عليه وسلم praying pairs of rak'ahs and asking about the sun until it became clear."},"heading":{"title":"Solar Eclipse Prayer Hadith: Praying Until the Sun Became Clear","description":"This narration from An-Nu'man ibn Bashir describes the Prophet’s صلى الله عليه وسلم response to a solar eclipse in a simple way. When the eclipse happened, he began to pray pairs of rak'ahs. At the end of them, he would ask about the sun, and he continued until it became clear. The wording gives us a practical picture: prayer continued while the eclipse remained, and the state of the sun was checked. The hadith does not mention a long recitation, a sermon, or charity in this wording. Its focus is steady prayer during the event. For people searching for solar eclipse prayer hadith, this report shows prayer lasting until the eclipse passed."},"teachings":["The Prophet صلى الله عليه وسلم prayed during the solar eclipse.","The narration mentions pairs of rak'ahs.","He asked about the sun until it became clear.","The report connects prayer with the duration of the eclipse."],"related_hadiths":[{"id":"1060","book_id":"1","label":"Sahih Bukhari"},{"id":"1063","book_id":"1","label":"Sahih Bukhari"},{"id":"1041","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pairs of Rak'ahs Until Clear","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith describes the Prophet صلى الله عليه وسلم praying pairs of rak'ahs and asking about the sun until it became clear."},"heading":{"title":"Solar Eclipse Prayer Hadith: Praying Until the Sun Became Clear","description":"This narration from An-Nu'man ibn Bashir describes the Prophet’s صلى الله عليه وسلم response to a solar eclipse in a simple way. When the eclipse happened, he began to pray pairs of rak'ahs. At the end of them, he would ask about the sun, and he continued until it became clear. The wording gives us a practical picture: prayer continued while the eclipse remained, and the state of the sun was checked. The hadith does not mention a long recitation, a sermon, or charity in this wording. Its focus is steady prayer during the event. For people searching for solar eclipse prayer hadith, this report shows prayer lasting until the eclipse passed."},"teachings":["The Prophet صلى الله عليه وسلم prayed during the solar eclipse.","The narration mentions pairs of rak'ahs.","He asked about the sun until it became clear.","The report connects prayer with the duration of the eclipse."],"related_hadiths":[{"id":"1060","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1063","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1041","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E124" s="4" t="n"/>
@@ -3325,7 +3329,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Protection Through Istighfar","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet صلى الله عليه وسلم prolonging eclipse prayer and calling on Allah’s promise linked with his presence and forgiveness."},"heading":{"title":"Eclipse Prayer Hadith: Long Sujud and Seeking Forgiveness","description":"This hadith describes a very intense eclipse prayer. Abdullah ibn Amr reports that during a solar eclipse, the Messenger of Allah صلى الله عليه وسلم stood so long that it seemed he was not going to bow until he did. He bowed for a long time, raised his head, then prolonged the movements in the same way, including prostration. He did the same in the second rak'ah. In the last prostration he said, “Fie, Fie!” Then he called upon Allah, mentioning Allah’s promise not to punish them while he was among them and while they sought forgiveness. The prayer ended when the sun was clear. The core message is prayer, awe, and istighfar."},"teachings":["The Prophet صلى الله عليه وسلم prolonged the standing, bowing, and prostration during the eclipse.","He made a supplication in the last prostration.","The supplication mentioned seeking forgiveness from Allah.","The prayer ended when the sun had become clear."],"related_hadiths":[{"id":"1051","book_id":"1","label":"Sahih Bukhari"},{"id":"1059","book_id":"1","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Protection Through Istighfar","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows the Prophet صلى الله عليه وسلم prolonging eclipse prayer and calling on Allah’s promise linked with his presence and forgiveness."},"heading":{"title":"Eclipse Prayer Hadith: Long Sujud and Seeking Forgiveness","description":"This hadith describes a very intense eclipse prayer. Abdullah ibn Amr reports that during a solar eclipse, the Messenger of Allah صلى الله عليه وسلم stood so long that it seemed he was not going to bow until he did. He bowed for a long time, raised his head, then prolonged the movements in the same way, including prostration. He did the same in the second rak'ah. In the last prostration he said, “Fie, Fie!” Then he called upon Allah, mentioning Allah’s promise not to punish them while he was among them and while they sought forgiveness. The prayer ended when the sun was clear. The core message is prayer, awe, and istighfar."},"teachings":["The Prophet صلى الله عليه وسلم prolonged the standing, bowing, and prostration during the eclipse.","He made a supplication in the last prostration.","The supplication mentioned seeking forgiveness from Allah.","The prayer ended when the sun had become clear."],"related_hadiths":[{"id":"1051","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1059","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E125" s="4" t="n"/>
@@ -3348,7 +3352,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr and Dua During Eclipse","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows the Prophet صلى الله عليه وسلم raising his hands, glorifying Allah, praising Him, declaring His oneness, and making dua until the sun cleared."},"heading":{"title":"Solar Eclipse Hadith: Dhikr, Dua, and Prayer Until the Sun Cleared","description":"This hadith gives a personal scene from Abd al-Rahman b. Samurah. He was shooting arrows when a solar eclipse took place. He threw the arrows away because he wanted to see how the Messenger of Allah صلى الله عليه وسلم would act during the eclipse. He found him standing in prayer, raising his hands, glorifying Allah, praising Him, declaring that Allah is the only Deity, and making dua until the sun became clear. After that, he recited two surahs and prayed two rak'ahs. The report highlights dhikr during eclipse, dua during eclipse, and prayer. It also shows the narrator leaving his own activity to learn from the Prophet’s صلى الله عليه وسلم response."},"teachings":["The narrator left his arrows to see the Prophet’s صلى الله عليه وسلم response.","The Prophet صلى الله عليه وسلم raised his hands in worship.","He glorified Allah, praised Him, declared His oneness, and made dua.","The report mentions two surahs and two rak'ahs after the sun cleared."],"related_hadiths":[{"id":"1059","book_id":"1","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","label":"Sahih Bukhari"},{"id":"1043","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr and Dua During Eclipse","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows the Prophet صلى الله عليه وسلم raising his hands, glorifying Allah, praising Him, declaring His oneness, and making dua until the sun cleared."},"heading":{"title":"Solar Eclipse Hadith: Dhikr, Dua, and Prayer Until the Sun Cleared","description":"This hadith gives a personal scene from Abd al-Rahman b. Samurah. He was shooting arrows when a solar eclipse took place. He threw the arrows away because he wanted to see how the Messenger of Allah صلى الله عليه وسلم would act during the eclipse. He found him standing in prayer, raising his hands, glorifying Allah, praising Him, declaring that Allah is the only Deity, and making dua until the sun became clear. After that, he recited two surahs and prayed two rak'ahs. The report highlights dhikr during eclipse, dua during eclipse, and prayer. It also shows the narrator leaving his own activity to learn from the Prophet’s صلى الله عليه وسلم response."},"teachings":["The narrator left his arrows to see the Prophet’s صلى الله عليه وسلم response.","The Prophet صلى الله عليه وسلم raised his hands in worship.","He glorified Allah, praised Him, declared His oneness, and made dua.","The report mentions two surahs and two rak'ahs after the sun cleared."],"related_hadiths":[{"id":"1059","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1060","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1043","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E126" s="4" t="n"/>
@@ -3371,7 +3375,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostrating When Seeing a Sign","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas prostrated on hearing of a wife of the Prophet’s صلى الله عليه وسلم death, citing the command to prostrate when seeing a sign."},"heading":{"title":"Hadith About Prostration: When You See a Sign, Prostrate","description":"This hadith moves from eclipse reports to the wider idea of responding to signs. Ikrimah says Ibn Abbas was told that one of the wives of the Prophet صلى الله عليه وسلم had died. He fell down in prostration. When someone asked why he prostrated at that moment, he answered with the statement of the Messenger of Allah صلى الله عليه وسلم: “When you see a portent, prostrate yourselves.” Then Ibn Abbas said, “Which portent can be greater than the death of a wife of the Prophet صلى الله عليه وسلم?” The report shows how Ibn Abbas understood the loss as a serious sign. The teaching should be kept close to the text: when a sign is seen, the response mentioned here is prostration."},"teachings":["Ibn Abbas prostrated when he heard the news.","He based his action on the Prophet’s صلى الله عليه وسلم words about seeing a sign.","He viewed the death of a wife of the Prophet صلى الله عليه وسلم as a great portent.","The report links signs with prostration."],"related_hadiths":[{"id":"3891","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1059","book_id":"1","label":"Sahih Bukhari"},{"id":"1048","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostrating When Seeing a Sign","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas prostrated on hearing of a wife of the Prophet’s صلى الله عليه وسلم death, citing the command to prostrate when seeing a sign."},"heading":{"title":"Hadith About Prostration: When You See a Sign, Prostrate","description":"This hadith moves from eclipse reports to the wider idea of responding to signs. Ikrimah says Ibn Abbas was told that one of the wives of the Prophet صلى الله عليه وسلم had died. He fell down in prostration. When someone asked why he prostrated at that moment, he answered with the statement of the Messenger of Allah صلى الله عليه وسلم: “When you see a portent, prostrate yourselves.” Then Ibn Abbas said, “Which portent can be greater than the death of a wife of the Prophet صلى الله عليه وسلم?” The report shows how Ibn Abbas understood the loss as a serious sign. The teaching should be kept close to the text: when a sign is seen, the response mentioned here is prostration."},"teachings":["Ibn Abbas prostrated when he heard the news.","He based his action on the Prophet’s صلى الله عليه وسلم words about seeing a sign.","He viewed the death of a wife of the Prophet صلى الله عليه وسلم as a great portent.","The report links signs with prostration."],"related_hadiths":[{"id":"3891","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1059","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1048","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E127" s="4" t="n"/>
@@ -3394,7 +3398,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Original Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports that prayer was first prescribed as two rak'ahs, with travel prayer kept as it was and resident prayer increased."},"heading":{"title":"Travel Prayer Hadith: Prayer Was Prescribed as Two Rak'ahs","description":"This hadith is about travel prayer and the number of rak'ahs. Aishah reports that prayer was prescribed as two rak'ahs, both for those who were resident and those who were travelling. Then the prayer while travelling was left according to the original prescription, while the prayer of the resident person was increased. The narration is clear and should not be stretched beyond its words. It explains why shortened prayer during travel is connected to the early form of prayer. For people searching for qasr prayer hadith or travel prayer in Islam, this report gives a simple foundation: travel prayer remained two rak'ahs, while resident prayer was enhanced."},"teachings":["Prayer was first prescribed as two rak'ahs in this report.","The travel prayer was left according to that original prescription.","The prayer of the resident person was increased.","The hadith explains the basis of shortened prayer during travel."],"related_hadiths":[{"id":"1090","book_id":"1","label":"Sahih Bukhari"},{"id":"685c","book_id":"2","label":"Sahih Muslim"},{"id":"1081","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Original Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports that prayer was first prescribed as two rak'ahs, with travel prayer kept as it was and resident prayer increased."},"heading":{"title":"Travel Prayer Hadith: Prayer Was Prescribed as Two Rak'ahs","description":"This hadith is about travel prayer and the number of rak'ahs. Aishah reports that prayer was prescribed as two rak'ahs, both for those who were resident and those who were travelling. Then the prayer while travelling was left according to the original prescription, while the prayer of the resident person was increased. The narration is clear and should not be stretched beyond its words. It explains why shortened prayer during travel is connected to the early form of prayer. For people searching for qasr prayer hadith or travel prayer in Islam, this report gives a simple foundation: travel prayer remained two rak'ahs, while resident prayer was enhanced."},"teachings":["Prayer was first prescribed as two rak'ahs in this report.","The travel prayer was left according to that original prescription.","The prayer of the resident person was increased.","The hadith explains the basis of shortened prayer during travel."],"related_hadiths":[{"id":"1090","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"685c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1081","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E128" s="4" t="n"/>
@@ -3417,7 +3421,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Accepting Allah’s Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains that shortening prayer in travel is a charity from Allah, so believers should accept it."},"heading":{"title":"Qasr Prayer Hadith: Shortening Prayer Is Allah’s Charity","description":"This travel prayer hadith answers a question about shortening prayer. Ya'la b. Umayyah asked Umar about people shortening the prayer even though the verse mentions fear from disbelievers, while that fear had passed. Umar said he had wondered the same thing and had asked the Messenger of Allah صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم replied that it is an act of charity which Allah has given to them, so they should accept His charity. The core teaching is simple: qasr prayer is not only tied to the fear mentioned in the question. In this report, the Prophet صلى الله عليه وسلم describes it as Allah’s charity. The wording calls believers to accept what Allah has granted."},"teachings":["Ya'la asked Umar about shortening prayer after fear had passed.","Umar had asked the Prophet صلى الله عليه وسلم the same question.","The Prophet صلى الله عليه وسلم described it as a charity from Allah.","The instruction in the hadith is to accept Allah’s charity."],"related_hadiths":[{"id":"686a","book_id":"2","label":"Sahih Muslim"},{"id":"1083","book_id":"1","label":"Sahih Bukhari"},{"id":"1102","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Accepting Allah’s Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains that shortening prayer in travel is a charity from Allah, so believers should accept it."},"heading":{"title":"Qasr Prayer Hadith: Shortening Prayer Is Allah’s Charity","description":"This travel prayer hadith answers a question about shortening prayer. Ya'la b. Umayyah asked Umar about people shortening the prayer even though the verse mentions fear from disbelievers, while that fear had passed. Umar said he had wondered the same thing and had asked the Messenger of Allah صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم replied that it is an act of charity which Allah has given to them, so they should accept His charity. The core teaching is simple: qasr prayer is not only tied to the fear mentioned in the question. In this report, the Prophet صلى الله عليه وسلم describes it as Allah’s charity. The wording calls believers to accept what Allah has granted."},"teachings":["Ya'la asked Umar about shortening prayer after fear had passed.","Umar had asked the Prophet صلى الله عليه وسلم the same question.","The Prophet صلى الله عليه وسلم described it as a charity from Allah.","The instruction in the hadith is to accept Allah’s charity."],"related_hadiths":[{"id":"686a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1083","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1102","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E129" s="4" t="n"/>
@@ -3440,7 +3444,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Facing Jerusalem While Relieving Himself","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar saw the Prophet صلى الله عليه وسلم sitting on two bricks facing Bait al-Maqdis while relieving himself."},"heading":{"title":"Hadith About Facing Bait al-Maqdis While Relieving Oneself","description":"This hadith reports what Abdullah ibn Umar saw from the roof of a house. He said he saw the Messenger of Allah صلى الله عليه وسلم sitting on two bricks, facing Jerusalem, Bait al-Maqdis, while relieving himself. The narration is brief and visual. It does not give a long ruling by itself, so the explanation should not stretch it beyond the words. The core topic is qiblah direction and screened or built spaces. Readers searching for hadith about Prophet facing Bait al-Maqdis in toilet often compare this with reports about not facing the qiblah in open areas. Within this text, the main point is simply the witnessed action described by Ibn Umar."},"teachings":["The narration reports a specific witnessed action of the Prophet صلى الله عليه وسلم.","Ibn Umar mentions the Prophet صلى الله عليه وسلم sitting on two bricks and facing Bait al-Maqdis.","The text should be read carefully without adding details not stated in it."],"related_hadiths":[{"id":"11","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3102","book_id":"1","label":"Sahih Bukhari"},{"id":"13","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Facing Jerusalem While Relieving Himself","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar saw the Prophet صلى الله عليه وسلم sitting on two bricks facing Bait al-Maqdis while relieving himself."},"heading":{"title":"Hadith About Facing Bait al-Maqdis While Relieving Oneself","description":"This hadith reports what Abdullah ibn Umar saw from the roof of a house. He said he saw the Messenger of Allah صلى الله عليه وسلم sitting on two bricks, facing Jerusalem, Bait al-Maqdis, while relieving himself. The narration is brief and visual. It does not give a long ruling by itself, so the explanation should not stretch it beyond the words. The core topic is qiblah direction and screened or built spaces. Readers searching for hadith about Prophet facing Bait al-Maqdis in toilet often compare this with reports about not facing the qiblah in open areas. Within this text, the main point is simply the witnessed action described by Ibn Umar."},"teachings":["The narration reports a specific witnessed action of the Prophet صلى الله عليه وسلم.","Ibn Umar mentions the Prophet صلى الله عليه وسلم sitting on two bricks and facing Bait al-Maqdis.","The text should be read carefully without adding details not stated in it."],"related_hadiths":[{"id":"11","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"3102","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"13","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E130" s="4" t="n"/>
@@ -3463,7 +3467,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping the Head in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains how the Prophet صلى الله عليه وسلم wiped his head in wudu from the front to the nape and back again."},"heading":{"title":"Wiping the Head in Wudu: The Prophet’s Method","description":"This Hadith focuses on wiping the head in wudu. Al-Miqdam reported that he saw the Messenger of Allah صلى الله عليه وسلم perform ablution. When the Prophet صلى الله عليه وسلم reached the part of wiping his head, he placed his palms on the front of the head, moved them until he reached the nape, and then brought them back to the starting point. The main search phrase is wiping head in wudu, and this report gives a clear picture of that action. It does not discuss every part of wudu in detail. Its focus is the movement of the hands over the head. This makes it useful for readers who want a direct Hadith about how the Prophet صلى الله عليه وسلم wiped his head during ablution."},"teachings":["The Prophet صلى الله عليه وسلم began wiping the head from the front in this narration.","He moved his hands to the nape and then returned them to the starting place.","The report teaches attention to the actual movement used in wudu."],"related_hadiths":[{"id":"160","book_id":"1","label":"Sahih Bukhari"},{"id":"226a","book_id":"2","label":"Sahih Muslim"},{"id":"442","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping the Head in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith explains how the Prophet صلى الله عليه وسلم wiped his head in wudu from the front to the nape and back again."},"heading":{"title":"Wiping the Head in Wudu: The Prophet’s Method","description":"This Hadith focuses on wiping the head in wudu. Al-Miqdam reported that he saw the Messenger of Allah صلى الله عليه وسلم perform ablution. When the Prophet صلى الله عليه وسلم reached the part of wiping his head, he placed his palms on the front of the head, moved them until he reached the nape, and then brought them back to the starting point. The main search phrase is wiping head in wudu, and this report gives a clear picture of that action. It does not discuss every part of wudu in detail. Its focus is the movement of the hands over the head. This makes it useful for readers who want a direct Hadith about how the Prophet صلى الله عليه وسلم wiped his head during ablution."},"teachings":["The Prophet صلى الله عليه وسلم began wiping the head from the front in this narration.","He moved his hands to the nape and then returned them to the starting place.","The report teaches attention to the actual movement used in wudu."],"related_hadiths":[{"id":"160","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"226a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"442","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E131" s="4" t="n"/>
@@ -3486,7 +3490,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fear Prayer and Safe Rows","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear report on Salat al-Khawf, showing how rows moved during prayer while facing a threat."},"heading":{"title":"Fear Prayer Hadith: Moving Rows Safely in Salat al-Khawf","description":"This fear prayer hadith describes a report from Abu Hurairah about the Messenger of Allah صلى الله عليه وسلم going toward Najd and reaching Dhat ar-Riqa at Nakhl. A group from Ghatafan was met there. The main focus is not the whole journey, but a detail about Salat al-Khawf, the prayer in danger. The report says that after bowing and prostrating with those who were with him, the group stood up and retraced their steps to the rows of their companions. It also notes that this version did not mention their backs being toward the qiblah. In simple words, the narration preserves a careful detail about how the praying group changed places while still staying linked to the prayer and the group."},"teachings":["Prayer remained important even when the group was facing danger.","The praying group moved back to their companions after bowing and prostrating.","The narration pays close attention to exact wording and what was or was not mentioned.","Salat al-Khawf shows order and care during a difficult moment."],"related_hadiths":[{"id":"942","book_id":"1","label":"Sahih Bukhari"},{"id":"943","book_id":"1","label":"Sahih Bukhari"},{"id":"839a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fear Prayer and Safe Rows","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear report on Salat al-Khawf, showing how rows moved during prayer while facing a threat."},"heading":{"title":"Fear Prayer Hadith: Moving Rows Safely in Salat al-Khawf","description":"This fear prayer hadith describes a report from Abu Hurairah about the Messenger of Allah صلى الله عليه وسلم going toward Najd and reaching Dhat ar-Riqa at Nakhl. A group from Ghatafan was met there. The main focus is not the whole journey, but a detail about Salat al-Khawf, the prayer in danger. The report says that after bowing and prostrating with those who were with him, the group stood up and retraced their steps to the rows of their companions. It also notes that this version did not mention their backs being toward the qiblah. In simple words, the narration preserves a careful detail about how the praying group changed places while still staying linked to the prayer and the group."},"teachings":["Prayer remained important even when the group was facing danger.","The praying group moved back to their companions after bowing and prostrating.","The narration pays close attention to exact wording and what was or was not mentioned.","Salat al-Khawf shows order and care during a difficult moment."],"related_hadiths":[{"id":"942","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"943","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"839a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E132" s="4" t="n"/>
@@ -3509,7 +3513,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Full Participation in Fear Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration explains how both groups joined the prayer with the Prophet صلى الله عليه وسلم during danger."},"heading":{"title":"Salat al-Khawf Hadith: How Everyone Shared in the Prayer","description":"This fear prayer hadith gives a detailed account from Aishah through another chain. The Prophet صلى الله عليه وسلم began with takbir, and the section in the same row with him also said takbir. They bowed and prostrated with him. Then he remained seated while they completed a prostration alone, stood, moved back, and another section came forward. The second group also joined parts of the prayer. Later both sections stood and prayed with the Messenger of Allah صلى الله عليه وسلم together. The narration ends by saying that the people had participated in the whole prayer. The key point is clear: even in a time of danger, prayer was kept in an organized way, with each section taking its place and joining the imam."},"teachings":["The prayer began with takbir and clear group order.","Each section had a role while the prayer continued.","The narration shows careful movement without leaving the prayer behind.","Both sections were included in the prayer with the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"942","book_id":"1","label":"Sahih Bukhari"},{"id":"943","book_id":"1","label":"Sahih Bukhari"},{"id":"839a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Full Participation in Fear Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration explains how both groups joined the prayer with the Prophet صلى الله عليه وسلم during danger."},"heading":{"title":"Salat al-Khawf Hadith: How Everyone Shared in the Prayer","description":"This fear prayer hadith gives a detailed account from Aishah through another chain. The Prophet صلى الله عليه وسلم began with takbir, and the section in the same row with him also said takbir. They bowed and prostrated with him. Then he remained seated while they completed a prostration alone, stood, moved back, and another section came forward. The second group also joined parts of the prayer. Later both sections stood and prayed with the Messenger of Allah صلى الله عليه وسلم together. The narration ends by saying that the people had participated in the whole prayer. The key point is clear: even in a time of danger, prayer was kept in an organized way, with each section taking its place and joining the imam."},"teachings":["The prayer began with takbir and clear group order.","Each section had a role while the prayer continued.","The narration shows careful movement without leaving the prayer behind.","Both sections were included in the prayer with the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"942","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"943","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"839a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E133" s="4" t="n"/>
@@ -3532,7 +3536,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Rak'ah with Each Group","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports a form of Salat al-Khawf where each section prayed one rak'ah with the Prophet صلى الله عليه وسلم."},"heading":{"title":"Prayer in Danger Hadith: One Rak'ah with Each Section","description":"This prayer in danger hadith from Ibn Umar explains a clear form of Salat al-Khawf. The Messenger of Allah صلى الله عليه وسلم led one section in one rak'ah while the other section faced the enemy. Then the first section moved away and took the place of the section that had been watching. The second section came and prayed the second rak'ah with the Prophet صلى الله عليه وسلم. After that, he gave salutation. Then each section stood and completed the remaining rak'ah. The teaching stays very close to the text: the prayer was arranged in sections, one group prayed while another watched, and then both groups completed what remained. It shows prayer, leadership, and alertness together in one setting."},"teachings":["One group prayed while another faced the enemy.","The two sections changed places in an ordered way.","The Prophet صلى الله عليه وسلم led each section in one rak'ah.","Each group completed the remaining rak'ah after the salutation."],"related_hadiths":[{"id":"943","book_id":"1","label":"Sahih Bukhari"},{"id":"945","book_id":"1","label":"Sahih Bukhari"},{"id":"839c","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Rak'ah with Each Group","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports a form of Salat al-Khawf where each section prayed one rak'ah with the Prophet صلى الله عليه وسلم."},"heading":{"title":"Prayer in Danger Hadith: One Rak'ah with Each Section","description":"This prayer in danger hadith from Ibn Umar explains a clear form of Salat al-Khawf. The Messenger of Allah صلى الله عليه وسلم led one section in one rak'ah while the other section faced the enemy. Then the first section moved away and took the place of the section that had been watching. The second section came and prayed the second rak'ah with the Prophet صلى الله عليه وسلم. After that, he gave salutation. Then each section stood and completed the remaining rak'ah. The teaching stays very close to the text: the prayer was arranged in sections, one group prayed while another watched, and then both groups completed what remained. It shows prayer, leadership, and alertness together in one setting."},"teachings":["One group prayed while another faced the enemy.","The two sections changed places in an ordered way.","The Prophet صلى الله عليه وسلم led each section in one rak'ah.","Each group completed the remaining rak'ah after the salutation."],"related_hadiths":[{"id":"943","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"945","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"839c","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E134" s="4" t="n"/>
@@ -3555,7 +3559,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rows in Time of Danger","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows two rows in danger: one behind the Prophet صلى الله عليه وسلم and one facing the enemy."},"heading":{"title":"Fear Prayer Hadith: Two Rows and Shared Responsibility","description":"This fear prayer hadith from Abdullah ibn Mas'ud describes the prayer in the time of danger. The people stood in two rows. One row was behind the Messenger of Allah صلى الله عليه وسلم, and the other row faced the enemy. The Prophet صلى الله عليه وسلم led the first row in one rak'ah. Then the other section came and took their place, while the first group went to face the enemy. He led the second section in one rak'ah and gave salutation. After that, each section completed its own second rak'ah and gave salutation. The simple message is that the prayer was not dropped, and the people did not act without order. Each row prayed and also took care of the danger facing the group."},"teachings":["The people were arranged in two rows for prayer and protection.","Each row prayed one rak'ah with the Prophet صلى الله عليه وسلم.","The rows exchanged places so each group could take its turn.","Each section completed its own prayer after the Prophet’s salutation."],"related_hadiths":[{"id":"942","book_id":"1","label":"Sahih Bukhari"},{"id":"943","book_id":"1","label":"Sahih Bukhari"},{"id":"839a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rows in Time of Danger","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows two rows in danger: one behind the Prophet صلى الله عليه وسلم and one facing the enemy."},"heading":{"title":"Fear Prayer Hadith: Two Rows and Shared Responsibility","description":"This fear prayer hadith from Abdullah ibn Mas'ud describes the prayer in the time of danger. The people stood in two rows. One row was behind the Messenger of Allah صلى الله عليه وسلم, and the other row faced the enemy. The Prophet صلى الله عليه وسلم led the first row in one rak'ah. Then the other section came and took their place, while the first group went to face the enemy. He led the second section in one rak'ah and gave salutation. After that, each section completed its own second rak'ah and gave salutation. The simple message is that the prayer was not dropped, and the people did not act without order. Each row prayed and also took care of the danger facing the group."},"teachings":["The people were arranged in two rows for prayer and protection.","Each row prayed one rak'ah with the Prophet صلى الله عليه وسلم.","The rows exchanged places so each group could take its turn.","Each section completed its own prayer after the Prophet’s salutation."],"related_hadiths":[{"id":"942","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"943","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"839a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E135" s="4" t="n"/>
@@ -3578,7 +3582,7 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Takbir with Both Rows","description":"$book_name$ $hadith_number$ - $chapter_name$. This report adds that the Prophet صلى الله عليه وسلم and both rows said takbir together in Salat al-Khawf."},"heading":{"title":"Salat al-Khawf Hadith: Takbir and Order in Fear Prayer","description":"This Salat al-Khawf hadith is connected to the previous report and adds an important detail: the Prophet of Allah صلى الله عليه وسلم uttered takbir, and both rows uttered takbir together. The narration then mentions that Abd al-Rahman ibn Samurah prayed in a similar way. It also describes a form where one section prayed one rak'ah with the Prophet صلى الله عليه وسلم, moved to the place of its companions, and the other section came and prayed by itself. The value of this text is in its exact detail. It shows that the opening of prayer was shared, the rows were aware of each other, and the movement of groups was part of the prayer arrangement during danger."},"teachings":["Both rows joined in the opening takbir together.","The report keeps the focus on order within the prayer.","The narration records a similar practice by Abd al-Rahman ibn Samurah.","The text shows that group movement was handled with care."],"related_hadiths":[{"id":"942","book_id":"1","label":"Sahih Bukhari"},{"id":"943","book_id":"1","label":"Sahih Bukhari"},{"id":"839a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Takbir with Both Rows","description":"$book_name$ $hadith_number$ - $chapter_name$. This report adds that the Prophet صلى الله عليه وسلم and both rows said takbir together in Salat al-Khawf."},"heading":{"title":"Salat al-Khawf Hadith: Takbir and Order in Fear Prayer","description":"This Salat al-Khawf hadith is connected to the previous report and adds an important detail: the Prophet of Allah صلى الله عليه وسلم uttered takbir, and both rows uttered takbir together. The narration then mentions that Abd al-Rahman ibn Samurah prayed in a similar way. It also describes a form where one section prayed one rak'ah with the Prophet صلى الله عليه وسلم, moved to the place of its companions, and the other section came and prayed by itself. The value of this text is in its exact detail. It shows that the opening of prayer was shared, the rows were aware of each other, and the movement of groups was part of the prayer arrangement during danger."},"teachings":["Both rows joined in the opening takbir together.","The report keeps the focus on order within the prayer.","The narration records a similar practice by Abd al-Rahman ibn Samurah.","The text shows that group movement was handled with care."],"related_hadiths":[{"id":"942","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"943","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"839a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E136" s="4" t="n"/>
@@ -3601,7 +3605,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Rak'ah in Danger","description":"$book_name$ $hadith_number$ - $chapter_name$. Hudhayfah reports a form of fear prayer where each section prayed one rak'ah."},"heading":{"title":"One Rak'ah Fear Prayer Hadith: Salat al-Khawf in Danger","description":"This one rak'ah fear prayer hadith reports that Tha'labah ibn Zahdam was with Sa'd ibn al-'As at Tabaristan. Sa'd asked who had prayed the fear prayer with the Messenger of Allah صلى الله عليه وسلم. Hudhayfah answered that he had. He then led one section in one rak'ah and the other section in one rak'ah, and they did not pray a second rak'ah by themselves in that report. Abu Dawud then mentions other narrations with similar wording, and also notes that some narrators said the second rak'ah was completed. The main lesson from the provided text is that Salat al-Khawf was reported with precise forms, and narrators carefully preserved where reports agreed and where wording differed."},"teachings":["Hudhayfah connected this form of prayer to his experience with the Prophet صلى الله عليه وسلم.","Each section prayed one rak'ah in this report.","Abu Dawud noted differences found in related reports.","The narration shows care in recording exact forms of prayer."],"related_hadiths":[{"id":"839a","book_id":"2","label":"Sahih Muslim"},{"id":"839c","book_id":"2","label":"Sahih Muslim"},{"id":"945","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Rak'ah in Danger","description":"$book_name$ $hadith_number$ - $chapter_name$. Hudhayfah reports a form of fear prayer where each section prayed one rak'ah."},"heading":{"title":"One Rak'ah Fear Prayer Hadith: Salat al-Khawf in Danger","description":"This one rak'ah fear prayer hadith reports that Tha'labah ibn Zahdam was with Sa'd ibn al-'As at Tabaristan. Sa'd asked who had prayed the fear prayer with the Messenger of Allah صلى الله عليه وسلم. Hudhayfah answered that he had. He then led one section in one rak'ah and the other section in one rak'ah, and they did not pray a second rak'ah by themselves in that report. Abu Dawud then mentions other narrations with similar wording, and also notes that some narrators said the second rak'ah was completed. The main lesson from the provided text is that Salat al-Khawf was reported with precise forms, and narrators carefully preserved where reports agreed and where wording differed."},"teachings":["Hudhayfah connected this form of prayer to his experience with the Prophet صلى الله عليه وسلم.","Each section prayed one rak'ah in this report.","Abu Dawud noted differences found in related reports.","The narration shows care in recording exact forms of prayer."],"related_hadiths":[{"id":"839a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"839c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"945","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E137" s="4" t="n"/>
@@ -3624,7 +3628,7 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Length in Danger","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas states that prayer is four rak'ahs at home, two in travel, and one in danger."},"heading":{"title":"Fear Prayer Hadith: Four at Home, Two in Travel, One in Danger","description":"This fear prayer hadith from Ibn Abbas is short but very clear. He says that Allah, through the tongue of the Prophet صلى الله عليه وسلم, prescribed prayer as four rak'ahs while resident, two rak'ahs while travelling, and one rak'ah in time of danger. The report directly links the number of rak'ahs to three states: normal residence, travel, and fear. The wording should not be stretched beyond the text. Its main point is the stated difference in prayer length based on the situation. For a reader searching for hadith about prayer in danger, this narration gives a simple summary: worship remains, but the form mentioned here changes when the situation is fear."},"teachings":["The report names three states: residence, travel, and danger.","Four rak'ahs are mentioned for the resident state.","Two rak'ahs are mentioned for travel.","One rak'ah is mentioned for the time of danger."],"related_hadiths":[{"id":"839c","book_id":"2","label":"Sahih Muslim"},{"id":"945","book_id":"1","label":"Sahih Bukhari"},{"id":"693a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Length in Danger","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas states that prayer is four rak'ahs at home, two in travel, and one in danger."},"heading":{"title":"Fear Prayer Hadith: Four at Home, Two in Travel, One in Danger","description":"This fear prayer hadith from Ibn Abbas is short but very clear. He says that Allah, through the tongue of the Prophet صلى الله عليه وسلم, prescribed prayer as four rak'ahs while resident, two rak'ahs while travelling, and one rak'ah in time of danger. The report directly links the number of rak'ahs to three states: normal residence, travel, and fear. The wording should not be stretched beyond the text. Its main point is the stated difference in prayer length based on the situation. For a reader searching for hadith about prayer in danger, this narration gives a simple summary: worship remains, but the form mentioned here changes when the situation is fear."},"teachings":["The report names three states: residence, travel, and danger.","Four rak'ahs are mentioned for the resident state.","Two rak'ahs are mentioned for travel.","One rak'ah is mentioned for the time of danger."],"related_hadiths":[{"id":"839c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"945","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"693a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E138" s="4" t="n"/>
@@ -3647,7 +3651,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Noon Prayer in Danger","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakrah reports the noon fear prayer where the Prophet صلى الله عليه وسلم prayed four and companions prayed two each."},"heading":{"title":"Noon Fear Prayer Hadith: Two Groups Behind the Imam","description":"This noon fear prayer hadith from Abu Bakrah describes the Prophet صلى الله عليه وسلم offering the noon prayer in a time of danger. Some people formed a row behind him, while others stood against the enemy. He led the first group in two rak'ahs and gave salutation. Then that group went and stood in the place of their companions before the enemy. The second group came and prayed behind him. He led them in two rak'ahs and gave salutation. The narration states the result clearly: the Messenger of Allah صلى الله عليه وسلم offered four rak'ahs, while his companions offered two rak'ahs each. Abu Dawud also notes how this would apply to sunset prayer in the report."},"teachings":["One group prayed while another stood against the enemy.","Each group prayed two rak'ahs behind the Prophet صلى الله عليه وسلم.","The Prophet صلى الله عليه وسلم prayed four rak'ahs in total in this report.","The companions prayed two rak'ahs each."],"related_hadiths":[{"id":"942","book_id":"1","label":"Sahih Bukhari"},{"id":"839a","book_id":"2","label":"Sahih Muslim"},{"id":"839c","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Noon Prayer in Danger","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakrah reports the noon fear prayer where the Prophet صلى الله عليه وسلم prayed four and companions prayed two each."},"heading":{"title":"Noon Fear Prayer Hadith: Two Groups Behind the Imam","description":"This noon fear prayer hadith from Abu Bakrah describes the Prophet صلى الله عليه وسلم offering the noon prayer in a time of danger. Some people formed a row behind him, while others stood against the enemy. He led the first group in two rak'ahs and gave salutation. Then that group went and stood in the place of their companions before the enemy. The second group came and prayed behind him. He led them in two rak'ahs and gave salutation. The narration states the result clearly: the Messenger of Allah صلى الله عليه وسلم offered four rak'ahs, while his companions offered two rak'ahs each. Abu Dawud also notes how this would apply to sunset prayer in the report."},"teachings":["One group prayed while another stood against the enemy.","Each group prayed two rak'ahs behind the Prophet صلى الله عليه وسلم.","The Prophet صلى الله عليه وسلم prayed four rak'ahs in total in this report.","The companions prayed two rak'ahs each."],"related_hadiths":[{"id":"942","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"839a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"839c","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E139" s="4" t="n"/>
@@ -3670,7 +3674,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer While Walking in Danger","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows prayer by signs while walking when delay was feared during a specific mission."},"heading":{"title":"Prayer by Signs Hadith: Remembering Salah During Danger","description":"This hadith reports a specific mission involving Abdullah ibn Unais and Khalid ibn Sufyan al-Hudhali. The part most tied to prayer is that the time of Asr had come, and Abdullah feared that a fight between him and Khalid might delay the prayer. So he continued walking toward him while praying by making signs. This is a report about a serious danger setting, not a normal daily situation. According to Islamic scholars, narrations like this are not treated as a personal license for people to take violent action on their own. Staying strictly with the text, the lesson is that Abdullah was deeply concerned about not delaying prayer, even while facing a difficult task."},"teachings":["The time of Asr mattered to Abdullah ibn Unais in a hard situation.","He feared that conflict might cause the prayer to be delayed.","He prayed while walking by making signs.","The narration is a specific report and should not be turned into a general personal order."],"related_hadiths":[{"id":"945","book_id":"1","label":"Sahih Bukhari"},{"id":"839c","book_id":"2","label":"Sahih Muslim"},{"id":"839a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer While Walking in Danger","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows prayer by signs while walking when delay was feared during a specific mission."},"heading":{"title":"Prayer by Signs Hadith: Remembering Salah During Danger","description":"This hadith reports a specific mission involving Abdullah ibn Unais and Khalid ibn Sufyan al-Hudhali. The part most tied to prayer is that the time of Asr had come, and Abdullah feared that a fight between him and Khalid might delay the prayer. So he continued walking toward him while praying by making signs. This is a report about a serious danger setting, not a normal daily situation. According to Islamic scholars, narrations like this are not treated as a personal license for people to take violent action on their own. Staying strictly with the text, the lesson is that Abdullah was deeply concerned about not delaying prayer, even while facing a difficult task."},"teachings":["The time of Asr mattered to Abdullah ibn Unais in a hard situation.","He feared that conflict might cause the prayer to be delayed.","He prayed while walking by making signs.","The narration is a specific report and should not be turned into a general personal order."],"related_hadiths":[{"id":"945","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"839c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"839a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E140" s="4" t="n"/>
@@ -3693,7 +3697,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Voluntary Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet’s voluntary prayers around daily prayers, night prayer, witr, and dawn."},"heading":{"title":"Sunnah Prayers Hadith: Aishah Describes the Prophet’s Routine","description":"This sunnah prayers hadith gives a broad picture of the voluntary prayers of the Messenger of Allah صلى الله عليه وسلم as described by Aishah. She mentions four rak'ahs before the noon prayer in her house, then two after he returned. She also mentions two after Maghrib, two after Isha, nine rak'ahs at night including witr, and two rak'ahs when dawn came before leading Fajr. The report also says he prayed at night for a long time standing and for a long time sitting. When he recited standing, he bowed and prostrated from standing. When he recited sitting, he bowed and prostrated from sitting. The main point is a clear, simple record of his voluntary prayer pattern."},"teachings":["Aishah described several voluntary prayers linked to the daily prayers.","The Prophet صلى الله عليه وسلم prayed night prayer, including witr, in this report.","He prayed at night both standing and sitting.","He prayed two rak'ahs after dawn before leading Fajr."],"related_hadiths":[{"id":"937","book_id":"1","label":"Sahih Bukhari"},{"id":"1180","book_id":"1","label":"Sahih Bukhari"},{"id":"724a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Voluntary Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet’s voluntary prayers around daily prayers, night prayer, witr, and dawn."},"heading":{"title":"Sunnah Prayers Hadith: Aishah Describes the Prophet’s Routine","description":"This sunnah prayers hadith gives a broad picture of the voluntary prayers of the Messenger of Allah صلى الله عليه وسلم as described by Aishah. She mentions four rak'ahs before the noon prayer in her house, then two after he returned. She also mentions two after Maghrib, two after Isha, nine rak'ahs at night including witr, and two rak'ahs when dawn came before leading Fajr. The report also says he prayed at night for a long time standing and for a long time sitting. When he recited standing, he bowed and prostrated from standing. When he recited sitting, he bowed and prostrated from sitting. The main point is a clear, simple record of his voluntary prayer pattern."},"teachings":["Aishah described several voluntary prayers linked to the daily prayers.","The Prophet صلى الله عليه وسلم prayed night prayer, including witr, in this report.","He prayed at night both standing and sitting.","He prayed two rak'ahs after dawn before leading Fajr."],"related_hadiths":[{"id":"937","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1180","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"724a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E141" s="4" t="n"/>
@@ -3716,7 +3720,7 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sunnah Prayers Around Fard","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports two rak'ahs before and after Zuhr, after Maghrib, after Isha, and after Jumu'ah at home."},"heading":{"title":"Sunnah Prayers Hadith: Two Rak'ahs Before and After Key Prayers","description":"This sunnah prayers hadith from Abdullah ibn Umar describes specific voluntary prayers of the Messenger of Allah صلى الله عليه وسلم. He would pray two rak'ahs before the noon prayer and two after it. He would pray two after the sunset prayer in his house and two after the night prayer. The narration also says he did not pray after the Friday prayer until he departed, then he prayed two rak'ahs. This report is useful for people searching for “sunnah prayers before and after fard” because it gives a clear list from the narrator. The explanation should stay close to the wording: it mentions these prayers and the place for some of them, especially in the house."},"teachings":["Two rak'ahs before and two after Zuhr are mentioned.","Two rak'ahs after Maghrib were prayed in his house.","Two rak'ahs after Isha are mentioned.","After Jumu'ah, he prayed two rak'ahs after departing."],"related_hadiths":[{"id":"937","book_id":"1","label":"Sahih Bukhari"},{"id":"1180","book_id":"1","label":"Sahih Bukhari"},{"id":"1181","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sunnah Prayers Around Fard","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports two rak'ahs before and after Zuhr, after Maghrib, after Isha, and after Jumu'ah at home."},"heading":{"title":"Sunnah Prayers Hadith: Two Rak'ahs Before and After Key Prayers","description":"This sunnah prayers hadith from Abdullah ibn Umar describes specific voluntary prayers of the Messenger of Allah صلى الله عليه وسلم. He would pray two rak'ahs before the noon prayer and two after it. He would pray two after the sunset prayer in his house and two after the night prayer. The narration also says he did not pray after the Friday prayer until he departed, then he prayed two rak'ahs. This report is useful for people searching for “sunnah prayers before and after fard” because it gives a clear list from the narrator. The explanation should stay close to the wording: it mentions these prayers and the place for some of them, especially in the house."},"teachings":["Two rak'ahs before and two after Zuhr are mentioned.","Two rak'ahs after Maghrib were prayed in his house.","Two rak'ahs after Isha are mentioned.","After Jumu'ah, he prayed two rak'ahs after departing."],"related_hadiths":[{"id":"937","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1180","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1181","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E142" s="4" t="n"/>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Care for Two Rak'ahs Before Dawn","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah says the Prophet صلى الله عليه وسلم was especially particular about the two rak'ahs before dawn."},"heading":{"title":"Fajr Sunnah Hadith: The Prophet’s Special Care for Two Rak'ahs","description":"This Fajr Sunnah hadith from Aishah focuses on the two supererogatory rak'ahs before the dawn prayer. She says the Messenger of Allah صلى الله عليه وسلم was more particular about observing them than any other supererogatory prayers. The wording shows strong care for these two rak'ahs, but it does not list their recitation or length here. It simply highlights how carefully the Prophet صلى الله عليه وسلم kept them. For readers searching “importance of Sunnah before Fajr,” this hadith gives a clear answer from Aishah’s observation. The core teaching is not complicated: among voluntary prayers, the two before Subh had a special place in the practice described in this report."},"teachings":["The two rak'ahs before dawn are singled out in this narration.","Aishah describes the Prophet صلى الله عليه وسلم as especially careful about them.","The hadith focuses on regular observance, not on extra details.","The report helps show the value of Fajr Sunnah prayer."],"related_hadiths":[{"id":"724f","book_id":"2","label":"Sahih Muslim"},{"id":"725a","book_id":"2","label":"Sahih Muslim"},{"id":"1182","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Care for Two Rak'ahs Before Dawn","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah says the Prophet صلى الله عليه وسلم was especially particular about the two rak'ahs before dawn."},"heading":{"title":"Fajr Sunnah Hadith: The Prophet’s Special Care for Two Rak'ahs","description":"This Fajr Sunnah hadith from Aishah focuses on the two supererogatory rak'ahs before the dawn prayer. She says the Messenger of Allah صلى الله عليه وسلم was more particular about observing them than any other supererogatory prayers. The wording shows strong care for these two rak'ahs, but it does not list their recitation or length here. It simply highlights how carefully the Prophet صلى الله عليه وسلم kept them. For readers searching “importance of Sunnah before Fajr,” this hadith gives a clear answer from Aishah’s observation. The core teaching is not complicated: among voluntary prayers, the two before Subh had a special place in the practice described in this report."},"teachings":["The two rak'ahs before dawn are singled out in this narration.","Aishah describes the Prophet صلى الله عليه وسلم as especially careful about them.","The hadith focuses on regular observance, not on extra details.","The report helps show the value of Fajr Sunnah prayer."],"related_hadiths":[{"id":"724f","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"725a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1182","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E143" s="4" t="n"/>
@@ -3762,7 +3766,7 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Light Fajr Sunnah Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah says the Prophet صلى الله عليه وسلم prayed the two rak'ahs before Fajr so lightly she wondered about al-Fatihah."},"heading":{"title":"Two Rak'ahs Before Fajr Hadith: Praying Them Lightly","description":"This two rak'ahs before Fajr hadith from Aishah describes the lightness of the Prophet’s Sunnah prayer before dawn. She says he would pray the two rak'ahs before the dawn prayer so lightly that she would say, “Did he recite Surah al-Fatihah in them?” This does not mean the narration denies recitation. Rather, the wording shows how brief and light the prayer appeared to her. The main point is the manner described in the text: these two rak'ahs were prayed lightly. For people looking for “how did the Prophet pray Fajr Sunnah,” this hadith gives one clear detail: the prayer was short in the way Aishah observed it."},"teachings":["The two rak'ahs before Fajr were prayed lightly in this report.","Aishah’s question shows how brief they appeared to her.","The narration mentions Surah al-Fatihah as part of her observation.","The hadith focuses on the manner of the prayer, not a full legal discussion."],"related_hadiths":[{"id":"724d","book_id":"2","label":"Sahih Muslim"},{"id":"724e","book_id":"2","label":"Sahih Muslim"},{"id":"724a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Light Fajr Sunnah Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah says the Prophet صلى الله عليه وسلم prayed the two rak'ahs before Fajr so lightly she wondered about al-Fatihah."},"heading":{"title":"Two Rak'ahs Before Fajr Hadith: Praying Them Lightly","description":"This two rak'ahs before Fajr hadith from Aishah describes the lightness of the Prophet’s Sunnah prayer before dawn. She says he would pray the two rak'ahs before the dawn prayer so lightly that she would say, “Did he recite Surah al-Fatihah in them?” This does not mean the narration denies recitation. Rather, the wording shows how brief and light the prayer appeared to her. The main point is the manner described in the text: these two rak'ahs were prayed lightly. For people looking for “how did the Prophet pray Fajr Sunnah,” this hadith gives one clear detail: the prayer was short in the way Aishah observed it."},"teachings":["The two rak'ahs before Fajr were prayed lightly in this report.","Aishah’s question shows how brief they appeared to her.","The narration mentions Surah al-Fatihah as part of her observation.","The hadith focuses on the manner of the prayer, not a full legal discussion."],"related_hadiths":[{"id":"724d","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"724e","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"724a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E144" s="4" t="n"/>
@@ -3785,7 +3789,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surahs in Fajr Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah reports that the Prophet صلى الله عليه وسلم recited Surah al-Kafirun and Surah al-Ikhlas in the two dawn rak'ahs."},"heading":{"title":"Fajr Sunnah Recitation Hadith: Al-Kafirun and Al-Ikhlas","description":"This Fajr Sunnah recitation hadith from Abu Hurairah tells us what the Prophet صلى الله عليه وسلم recited in the two supererogatory rak'ahs of the dawn prayer. The report says he recited “Say, O unbelievers,” meaning Surah al-Kafirun, and “Say: He is Allah, the One,” meaning Surah al-Ikhlas. The text is direct and easy to apply in understanding the narration: it names two surahs connected to the two dawn Sunnah rak'ahs. It does not say these were the only verses ever recited in every report, so the explanation should not add that. The teaching is simply that these two surahs were recited by the Prophet صلى الله عليه وسلم in this prayer."},"teachings":["Surah al-Kafirun is mentioned in the two dawn Sunnah rak'ahs.","Surah al-Ikhlas is also mentioned in this report.","The narration connects these recitations to the prayer before Fajr.","The text names the surahs without adding a longer ruling."],"related_hadiths":[{"id":"726","book_id":"2","label":"Sahih Muslim"},{"id":"727a","book_id":"2","label":"Sahih Muslim"},{"id":"727b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surahs in Fajr Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah reports that the Prophet صلى الله عليه وسلم recited Surah al-Kafirun and Surah al-Ikhlas in the two dawn rak'ahs."},"heading":{"title":"Fajr Sunnah Recitation Hadith: Al-Kafirun and Al-Ikhlas","description":"This Fajr Sunnah recitation hadith from Abu Hurairah tells us what the Prophet صلى الله عليه وسلم recited in the two supererogatory rak'ahs of the dawn prayer. The report says he recited “Say, O unbelievers,” meaning Surah al-Kafirun, and “Say: He is Allah, the One,” meaning Surah al-Ikhlas. The text is direct and easy to apply in understanding the narration: it names two surahs connected to the two dawn Sunnah rak'ahs. It does not say these were the only verses ever recited in every report, so the explanation should not add that. The teaching is simply that these two surahs were recited by the Prophet صلى الله عليه وسلم in this prayer."},"teachings":["Surah al-Kafirun is mentioned in the two dawn Sunnah rak'ahs.","Surah al-Ikhlas is also mentioned in this report.","The narration connects these recitations to the prayer before Fajr.","The text names the surahs without adding a longer ruling."],"related_hadiths":[{"id":"726","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"727a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"727b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E145" s="4" t="n"/>
@@ -3808,7 +3812,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying Fajr Sunnah Even When Late","description":"$book_name$ $hadith_number$ - $chapter_name$. Bilal reports that the Prophet صلى الله عليه وسلم prayed the two Fajr Sunnah rak'ahs even after the morning became bright."},"heading":{"title":"Fajr Sunnah Hadith: The Prophet صلى الله عليه وسلم Still Prayed the Two Rak'ahs","description":"This Fajr Sunnah hadith from Bilal describes a delay before the dawn prayer. Bilal came to inform the Messenger of Allah صلى الله عليه وسلم about the prayer, but Aishah kept him busy with a matter she asked about until the day became bright. Bilal called the Prophet صلى الله عليه وسلم to prayer more than once. When the Prophet صلى الله عليه وسلم came out, he led the people in prayer. Bilal then explained what happened and mentioned that the dawn had become fairly bright. The Prophet صلى الله عليه وسلم replied that he had prayed the two rak'ahs of Fajr, and said that even if it had become brighter, he would pray them well and beautifully. The hadith shows his care for these two rak'ahs."},"teachings":["Bilal came to call the Prophet صلى الله عليه وسلم for the dawn prayer.","A delay happened because Aishah had asked Bilal about a matter.","The Prophet صلى الله عليه وسلم still prayed the two rak'ahs of Fajr.","He spoke about praying them well even if the morning became brighter."],"related_hadiths":[{"id":"724a","book_id":"2","label":"Sahih Muslim"},{"id":"724f","book_id":"2","label":"Sahih Muslim"},{"id":"725a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying Fajr Sunnah Even When Late","description":"$book_name$ $hadith_number$ - $chapter_name$. Bilal reports that the Prophet صلى الله عليه وسلم prayed the two Fajr Sunnah rak'ahs even after the morning became bright."},"heading":{"title":"Fajr Sunnah Hadith: The Prophet صلى الله عليه وسلم Still Prayed the Two Rak'ahs","description":"This Fajr Sunnah hadith from Bilal describes a delay before the dawn prayer. Bilal came to inform the Messenger of Allah صلى الله عليه وسلم about the prayer, but Aishah kept him busy with a matter she asked about until the day became bright. Bilal called the Prophet صلى الله عليه وسلم to prayer more than once. When the Prophet صلى الله عليه وسلم came out, he led the people in prayer. Bilal then explained what happened and mentioned that the dawn had become fairly bright. The Prophet صلى الله عليه وسلم replied that he had prayed the two rak'ahs of Fajr, and said that even if it had become brighter, he would pray them well and beautifully. The hadith shows his care for these two rak'ahs."},"teachings":["Bilal came to call the Prophet صلى الله عليه وسلم for the dawn prayer.","A delay happened because Aishah had asked Bilal about a matter.","The Prophet صلى الله عليه وسلم still prayed the two rak'ahs of Fajr.","He spoke about praying them well even if the morning became brighter."],"related_hadiths":[{"id":"724a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"724f","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"725a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E146" s="4" t="n"/>
@@ -3831,7 +3835,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Omit Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said not to omit the two rak'ahs before dawn even when driven away by horses."},"heading":{"title":"Two Rak'ahs Before Fajr Hadith: Do Not Leave Them","description":"This two rak'ahs before Fajr hadith from Abu Hurairah is brief and strong in wording. The Prophet صلى الله عليه وسلم said, “Do not omit them,” referring to the two rak'ahs before the dawn prayer, “even if you are driven away by the horses.” The phrase points to a hard and urgent situation. The text itself teaches care for these two rak'ahs, even under pressure. It should not be turned into a claim that every person in every condition must act without any scholarly detail. Staying with the wording, the hadith shows that the two Sunnah rak'ahs before Fajr were treated with serious attention and should not be taken lightly."},"teachings":["The two rak'ahs before dawn are the focus of the command.","The hadith uses a strong image of pressure and danger.","The wording teaches serious care for Fajr Sunnah.","The narration does not discuss every possible personal situation."],"related_hadiths":[{"id":"724f","book_id":"2","label":"Sahih Muslim"},{"id":"725a","book_id":"2","label":"Sahih Muslim"},{"id":"1182","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Omit Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said not to omit the two rak'ahs before dawn even when driven away by horses."},"heading":{"title":"Two Rak'ahs Before Fajr Hadith: Do Not Leave Them","description":"This two rak'ahs before Fajr hadith from Abu Hurairah is brief and strong in wording. The Prophet صلى الله عليه وسلم said, “Do not omit them,” referring to the two rak'ahs before the dawn prayer, “even if you are driven away by the horses.” The phrase points to a hard and urgent situation. The text itself teaches care for these two rak'ahs, even under pressure. It should not be turned into a claim that every person in every condition must act without any scholarly detail. Staying with the wording, the hadith shows that the two Sunnah rak'ahs before Fajr were treated with serious attention and should not be taken lightly."},"teachings":["The two rak'ahs before dawn are the focus of the command.","The hadith uses a strong image of pressure and danger.","The wording teaches serious care for Fajr Sunnah.","The narration does not discuss every possible personal situation."],"related_hadiths":[{"id":"724f","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"725a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1182","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E147" s="4" t="n"/>
@@ -3854,7 +3858,7 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Verses Recited Before Fajr","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports verses the Prophet صلى الله عليه وسلم often recited in the two dawn Sunnah rak'ahs."},"heading":{"title":"Fajr Sunnah Recitation Hadith: Verses of Belief and Submission","description":"This Fajr Sunnah recitation hadith from Ibn Abbas reports that the Messenger of Allah صلى الله عليه وسلم used to recite in the two rak'ahs of the dawn prayer. In the first rak'ah, he recited the verse beginning, “Say: We believe in Allah and in the revelation given to us.” In the second rak'ah, he recited, “We believe in Allah and bear witness that we submit ourselves to Him.” The focus of the narration is the recitation chosen in these two Sunnah rak'ahs. The words quoted in the report speak about belief in Allah, revelation, and submission. For readers searching what to recite in Fajr Sunnah, this hadith gives one reported practice from Ibn Abbas."},"teachings":["The first rak'ah included a verse about belief in Allah and revelation.","The second rak'ah included words of belief and submission.","The narration connects these verses to the two dawn Sunnah rak'ahs.","The report gives a recitation practice without adding extra details."],"related_hadiths":[{"id":"727a","book_id":"2","label":"Sahih Muslim"},{"id":"727b","book_id":"2","label":"Sahih Muslim"},{"id":"726","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Verses Recited Before Fajr","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports verses the Prophet صلى الله عليه وسلم often recited in the two dawn Sunnah rak'ahs."},"heading":{"title":"Fajr Sunnah Recitation Hadith: Verses of Belief and Submission","description":"This Fajr Sunnah recitation hadith from Ibn Abbas reports that the Messenger of Allah صلى الله عليه وسلم used to recite in the two rak'ahs of the dawn prayer. In the first rak'ah, he recited the verse beginning, “Say: We believe in Allah and in the revelation given to us.” In the second rak'ah, he recited, “We believe in Allah and bear witness that we submit ourselves to Him.” The focus of the narration is the recitation chosen in these two Sunnah rak'ahs. The words quoted in the report speak about belief in Allah, revelation, and submission. For readers searching what to recite in Fajr Sunnah, this hadith gives one reported practice from Ibn Abbas."},"teachings":["The first rak'ah included a verse about belief in Allah and revelation.","The second rak'ah included words of belief and submission.","The narration connects these verses to the two dawn Sunnah rak'ahs.","The report gives a recitation practice without adding extra details."],"related_hadiths":[{"id":"727a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"727b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"726","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E148" s="4" t="n"/>
@@ -3877,7 +3881,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Different Reported Verse in Fajr Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah reports the Prophet’s recitation in dawn Sunnah, with doubt over the second verse."},"heading":{"title":"Fajr Sunnah Recitation Hadith: Reported Verses and Narrator Doubt","description":"This Fajr Sunnah recitation hadith from Abu Hurairah reports that he heard the Prophet صلى الله عليه وسلم recite in the two rak'ahs of dawn. In the first rak'ah, he recited the verse beginning, “Say: We believe in Allah, and in the revelation given to us.” In the second rak'ah, the report mentions either “Our Lord, we have believed in what You have sent down, and we follow the Messenger,” or “Surely, We have sent you with the truth as a bringer of glad tidings and a warner.” The narrator al-Darawardi was unsure which verse was recited. This detail matters because it shows honesty in narration: the doubt is preserved instead of being hidden."},"teachings":["The first rak'ah included a verse about belief in Allah and revelation.","The second rak'ah is reported with narrator doubt between two verses.","The narration openly records al-Darawardi’s uncertainty.","The hadith remains focused on recitation in the two dawn Sunnah rak'ahs."],"related_hadiths":[{"id":"727a","book_id":"2","label":"Sahih Muslim"},{"id":"727b","book_id":"2","label":"Sahih Muslim"},{"id":"726","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Different Reported Verse in Fajr Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah reports the Prophet’s recitation in dawn Sunnah, with doubt over the second verse."},"heading":{"title":"Fajr Sunnah Recitation Hadith: Reported Verses and Narrator Doubt","description":"This Fajr Sunnah recitation hadith from Abu Hurairah reports that he heard the Prophet صلى الله عليه وسلم recite in the two rak'ahs of dawn. In the first rak'ah, he recited the verse beginning, “Say: We believe in Allah, and in the revelation given to us.” In the second rak'ah, the report mentions either “Our Lord, we have believed in what You have sent down, and we follow the Messenger,” or “Surely, We have sent you with the truth as a bringer of glad tidings and a warner.” The narrator al-Darawardi was unsure which verse was recited. This detail matters because it shows honesty in narration: the doubt is preserved instead of being hidden."},"teachings":["The first rak'ah included a verse about belief in Allah and revelation.","The second rak'ah is reported with narrator doubt between two verses.","The narration openly records al-Darawardi’s uncertainty.","The hadith remains focused on recitation in the two dawn Sunnah rak'ahs."],"related_hadiths":[{"id":"727a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"727b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"726","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E149" s="4" t="n"/>
@@ -3900,7 +3904,7 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fajr Sunnah and Resting on the Right Side","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the Fajr Sunnah of lying on the right side after two rak'ahs, with Abu Hurairah's careful memory."},"heading":{"title":"Fajr Sunnah Hadith: Lying on the Right Side After Two Rak'ahs","description":"This hadith about Fajr Sunnah teaches a simple practice after praying the two rak'ahs before the dawn prayer. The Prophet صلى الله عليه وسلم said that when one of you prays these two rak'ahs, he should lie on his right side. The report also shows a respectful discussion among the Companions. Marwan asked whether walking to the mosque would be enough instead of lying down. Abu Hurairah answered no, based on what he remembered. Ibn Umar did not reject the narration, but said Abu Hurairah had been bold in narrating while others had been cautious. Abu Hurairah then said, what was his fault if he remembered and they forgot? The main lesson is about following the Sunnah of Fajr and valuing accurate memory in narrating hadith."},"teachings":["The two rak'ahs before Fajr have a special Sunnah connected to them.","The hadith directly mentions lying on the right side after these two rak'ahs.","The Companions discussed narrations carefully and did not treat memory lightly.","Remembering and sharing a hadith is a trust when done with care."],"related_hadiths":[{"id":"1160","book_id":"1","label":"Sahih Bukhari"},{"id":"743a","book_id":"2","label":"Sahih Muslim"},{"id":"725a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fajr Sunnah and Resting on the Right Side","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the Fajr Sunnah of lying on the right side after two rak'ahs, with Abu Hurairah's careful memory."},"heading":{"title":"Fajr Sunnah Hadith: Lying on the Right Side After Two Rak'ahs","description":"This hadith about Fajr Sunnah teaches a simple practice after praying the two rak'ahs before the dawn prayer. The Prophet صلى الله عليه وسلم said that when one of you prays these two rak'ahs, he should lie on his right side. The report also shows a respectful discussion among the Companions. Marwan asked whether walking to the mosque would be enough instead of lying down. Abu Hurairah answered no, based on what he remembered. Ibn Umar did not reject the narration, but said Abu Hurairah had been bold in narrating while others had been cautious. Abu Hurairah then said, what was his fault if he remembered and they forgot? The main lesson is about following the Sunnah of Fajr and valuing accurate memory in narrating hadith."},"teachings":["The two rak'ahs before Fajr have a special Sunnah connected to them.","The hadith directly mentions lying on the right side after these two rak'ahs.","The Companions discussed narrations carefully and did not treat memory lightly.","Remembering and sharing a hadith is a trust when done with care."],"related_hadiths":[{"id":"1160","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"743a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"725a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E150" s="4" t="n"/>
@@ -3923,7 +3927,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aisha on the Fajr Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Aisha reports that after the two Fajr rak'ahs, the Prophet either rested or spoke with her."},"heading":{"title":"Fajr Sunnah Hadith: Resting or Speaking After Two Rak'ahs","description":"This narration from Aishah is short but very meaningful. It describes what the Prophet صلى الله عليه وسلم would do after praying the two rak'ahs of Fajr. If Aishah was asleep, he would lie down. If she was awake, he would talk to her. The hadith about Fajr Sunnah here is not only about prayer, but also about a gentle and natural home life. The Prophet's action was calm and simple. He did not disturb her if she was asleep, and he spoke to her if she was awake. The text directly supports the idea that the two rak'ahs before Fajr were followed by either rest or conversation, depending on the situation. It teaches us to see worship and kindness together, without adding details beyond the narration."},"teachings":["The two rak'ahs of Fajr are clearly mentioned as part of the Prophet's practice.","If Aishah was sleeping, the Prophet صلى الله عليه وسلم would lie down.","If Aishah was awake, he would speak with her.","The narration shows gentleness in the Prophet's home life."],"related_hadiths":[{"id":"743a","book_id":"2","label":"Sahih Muslim"},{"id":"1160","book_id":"1","label":"Sahih Bukhari"},{"id":"725b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aisha on the Fajr Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Aisha reports that after the two Fajr rak'ahs, the Prophet either rested or spoke with her."},"heading":{"title":"Fajr Sunnah Hadith: Resting or Speaking After Two Rak'ahs","description":"This narration from Aishah is short but very meaningful. It describes what the Prophet صلى الله عليه وسلم would do after praying the two rak'ahs of Fajr. If Aishah was asleep, he would lie down. If she was awake, he would talk to her. The hadith about Fajr Sunnah here is not only about prayer, but also about a gentle and natural home life. The Prophet's action was calm and simple. He did not disturb her if she was asleep, and he spoke to her if she was awake. The text directly supports the idea that the two rak'ahs before Fajr were followed by either rest or conversation, depending on the situation. It teaches us to see worship and kindness together, without adding details beyond the narration."},"teachings":["The two rak'ahs of Fajr are clearly mentioned as part of the Prophet's practice.","If Aishah was sleeping, the Prophet صلى الله عليه وسلم would lie down.","If Aishah was awake, he would speak with her.","The narration shows gentleness in the Prophet's home life."],"related_hadiths":[{"id":"743a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1160","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"725b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E151" s="4" t="n"/>
@@ -3946,7 +3950,7 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Calling People to Fajr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet called or gently moved sleeping people while going out for the dawn prayer."},"heading":{"title":"Fajr Prayer Hadith: Calling Others to the Dawn Prayer","description":"This hadith about Fajr prayer shows the Prophet صلى الله عليه وسلم going out to offer the dawn prayer with Abu Bakrah. As he passed by a sleeping man, he called him for prayer or moved him with his foot. The report is simple and direct. It shows concern for someone who was asleep at the time of prayer. The main message is not about blame or harshness. It is about waking someone for Salah when the dawn prayer is being offered. The hadith also shows that calling people to prayer can be done through action, not only words. The narrator mentions that Ziyad said this tradition was reported by AbulFadl, so the text also preserves the chain detail. The teaching remains clear: Fajr prayer matters, and helping someone wake for it is a caring act."},"teachings":["The Prophet صلى الله عليه وسلم cared about people being present for the dawn prayer.","Calling someone to prayer can be done with words or a gentle action.","The hadith shows concern for a sleeping person at prayer time.","Fajr prayer is treated as something worth waking others for."],"related_hadiths":[{"id":"725a","book_id":"2","label":"Sahih Muslim"},{"id":"586","book_id":"1","label":"Sahih Bukhari"},{"id":"827","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Calling People to Fajr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet called or gently moved sleeping people while going out for the dawn prayer."},"heading":{"title":"Fajr Prayer Hadith: Calling Others to the Dawn Prayer","description":"This hadith about Fajr prayer shows the Prophet صلى الله عليه وسلم going out to offer the dawn prayer with Abu Bakrah. As he passed by a sleeping man, he called him for prayer or moved him with his foot. The report is simple and direct. It shows concern for someone who was asleep at the time of prayer. The main message is not about blame or harshness. It is about waking someone for Salah when the dawn prayer is being offered. The hadith also shows that calling people to prayer can be done through action, not only words. The narrator mentions that Ziyad said this tradition was reported by AbulFadl, so the text also preserves the chain detail. The teaching remains clear: Fajr prayer matters, and helping someone wake for it is a caring act."},"teachings":["The Prophet صلى الله عليه وسلم cared about people being present for the dawn prayer.","Calling someone to prayer can be done with words or a gentle action.","The hadith shows concern for a sleeping person at prayer time.","Fajr prayer is treated as something worth waking others for."],"related_hadiths":[{"id":"725a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"586","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"827","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E152" s="4" t="n"/>
@@ -3969,7 +3973,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Rak'ahs Before Zuhr","description":"$book_name$ $hadith_number$ - $chapter_name$. A report mentions four rak'ahs before Zuhr and notes Abu Dawud's comment on weakness."},"heading":{"title":"Four Rak'ahs Before Zuhr: Gates of Heaven Report","description":"This hadith about four rak'ahs before Zuhr says that the gates of heaven are opened for four rak'ahs before the noon prayer, with no taslim between them as mentioned in the wording. The report also includes important hadith notes from Abu Dawud. He mentions a statement from Yahya bin Said al-Qattan about narrating this report from Ubaidah, and then Abu Dawud clearly says that Ubaidah is weak. He also clarifies the name of Ibn Minjab as Sahm. Because the text itself includes this grading-related note, a careful explanation should mention it. The main message found in the wording is the virtue attached to four rak'ahs before Zuhr, while the transmission note reminds readers not to ignore the condition of narrators when studying hadith."},"teachings":["The report mentions four rak'ahs before the noon prayer.","The wording links these rak'ahs with the gates of heaven being opened.","Abu Dawud directly notes that Ubaidah is weak.","Hadith study includes both the text and the reliability of its chain."],"related_hadiths":[{"id":"730a","book_id":"2","label":"Sahih Muslim"},{"id":"1817","book_id":"3","label":"Sunan an-Nasai"},{"id":"1812","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Rak'ahs Before Zuhr","description":"$book_name$ $hadith_number$ - $chapter_name$. A report mentions four rak'ahs before Zuhr and notes Abu Dawud's comment on weakness."},"heading":{"title":"Four Rak'ahs Before Zuhr: Gates of Heaven Report","description":"This hadith about four rak'ahs before Zuhr says that the gates of heaven are opened for four rak'ahs before the noon prayer, with no taslim between them as mentioned in the wording. The report also includes important hadith notes from Abu Dawud. He mentions a statement from Yahya bin Said al-Qattan about narrating this report from Ubaidah, and then Abu Dawud clearly says that Ubaidah is weak. He also clarifies the name of Ibn Minjab as Sahm. Because the text itself includes this grading-related note, a careful explanation should mention it. The main message found in the wording is the virtue attached to four rak'ahs before Zuhr, while the transmission note reminds readers not to ignore the condition of narrators when studying hadith."},"teachings":["The report mentions four rak'ahs before the noon prayer.","The wording links these rak'ahs with the gates of heaven being opened.","Abu Dawud directly notes that Ubaidah is weak.","Hadith study includes both the text and the reliability of its chain."],"related_hadiths":[{"id":"730a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1817","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"1812","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E153" s="4" t="n"/>
@@ -3992,7 +3996,7 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs Before Maghrib","description":"$book_name$ $hadith_number$ - $chapter_name$. Two rak'ahs before Maghrib are for whoever wishes, showing care not to make optional prayer seem fixed."},"heading":{"title":"Two Rak'ahs Before Maghrib Hadith: An Optional Prayer With Care","description":"This two rakahs before Maghrib hadith teaches a clear and balanced point about optional prayer. The Messenger of Allah (صلى الله عليه وسلم) said to pray two rak'ahs before the Maghrib prayer, then repeated it. After that, he added that it is for those who wish to do so. The wording matters. It shows that this prayer was encouraged, yet not made binding on everyone. The report also says he feared that people might treat it as sunnah in a fixed way. So the main lesson is not only about praying before Maghrib, but also about keeping optional worship in its proper place. A believer can love extra prayer while still respecting the exact limits given in the hadith."},"teachings":["Two rak'ahs before Maghrib are mentioned as an optional act for those who wish.","The Prophet (صلى الله عليه وسلم) clarified the matter so people would not treat it as fixed for all.","Extra worship should be practiced with care and with respect for the wording of the hadith.","Optional prayer has value, but it should not be presented as an obligation."],"related_hadiths":[{"id":"1183","book_id":"1","label":"Sahih Bukhari"},{"id":"627","book_id":"1","label":"Sahih Bukhari"},{"id":"838a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs Before Maghrib","description":"$book_name$ $hadith_number$ - $chapter_name$. Two rak'ahs before Maghrib are for whoever wishes, showing care not to make optional prayer seem fixed."},"heading":{"title":"Two Rak'ahs Before Maghrib Hadith: An Optional Prayer With Care","description":"This two rakahs before Maghrib hadith teaches a clear and balanced point about optional prayer. The Messenger of Allah (صلى الله عليه وسلم) said to pray two rak'ahs before the Maghrib prayer, then repeated it. After that, he added that it is for those who wish to do so. The wording matters. It shows that this prayer was encouraged, yet not made binding on everyone. The report also says he feared that people might treat it as sunnah in a fixed way. So the main lesson is not only about praying before Maghrib, but also about keeping optional worship in its proper place. A believer can love extra prayer while still respecting the exact limits given in the hadith."},"teachings":["Two rak'ahs before Maghrib are mentioned as an optional act for those who wish.","The Prophet (صلى الله عليه وسلم) clarified the matter so people would not treat it as fixed for all.","Extra worship should be practiced with care and with respect for the wording of the hadith.","Optional prayer has value, but it should not be presented as an obligation."],"related_hadiths":[{"id":"1183","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"627","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"838a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E154" s="4" t="n"/>
@@ -4015,7 +4019,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying Before Maghrib","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas prayed two rak'ahs before Maghrib, and the Prophet saw it without command or prohibition."},"heading":{"title":"Praying Before Maghrib Hadith: The Prophet Saw and Did Not Forbid","description":"This praying before Maghrib hadith gives a simple picture from the time of the Messenger of Allah (صلى الله عليه وسلم). Anas b. Malik said that he offered two rak'ahs before the obligatory Maghrib prayer during the Prophet's time. When he was asked whether the Messenger of Allah (صلى الله عليه وسلم) saw them, he answered yes. He then made it clear that the Prophet neither commanded them nor forbade them. The wording is very important for understanding this specific report. It shows that the act was seen and was not stopped, but it was also not ordered here. So the hadith keeps the matter balanced: it records practice, approval by silence, and the absence of a direct command in this narration."},"teachings":["Anas prayed two rak'ahs before Maghrib during the Prophet's lifetime.","The Prophet (صلى الله عليه وسلم) saw this act and did not forbid it.","This narration does not present the act as a direct command from the Prophet.","A silent approval in a report should be understood with the wording given."],"related_hadiths":[{"id":"625","book_id":"1","label":"Sahih Bukhari"},{"id":"1183","book_id":"1","label":"Sahih Bukhari"},{"id":"838a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying Before Maghrib","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas prayed two rak'ahs before Maghrib, and the Prophet saw it without command or prohibition."},"heading":{"title":"Praying Before Maghrib Hadith: The Prophet Saw and Did Not Forbid","description":"This praying before Maghrib hadith gives a simple picture from the time of the Messenger of Allah (صلى الله عليه وسلم). Anas b. Malik said that he offered two rak'ahs before the obligatory Maghrib prayer during the Prophet's time. When he was asked whether the Messenger of Allah (صلى الله عليه وسلم) saw them, he answered yes. He then made it clear that the Prophet neither commanded them nor forbade them. The wording is very important for understanding this specific report. It shows that the act was seen and was not stopped, but it was also not ordered here. So the hadith keeps the matter balanced: it records practice, approval by silence, and the absence of a direct command in this narration."},"teachings":["Anas prayed two rak'ahs before Maghrib during the Prophet's lifetime.","The Prophet (صلى الله عليه وسلم) saw this act and did not forbid it.","This narration does not present the act as a direct command from the Prophet.","A silent approval in a report should be understood with the wording given."],"related_hadiths":[{"id":"625","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1183","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"838a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E155" s="4" t="n"/>
@@ -4038,7 +4042,7 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Between Adhan and Iqamah","description":"$book_name$ $hadith_number$ - $chapter_name$. Between the two adhans there is a prayer for whoever wishes, showing room for voluntary worship."},"heading":{"title":"Prayer Between Adhan and Iqamah Hadith: For Whoever Wishes","description":"This prayer between Adhan and Iqamah hadith speaks about a short but meaningful chance for voluntary prayer. The Messenger of Allah (صلى الله عليه وسلم) said that between the two adhans there is a prayer, and he repeated the meaning. The report then adds that it is for one who desires to offer it. Here, the phrase “two adhans” refers in the translation to the call and the second call connected to the prayer time. The core message is simple: a person may use the time between the call to prayer and the start of the prayer for extra salah. At the same time, the hadith keeps it optional by saying it is for whoever wishes."},"teachings":["There is room for voluntary prayer between the two calls connected to salah.","The act is described for the one who wishes to offer it.","Repeating the statement shows encouragement within the wording of the hadith.","The hadith teaches using small windows of time for worship."],"related_hadiths":[{"id":"624","book_id":"1","label":"Sahih Bukhari"},{"id":"627","book_id":"1","label":"Sahih Bukhari"},{"id":"838a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Between Adhan and Iqamah","description":"$book_name$ $hadith_number$ - $chapter_name$. Between the two adhans there is a prayer for whoever wishes, showing room for voluntary worship."},"heading":{"title":"Prayer Between Adhan and Iqamah Hadith: For Whoever Wishes","description":"This prayer between Adhan and Iqamah hadith speaks about a short but meaningful chance for voluntary prayer. The Messenger of Allah (صلى الله عليه وسلم) said that between the two adhans there is a prayer, and he repeated the meaning. The report then adds that it is for one who desires to offer it. Here, the phrase “two adhans” refers in the translation to the call and the second call connected to the prayer time. The core message is simple: a person may use the time between the call to prayer and the start of the prayer for extra salah. At the same time, the hadith keeps it optional by saying it is for whoever wishes."},"teachings":["There is room for voluntary prayer between the two calls connected to salah.","The act is described for the one who wishes to offer it.","Repeating the statement shows encouragement within the wording of the hadith.","The hadith teaches using small windows of time for worship."],"related_hadiths":[{"id":"624","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"627","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"838a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E156" s="4" t="n"/>
@@ -4061,7 +4065,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Umar on Prayer Before Maghrib","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar said he did not see the two rak'ahs before Maghrib in the Prophet's time."},"heading":{"title":"Ibn Umar on Two Rak'ahs Before Maghrib: A Careful Report","description":"This Ibn Umar two rakahs before Maghrib hadith reports a specific answer from Ibn Umar. He was asked about praying two rak'ahs before the Maghrib prayer. His reply was that he did not see anyone praying them during the time of the Messenger of Allah (صلى الله عليه وسلم). The narration also says that he permitted two rak'ahs after the Asr prayer. This report should be read as his stated observation in this text. It does not add a direct command or prohibition from the Prophet in the wording given here. The last part is a narrator note from Abu Dawud about the name of Abu Shu'aib, showing care in preserving the chain and wording."},"teachings":["Ibn Umar answered based on what he said he had seen during the Prophet's time.","This narration records observation rather than a direct Prophetic command.","The report mentions permission for two rak'ahs after Asr from Ibn Umar.","Abu Dawud's note shows attention to accuracy in narrator names."],"related_hadiths":[{"id":"627","book_id":"1","label":"Sahih Bukhari"},{"id":"838a","book_id":"2","label":"Sahih Muslim"},{"id":"586","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Umar on Prayer Before Maghrib","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar said he did not see the two rak'ahs before Maghrib in the Prophet's time."},"heading":{"title":"Ibn Umar on Two Rak'ahs Before Maghrib: A Careful Report","description":"This Ibn Umar two rakahs before Maghrib hadith reports a specific answer from Ibn Umar. He was asked about praying two rak'ahs before the Maghrib prayer. His reply was that he did not see anyone praying them during the time of the Messenger of Allah (صلى الله عليه وسلم). The narration also says that he permitted two rak'ahs after the Asr prayer. This report should be read as his stated observation in this text. It does not add a direct command or prohibition from the Prophet in the wording given here. The last part is a narrator note from Abu Dawud about the name of Abu Shu'aib, showing care in preserving the chain and wording."},"teachings":["Ibn Umar answered based on what he said he had seen during the Prophet's time.","This narration records observation rather than a direct Prophetic command.","The report mentions permission for two rak'ahs after Asr from Ibn Umar.","Abu Dawud's note shows attention to accuracy in narrator names."],"related_hadiths":[{"id":"627","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"838a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"586","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E157" s="4" t="n"/>
@@ -4084,7 +4088,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Duha Prayer and Daily Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Everyday good deeds count as charity, and two rak'ahs of Duha serve instead of them."},"heading":{"title":"Duha Prayer Charity Hadith: Everyday Good Deeds Count","description":"This Duha prayer charity hadith teaches that charity is not limited to money. The Prophet (صلى الله عليه وسلم) said that in the morning alms are due for every bone in a person's body. Then the hadith gives plain examples: greeting someone is alms, enjoining good is alms, forbidding evil is alms, removing harm from the road is alms, and lawful intimacy with one's wife is also counted as alms. The narration ends by saying that two rak'ahs prayed in Duha serve instead of all of that. The teaching is practical and close to daily life. A Muslim can turn simple, lawful, helpful actions into acts of worship, and Duha prayer is given a special place in this report."},"teachings":["Charity can include words, actions, and helpful behavior.","Greeting people, guiding to good, and removing harm are all named as alms.","Lawful marital intimacy is counted as alms in this narration.","Two rak'ahs of Duha serve instead of the daily charity mentioned in the hadith."],"related_hadiths":[{"id":"720","book_id":"2","label":"Sahih Muslim"},{"id":"1981","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Duha Prayer and Daily Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Everyday good deeds count as charity, and two rak'ahs of Duha serve instead of them."},"heading":{"title":"Duha Prayer Charity Hadith: Everyday Good Deeds Count","description":"This Duha prayer charity hadith teaches that charity is not limited to money. The Prophet (صلى الله عليه وسلم) said that in the morning alms are due for every bone in a person's body. Then the hadith gives plain examples: greeting someone is alms, enjoining good is alms, forbidding evil is alms, removing harm from the road is alms, and lawful intimacy with one's wife is also counted as alms. The narration ends by saying that two rak'ahs prayed in Duha serve instead of all of that. The teaching is practical and close to daily life. A Muslim can turn simple, lawful, helpful actions into acts of worship, and Duha prayer is given a special place in this report."},"teachings":["Charity can include words, actions, and helpful behavior.","Greeting people, guiding to good, and removing harm are all named as alms.","Lawful marital intimacy is counted as alms in this narration.","Two rak'ahs of Duha serve instead of the daily charity mentioned in the hadith."],"related_hadiths":[{"id":"720","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1981","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -4111,7 +4115,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Duha Prayer Replaces Daily Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Prayer, fasting, Hajj, tasbih, takbir, and tahmid are charity, and Duha can serve instead."},"heading":{"title":"Two Rak'ahs of Duha Hadith: A Daily Act of Gratitude","description":"This two rakahs of Duha hadith repeats the theme that each day brings chances to give charity through worship. Abu al-Aswad al-Dailani reported that Abu Dharr said alms are due every day. The report lists prayer as charity, fasting as charity, Hajj as charity, saying “Glory be to Allah” as charity, saying “Allah is most great” as charity, and saying “Praise be to Allah” as charity. The Messenger of Allah (صلى الله عليه وسلم) counted these kinds of good works, then said that two rak'ahs of Duha serve instead of that. The hadith helps a person see Duha prayer as a simple daily worship tied to gratitude, remembrance, and good deeds."},"teachings":["Daily worship can be counted as charity in the wording of this narration.","Tasbih, takbir, and tahmid are named among good works.","Two rak'ahs of Duha serve instead of the listed daily charity.","The hadith links worship, remembrance, and charity in a simple way."],"related_hadiths":[{"id":"720","book_id":"2","label":"Sahih Muslim"},{"id":"1981","book_id":"1","label":"Sahih Bukhari"},{"id":"719a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Duha Prayer Replaces Daily Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Prayer, fasting, Hajj, tasbih, takbir, and tahmid are charity, and Duha can serve instead."},"heading":{"title":"Two Rak'ahs of Duha Hadith: A Daily Act of Gratitude","description":"This two rakahs of Duha hadith repeats the theme that each day brings chances to give charity through worship. Abu al-Aswad al-Dailani reported that Abu Dharr said alms are due every day. The report lists prayer as charity, fasting as charity, Hajj as charity, saying “Glory be to Allah” as charity, saying “Allah is most great” as charity, and saying “Praise be to Allah” as charity. The Messenger of Allah (صلى الله عليه وسلم) counted these kinds of good works, then said that two rak'ahs of Duha serve instead of that. The hadith helps a person see Duha prayer as a simple daily worship tied to gratitude, remembrance, and good deeds."},"teachings":["Daily worship can be counted as charity in the wording of this narration.","Tasbih, takbir, and tahmid are named among good works.","Two rak'ahs of Duha serve instead of the listed daily charity.","The hadith links worship, remembrance, and charity in a simple way."],"related_hadiths":[{"id":"720","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1981","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"719a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E159" s="4" t="n"/>
@@ -4134,7 +4138,7 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sitting After Fajr and Duha","description":"$book_name$ $hadith_number$ - $chapter_name$. Sitting after dawn prayer until Duha with only good speech is linked to forgiveness."},"heading":{"title":"Sitting After Fajr Until Duha Hadith: Good Speech and Forgiveness","description":"This sitting after Fajr until Duha hadith describes a focused act of worship after the dawn prayer. The Prophet (صلى الله عليه وسلم) said that if someone sits in his place of prayer after finishing the dawn prayer until he prays the two rak'ahs of the forenoon, and says nothing except what is good, his sins will be forgiven even if they are more than the foam of the sea. The hadith brings together three clear actions: staying in the prayer place, waiting until the Duha prayer, and guarding the tongue from anything except good. Its message is direct. A quiet morning filled with prayer and good speech is shown as a means of great forgiveness in this narration."},"teachings":["The hadith praises sitting in the prayer place after the dawn prayer.","It connects that sitting with praying two rak'ahs of Duha.","It highlights the value of saying only what is good.","The narration states forgiveness even if sins are more than the foam of the sea."],"related_hadiths":[{"id":"586","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"720","book_id":"2","label":"Sahih Muslim"},{"id":"719a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sitting After Fajr and Duha","description":"$book_name$ $hadith_number$ - $chapter_name$. Sitting after dawn prayer until Duha with only good speech is linked to forgiveness."},"heading":{"title":"Sitting After Fajr Until Duha Hadith: Good Speech and Forgiveness","description":"This sitting after Fajr until Duha hadith describes a focused act of worship after the dawn prayer. The Prophet (صلى الله عليه وسلم) said that if someone sits in his place of prayer after finishing the dawn prayer until he prays the two rak'ahs of the forenoon, and says nothing except what is good, his sins will be forgiven even if they are more than the foam of the sea. The hadith brings together three clear actions: staying in the prayer place, waiting until the Duha prayer, and guarding the tongue from anything except good. Its message is direct. A quiet morning filled with prayer and good speech is shown as a means of great forgiveness in this narration."},"teachings":["The hadith praises sitting in the prayer place after the dawn prayer.","It connects that sitting with praying two rak'ahs of Duha.","It highlights the value of saying only what is good.","The narration states forgiveness even if sins are more than the foam of the sea."],"related_hadiths":[{"id":"586","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"720","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"719a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E160" s="4" t="n"/>
@@ -4157,7 +4161,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer After Prayer Without Idle Talk","description":"$book_name$ $hadith_number$ - $chapter_name$. A prayer followed by prayer with no idle talk between them is recorded in Illiyyun."},"heading":{"title":"Prayer After Prayer Hadith: No Idle Talk Between Worship","description":"This prayer after prayer hadith gives a short but strong lesson about protecting the time between acts of worship. The Prophet (صلى الله عليه وسلم) said that a prayer followed by a prayer, with no idle talk between the two, is recorded in Illiyyun. The hadith does not list many details. It focuses on one clear behavior: avoiding useless speech between prayers. This makes the time between two prayers feel valuable, not empty. A believer can use that time with silence, remembrance, or good words instead of talk that has no benefit. The phrase “recorded in Illiyyun” is exactly how the reward is described in the text, so the explanation should stay close to that wording."},"teachings":["The hadith praises connecting one prayer to another.","It warns against idle talk between acts of worship.","The narration says such prayer is recorded in Illiyyun.","Time between prayers should be treated with care."],"related_hadiths":[{"id":"627","book_id":"1","label":"Sahih Bukhari"},{"id":"838a","book_id":"2","label":"Sahih Muslim"},{"id":"586","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer After Prayer Without Idle Talk","description":"$book_name$ $hadith_number$ - $chapter_name$. A prayer followed by prayer with no idle talk between them is recorded in Illiyyun."},"heading":{"title":"Prayer After Prayer Hadith: No Idle Talk Between Worship","description":"This prayer after prayer hadith gives a short but strong lesson about protecting the time between acts of worship. The Prophet (صلى الله عليه وسلم) said that a prayer followed by a prayer, with no idle talk between the two, is recorded in Illiyyun. The hadith does not list many details. It focuses on one clear behavior: avoiding useless speech between prayers. This makes the time between two prayers feel valuable, not empty. A believer can use that time with silence, remembrance, or good words instead of talk that has no benefit. The phrase “recorded in Illiyyun” is exactly how the reward is described in the text, so the explanation should stay close to that wording."},"teachings":["The hadith praises connecting one prayer to another.","It warns against idle talk between acts of worship.","The narration says such prayer is recorded in Illiyyun.","Time between prayers should be treated with care."],"related_hadiths":[{"id":"627","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"838a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"586","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E161" s="4" t="n"/>
@@ -4180,7 +4184,7 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Rak'ahs at the Beginning of the Day","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah says four rak'ahs at the start of the day are tied to His care until day's end."},"heading":{"title":"Four Rak'ahs at the Beginning of the Day Hadith: Start With Prayer","description":"This four rakahs at the beginning of the day hadith is narrated as a statement from Allah, the Exalted. The Prophet (صلى الله عليه وسلم) said that Allah says: Son of Adam, do not be helpless in performing four rak'ahs for Me at the beginning of the day; I will supply what you need until the end of it. The wording gives a clear call to begin the day with prayer. It does not list the details of each rak'ah in this narration. It focuses on the number, the time, and the promise mentioned in the text. The hadith encourages a believer not to neglect early worship and to meet the day with salah before becoming busy with other matters."},"teachings":["The hadith calls for four rak'ahs at the beginning of the day.","It teaches not to be helpless or neglectful in early prayer.","The narration states that Allah will supply what is needed until the end of the day.","Starting the day with prayer is presented as a meaningful act of worship."],"related_hadiths":[{"id":"475","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"719a","book_id":"2","label":"Sahih Muslim"},{"id":"1981","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Rak'ahs at the Beginning of the Day","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah says four rak'ahs at the start of the day are tied to His care until day's end."},"heading":{"title":"Four Rak'ahs at the Beginning of the Day Hadith: Start With Prayer","description":"This four rakahs at the beginning of the day hadith is narrated as a statement from Allah, the Exalted. The Prophet (صلى الله عليه وسلم) said that Allah says: Son of Adam, do not be helpless in performing four rak'ahs for Me at the beginning of the day; I will supply what you need until the end of it. The wording gives a clear call to begin the day with prayer. It does not list the details of each rak'ah in this narration. It focuses on the number, the time, and the promise mentioned in the text. The hadith encourages a believer not to neglect early worship and to meet the day with salah before becoming busy with other matters."},"teachings":["The hadith calls for four rak'ahs at the beginning of the day.","It teaches not to be helpless or neglectful in early prayer.","The narration states that Allah will supply what is needed until the end of the day.","Starting the day with prayer is presented as a meaningful act of worship."],"related_hadiths":[{"id":"475","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"719a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1981","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E162" s="4" t="n"/>
@@ -4203,7 +4207,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eight Rak'ahs of Duha","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Hani reports eight rak'ahs on the day of the Conquest, with salutation after every two."},"heading":{"title":"Eight Rak'ahs of Duha Hadith: Salutation After Every Two","description":"This eight rakahs of Duha hadith reports what Umm Hani bint Abi Talib saw on the day of the Conquest of Mecca. The Messenger of Allah (صلى الله عليه وسلم) prayed eight rak'ahs and gave salutation after every two rak'ahs. The report is focused on the action itself: the day, the number of rak'ahs, and the way the prayer was divided. Abu Dawud also mentions wording differences from narrators. One version clearly says it was the forenoon prayer on the day of the Conquest, while another version says the Messenger of Allah entered upon Umm Hani and does not mention the forenoon prayer in that wording. The safe reading is to stay with the details each version gives."},"teachings":["Umm Hani reported eight rak'ahs connected to the day of the Conquest.","The prayer was described as being completed with salutation after every two rak'ahs.","The narration preserves differences in wording between transmitters.","The hadith teaches careful attention to how each report is worded."],"related_hadiths":[{"id":"1176","book_id":"1","label":"Sahih Bukhari"},{"id":"336f","book_id":"2","label":"Sahih Muslim"},{"id":"336g","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eight Rak'ahs of Duha","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Hani reports eight rak'ahs on the day of the Conquest, with salutation after every two."},"heading":{"title":"Eight Rak'ahs of Duha Hadith: Salutation After Every Two","description":"This eight rakahs of Duha hadith reports what Umm Hani bint Abi Talib saw on the day of the Conquest of Mecca. The Messenger of Allah (صلى الله عليه وسلم) prayed eight rak'ahs and gave salutation after every two rak'ahs. The report is focused on the action itself: the day, the number of rak'ahs, and the way the prayer was divided. Abu Dawud also mentions wording differences from narrators. One version clearly says it was the forenoon prayer on the day of the Conquest, while another version says the Messenger of Allah entered upon Umm Hani and does not mention the forenoon prayer in that wording. The safe reading is to stay with the details each version gives."},"teachings":["Umm Hani reported eight rak'ahs connected to the day of the Conquest.","The prayer was described as being completed with salutation after every two rak'ahs.","The narration preserves differences in wording between transmitters.","The hadith teaches careful attention to how each report is worded."],"related_hadiths":[{"id":"1176","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"336f","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"336g","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E163" s="4" t="n"/>
@@ -4226,7 +4230,7 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aishah on Duha Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah said the Prophet did not pray Duha except when returning from a journey."},"heading":{"title":"Aishah on Duha Prayer Hadith: Returning From a Journey","description":"This Aishah on Duha prayer hadith gives a direct question and answer. Abd Allah b. Shaqiq asked Aishah whether the Messenger of Allah (صلى الله عليه وسلم) prayed in the Duha. She replied: no, except when he returned from his journey. The same report then moves to another question about reciting surahs together. Aishah said he would do so in the mufassal surahs. For this specific hadith, the core message about Duha is tied to return from travel. It should not be stretched into details not found in the text. The narration also shows how companions and later narrators asked clear questions about the Prophet's prayer practice and preserved concise answers."},"teachings":["Aishah answered that the Prophet (صلى الله عليه وسلم) did not pray Duha except when returning from travel.","The narration keeps the Duha detail tied to a specific condition.","The report also mentions combining surahs from the mufassal surahs.","Clear questions helped preserve details about the Prophet's prayer."],"related_hadiths":[{"id":"719a","book_id":"2","label":"Sahih Muslim"},{"id":"1176","book_id":"1","label":"Sahih Bukhari"},{"id":"336f","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aishah on Duha Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah said the Prophet did not pray Duha except when returning from a journey."},"heading":{"title":"Aishah on Duha Prayer Hadith: Returning From a Journey","description":"This Aishah on Duha prayer hadith gives a direct question and answer. Abd Allah b. Shaqiq asked Aishah whether the Messenger of Allah (صلى الله عليه وسلم) prayed in the Duha. She replied: no, except when he returned from his journey. The same report then moves to another question about reciting surahs together. Aishah said he would do so in the mufassal surahs. For this specific hadith, the core message about Duha is tied to return from travel. It should not be stretched into details not found in the text. The narration also shows how companions and later narrators asked clear questions about the Prophet's prayer practice and preserved concise answers."},"teachings":["Aishah answered that the Prophet (صلى الله عليه وسلم) did not pray Duha except when returning from travel.","The narration keeps the Duha detail tied to a specific condition.","The report also mentions combining surahs from the mufassal surahs.","Clear questions helped preserve details about the Prophet's prayer."],"related_hadiths":[{"id":"719a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1176","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"336f","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E164" s="4" t="n"/>
@@ -4249,7 +4253,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Why the Prophet Left Some Good Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah explains that the Prophet left some loved actions so they would not become prescribed."},"heading":{"title":"Why the Prophet Left Some Good Deeds: Aishah on Duha Prayer","description":"This hadith about why the Prophet left some good deeds is explained through Aishah's words. She said that the Messenger of Allah (صلى الله عليه وسلم) never offered the forenoon prayer, but she herself offered it. Then she gave a reason connected to the Prophet's care for the people. He would leave an action, though he liked to do it, out of fear that people would continue doing it and it would be prescribed for them. The main lesson is about mercy and caution in worship. The hadith does not say people should reject the forenoon prayer, because Aishah says she offered it. It says the Prophet sometimes left a loved action to protect the community from extra burden."},"teachings":["Aishah said she offered the forenoon prayer though the Prophet did not do so in this report.","The Prophet (صلى الله عليه وسلم) could leave an action he liked out of care for the people.","The hadith shows fear that a repeated action might become prescribed for the community.","A loved act of worship may still be left for a wise reason."],"related_hadiths":[{"id":"731","book_id":"1","label":"Sahih Bukhari"},{"id":"719a","book_id":"2","label":"Sahih Muslim"},{"id":"1176","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Why the Prophet Left Some Good Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah explains that the Prophet left some loved actions so they would not become prescribed."},"heading":{"title":"Why the Prophet Left Some Good Deeds: Aishah on Duha Prayer","description":"This hadith about why the Prophet left some good deeds is explained through Aishah's words. She said that the Messenger of Allah (صلى الله عليه وسلم) never offered the forenoon prayer, but she herself offered it. Then she gave a reason connected to the Prophet's care for the people. He would leave an action, though he liked to do it, out of fear that people would continue doing it and it would be prescribed for them. The main lesson is about mercy and caution in worship. The hadith does not say people should reject the forenoon prayer, because Aishah says she offered it. It says the Prophet sometimes left a loved action to protect the community from extra burden."},"teachings":["Aishah said she offered the forenoon prayer though the Prophet did not do so in this report.","The Prophet (صلى الله عليه وسلم) could leave an action he liked out of care for the people.","The hadith shows fear that a repeated action might become prescribed for the community.","A loved act of worship may still be left for a wise reason."],"related_hadiths":[{"id":"731","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"719a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1176","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E165" s="4" t="n"/>
@@ -4272,7 +4276,7 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sitting After Dawn Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet would remain where he prayed dawn until sunrise, then stand."},"heading":{"title":"Sitting After Dawn Prayer Hadith: Staying Until Sunrise","description":"This sitting after dawn prayer hadith comes through Jabir b. Samurah. He was asked whether he sat in the company of the Messenger of Allah (صلى الله عليه وسلم), and he replied that he did so very often. He then described a regular scene: the Prophet would not stand from the place where he prayed the dawn prayer until the sun rose. When the sun rose, he would stand. The translation connects this with praying Duha. The clear point from the hadith is the Prophet's calm stay after the dawn prayer until sunrise. It shows a morning habit centered on prayer, waiting, and leaving the prayer place only after the sun had risen."},"teachings":["Jabir b. Samurah reported frequent sitting with the Prophet (صلى الله عليه وسلم).","The Prophet stayed in the place of the dawn prayer until sunrise.","The narration connects the time after Fajr with quiet waiting.","The report shows a morning practice tied to the prayer place."],"related_hadiths":[{"id":"670a","book_id":"2","label":"Sahih Muslim"},{"id":"1287","book_id":"4","label":"Sunan Abu Dawud"},{"id":"586","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sitting After Dawn Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet would remain where he prayed dawn until sunrise, then stand."},"heading":{"title":"Sitting After Dawn Prayer Hadith: Staying Until Sunrise","description":"This sitting after dawn prayer hadith comes through Jabir b. Samurah. He was asked whether he sat in the company of the Messenger of Allah (صلى الله عليه وسلم), and he replied that he did so very often. He then described a regular scene: the Prophet would not stand from the place where he prayed the dawn prayer until the sun rose. When the sun rose, he would stand. The translation connects this with praying Duha. The clear point from the hadith is the Prophet's calm stay after the dawn prayer until sunrise. It shows a morning habit centered on prayer, waiting, and leaving the prayer place only after the sun had risen."},"teachings":["Jabir b. Samurah reported frequent sitting with the Prophet (صلى الله عليه وسلم).","The Prophet stayed in the place of the dawn prayer until sunrise.","The narration connects the time after Fajr with quiet waiting.","The report shows a morning practice tied to the prayer place."],"related_hadiths":[{"id":"670a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1287","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"586","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E166" s="4" t="n"/>
@@ -4295,7 +4299,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer in Pairs of Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Night and day prayers are described as being offered in pairs of rak'ahs."},"heading":{"title":"Prayer in Pairs of Rak'ahs Hadith: Night and Day Prayer","description":"This prayer in pairs of rakahs hadith gives a short rule-like statement from the Prophet (صلى الله عليه وسلم). Abdullah ibn Umar narrated that prayer by night and day should consist of pairs of rak'ahs. The wording is simple: night and day prayer are mentioned, and the form is described as pairs. The hadith does not add a long explanation in this report. Its value is in how clear it is. When someone searches for “two by two prayer hadith” or “night prayer in pairs,” this narration directly speaks to that subject. It reminds the reader that the structure of voluntary prayer has guidance, and that pairs of rak'ahs are an important pattern in the prayer practice described here."},"teachings":["The hadith describes night and day prayer as pairs of rak'ahs.","Ibn Umar narrated this wording from the Prophet (صلى الله عليه وسلم).","The report gives a clear structure without extra detail.","Prayer form should be learned from narrated guidance."],"related_hadiths":[{"id":"990","book_id":"1","label":"Sahih Bukhari"},{"id":"749a","book_id":"2","label":"Sahih Muslim"},{"id":"1693","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer in Pairs of Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Night and day prayers are described as being offered in pairs of rak'ahs."},"heading":{"title":"Prayer in Pairs of Rak'ahs Hadith: Night and Day Prayer","description":"This prayer in pairs of rakahs hadith gives a short rule-like statement from the Prophet (صلى الله عليه وسلم). Abdullah ibn Umar narrated that prayer by night and day should consist of pairs of rak'ahs. The wording is simple: night and day prayer are mentioned, and the form is described as pairs. The hadith does not add a long explanation in this report. Its value is in how clear it is. When someone searches for “two by two prayer hadith” or “night prayer in pairs,” this narration directly speaks to that subject. It reminds the reader that the structure of voluntary prayer has guidance, and that pairs of rak'ahs are an important pattern in the prayer practice described here."},"teachings":["The hadith describes night and day prayer as pairs of rak'ahs.","Ibn Umar narrated this wording from the Prophet (صلى الله عليه وسلم).","The report gives a clear structure without extra detail.","Prayer form should be learned from narrated guidance."],"related_hadiths":[{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"749a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1693","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E167" s="4" t="n"/>
@@ -4318,7 +4322,7 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs With Humility","description":"$book_name$ $hadith_number$ - $chapter_name$. Prayer is described in pairs, with tashahhud, humility, raised hands, and supplication."},"heading":{"title":"Two Rak'ahs With Tashahhud Hadith: Humility in Prayer","description":"This two rakahs with tashahhud hadith describes prayer with both structure and feeling. The Prophet (صلى الله عليه وسلم) said that prayer is to be offered in two rak'ahs. He then mentioned reciting the tashahhud at the end of two rak'ahs, expressing distress and humility, raising the hands, and saying in supplication: O Allah, O Allah. The report says that whoever does not do so does not offer a perfect prayer. The focus is not only the number of rak'ahs. It also points to a humble heart and a needy posture before Allah. Abu Dawud's added answer about night prayer records a separate comment: it may be two if one likes and four if one likes."},"teachings":["The hadith describes prayer as being offered in two rak'ahs.","It mentions tashahhud at the end of two rak'ahs.","Humility, need, raised hands, and supplication are named in the report.","The narration says leaving this makes the prayer imperfect."],"related_hadiths":[{"id":"990","book_id":"1","label":"Sahih Bukhari"},{"id":"749a","book_id":"2","label":"Sahih Muslim"},{"id":"1295","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs With Humility","description":"$book_name$ $hadith_number$ - $chapter_name$. Prayer is described in pairs, with tashahhud, humility, raised hands, and supplication."},"heading":{"title":"Two Rak'ahs With Tashahhud Hadith: Humility in Prayer","description":"This two rakahs with tashahhud hadith describes prayer with both structure and feeling. The Prophet (صلى الله عليه وسلم) said that prayer is to be offered in two rak'ahs. He then mentioned reciting the tashahhud at the end of two rak'ahs, expressing distress and humility, raising the hands, and saying in supplication: O Allah, O Allah. The report says that whoever does not do so does not offer a perfect prayer. The focus is not only the number of rak'ahs. It also points to a humble heart and a needy posture before Allah. Abu Dawud's added answer about night prayer records a separate comment: it may be two if one likes and four if one likes."},"teachings":["The hadith describes prayer as being offered in two rak'ahs.","It mentions tashahhud at the end of two rak'ahs.","Humility, need, raised hands, and supplication are named in the report.","The narration says leaving this makes the prayer imperfect."],"related_hadiths":[{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"749a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1295","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E168" s="4" t="n"/>
@@ -4341,7 +4345,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Salat al-Tasbih Explained","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught al-Abbas four rak'ahs with repeated tasbih, tahmid, tahlil, and takbir."},"heading":{"title":"Salat al-Tasbih Hadith: Four Rak'ahs With Repeated Remembrance","description":"This Salat al-Tasbih hadith gives a detailed prayer taught to al-Abbas ibn AbdulMuttalib. The Prophet (صلى الله عليه وسلم) described four rak'ahs, with Fatihat al-Kitab and a surah in each rak'ah. After the recitation in the first rak'ah, the person says: Glory be to Allah, Praise be to Allah, there is no god but Allah, and Allah is most great, fifteen times while standing. The same words are then repeated ten times in bowing, after rising from bowing, in prostration, after rising, in the second prostration, and after rising again. The hadith also gives flexible timing: daily if possible, otherwise weekly, monthly, yearly, or once in a lifetime."},"teachings":["The prayer is described as four rak'ahs with Qur'an recitation in each rak'ah.","The hadith gives a repeated set of remembrance words in each prayer posture.","The narration mentions seventy-five repetitions in each rak'ah.","The timing is made flexible for what a person is able to do."],"related_hadiths":[{"id":"481","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1387","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Salat al-Tasbih Explained","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught al-Abbas four rak'ahs with repeated tasbih, tahmid, tahlil, and takbir."},"heading":{"title":"Salat al-Tasbih Hadith: Four Rak'ahs With Repeated Remembrance","description":"This Salat al-Tasbih hadith gives a detailed prayer taught to al-Abbas ibn AbdulMuttalib. The Prophet (صلى الله عليه وسلم) described four rak'ahs, with Fatihat al-Kitab and a surah in each rak'ah. After the recitation in the first rak'ah, the person says: Glory be to Allah, Praise be to Allah, there is no god but Allah, and Allah is most great, fifteen times while standing. The same words are then repeated ten times in bowing, after rising from bowing, in prostration, after rising, in the second prostration, and after rising again. The hadith also gives flexible timing: daily if possible, otherwise weekly, monthly, yearly, or once in a lifetime."},"teachings":["The prayer is described as four rak'ahs with Qur'an recitation in each rak'ah.","The hadith gives a repeated set of remembrance words in each prayer posture.","The narration mentions seventy-five repetitions in each rak'ah.","The timing is made flexible for what a person is able to do."],"related_hadiths":[{"id":"481","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1387","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
@@ -4368,7 +4372,7 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Salat al-Tasbih Timing","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions four rak'ahs after the day declines, with tasbih and flexible timing."},"heading":{"title":"Salat al-Tasbih Timing Hadith: Pray It by Night or Day","description":"This Salat al-Tasbih timing hadith is another report about the same type of prayer. The narrator first thought the Prophet (صلى الله عليه وسلم) would give him a material gift, but the Prophet taught him a prayer. He said that when the day declines, he should stand and pray four rak'ahs. The report then mentions words of glorification, praise, exaltation, and tahlil, said ten times in the sitting after the second prostration before standing. It also says this is done through the four rak'ahs. When the narrator asked what to do if he could not pray at that appointed hour, the Prophet answered that he should pray it by night or by day. The hadith focuses on worship as a gift."},"teachings":["The Prophet (صلى الله عليه وسلم) presented this prayer as a gift of worship.","The narration mentions praying four rak'ahs when the day declines.","It includes repeated tasbih, tahmid, takbir, and tahlil.","If the stated time cannot be met, the narration allows praying it by night or day."],"related_hadiths":[{"id":"481","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1387","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1297","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Salat al-Tasbih Timing","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions four rak'ahs after the day declines, with tasbih and flexible timing."},"heading":{"title":"Salat al-Tasbih Timing Hadith: Pray It by Night or Day","description":"This Salat al-Tasbih timing hadith is another report about the same type of prayer. The narrator first thought the Prophet (صلى الله عليه وسلم) would give him a material gift, but the Prophet taught him a prayer. He said that when the day declines, he should stand and pray four rak'ahs. The report then mentions words of glorification, praise, exaltation, and tahlil, said ten times in the sitting after the second prostration before standing. It also says this is done through the four rak'ahs. When the narrator asked what to do if he could not pray at that appointed hour, the Prophet answered that he should pray it by night or by day. The hadith focuses on worship as a gift."},"teachings":["The Prophet (صلى الله عليه وسلم) presented this prayer as a gift of worship.","The narration mentions praying four rak'ahs when the day declines.","It includes repeated tasbih, tahmid, takbir, and tahlil.","If the stated time cannot be met, the narration allows praying it by night or day."],"related_hadiths":[{"id":"481","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1387","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1297","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E170" s="4" t="n"/>
@@ -4391,7 +4395,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ja'far and Salat al-Tasbih","description":"$book_name$ $hadith_number$ - $chapter_name$. This version reports the same Tasbih prayer with an added wording about the second prostration."},"heading":{"title":"Ja'far Salat al-Tasbih Hadith: A Variant With Added Detail","description":"This Ja'far Salat al-Tasbih hadith is a short variant report. Urwah b. Ruwaim narrated that an Ansari told him that the Messenger of Allah (صلى الله عليه وسلم) said this hadith to Ja'far. The narration says it was reported in a similar manner to the earlier Tasbih prayer narration. Its special added wording is about “the second prostration of the first rak'ah,” matching the wording transmitted by Mahdi b. Maimun in the previous report. Because this text is brief, the safe explanation is also brief in meaning: it preserves another route of the Tasbih prayer report and highlights one added detail about where the repeated remembrance is placed in the prayer sequence."},"teachings":["This narration links the Tasbih prayer report to Ja'far.","It says the report was narrated in a similar manner to the earlier version.","The added detail concerns the second prostration of the first rak'ah.","The narration shows how small wording differences are preserved."],"related_hadiths":[{"id":"481","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1387","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1297","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ja'far and Salat al-Tasbih","description":"$book_name$ $hadith_number$ - $chapter_name$. This version reports the same Tasbih prayer with an added wording about the second prostration."},"heading":{"title":"Ja'far Salat al-Tasbih Hadith: A Variant With Added Detail","description":"This Ja'far Salat al-Tasbih hadith is a short variant report. Urwah b. Ruwaim narrated that an Ansari told him that the Messenger of Allah (صلى الله عليه وسلم) said this hadith to Ja'far. The narration says it was reported in a similar manner to the earlier Tasbih prayer narration. Its special added wording is about “the second prostration of the first rak'ah,” matching the wording transmitted by Mahdi b. Maimun in the previous report. Because this text is brief, the safe explanation is also brief in meaning: it preserves another route of the Tasbih prayer report and highlights one added detail about where the repeated remembrance is placed in the prayer sequence."},"teachings":["This narration links the Tasbih prayer report to Ja'far.","It says the report was narrated in a similar manner to the earlier version.","The added detail concerns the second prostration of the first rak'ah.","The narration shows how small wording differences are preserved."],"related_hadiths":[{"id":"481","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1387","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1297","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E171" s="4" t="n"/>
@@ -4414,7 +4418,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Voluntary Prayer at Home","description":"$book_name$ $hadith_number$ - $chapter_name$. After Maghrib, the Prophet pointed to voluntary prayer as a prayer for the houses."},"heading":{"title":"Voluntary Prayer at Home Hadith: The Prayer of the Houses","description":"This voluntary prayer at home hadith reports an event in the mosque of Banu AbdulAshhal. The Prophet (صلى الله عليه وسلم) came there and prayed the sunset prayer. After the people finished the prayer, he saw them praying the supererogatory prayer after it. He then said: This is the prayer to be offered in the houses. The hadith is focused on the prayer after Maghrib in this scene. It does not say that the obligatory Maghrib prayer is to be prayed at home. Rather, the wording points to the extra prayer after it. The main lesson is simple: some voluntary prayers have a place in the home, and worship should not be limited to the mosque only."},"teachings":["The Prophet (صلى الله عليه وسلم) prayed Maghrib in the mosque of Banu AbdulAshhal.","He saw people praying the supererogatory prayer after Maghrib.","He described that extra prayer as a prayer for the houses.","The narration shows that the home can be a place for voluntary worship."],"related_hadiths":[{"id":"731","book_id":"1","label":"Sahih Bukhari"},{"id":"781","book_id":"2","label":"Sahih Muslim"},{"id":"450","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Voluntary Prayer at Home","description":"$book_name$ $hadith_number$ - $chapter_name$. After Maghrib, the Prophet pointed to voluntary prayer as a prayer for the houses."},"heading":{"title":"Voluntary Prayer at Home Hadith: The Prayer of the Houses","description":"This voluntary prayer at home hadith reports an event in the mosque of Banu AbdulAshhal. The Prophet (صلى الله عليه وسلم) came there and prayed the sunset prayer. After the people finished the prayer, he saw them praying the supererogatory prayer after it. He then said: This is the prayer to be offered in the houses. The hadith is focused on the prayer after Maghrib in this scene. It does not say that the obligatory Maghrib prayer is to be prayed at home. Rather, the wording points to the extra prayer after it. The main lesson is simple: some voluntary prayers have a place in the home, and worship should not be limited to the mosque only."},"teachings":["The Prophet (صلى الله عليه وسلم) prayed Maghrib in the mosque of Banu AbdulAshhal.","He saw people praying the supererogatory prayer after Maghrib.","He described that extra prayer as a prayer for the houses.","The narration shows that the home can be a place for voluntary worship."],"related_hadiths":[{"id":"731","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"781","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"450","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E172" s="4" t="n"/>
@@ -4437,7 +4441,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mursal Report and Ibn Abbas Chain","description":"$book_name$ $hadith_number$ - $chapter_name$. Understand Abu Dawud's note on the mursal form and how Ya'qub linked these reports back to Ibn Abbas."},"heading":{"title":"Mursal Hadith Report on the Maghrib Sunnah Prayer Chain","description":"This narration is mainly about the chain of the previous report, so the core topic is hadith chain and mursal hadith. Sa'id b. Jubair narrated the meaning from the Prophet صلى الله عليه وسلم without naming the Companion in the chain, which is called mursal in the translation. Abu Dawud then records a statement from Ya'qub: anything he narrated from Ja'far, from Sa'id b. Jubair, from the Prophet صلى الله عليه وسلم, is actually connected through Ibn Abbas from the Prophet صلى الله عليه وسلم. For a reader searching mursal hadith meaning or Sunan Abu Dawud 1302 explanation, this hadith shows how scholars preserved details about transmission, not only the wording of the worship practice itself."},"teachings":["The narration gives attention to the way a hadith is transmitted.","Abu Dawud records a clarification about the missing Companion link.","The same meaning is connected to Ibn Abbas according to the report.","The text teaches care when quoting prophetic reports."],"related_hadiths":[{"id":"1172","book_id":"1","label":"Sahih Bukhari"},{"id":"1180","book_id":"1","label":"Sahih Bukhari"},{"id":"1183","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mursal Report and Ibn Abbas Chain","description":"$book_name$ $hadith_number$ - $chapter_name$. Understand Abu Dawud's note on the mursal form and how Ya'qub linked these reports back to Ibn Abbas."},"heading":{"title":"Mursal Hadith Report on the Maghrib Sunnah Prayer Chain","description":"This narration is mainly about the chain of the previous report, so the core topic is hadith chain and mursal hadith. Sa'id b. Jubair narrated the meaning from the Prophet صلى الله عليه وسلم without naming the Companion in the chain, which is called mursal in the translation. Abu Dawud then records a statement from Ya'qub: anything he narrated from Ja'far, from Sa'id b. Jubair, from the Prophet صلى الله عليه وسلم, is actually connected through Ibn Abbas from the Prophet صلى الله عليه وسلم. For a reader searching mursal hadith meaning or Sunan Abu Dawud 1302 explanation, this hadith shows how scholars preserved details about transmission, not only the wording of the worship practice itself."},"teachings":["The narration gives attention to the way a hadith is transmitted.","Abu Dawud records a clarification about the missing Companion link.","The same meaning is connected to Ibn Abbas according to the report.","The text teaches care when quoting prophetic reports."],"related_hadiths":[{"id":"1172","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1180","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1183","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E173" s="4" t="n"/>
@@ -4460,7 +4464,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four or Six Rak'ahs After Isha","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn from Aisha's report on the Prophet's night prayer after Isha and his simple worship during rain."},"heading":{"title":"Hadith About Night Prayer After Isha: Four or Six Rak'ahs","description":"This hadith is about night prayer after Isha, also searched as tahajjud prayer hadith and qiyam al layl hadith. Aisha was asked about the prayer of the Messenger of Allah صلى الله عليه وسلم. She said that whenever he prayed Isha and then came to her, he would offer four or six rak'ahs. The report also describes a rainy night. A piece of leather was spread for him, and Aisha remembered water flowing through a hole in it. She added that she did not see him protecting his clothes from the earth as he did then. The hadith gives a close view of worship in a home setting, with prayer continuing even during difficult weather."},"teachings":["The Prophet صلى الله عليه وسلم prayed after Isha when he came to Aisha.","Aisha described four or six rak'ahs in this report.","Rain and simple conditions did not stop the prayer mentioned here.","The report shows a remembered detail from the Prophet's home life."],"related_hadiths":[{"id":"1139","book_id":"1","label":"Sahih Bukhari"},{"id":"1140","book_id":"1","label":"Sahih Bukhari"},{"id":"1131","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four or Six Rak'ahs After Isha","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn from Aisha's report on the Prophet's night prayer after Isha and his simple worship during rain."},"heading":{"title":"Hadith About Night Prayer After Isha: Four or Six Rak'ahs","description":"This hadith is about night prayer after Isha, also searched as tahajjud prayer hadith and qiyam al layl hadith. Aisha was asked about the prayer of the Messenger of Allah صلى الله عليه وسلم. She said that whenever he prayed Isha and then came to her, he would offer four or six rak'ahs. The report also describes a rainy night. A piece of leather was spread for him, and Aisha remembered water flowing through a hole in it. She added that she did not see him protecting his clothes from the earth as he did then. The hadith gives a close view of worship in a home setting, with prayer continuing even during difficult weather."},"teachings":["The Prophet صلى الله عليه وسلم prayed after Isha when he came to Aisha.","Aisha described four or six rak'ahs in this report.","Rain and simple conditions did not stop the prayer mentioned here.","The report shows a remembered detail from the Prophet's home life."],"related_hadiths":[{"id":"1139","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1140","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1131","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E174" s="4" t="n"/>
@@ -4483,7 +4487,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah Al-Muzzammil and Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Read Ibn Abbas's explanation of Surah Al-Muzzammil, night prayer, ease in recitation, and early-night worship."},"heading":{"title":"Surah Al-Muzzammil Night Prayer Hadith and Easy Qur'an Recitation","description":"This narration is centered on Surah Al-Muzzammil night prayer and the command to recite what is easy from the Qur'an. Ibn Abbas explains that the earlier verses about standing at night were abrogated by the later verse that says Allah knew they could not count it fully and turned to them in mercy. He also explains that nashi'at al-layl refers to the early hours of the night. The hadith says the Companions prayed in the early part of the night because a person who sleeps does not know when he will wake up. It also says this time is better for understanding the Qur'an, while the day contains long work and engagement."},"teachings":["The later verse brought ease in night recitation.","Ibn Abbas linked early-night prayer with being able to complete it.","The report connects night worship with understanding the Qur'an.","The text notes that daytime has long periods of work."],"related_hadiths":[{"id":"1131","book_id":"1","label":"Sahih Bukhari"},{"id":"1137","book_id":"1","label":"Sahih Bukhari"},{"id":"1145","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah Al-Muzzammil and Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Read Ibn Abbas's explanation of Surah Al-Muzzammil, night prayer, ease in recitation, and early-night worship."},"heading":{"title":"Surah Al-Muzzammil Night Prayer Hadith and Easy Qur'an Recitation","description":"This narration is centered on Surah Al-Muzzammil night prayer and the command to recite what is easy from the Qur'an. Ibn Abbas explains that the earlier verses about standing at night were abrogated by the later verse that says Allah knew they could not count it fully and turned to them in mercy. He also explains that nashi'at al-layl refers to the early hours of the night. The hadith says the Companions prayed in the early part of the night because a person who sleeps does not know when he will wake up. It also says this time is better for understanding the Qur'an, while the day contains long work and engagement."},"teachings":["The later verse brought ease in night recitation.","Ibn Abbas linked early-night prayer with being able to complete it.","The report connects night worship with understanding the Qur'an.","The text notes that daytime has long periods of work."],"related_hadiths":[{"id":"1131","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1137","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1145","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E175" s="4" t="n"/>
@@ -4506,7 +4510,7 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Year of Early Night Worship","description":"$book_name$ $hadith_number$ - $chapter_name$. See how Ibn Abbas describes the Companions' night prayer after the first verses of Surah Al-Muzzammil."},"heading":{"title":"Surah Al-Muzzammil Qiyam Hadith: The Companions' Night Prayer","description":"This hadith speaks about Surah Al-Muzzammil qiyam and the Companions' night prayer. Ibn Abbas says that when the opening verses of Surah Al-Muzzammil were revealed, the Companions would stand in prayer for a length similar to their standing in Ramadan. This continued until the last verses of the surah were revealed. The report also states that the period between the opening and the final verses was one year. For people searching tahajjud in Surah Muzammil or qiyam al layl hadith, this narration gives a direct account of how the first command affected the Companions' worship. It also keeps the timing clear: one year passed between those revealed sections."},"teachings":["The early verses of Al-Muzzammil led to long night prayer.","The Companions stood in prayer like their standing in Ramadan.","The final verses came after a period of one year.","The report links revelation with changes in worship practice."],"related_hadiths":[{"id":"1131","book_id":"1","label":"Sahih Bukhari"},{"id":"1137","book_id":"1","label":"Sahih Bukhari"},{"id":"1140","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Year of Early Night Worship","description":"$book_name$ $hadith_number$ - $chapter_name$. See how Ibn Abbas describes the Companions' night prayer after the first verses of Surah Al-Muzzammil."},"heading":{"title":"Surah Al-Muzzammil Qiyam Hadith: The Companions' Night Prayer","description":"This hadith speaks about Surah Al-Muzzammil qiyam and the Companions' night prayer. Ibn Abbas says that when the opening verses of Surah Al-Muzzammil were revealed, the Companions would stand in prayer for a length similar to their standing in Ramadan. This continued until the last verses of the surah were revealed. The report also states that the period between the opening and the final verses was one year. For people searching tahajjud in Surah Muzammil or qiyam al layl hadith, this narration gives a direct account of how the first command affected the Companions' worship. It also keeps the timing clear: one year passed between those revealed sections."},"teachings":["The early verses of Al-Muzzammil led to long night prayer.","The Companions stood in prayer like their standing in Ramadan.","The final verses came after a period of one year.","The report links revelation with changes in worship practice."],"related_hadiths":[{"id":"1131","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1137","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1140","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E176" s="4" t="n"/>
@@ -4529,7 +4533,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Knots and Waking for Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how remembering Allah, making wudu, and praying are described as undoing the devil's knots after sleep."},"heading":{"title":"Three Knots Hadith: Dhikr, Wudu, and Night Prayer After Sleep","description":"This famous three knots hadith is about waking from sleep with dhikr, wudu, and prayer. The Prophet صلى الله عليه وسلم said the devil ties three knots at the back of a sleeping person's neck and says that the night is long, so sleep. If the person wakes and mentions Allah, one knot is loosened. If he performs ablution, another is loosened. If he prays, the third is loosened. The result stated in the hadith is that he rises in the morning active and in good spirits. If not, he rises in bad spirits and sluggish. The text gives a simple order for a strong start: remember Allah, make ablution, then pray."},"teachings":["Mentioning Allah after waking is directly praised in this report.","Wudu is described as loosening another knot.","Prayer completes the sequence mentioned in the hadith.","The hadith links these acts with a better morning state."],"related_hadiths":[{"id":"1142","book_id":"1","label":"Sahih Bukhari"},{"id":"3269","book_id":"1","label":"Sahih Bukhari"},{"id":"1329","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Knots and Waking for Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how remembering Allah, making wudu, and praying are described as undoing the devil's knots after sleep."},"heading":{"title":"Three Knots Hadith: Dhikr, Wudu, and Night Prayer After Sleep","description":"This famous three knots hadith is about waking from sleep with dhikr, wudu, and prayer. The Prophet صلى الله عليه وسلم said the devil ties three knots at the back of a sleeping person's neck and says that the night is long, so sleep. If the person wakes and mentions Allah, one knot is loosened. If he performs ablution, another is loosened. If he prays, the third is loosened. The result stated in the hadith is that he rises in the morning active and in good spirits. If not, he rises in bad spirits and sluggish. The text gives a simple order for a strong start: remember Allah, make ablution, then pray."},"teachings":["Mentioning Allah after waking is directly praised in this report.","Wudu is described as loosening another knot.","Prayer completes the sequence mentioned in the hadith.","The hadith links these acts with a better morning state."],"related_hadiths":[{"id":"1142","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"3269","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1329","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E177" s="4" t="n"/>
@@ -4552,7 +4556,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Give Up Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Read Aisha's advice not to leave night prayer and how the Prophet صلى الله عليه وسلم prayed sitting when ill or tired."},"heading":{"title":"Do Not Give Up Night Prayer Hadith: Consistency With Ease","description":"This hadith is about not giving up night prayer, a key topic for searches like tahajjud consistency hadith and qiyam al layl when tired. Aisha says, 'Do not give up prayer at night,' because the Messenger of Allah صلى الله عليه وسلم would not leave it. She also explains the gentle side of this practice: when he was ill or lethargic, he offered it sitting. The hadith does not demand the same strength from everyone at all times. It shows that regular worship can continue in a form a person can manage. The core message is steady night prayer with mercy and ease when the body is weak."},"teachings":["Aisha advised not leaving night prayer.","The Prophet صلى الله عليه وسلم kept night prayer as a regular practice.","When ill or tired, he prayed sitting according to this report.","The text shows worship can be done with what one can bear."],"related_hadiths":[{"id":"1117","book_id":"1","label":"Sahih Bukhari"},{"id":"1150","book_id":"1","label":"Sahih Bukhari"},{"id":"1132","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Give Up Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Read Aisha's advice not to leave night prayer and how the Prophet صلى الله عليه وسلم prayed sitting when ill or tired."},"heading":{"title":"Do Not Give Up Night Prayer Hadith: Consistency With Ease","description":"This hadith is about not giving up night prayer, a key topic for searches like tahajjud consistency hadith and qiyam al layl when tired. Aisha says, 'Do not give up prayer at night,' because the Messenger of Allah صلى الله عليه وسلم would not leave it. She also explains the gentle side of this practice: when he was ill or lethargic, he offered it sitting. The hadith does not demand the same strength from everyone at all times. It shows that regular worship can continue in a form a person can manage. The core message is steady night prayer with mercy and ease when the body is weak."},"teachings":["Aisha advised not leaving night prayer.","The Prophet صلى الله عليه وسلم kept night prayer as a regular practice.","When ill or tired, he prayed sitting according to this report.","The text shows worship can be done with what one can bear."],"related_hadiths":[{"id":"1117","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1150","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1132","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E178" s="4" t="n"/>
@@ -4575,7 +4579,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Spouses Waking Each Other for Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Discover the mercy mentioned for a husband and wife who wake each other for night prayer."},"heading":{"title":"Hadith About Husband and Wife Waking for Tahajjud Prayer","description":"This hadith is about husband and wife waking for tahajjud prayer, also searched as family night prayer hadith and spouse qiyam al layl hadith. The Prophet صلى الله عليه وسلم prayed for Allah's mercy upon a man who gets up at night, prays, and wakes his wife. If she refuses, he sprinkles water on her face. He also prayed for Allah's mercy upon a woman who gets up at night, prays, and wakes her husband. If he refuses, she sprinkles water on his face. The text presents night worship as something a married couple can help each other with. It keeps both sides balanced: the husband helps the wife, and the wife helps the husband."},"teachings":["Night prayer can be encouraged within marriage.","The hadith mentions both husband and wife in a balanced way.","Waking a spouse for prayer is linked with seeking Allah's mercy.","The report shows gentle shared effort in worship."],"related_hadiths":[{"id":"1131","book_id":"1","label":"Sahih Bukhari"},{"id":"1145","book_id":"1","label":"Sahih Bukhari"},{"id":"1137","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Spouses Waking Each Other for Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Discover the mercy mentioned for a husband and wife who wake each other for night prayer."},"heading":{"title":"Hadith About Husband and Wife Waking for Tahajjud Prayer","description":"This hadith is about husband and wife waking for tahajjud prayer, also searched as family night prayer hadith and spouse qiyam al layl hadith. The Prophet صلى الله عليه وسلم prayed for Allah's mercy upon a man who gets up at night, prays, and wakes his wife. If she refuses, he sprinkles water on her face. He also prayed for Allah's mercy upon a woman who gets up at night, prays, and wakes her husband. If he refuses, she sprinkles water on his face. The text presents night worship as something a married couple can help each other with. It keeps both sides balanced: the husband helps the wife, and the wife helps the husband."},"teachings":["Night prayer can be encouraged within marriage.","The hadith mentions both husband and wife in a balanced way.","Waking a spouse for prayer is linked with seeking Allah's mercy.","The report shows gentle shared effort in worship."],"related_hadiths":[{"id":"1131","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1145","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1137","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E179" s="4" t="n"/>
@@ -4598,7 +4602,7 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Couples Remembering Allah at Night","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how a husband and wife praying two rak'ahs at night are recorded among those who remember Allah."},"heading":{"title":"Hadith About Couples Praying Two Rak'ahs at Night Together","description":"This hadith is about couples praying two rak'ahs at night and being counted among those who remember Allah. The Prophet صلى الله عليه وسلم said that if a man awakens his wife at night and both pray, or both offer two rak'ahs together, the man is recorded among the men who mention Allah and the woman among the women who mention Allah. The narration also includes Abu Dawud's note that one route was reported as a statement of Abu Sa'id rather than a direct prophetic statement. Staying close to the text, the main message is shared night prayer and shared remembrance. It makes the home a place where both spouses can take part in worship."},"teachings":["Two spouses may support each other in night prayer.","Two rak'ahs together are specifically mentioned in the report.","The hadith connects night prayer with being recorded among those who remember Allah.","Abu Dawud notes a difference in how one route was reported."],"related_hadiths":[{"id":"1137","book_id":"1","label":"Sahih Bukhari"},{"id":"1142","book_id":"1","label":"Sahih Bukhari"},{"id":"1145","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Couples Remembering Allah at Night","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how a husband and wife praying two rak'ahs at night are recorded among those who remember Allah."},"heading":{"title":"Hadith About Couples Praying Two Rak'ahs at Night Together","description":"This hadith is about couples praying two rak'ahs at night and being counted among those who remember Allah. The Prophet صلى الله عليه وسلم said that if a man awakens his wife at night and both pray, or both offer two rak'ahs together, the man is recorded among the men who mention Allah and the woman among the women who mention Allah. The narration also includes Abu Dawud's note that one route was reported as a statement of Abu Sa'id rather than a direct prophetic statement. Staying close to the text, the main message is shared night prayer and shared remembrance. It makes the home a place where both spouses can take part in worship."},"teachings":["Two spouses may support each other in night prayer.","Two rak'ahs together are specifically mentioned in the report.","The hadith connects night prayer with being recorded among those who remember Allah.","Abu Dawud notes a difference in how one route was reported."],"related_hadiths":[{"id":"1137","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1142","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1145","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E180" s="4" t="n"/>
@@ -4621,7 +4625,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray With Energy, Sit When Tired","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the balanced guidance to pray while strong and sit when tired instead of leaning on a rope."},"heading":{"title":"Hadith About Praying With Energy and Sitting When Tired","description":"This hadith is a clear teaching on moderation in voluntary prayer. The Prophet صلى الله عليه وسلم entered the mosque and saw a rope tied between two pillars. He asked about it, and the people explained that it was used by a woman praying there, so when she became tired she would lean or hold on to it. The Prophet صلى الله عليه وسلم told them to undo it. He said one should pray as much as one has strength, and when tired, sit down. The main search phrase is pray as much as you have strength hadith, with related terms like rope between pillars hadith and sitting when tired in prayer. The text teaches steady worship without forcing the body past its strength."},"teachings":["The Prophet صلى الله عليه وسلم told them to remove the rope used for support.","A person should pray while he has strength and energy.","When tired, sitting down is directly mentioned in the report.","The hadith warns against forcing worship in a way the body cannot handle."],"related_hadiths":[{"id":"1150","book_id":"1","label":"Sahih Bukhari"},{"id":"1643","book_id":"3","label":"Sunan an-Nasai"},{"id":"1117","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray With Energy, Sit When Tired","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the balanced guidance to pray while strong and sit when tired instead of leaning on a rope."},"heading":{"title":"Hadith About Praying With Energy and Sitting When Tired","description":"This hadith is a clear teaching on moderation in voluntary prayer. The Prophet صلى الله عليه وسلم entered the mosque and saw a rope tied between two pillars. He asked about it, and the people explained that it was used by a woman praying there, so when she became tired she would lean or hold on to it. The Prophet صلى الله عليه وسلم told them to undo it. He said one should pray as much as one has strength, and when tired, sit down. The main search phrase is pray as much as you have strength hadith, with related terms like rope between pillars hadith and sitting when tired in prayer. The text teaches steady worship without forcing the body past its strength."},"teachings":["The Prophet صلى الله عليه وسلم told them to remove the rope used for support.","A person should pray while he has strength and energy.","When tired, sitting down is directly mentioned in the report.","The hadith warns against forcing worship in a way the body cannot handle."],"related_hadiths":[{"id":"1150","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1643","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"1117","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E181" s="4" t="n"/>
@@ -4644,7 +4648,7 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Finishing the Night Portion Before Dawn","description":"$book_name$ $hadith_number$ - $chapter_name$. See Aisha's report that Allah would awaken the Prophet صلى الله عليه وسلم at night and he finished his portion before dawn."},"heading":{"title":"Hadith About the Prophet Finishing His Night Recitation Before Dawn","description":"This hadith is about the Prophet's night portion of recitation. Aisha says that Allah, the Exalted, would awaken the Messenger of Allah صلى الله عليه وسلم at night, and when dawn came, he would have finished his daily portion. The main search phrase is Prophet finished his night recitation before dawn, with related terms like hizb at night hadith, tahajjud recitation hadith, and Prophet waking at night. The report does not give the exact size of the portion, nor does it mention a fixed time for every night. It simply shows that the Prophet صلى الله عليه وسلم had a night portion and completed it before the arrival of dawn."},"teachings":["Aisha reports that Allah would awaken the Prophet صلى الله عليه وسلم at night.","The Prophet صلى الله عليه وسلم had a daily portion mentioned in this report.","He finished that portion before dawn came.","The hadith shows regularity in night recitation."],"related_hadiths":[{"id":"1132","book_id":"1","label":"Sahih Bukhari"},{"id":"1133","book_id":"1","label":"Sahih Bukhari"},{"id":"1140","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Finishing the Night Portion Before Dawn","description":"$book_name$ $hadith_number$ - $chapter_name$. See Aisha's report that Allah would awaken the Prophet صلى الله عليه وسلم at night and he finished his portion before dawn."},"heading":{"title":"Hadith About the Prophet Finishing His Night Recitation Before Dawn","description":"This hadith is about the Prophet's night portion of recitation. Aisha says that Allah, the Exalted, would awaken the Messenger of Allah صلى الله عليه وسلم at night, and when dawn came, he would have finished his daily portion. The main search phrase is Prophet finished his night recitation before dawn, with related terms like hizb at night hadith, tahajjud recitation hadith, and Prophet waking at night. The report does not give the exact size of the portion, nor does it mention a fixed time for every night. It simply shows that the Prophet صلى الله عليه وسلم had a night portion and completed it before the arrival of dawn."},"teachings":["Aisha reports that Allah would awaken the Prophet صلى الله عليه وسلم at night.","The Prophet صلى الله عليه وسلم had a daily portion mentioned in this report.","He finished that portion before dawn came.","The hadith shows regularity in night recitation."],"related_hadiths":[{"id":"1132","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1133","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1140","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E182" s="4" t="n"/>
@@ -4667,7 +4671,7 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sleeping at Dawn","description":"$book_name$ $hadith_number$ - $chapter_name$. Read Aisha's brief report that the Prophet صلى الله عليه وسلم would be sleeping with her at dawn."},"heading":{"title":"Hadith About the Prophet Sleeping at Dawn in Aisha's Home","description":"This brief hadith is about the Prophet sleeping at dawn, based on Aisha's report. She said that when he was with her, dawn did not find him except sleeping. The translation explains that she was referring to the Prophet صلى الله عليه وسلم. The main search phrase is Prophet sleeping at dawn hadith, with related terms like Aisha dawn hadith and sleeping after night prayer. The narration is short, so the explanation should stay short in meaning too. It does not describe a ruling for every person, and it does not list the prayers he performed before that moment. It simply records what Aisha observed in her home at the time of dawn."},"teachings":["Aisha describes what she observed in her own home.","The report says he would be sleeping at dawn when with her.","The text is brief and should not be stretched beyond its wording.","It gives one detail from the Prophet's private home life."],"related_hadiths":[{"id":"1133","book_id":"1","label":"Sahih Bukhari"},{"id":"1131","book_id":"1","label":"Sahih Bukhari"},{"id":"1132","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sleeping at Dawn","description":"$book_name$ $hadith_number$ - $chapter_name$. Read Aisha's brief report that the Prophet صلى الله عليه وسلم would be sleeping with her at dawn."},"heading":{"title":"Hadith About the Prophet Sleeping at Dawn in Aisha's Home","description":"This brief hadith is about the Prophet sleeping at dawn, based on Aisha's report. She said that when he was with her, dawn did not find him except sleeping. The translation explains that she was referring to the Prophet صلى الله عليه وسلم. The main search phrase is Prophet sleeping at dawn hadith, with related terms like Aisha dawn hadith and sleeping after night prayer. The narration is short, so the explanation should stay short in meaning too. It does not describe a ruling for every person, and it does not list the prayers he performed before that moment. It simply records what Aisha observed in her home at the time of dawn."},"teachings":["Aisha describes what she observed in her own home.","The report says he would be sleeping at dawn when with her.","The text is brief and should not be stretched beyond its wording.","It gives one detail from the Prophet's private home life."],"related_hadiths":[{"id":"1133","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1131","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1132","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E183" s="4" t="n"/>
@@ -4690,7 +4694,7 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Head Once","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports wiping the head once up to the nape, with notes about the chain and wording."},"heading":{"title":"Wiping Head Once in Wudu: A Narration with Chain Notes","description":"This Hadith is about wiping head once in wudu. Talhah ibn Musarrif narrated from his father, from his grandfather, that he saw the Messenger of Allah صلى الله عليه وسلم wiping his head once up to his nape. Musaddad’s wording says he wiped his head from front to back until his hands came out from beneath the ears. The narration also includes a note from Abu Dawud that Ahmad mentioned Ibn ‘Uyainah considered this chain rejected and questioned the chain: Talhah from his father from his grandfather. So the content has two parts: the described action of wiping the head, and the narrator’s note about how the report was viewed. A careful reader should keep both parts in mind and not ignore the chain note included in the text."},"teachings":["The action described is wiping the head once up to the nape.","Another wording mentions wiping from front to back beneath the ears.","The text includes a cautionary note about the chain, which should not be overlooked."],"related_hadiths":[{"id":"160","book_id":"1","label":"Sahih Bukhari"},{"id":"226a","book_id":"2","label":"Sahih Muslim"},{"id":"442","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Head Once","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports wiping the head once up to the nape, with notes about the chain and wording."},"heading":{"title":"Wiping Head Once in Wudu: A Narration with Chain Notes","description":"This Hadith is about wiping head once in wudu. Talhah ibn Musarrif narrated from his father, from his grandfather, that he saw the Messenger of Allah صلى الله عليه وسلم wiping his head once up to his nape. Musaddad’s wording says he wiped his head from front to back until his hands came out from beneath the ears. The narration also includes a note from Abu Dawud that Ahmad mentioned Ibn ‘Uyainah considered this chain rejected and questioned the chain: Talhah from his father from his grandfather. So the content has two parts: the described action of wiping the head, and the narrator’s note about how the report was viewed. A careful reader should keep both parts in mind and not ignore the chain note included in the text."},"teachings":["The action described is wiping the head once up to the nape.","Another wording mentions wiping from front to back beneath the ears.","The text includes a cautionary note about the chain, which should not be overlooked."],"related_hadiths":[{"id":"160","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"226a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"442","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E184" s="4" t="n"/>
@@ -4713,7 +4717,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abundant Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. See the Prophet's advice to Rabi'ah: help me for yourself by making prostrations abundantly."},"heading":{"title":"Abundant Prostration Hadith: Help Yourself With Many Sujood","description":"This hadith is about abundant prostration, often searched as help me by making many prostrations hadith or Rabi'ah ibn Ka'b hadith. Rabi'ah used to stay with the Messenger of Allah صلى الله عليه وسلم at night and bring water for his ablution and needs. The Prophet صلى الله عليه وسلم told him to ask. Rabi'ah asked for the Prophet's company in Paradise. When asked if he wanted anything else, he said that was all. The Prophet صلى الله عليه وسلم replied: help me for yourself by making prostrations abundantly. The report connects a high request with personal effort in prayer. It does not give a fixed number of prostrations; it points to much sujood as the advised path in this text."},"teachings":["Rabi'ah served the Prophet صلى الله عليه وسلم at night by bringing water.","He asked for the Prophet's company in Paradise.","The Prophet صلى الله عليه وسلم directed him to abundant prostration.","The hadith links a great request with personal effort in prayer."],"related_hadiths":[{"id":"489","book_id":"2","label":"Sahih Muslim"},{"id":"488","book_id":"2","label":"Sahih Muslim"},{"id":"1424","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abundant Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. See the Prophet's advice to Rabi'ah: help me for yourself by making prostrations abundantly."},"heading":{"title":"Abundant Prostration Hadith: Help Yourself With Many Sujood","description":"This hadith is about abundant prostration, often searched as help me by making many prostrations hadith or Rabi'ah ibn Ka'b hadith. Rabi'ah used to stay with the Messenger of Allah صلى الله عليه وسلم at night and bring water for his ablution and needs. The Prophet صلى الله عليه وسلم told him to ask. Rabi'ah asked for the Prophet's company in Paradise. When asked if he wanted anything else, he said that was all. The Prophet صلى الله عليه وسلم replied: help me for yourself by making prostrations abundantly. The report connects a high request with personal effort in prayer. It does not give a fixed number of prostrations; it points to much sujood as the advised path in this text."},"teachings":["Rabi'ah served the Prophet صلى الله عليه وسلم at night by bringing water.","He asked for the Prophet's company in Paradise.","The Prophet صلى الله عليه وسلم directed him to abundant prostration.","The hadith links a great request with personal effort in prayer."],"related_hadiths":[{"id":"489","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"488","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1424","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E185" s="4" t="n"/>
@@ -4736,7 +4740,7 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Prayer in Ramadan and Eleven Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet's Ramadan night prayer as eleven beautiful, long rak'ahs ending with witr."},"heading":{"title":"Witr Prayer in Ramadan: The Prophet's Eleven Rak'ahs","description":"This Hadith answers a common search question: how many rak'ahs did the Prophet pray in Ramadan at night? Aishah said that the Messenger of Allah did not pray more than eleven rak'ahs in Ramadan or outside Ramadan. The focus is not only the number. She also points to the beauty and length of the prayer. He prayed four, then four, then three rak'ahs of witr. When she asked whether he slept before witr, he replied that his eyes slept but his heart did not sleep. So this Hadith about witr prayer and Ramadan night prayer shows a calm, steady pattern of worship, with careful attention to long, beautiful prayer."},"teachings":["The Prophet's night prayer in this report was eleven rak'ahs in Ramadan and outside Ramadan.","Aishah highlighted the beauty and length of the prayer, not only the number.","Witr came at the end of this described night prayer.","The Prophet's sleep was described in a special way: his eyes slept while his heart did not."],"related_hadiths":[{"id":"1147","book_id":"1","label":"Sahih Bukhari"},{"id":"2013","book_id":"1","label":"Sahih Bukhari"},{"id":"738a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Prayer in Ramadan and Eleven Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet's Ramadan night prayer as eleven beautiful, long rak'ahs ending with witr."},"heading":{"title":"Witr Prayer in Ramadan: The Prophet's Eleven Rak'ahs","description":"This Hadith answers a common search question: how many rak'ahs did the Prophet pray in Ramadan at night? Aishah said that the Messenger of Allah did not pray more than eleven rak'ahs in Ramadan or outside Ramadan. The focus is not only the number. She also points to the beauty and length of the prayer. He prayed four, then four, then three rak'ahs of witr. When she asked whether he slept before witr, he replied that his eyes slept but his heart did not sleep. So this Hadith about witr prayer and Ramadan night prayer shows a calm, steady pattern of worship, with careful attention to long, beautiful prayer."},"teachings":["The Prophet's night prayer in this report was eleven rak'ahs in Ramadan and outside Ramadan.","Aishah highlighted the beauty and length of the prayer, not only the number.","Witr came at the end of this described night prayer.","The Prophet's sleep was described in a special way: his eyes slept while his heart did not."],"related_hadiths":[{"id":"1147","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2013","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"738a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E186" s="4" t="n"/>
@@ -4759,7 +4763,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Night Prayer and Prophetic Balance","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah explains the Prophet's character, night prayer, witr, steady worship, and balanced practice."},"heading":{"title":"Night Prayer Hadith: Witr, Quranic Character, and Steady Worship","description":"This long Hadith brings together several key points about the night prayer of Prophet Muhammad. Sa'd asked Aishah about the Prophet's character, and she answered that his character was the Qur'an. She then explained the night prayer and witr prayer. In the report, the early night prayer linked to Surah al-Muzzammil later became voluntary after being obligatory. Aishah also described the Prophet's witr with detailed rak'ah patterns, and she said he did not pray through the whole night, recite the whole Qur'an in one night, or fast a complete month except Ramadan. The simple lesson is clear: his worship was deep, regular, and balanced."},"teachings":["The Prophet's character is described in this report as the Qur'an.","Night prayer became voluntary after the earlier obligation mentioned in the report.","The Prophet's witr was described with clear rak'ah patterns, including nine and seven.","He kept worship regular without turning every act into an all-night or all-month practice."],"related_hadiths":[{"id":"746a","book_id":"2","label":"Sahih Muslim"},{"id":"990","book_id":"1","label":"Sahih Bukhari"},{"id":"751a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Night Prayer and Prophetic Balance","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah explains the Prophet's character, night prayer, witr, steady worship, and balanced practice."},"heading":{"title":"Night Prayer Hadith: Witr, Quranic Character, and Steady Worship","description":"This long Hadith brings together several key points about the night prayer of Prophet Muhammad. Sa'd asked Aishah about the Prophet's character, and she answered that his character was the Qur'an. She then explained the night prayer and witr prayer. In the report, the early night prayer linked to Surah al-Muzzammil later became voluntary after being obligatory. Aishah also described the Prophet's witr with detailed rak'ah patterns, and she said he did not pray through the whole night, recite the whole Qur'an in one night, or fast a complete month except Ramadan. The simple lesson is clear: his worship was deep, regular, and balanced."},"teachings":["The Prophet's character is described in this report as the Qur'an.","Night prayer became voluntary after the earlier obligation mentioned in the report.","The Prophet's witr was described with clear rak'ah patterns, including nine and seven.","He kept worship regular without turning every act into an all-night or all-month practice."],"related_hadiths":[{"id":"746a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"751a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E187" s="4" t="n"/>
@@ -4782,7 +4786,7 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Prayer with Dhikr and Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds how the Prophet sat, remembered Allah, made dua, and ended witr audibly."},"heading":{"title":"Witr Prayer Hadith: Sitting, Dhikr, Dua, and Audible Salam","description":"This Hadith is another chain for the earlier report, but it adds important wording about the Prophet's witr prayer. It says he prayed eight rak'ahs without sitting except in the eighth. He then sat, remembered Allah, made dua, and gave salam in a voice that those present could hear. After that, he prayed two rak'ahs sitting, then one rak'ah, making eleven rak'ahs. The report also says that when he grew older and became heavier, he offered seven rak'ahs of witr and then prayed two rak'ahs sitting after salam. This Hadith about tahajjud and witr shows careful prayer, remembrance, supplication, and a clear ending with salam."},"teachings":["The Prophet sat in the eighth rak'ah in this version and remembered Allah.","Dua is mentioned clearly before the audible salam.","The report gives an eleven-rak'ah pattern, then a later seven-rak'ah witr pattern.","The two rak'ahs sitting after salam are part of this described night prayer practice."],"related_hadiths":[{"id":"746a","book_id":"2","label":"Sahih Muslim"},{"id":"738b","book_id":"2","label":"Sahih Muslim"},{"id":"990","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Prayer with Dhikr and Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds how the Prophet sat, remembered Allah, made dua, and ended witr audibly."},"heading":{"title":"Witr Prayer Hadith: Sitting, Dhikr, Dua, and Audible Salam","description":"This Hadith is another chain for the earlier report, but it adds important wording about the Prophet's witr prayer. It says he prayed eight rak'ahs without sitting except in the eighth. He then sat, remembered Allah, made dua, and gave salam in a voice that those present could hear. After that, he prayed two rak'ahs sitting, then one rak'ah, making eleven rak'ahs. The report also says that when he grew older and became heavier, he offered seven rak'ahs of witr and then prayed two rak'ahs sitting after salam. This Hadith about tahajjud and witr shows careful prayer, remembrance, supplication, and a clear ending with salam."},"teachings":["The Prophet sat in the eighth rak'ah in this version and remembered Allah.","Dua is mentioned clearly before the audible salam.","The report gives an eleven-rak'ah pattern, then a later seven-rak'ah witr pattern.","The two rak'ahs sitting after salam are part of this described night prayer practice."],"related_hadiths":[{"id":"746a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"738b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E188" s="4" t="n"/>
@@ -4805,7 +4809,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Audible Salam in Witr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration confirms the same report and highlights the Prophet's salam being heard clearly."},"heading":{"title":"Audible Salam in Witr Prayer: A Short Hadith Note","description":"This Hadith is brief, but it has a clear focus for anyone searching for a hadith about audible salam in witr prayer. It states that the same report was transmitted by Yahya b. Sa'id and adds that the Prophet uttered the salam loudly enough that those present could hear it. The narration does not introduce a new rak'ah count or a new event. Its value is in confirming a wording detail within the wider night prayer report. So the main point is simple: in this version of the Prophet's witr prayer, the closing salam was not hidden or silent; it was heard by those near him."},"teachings":["This report confirms the same general night prayer narration.","The added wording focuses on the salam being heard.","It does not add a different rak'ah count in the provided text.","The Hadith shows how small wording details are preserved in narration."],"related_hadiths":[{"id":"746a","book_id":"2","label":"Sahih Muslim"},{"id":"738b","book_id":"2","label":"Sahih Muslim"},{"id":"990","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Audible Salam in Witr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration confirms the same report and highlights the Prophet's salam being heard clearly."},"heading":{"title":"Audible Salam in Witr Prayer: A Short Hadith Note","description":"This Hadith is brief, but it has a clear focus for anyone searching for a hadith about audible salam in witr prayer. It states that the same report was transmitted by Yahya b. Sa'id and adds that the Prophet uttered the salam loudly enough that those present could hear it. The narration does not introduce a new rak'ah count or a new event. Its value is in confirming a wording detail within the wider night prayer report. So the main point is simple: in this version of the Prophet's witr prayer, the closing salam was not hidden or silent; it was heard by those near him."},"teachings":["This report confirms the same general night prayer narration.","The added wording focuses on the salam being heard.","It does not add a different rak'ah count in the provided text.","The Hadith shows how small wording details are preserved in narration."],"related_hadiths":[{"id":"746a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"738b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E189" s="4" t="n"/>
@@ -4828,7 +4832,7 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Salam Heard Clearly","description":"$book_name$ $hadith_number$ - $chapter_name$. Another chain preserves the wording that the Prophet's salam in witr could be heard."},"heading":{"title":"Witr Prayer Salam: The Prophet's Closing Was Heard","description":"This Hadith is another transmission of the same night prayer report. Its special wording says that the Prophet uttered the salam in a way that those present could hear it. Like the previous report, this Hadith does not give a new story or a separate ruling. It protects a detail in the wording of the witr prayer narration. For readers searching for witr prayer hadith, taslim in prayer, or audible salam, the key point is that the narration mentions a clear, heard salam at the end. It also shows how the hadith transmitters kept track of small differences between similar reports."},"teachings":["The narration preserves a wording detail about the Prophet's salam.","The salam is described as audible to those present.","This version stays tied to the same wider night prayer report.","The text shows careful reporting through a different chain of narrators."],"related_hadiths":[{"id":"746a","book_id":"2","label":"Sahih Muslim"},{"id":"738b","book_id":"2","label":"Sahih Muslim"},{"id":"990","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Salam Heard Clearly","description":"$book_name$ $hadith_number$ - $chapter_name$. Another chain preserves the wording that the Prophet's salam in witr could be heard."},"heading":{"title":"Witr Prayer Salam: The Prophet's Closing Was Heard","description":"This Hadith is another transmission of the same night prayer report. Its special wording says that the Prophet uttered the salam in a way that those present could hear it. Like the previous report, this Hadith does not give a new story or a separate ruling. It protects a detail in the wording of the witr prayer narration. For readers searching for witr prayer hadith, taslim in prayer, or audible salam, the key point is that the narration mentions a clear, heard salam at the end. It also shows how the hadith transmitters kept track of small differences between similar reports."},"teachings":["The narration preserves a wording detail about the Prophet's salam.","The salam is described as audible to those present.","This version stays tied to the same wider night prayer report.","The text shows careful reporting through a different chain of narrators."],"related_hadiths":[{"id":"746a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"738b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E190" s="4" t="n"/>
@@ -4851,7 +4855,7 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Midnight Prayer and Witr Routine","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet's midnight prayer, siwak, ablution, recitation, dua, and witr."},"heading":{"title":"Midnight Prayer Hadith: Siwak, Wudu, Recitation, and Witr","description":"This Hadith gives a detailed picture of the Prophet's midnight prayer. Aishah said he prayed Isha in congregation, returned home, prayed four rak'ahs, then slept with water for ablution covered near his head and his tooth-stick ready. When Allah awakened him, he used the tooth-stick, performed ablution well, and prayed eight rak'ahs. He recited al-Fatihah and another part of the Qur'an as Allah willed. He sat after the eighth, continued with the ninth, made dua, asked Allah, and turned to Him. He then gave one strong salam, followed by two rak'ahs while sitting. This is a rich hadith about tahajjud prayer preparation and witr."},"teachings":["The Prophet prepared for night prayer with water and a tooth-stick nearby.","He used the tooth-stick and performed ablution carefully after waking.","The report describes recitation, dua, and turning to Allah during the prayer.","His later age and body change are mentioned with a shorter standing pattern."],"related_hadiths":[{"id":"746a","book_id":"2","label":"Sahih Muslim"},{"id":"1164","book_id":"1","label":"Sahih Bukhari"},{"id":"749g","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Midnight Prayer and Witr Routine","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet's midnight prayer, siwak, ablution, recitation, dua, and witr."},"heading":{"title":"Midnight Prayer Hadith: Siwak, Wudu, Recitation, and Witr","description":"This Hadith gives a detailed picture of the Prophet's midnight prayer. Aishah said he prayed Isha in congregation, returned home, prayed four rak'ahs, then slept with water for ablution covered near his head and his tooth-stick ready. When Allah awakened him, he used the tooth-stick, performed ablution well, and prayed eight rak'ahs. He recited al-Fatihah and another part of the Qur'an as Allah willed. He sat after the eighth, continued with the ninth, made dua, asked Allah, and turned to Him. He then gave one strong salam, followed by two rak'ahs while sitting. This is a rich hadith about tahajjud prayer preparation and witr."},"teachings":["The Prophet prepared for night prayer with water and a tooth-stick nearby.","He used the tooth-stick and performed ablution carefully after waking.","The report describes recitation, dua, and turning to Allah during the prayer.","His later age and body change are mentioned with a shorter standing pattern."],"related_hadiths":[{"id":"746a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1164","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"749g","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E191" s="4" t="n"/>
@@ -4874,7 +4878,7 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Balanced Night Prayer and Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. This version describes equal recitation, bowing, prostration, one-rak'ah witr, and loud salam."},"heading":{"title":"Balanced Night Prayer: Equal Recitation, Ruku, Sujud, and Witr","description":"This version of the Hadith adds a clear detail about the Prophet's night prayer. It says he prayed eight rak'ahs, making the recitation, bowing, and prostration equal in them. He did not sit during them except in the eighth. Then he stood without giving salam, prayed one rak'ah as witr, and gave salam with a raised voice. The text also says this version does not mention the four rak'ahs before sleep. So the explanation should stay with what this report says: the prayer was measured, balanced, and ended with witr and a clear salam. It is a useful hadith for searching tahajjud prayer method."},"teachings":["The recitation, bowing, and prostration are described as equal in this version.","The Prophet sat only after the eighth rak'ah before standing for witr.","Witr was observed with one rak'ah after the eight.","The raised voice in salam is mentioned in this narration."],"related_hadiths":[{"id":"746a","book_id":"2","label":"Sahih Muslim"},{"id":"749g","book_id":"2","label":"Sahih Muslim"},{"id":"990","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Balanced Night Prayer and Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. This version describes equal recitation, bowing, prostration, one-rak'ah witr, and loud salam."},"heading":{"title":"Balanced Night Prayer: Equal Recitation, Ruku, Sujud, and Witr","description":"This version of the Hadith adds a clear detail about the Prophet's night prayer. It says he prayed eight rak'ahs, making the recitation, bowing, and prostration equal in them. He did not sit during them except in the eighth. Then he stood without giving salam, prayed one rak'ah as witr, and gave salam with a raised voice. The text also says this version does not mention the four rak'ahs before sleep. So the explanation should stay with what this report says: the prayer was measured, balanced, and ended with witr and a clear salam. It is a useful hadith for searching tahajjud prayer method."},"teachings":["The recitation, bowing, and prostration are described as equal in this version.","The Prophet sat only after the eighth rak'ah before standing for witr.","Witr was observed with one rak'ah after the eight.","The raised voice in salam is mentioned in this narration."],"related_hadiths":[{"id":"746a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"749g","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E192" s="4" t="n"/>
@@ -4897,7 +4901,7 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hadith Transmission Note","description":"$book_name$ $hadith_number$ - $chapter_name$. This report notes a different chain from Aishah and compares Hammad b. Salamah's version with others."},"heading":{"title":"Hadith Transmission Note: Aishah's Night Prayer Report","description":"This Hadith is not a full new description of the Prophet's night prayer. It is a transmission note. It says that the same tradition was also transmitted from Aishah through another chain of narrators. Then it adds that the tradition narrated by Hammad b. Salamah is not equal to the tradition narrated by others. For readers searching for hadith narration chain, Aishah night prayer hadith, or Hammad b. Salamah narration, the point is about how this report reached the collectors and how its wording is compared. The safest explanation is to stay with the text: it records a related chain and marks a difference from the fuller reports."},"teachings":["This text is mainly about transmission, not a new prayer method.","It links the report back to Aishah through a different chain.","The narration of Hammad b. Salamah is said not to be equal to the others.","The Hadith shows that differences between reports were noted carefully."],"related_hadiths":[{"id":"746a","book_id":"2","label":"Sahih Muslim"},{"id":"738b","book_id":"2","label":"Sahih Muslim"},{"id":"1123","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hadith Transmission Note","description":"$book_name$ $hadith_number$ - $chapter_name$. This report notes a different chain from Aishah and compares Hammad b. Salamah's version with others."},"heading":{"title":"Hadith Transmission Note: Aishah's Night Prayer Report","description":"This Hadith is not a full new description of the Prophet's night prayer. It is a transmission note. It says that the same tradition was also transmitted from Aishah through another chain of narrators. Then it adds that the tradition narrated by Hammad b. Salamah is not equal to the tradition narrated by others. For readers searching for hadith narration chain, Aishah night prayer hadith, or Hammad b. Salamah narration, the point is about how this report reached the collectors and how its wording is compared. The safest explanation is to stay with the text: it records a related chain and marks a difference from the fuller reports."},"teachings":["This text is mainly about transmission, not a new prayer method.","It links the report back to Aishah through a different chain.","The narration of Hammad b. Salamah is said not to be equal to the others.","The Hadith shows that differences between reports were noted carefully."],"related_hadiths":[{"id":"746a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"738b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1123","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E193" s="4" t="n"/>
@@ -4920,7 +4924,7 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Thirteen Rak'ahs and Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports thirteen night rak'ahs, witr, two sitting rak'ahs, and the two rak'ahs before Fajr."},"heading":{"title":"Thirteen Rak'ahs Hadith: Night Prayer, Witr, and Fajr Sunnah","description":"This Hadith gives a shorter report from Aishah about the Prophet's night prayer. She said the Messenger of Allah used to pray thirteen rak'ahs during the night. The report says he observed witr with nine, or as she stated, and that he prayed two rak'ahs while sitting. It also mentions the two rak'ahs of the dawn prayer between the adhan and iqamah. For people searching for thirteen rak'ahs night prayer hadith or witr prayer hadith Aishah, the text gives a clear count and connects it with the early morning prayer time. It should be read as this specific narration's description, without forcing it to cancel other narrated patterns."},"teachings":["Aishah reports thirteen rak'ahs during the night in this narration.","The report mentions witr and two rak'ahs while sitting.","The two rak'ahs of dawn prayer are placed between adhan and iqamah.","The wording includes uncertainty in the phrase or as she said, so it should be handled carefully."],"related_hadiths":[{"id":"1164","book_id":"1","label":"Sahih Bukhari"},{"id":"1138","book_id":"1","label":"Sahih Bukhari"},{"id":"738a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Thirteen Rak'ahs and Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports thirteen night rak'ahs, witr, two sitting rak'ahs, and the two rak'ahs before Fajr."},"heading":{"title":"Thirteen Rak'ahs Hadith: Night Prayer, Witr, and Fajr Sunnah","description":"This Hadith gives a shorter report from Aishah about the Prophet's night prayer. She said the Messenger of Allah used to pray thirteen rak'ahs during the night. The report says he observed witr with nine, or as she stated, and that he prayed two rak'ahs while sitting. It also mentions the two rak'ahs of the dawn prayer between the adhan and iqamah. For people searching for thirteen rak'ahs night prayer hadith or witr prayer hadith Aishah, the text gives a clear count and connects it with the early morning prayer time. It should be read as this specific narration's description, without forcing it to cancel other narrated patterns."},"teachings":["Aishah reports thirteen rak'ahs during the night in this narration.","The report mentions witr and two rak'ahs while sitting.","The two rak'ahs of dawn prayer are placed between adhan and iqamah.","The wording includes uncertainty in the phrase or as she said, so it should be handled carefully."],"related_hadiths":[{"id":"1164","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1138","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"738a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E194" s="4" t="n"/>
@@ -4943,7 +4947,7 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Nine and Seven Rak'ah Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet's witr as nine, then seven, with two sitting rak'ahs afterward."},"heading":{"title":"Witr Prayer Hadith: Nine Rak'ahs, Seven Rak'ahs, and Two Sitting","description":"This Hadith focuses on the witr prayer of the Prophet. Aishah said he used to observe witr with nine rak'ahs, then later with seven rak'ahs. She also described two rak'ahs after witr while sitting. In those two, he recited the Qur'an while sitting, and when he wanted to bow, he stood up, bowed, and then prostrated. The report also includes a note from Abu Dawud about related transmissions by Khalid b. Abd Allah al-Wasiti and a question from Alqamah b. Waqqas about how those two rak'ahs were prayed. For searches like nine rak'ah witr hadith and two rak'ahs after witr, this is a direct narration."},"teachings":["The Prophet's witr is described as nine rak'ahs, then seven rak'ahs.","Two rak'ahs sitting after witr are mentioned in this report.","He recited while sitting, then stood when he wished to bow.","The narration includes a transmission note about similar reports."],"related_hadiths":[{"id":"746a","book_id":"2","label":"Sahih Muslim"},{"id":"990","book_id":"1","label":"Sahih Bukhari"},{"id":"751a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Nine and Seven Rak'ah Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet's witr as nine, then seven, with two sitting rak'ahs afterward."},"heading":{"title":"Witr Prayer Hadith: Nine Rak'ahs, Seven Rak'ahs, and Two Sitting","description":"This Hadith focuses on the witr prayer of the Prophet. Aishah said he used to observe witr with nine rak'ahs, then later with seven rak'ahs. She also described two rak'ahs after witr while sitting. In those two, he recited the Qur'an while sitting, and when he wanted to bow, he stood up, bowed, and then prostrated. The report also includes a note from Abu Dawud about related transmissions by Khalid b. Abd Allah al-Wasiti and a question from Alqamah b. Waqqas about how those two rak'ahs were prayed. For searches like nine rak'ah witr hadith and two rak'ahs after witr, this is a direct narration."},"teachings":["The Prophet's witr is described as nine rak'ahs, then seven rak'ahs.","Two rak'ahs sitting after witr are mentioned in this report.","He recited while sitting, then stood when he wished to bow.","The narration includes a transmission note about similar reports."],"related_hadiths":[{"id":"746a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"751a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E195" s="4" t="n"/>
@@ -4966,7 +4970,7 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet's Night Prayer Routine","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes Isha, sleep, midnight wudu, eight rak'ahs, one-rak'ah witr, and two sitting rak'ahs."},"heading":{"title":"Prophet's Night Prayer Routine: Eight Rak'ahs, Witr, and Rest","description":"This Hadith gives another clear account of the Prophet's night prayer routine. Aishah said he led the people in the night prayer, went to bed, and slept. Around midnight he got up, attended to his need, performed ablution, entered the mosque, and prayed eight rak'ahs. The narrator says it seemed that recitation, bowing, and prostration were equal. He then observed witr with one rak'ah, prayed two rak'ahs sitting, and lay down. Sometimes Bilal came to call him for prayer, and the narrator noticed a light doze or was unsure about it. This Hadith is useful for searches about tahajjud prayer method and witr after eight rak'ahs."},"teachings":["The report describes sleep before the later night prayer.","The Prophet performed ablution before entering the mosque for prayer.","He prayed eight rak'ahs, then one rak'ah of witr, then two sitting rak'ahs.","The narration mentions Bilal coming to call him for prayer."],"related_hadiths":[{"id":"117","book_id":"1","label":"Sahih Bukhari"},{"id":"138","book_id":"1","label":"Sahih Bukhari"},{"id":"746a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet's Night Prayer Routine","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes Isha, sleep, midnight wudu, eight rak'ahs, one-rak'ah witr, and two sitting rak'ahs."},"heading":{"title":"Prophet's Night Prayer Routine: Eight Rak'ahs, Witr, and Rest","description":"This Hadith gives another clear account of the Prophet's night prayer routine. Aishah said he led the people in the night prayer, went to bed, and slept. Around midnight he got up, attended to his need, performed ablution, entered the mosque, and prayed eight rak'ahs. The narrator says it seemed that recitation, bowing, and prostration were equal. He then observed witr with one rak'ah, prayed two rak'ahs sitting, and lay down. Sometimes Bilal came to call him for prayer, and the narrator noticed a light doze or was unsure about it. This Hadith is useful for searches about tahajjud prayer method and witr after eight rak'ahs."},"teachings":["The report describes sleep before the later night prayer.","The Prophet performed ablution before entering the mosque for prayer.","He prayed eight rak'ahs, then one rak'ah of witr, then two sitting rak'ahs.","The narration mentions Bilal coming to call him for prayer."],"related_hadiths":[{"id":"117","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"138","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"746a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E196" s="4" t="n"/>
@@ -4989,7 +4993,7 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Light in Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports siwak, wudu, reciting Aal Imran verses, long prayer, witr, and the dua for light."},"heading":{"title":"Dua for Light Hadith: Ibn Abbas on the Prophet's Night Prayer","description":"This Hadith is well known for the dua for light, but the report also describes the Prophet's night prayer. Ibn Abbas slept near the Prophet and saw him wake up, use the tooth-stick, perform ablution, and recite verses from Aal Imran beginning with the creation of the heavens and earth. He then prayed two rak'ahs with long standing, bowing, and prostration, slept again, and repeated this until six rak'ahs were completed. He used the tooth-stick, made ablution, and recited those verses each time. He then observed witr and later went out for prayer. The report ends with the supplication asking Allah for light in the heart, tongue, hearing, sight, and all directions."},"teachings":["The Prophet used the tooth-stick and performed ablution after waking.","He recited verses from Aal Imran before standing for prayer.","The prayer included long standing, bowing, and prostration.","The supplication asks Allah for light in the heart, senses, and around the person."],"related_hadiths":[{"id":"763a","book_id":"2","label":"Sahih Muslim"},{"id":"1138","book_id":"1","label":"Sahih Bukhari"},{"id":"117","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Light in Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports siwak, wudu, reciting Aal Imran verses, long prayer, witr, and the dua for light."},"heading":{"title":"Dua for Light Hadith: Ibn Abbas on the Prophet's Night Prayer","description":"This Hadith is well known for the dua for light, but the report also describes the Prophet's night prayer. Ibn Abbas slept near the Prophet and saw him wake up, use the tooth-stick, perform ablution, and recite verses from Aal Imran beginning with the creation of the heavens and earth. He then prayed two rak'ahs with long standing, bowing, and prostration, slept again, and repeated this until six rak'ahs were completed. He used the tooth-stick, made ablution, and recited those verses each time. He then observed witr and later went out for prayer. The report ends with the supplication asking Allah for light in the heart, tongue, hearing, sight, and all directions."},"teachings":["The Prophet used the tooth-stick and performed ablution after waking.","He recited verses from Aal Imran before standing for prayer.","The prayer included long standing, bowing, and prostration.","The supplication asks Allah for light in the heart, senses, and around the person."],"related_hadiths":[{"id":"763a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1138","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"117","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E197" s="4" t="n"/>
@@ -5012,7 +5016,7 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abundant Light Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. This version preserves the wording asking Allah to give abundant light and notes related chains."},"heading":{"title":"Abundant Light Dua: A Hadith Transmission Note","description":"This Hadith is a short version connected to the previous report about the Prophet's night prayer and the dua for light. It says that Husain transmitted the tradition through another chain in a similar way. The wording highlighted here is, and give me abundant light. Abu Dawud also notes that Abu Khalid al-Dalani, Habib, Salamah b. Kuhail, Abu Rishdin, and Ibn Abbas transmitted it in a similar manner. For readers searching for dua for light hadith or abundant light dua, this narration mainly preserves a phrase and points to how the report was transmitted. It should not be treated as a separate full story from the longer account."},"teachings":["The highlighted wording asks Allah for abundant light.","This text connects to the longer Ibn Abbas night prayer report.","Several names in the chain are mentioned to show related transmission paths.","The report focuses on wording preservation rather than a new prayer count."],"related_hadiths":[{"id":"763a","book_id":"2","label":"Sahih Muslim"},{"id":"1138","book_id":"1","label":"Sahih Bukhari"},{"id":"117","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abundant Light Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. This version preserves the wording asking Allah to give abundant light and notes related chains."},"heading":{"title":"Abundant Light Dua: A Hadith Transmission Note","description":"This Hadith is a short version connected to the previous report about the Prophet's night prayer and the dua for light. It says that Husain transmitted the tradition through another chain in a similar way. The wording highlighted here is, and give me abundant light. Abu Dawud also notes that Abu Khalid al-Dalani, Habib, Salamah b. Kuhail, Abu Rishdin, and Ibn Abbas transmitted it in a similar manner. For readers searching for dua for light hadith or abundant light dua, this narration mainly preserves a phrase and points to how the report was transmitted. It should not be treated as a separate full story from the longer account."},"teachings":["The highlighted wording asks Allah for abundant light.","This text connects to the longer Ibn Abbas night prayer report.","Several names in the chain are mentioned to show related transmission paths.","The report focuses on wording preservation rather than a new prayer count."],"related_hadiths":[{"id":"763a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1138","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"117","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E198" s="4" t="n"/>
@@ -5035,7 +5039,7 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Watching the Prophet's Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Fadl b. Abbas observes the Prophet's wudu, siwak, Aal Imran recitation, ten rak'ahs, witr, and Fajr."},"heading":{"title":"Night Prayer Hadith: Fadl ibn Abbas Observes Wudu, Siwak, and Witr","description":"This Hadith records Fadl b. Abbas spending a night with the Prophet to see how he prayed. The Prophet got up, performed ablution, and prayed two rak'ahs. His standing, bowing, and prostration are described as equal in length. He then slept, woke again, performed ablution, used the tooth-stick, and recited five verses from Surah Aal Imran about the creation of the heavens and earth and the change of night and day. He continued this pattern until he prayed ten rak'ahs, then prayed one rak'ah as witr. When the caller finished the adhan, he prayed two light rak'ahs and remained sitting until the dawn prayer."},"teachings":["Fadl b. Abbas watched the Prophet's night prayer to learn how he prayed.","The report mentions ablution, siwak, and recitation from Aal Imran.","The standing, bowing, and prostration are described as equal in the two rak'ahs.","The Prophet prayed ten rak'ahs, then one witr, then two light rak'ahs before dawn prayer."],"related_hadiths":[{"id":"763a","book_id":"2","label":"Sahih Muslim"},{"id":"1138","book_id":"1","label":"Sahih Bukhari"},{"id":"990","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Watching the Prophet's Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Fadl b. Abbas observes the Prophet's wudu, siwak, Aal Imran recitation, ten rak'ahs, witr, and Fajr."},"heading":{"title":"Night Prayer Hadith: Fadl ibn Abbas Observes Wudu, Siwak, and Witr","description":"This Hadith records Fadl b. Abbas spending a night with the Prophet to see how he prayed. The Prophet got up, performed ablution, and prayed two rak'ahs. His standing, bowing, and prostration are described as equal in length. He then slept, woke again, performed ablution, used the tooth-stick, and recited five verses from Surah Aal Imran about the creation of the heavens and earth and the change of night and day. He continued this pattern until he prayed ten rak'ahs, then prayed one rak'ah as witr. When the caller finished the adhan, he prayed two light rak'ahs and remained sitting until the dawn prayer."},"teachings":["Fadl b. Abbas watched the Prophet's night prayer to learn how he prayed.","The report mentions ablution, siwak, and recitation from Aal Imran.","The standing, bowing, and prostration are described as equal in the two rak'ahs.","The Prophet prayed ten rak'ahs, then one witr, then two light rak'ahs before dawn prayer."],"related_hadiths":[{"id":"763a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1138","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E199" s="4" t="n"/>
@@ -5058,7 +5062,7 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Five or Seven Rak'ah Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet prayed five or seven rak'ahs for witr and saluted only at the end."},"heading":{"title":"Five or Seven Rak'ah Witr: Ibn Abbas at Maimunah's House","description":"This Hadith is a short report from Ibn Abbas while he stayed with his maternal aunt Maimunah. The Messenger of Allah came after evening and asked whether the boy had prayed. When they answered yes, he lay down until part of the night had passed as Allah willed. Then he got up, performed ablution, and prayed seven or five rak'ahs, observing witr with them. The important wording is that he gave salam only at the last of them. For search terms like five rak'ah witr hadith, seven rak'ah witr hadith, and Ibn Abbas Maimunah night prayer, this report gives a direct description of a connected witr pattern."},"teachings":["The Prophet asked whether Ibn Abbas had prayed.","He rested before rising later in the night.","The report mentions seven or five rak'ahs for witr.","The salam is described as coming only at the end of those rak'ahs."],"related_hadiths":[{"id":"990","book_id":"1","label":"Sahih Bukhari"},{"id":"993","book_id":"1","label":"Sahih Bukhari"},{"id":"749g","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Five or Seven Rak'ah Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet prayed five or seven rak'ahs for witr and saluted only at the end."},"heading":{"title":"Five or Seven Rak'ah Witr: Ibn Abbas at Maimunah's House","description":"This Hadith is a short report from Ibn Abbas while he stayed with his maternal aunt Maimunah. The Messenger of Allah came after evening and asked whether the boy had prayed. When they answered yes, he lay down until part of the night had passed as Allah willed. Then he got up, performed ablution, and prayed seven or five rak'ahs, observing witr with them. The important wording is that he gave salam only at the last of them. For search terms like five rak'ah witr hadith, seven rak'ah witr hadith, and Ibn Abbas Maimunah night prayer, this report gives a direct description of a connected witr pattern."},"teachings":["The Prophet asked whether Ibn Abbas had prayed.","He rested before rising later in the night.","The report mentions seven or five rak'ahs for witr.","The salam is described as coming only at the end of those rak'ahs."],"related_hadiths":[{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"993","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"749g","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E200" s="4" t="n"/>
@@ -5081,7 +5085,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing on the Right in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports night prayer at Maimunah's house and being moved from the left to the right side."},"heading":{"title":"Standing on the Right in Prayer: Ibn Abbas and the Prophet's Night Prayer","description":"This Hadith gives a memorable moment from Ibn Abbas at the house of his aunt Maimunah. The Prophet prayed Isha, came home, prayed four rak'ahs, and slept. Then he stood to pray, and Ibn Abbas stood on his left side. The Prophet moved him around and made him stand on his right side. After that, the Prophet prayed five rak'ahs, slept until Ibn Abbas heard his snoring, then got up and prayed two rak'ahs. He then went out and offered the dawn prayer. For people searching for standing on the right in prayer hadith, this report connects that lesson with the Prophet's night prayer routine."},"teachings":["Ibn Abbas joined the Prophet's prayer and first stood on the left.","The Prophet moved him to the right side.","The report describes prayer, sleep, more prayer, and then the dawn prayer.","The Hadith shows a practical correction made during prayer."],"related_hadiths":[{"id":"117","book_id":"1","label":"Sahih Bukhari"},{"id":"138","book_id":"1","label":"Sahih Bukhari"},{"id":"1138","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing on the Right in Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports night prayer at Maimunah's house and being moved from the left to the right side."},"heading":{"title":"Standing on the Right in Prayer: Ibn Abbas and the Prophet's Night Prayer","description":"This Hadith gives a memorable moment from Ibn Abbas at the house of his aunt Maimunah. The Prophet prayed Isha, came home, prayed four rak'ahs, and slept. Then he stood to pray, and Ibn Abbas stood on his left side. The Prophet moved him around and made him stand on his right side. After that, the Prophet prayed five rak'ahs, slept until Ibn Abbas heard his snoring, then got up and prayed two rak'ahs. He then went out and offered the dawn prayer. For people searching for standing on the right in prayer hadith, this report connects that lesson with the Prophet's night prayer routine."},"teachings":["Ibn Abbas joined the Prophet's prayer and first stood on the left.","The Prophet moved him to the right side.","The report describes prayer, sleep, more prayer, and then the dawn prayer.","The Hadith shows a practical correction made during prayer."],"related_hadiths":[{"id":"117","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"138","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1138","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E201" s="4" t="n"/>
@@ -5104,7 +5108,7 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eight Rak'ahs and Five Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports eight rak'ahs in pairs, then five rak'ahs of witr without sitting between them."},"heading":{"title":"Eight Rak'ahs in Pairs and Five Witr: A Night Prayer Hadith","description":"This Hadith is a concise report from Ibn Abbas through Sa'id b. Jubair. It says that the Prophet got up and prayed two rak'ahs at a time until he completed eight rak'ahs. Then he observed witr with five rak'ahs and did not sit between them. The text is short, so the explanation should stay short and clear as well. For people searching for eight rak'ahs tahajjud hadith or five rak'ah witr without sitting, this narration gives the main pattern: pairs of two before witr, then five connected rak'ahs for witr. It is one of the reports showing the Prophet's night prayer described in a specific form."},"teachings":["The Prophet prayed eight rak'ahs in pairs in this report.","The witr is described as five rak'ahs.","He did not sit between the five witr rak'ahs.","The narration gives a specific night prayer pattern from Ibn Abbas."],"related_hadiths":[{"id":"990","book_id":"1","label":"Sahih Bukhari"},{"id":"993","book_id":"1","label":"Sahih Bukhari"},{"id":"749c","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eight Rak'ahs and Five Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports eight rak'ahs in pairs, then five rak'ahs of witr without sitting between them."},"heading":{"title":"Eight Rak'ahs in Pairs and Five Witr: A Night Prayer Hadith","description":"This Hadith is a concise report from Ibn Abbas through Sa'id b. Jubair. It says that the Prophet got up and prayed two rak'ahs at a time until he completed eight rak'ahs. Then he observed witr with five rak'ahs and did not sit between them. The text is short, so the explanation should stay short and clear as well. For people searching for eight rak'ahs tahajjud hadith or five rak'ah witr without sitting, this narration gives the main pattern: pairs of two before witr, then five connected rak'ahs for witr. It is one of the reports showing the Prophet's night prayer described in a specific form."},"teachings":["The Prophet prayed eight rak'ahs in pairs in this report.","The witr is described as five rak'ahs.","He did not sit between the five witr rak'ahs.","The narration gives a specific night prayer pattern from Ibn Abbas."],"related_hadiths":[{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"993","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"749c","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E202" s="4" t="n"/>
@@ -5127,7 +5131,7 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Thirteen Rak'ahs and Five Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports thirteen rak'ahs including Fajr Sunnah, with six in pairs and five witr together."},"heading":{"title":"Thirteen Rak'ahs Hadith: Six in Pairs and Five Witr","description":"This Hadith from Aishah describes the Prophet's prayer as thirteen rak'ahs, including the two rak'ahs before the dawn prayer. In the report, he prayed six rak'ahs two by two, then observed witr with five rak'ahs. It also says he did not sit between the five except in the last of them. This is a useful text for searches like thirteen rak'ahs night prayer, five rak'ah witr hadith, and Aishah witr prayer narration. The wording should be kept as it is: the thirteen count here includes the two before Fajr, and the witr pattern in this report is five with sitting only at the end."},"teachings":["The thirteen rak'ahs in this report include the two before the dawn prayer.","The Prophet prayed six rak'ahs in pairs.","Witr is described as five rak'ahs.","He sat only in the last of the five witr rak'ahs."],"related_hadiths":[{"id":"1164","book_id":"1","label":"Sahih Bukhari"},{"id":"1138","book_id":"1","label":"Sahih Bukhari"},{"id":"738a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Thirteen Rak'ahs and Five Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports thirteen rak'ahs including Fajr Sunnah, with six in pairs and five witr together."},"heading":{"title":"Thirteen Rak'ahs Hadith: Six in Pairs and Five Witr","description":"This Hadith from Aishah describes the Prophet's prayer as thirteen rak'ahs, including the two rak'ahs before the dawn prayer. In the report, he prayed six rak'ahs two by two, then observed witr with five rak'ahs. It also says he did not sit between the five except in the last of them. This is a useful text for searches like thirteen rak'ahs night prayer, five rak'ah witr hadith, and Aishah witr prayer narration. The wording should be kept as it is: the thirteen count here includes the two before Fajr, and the witr pattern in this report is five with sitting only at the end."},"teachings":["The thirteen rak'ahs in this report include the two before the dawn prayer.","The Prophet prayed six rak'ahs in pairs.","Witr is described as five rak'ahs.","He sat only in the last of the five witr rak'ahs."],"related_hadiths":[{"id":"1164","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1138","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"738a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E203" s="4" t="n"/>
@@ -5150,7 +5154,7 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Thirteen Night Rak'ahs Including Fajr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah states that the Prophet prayed thirteen rak'ahs at night including the two rak'ahs of Fajr."},"heading":{"title":"Thirteen Night Rak'ahs Including Fajr: Aishah's Report","description":"This Hadith is a very brief report from Aishah. She states that the Prophet used to pray thirteen rak'ahs during the night, including the two rak'ahs of the dawn prayer. The text does not give the full order, length, sitting positions, or detailed witr form. It only gives the total as reported here and explains that the two rak'ahs of Fajr are counted in that number. For users searching for thirteen rak'ahs night prayer hadith, Aishah hadith about tahajjud, or Fajr sunnah included in night prayer count, the safest reading is simple: this narration gives a count and includes the two rak'ahs of dawn prayer within it."},"teachings":["Aishah reports thirteen rak'ahs during the night.","The two rak'ahs of Fajr are included in the count.","The report is brief and does not describe every step of the prayer.","The Hadith should be read as this narration's count, alongside other reports with more detail."],"related_hadiths":[{"id":"1164","book_id":"1","label":"Sahih Bukhari"},{"id":"1138","book_id":"1","label":"Sahih Bukhari"},{"id":"738a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Thirteen Night Rak'ahs Including Fajr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah states that the Prophet prayed thirteen rak'ahs at night including the two rak'ahs of Fajr."},"heading":{"title":"Thirteen Night Rak'ahs Including Fajr: Aishah's Report","description":"This Hadith is a very brief report from Aishah. She states that the Prophet used to pray thirteen rak'ahs during the night, including the two rak'ahs of the dawn prayer. The text does not give the full order, length, sitting positions, or detailed witr form. It only gives the total as reported here and explains that the two rak'ahs of Fajr are counted in that number. For users searching for thirteen rak'ahs night prayer hadith, Aishah hadith about tahajjud, or Fajr sunnah included in night prayer count, the safest reading is simple: this narration gives a count and includes the two rak'ahs of dawn prayer within it."},"teachings":["Aishah reports thirteen rak'ahs during the night.","The two rak'ahs of Fajr are included in the count.","The report is brief and does not describe every step of the prayer.","The Hadith should be read as this narration's count, alongside other reports with more detail."],"related_hadiths":[{"id":"1164","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1138","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"738a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E204" s="4" t="n"/>
@@ -5173,7 +5177,7 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Night Prayer and Two Steady Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet's night prayer, eight rak'ahs, and two rak'ahs he did not leave before dawn."},"heading":{"title":"Hadith About Night Prayer and the Two Rak'ahs Before Fajr","description":"This hadith about night prayer shows a clear pattern from the practice of the Messenger of Allah (صلى الله عليه وسلم). Aishah reports that after the night prayer, he prayed eight rak'ahs standing, then prayed two rak'ahs between the two adhans, meaning between the adhan for Fajr and the iqamah. The main lesson is steady worship. The text says he never left those two rak'ahs. Another narrator adds that in his version, these two rak'ahs were prayed sitting. So the focus is not on making extra claims, but on what is stated: the Prophet (صلى الله عليه وسلم) kept a regular night prayer routine and gave special care to the two rak'ahs before dawn. For anyone searching for the sunnah before Fajr, this hadith highlights consistency, prayer at night, and the habit of not leaving a known act of worship."},"teachings":["The Prophet (صلى الله عليه وسلم) had a regular practice of praying at night.","The two rak'ahs before the dawn prayer were something he did not leave.","The narration records both standing night prayer and a version mentioning two rak'ahs sitting.","A steady act of worship can hold a clear place in a believer's daily routine."],"related_hadiths":[{"id":"1362","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1363","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1367","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Night Prayer and Two Steady Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet's night prayer, eight rak'ahs, and two rak'ahs he did not leave before dawn."},"heading":{"title":"Hadith About Night Prayer and the Two Rak'ahs Before Fajr","description":"This hadith about night prayer shows a clear pattern from the practice of the Messenger of Allah (صلى الله عليه وسلم). Aishah reports that after the night prayer, he prayed eight rak'ahs standing, then prayed two rak'ahs between the two adhans, meaning between the adhan for Fajr and the iqamah. The main lesson is steady worship. The text says he never left those two rak'ahs. Another narrator adds that in his version, these two rak'ahs were prayed sitting. So the focus is not on making extra claims, but on what is stated: the Prophet (صلى الله عليه وسلم) kept a regular night prayer routine and gave special care to the two rak'ahs before dawn. For anyone searching for the sunnah before Fajr, this hadith highlights consistency, prayer at night, and the habit of not leaving a known act of worship."},"teachings":["The Prophet (صلى الله عليه وسلم) had a regular practice of praying at night.","The two rak'ahs before the dawn prayer were something he did not leave.","The narration records both standing night prayer and a version mentioning two rak'ahs sitting.","A steady act of worship can hold a clear place in a believer's daily routine."],"related_hadiths":[{"id":"1362","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1363","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1367","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E205" s="4" t="n"/>
@@ -5196,7 +5200,7 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | How the Prophet Prayed Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah explains the Prophet's witr prayer, its rak'ah counts, and that he did not abandon this night worship."},"heading":{"title":"Witr Prayer Hadith: How Many Rak'ahs Did the Prophet Pray?","description":"This witr prayer hadith answers a direct question: how many rak'ahs would the Messenger of Allah (صلى الله عليه وسلم) pray for witr? Aishah gives several counts: four and three, six and three, eight and three, and ten and three. She also says he did not pray less than seven or more than thirteen. The report then mentions a version that adds he would not observe witr with two rak'ahs before dawn, and when asked what he used for witr, Aishah said he would never leave it. The key point is that witr had a firm place in his night prayer. The hadith also shows that the reported rak'ah counts varied within the practice mentioned here. For readers searching how many rak'ahs in witr, this narration gives a focused answer from Aishah's report without adding extra details outside the text."},"teachings":["Witr was a regular part of the Prophet's night prayer.","The narration mentions different rak'ah patterns for witr.","Aishah states that he did not leave witr.","Questions about worship can be answered by carefully reporting the Prophet's practice."],"related_hadiths":[{"id":"1361","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1363","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1366","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | How the Prophet Prayed Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah explains the Prophet's witr prayer, its rak'ah counts, and that he did not abandon this night worship."},"heading":{"title":"Witr Prayer Hadith: How Many Rak'ahs Did the Prophet Pray?","description":"This witr prayer hadith answers a direct question: how many rak'ahs would the Messenger of Allah (صلى الله عليه وسلم) pray for witr? Aishah gives several counts: four and three, six and three, eight and three, and ten and three. She also says he did not pray less than seven or more than thirteen. The report then mentions a version that adds he would not observe witr with two rak'ahs before dawn, and when asked what he used for witr, Aishah said he would never leave it. The key point is that witr had a firm place in his night prayer. The hadith also shows that the reported rak'ah counts varied within the practice mentioned here. For readers searching how many rak'ahs in witr, this narration gives a focused answer from Aishah's report without adding extra details outside the text."},"teachings":["Witr was a regular part of the Prophet's night prayer.","The narration mentions different rak'ah patterns for witr.","Aishah states that he did not leave witr.","Questions about worship can be answered by carefully reporting the Prophet's practice."],"related_hadiths":[{"id":"1361","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1363","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1366","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E206" s="4" t="n"/>
@@ -5219,7 +5223,7 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Abbas Witnesses the Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet's night prayer, ablution, light rak'ahs, witr, rest, and dawn prayer."},"heading":{"title":"Hadith About the Prophet's Night Prayer Observed by Ibn Abbas","description":"This hadith about the Prophet's night prayer gives a close report from Ibn Abbas through the client of Ibn Abbas. He spent the night while the Prophet (صلى الله عليه وسلم) was with Maimunah. After sleeping for part of the night, the Prophet got up, performed ablution, and Ibn Abbas did the same. Ibn Abbas first stood on the left, and the Prophet moved him to the right. The Prophet then touched his head and ear, as the report says, as if awakening him. He prayed two light rak'ahs with Surah al-Fatihah in each, then continued until he prayed eleven rak'ahs with witr. After sleeping again, Bilal came to call him, and he prayed two rak'ahs before leading the people. This narration is useful for searches about tahajjud prayer, witr, and the Prophet's night routine because it gives a step-by-step report from the text itself."},"teachings":["The Prophet (صلى الله عليه وسلم) began his night prayer after waking and performing ablution.","Ibn Abbas was gently moved from the left side to the right side during prayer.","The report mentions two light rak'ahs before the longer night prayer and witr.","The Prophet prayed two rak'ahs after Bilal called him, then led the people."],"related_hadiths":[{"id":"1367","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1365","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1363","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Abbas Witnesses the Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet's night prayer, ablution, light rak'ahs, witr, rest, and dawn prayer."},"heading":{"title":"Hadith About the Prophet's Night Prayer Observed by Ibn Abbas","description":"This hadith about the Prophet's night prayer gives a close report from Ibn Abbas through the client of Ibn Abbas. He spent the night while the Prophet (صلى الله عليه وسلم) was with Maimunah. After sleeping for part of the night, the Prophet got up, performed ablution, and Ibn Abbas did the same. Ibn Abbas first stood on the left, and the Prophet moved him to the right. The Prophet then touched his head and ear, as the report says, as if awakening him. He prayed two light rak'ahs with Surah al-Fatihah in each, then continued until he prayed eleven rak'ahs with witr. After sleeping again, Bilal came to call him, and he prayed two rak'ahs before leading the people. This narration is useful for searches about tahajjud prayer, witr, and the Prophet's night routine because it gives a step-by-step report from the text itself."},"teachings":["The Prophet (صلى الله عليه وسلم) began his night prayer after waking and performing ablution.","Ibn Abbas was gently moved from the left side to the right side during prayer.","The report mentions two light rak'ahs before the longer night prayer and witr.","The Prophet prayed two rak'ahs after Bilal called him, then led the people."],"related_hadiths":[{"id":"1367","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1365","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1363","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E207" s="4" t="n"/>
@@ -5242,7 +5246,7 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Thirteen Rak'ahs at Night","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas describes the Prophet's night prayer as thirteen rak'ahs, including the two rak'ahs of dawn."},"heading":{"title":"Tahajjud Hadith: The Prophet Prayed Thirteen Rak'ahs at Night","description":"This tahajjud hadith is another report from Abdullah ibn Abbas about spending the night with his maternal aunt Maymunah. He says the Prophet (صلى الله عليه وسلم) got up to pray at night and prayed thirteen rak'ahs, including the two rak'ahs of the dawn prayer. Ibn Abbas also gives an estimate of the standing in each rak'ah, saying it was about the time one could recite Surah al-Muzzammil. The narration is short, but it gives two clear points: the number of rak'ahs mentioned in this report and the length of standing as estimated by Ibn Abbas. For people searching for hadith about tahajjud rak'ahs, Prophet night prayer, or thirteen rak'ahs at night, this hadith gives a direct witness report. It does not add extra rulings; it simply records what Ibn Abbas observed."},"teachings":["Ibn Abbas reports the Prophet's night prayer from what he personally observed.","The narration mentions thirteen rak'ahs, including two rak'ahs of dawn prayer.","The standing in prayer was long enough to be compared with reciting Surah al-Muzzammil.","Careful observation helps preserve details of worship."],"related_hadiths":[{"id":"1364","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1367","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1366","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Thirteen Rak'ahs at Night","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas describes the Prophet's night prayer as thirteen rak'ahs, including the two rak'ahs of dawn."},"heading":{"title":"Tahajjud Hadith: The Prophet Prayed Thirteen Rak'ahs at Night","description":"This tahajjud hadith is another report from Abdullah ibn Abbas about spending the night with his maternal aunt Maymunah. He says the Prophet (صلى الله عليه وسلم) got up to pray at night and prayed thirteen rak'ahs, including the two rak'ahs of the dawn prayer. Ibn Abbas also gives an estimate of the standing in each rak'ah, saying it was about the time one could recite Surah al-Muzzammil. The narration is short, but it gives two clear points: the number of rak'ahs mentioned in this report and the length of standing as estimated by Ibn Abbas. For people searching for hadith about tahajjud rak'ahs, Prophet night prayer, or thirteen rak'ahs at night, this hadith gives a direct witness report. It does not add extra rulings; it simply records what Ibn Abbas observed."},"teachings":["Ibn Abbas reports the Prophet's night prayer from what he personally observed.","The narration mentions thirteen rak'ahs, including two rak'ahs of dawn prayer.","The standing in prayer was long enough to be compared with reciting Surah al-Muzzammil.","Careful observation helps preserve details of worship."],"related_hadiths":[{"id":"1364","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1367","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1366","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E208" s="4" t="n"/>
@@ -5265,7 +5269,7 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Long and Gradual Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Khalid al-Juhani observes the Prophet's night prayer beginning light, then long, then shorter by stages."},"heading":{"title":"Hadith About the Prophet's Long Night Prayer in Thirteen Rak'ahs","description":"This hadith about night prayer comes from Khalid al-Juhani, who wanted to watch the prayer of the Messenger of Allah (صلى الله عليه وسلم) at night. He slept near the threshold of the Prophet's door or tent and observed the prayer. The Prophet began with two light rak'ahs. Then he prayed two very long rak'ahs. After that, he prayed pairs of two rak'ahs that became shorter than the pair before them. Finally, he observed witr. The report says the total was thirteen rak'ahs. The main idea is the structure of the night prayer as seen by the narrator: a light opening, long standing, then shorter pairs, ending with witr. For searches like Prophet night prayer thirteen rak'ahs, tahajjud hadith, and witr at the end of night prayer, this narration gives a clear and vivid description from the text."},"teachings":["The Prophet (صلى الله عليه وسلم) began this night prayer with two light rak'ahs.","The report describes a long prayer followed by shorter pairs of rak'ahs.","Witr came at the end of the prayer in this narration.","The total number reported here is thirteen rak'ahs."],"related_hadiths":[{"id":"1365","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1363","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1367","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Long and Gradual Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Khalid al-Juhani observes the Prophet's night prayer beginning light, then long, then shorter by stages."},"heading":{"title":"Hadith About the Prophet's Long Night Prayer in Thirteen Rak'ahs","description":"This hadith about night prayer comes from Khalid al-Juhani, who wanted to watch the prayer of the Messenger of Allah (صلى الله عليه وسلم) at night. He slept near the threshold of the Prophet's door or tent and observed the prayer. The Prophet began with two light rak'ahs. Then he prayed two very long rak'ahs. After that, he prayed pairs of two rak'ahs that became shorter than the pair before them. Finally, he observed witr. The report says the total was thirteen rak'ahs. The main idea is the structure of the night prayer as seen by the narrator: a light opening, long standing, then shorter pairs, ending with witr. For searches like Prophet night prayer thirteen rak'ahs, tahajjud hadith, and witr at the end of night prayer, this narration gives a clear and vivid description from the text."},"teachings":["The Prophet (صلى الله عليه وسلم) began this night prayer with two light rak'ahs.","The report describes a long prayer followed by shorter pairs of rak'ahs.","Witr came at the end of the prayer in this narration.","The total number reported here is thirteen rak'ahs."],"related_hadiths":[{"id":"1365","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1363","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1367","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E209" s="4" t="n"/>
@@ -5288,7 +5292,7 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Waking for Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet waking, reciting from Al Imran, making ablution, praying, and ending with witr."},"heading":{"title":"Hadith About Waking for Night Prayer and Ending with Witr","description":"This hadith about night prayer gives a detailed report from Abdullah ibn Abbas during a night he spent with Maimunah, the wife of the Prophet (صلى الله عليه وسلم). The Prophet slept, then woke around the middle of the night, rubbed sleep from his face, and recited ten verses from the end of Surah Al Imran. He then made a careful ablution from a hanging water bag and stood to pray. Ibn Abbas copied what he did and stood beside him. The Prophet placed his right hand on Ibn Abbas's head and took him by the ear. He prayed pairs of two rak'ahs, then observed witr, then lay down until the mu'adhdhin came. After that he prayed two light rak'ahs and went out for the dawn prayer. This report is useful for learning the Prophet's night prayer routine from the wording itself."},"teachings":["The Prophet (صلى الله عليه وسلم) woke for night prayer around the middle of the night in this report.","He recited ten verses from the end of Surah Al Imran before prayer.","He performed ablution well before standing to pray.","His night prayer ended with witr, followed later by two light rak'ahs before dawn prayer."],"related_hadiths":[{"id":"1364","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1365","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1366","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Waking for Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet waking, reciting from Al Imran, making ablution, praying, and ending with witr."},"heading":{"title":"Hadith About Waking for Night Prayer and Ending with Witr","description":"This hadith about night prayer gives a detailed report from Abdullah ibn Abbas during a night he spent with Maimunah, the wife of the Prophet (صلى الله عليه وسلم). The Prophet slept, then woke around the middle of the night, rubbed sleep from his face, and recited ten verses from the end of Surah Al Imran. He then made a careful ablution from a hanging water bag and stood to pray. Ibn Abbas copied what he did and stood beside him. The Prophet placed his right hand on Ibn Abbas's head and took him by the ear. He prayed pairs of two rak'ahs, then observed witr, then lay down until the mu'adhdhin came. After that he prayed two light rak'ahs and went out for the dawn prayer. This report is useful for learning the Prophet's night prayer routine from the wording itself."},"teachings":["The Prophet (صلى الله عليه وسلم) woke for night prayer around the middle of the night in this report.","He recited ten verses from the end of Surah Al Imran before prayer.","He performed ablution well before standing to pray.","His night prayer ended with witr, followed later by two light rak'ahs before dawn prayer."],"related_hadiths":[{"id":"1364","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1365","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1366","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E210" s="4" t="n"/>
@@ -5311,7 +5315,7 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Balance in Worship and Rights","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet reminds Uthman that worship must sit with the rights of family, guests, and one's own self."},"heading":{"title":"Hadith About Balance in Worship and Giving Each Right Its Due","description":"This hadith about balance in worship records the Prophet's advice to Uthman ibn Maz'un. The Prophet (صلى الله عليه وسلم) asked him whether he disliked his practice. Uthman replied that he did not, and that he sought the Prophet's practice. The Prophet then explained his way: he sleeps and prays, fasts and sometimes leaves fasting, and marries women. He then told Uthman to fear Allah and reminded him that his wife had a right over him, his guest had a right over him, and his own self had a right over him. The final advice is clear: fast and sometimes leave fasting, pray and sleep. The hadith speaks directly to balanced worship, family rights, guest rights, and self-care. It does not reject worship; it places worship in a steady and human pattern."},"teachings":["The Prophet's practice included worship, rest, fasting, and sometimes not fasting.","A wife, a guest, and one's own self each have rights.","Religious effort should not ignore the responsibilities named in the hadith.","The Prophet guided Uthman toward prayer with sleep and fasting with breaks."],"related_hadiths":[{"id":"1368","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1370","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Balance in Worship and Rights","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet reminds Uthman that worship must sit with the rights of family, guests, and one's own self."},"heading":{"title":"Hadith About Balance in Worship and Giving Each Right Its Due","description":"This hadith about balance in worship records the Prophet's advice to Uthman ibn Maz'un. The Prophet (صلى الله عليه وسلم) asked him whether he disliked his practice. Uthman replied that he did not, and that he sought the Prophet's practice. The Prophet then explained his way: he sleeps and prays, fasts and sometimes leaves fasting, and marries women. He then told Uthman to fear Allah and reminded him that his wife had a right over him, his guest had a right over him, and his own self had a right over him. The final advice is clear: fast and sometimes leave fasting, pray and sleep. The hadith speaks directly to balanced worship, family rights, guest rights, and self-care. It does not reject worship; it places worship in a steady and human pattern."},"teachings":["The Prophet's practice included worship, rest, fasting, and sometimes not fasting.","A wife, a guest, and one's own self each have rights.","Religious effort should not ignore the responsibilities named in the hadith.","The Prophet guided Uthman toward prayer with sleep and fasting with breaks."],"related_hadiths":[{"id":"1368","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1370","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E211" s="4" t="n"/>
@@ -5334,7 +5338,7 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Regular Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah says the Prophet's actions were regular, not limited to special days, and his strength was unique."},"heading":{"title":"Hadith About Regular Worship and the Prophet's Steady Actions","description":"This hadith about regular worship answers a question put to Aishah. She was asked whether the Messenger of Allah (صلى الله عليه وسلم) used to single out certain actions for particular days. Her answer was no. She said all his actions were regular. She then asked who among the people could have the same strength as the Messenger of Allah (صلى الله عليه وسلم). The meaning from the text is clear: his worship was steady, but people should also recognize that his strength was not like theirs. This hadith connects closely with the idea of consistent good deeds and worship one can maintain. It does not push a person to copy beyond ability. It shows the Prophet's practice as steady and continuous, while also pointing to his special strength in worship."},"teachings":["Aishah describes the Prophet's actions as regular and steady.","The report does not present his worship as limited to selected special days.","Aishah reminds people that the Prophet's strength was greater than theirs.","The hadith supports steady worship while recognizing human limits."],"related_hadiths":[{"id":"1368","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1369","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Regular Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah says the Prophet's actions were regular, not limited to special days, and his strength was unique."},"heading":{"title":"Hadith About Regular Worship and the Prophet's Steady Actions","description":"This hadith about regular worship answers a question put to Aishah. She was asked whether the Messenger of Allah (صلى الله عليه وسلم) used to single out certain actions for particular days. Her answer was no. She said all his actions were regular. She then asked who among the people could have the same strength as the Messenger of Allah (صلى الله عليه وسلم). The meaning from the text is clear: his worship was steady, but people should also recognize that his strength was not like theirs. This hadith connects closely with the idea of consistent good deeds and worship one can maintain. It does not push a person to copy beyond ability. It shows the Prophet's practice as steady and continuous, while also pointing to his special strength in worship."},"teachings":["Aishah describes the Prophet's actions as regular and steady.","The report does not present his worship as limited to selected special days.","Aishah reminds people that the Prophet's strength was greater than theirs.","The hadith supports steady worship while recognizing human limits."],"related_hadiths":[{"id":"1368","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1369","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E212" s="4" t="n"/>
@@ -5357,7 +5361,7 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu Once","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم performed ablution by washing each limb once only."},"heading":{"title":"Wudu Once: Ibn Abbas Reports Washing Each Limb One Time","description":"This Hadith focuses on wudu once. Ibn Abbas asked, “May I not tell you how the Messenger of Allah صلى الله عليه وسلم performed ablution?” He then performed ablution washing each limb once only. The narration is short, but it answers a common search question: can wudu be described with one wash for each limb in Hadith? Based on this text, Ibn Abbas showed a form of ablution where each limb was washed one time. The report does not give a long list of steps in the translation provided, and it does not discuss other counts. So the explanation should stay close to the wording. Its main lesson is that Ibn Abbas used a practical demonstration to teach the Prophet’s ablution."},"teachings":["Ibn Abbas introduced the act as a way to show the Prophet’s wudu.","The narration mentions washing each limb once only.","The teaching was given through a practical demonstration."],"related_hadiths":[{"id":"157","book_id":"1","label":"Sahih Bukhari"},{"id":"158","book_id":"1","label":"Sahih Bukhari"},{"id":"159","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu Once","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم performed ablution by washing each limb once only."},"heading":{"title":"Wudu Once: Ibn Abbas Reports Washing Each Limb One Time","description":"This Hadith focuses on wudu once. Ibn Abbas asked, “May I not tell you how the Messenger of Allah صلى الله عليه وسلم performed ablution?” He then performed ablution washing each limb once only. The narration is short, but it answers a common search question: can wudu be described with one wash for each limb in Hadith? Based on this text, Ibn Abbas showed a form of ablution where each limb was washed one time. The report does not give a long list of steps in the translation provided, and it does not discuss other counts. So the explanation should stay close to the wording. Its main lesson is that Ibn Abbas used a practical demonstration to teach the Prophet’s ablution."},"teachings":["Ibn Abbas introduced the act as a way to show the Prophet’s wudu.","The narration mentions washing each limb once only.","The teaching was given through a practical demonstration."],"related_hadiths":[{"id":"157","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"158","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"159","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E213" s="4" t="n"/>
@@ -5380,7 +5384,7 @@
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Laylat al-Qadr in Ramadan","description":"$book_name$ $hadith_number$ - $chapter_name$. Seek Laylat al-Qadr in Ramadan’s last ten nights, especially when nine, seven, or five nights remain."},"heading":{"title":"Hadith About Laylat al-Qadr in the Last Ten Nights of Ramadan","description":"This Hadith focuses on Laylat al-Qadr and where a believer should look for it. The Prophet صلى الله عليه وسلم told the people to seek Laylat al-Qadr in the last ten nights of Ramadan. He then pointed to specific times: when nine nights remain, when seven nights remain, and when five nights remain. In simple words, this Hadith teaches us not to treat the last part of Ramadan lightly. The main search focus here is “Laylat al-Qadr in the last ten nights,” along with related terms like “odd nights of Ramadan” and “Night of Decree Hadith.” The Hadith does not tell us to limit worship to only one night. It guides us to be alert and serious during these blessed nights."},"teachings":["Laylat al-Qadr should be sought in the last ten nights of Ramadan.","The Hadith highlights nights counted by how many nights remain.","A believer should stay active in worship near the end of Ramadan.","The exact search for Laylat al-Qadr needs effort, not guesswork only."],"related_hadiths":[{"id":"1382","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1383","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1385","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Laylat al-Qadr in Ramadan","description":"$book_name$ $hadith_number$ - $chapter_name$. Seek Laylat al-Qadr in Ramadan’s last ten nights, especially when nine, seven, or five nights remain."},"heading":{"title":"Hadith About Laylat al-Qadr in the Last Ten Nights of Ramadan","description":"This Hadith focuses on Laylat al-Qadr and where a believer should look for it. The Prophet صلى الله عليه وسلم told the people to seek Laylat al-Qadr in the last ten nights of Ramadan. He then pointed to specific times: when nine nights remain, when seven nights remain, and when five nights remain. In simple words, this Hadith teaches us not to treat the last part of Ramadan lightly. The main search focus here is “Laylat al-Qadr in the last ten nights,” along with related terms like “odd nights of Ramadan” and “Night of Decree Hadith.” The Hadith does not tell us to limit worship to only one night. It guides us to be alert and serious during these blessed nights."},"teachings":["Laylat al-Qadr should be sought in the last ten nights of Ramadan.","The Hadith highlights nights counted by how many nights remain.","A believer should stay active in worship near the end of Ramadan.","The exact search for Laylat al-Qadr needs effort, not guesswork only."],"related_hadiths":[{"id":"1382","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1383","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1385","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E214" s="4" t="n"/>
@@ -5403,7 +5407,7 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lowering Garment Near the Ground","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم would not raise his garment until he was close to the ground, showing modesty."},"heading":{"title":"Hadith About Modesty When Relieving Oneself","description":"This hadith teaches modesty through a small physical action. Abdullah ibn Umar narrates that when the Prophet صلى الله عليه وسلم wanted to relieve himself, he would not raise his garment until he lowered himself near the ground. Abu Dawud also notes weakness in a chain connected to another route, so the wording should be handled with care. The core topic is modesty when relieving oneself. The lesson from the stated text is simple: privacy and covering were treated seriously. The narration does not speak about public display or other matters, so we should not add extra claims. It shows that modesty can be practiced in the timing of even a small movement."},"teachings":["The narration points to care in covering oneself.","Modesty is shown before and during private acts.","Abu Dawud’s note reminds readers to be careful with reported chains."],"related_hadiths":[{"id":"1","book_id":"4","label":"Sunan Abu Dawud"},{"id":"2","book_id":"4","label":"Sunan Abu Dawud"},{"id":"15","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lowering Garment Near the Ground","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم would not raise his garment until he was close to the ground, showing modesty."},"heading":{"title":"Hadith About Modesty When Relieving Oneself","description":"This hadith teaches modesty through a small physical action. Abdullah ibn Umar narrates that when the Prophet صلى الله عليه وسلم wanted to relieve himself, he would not raise his garment until he lowered himself near the ground. Abu Dawud also notes weakness in a chain connected to another route, so the wording should be handled with care. The core topic is modesty when relieving oneself. The lesson from the stated text is simple: privacy and covering were treated seriously. The narration does not speak about public display or other matters, so we should not add extra claims. It shows that modesty can be practiced in the timing of even a small movement."},"teachings":["The narration points to care in covering oneself.","Modesty is shown before and during private acts.","Abu Dawud’s note reminds readers to be careful with reported chains."],"related_hadiths":[{"id":"1","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"2","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"15","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E215" s="4" t="n"/>
@@ -5426,7 +5430,7 @@
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Fifteen Prostrations in Qur'an Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught fifteen prostrations in Qur'an recitation, including places in al-Mufassal and Surah al-Hajj."},"heading":{"title":"Sujud Tilawah Hadith: Fifteen Prostrations in the Qur'an","description":"This hadith focuses on sujud tilawah, the prostration made when reciting certain verses of the Qur'an. Amr ibn al-'As reports that the Prophet صلى الله عليه وسلم taught him fifteen prostrations in Qur'an recitation. The text also points out that three of them are in al-Mufassal and two are in Surah al-Hajj. This makes the hadith useful for people searching for hadith about sajdah in Quran, prostration while reciting Quran, and how many sajdah in Quran. Abu Dawud also mentions another report from Abu al-Darda' about eleven prostrations, but he clearly says its chain is weak. So the core teaching here is to pay careful attention to the narrated count and the note about reliability."},"teachings":["The hadith reports fifteen prostrations connected to Qur'an recitation.","It mentions three prostrations in al-Mufassal and two in Surah al-Hajj.","Abu Dawud's note reminds readers to notice the strength or weakness of a report.","The wording shows that learning Qur'an recitation includes learning where prostration is made."],"related_hadiths":[{"id":"1402","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1407","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Fifteen Prostrations in Qur'an Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught fifteen prostrations in Qur'an recitation, including places in al-Mufassal and Surah al-Hajj."},"heading":{"title":"Sujud Tilawah Hadith: Fifteen Prostrations in the Qur'an","description":"This hadith focuses on sujud tilawah, the prostration made when reciting certain verses of the Qur'an. Amr ibn al-'As reports that the Prophet صلى الله عليه وسلم taught him fifteen prostrations in Qur'an recitation. The text also points out that three of them are in al-Mufassal and two are in Surah al-Hajj. This makes the hadith useful for people searching for hadith about sajdah in Quran, prostration while reciting Quran, and how many sajdah in Quran. Abu Dawud also mentions another report from Abu al-Darda' about eleven prostrations, but he clearly says its chain is weak. So the core teaching here is to pay careful attention to the narrated count and the note about reliability."},"teachings":["The hadith reports fifteen prostrations connected to Qur'an recitation.","It mentions three prostrations in al-Mufassal and two in Surah al-Hajj.","Abu Dawud's note reminds readers to notice the strength or weakness of a report.","The wording shows that learning Qur'an recitation includes learning where prostration is made."],"related_hadiths":[{"id":"1402","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1407","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E216" s="4" t="n"/>
@@ -5449,7 +5453,7 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Prostrations in Surah al-Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet confirmed two prostrations in Surah al-Hajj and linked reciting them with making the prostrations."},"heading":{"title":"Surah al-Hajj Two Prostrations Hadith and Sujud Tilawah","description":"This hadith answers a direct question about sujud tilawah in Surah al-Hajj. Uqbah ibn Amir asked the Messenger of Allah صلى الله عليه وسلم whether Surah al-Hajj contains two prostrations. The Prophet صلى الله عليه وسلم replied yes, then added that whoever does not make the two prostrations should not recite them. The wording is short, but it strongly connects Qur'an recitation with the response of prostration at those places. For readers searching for Surah Hajj two sajdah hadith, prostration in Surah al-Hajj, or sajdah tilawat in Quran, this narration gives a focused answer from the hadith text itself. It does not discuss other surahs or wider rulings, so the safest explanation stays with the question and answer in this report."},"teachings":["The hadith directly confirms two prostrations in Surah al-Hajj.","Reciting these places is linked with making the two prostrations.","The Companion asked clearly, and the Prophet صلى الله عليه وسلم answered clearly.","The report teaches care when reaching verses of prostration in Qur'an recitation."],"related_hadiths":[{"id":"1401","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1413","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Prostrations in Surah al-Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet confirmed two prostrations in Surah al-Hajj and linked reciting them with making the prostrations."},"heading":{"title":"Surah al-Hajj Two Prostrations Hadith and Sujud Tilawah","description":"This hadith answers a direct question about sujud tilawah in Surah al-Hajj. Uqbah ibn Amir asked the Messenger of Allah صلى الله عليه وسلم whether Surah al-Hajj contains two prostrations. The Prophet صلى الله عليه وسلم replied yes, then added that whoever does not make the two prostrations should not recite them. The wording is short, but it strongly connects Qur'an recitation with the response of prostration at those places. For readers searching for Surah Hajj two sajdah hadith, prostration in Surah al-Hajj, or sajdah tilawat in Quran, this narration gives a focused answer from the hadith text itself. It does not discuss other surahs or wider rulings, so the safest explanation stays with the question and answer in this report."},"teachings":["The hadith directly confirms two prostrations in Surah al-Hajj.","Reciting these places is linked with making the two prostrations.","The Companion asked clearly, and the Prophet صلى الله عليه وسلم answered clearly.","The report teaches care when reaching verses of prostration in Qur'an recitation."],"related_hadiths":[{"id":"1401","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1413","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E217" s="4" t="n"/>
@@ -5472,7 +5476,7 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Prostration in al-Mufassal After Hijrah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet did not prostrate in al-Mufassal after moving to Medina."},"heading":{"title":"Hadith About al-Mufassal Prostration and Sujud Tilawah","description":"This hadith presents a specific report from Abdullah ibn Abbas about sujud tilawah in al-Mufassal. He says that the Messenger of Allah صلى الله عليه وسلم did not make a prostration at any verse in al-Mufassal from the time he moved to Medina. The main point is narrow and should not be stretched beyond the text. It speaks about a time period after the move to Medina and about al-Mufassal in particular. People searching for al-Mufassal sajdah hadith, did the Prophet prostrate in al-Mufassal, or sujud tilawah in short surahs may find this narration important because it records what Ibn Abbas reported. The hadith does not list every verse, and it does not explain the reason, so the explanation should stay with the wording given."},"teachings":["The report is about al-Mufassal specifically.","It connects the practice mentioned to the period after the Prophet صلى الله عليه وسلم moved to Medina.","The hadith shows that reports on sujud tilawah can mention both action and non-action.","It reminds the reader not to add reasons that are not stated in the text."],"related_hadiths":[{"id":"1404","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1405","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Prostration in al-Mufassal After Hijrah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet did not prostrate in al-Mufassal after moving to Medina."},"heading":{"title":"Hadith About al-Mufassal Prostration and Sujud Tilawah","description":"This hadith presents a specific report from Abdullah ibn Abbas about sujud tilawah in al-Mufassal. He says that the Messenger of Allah صلى الله عليه وسلم did not make a prostration at any verse in al-Mufassal from the time he moved to Medina. The main point is narrow and should not be stretched beyond the text. It speaks about a time period after the move to Medina and about al-Mufassal in particular. People searching for al-Mufassal sajdah hadith, did the Prophet prostrate in al-Mufassal, or sujud tilawah in short surahs may find this narration important because it records what Ibn Abbas reported. The hadith does not list every verse, and it does not explain the reason, so the explanation should stay with the wording given."},"teachings":["The report is about al-Mufassal specifically.","It connects the practice mentioned to the period after the Prophet صلى الله عليه وسلم moved to Medina.","The hadith shows that reports on sujud tilawah can mention both action and non-action.","It reminds the reader not to add reasons that are not stated in the text."],"related_hadiths":[{"id":"1404","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1405","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E218" s="4" t="n"/>
@@ -5495,7 +5499,7 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah an-Najm Without Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. Zaid bin Thabit recited Surah an-Najm to the Prophet, and the Prophet did not prostrate in it."},"heading":{"title":"Surah an-Najm Prostration Hadith: When No Sajdah Was Made","description":"This hadith is about Surah an-Najm and sujud tilawah. Zaid bin Thabit says that he recited Surah an-Najm to the Messenger of Allah صلى الله عليه وسلم, and the Prophet صلى الله عليه وسلم did not prostrate in it. The report is simple and should be read exactly as it comes. It does not deny that other narrations mention prostration in Surah an-Najm; it only reports this specific incident where no prostration happened. That is why this hadith is useful for searches like Surah Najm prostration hadith, Zaid bin Thabit An-Najm, and hadith no sajdah in Surah Najm. The main lesson is careful reading: one narration may describe a particular event without giving a full rule for every situation."},"teachings":["Zaid bin Thabit recited Surah an-Najm to the Prophet صلى الله عليه وسلم.","In this reported incident, the Prophet صلى الله عليه وسلم did not prostrate.","The hadith teaches careful attention to the exact event being described.","It should not be expanded beyond what the narration states."],"related_hadiths":[{"id":"1405","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"1","label":"Sahih Bukhari"},{"id":"577","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah an-Najm Without Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. Zaid bin Thabit recited Surah an-Najm to the Prophet, and the Prophet did not prostrate in it."},"heading":{"title":"Surah an-Najm Prostration Hadith: When No Sajdah Was Made","description":"This hadith is about Surah an-Najm and sujud tilawah. Zaid bin Thabit says that he recited Surah an-Najm to the Messenger of Allah صلى الله عليه وسلم, and the Prophet صلى الله عليه وسلم did not prostrate in it. The report is simple and should be read exactly as it comes. It does not deny that other narrations mention prostration in Surah an-Najm; it only reports this specific incident where no prostration happened. That is why this hadith is useful for searches like Surah Najm prostration hadith, Zaid bin Thabit An-Najm, and hadith no sajdah in Surah Najm. The main lesson is careful reading: one narration may describe a particular event without giving a full rule for every situation."},"teachings":["Zaid bin Thabit recited Surah an-Najm to the Prophet صلى الله عليه وسلم.","In this reported incident, the Prophet صلى الله عليه وسلم did not prostrate.","The hadith teaches careful attention to the exact event being described.","It should not be expanded beyond what the narration states."],"related_hadiths":[{"id":"1405","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"577","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E219" s="4" t="n"/>
@@ -5518,7 +5522,7 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zaid bin Thabit and Surah an-Najm","description":"$book_name$ $hadith_number$ - $chapter_name$. Another chain reports the same meaning from Zaid, with Abu Dawud noting he was imam and did not prostrate."},"heading":{"title":"Zaid bin Thabit Hadith on Surah an-Najm and Sujud Tilawah","description":"This narration supports the previous report about Surah an-Najm and sujud tilawah. It says the same meaning has been transmitted from Zaid bin Thabit through another chain. Abu Dawud then adds a note: Zaid was the imam in a prayer and did not make prostration in it. The hadith is useful for readers searching for Zaid bin Thabit Surah Najm hadith, imam did not make sajdah, or sujud tilawah in prayer. The key point is not to turn the note into a wider claim than the text gives. It tells us what happened in this report and how Abu Dawud explained the setting. The narration teaches us to read hadith details with care, including narrator notes."},"teachings":["The report gives another chain for the same meaning from Zaid bin Thabit.","Abu Dawud notes that Zaid was the imam and did not prostrate.","The hadith highlights the value of narrator notes in understanding a report.","It stays focused on this specific event connected to Surah an-Najm."],"related_hadiths":[{"id":"1404","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1403","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zaid bin Thabit and Surah an-Najm","description":"$book_name$ $hadith_number$ - $chapter_name$. Another chain reports the same meaning from Zaid, with Abu Dawud noting he was imam and did not prostrate."},"heading":{"title":"Zaid bin Thabit Hadith on Surah an-Najm and Sujud Tilawah","description":"This narration supports the previous report about Surah an-Najm and sujud tilawah. It says the same meaning has been transmitted from Zaid bin Thabit through another chain. Abu Dawud then adds a note: Zaid was the imam in a prayer and did not make prostration in it. The hadith is useful for readers searching for Zaid bin Thabit Surah Najm hadith, imam did not make sajdah, or sujud tilawah in prayer. The key point is not to turn the note into a wider claim than the text gives. It tells us what happened in this report and how Abu Dawud explained the setting. The narration teaches us to read hadith details with care, including narrator notes."},"teachings":["The report gives another chain for the same meaning from Zaid bin Thabit.","Abu Dawud notes that Zaid was the imam and did not prostrate.","The hadith highlights the value of narrator notes in understanding a report.","It stays focused on this specific event connected to Surah an-Najm."],"related_hadiths":[{"id":"1404","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1403","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E220" s="4" t="n"/>
@@ -5541,7 +5545,7 @@
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah an-Najm Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited Surah an-Najm and prostrated, and those present prostrated with him."},"heading":{"title":"Surah an-Najm Prostration Hadith and the Response of the People","description":"This hadith gives a vivid report about sujud tilawah in Surah an-Najm. Abdullah ibn Mas'ud says that the Messenger of Allah صلى الله عليه وسلم recited Surah an-Najm and prostrated. Everyone present prostrated with him, except a man who took pebbles or dust, raised it to his face, and said that it was enough for him. Ibn Mas'ud later says he saw that man killed as an unbeliever. For searches like Surah Najm sajdah hadith, Prophet prostrated in An-Najm, and sujud tilawah hadith, this narration shows the public response to a verse of prostration. The explanation should not add extra details about the man or the setting beyond what the hadith states."},"teachings":["The Prophet صلى الله عليه وسلم recited Surah an-Najm and prostrated.","The people present prostrated along with him.","One man avoided full prostration by lifting pebbles or dust to his face.","The narration records Ibn Mas'ud's later statement without adding more background."],"related_hadiths":[{"id":"1070","book_id":"1","label":"Sahih Bukhari"},{"id":"1071","book_id":"1","label":"Sahih Bukhari"},{"id":"576","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah an-Najm Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited Surah an-Najm and prostrated, and those present prostrated with him."},"heading":{"title":"Surah an-Najm Prostration Hadith and the Response of the People","description":"This hadith gives a vivid report about sujud tilawah in Surah an-Najm. Abdullah ibn Mas'ud says that the Messenger of Allah صلى الله عليه وسلم recited Surah an-Najm and prostrated. Everyone present prostrated with him, except a man who took pebbles or dust, raised it to his face, and said that it was enough for him. Ibn Mas'ud later says he saw that man killed as an unbeliever. For searches like Surah Najm sajdah hadith, Prophet prostrated in An-Najm, and sujud tilawah hadith, this narration shows the public response to a verse of prostration. The explanation should not add extra details about the man or the setting beyond what the hadith states."},"teachings":["The Prophet صلى الله عليه وسلم recited Surah an-Najm and prostrated.","The people present prostrated along with him.","One man avoided full prostration by lifting pebbles or dust to his face.","The narration records Ibn Mas'ud's later statement without adding more background."],"related_hadiths":[{"id":"1070","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1071","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"576","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E221" s="4" t="n"/>
@@ -5564,7 +5568,7 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostration in Inshiqaq and Alaq","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah reports prostration with the Prophet during Surah al-Inshiqaq and Surah al-Alaq."},"heading":{"title":"Sujud Tilawah in Surah al-Inshiqaq and Surah al-Alaq Hadith","description":"This hadith records two places of sujud tilawah connected to Qur'an recitation. Abu Hurairah says, We prostrated along with the Messenger of Allah صلى الله عليه وسلم on account of the verses from Surah al-Inshiqaq and Surah al-Alaq. The report is short, but it is helpful for people searching for sajdah in Surah Inshiqaq, sajdah in Surah Alaq, or prostration while reciting Quran. It shows that the Companions followed the Prophet صلى الله عليه وسلم in prostration when these verses were recited. The hadith does not describe the full prayer setting or the exact wording of the prostration. Its main value is naming these two recitations as connected with prostration in the Prophet's practice."},"teachings":["Abu Hurairah reports prostration with the Prophet صلى الله عليه وسلم in two recitations.","The named recitations are Surah al-Inshiqaq and Surah al-Alaq.","The Companions followed the Prophet صلى الله عليه وسلم in the act of prostration.","The hadith keeps the focus on the recited verses that led to sujud."],"related_hadiths":[{"id":"1408","book_id":"4","label":"Sunan Abu Dawud"},{"id":"578c","book_id":"2","label":"Sahih Muslim"},{"id":"578d","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prostration in Inshiqaq and Alaq","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah reports prostration with the Prophet during Surah al-Inshiqaq and Surah al-Alaq."},"heading":{"title":"Sujud Tilawah in Surah al-Inshiqaq and Surah al-Alaq Hadith","description":"This hadith records two places of sujud tilawah connected to Qur'an recitation. Abu Hurairah says, We prostrated along with the Messenger of Allah صلى الله عليه وسلم on account of the verses from Surah al-Inshiqaq and Surah al-Alaq. The report is short, but it is helpful for people searching for sajdah in Surah Inshiqaq, sajdah in Surah Alaq, or prostration while reciting Quran. It shows that the Companions followed the Prophet صلى الله عليه وسلم in prostration when these verses were recited. The hadith does not describe the full prayer setting or the exact wording of the prostration. Its main value is naming these two recitations as connected with prostration in the Prophet's practice."},"teachings":["Abu Hurairah reports prostration with the Prophet صلى الله عليه وسلم in two recitations.","The named recitations are Surah al-Inshiqaq and Surah al-Alaq.","The Companions followed the Prophet صلى الله عليه وسلم in the act of prostration.","The hadith keeps the focus on the recited verses that led to sujud."],"related_hadiths":[{"id":"1408","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"578c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"578d","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E222" s="4" t="n"/>
@@ -5587,7 +5591,7 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Hurairah's Prostration in Inshiqaq","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah prostrated in Surah al-Inshiqaq and said he did so behind the Prophet."},"heading":{"title":"Surah al-Inshiqaq Prostration Hadith and Sujud Tilawah","description":"This hadith explains why Abu Hurairah made sujud tilawah when reciting Surah al-Inshiqaq in the night prayer. Abu Rafi says he prayed behind Abu Hurairah. Abu Hurairah recited the surah, prostrated, and then explained that he had prostrated on account of it behind Abu al-Qasim, meaning the Prophet صلى الله عليه وسلم. He added that he would continue doing so until he met him. For readers searching for Surah Inshiqaq prostration hadith, Abu Hurairah sajdah, or sujud tilawah in Isha prayer, this narration shows a Companion holding to a practice he personally witnessed behind the Prophet صلى الله عليه وسلم. The report is about this surah and this act of prostration."},"teachings":["Abu Hurairah prostrated during Surah al-Inshiqaq.","He linked his action to what he did behind the Prophet صلى الله عليه وسلم.","The report shows a Companion continuing a practice he witnessed.","The hadith explains the prostration through Abu Hurairah's own answer."],"related_hadiths":[{"id":"1407","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1078","book_id":"1","label":"Sahih Bukhari"},{"id":"578a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Hurairah's Prostration in Inshiqaq","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah prostrated in Surah al-Inshiqaq and said he did so behind the Prophet."},"heading":{"title":"Surah al-Inshiqaq Prostration Hadith and Sujud Tilawah","description":"This hadith explains why Abu Hurairah made sujud tilawah when reciting Surah al-Inshiqaq in the night prayer. Abu Rafi says he prayed behind Abu Hurairah. Abu Hurairah recited the surah, prostrated, and then explained that he had prostrated on account of it behind Abu al-Qasim, meaning the Prophet صلى الله عليه وسلم. He added that he would continue doing so until he met him. For readers searching for Surah Inshiqaq prostration hadith, Abu Hurairah sajdah, or sujud tilawah in Isha prayer, this narration shows a Companion holding to a practice he personally witnessed behind the Prophet صلى الله عليه وسلم. The report is about this surah and this act of prostration."},"teachings":["Abu Hurairah prostrated during Surah al-Inshiqaq.","He linked his action to what he did behind the Prophet صلى الله عليه وسلم.","The report shows a Companion continuing a practice he witnessed.","The hadith explains the prostration through Abu Hurairah's own answer."],"related_hadiths":[{"id":"1407","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1078","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"578a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E223" s="4" t="n"/>
@@ -5610,7 +5614,7 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sajdah in Surah Sad","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas says the prostration in Surah Sad is not among the commanded prostrations, yet he saw the Prophet prostrate."},"heading":{"title":"Surah Sad Prostration Hadith and Sujud Tilawah","description":"This hadith gives a balanced statement about the prostration in Surah Sad. Ibn Abbas says that the prostration when reciting Sad is not one of the divinely commanded prostrations, but he also says that he saw the Messenger of Allah صلى الله عليه وسلم prostrate in it. The report is useful for searches like Surah Sad sajdah hadith, is sajdah in Surah Sad compulsory, and Prophet prostrated in Surah Sad. The safest reading is to keep both parts together. The hadith does not ignore the Prophet's action, and it also does not describe this prostration as one of the commanded ones. This is a good example of how hadith wording can carry a careful distinction."},"teachings":["Ibn Abbas says the prostration in Surah Sad is not among the commanded prostrations.","He also reports seeing the Prophet صلى الله عليه وسلم prostrate in it.","The hadith teaches readers to keep both parts of a narration together.","It supports careful wording when speaking about sujud tilawah."],"related_hadiths":[{"id":"1410","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3422","book_id":"1","label":"Sahih Bukhari"},{"id":"1413","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sajdah in Surah Sad","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas says the prostration in Surah Sad is not among the commanded prostrations, yet he saw the Prophet prostrate."},"heading":{"title":"Surah Sad Prostration Hadith and Sujud Tilawah","description":"This hadith gives a balanced statement about the prostration in Surah Sad. Ibn Abbas says that the prostration when reciting Sad is not one of the divinely commanded prostrations, but he also says that he saw the Messenger of Allah صلى الله عليه وسلم prostrate in it. The report is useful for searches like Surah Sad sajdah hadith, is sajdah in Surah Sad compulsory, and Prophet prostrated in Surah Sad. The safest reading is to keep both parts together. The hadith does not ignore the Prophet's action, and it also does not describe this prostration as one of the commanded ones. This is a good example of how hadith wording can carry a careful distinction."},"teachings":["Ibn Abbas says the prostration in Surah Sad is not among the commanded prostrations.","He also reports seeing the Prophet صلى الله عليه وسلم prostrate in it.","The hadith teaches readers to keep both parts of a narration together.","It supports careful wording when speaking about sujud tilawah."],"related_hadiths":[{"id":"1410","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"3422","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1413","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E224" s="4" t="n"/>
@@ -5633,7 +5637,7 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Clean the Nose Well in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches careful nose cleansing in wudu, done twice or three times, with attention and balance."},"heading":{"title":"Hadith About Wudu Nose Cleaning: Cleanse the Nose Well","description":"This hadith about wudu nose cleaning gives a short and clear instruction from the Messenger of Allah (صلى الله عليه وسلم). He told Muslims to cleanse the nose well after taking water into it, doing so twice or three times. The main lesson is careful cleanliness during ablution. It is not described as a random habit, but as a set part of the washing process. The words also show balance. The number is not left as endless; it is twice or three times. So the believer learns to do the action properly without turning it into hardship. For anyone searching for how to clean the nose in wudu, this narration points to a simple Sunnah method: use water, clear the nose well, and keep the action measured."},"teachings":["Clean the nose well as part of wudu.","Repeating the action twice or three times is mentioned in the text.","Wudu should be done with care, not in a careless way.","The hadith teaches measured practice without excess."],"related_hadiths":[{"id":"161","book_id":"1","label":"Sahih Bukhari"},{"id":"191","book_id":"1","label":"Sahih Bukhari"},{"id":"135","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Clean the Nose Well in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches careful nose cleansing in wudu, done twice or three times, with attention and balance."},"heading":{"title":"Hadith About Wudu Nose Cleaning: Cleanse the Nose Well","description":"This hadith about wudu nose cleaning gives a short and clear instruction from the Messenger of Allah (صلى الله عليه وسلم). He told Muslims to cleanse the nose well after taking water into it, doing so twice or three times. The main lesson is careful cleanliness during ablution. It is not described as a random habit, but as a set part of the washing process. The words also show balance. The number is not left as endless; it is twice or three times. So the believer learns to do the action properly without turning it into hardship. For anyone searching for how to clean the nose in wudu, this narration points to a simple Sunnah method: use water, clear the nose well, and keep the action measured."},"teachings":["Clean the nose well as part of wudu.","Repeating the action twice or three times is mentioned in the text.","Wudu should be done with care, not in a careless way.","The hadith teaches measured practice without excess."],"related_hadiths":[{"id":"161","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"191","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"135","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E225" s="4" t="n"/>
@@ -5656,7 +5660,7 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah Sad and the Repentance of a Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited Surah Sad on the pulpit, prostrated, and described it as the repentance of a Prophet."},"heading":{"title":"Surah Sad Prostration Hadith: Repentance and Sujud Tilawah","description":"This hadith describes the Prophet صلى الله عليه وسلم reciting Surah Sad on the pulpit. When he reached the place of prostration, he came down and prostrated, and the people prostrated with him. On another day, the people prepared for prostration when he reached the same place. The Prophet صلى الله عليه وسلم said that it was the repentance of a Prophet, but when he saw them ready for prostration, he descended and prostrated, and they prostrated with him. For searches like Surah Sad prostration hadith, repentance of a Prophet hadith, and sujud tilawah on the pulpit, this narration shows both the explanation he gave and the action he performed. It should be explained without adding details beyond the report."},"teachings":["The Prophet صلى الله عليه وسلم recited Surah Sad on the pulpit.","He described the prostration as the repentance of a Prophet.","When the people were ready to prostrate, he prostrated and they followed.","The hadith shows how the Prophet صلى الله عليه وسلم taught through both words and action."],"related_hadiths":[{"id":"1409","book_id":"4","label":"Sunan Abu Dawud"},{"id":"3422","book_id":"1","label":"Sahih Bukhari"},{"id":"1412","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah Sad and the Repentance of a Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited Surah Sad on the pulpit, prostrated, and described it as the repentance of a Prophet."},"heading":{"title":"Surah Sad Prostration Hadith: Repentance and Sujud Tilawah","description":"This hadith describes the Prophet صلى الله عليه وسلم reciting Surah Sad on the pulpit. When he reached the place of prostration, he came down and prostrated, and the people prostrated with him. On another day, the people prepared for prostration when he reached the same place. The Prophet صلى الله عليه وسلم said that it was the repentance of a Prophet, but when he saw them ready for prostration, he descended and prostrated, and they prostrated with him. For searches like Surah Sad prostration hadith, repentance of a Prophet hadith, and sujud tilawah on the pulpit, this narration shows both the explanation he gave and the action he performed. It should be explained without adding details beyond the report."},"teachings":["The Prophet صلى الله عليه وسلم recited Surah Sad on the pulpit.","He described the prostration as the repentance of a Prophet.","When the people were ready to prostrate, he prostrated and they followed.","The hadith shows how the Prophet صلى الله عليه وسلم taught through both words and action."],"related_hadiths":[{"id":"1409","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"3422","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1412","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E226" s="4" t="n"/>
@@ -5679,7 +5683,7 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Group Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. During the year of Conquest, the Prophet recited a verse of prostration and all the people prostrated."},"heading":{"title":"Group Sujud Tilawah Hadith During Qur'an Recitation","description":"This hadith shows a large group responding to a verse of prostration. Abdullah ibn Umar reports that in the year of Conquest, the Messenger of Allah صلى الله عليه وسلم recited a verse at which prostration should be made, and all the people prostrated. Some were mounted, some prostrated on the ground, and those mounted prostrated on their hands. The hadith is useful for searches such as group sujud tilawah hadith, prostration while riding hadith, and verse of prostration in Quran. The text does not name the exact verse, so the explanation should not guess it. The clear message is that the people responded together to the verse, each according to the position described in the report."},"teachings":["The Prophet صلى الله عليه وسلم recited a verse at which prostration should be made.","All the people in the report prostrated.","Some were mounted, and some were on the ground.","Those who were mounted prostrated on their hands as described in the text."],"related_hadiths":[{"id":"1412","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1413","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Group Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. During the year of Conquest, the Prophet recited a verse of prostration and all the people prostrated."},"heading":{"title":"Group Sujud Tilawah Hadith During Qur'an Recitation","description":"This hadith shows a large group responding to a verse of prostration. Abdullah ibn Umar reports that in the year of Conquest, the Messenger of Allah صلى الله عليه وسلم recited a verse at which prostration should be made, and all the people prostrated. Some were mounted, some prostrated on the ground, and those mounted prostrated on their hands. The hadith is useful for searches such as group sujud tilawah hadith, prostration while riding hadith, and verse of prostration in Quran. The text does not name the exact verse, so the explanation should not guess it. The clear message is that the people responded together to the verse, each according to the position described in the report."},"teachings":["The Prophet صلى الله عليه وسلم recited a verse at which prostration should be made.","All the people in the report prostrated.","Some were mounted, and some were on the ground.","Those who were mounted prostrated on their hands as described in the text."],"related_hadiths":[{"id":"1412","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1413","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E227" s="4" t="n"/>
@@ -5702,7 +5706,7 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Crowded Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited a surah, prostrated, and the people prostrated until there was hardly space for foreheads."},"heading":{"title":"Crowded Sujud Tilawah Hadith: Prostrating with the Prophet","description":"This hadith gives a simple picture of people following the Prophet صلى الله عليه وسلم in sujud tilawah. Ibn Umar says the Messenger of Allah صلى الله عليه وسلم would recite a surah to them, and according to one version this happened outside the prayer. Then he would prostrate, and they would prostrate with him until none of them could find a place for his forehead. For searches like sujud tilawah outside prayer, crowded prostration hadith, and prostrating with the Prophet, this narration highlights the shared response to Qur'an recitation. The text does not name the surah or give a separate rule for every case. It simply reports the Prophet's action and the people's close following of it."},"teachings":["The Prophet صلى الله عليه وسلم recited a surah and then prostrated.","The people prostrated along with him.","According to one version, this was outside the prayer.","The crowd was so close that people could hardly find a place for the forehead."],"related_hadiths":[{"id":"1411","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1413","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Crowded Prostration","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited a surah, prostrated, and the people prostrated until there was hardly space for foreheads."},"heading":{"title":"Crowded Sujud Tilawah Hadith: Prostrating with the Prophet","description":"This hadith gives a simple picture of people following the Prophet صلى الله عليه وسلم in sujud tilawah. Ibn Umar says the Messenger of Allah صلى الله عليه وسلم would recite a surah to them, and according to one version this happened outside the prayer. Then he would prostrate, and they would prostrate with him until none of them could find a place for his forehead. For searches like sujud tilawah outside prayer, crowded prostration hadith, and prostrating with the Prophet, this narration highlights the shared response to Qur'an recitation. The text does not name the surah or give a separate rule for every case. It simply reports the Prophet's action and the people's close following of it."},"teachings":["The Prophet صلى الله عليه وسلم recited a surah and then prostrated.","The people prostrated along with him.","According to one version, this was outside the prayer.","The crowd was so close that people could hardly find a place for the forehead."],"related_hadiths":[{"id":"1411","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1413","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E228" s="4" t="n"/>
@@ -5725,7 +5729,7 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Takbir in Sajdah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet would say takbir when reaching a verse of prostration, then prostrate, and the people prostrated with him."},"heading":{"title":"Takbir in Sujud Tilawah Hadith During Qur'an Recitation","description":"This hadith highlights a specific action connected to sujud tilawah: saying takbir. Ibn Umar reports that the Messenger of Allah صلى الله عليه وسلم used to recite the Qur'an to them. When he passed by a verse of prostration, he would say Allahu akbar, prostrate, and the people would prostrate with him. The narrator Abd al-Razzaq says al-Thawri liked this hadith very much, and Abu Dawud explains that he liked it because it contains the uttering of takbir. For readers searching for takbir in sujud tilawah, how to make sajdah tilawat, or Prophet's way of prostration during recitation, this narration points to the takbir mentioned in the report without adding more steps."},"teachings":["The Prophet صلى الله عليه وسلم recited Qur'an to the people.","When he reached a verse of prostration, he said takbir.","He prostrated, and the people prostrated with him.","Abu Dawud notes that the report was valued because it mentions takbir."],"related_hadiths":[{"id":"1412","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1411","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Takbir in Sajdah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet would say takbir when reaching a verse of prostration, then prostrate, and the people prostrated with him."},"heading":{"title":"Takbir in Sujud Tilawah Hadith During Qur'an Recitation","description":"This hadith highlights a specific action connected to sujud tilawah: saying takbir. Ibn Umar reports that the Messenger of Allah صلى الله عليه وسلم used to recite the Qur'an to them. When he passed by a verse of prostration, he would say Allahu akbar, prostrate, and the people would prostrate with him. The narrator Abd al-Razzaq says al-Thawri liked this hadith very much, and Abu Dawud explains that he liked it because it contains the uttering of takbir. For readers searching for takbir in sujud tilawah, how to make sajdah tilawat, or Prophet's way of prostration during recitation, this narration points to the takbir mentioned in the report without adding more steps."},"teachings":["The Prophet صلى الله عليه وسلم recited Qur'an to the people.","When he reached a verse of prostration, he said takbir.","He prostrated, and the people prostrated with him.","Abu Dawud notes that the report was valued because it mentions takbir."],"related_hadiths":[{"id":"1412","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1411","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1070","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E229" s="4" t="n"/>
@@ -5748,7 +5752,7 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sujud Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said a repeated supplication in the prostration of Qur'an recitation at night."},"heading":{"title":"Dua for Sujud Tilawah Hadith: My Face Prostrates to Its Creator","description":"This hadith gives wording the Prophet صلى الله عليه وسلم said in the prostration of Qur'an recitation at night. Aisha reports that he would prostrate while reciting the Qur'an at night and repeatedly say that his face prostrates to the One who created it and brought forth its hearing and seeing by His might and power. For searches like dua for sujud tilawah, sajdah tilawat dua hadith, and what to say in sujud tilawah, this narration is very direct. It links the words of the dua to Allah's creation of the face, hearing, and sight. The hadith does not mention other supplications here, so the explanation should stay with this wording and its meaning."},"teachings":["The Prophet صلى الله عليه وسلم prostrated at night while reciting the Qur'an.","He repeated a supplication in that prostration.","The supplication mentions Allah creating the face, hearing, and sight.","The wording teaches humility before the Creator through the act of prostration."],"related_hadiths":[{"id":"1413","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1407","book_id":"4","label":"Sunan Abu Dawud"},{"id":"578c","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sujud Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said a repeated supplication in the prostration of Qur'an recitation at night."},"heading":{"title":"Dua for Sujud Tilawah Hadith: My Face Prostrates to Its Creator","description":"This hadith gives wording the Prophet صلى الله عليه وسلم said in the prostration of Qur'an recitation at night. Aisha reports that he would prostrate while reciting the Qur'an at night and repeatedly say that his face prostrates to the One who created it and brought forth its hearing and seeing by His might and power. For searches like dua for sujud tilawah, sajdah tilawat dua hadith, and what to say in sujud tilawah, this narration is very direct. It links the words of the dua to Allah's creation of the face, hearing, and sight. The hadith does not mention other supplications here, so the explanation should stay with this wording and its meaning."},"teachings":["The Prophet صلى الله عليه وسلم prostrated at night while reciting the Qur'an.","He repeated a supplication in that prostration.","The supplication mentions Allah creating the face, hearing, and sight.","The wording teaches humility before the Creator through the act of prostration."],"related_hadiths":[{"id":"1413","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1407","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"578c","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E230" s="4" t="n"/>
@@ -5771,7 +5775,7 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sujud Tilawah After Fajr","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar stopped prostration after dawn prayer and cited the Prophet, Abu Bakr, Umar, and Uthman waiting until sunrise."},"heading":{"title":"Sujud Tilawah After Fajr Hadith and Waiting Until Sunrise","description":"This hadith is about the timing of sujud tilawah after the dawn prayer. Abu Tamimah al-Hujaymi says he used to preach after Fajr and prostrate because of Qur'an recitation. Ibn Umar stopped him three times. Then Ibn Umar explained that he had prayed behind the Messenger of Allah صلى الله عليه وسلم, Abu Bakr, Umar, and Uthman, and they would not prostrate on account of Qur'an recitation until the sun had risen. For searches like sujud tilawah after Fajr, sajdah tilawat after dawn prayer, and Ibn Umar prostration after Fajr, this narration gives the reported practice he used as his reason. The text is focused on waiting until sunrise in this setting."},"teachings":["Abu Tamimah used to prostrate after Fajr due to Qur'an recitation.","Ibn Umar stopped him more than once.","Ibn Umar cited the practice of the Prophet صلى الله عليه وسلم and the first three caliphs.","The report specifically mentions waiting until the sun had risen."],"related_hadiths":[{"id":"1413","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1412","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sujud Tilawah After Fajr","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar stopped prostration after dawn prayer and cited the Prophet, Abu Bakr, Umar, and Uthman waiting until sunrise."},"heading":{"title":"Sujud Tilawah After Fajr Hadith and Waiting Until Sunrise","description":"This hadith is about the timing of sujud tilawah after the dawn prayer. Abu Tamimah al-Hujaymi says he used to preach after Fajr and prostrate because of Qur'an recitation. Ibn Umar stopped him three times. Then Ibn Umar explained that he had prayed behind the Messenger of Allah صلى الله عليه وسلم, Abu Bakr, Umar, and Uthman, and they would not prostrate on account of Qur'an recitation until the sun had risen. For searches like sujud tilawah after Fajr, sajdah tilawat after dawn prayer, and Ibn Umar prostration after Fajr, this narration gives the reported practice he used as his reason. The text is focused on waiting until sunrise in this setting."},"teachings":["Abu Tamimah used to prostrate after Fajr due to Qur'an recitation.","Ibn Umar stopped him more than once.","Ibn Umar cited the practice of the Prophet صلى الله عليه وسلم and the first three caliphs.","The report specifically mentions waiting until the sun had risen."],"related_hadiths":[{"id":"1413","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1412","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1072","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E231" s="4" t="n"/>
@@ -5794,7 +5798,7 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah Loves Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said Allah is single and loves what is single, so the people of the Qur'an should observe Witr."},"heading":{"title":"Witr Prayer Hadith: Allah Loves What Is Single","description":"This hadith moves to the topic of Witr prayer. Ali ibn Abi Talib reports that the Prophet صلى الله عليه وسلم said Allah is Witr, meaning single, and loves what is single, so the people of the Qur'an should observe Witr. The wording speaks directly to those connected with the Qur'an and calls them to pray Witr. For people searching for witr prayer hadith, Allah loves witr hadith, or O people of the Quran pray witr, this narration is a key text. The hadith does not give the number of rak'ahs or a full method here. Its main teaching is the value of Witr and the link between Allah's oneness and loving what is odd or single."},"teachings":["Allah is described as Witr, single.","The Prophet صلى الله عليه وسلم said Allah loves what is single.","The people of the Qur'an are told to observe Witr.","The hadith highlights the value of Witr without giving its full method."],"related_hadiths":[{"id":"1417","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1418","book_id":"4","label":"Sunan Abu Dawud"},{"id":"990","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah Loves Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said Allah is single and loves what is single, so the people of the Qur'an should observe Witr."},"heading":{"title":"Witr Prayer Hadith: Allah Loves What Is Single","description":"This hadith moves to the topic of Witr prayer. Ali ibn Abi Talib reports that the Prophet صلى الله عليه وسلم said Allah is Witr, meaning single, and loves what is single, so the people of the Qur'an should observe Witr. The wording speaks directly to those connected with the Qur'an and calls them to pray Witr. For people searching for witr prayer hadith, Allah loves witr hadith, or O people of the Quran pray witr, this narration is a key text. The hadith does not give the number of rak'ahs or a full method here. Its main teaching is the value of Witr and the link between Allah's oneness and loving what is odd or single."},"teachings":["Allah is described as Witr, single.","The Prophet صلى الله عليه وسلم said Allah loves what is single.","The people of the Qur'an are told to observe Witr.","The hadith highlights the value of Witr without giving its full method."],"related_hadiths":[{"id":"1417","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1418","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E232" s="4" t="n"/>
@@ -5817,7 +5821,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr for People of the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. A similar report from Ibn Mas'ud adds that a Bedouin was told this address was not for him or his companions."},"heading":{"title":"Witr Prayer Hadith for the People of the Qur'an","description":"This narration carries the same meaning as the previous Witr prayer hadith through another chain from Abdullah ibn Mas'ud. It includes an added exchange: a Bedouin asked what was being said, and the reply was that it was neither for him nor for his companions. The core message still centers on Witr and the address to the people of the Qur'an. Readers searching for witr prayer hadith, people of the Quran pray witr, or Ibn Masud witr narration will find that this report gives a related wording and a small added detail. The safe explanation is not to guess why the Bedouin was answered that way. The text simply records the exchange and keeps the focus on Witr."},"teachings":["The narration gives a similar meaning about Witr through Ibn Mas'ud.","It includes an added exchange with a Bedouin.","The main topic remains the call to observe Witr.","The text does not explain the reason behind the added reply, so it should not be guessed."],"related_hadiths":[{"id":"1416","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1418","book_id":"4","label":"Sunan Abu Dawud"},{"id":"754a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr for People of the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. A similar report from Ibn Mas'ud adds that a Bedouin was told this address was not for him or his companions."},"heading":{"title":"Witr Prayer Hadith for the People of the Qur'an","description":"This narration carries the same meaning as the previous Witr prayer hadith through another chain from Abdullah ibn Mas'ud. It includes an added exchange: a Bedouin asked what was being said, and the reply was that it was neither for him nor for his companions. The core message still centers on Witr and the address to the people of the Qur'an. Readers searching for witr prayer hadith, people of the Quran pray witr, or Ibn Masud witr narration will find that this report gives a related wording and a small added detail. The safe explanation is not to guess why the Bedouin was answered that way. The text simply records the exchange and keeps the focus on Witr."},"teachings":["The narration gives a similar meaning about Witr through Ibn Mas'ud.","It includes an added exchange with a Bedouin.","The main topic remains the call to observe Witr.","The text does not explain the reason behind the added reply, so it should not be guessed."],"related_hadiths":[{"id":"1416","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1418","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"754a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E233" s="4" t="n"/>
@@ -5840,7 +5844,7 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Between Isha and Fajr","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet described Witr as an extra prayer appointed between the night prayer and daybreak."},"heading":{"title":"Witr Prayer Time Hadith: Between Isha and Daybreak","description":"This hadith gives a clear time frame for Witr prayer. Kharijah ibn Hudhafah reports that the Messenger of Allah صلى الله عليه وسلم came out and said that Allah had given the Muslims an extra prayer, better for them than red camels, and that this prayer is Witr. He then said Allah appointed it between the night prayer and the daybreak. For searches like witr prayer time hadith, when to pray Witr, Witr between Isha and Fajr, and extra prayer after Isha, this narration is very focused. The hadith describes Witr as a valuable prayer and names its time window. It does not give all details of how many rak'ahs or how to recite, so those points should not be added here."},"teachings":["Witr is described as an extra prayer given by Allah.","The hadith says it is better for the believers than red camels.","Its time is stated as between the night prayer and daybreak.","The report names the prayer clearly as Witr."],"related_hadiths":[{"id":"1416","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1419","book_id":"4","label":"Sunan Abu Dawud"},{"id":"996","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Between Isha and Fajr","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet described Witr as an extra prayer appointed between the night prayer and daybreak."},"heading":{"title":"Witr Prayer Time Hadith: Between Isha and Daybreak","description":"This hadith gives a clear time frame for Witr prayer. Kharijah ibn Hudhafah reports that the Messenger of Allah صلى الله عليه وسلم came out and said that Allah had given the Muslims an extra prayer, better for them than red camels, and that this prayer is Witr. He then said Allah appointed it between the night prayer and the daybreak. For searches like witr prayer time hadith, when to pray Witr, Witr between Isha and Fajr, and extra prayer after Isha, this narration is very focused. The hadith describes Witr as a valuable prayer and names its time window. It does not give all details of how many rak'ahs or how to recite, so those points should not be added here."},"teachings":["Witr is described as an extra prayer given by Allah.","The hadith says it is better for the believers than red camels.","Its time is stated as between the night prayer and daybreak.","The report names the prayer clearly as Witr."],"related_hadiths":[{"id":"1416","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1419","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"996","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E234" s="4" t="n"/>
@@ -5863,7 +5867,7 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Is a Duty","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet repeated that Witr is a duty and warned against leaving it."},"heading":{"title":"Witr Is a Duty Hadith and the Seriousness of Witr Prayer","description":"This hadith gives a strong warning about Witr prayer. Buraydah ibn al-Hasib says he heard the Messenger of Allah صلى الله عليه وسلم say three times that Witr is a duty, and whoever does not observe it does not belong to us. Since the wording is repeated, the report places clear stress on not neglecting Witr. People searching for is Witr wajib hadith, Witr is a duty hadith, or whoever does not pray Witr does not belong to us will find this narration direct and serious. At the same time, the explanation should not add a full legal debate from outside the text. The hadith itself simply states the importance of Witr and repeats the warning three times."},"teachings":["The Prophet صلى الله عليه وسلم called Witr a duty in this report.","The statement is repeated three times.","The hadith warns against neglecting Witr.","The narration shows strong stress on observing Witr without giving its full method."],"related_hadiths":[{"id":"1418","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1420","book_id":"4","label":"Sunan Abu Dawud"},{"id":"754a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Is a Duty","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet repeated that Witr is a duty and warned against leaving it."},"heading":{"title":"Witr Is a Duty Hadith and the Seriousness of Witr Prayer","description":"This hadith gives a strong warning about Witr prayer. Buraydah ibn al-Hasib says he heard the Messenger of Allah صلى الله عليه وسلم say three times that Witr is a duty, and whoever does not observe it does not belong to us. Since the wording is repeated, the report places clear stress on not neglecting Witr. People searching for is Witr wajib hadith, Witr is a duty hadith, or whoever does not pray Witr does not belong to us will find this narration direct and serious. At the same time, the explanation should not add a full legal debate from outside the text. The hadith itself simply states the importance of Witr and repeats the warning three times."},"teachings":["The Prophet صلى الله عليه وسلم called Witr a duty in this report.","The statement is repeated three times.","The hadith warns against neglecting Witr.","The narration shows strong stress on observing Witr without giving its full method."],"related_hadiths":[{"id":"1418","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1420","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"754a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E235" s="4" t="n"/>
@@ -5886,7 +5890,7 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Perfect Wudu and Gentle Family Advice","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration highlights full wudu, cleaning between the fingers, deep nose rinsing, and care when fasting."},"heading":{"title":"Hadith About Full Wudu: Complete Ablution with Care","description":"This long hadith brings several lessons, but its core wudu teaching is very direct. The Messenger of Allah (صلى الله عليه وسلم) told Laqit ibn Sabirah to perform ablution in full, make water go through the fingers and beard, and sniff water well into the nose except while fasting. This makes the hadith a key text for searches like full wudu hadith, rinsing nose in wudu, and wudu while fasting. The narration also includes the Prophet’s practical guidance in family life: when Laqit spoke about harsh speech from his wife, he was told first about divorce, then, after mentioning their companionship and children, he was told to advise her and not beat her like a slave-girl. The explanation should stay with the text: the hadith teaches careful purification, measured action while fasting, and a calmer way of dealing with family trouble."},"teachings":["Perform wudu fully and with attention.","Clean between the fingers and let water reach the beard.","Sniff water well into the nose, but avoid deep sniffing while fasting.","Family problems should be handled with advice and restraint as shown in the text."],"related_hadiths":[{"id":"135","book_id":"4","label":"Sunan Abu Dawud"},{"id":"191","book_id":"1","label":"Sahih Bukhari"},{"id":"161","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Perfect Wudu and Gentle Family Advice","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration highlights full wudu, cleaning between the fingers, deep nose rinsing, and care when fasting."},"heading":{"title":"Hadith About Full Wudu: Complete Ablution with Care","description":"This long hadith brings several lessons, but its core wudu teaching is very direct. The Messenger of Allah (صلى الله عليه وسلم) told Laqit ibn Sabirah to perform ablution in full, make water go through the fingers and beard, and sniff water well into the nose except while fasting. This makes the hadith a key text for searches like full wudu hadith, rinsing nose in wudu, and wudu while fasting. The narration also includes the Prophet’s practical guidance in family life: when Laqit spoke about harsh speech from his wife, he was told first about divorce, then, after mentioning their companionship and children, he was told to advise her and not beat her like a slave-girl. The explanation should stay with the text: the hadith teaches careful purification, measured action while fasting, and a calmer way of dealing with family trouble."},"teachings":["Perform wudu fully and with attention.","Clean between the fingers and let water reach the beard.","Sniff water well into the nose, but avoid deep sniffing while fasting.","Family problems should be handled with advice and restraint as shown in the text."],"related_hadiths":[{"id":"135","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"191","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"161","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E236" s="4" t="n"/>
@@ -5909,7 +5913,7 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Five Prescribed Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. Ubadah reports that Allah prescribed five prayers, with a promise for those who preserve them and no promise for those who neglect them."},"heading":{"title":"Five Daily Prayers Hadith and the Place of Witr","description":"This hadith records a discussion about whether Witr is wajib, then gives a statement about the five prescribed prayers. Al-Makhdaji heard a man in Syria say that Witr is a duty and took the matter to Ubadah ibn as-Samit. Ubadah rejected that statement and said he heard the Messenger of Allah صلى الله عليه وسلم say that Allah prescribed five prayers on His servants. Whoever offers them without losing any or treating them lightly has a promise from Allah to be admitted to Paradise. Whoever does not offer them has no such promise; Allah may punish him or admit him to Paradise. For searches like five daily prayers hadith, is Witr wajib, and prescribed prayers in Islam, this narration is direct and carefully worded."},"teachings":["The narration reports a dispute about calling Witr wajib.","Ubadah responds by citing the hadith about five prescribed prayers.","The hadith warns against losing prayers or treating their rights lightly.","It states a promise for preserving the five prayers and leaves the other case to Allah's will."],"related_hadiths":[{"id":"1419","book_id":"4","label":"Sunan Abu Dawud"},{"id":"990","book_id":"1","label":"Sahih Bukhari"},{"id":"754a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Five Prescribed Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. Ubadah reports that Allah prescribed five prayers, with a promise for those who preserve them and no promise for those who neglect them."},"heading":{"title":"Five Daily Prayers Hadith and the Place of Witr","description":"This hadith records a discussion about whether Witr is wajib, then gives a statement about the five prescribed prayers. Al-Makhdaji heard a man in Syria say that Witr is a duty and took the matter to Ubadah ibn as-Samit. Ubadah rejected that statement and said he heard the Messenger of Allah صلى الله عليه وسلم say that Allah prescribed five prayers on His servants. Whoever offers them without losing any or treating them lightly has a promise from Allah to be admitted to Paradise. Whoever does not offer them has no such promise; Allah may punish him or admit him to Paradise. For searches like five daily prayers hadith, is Witr wajib, and prescribed prayers in Islam, this narration is direct and carefully worded."},"teachings":["The narration reports a dispute about calling Witr wajib.","Ubadah responds by citing the hadith about five prescribed prayers.","The hadith warns against losing prayers or treating their rights lightly.","It states a promise for preserving the five prayers and leaves the other case to Allah's will."],"related_hadiths":[{"id":"1419","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"990","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"754a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E237" s="4" t="n"/>
@@ -5932,7 +5936,7 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Prayer in Pairs and One Rak'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how night prayer is offered in pairs and how witr is completed with one rak'ah near the end of the night."},"heading":{"title":"Witr Prayer: Night Prayer in Pairs and One Rak'ah","description":"This hadith about witr prayer gives a simple answer to a direct question. A man from the desert asked the Prophet (صلى الله عليه وسلم) about night prayer. The reply showed that the night prayer is offered two by two, meaning in pairs. Then the Prophet (صلى الله عليه وسلم) explained that witr is one rak'ah toward the end of the night. The core lesson is clear: witr prayer has a special place at night, and it can close the night prayer with an odd rak'ah. For someone searching how to pray witr, this narration gives the basic shape without adding extra details. It keeps the matter easy and focused."},"teachings":["Night prayer is described as being prayed in pairs.","Witr may be one rak'ah near the end of the night.","A clear question about worship should be answered in a clear way."],"related_hadiths":[{"id":"1422","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1439","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Prayer in Pairs and One Rak'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how night prayer is offered in pairs and how witr is completed with one rak'ah near the end of the night."},"heading":{"title":"Witr Prayer: Night Prayer in Pairs and One Rak'ah","description":"This hadith about witr prayer gives a simple answer to a direct question. A man from the desert asked the Prophet (صلى الله عليه وسلم) about night prayer. The reply showed that the night prayer is offered two by two, meaning in pairs. Then the Prophet (صلى الله عليه وسلم) explained that witr is one rak'ah toward the end of the night. The core lesson is clear: witr prayer has a special place at night, and it can close the night prayer with an odd rak'ah. For someone searching how to pray witr, this narration gives the basic shape without adding extra details. It keeps the matter easy and focused."},"teachings":["Night prayer is described as being prayed in pairs.","Witr may be one rak'ah near the end of the night.","A clear question about worship should be answered in a clear way."],"related_hadiths":[{"id":"1422","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1439","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E238" s="4" t="n"/>
@@ -5955,7 +5959,7 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Prayer Options: Five, Three, or One","description":"$book_name$ $hadith_number$ - $chapter_name$. Understand the Prophet's teaching that witr is a right for Muslims and may be prayed as five, three, or one rak'ah."},"heading":{"title":"Witr Prayer: Five, Three, or One Rak'ah","description":"This hadith about witr prayer speaks about ease and choice within the wording of the narration. The Prophet (صلى الله عليه وسلم) said that witr is a right for every Muslim. He then mentioned different ways a person may observe it: five rak'ahs, three rak'ahs, or one rak'ah. The hadith does not make the matter hard for the listener. It shows that witr has value, while also allowing more than one number of rak'ahs. For people searching witr prayer rakats, this report answers the common question in a direct way. It teaches that a Muslim should not ignore witr, and should choose a form that he or she can keep with care."},"teachings":["Witr is described as a right for every Muslim.","The narration mentions five, three, and one rak'ah as options.","A person may choose a number of rak'ahs mentioned in the hadith."],"related_hadiths":[{"id":"1421","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1431","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1432","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Prayer Options: Five, Three, or One","description":"$book_name$ $hadith_number$ - $chapter_name$. Understand the Prophet's teaching that witr is a right for Muslims and may be prayed as five, three, or one rak'ah."},"heading":{"title":"Witr Prayer: Five, Three, or One Rak'ah","description":"This hadith about witr prayer speaks about ease and choice within the wording of the narration. The Prophet (صلى الله عليه وسلم) said that witr is a right for every Muslim. He then mentioned different ways a person may observe it: five rak'ahs, three rak'ahs, or one rak'ah. The hadith does not make the matter hard for the listener. It shows that witr has value, while also allowing more than one number of rak'ahs. For people searching witr prayer rakats, this report answers the common question in a direct way. It teaches that a Muslim should not ignore witr, and should choose a form that he or she can keep with care."},"teachings":["Witr is described as a right for every Muslim.","The narration mentions five, three, and one rak'ah as options.","A person may choose a number of rak'ahs mentioned in the hadith."],"related_hadiths":[{"id":"1421","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1431","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1432","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E239" s="4" t="n"/>
@@ -5978,7 +5982,7 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surahs Recited in Witr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. See the surahs the Messenger of Allah recited in witr: Al-A'la, Al-Kafirun, and Al-Ikhlas."},"heading":{"title":"Witr Prayer Surahs: What the Prophet Recited","description":"This hadith about witr prayer focuses on Qur'an recitation in witr. Ubayy ibn Ka'b reported that the Messenger of Allah (صلى الله عليه وسلم) used to observe witr while reciting Surah Al-A'la, Surah Al-Kafirun, and Surah Al-Ikhlas. The report gives a clear practice linked to witr prayer surahs. It does not discuss every possible recitation. It simply tells us what he used to recite in this narration. For someone searching which surah to read in witr, this hadith points to three short and well-known chapters. The message is easy: witr is not only an ending prayer of the night, but also a time for meaningful Qur'an recitation."},"teachings":["The Prophet (صلى الله عليه وسلم) recited named surahs in witr.","Surah Al-A'la, Al-Kafirun, and Al-Ikhlas are mentioned in this report.","Witr includes prayer and Qur'an recitation together."],"related_hadiths":[{"id":"1424","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1430","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1421","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surahs Recited in Witr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. See the surahs the Messenger of Allah recited in witr: Al-A'la, Al-Kafirun, and Al-Ikhlas."},"heading":{"title":"Witr Prayer Surahs: What the Prophet Recited","description":"This hadith about witr prayer focuses on Qur'an recitation in witr. Ubayy ibn Ka'b reported that the Messenger of Allah (صلى الله عليه وسلم) used to observe witr while reciting Surah Al-A'la, Surah Al-Kafirun, and Surah Al-Ikhlas. The report gives a clear practice linked to witr prayer surahs. It does not discuss every possible recitation. It simply tells us what he used to recite in this narration. For someone searching which surah to read in witr, this hadith points to three short and well-known chapters. The message is easy: witr is not only an ending prayer of the night, but also a time for meaningful Qur'an recitation."},"teachings":["The Prophet (صلى الله عليه وسلم) recited named surahs in witr.","Surah Al-A'la, Al-Kafirun, and Al-Ikhlas are mentioned in this report.","Witr includes prayer and Qur'an recitation together."],"related_hadiths":[{"id":"1424","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1430","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1421","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E240" s="4" t="n"/>
@@ -6001,7 +6005,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Surahs and the Mu'awwidhatayn","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reported the witr recitation, adding that the third rak'ah included Al-Ikhlas and the two refuge-seeking surahs."},"heading":{"title":"Witr Prayer Surahs: Al-Ikhlas and the Mu'awwidhatayn","description":"This hadith about witr prayer adds detail to the question of recitation. AbdulAziz ibn Jurayj asked Aishah, the mother of the believers, what the Messenger of Allah (صلى الله عليه وسلم) used to recite in witr. Her report matched the meaning of the narration from Ubayy ibn Ka'b, and this version adds that in the third rak'ah he would recite Surah Al-Ikhlas and the Mu'awwidhatayn, meaning Surah Al-Falaq and Surah An-Nas. The hadith is useful for people searching witr prayer surahs because it names the recitation clearly. It also shows the care of the Companions in asking about the Prophet's worship in detail."},"teachings":["Aishah was asked about the Prophet's recitation in witr.","The third rak'ah included Surah Al-Ikhlas and the two refuge-seeking surahs.","Learning prayer details through careful questions is shown in this narration."],"related_hadiths":[{"id":"1423","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1430","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1425","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witr Surahs and the Mu'awwidhatayn","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reported the witr recitation, adding that the third rak'ah included Al-Ikhlas and the two refuge-seeking surahs."},"heading":{"title":"Witr Prayer Surahs: Al-Ikhlas and the Mu'awwidhatayn","description":"This hadith about witr prayer adds detail to the question of recitation. AbdulAziz ibn Jurayj asked Aishah, the mother of the believers, what the Messenger of Allah (صلى الله عليه وسلم) used to recite in witr. Her report matched the meaning of the narration from Ubayy ibn Ka'b, and this version adds that in the third rak'ah he would recite Surah Al-Ikhlas and the Mu'awwidhatayn, meaning Surah Al-Falaq and Surah An-Nas. The hadith is useful for people searching witr prayer surahs because it names the recitation clearly. It also shows the care of the Companions in asking about the Prophet's worship in detail."},"teachings":["Aishah was asked about the Prophet's recitation in witr.","The third rak'ah included Surah Al-Ikhlas and the two refuge-seeking surahs.","Learning prayer details through careful questions is shown in this narration."],"related_hadiths":[{"id":"1423","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1430","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1425","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E241" s="4" t="n"/>
@@ -6024,7 +6028,7 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Qunut in Witr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the supplication taught for witr, asking Allah for guidance, safety, blessing, protection, and His care."},"heading":{"title":"Dua Qunut in Witr: Guidance, Safety, and Blessing","description":"This hadith about dua qunut in witr gives the exact words taught by the Messenger of Allah (صلى الله عليه وسلم) to Al-Hasan ibn Ali. The supplication asks Allah for guidance among those He has guided, security among those He has granted security, care among those He has taken into His care, blessing in what He has given, and protection from the evil of what He has decreed. It also affirms that Allah decrees and none decrees over Him. For someone searching dua qunut witr, this narration is central because it gives the prayer text itself. The tone of the dua is humble, needy, and full of trust in Allah."},"teachings":["The Prophet (صلى الله عليه وسلم) taught specific words for witr supplication.","The dua asks Allah for guidance, safety, care, blessing, and protection.","The supplication ends by praising Allah as blessed and exalted."],"related_hadiths":[{"id":"1426","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1427","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1428","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Qunut in Witr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the supplication taught for witr, asking Allah for guidance, safety, blessing, protection, and His care."},"heading":{"title":"Dua Qunut in Witr: Guidance, Safety, and Blessing","description":"This hadith about dua qunut in witr gives the exact words taught by the Messenger of Allah (صلى الله عليه وسلم) to Al-Hasan ibn Ali. The supplication asks Allah for guidance among those He has guided, security among those He has granted security, care among those He has taken into His care, blessing in what He has given, and protection from the evil of what He has decreed. It also affirms that Allah decrees and none decrees over Him. For someone searching dua qunut witr, this narration is central because it gives the prayer text itself. The tone of the dua is humble, needy, and full of trust in Allah."},"teachings":["The Prophet (صلى الله عليه وسلم) taught specific words for witr supplication.","The dua asks Allah for guidance, safety, care, blessing, and protection.","The supplication ends by praising Allah as blessed and exalted."],"related_hadiths":[{"id":"1426","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1427","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1428","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E242" s="4" t="n"/>
@@ -6047,7 +6051,7 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Another Report on Dua Qunut in Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. This report transmits the same witr supplication wording and notes a wording difference about saying it in qunut."},"heading":{"title":"Qunut Witr Hadith: Same Meaning with a Wording Note","description":"This hadith is linked to the dua qunut in witr taught in the previous report. It says that Abu Ishaq transmitted the same tradition with the same chain and meaning. The ending has a wording note: the version says he would recite the supplication of the witr, and it does not mention the words, I say them in the witr. Abu Dawud also notes the name of Abu al-Hawra' as Rabi'ah ibn Shaiban. The main point for readers searching qunut witr hadith is that this report preserves the same meaning while pointing out a small wording difference. It shows how hadith reports may note exact wording with care."},"teachings":["The report carries the same meaning as the witr supplication narration.","A wording difference is noted about saying the supplication in witr qunut.","Abu Dawud identifies Abu al-Hawra' by name."],"related_hadiths":[{"id":"1425","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1427","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1429","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Another Report on Dua Qunut in Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. This report transmits the same witr supplication wording and notes a wording difference about saying it in qunut."},"heading":{"title":"Qunut Witr Hadith: Same Meaning with a Wording Note","description":"This hadith is linked to the dua qunut in witr taught in the previous report. It says that Abu Ishaq transmitted the same tradition with the same chain and meaning. The ending has a wording note: the version says he would recite the supplication of the witr, and it does not mention the words, I say them in the witr. Abu Dawud also notes the name of Abu al-Hawra' as Rabi'ah ibn Shaiban. The main point for readers searching qunut witr hadith is that this report preserves the same meaning while pointing out a small wording difference. It shows how hadith reports may note exact wording with care."},"teachings":["The report carries the same meaning as the witr supplication narration.","A wording difference is noted about saying the supplication in witr qunut.","Abu Dawud identifies Abu al-Hawra' by name."],"related_hadiths":[{"id":"1425","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1427","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1429","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E243" s="4" t="n"/>
@@ -6070,7 +6074,7 @@
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Refuge at the End of Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the Prophet's supplication at the end of witr, seeking Allah's pleasure, forgiveness, mercy, and true praise."},"heading":{"title":"Witr Dua: Seeking Allah's Pleasure and Forgiveness","description":"This hadith about witr dua reports words the Messenger of Allah (صلى الله عليه وسلم) used to say at the end of his witr. The supplication seeks refuge in Allah's good pleasure from His anger, in His forgiveness from His punishment, and with Him from Him. It ends with a humble statement that no one can fully count the praise due to Allah, and that He is as He praised Himself. The report also includes Abu Dawud's notes about chains and mention of qunut before bowing in some reports. For a reader searching end of witr dua, the main teaching in the text is deep dependence on Allah and careful praise of Him."},"teachings":["The supplication seeks Allah's pleasure, forgiveness, and mercy.","The wording admits that Allah's praise cannot be fully counted by the servant.","The report includes hadith notes about qunut and its transmission."],"related_hadiths":[{"id":"1425","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1426","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1428","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Refuge at the End of Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the Prophet's supplication at the end of witr, seeking Allah's pleasure, forgiveness, mercy, and true praise."},"heading":{"title":"Witr Dua: Seeking Allah's Pleasure and Forgiveness","description":"This hadith about witr dua reports words the Messenger of Allah (صلى الله عليه وسلم) used to say at the end of his witr. The supplication seeks refuge in Allah's good pleasure from His anger, in His forgiveness from His punishment, and with Him from Him. It ends with a humble statement that no one can fully count the praise due to Allah, and that He is as He praised Himself. The report also includes Abu Dawud's notes about chains and mention of qunut before bowing in some reports. For a reader searching end of witr dua, the main teaching in the text is deep dependence on Allah and careful praise of Him."},"teachings":["The supplication seeks Allah's pleasure, forgiveness, and mercy.","The wording admits that Allah's praise cannot be fully counted by the servant.","The report includes hadith notes about qunut and its transmission."],"related_hadiths":[{"id":"1425","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1426","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1428","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E244" s="4" t="n"/>
@@ -6093,7 +6097,7 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut in the Second Half of Ramadan","description":"$book_name$ $hadith_number$ - $chapter_name$. Ubayy ibn Ka'b led prayer in Ramadan and recited the witr supplication during the second half of the month."},"heading":{"title":"Ramadan Qunut: Witr Supplication in the Second Half","description":"This hadith about Ramadan qunut reports that Ubayy ibn Ka'b led people in prayer during Ramadan. The narration says he used to recite the supplication in witr during the second half of Ramadan. The text is short, but it gives a clear practice connected to Ramadan night prayer and witr. It does not say that he recited it every night of the month. It states the second half. For someone searching qunut in Ramadan witr, this report is useful because it ties the practice to a named Companion and to a clear part of the month. The lesson is to report worship details exactly as they are given."},"teachings":["Ubayy ibn Ka'b led people in prayer during Ramadan.","The supplication in witr is mentioned for the second half of Ramadan.","The narration keeps the timing specific and does not expand beyond it."],"related_hadiths":[{"id":"1429","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1425","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1427","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut in the Second Half of Ramadan","description":"$book_name$ $hadith_number$ - $chapter_name$. Ubayy ibn Ka'b led prayer in Ramadan and recited the witr supplication during the second half of the month."},"heading":{"title":"Ramadan Qunut: Witr Supplication in the Second Half","description":"This hadith about Ramadan qunut reports that Ubayy ibn Ka'b led people in prayer during Ramadan. The narration says he used to recite the supplication in witr during the second half of Ramadan. The text is short, but it gives a clear practice connected to Ramadan night prayer and witr. It does not say that he recited it every night of the month. It states the second half. For someone searching qunut in Ramadan witr, this report is useful because it ties the practice to a named Companion and to a clear part of the month. The lesson is to report worship details exactly as they are given."},"teachings":["Ubayy ibn Ka'b led people in prayer during Ramadan.","The supplication in witr is mentioned for the second half of Ramadan.","The narration keeps the timing specific and does not expand beyond it."],"related_hadiths":[{"id":"1429","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1425","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1427","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E245" s="4" t="n"/>
@@ -6116,7 +6120,7 @@
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ubayy ibn Ka'b and Qunut in Ramadan","description":"$book_name$ $hadith_number$ - $chapter_name$. Umar gathered people behind Ubayy for Ramadan prayer; qunut was recited only in the remaining half, with notes from Abu Dawud."},"heading":{"title":"Ramadan Qunut Hadith: Ubayy ibn Ka'b Leading Prayer","description":"This hadith about Ramadan qunut describes Umar ibn al-Khattab gathering the people behind Ubayy ibn Ka'b for prayer. Ubayy led them for twenty nights in Ramadan and did not recite qunut except in the remaining half. When the last ten days came, he stayed away from them and prayed in his house, and people said that Ubayy had run away. Abu Dawud then comments that these reports show weakness in a report saying the Prophet (صلى الله عليه وسلم) recited qunut in witr. The hadith is useful for people searching tarawih witr qunut because it gives a careful report, including timing and the compiler's note."},"teachings":["Umar gathered people behind Ubayy ibn Ka'b for Ramadan prayer.","Ubayy recited qunut only in the remaining half of Ramadan.","The narration includes Abu Dawud's note about weakness in another report."],"related_hadiths":[{"id":"1428","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1427","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1439","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ubayy ibn Ka'b and Qunut in Ramadan","description":"$book_name$ $hadith_number$ - $chapter_name$. Umar gathered people behind Ubayy for Ramadan prayer; qunut was recited only in the remaining half, with notes from Abu Dawud."},"heading":{"title":"Ramadan Qunut Hadith: Ubayy ibn Ka'b Leading Prayer","description":"This hadith about Ramadan qunut describes Umar ibn al-Khattab gathering the people behind Ubayy ibn Ka'b for prayer. Ubayy led them for twenty nights in Ramadan and did not recite qunut except in the remaining half. When the last ten days came, he stayed away from them and prayed in his house, and people said that Ubayy had run away. Abu Dawud then comments that these reports show weakness in a report saying the Prophet (صلى الله عليه وسلم) recited qunut in witr. The hadith is useful for people searching tarawih witr qunut because it gives a careful report, including timing and the compiler's note."},"teachings":["Umar gathered people behind Ubayy ibn Ka'b for Ramadan prayer.","Ubayy recited qunut only in the remaining half of Ramadan.","The narration includes Abu Dawud's note about weakness in another report."],"related_hadiths":[{"id":"1428","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1427","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1439","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E246" s="4" t="n"/>
@@ -6139,7 +6143,7 @@
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Laqit ibn Sabirah Narration Variant","description":"$book_name$ $hadith_number$ - $chapter_name$. This report preserves a close wording of Laqit’s narration, noting the Prophet’s arrival and a dish-name variant."},"heading":{"title":"Laqit ibn Sabirah Hadith: Careful Reporting of the Sunnah","description":"This narration is a shorter version connected to the report of Laqit ibn Sabirah. It says he was the leader of Banu’l-Muntafiq, came to Aisha, and narrated the tradition in a similar way. This version also mentions that the Prophet (صلى الله عليه وسلم) came shortly, walking with rapid forward steps. It then notes a wording difference: the dish is called asidah in this version instead of Khazirah. The core topic here is careful hadith reporting. For readers searching Laqit ibn Sabirah hadith or Banu al-Muntafiq delegation hadith, this text shows how narrators preserved both the meaning and small wording details. It does not add a new ruling by itself in the translation, but it supports the earlier report by recording how the same event was transmitted with a small difference in wording."},"teachings":["Hadith narrators preserved small wording details.","A shorter version may support a longer report without repeating every point.","The text notes a difference between asidah and Khazirah.","Careful reporting helps readers see how the narration was transmitted."],"related_hadiths":[{"id":"135","book_id":"4","label":"Sunan Abu Dawud"},{"id":"191","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Laqit ibn Sabirah Narration Variant","description":"$book_name$ $hadith_number$ - $chapter_name$. This report preserves a close wording of Laqit’s narration, noting the Prophet’s arrival and a dish-name variant."},"heading":{"title":"Laqit ibn Sabirah Hadith: Careful Reporting of the Sunnah","description":"This narration is a shorter version connected to the report of Laqit ibn Sabirah. It says he was the leader of Banu’l-Muntafiq, came to Aisha, and narrated the tradition in a similar way. This version also mentions that the Prophet (صلى الله عليه وسلم) came shortly, walking with rapid forward steps. It then notes a wording difference: the dish is called asidah in this version instead of Khazirah. The core topic here is careful hadith reporting. For readers searching Laqit ibn Sabirah hadith or Banu al-Muntafiq delegation hadith, this text shows how narrators preserved both the meaning and small wording details. It does not add a new ruling by itself in the translation, but it supports the earlier report by recording how the same event was transmitted with a small difference in wording."},"teachings":["Hadith narrators preserved small wording details.","A shorter version may support a longer report without repeating every point.","The text notes a difference between asidah and Khazirah.","Careful reporting helps readers see how the narration was transmitted."],"related_hadiths":[{"id":"135","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"191","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E247" s="4" t="n"/>
@@ -6162,7 +6166,7 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr After Witr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the phrase the Prophet said after salutation in witr: Glory be to the King, the Most Holy."},"heading":{"title":"Dhikr After Witr: Glory Be to the King, the Most Holy","description":"This hadith about dhikr after witr gives a short phrase said by the Messenger of Allah (صلى الله عليه وسلم) after offering salutation in the witr prayer. Ubayy ibn Ka'b reported that when the Prophet (صلى الله عليه وسلم) finished witr, he said: Glory be to the King, the Most Holy. The teaching is brief and easy to remember. It connects the end of witr with praise of Allah as King and Most Holy. For people searching what to say after witr prayer, this narration gives a direct answer from the text. It also shows that worship does not end with movement only; the tongue also remembers and glorifies Allah."},"teachings":["The Prophet (صلى الله عليه وسلم) said a phrase of glorification after witr.","The wording praises Allah as the King and the Most Holy.","A short dhikr can be linked to the end of a prayer."],"related_hadiths":[{"id":"1423","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1424","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr After Witr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the phrase the Prophet said after salutation in witr: Glory be to the King, the Most Holy."},"heading":{"title":"Dhikr After Witr: Glory Be to the King, the Most Holy","description":"This hadith about dhikr after witr gives a short phrase said by the Messenger of Allah (صلى الله عليه وسلم) after offering salutation in the witr prayer. Ubayy ibn Ka'b reported that when the Prophet (صلى الله عليه وسلم) finished witr, he said: Glory be to the King, the Most Holy. The teaching is brief and easy to remember. It connects the end of witr with praise of Allah as King and Most Holy. For people searching what to say after witr prayer, this narration gives a direct answer from the text. It also shows that worship does not end with movement only; the tongue also remembers and glorifies Allah."},"teachings":["The Prophet (صلى الله عليه وسلم) said a phrase of glorification after witr.","The wording praises Allah as the King and the Most Holy.","A short dhikr can be linked to the end of a prayer."],"related_hadiths":[{"id":"1423","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1424","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E248" s="4" t="n"/>
@@ -6185,7 +6189,7 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying Witr After Sleep or Forgetfulness","description":"$book_name$ $hadith_number$ - $chapter_name$. If someone sleeps through witr or forgets it, the Prophet taught that the person should pray it when remembered."},"heading":{"title":"Missed Witr Prayer: Pray It When You Remember","description":"This hadith about missed witr prayer gives comfort and direction. Abu Sa'id al-Khudri reported that the Prophet (صلى الله عليه وسلم) said if anyone oversleeps and misses witr, or forgets it, he should pray when he remembers. The wording deals with two common human cases: sleep and forgetfulness. It does not shame the person. It tells the person what to do next. For someone searching what if I miss witr, this narration gives a clear action: pray it when it comes back to mind. The lesson is that worship should be treated with care, and a missed act should not simply be ignored when remembered."},"teachings":["Sleep and forgetfulness are both mentioned as reasons for missing witr.","The person is told to pray witr when he remembers.","The hadith points to care for witr even after a missed time."],"related_hadiths":[{"id":"1432","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1436","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Praying Witr After Sleep or Forgetfulness","description":"$book_name$ $hadith_number$ - $chapter_name$. If someone sleeps through witr or forgets it, the Prophet taught that the person should pray it when remembered."},"heading":{"title":"Missed Witr Prayer: Pray It When You Remember","description":"This hadith about missed witr prayer gives comfort and direction. Abu Sa'id al-Khudri reported that the Prophet (صلى الله عليه وسلم) said if anyone oversleeps and misses witr, or forgets it, he should pray when he remembers. The wording deals with two common human cases: sleep and forgetfulness. It does not shame the person. It tells the person what to do next. For someone searching what if I miss witr, this narration gives a clear action: pray it when it comes back to mind. The lesson is that worship should be treated with care, and a missed act should not simply be ignored when remembered."},"teachings":["Sleep and forgetfulness are both mentioned as reasons for missing witr.","The person is told to pray witr when he remembers.","The hadith points to care for witr even after a missed time."],"related_hadiths":[{"id":"1432","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1436","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E249" s="4" t="n"/>
@@ -6208,7 +6212,7 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Practices: Duha, Monthly Fasting, and Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah was advised to keep three practices at home and while traveling: Duha, three monthly fasts, and witr before sleep."},"heading":{"title":"Witr Before Sleep and Three Steady Acts of Worship","description":"This hadith about witr before sleep reports advice given to Abu Hurairah by his close friend, meaning the Prophet (صلى الله عليه وسلم). He instructed him to keep three practices while traveling and while resident: praying two rak'ahs in the forenoon, fasting three days every month, and not sleeping except after observing witr. The report brings together prayer, fasting, and a bedtime worship habit. For people searching witr before sleeping hadith, this narration shows that Abu Hurairah treated this advice as something he did not leave. The text also reminds us that worship can be kept in simple, steady actions during travel and at home."},"teachings":["Abu Hurairah was advised to keep three practices.","The practices were for both travel and residence.","Witr before sleep is named as one of the advised acts."],"related_hadiths":[{"id":"1433","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1431","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1434","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Practices: Duha, Monthly Fasting, and Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah was advised to keep three practices at home and while traveling: Duha, three monthly fasts, and witr before sleep."},"heading":{"title":"Witr Before Sleep and Three Steady Acts of Worship","description":"This hadith about witr before sleep reports advice given to Abu Hurairah by his close friend, meaning the Prophet (صلى الله عليه وسلم). He instructed him to keep three practices while traveling and while resident: praying two rak'ahs in the forenoon, fasting three days every month, and not sleeping except after observing witr. The report brings together prayer, fasting, and a bedtime worship habit. For people searching witr before sleeping hadith, this narration shows that Abu Hurairah treated this advice as something he did not leave. The text also reminds us that worship can be kept in simple, steady actions during travel and at home."},"teachings":["Abu Hurairah was advised to keep three practices.","The practices were for both travel and residence.","Witr before sleep is named as one of the advised acts."],"related_hadiths":[{"id":"1433","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1431","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1434","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E250" s="4" t="n"/>
@@ -6231,7 +6235,7 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Practices Taught to Abu Al-Darda'","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Al-Darda' was instructed to keep monthly fasting, witr before sleep, and Duha prayer while traveling and at home."},"heading":{"title":"Three Steady Acts: Fasting, Witr, and Duha Prayer","description":"This hadith about daily worship reports Abu Al-Darda' saying that his close friend, the Prophet (صلى الله عليه وسلم), instructed him to keep three practices. He was told to fast three days every month, not to sleep except after witr, and to observe the forenoon voluntary prayer while resident and while traveling. The wording is close to another report from Abu Hurairah, but this narration is from Abu Al-Darda'. For people searching hadith about three days fasting and witr, this text brings the practices together in one short plan. It shows worship that can fit normal life: a monthly fast, a prayer before sleep, and Duha prayer."},"teachings":["Abu Al-Darda' was advised to keep three practices.","Monthly fasting, witr before sleep, and Duha prayer are mentioned.","The forenoon prayer is mentioned for both travel and residence."],"related_hadiths":[{"id":"1432","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1431","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1434","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Practices Taught to Abu Al-Darda'","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Al-Darda' was instructed to keep monthly fasting, witr before sleep, and Duha prayer while traveling and at home."},"heading":{"title":"Three Steady Acts: Fasting, Witr, and Duha Prayer","description":"This hadith about daily worship reports Abu Al-Darda' saying that his close friend, the Prophet (صلى الله عليه وسلم), instructed him to keep three practices. He was told to fast three days every month, not to sleep except after witr, and to observe the forenoon voluntary prayer while resident and while traveling. The wording is close to another report from Abu Hurairah, but this narration is from Abu Al-Darda'. For people searching hadith about three days fasting and witr, this text brings the practices together in one short plan. It shows worship that can fit normal life: a monthly fast, a prayer before sleep, and Duha prayer."},"teachings":["Abu Al-Darda' was advised to keep three practices.","Monthly fasting, witr before sleep, and Duha prayer are mentioned.","The forenoon prayer is mentioned for both travel and residence."],"related_hadiths":[{"id":"1432","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1431","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1434","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E251" s="4" t="n"/>
@@ -6254,7 +6258,7 @@
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Early or Late Witr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet heard Abu Bakr pray witr early and Umar pray it late, then praised each approach with fitting words."},"heading":{"title":"Best Time for Witr Prayer: Early Care and Late Strength","description":"This hadith about the time for witr prayer shows two different habits. The Prophet (صلى الله عليه وسلم) asked Abu Bakr when he observed witr, and he said he prayed it in the early hours of the night. Then he asked Umar, who said he prayed it at the end of the night. The Prophet (صلى الله عليه وسلم) said about Abu Bakr that he had taken it with care, and about Umar that he had taken it with strength. The text does not force one single timing in this report. It shows that early witr can be linked with caution, while late witr can be linked with strength. This helps people searching best time for witr prayer understand the wording of this hadith."},"teachings":["Abu Bakr prayed witr in the early part of the night.","Umar prayed witr at the end of the night.","The Prophet (صلى الله عليه وسلم) responded to each with praise suited to his choice."],"related_hadiths":[{"id":"1435","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1436","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Early or Late Witr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet heard Abu Bakr pray witr early and Umar pray it late, then praised each approach with fitting words."},"heading":{"title":"Best Time for Witr Prayer: Early Care and Late Strength","description":"This hadith about the time for witr prayer shows two different habits. The Prophet (صلى الله عليه وسلم) asked Abu Bakr when he observed witr, and he said he prayed it in the early hours of the night. Then he asked Umar, who said he prayed it at the end of the night. The Prophet (صلى الله عليه وسلم) said about Abu Bakr that he had taken it with care, and about Umar that he had taken it with strength. The text does not force one single timing in this report. It shows that early witr can be linked with caution, while late witr can be linked with strength. This helps people searching best time for witr prayer understand the wording of this hadith."},"teachings":["Abu Bakr prayed witr in the early part of the night.","Umar prayed witr at the end of the night.","The Prophet (صلى الله عليه وسلم) responded to each with praise suited to his choice."],"related_hadiths":[{"id":"1435","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1436","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E252" s="4" t="n"/>
@@ -6277,7 +6281,7 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Witr at Different Times","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reported that the Prophet prayed witr early, middle, and late, and near dawn toward the end of his life."},"heading":{"title":"Witr Prayer Time: Early Night, Midnight, or Before Dawn","description":"This hadith about witr prayer time comes from Aishah through Masruq. When he asked when the Messenger of Allah (صلى الله عليه وسلم) observed witr, she answered that he did all of that: sometimes in the early hours of the night, sometimes at midnight, and sometimes toward the end of it. She then said that his witr, when he died, had reached the time just before dawn. For someone searching when did the Prophet pray witr, this narration gives a broad answer from the text. It shows that witr was observed at different times, while also noting the final practice mentioned by Aishah."},"teachings":["The Prophet (صلى الله عليه وسلم) prayed witr at different times of the night.","Aishah mentioned early night, middle night, and the end of the night.","She said his witr near the time of death was just before dawn."],"related_hadiths":[{"id":"1434","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1436","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Witr at Different Times","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reported that the Prophet prayed witr early, middle, and late, and near dawn toward the end of his life."},"heading":{"title":"Witr Prayer Time: Early Night, Midnight, or Before Dawn","description":"This hadith about witr prayer time comes from Aishah through Masruq. When he asked when the Messenger of Allah (صلى الله عليه وسلم) observed witr, she answered that he did all of that: sometimes in the early hours of the night, sometimes at midnight, and sometimes toward the end of it. She then said that his witr, when he died, had reached the time just before dawn. For someone searching when did the Prophet pray witr, this narration gives a broad answer from the text. It shows that witr was observed at different times, while also noting the final practice mentioned by Aishah."},"teachings":["The Prophet (صلى الله عليه وسلم) prayed witr at different times of the night.","Aishah mentioned early night, middle night, and the end of the night.","She said his witr near the time of death was just before dawn."],"related_hadiths":[{"id":"1434","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1436","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E253" s="4" t="n"/>
@@ -6300,7 +6304,7 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray Witr Before Morning","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet instructed believers to make haste with witr before morning arrives."},"heading":{"title":"Witr Before Fajr: Make Haste Before Morning","description":"This hadith about witr before Fajr is short and direct. Ibn Umar reported that the Prophet (صلى الله عليه وسلم) said to make haste to observe the witr prayer before morning. The wording points to attention and timing. Witr belongs to the night, so the listener is urged not to delay it until morning comes. For someone searching can I pray witr before Fajr, this narration is often found because it speaks about doing witr before morning. The hadith does not discuss every case of missing witr; it simply tells people to be quick with witr before the morning enters. Its message is simple: do not be careless with the end of the night prayer."},"teachings":["The Prophet (صلى الله عليه وسلم) told people to hasten with witr before morning.","The hadith links witr to the night before morning arrives.","It teaches care in timing the witr prayer."],"related_hadiths":[{"id":"1435","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1431","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Pray Witr Before Morning","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet instructed believers to make haste with witr before morning arrives."},"heading":{"title":"Witr Before Fajr: Make Haste Before Morning","description":"This hadith about witr before Fajr is short and direct. Ibn Umar reported that the Prophet (صلى الله عليه وسلم) said to make haste to observe the witr prayer before morning. The wording points to attention and timing. Witr belongs to the night, so the listener is urged not to delay it until morning comes. For someone searching can I pray witr before Fajr, this narration is often found because it speaks about doing witr before morning. The hadith does not discuss every case of missing witr; it simply tells people to be quick with witr before the morning enters. Its message is simple: do not be careless with the end of the night prayer."},"teachings":["The Prophet (صلى الله عليه وسلم) told people to hasten with witr before morning.","The hadith links witr to the night before morning arrives.","It teaches care in timing the witr prayer."],"related_hadiths":[{"id":"1435","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1431","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E254" s="4" t="n"/>
@@ -6323,7 +6327,7 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Quiet and Loud Recitation in Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reported that the Prophet sometimes prayed witr early or late, recited quietly or loudly, and slept after ghusl or ablution."},"heading":{"title":"Witr Practice: Timing, Recitation, and Sleep","description":"This hadith about the Prophet's witr practice gives several details from Aishah. She was asked about his witr and said that he sometimes observed it in the early part of the night and sometimes at the end. When asked about Qur'an recitation, she said he sometimes recited quietly and sometimes loudly. She also mentioned that sometimes he took a bath and slept, and sometimes he performed ablution and slept. Abu Dawud notes that other narrators understood the bath to refer to sexual defilement. For readers searching quiet or loud recitation in witr, this hadith shows more than one practice within the report."},"teachings":["Aishah mentioned both early and late witr in the Prophet's practice.","His recitation was sometimes quiet and sometimes loud.","The report also mentions sleep after ghusl or after ablution."],"related_hadiths":[{"id":"1435","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1434","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Quiet and Loud Recitation in Witr","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reported that the Prophet sometimes prayed witr early or late, recited quietly or loudly, and slept after ghusl or ablution."},"heading":{"title":"Witr Practice: Timing, Recitation, and Sleep","description":"This hadith about the Prophet's witr practice gives several details from Aishah. She was asked about his witr and said that he sometimes observed it in the early part of the night and sometimes at the end. When asked about Qur'an recitation, she said he sometimes recited quietly and sometimes loudly. She also mentioned that sometimes he took a bath and slept, and sometimes he performed ablution and slept. Abu Dawud notes that other narrators understood the bath to refer to sexual defilement. For readers searching quiet or loud recitation in witr, this hadith shows more than one practice within the report."},"teachings":["Aishah mentioned both early and late witr in the Prophet's practice.","His recitation was sometimes quiet and sometimes loud.","The report also mentions sleep after ghusl or after ablution."],"related_hadiths":[{"id":"1435","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1434","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1438","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E255" s="4" t="n"/>
@@ -6346,7 +6350,7 @@
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Make Witr the Last Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that the last prayer of the night should be witr."},"heading":{"title":"Witr Prayer: Make It the Last Prayer at Night","description":"This hadith about witr prayer gives a clear instruction from the Prophet (صلى الله عليه وسلم): make the last of your prayer at night a witr. The meaning in the text is simple. After praying at night, the closing prayer should be witr, which is odd-numbered. This hadith is one of the common search results for people asking should witr be the last prayer. It does not discuss every later situation in this wording. It gives the main order for the night prayer: end it with witr. The teaching helps a worshipper plan the night in a neat way, so the final prayer before sleep or before dawn is witr."},"teachings":["The last prayer at night is instructed to be witr.","The hadith gives a simple order for closing night prayer.","It connects witr with the end of the night's worship."],"related_hadiths":[{"id":"1436","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1435","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1439","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Make Witr the Last Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that the last prayer of the night should be witr."},"heading":{"title":"Witr Prayer: Make It the Last Prayer at Night","description":"This hadith about witr prayer gives a clear instruction from the Prophet (صلى الله عليه وسلم): make the last of your prayer at night a witr. The meaning in the text is simple. After praying at night, the closing prayer should be witr, which is odd-numbered. This hadith is one of the common search results for people asking should witr be the last prayer. It does not discuss every later situation in this wording. It gives the main order for the night prayer: end it with witr. The teaching helps a worshipper plan the night in a neat way, so the final prayer before sleep or before dawn is witr."},"teachings":["The last prayer at night is instructed to be witr.","The hadith gives a simple order for closing night prayer.","It connects witr with the end of the night's worship."],"related_hadiths":[{"id":"1436","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1435","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1439","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E256" s="4" t="n"/>
@@ -6369,7 +6373,7 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Two Witrs in One Night","description":"$book_name$ $hadith_number$ - $chapter_name$. Talq ibn Ali reported the Prophet's teaching that there are no two witr prayers in one night."},"heading":{"title":"No Two Witrs in One Night: A Clear Witr Hadith","description":"This hadith about no two witrs in one night gives a practical example. Talq ibn Ali led people in witr during Ramadan, then went to his own mosque and led them in prayer. When the witr remained, he put another man forward and told him to lead the people in witr. Talq explained that he heard the Messenger of Allah (صلى الله عليه وسلم) say there are no two witrs during one night. For someone searching can I pray witr twice, this narration gives the answer in plain wording. It also shows Talq acting according to what he had heard, avoiding a second witr for himself while still helping others pray."},"teachings":["Talq ibn Ali avoided praying witr twice in one night.","He put another man forward to lead the second group's witr.","The Prophet's wording says there are no two witrs during one night."],"related_hadiths":[{"id":"1438","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1421","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1422","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Two Witrs in One Night","description":"$book_name$ $hadith_number$ - $chapter_name$. Talq ibn Ali reported the Prophet's teaching that there are no two witr prayers in one night."},"heading":{"title":"No Two Witrs in One Night: A Clear Witr Hadith","description":"This hadith about no two witrs in one night gives a practical example. Talq ibn Ali led people in witr during Ramadan, then went to his own mosque and led them in prayer. When the witr remained, he put another man forward and told him to lead the people in witr. Talq explained that he heard the Messenger of Allah (صلى الله عليه وسلم) say there are no two witrs during one night. For someone searching can I pray witr twice, this narration gives the answer in plain wording. It also shows Talq acting according to what he had heard, avoiding a second witr for himself while still helping others pray."},"teachings":["Talq ibn Ali avoided praying witr twice in one night.","He put another man forward to lead the second group's witr.","The Prophet's wording says there are no two witrs during one night."],"related_hadiths":[{"id":"1438","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1421","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1422","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E257" s="4" t="n"/>
@@ -6392,7 +6396,7 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut in the Last Rak'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah described praying like the Prophet and reciting qunut in the last rak'ah of noon, night, and dawn prayers."},"heading":{"title":"Qunut in Prayer: Supplication in the Last Rak'ah","description":"This hadith about qunut in prayer reports Abu Hurairah saying by Allah that he would offer prayer like that of the Messenger of Allah (صلى الله عليه وسلم). The narrator then says Abu Hurairah used to recite the supplication in the last rak'ah of the noon prayer, the night prayer, and the dawn prayer. He would supplicate for the believers and curse the disbelievers. The report is specific about the prayers named and the last rak'ah. For readers searching qunut in prayer hadith, this narration should be read as it stands, without adding other prayer times or extra details. Its focus is supplication within prayer and concern for the believers."},"teachings":["Abu Hurairah aimed to pray like the Messenger of Allah (صلى الله عليه وسلم).","Qunut is mentioned in the last rak'ah of noon, night, and dawn prayers.","His supplication included prayer for the believers."],"related_hadiths":[{"id":"1425","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1427","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1428","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut in the Last Rak'ah","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah described praying like the Prophet and reciting qunut in the last rak'ah of noon, night, and dawn prayers."},"heading":{"title":"Qunut in Prayer: Supplication in the Last Rak'ah","description":"This hadith about qunut in prayer reports Abu Hurairah saying by Allah that he would offer prayer like that of the Messenger of Allah (صلى الله عليه وسلم). The narrator then says Abu Hurairah used to recite the supplication in the last rak'ah of the noon prayer, the night prayer, and the dawn prayer. He would supplicate for the believers and curse the disbelievers. The report is specific about the prayers named and the last rak'ah. For readers searching qunut in prayer hadith, this narration should be read as it stands, without adding other prayer times or extra details. Its focus is supplication within prayer and concern for the believers."},"teachings":["Abu Hurairah aimed to pray like the Messenger of Allah (صلى الله عليه وسلم).","Qunut is mentioned in the last rak'ah of noon, night, and dawn prayers.","His supplication included prayer for the believers."],"related_hadiths":[{"id":"1425","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1427","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1428","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E258" s="4" t="n"/>
@@ -6415,7 +6419,7 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut in Fajr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited Qunut in Fajr, with one report also naming Maghrib."},"heading":{"title":"Qunut in Fajr Prayer: A Clear Hadith on Supplication in Salah","description":"This Hadith about Qunut in Fajr prayer shows a simple report from Al-Bara'. He said the Prophet صلى الله عليه وسلم used to recite the supplication in the dawn prayer. The wording is short, but the message is focused: Qunut is a form of dua made inside Salah. The report also notes a version from Ibn Mu'adh that adds the sunset prayer, Maghrib. So the Hadith points to Qunut supplication in prayer without adding extra details beyond the text. For readers searching for dua Qunut in Fajr or Qunut in Salah, this narration highlights that the Prophet صلى الله عليه وسلم made this supplication in a named prayer, and another version mentions an added prayer as well."},"teachings":["Qunut is a supplication made within Salah.","The dawn prayer is clearly mentioned in this report.","One narrated version also mentions Maghrib prayer.","Hadith wording should be read carefully when versions differ."],"related_hadiths":[{"id":"1001","book_id":"1","label":"Sahih Bukhari"},{"id":"1003","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut in Fajr Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited Qunut in Fajr, with one report also naming Maghrib."},"heading":{"title":"Qunut in Fajr Prayer: A Clear Hadith on Supplication in Salah","description":"This Hadith about Qunut in Fajr prayer shows a simple report from Al-Bara'. He said the Prophet صلى الله عليه وسلم used to recite the supplication in the dawn prayer. The wording is short, but the message is focused: Qunut is a form of dua made inside Salah. The report also notes a version from Ibn Mu'adh that adds the sunset prayer, Maghrib. So the Hadith points to Qunut supplication in prayer without adding extra details beyond the text. For readers searching for dua Qunut in Fajr or Qunut in Salah, this narration highlights that the Prophet صلى الله عليه وسلم made this supplication in a named prayer, and another version mentions an added prayer as well."},"teachings":["Qunut is a supplication made within Salah.","The dawn prayer is clearly mentioned in this report.","One narrated version also mentions Maghrib prayer.","Hadith wording should be read carefully when versions differ."],"related_hadiths":[{"id":"1001","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1003","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E259" s="4" t="n"/>
@@ -6438,7 +6442,7 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut for the Weak Believers","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet made Qunut for a month, asking Allah to rescue named weak believers."},"heading":{"title":"Qunut Dua for the Weak Believers in Night Prayer","description":"This Hadith about Qunut dua shows the Prophet صلى الله عليه وسلم making a clear supplication in the night prayer for one month. He asked Allah to rescue al-Walid b. al-Walid, Salamah b. Hisham, and the weak believers. The Hadith also records his words against Mudar, including a request for a famine like that of Joseph. Then Abu Hurairah noticed that the Prophet صلى الله عليه وسلم stopped making that supplication one morning. When he mentioned it, the Prophet صلى الله عليه وسلم replied that they had come back. The key point is that Qunut in prayer was used here as a direct plea to Allah for people in need, and it was stopped when the stated matter changed."},"teachings":["Qunut can include specific dua for named people in need.","The supplication in this report continued for one month.","The Prophet stopped that dua when the people had returned.","The wording teaches care when linking dua to a specific situation."],"related_hadiths":[{"id":"1006","book_id":"1","label":"Sahih Bukhari"},{"id":"2932","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut for the Weak Believers","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet made Qunut for a month, asking Allah to rescue named weak believers."},"heading":{"title":"Qunut Dua for the Weak Believers in Night Prayer","description":"This Hadith about Qunut dua shows the Prophet صلى الله عليه وسلم making a clear supplication in the night prayer for one month. He asked Allah to rescue al-Walid b. al-Walid, Salamah b. Hisham, and the weak believers. The Hadith also records his words against Mudar, including a request for a famine like that of Joseph. Then Abu Hurairah noticed that the Prophet صلى الله عليه وسلم stopped making that supplication one morning. When he mentioned it, the Prophet صلى الله عليه وسلم replied that they had come back. The key point is that Qunut in prayer was used here as a direct plea to Allah for people in need, and it was stopped when the stated matter changed."},"teachings":["Qunut can include specific dua for named people in need.","The supplication in this report continued for one month.","The Prophet stopped that dua when the people had returned.","The wording teaches care when linking dua to a specific situation."],"related_hadiths":[{"id":"1006","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2932","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E260" s="4" t="n"/>
@@ -6461,7 +6465,7 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut in Five Daily Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited Qunut for a month in all five prayers after rising from bowing."},"heading":{"title":"Qunut in Five Prayers: A Hadith on Supplication After Ruku","description":"This Hadith about Qunut in five daily prayers gives a clear time and place for the supplication. Ibn Abbas narrated that the Messenger of Allah صلى الله عليه وسلم recited Qunut daily for a month in Dhuhr, Asr, Maghrib, Isha, and Fajr. The Hadith says this happened in the last rak'ah after he said, “Allah listens to him who praises Him.” The supplication was against some clans of Banu Sulaym: Ri'l, Dhakwan, and Usayyah. Those praying behind him said Ameen. The teaching is direct: in this report, Qunut was made after rising from bowing, in the final rak'ah, and the congregation joined by saying Ameen."},"teachings":["The report mentions Qunut in all five prayers for one month.","The timing given is after rising from bowing in the last rak'ah.","People behind the Prophet said Ameen to the supplication.","The narration names the specific groups mentioned in the dua."],"related_hadiths":[{"id":"1003","book_id":"1","label":"Sahih Bukhari"},{"id":"1070","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut in Five Daily Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited Qunut for a month in all five prayers after rising from bowing."},"heading":{"title":"Qunut in Five Prayers: A Hadith on Supplication After Ruku","description":"This Hadith about Qunut in five daily prayers gives a clear time and place for the supplication. Ibn Abbas narrated that the Messenger of Allah صلى الله عليه وسلم recited Qunut daily for a month in Dhuhr, Asr, Maghrib, Isha, and Fajr. The Hadith says this happened in the last rak'ah after he said, “Allah listens to him who praises Him.” The supplication was against some clans of Banu Sulaym: Ri'l, Dhakwan, and Usayyah. Those praying behind him said Ameen. The teaching is direct: in this report, Qunut was made after rising from bowing, in the final rak'ah, and the congregation joined by saying Ameen."},"teachings":["The report mentions Qunut in all five prayers for one month.","The timing given is after rising from bowing in the last rak'ah.","People behind the Prophet said Ameen to the supplication.","The narration names the specific groups mentioned in the dua."],"related_hadiths":[{"id":"1003","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1070","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E261" s="4" t="n"/>
@@ -6484,7 +6488,7 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut After Ruku in Fajr","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas said the Prophet recited Qunut in Fajr after bowing, for a short period."},"heading":{"title":"Qunut After Ruku in Fajr: What Anas Reported","description":"This Hadith about Qunut after ruku answers a very specific question. Anas b. Malik was asked whether the Messenger of Allah صلى الله عليه وسلم recited supplication in the dawn prayer. He said yes. He was then asked whether it was before bowing or after bowing. He answered: after bowing. One version adds that this was for a short period. The value of the Hadith is in its precision. It does not give a long discussion, and it does not add a full ruling. It simply records the answer of Anas about Qunut in Fajr prayer, its place after ruku, and the short period mentioned in one version."},"teachings":["Anas confirmed Qunut in the dawn prayer.","The place mentioned here is after bowing.","One version adds that it was for a short period.","Specific questions in Hadith often receive specific answers."],"related_hadiths":[{"id":"1001","book_id":"1","label":"Sahih Bukhari"},{"id":"1002","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut After Ruku in Fajr","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas said the Prophet recited Qunut in Fajr after bowing, for a short period."},"heading":{"title":"Qunut After Ruku in Fajr: What Anas Reported","description":"This Hadith about Qunut after ruku answers a very specific question. Anas b. Malik was asked whether the Messenger of Allah صلى الله عليه وسلم recited supplication in the dawn prayer. He said yes. He was then asked whether it was before bowing or after bowing. He answered: after bowing. One version adds that this was for a short period. The value of the Hadith is in its precision. It does not give a long discussion, and it does not add a full ruling. It simply records the answer of Anas about Qunut in Fajr prayer, its place after ruku, and the short period mentioned in one version."},"teachings":["Anas confirmed Qunut in the dawn prayer.","The place mentioned here is after bowing.","One version adds that it was for a short period.","Specific questions in Hadith often receive specific answers."],"related_hadiths":[{"id":"1001","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1002","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E262" s="4" t="n"/>
@@ -6507,7 +6511,7 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut for One Month","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas reported that the Prophet recited Qunut for a month and then left it."},"heading":{"title":"Qunut for One Month: A Short Hadith with a Clear Limit","description":"This Hadith about Qunut for one month is brief, but it gives an important detail. Anas b. Malik said the Prophet صلى الله عليه وسلم recited the supplication for a month in prayer and then gave it up. The wording does not list the full dua here, nor does it name the prayer in this short report. It focuses on the length of time and the fact that the practice was then left. For anyone searching for hadith about Qunut for one month, this narration is useful because it shows that the act was tied to a limited period in this report. A careful reader should not add more than the text says."},"teachings":["The Prophet recited Qunut for one month in this report.","The Hadith also states that he later left it.","The text does not provide the full supplication here.","Short Hadiths should not be stretched beyond their wording."],"related_hadiths":[{"id":"1002","book_id":"1","label":"Sahih Bukhari"},{"id":"1003","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Qunut for One Month","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas reported that the Prophet recited Qunut for a month and then left it."},"heading":{"title":"Qunut for One Month: A Short Hadith with a Clear Limit","description":"This Hadith about Qunut for one month is brief, but it gives an important detail. Anas b. Malik said the Prophet صلى الله عليه وسلم recited the supplication for a month in prayer and then gave it up. The wording does not list the full dua here, nor does it name the prayer in this short report. It focuses on the length of time and the fact that the practice was then left. For anyone searching for hadith about Qunut for one month, this narration is useful because it shows that the act was tied to a limited period in this report. A careful reader should not add more than the text says."},"teachings":["The Prophet recited Qunut for one month in this report.","The Hadith also states that he later left it.","The text does not provide the full supplication here.","Short Hadiths should not be stretched beyond their wording."],"related_hadiths":[{"id":"1002","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1003","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E263" s="4" t="n"/>
@@ -6530,7 +6534,7 @@
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing Briefly After Fajr Ruku","description":"$book_name$ $hadith_number$ - $chapter_name$. A person who prayed Fajr with the Prophet said he stood briefly after the second rak'ah."},"heading":{"title":"Brief Standing After the Second Rak'ah in Fajr Prayer","description":"This Hadith describes a small but meaningful prayer detail. Muhammad ibn Sirin said that someone who prayed the morning prayer with the Prophet صلى الله عليه وسلم told him that when the Prophet raised his head after the second rak'ah, he remained standing for a short while. The report does not quote a supplication, and it does not give extra detail about what was said. Its focus is the brief standing after rising in the second rak'ah of Fajr. Readers looking for Qunut in Fajr or standing after ruku should note the careful wording: the narration mentions the action and the short length of time, without adding more explanation."},"teachings":["The report describes standing after the second rak'ah of Fajr.","The standing was for a short while.","The text does not quote the words said in that standing.","Prayer details in Hadith can be brief and exact."],"related_hadiths":[{"id":"1001","book_id":"1","label":"Sahih Bukhari"},{"id":"1002","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing Briefly After Fajr Ruku","description":"$book_name$ $hadith_number$ - $chapter_name$. A person who prayed Fajr with the Prophet said he stood briefly after the second rak'ah."},"heading":{"title":"Brief Standing After the Second Rak'ah in Fajr Prayer","description":"This Hadith describes a small but meaningful prayer detail. Muhammad ibn Sirin said that someone who prayed the morning prayer with the Prophet صلى الله عليه وسلم told him that when the Prophet raised his head after the second rak'ah, he remained standing for a short while. The report does not quote a supplication, and it does not give extra detail about what was said. Its focus is the brief standing after rising in the second rak'ah of Fajr. Readers looking for Qunut in Fajr or standing after ruku should note the careful wording: the narration mentions the action and the short length of time, without adding more explanation."},"teachings":["The report describes standing after the second rak'ah of Fajr.","The standing was for a short while.","The text does not quote the words said in that standing.","Prayer details in Hadith can be brief and exact."],"related_hadiths":[{"id":"1001","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1002","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E264" s="4" t="n"/>
@@ -6553,7 +6557,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Voluntary Prayer at Home","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that a man's prayer is better at home except the obligatory prayer."},"heading":{"title":"Voluntary Prayer at Home: The Best Prayer Outside Obligatory Salah","description":"This Hadith about voluntary prayer at home tells how the Prophet صلى الله عليه وسلم made a chamber in the mosque and prayed there at night. Some people began praying with him and kept coming. When he did not come out one night, they coughed, raised their voices, and threw pebbles and sand at his door. The Prophet صلى الله عليه وسلم came out angry and said their action made him think that the prayer might be prescribed for them. He then told them to pray in their houses, because a man's prayer is better in his house except the obligatory prayer. The message is simple: do not pressure religious practice into hardship, and keep voluntary prayer alive at home."},"teachings":["Voluntary prayers have a strong place in the home.","Obligatory prayers are excepted in the wording of the Hadith.","The people were corrected for pressuring the Prophet to come out.","The Prophet showed concern that extra prayer might become prescribed for them."],"related_hadiths":[{"id":"731","book_id":"1","label":"Sahih Bukhari"},{"id":"1187","book_id":"1","label":"Sahih Bukhari"},{"id":"761b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Voluntary Prayer at Home","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that a man's prayer is better at home except the obligatory prayer."},"heading":{"title":"Voluntary Prayer at Home: The Best Prayer Outside Obligatory Salah","description":"This Hadith about voluntary prayer at home tells how the Prophet صلى الله عليه وسلم made a chamber in the mosque and prayed there at night. Some people began praying with him and kept coming. When he did not come out one night, they coughed, raised their voices, and threw pebbles and sand at his door. The Prophet صلى الله عليه وسلم came out angry and said their action made him think that the prayer might be prescribed for them. He then told them to pray in their houses, because a man's prayer is better in his house except the obligatory prayer. The message is simple: do not pressure religious practice into hardship, and keep voluntary prayer alive at home."},"teachings":["Voluntary prayers have a strong place in the home.","Obligatory prayers are excepted in the wording of the Hadith.","The people were corrected for pressuring the Prophet to come out.","The Prophet showed concern that extra prayer might become prescribed for them."],"related_hadiths":[{"id":"731","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1187","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"761b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E265" s="4" t="n"/>
@@ -6576,7 +6580,7 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Make Homes Like Graves","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet told Muslims to offer some prayers at home and not make homes like graves."},"heading":{"title":"Pray Some Salah at Home: Do Not Make Houses Like Graves","description":"This Hadith about prayer at home is short and easy to remember. Ibn Umar reported that the Messenger of Allah صلى الله عليه وسلم said to make some of your prayers in your houses and not to take them as graves. The meaning stays close to the wording: a Muslim home should not be empty of Salah. The Hadith does not say to leave the obligatory prayers, and nearby reports explain the exception of required prayers. Here the focus is on keeping worship present inside the home. For people searching “do not make your houses graves hadith,” this narration gives a direct reminder that prayer brings spiritual life into the house."},"teachings":["A Muslim home should have some prayer in it.","The Prophet warned against making houses like graves.","The Hadith encourages private worship at home.","The wording is short, direct, and easy to act on."],"related_hadiths":[{"id":"1187","book_id":"1","label":"Sahih Bukhari"},{"id":"731","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Make Homes Like Graves","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet told Muslims to offer some prayers at home and not make homes like graves."},"heading":{"title":"Pray Some Salah at Home: Do Not Make Houses Like Graves","description":"This Hadith about prayer at home is short and easy to remember. Ibn Umar reported that the Messenger of Allah صلى الله عليه وسلم said to make some of your prayers in your houses and not to take them as graves. The meaning stays close to the wording: a Muslim home should not be empty of Salah. The Hadith does not say to leave the obligatory prayers, and nearby reports explain the exception of required prayers. Here the focus is on keeping worship present inside the home. For people searching “do not make your houses graves hadith,” this narration gives a direct reminder that prayer brings spiritual life into the house."},"teachings":["A Muslim home should have some prayer in it.","The Prophet warned against making houses like graves.","The Hadith encourages private worship at home.","The wording is short, direct, and easy to act on."],"related_hadiths":[{"id":"1187","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"731","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E266" s="4" t="n"/>
@@ -6599,7 +6603,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Long Standing and Sincere Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet named long standing in prayer and charity from limited means as better deeds."},"heading":{"title":"Best Deeds in Hadith: Long Standing, Charity, and Leaving the Forbidden","description":"This Hadith about the best deeds records a series of questions asked to the Prophet صلى الله عليه وسلم. He said that long standing in prayer is a better action. When asked about charity, he said it is the charity given by a person with small means from what he has earned. The Arabic text also mentions answers about hijrah, striving, and the most honorable kind of being killed. The main lesson is that value is not only in public size or outward amount. Long standing in prayer shows devotion, and charity from limited means shows real effort. For searches like best deeds in Islam hadith or best charity hadith, the wording points to sincere effort in worship and giving."},"teachings":["Long standing in prayer is praised in this report.","Charity from limited means is valued in the Hadith.","Leaving what Allah has forbidden is named as a form of hijrah in the Arabic text.","The Hadith links good deeds with effort, sacrifice, and obedience."],"related_hadiths":[{"id":"2526","book_id":"3","label":"Sunan an-Nasai"},{"id":"2607","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1163","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Long Standing and Sincere Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet named long standing in prayer and charity from limited means as better deeds."},"heading":{"title":"Best Deeds in Hadith: Long Standing, Charity, and Leaving the Forbidden","description":"This Hadith about the best deeds records a series of questions asked to the Prophet صلى الله عليه وسلم. He said that long standing in prayer is a better action. When asked about charity, he said it is the charity given by a person with small means from what he has earned. The Arabic text also mentions answers about hijrah, striving, and the most honorable kind of being killed. The main lesson is that value is not only in public size or outward amount. Long standing in prayer shows devotion, and charity from limited means shows real effort. For searches like best deeds in Islam hadith or best charity hadith, the wording points to sincere effort in worship and giving."},"teachings":["Long standing in prayer is praised in this report.","Charity from limited means is valued in the Hadith.","Leaving what Allah has forbidden is named as a form of hijrah in the Arabic text.","The Hadith links good deeds with effort, sacrifice, and obedience."],"related_hadiths":[{"id":"2526","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"2607","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1163","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E267" s="4" t="n"/>
@@ -6622,7 +6626,7 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Running Water Through the Beard","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows the Prophet passing water through his beard during wudu as an act he was commanded to do."},"heading":{"title":"Hadith About Wudu Beard Washing: Water Through the Beard","description":"This hadith about wudu beard washing describes an action of the Messenger of Allah (صلى الله عليه وسلم). Whenever he performed ablution, he took a handful of water, placed it under his chin, and passed it through his beard. He then said, “Thus did my Lord command me.” The narration is focused and practical. It shows that the beard was not ignored during wudu. Water was brought under the chin and made to pass through it. For people searching running fingers through beard in wudu hadith, this text gives a direct report from Anas ibn Malik. The explanation should stay with the action described: a handful of water, under the chin, through the beard, connected to the command of Allah as stated in the hadith."},"teachings":["The Prophet (صلى الله عليه وسلم) passed water through his beard during wudu.","The action was done with a handful of water under the chin.","The hadith connects this practice to the command of Allah.","Beard care in wudu should be based on the described Sunnah action."],"related_hadiths":[{"id":"135","book_id":"4","label":"Sunan Abu Dawud"},{"id":"191","book_id":"1","label":"Sahih Bukhari"},{"id":"182","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Running Water Through the Beard","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows the Prophet passing water through his beard during wudu as an act he was commanded to do."},"heading":{"title":"Hadith About Wudu Beard Washing: Water Through the Beard","description":"This hadith about wudu beard washing describes an action of the Messenger of Allah (صلى الله عليه وسلم). Whenever he performed ablution, he took a handful of water, placed it under his chin, and passed it through his beard. He then said, “Thus did my Lord command me.” The narration is focused and practical. It shows that the beard was not ignored during wudu. Water was brought under the chin and made to pass through it. For people searching running fingers through beard in wudu hadith, this text gives a direct report from Anas ibn Malik. The explanation should stay with the action described: a handful of water, under the chin, through the beard, connected to the command of Allah as stated in the hadith."},"teachings":["The Prophet (صلى الله عليه وسلم) passed water through his beard during wudu.","The action was done with a handful of water under the chin.","The hadith connects this practice to the command of Allah.","Beard care in wudu should be based on the described Sunnah action."],"related_hadiths":[{"id":"135","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"191","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"182","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E268" s="4" t="n"/>
@@ -6645,7 +6649,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Spouses Waking for Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet prayed for mercy on spouses who wake each other for night prayer."},"heading":{"title":"Night Prayer for Couples: Waking Your Spouse for Salah","description":"This Hadith about night prayer for couples shows a gentle pattern of shared worship. Abu Hurairah narrated that the Prophet صلى الله عليه وسلم asked Allah to show mercy to a man who gets up at night, prays, wakes his wife, and she prays. If she refuses, he sprinkles water on her face. The Hadith then gives the same wording for a woman who wakes, prays, wakes her husband, and if he refuses, sprinkles water on his face. The focus is mutual help in worship. It is not one-sided. Both husband and wife are encouraged to support each other in night prayer, with mercy being asked for both."},"teachings":["Spouses can help each other wake for night prayer.","The Hadith mentions mercy for both husband and wife.","Shared worship is presented in a balanced way.","The action is linked to waking, praying, and encouraging the other spouse."],"related_hadiths":[{"id":"1610","book_id":"3","label":"Sunan an-Nasai"},{"id":"1336","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Spouses Waking for Night Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet prayed for mercy on spouses who wake each other for night prayer."},"heading":{"title":"Night Prayer for Couples: Waking Your Spouse for Salah","description":"This Hadith about night prayer for couples shows a gentle pattern of shared worship. Abu Hurairah narrated that the Prophet صلى الله عليه وسلم asked Allah to show mercy to a man who gets up at night, prays, wakes his wife, and she prays. If she refuses, he sprinkles water on her face. The Hadith then gives the same wording for a woman who wakes, prays, wakes her husband, and if he refuses, sprinkles water on his face. The focus is mutual help in worship. It is not one-sided. Both husband and wife are encouraged to support each other in night prayer, with mercy being asked for both."},"teachings":["Spouses can help each other wake for night prayer.","The Hadith mentions mercy for both husband and wife.","Shared worship is presented in a balanced way.","The action is linked to waking, praying, and encouraging the other spouse."],"related_hadiths":[{"id":"1610","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"1336","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E269" s="4" t="n"/>
@@ -6668,7 +6672,7 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs Together at Night","description":"$book_name$ $hadith_number$ - $chapter_name$. A couple who wake and pray two rak'ahs are recorded among those who remember Allah much."},"heading":{"title":"Two Rak'ahs at Night: A Hadith on Couples Remembering Allah","description":"This Hadith about two rak'ahs at night gives a clear promise within the text. Abu Sa'id and Abu Hurairah reported that when a man wakes at night, wakes his wife, and they pray two rak'ahs together, they are recorded among the men and women who make much mention of Allah. The report is short and hopeful. It does not require a long night or many rak'ahs in this wording. It names waking, helping the spouse wake, and praying two rak'ahs together. For readers searching for tahajjud with spouse hadith or two rak'ahs at night hadith, this narration shows how a small shared act can be linked with much remembrance of Allah."},"teachings":["Two rak'ahs at night are specifically mentioned.","The Hadith encourages spouses to pray together.","The reward stated is being recorded among those who remember Allah much.","The wording shows that a small act can carry great meaning."],"related_hadiths":[{"id":"1335","book_id":"6","label":"Sunan Ibn Majah"},{"id":"1610","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Rak'ahs Together at Night","description":"$book_name$ $hadith_number$ - $chapter_name$. A couple who wake and pray two rak'ahs are recorded among those who remember Allah much."},"heading":{"title":"Two Rak'ahs at Night: A Hadith on Couples Remembering Allah","description":"This Hadith about two rak'ahs at night gives a clear promise within the text. Abu Sa'id and Abu Hurairah reported that when a man wakes at night, wakes his wife, and they pray two rak'ahs together, they are recorded among the men and women who make much mention of Allah. The report is short and hopeful. It does not require a long night or many rak'ahs in this wording. It names waking, helping the spouse wake, and praying two rak'ahs together. For readers searching for tahajjud with spouse hadith or two rak'ahs at night hadith, this narration shows how a small shared act can be linked with much remembrance of Allah."},"teachings":["Two rak'ahs at night are specifically mentioned.","The Hadith encourages spouses to pray together.","The reward stated is being recorded among those who remember Allah much.","The wording shows that a small act can carry great meaning."],"related_hadiths":[{"id":"1335","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"1610","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E270" s="4" t="n"/>
@@ -6691,7 +6695,7 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learn and Teach the Quran","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said the best among you are those who learn the Qur'an and teach it."},"heading":{"title":"Learn and Teach the Quran: The Best Among You Hadith","description":"This famous Hadith about learning and teaching the Quran is simple and powerful. Uthman reported that the Prophet صلى الله عليه وسلم said, “The best among you is he who learns and teaches the Qur'an.” The teaching is direct: the Quran should be learned and passed on. The Hadith does not limit this to one age, one place, or one group in the wording given. It joins learning with teaching, so a person benefits himself and then benefits others. For people searching “best among you learn Quran and teach it,” this narration is one of the main texts used because its message is clear, short, and easy to share."},"teachings":["Learning the Qur'an is praised in the Hadith.","Teaching the Qur'an is joined with learning it.","The wording encourages benefit for oneself and others.","The best among you is tied here to Qur'an learning and teaching."],"related_hadiths":[{"id":"5027","book_id":"1","label":"Sahih Bukhari"},{"id":"5028","book_id":"1","label":"Sahih Bukhari"},{"id":"2907","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learn and Teach the Quran","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said the best among you are those who learn the Qur'an and teach it."},"heading":{"title":"Learn and Teach the Quran: The Best Among You Hadith","description":"This famous Hadith about learning and teaching the Quran is simple and powerful. Uthman reported that the Prophet صلى الله عليه وسلم said, “The best among you is he who learns and teaches the Qur'an.” The teaching is direct: the Quran should be learned and passed on. The Hadith does not limit this to one age, one place, or one group in the wording given. It joins learning with teaching, so a person benefits himself and then benefits others. For people searching “best among you learn Quran and teach it,” this narration is one of the main texts used because its message is clear, short, and easy to share."},"teachings":["Learning the Qur'an is praised in the Hadith.","Teaching the Qur'an is joined with learning it.","The wording encourages benefit for oneself and others.","The best among you is tied here to Qur'an learning and teaching."],"related_hadiths":[{"id":"5027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5028","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2907","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E271" s="4" t="n"/>
@@ -6714,7 +6718,7 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Skilled and Struggling Quran Reciters","description":"$book_name$ $hadith_number$ - $chapter_name$. The skilled reciter is with noble angels, while the struggling reciter has two rewards."},"heading":{"title":"Skilled and Struggling Quran Reciters: Hope for Every Learner","description":"This Hadith about Quran recitation gives hope to two types of readers. Aishah reported that the Prophet صلى الله عليه وسلم said the one who is skilled in the Qur'an is with the noble, upright recording angels. He also said that the one who falters while reciting and finds it hard will have a double reward. The wording is comforting because it honors skill but does not leave out the learner who struggles. A person who finds Quran recitation difficult should not feel pushed away by the difficulty. The Hadith says effort with hardship has reward. For searches like struggling to read Quran hadith or skilled reciter with angels, this narration speaks clearly."},"teachings":["A skilled reciter of the Qur'an is praised in the Hadith.","The struggling reciter is not left without reward.","Difficulty in recitation can be part of rewarded effort.","The Hadith encourages both skill and patient learning."],"related_hadiths":[{"id":"798a","book_id":"2","label":"Sahih Muslim"},{"id":"4937","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Skilled and Struggling Quran Reciters","description":"$book_name$ $hadith_number$ - $chapter_name$. The skilled reciter is with noble angels, while the struggling reciter has two rewards."},"heading":{"title":"Skilled and Struggling Quran Reciters: Hope for Every Learner","description":"This Hadith about Quran recitation gives hope to two types of readers. Aishah reported that the Prophet صلى الله عليه وسلم said the one who is skilled in the Qur'an is with the noble, upright recording angels. He also said that the one who falters while reciting and finds it hard will have a double reward. The wording is comforting because it honors skill but does not leave out the learner who struggles. A person who finds Quran recitation difficult should not feel pushed away by the difficulty. The Hadith says effort with hardship has reward. For searches like struggling to read Quran hadith or skilled reciter with angels, this narration speaks clearly."},"teachings":["A skilled reciter of the Qur'an is praised in the Hadith.","The struggling reciter is not left without reward.","Difficulty in recitation can be part of rewarded effort.","The Hadith encourages both skill and patient learning."],"related_hadiths":[{"id":"798a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"4937","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E272" s="4" t="n"/>
@@ -6737,7 +6741,7 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gathering to Study the Quran","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith describes calmness, mercy, angels, and Allah's mention for Qur'an study gatherings."},"heading":{"title":"Gathering to Study the Quran: Sakinah, Mercy, and Angels","description":"This Hadith about gathering to study the Quran describes a beautiful scene in a house of Allah. Abu Hurairah reported that when people gather in a mosque, recite the Book of Allah, and learn it together among themselves, calmness descends on them, mercy covers them, angels surround them, and Allah mentions them among those with Him. The Hadith is direct about the setting and the action: people gather, recite, and study together. It does not speak about showing off or arguing. It is about shared Qur'an learning. For readers searching for Quran study circle hadith or sakinah descends hadith, this narration gives the wording they need."},"teachings":["Gathering in a mosque to recite and study the Qur'an is praised.","The Hadith mentions calmness descending on such a gathering.","Mercy and angels are also named in the narration.","Allah's mention of them is part of the stated blessing."],"related_hadiths":[{"id":"2699a","book_id":"2","label":"Sahih Muslim"},{"id":"5027","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Gathering to Study the Quran","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith describes calmness, mercy, angels, and Allah's mention for Qur'an study gatherings."},"heading":{"title":"Gathering to Study the Quran: Sakinah, Mercy, and Angels","description":"This Hadith about gathering to study the Quran describes a beautiful scene in a house of Allah. Abu Hurairah reported that when people gather in a mosque, recite the Book of Allah, and learn it together among themselves, calmness descends on them, mercy covers them, angels surround them, and Allah mentions them among those with Him. The Hadith is direct about the setting and the action: people gather, recite, and study together. It does not speak about showing off or arguing. It is about shared Qur'an learning. For readers searching for Quran study circle hadith or sakinah descends hadith, this narration gives the wording they need."},"teachings":["Gathering in a mosque to recite and study the Qur'an is praised.","The Hadith mentions calmness descending on such a gathering.","Mercy and angels are also named in the narration.","Allah's mention of them is part of the stated blessing."],"related_hadiths":[{"id":"2699a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"5027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E273" s="4" t="n"/>
@@ -6760,7 +6764,7 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Verses Better Than Camels","description":"$book_name$ $hadith_number$ - $chapter_name$. Learning two verses from the Qur'an is described as better than two valuable she-camels."},"heading":{"title":"Learning Two Quran Verses: Better Than Valuable Camels","description":"This Hadith about learning Quran verses uses a comparison that the listeners could understand. Uqbah b. Amir said they were in the Suffah when the Prophet صلى الله عليه وسلم asked who would like to go every morning to Buthan or Al-'Aqiq and bring two large, fat she-camels without sin or cutting family ties. They all wanted that. He then said that going to the mosque and learning two verses from the Book of Allah is better than two she-camels, three verses better than three, and so on. The point is clear: learning even a small number of Quran verses is valuable, and the Hadith uses worldly value to help people see it."},"teachings":["Learning two verses of the Qur'an is praised highly.","The comparison uses valuable she-camels to make the lesson clear.","The Hadith says more verses bring more value in the same pattern.","The learning mentioned is connected to going to the mosque in the morning."],"related_hadiths":[{"id":"803","book_id":"2","label":"Sahih Muslim"},{"id":"5027","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Two Verses Better Than Camels","description":"$book_name$ $hadith_number$ - $chapter_name$. Learning two verses from the Qur'an is described as better than two valuable she-camels."},"heading":{"title":"Learning Two Quran Verses: Better Than Valuable Camels","description":"This Hadith about learning Quran verses uses a comparison that the listeners could understand. Uqbah b. Amir said they were in the Suffah when the Prophet صلى الله عليه وسلم asked who would like to go every morning to Buthan or Al-'Aqiq and bring two large, fat she-camels without sin or cutting family ties. They all wanted that. He then said that going to the mosque and learning two verses from the Book of Allah is better than two she-camels, three verses better than three, and so on. The point is clear: learning even a small number of Quran verses is valuable, and the Hadith uses worldly value to help people see it."},"teachings":["Learning two verses of the Qur'an is praised highly.","The comparison uses valuable she-camels to make the lesson clear.","The Hadith says more verses bring more value in the same pattern.","The learning mentioned is connected to going to the mosque in the morning."],"related_hadiths":[{"id":"803","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"5027","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E274" s="4" t="n"/>
@@ -6783,7 +6787,7 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Al-Fatihah as Umm al-Quran","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet named Al-Fatihah the basis of the Qur'an and the seven oft-repeated verses."},"heading":{"title":"Surah Al-Fatihah Hadith: Umm al-Quran and Seven Oft-Repeated Verses","description":"This Hadith about Surah Al-Fatihah explains the rank of the opening words, “All praise be to Allah, the Lord of the Universe.” Abu Hurairah reported that the Prophet صلى الله عليه وسلم called it the epitome or basis of the Qur'an, the epitome or basis of the Book, and the seven oft-repeated verses. The narration is focused on naming and honoring this surah. It does not list all of its meanings here, but it gives important titles: Umm al-Quran, Umm al-Kitab, and As-Sab' al-Mathani. For people searching for Surah Al-Fatihah hadith or seven oft repeated verses, this Hadith directly gives those phrases. This is why the title appears often in searches."},"teachings":["Al-Fatihah is called the basis of the Qur'an in this report.","It is also called the basis of the Book.","The Hadith names it the seven oft-repeated verses.","The narration highlights the special status of Al-Fatihah."],"related_hadiths":[{"id":"4474","book_id":"1","label":"Sahih Bukhari"},{"id":"5006","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Al-Fatihah as Umm al-Quran","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet named Al-Fatihah the basis of the Qur'an and the seven oft-repeated verses."},"heading":{"title":"Surah Al-Fatihah Hadith: Umm al-Quran and Seven Oft-Repeated Verses","description":"This Hadith about Surah Al-Fatihah explains the rank of the opening words, “All praise be to Allah, the Lord of the Universe.” Abu Hurairah reported that the Prophet صلى الله عليه وسلم called it the epitome or basis of the Qur'an, the epitome or basis of the Book, and the seven oft-repeated verses. The narration is focused on naming and honoring this surah. It does not list all of its meanings here, but it gives important titles: Umm al-Quran, Umm al-Kitab, and As-Sab' al-Mathani. For people searching for Surah Al-Fatihah hadith or seven oft repeated verses, this Hadith directly gives those phrases. This is why the title appears often in searches."},"teachings":["Al-Fatihah is called the basis of the Qur'an in this report.","It is also called the basis of the Book.","The Hadith names it the seven oft-repeated verses.","The narration highlights the special status of Al-Fatihah."],"related_hadiths":[{"id":"4474","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5006","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E275" s="4" t="n"/>
@@ -6806,7 +6810,7 @@
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Greatest Surah in the Quran","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that Al-Fatihah is the greatest surah and the mighty Qur'an."},"heading":{"title":"Greatest Surah in the Quran: Surah Al-Fatihah Hadith","description":"This Hadith about the greatest surah in the Quran begins with Abu Sa'id b. al-Mu'alla praying when the Prophet صلى الله عليه وسلم called him. After he finished and came, the Prophet asked what stopped him from answering. Abu Sa'id said he was praying. The Prophet then cited the meaning of responding to Allah and the Messenger when called to what gives life. He promised to teach the greatest surah before leaving the mosque. The surah was “Praise be to Allah, the Lord of the Universe,” meaning Al-Fatihah. The Hadith also calls it the seven oft-repeated verses and the mighty Qur'an. The text centers on the high rank of Al-Fatihah."},"teachings":["The Prophet called Al-Fatihah the greatest surah in this report.","The Hadith links Al-Fatihah with the seven oft-repeated verses.","The narration also mentions responding to the Messenger's call.","The teaching was given before leaving the mosque, as stated in the Hadith."],"related_hadiths":[{"id":"4474","book_id":"1","label":"Sahih Bukhari"},{"id":"4647","book_id":"1","label":"Sahih Bukhari"},{"id":"5006","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Greatest Surah in the Quran","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that Al-Fatihah is the greatest surah and the mighty Qur'an."},"heading":{"title":"Greatest Surah in the Quran: Surah Al-Fatihah Hadith","description":"This Hadith about the greatest surah in the Quran begins with Abu Sa'id b. al-Mu'alla praying when the Prophet صلى الله عليه وسلم called him. After he finished and came, the Prophet asked what stopped him from answering. Abu Sa'id said he was praying. The Prophet then cited the meaning of responding to Allah and the Messenger when called to what gives life. He promised to teach the greatest surah before leaving the mosque. The surah was “Praise be to Allah, the Lord of the Universe,” meaning Al-Fatihah. The Hadith also calls it the seven oft-repeated verses and the mighty Qur'an. The text centers on the high rank of Al-Fatihah."},"teachings":["The Prophet called Al-Fatihah the greatest surah in this report.","The Hadith links Al-Fatihah with the seven oft-repeated verses.","The narration also mentions responding to the Messenger's call.","The teaching was given before leaving the mosque, as stated in the Hadith."],"related_hadiths":[{"id":"4474","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4647","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5006","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E276" s="4" t="n"/>
@@ -6829,7 +6833,7 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seven Repeated Long Surahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas said the Messenger was given seven repeated long surahs, while Moses was given six."},"heading":{"title":"Seven Repeated Long Surahs: A Hadith from Ibn Abbas","description":"This Hadith about seven repeated long surahs reports a statement from Abdullah ibn Abbas. He said that the Messenger of Allah صلى الله عليه وسلم was given seven repeated long surahs, while Moses was given six. The narration then says that when Moses threw the tablets, two of them were withdrawn and four remained. The text is brief and should be handled with care. It does not name the seven surahs in this wording, and it does not give a long explanation of the tablets. So the safest explanation is to stay with what the report says: a comparison is made between what was given to the Messenger صلى الله عليه وسلم and what was given to Moses, with a note about the tablets."},"teachings":["The Hadith mentions seven repeated long surahs given to the Messenger صلى الله عليه وسلم.","It states that Moses was given six.","The report says two tablets were withdrawn after Moses threw them.","The narration is brief, so extra details should not be added without clear support."],"related_hadiths":[{"id":"4703","book_id":"1","label":"Sahih Bukhari"},{"id":"5006","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seven Repeated Long Surahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas said the Messenger was given seven repeated long surahs, while Moses was given six."},"heading":{"title":"Seven Repeated Long Surahs: A Hadith from Ibn Abbas","description":"This Hadith about seven repeated long surahs reports a statement from Abdullah ibn Abbas. He said that the Messenger of Allah صلى الله عليه وسلم was given seven repeated long surahs, while Moses was given six. The narration then says that when Moses threw the tablets, two of them were withdrawn and four remained. The text is brief and should be handled with care. It does not name the seven surahs in this wording, and it does not give a long explanation of the tablets. So the safest explanation is to stay with what the report says: a comparison is made between what was given to the Messenger صلى الله عليه وسلم and what was given to Moses, with a note about the tablets."},"teachings":["The Hadith mentions seven repeated long surahs given to the Messenger صلى الله عليه وسلم.","It states that Moses was given six.","The report says two tablets were withdrawn after Moses threw them.","The narration is brief, so extra details should not be added without clear support."],"related_hadiths":[{"id":"4703","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5006","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E277" s="4" t="n"/>
@@ -6852,7 +6856,7 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Over Turbans and Stockings in Cold","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows a practical allowance to wipe over turbans and stockings when cold affected an expedition."},"heading":{"title":"Hadith About Wiping Over Turban and Stockings in Wudu","description":"This hadith about wiping over turban and stockings in wudu is tied to a clear situation in the text. The Messenger of Allah (صلى الله عليه وسلم) sent out an expedition, and the people were affected by cold. When they came back, he commanded them to wipe over turbans and stockings. The wording shows practical guidance in a hard condition. It does not give every legal detail about the subject, but it clearly records the command in that setting. For searches like wiping over socks in wudu and wiping over turban hadith, this narration is highly relevant. The safe lesson is that Islamic purification includes ease when there is a need shown in the text, such as cold during a journey or expedition."},"teachings":["The Prophet (صلى الله عليه وسلم) commanded wiping over turbans and stockings in this situation.","The command came after the group was affected by cold.","The hadith shows practical ease in purification.","The ruling details should not be expanded beyond the text here."],"related_hadiths":[{"id":"204","book_id":"1","label":"Sahih Bukhari"},{"id":"561","book_id":"6","label":"Sunan Ibn Majah"},{"id":"274a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Over Turbans and Stockings in Cold","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows a practical allowance to wipe over turbans and stockings when cold affected an expedition."},"heading":{"title":"Hadith About Wiping Over Turban and Stockings in Wudu","description":"This hadith about wiping over turban and stockings in wudu is tied to a clear situation in the text. The Messenger of Allah (صلى الله عليه وسلم) sent out an expedition, and the people were affected by cold. When they came back, he commanded them to wipe over turbans and stockings. The wording shows practical guidance in a hard condition. It does not give every legal detail about the subject, but it clearly records the command in that setting. For searches like wiping over socks in wudu and wiping over turban hadith, this narration is highly relevant. The safe lesson is that Islamic purification includes ease when there is a need shown in the text, such as cold during a journey or expedition."},"teachings":["The Prophet (صلى الله عليه وسلم) commanded wiping over turbans and stockings in this situation.","The command came after the group was affected by cold.","The hadith shows practical ease in purification.","The ruling details should not be expanded beyond the text here."],"related_hadiths":[{"id":"204","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"561","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E278" s="4" t="n"/>
@@ -6875,7 +6879,7 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ayat al-Kursi as the Greatest Verse","description":"$book_name$ $hadith_number$ - $chapter_name$. Ubayy identified Ayat al-Kursi as the greatest verse, and the Prophet praised his knowledge."},"heading":{"title":"Ayat al-Kursi Hadith: The Greatest Verse in the Quran","description":"This Hadith about Ayat al-Kursi shows the Prophet صلى الله عليه وسلم testing and honoring the knowledge of Ubayy b. Ka'b, also called Abu al-Mundhir. The Prophet asked him which verse of Allah's Book was greatest. Ubayy first replied, “Allah and His Apostle know best.” When asked again, he answered with the opening of Ayat al-Kursi: “Allah, there is no god but He, the Living, the Eternal.” The Prophet صلى الله عليه وسلم then struck him on the chest and said, “May knowledge be pleasant for you, Abu al-Mundhir.” The Hadith centers on the greatness of this verse and the praise of sound Qur'an knowledge. This makes the report easy to remember."},"teachings":["Ayat al-Kursi is identified as the greatest verse in this Hadith.","Ubayy first answered with humility before giving the verse.","The Prophet praised Ubayy's knowledge after his answer.","The narration highlights learning and recognizing the rank of Qur'anic verses."],"related_hadiths":[{"id":"810","book_id":"2","label":"Sahih Muslim"},{"id":"5010","book_id":"1","label":"Sahih Bukhari"},{"id":"2311","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ayat al-Kursi as the Greatest Verse","description":"$book_name$ $hadith_number$ - $chapter_name$. Ubayy identified Ayat al-Kursi as the greatest verse, and the Prophet praised his knowledge."},"heading":{"title":"Ayat al-Kursi Hadith: The Greatest Verse in the Quran","description":"This Hadith about Ayat al-Kursi shows the Prophet صلى الله عليه وسلم testing and honoring the knowledge of Ubayy b. Ka'b, also called Abu al-Mundhir. The Prophet asked him which verse of Allah's Book was greatest. Ubayy first replied, “Allah and His Apostle know best.” When asked again, he answered with the opening of Ayat al-Kursi: “Allah, there is no god but He, the Living, the Eternal.” The Prophet صلى الله عليه وسلم then struck him on the chest and said, “May knowledge be pleasant for you, Abu al-Mundhir.” The Hadith centers on the greatness of this verse and the praise of sound Qur'an knowledge. This makes the report easy to remember."},"teachings":["Ayat al-Kursi is identified as the greatest verse in this Hadith.","Ubayy first answered with humility before giving the verse.","The Prophet praised Ubayy's knowledge after his answer.","The narration highlights learning and recognizing the rank of Qur'anic verses."],"related_hadiths":[{"id":"810","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"5010","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2311","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E279" s="4" t="n"/>
@@ -6898,7 +6902,7 @@
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah Ikhlas Equals One Third of the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the great value of Surah Ikhlas and why the Prophet taught that it equals one third of the Qur'an."},"heading":{"title":"Surah Ikhlas Hadith: Equal to One Third of the Qur'an","description":"This hadith about Surah Ikhlas shows how a short surah can carry a very high value. A man heard another person repeating the words of Surah Al-Ikhlas. The next morning, he told the Messenger of Allah, and it seems he thought the surah was small because it is brief. The Prophet corrected that view with a strong statement: by the One in Whose Hand is his life, this surah is equal to a third of the Qur'an. The lesson is simple. Do not judge Qur'an recitation by length alone. Surah Ikhlas is short, easy to repeat, and full of meaning about Allah's oneness. This makes it a powerful part of Qur'an recitation and daily worship."},"teachings":["A short surah can have great value in the sight of Allah.","Surah Ikhlas should not be looked down upon because of its length.","Repeating Qur'an with care can be a meaningful act of worship.","The Prophet corrected weak assumptions about the Qur'an with clear guidance."],"related_hadiths":[{"id":"5013","book_id":"1","label":"Sahih Bukhari"},{"id":"1464","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1468","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Surah Ikhlas Equals One Third of the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the great value of Surah Ikhlas and why the Prophet taught that it equals one third of the Qur'an."},"heading":{"title":"Surah Ikhlas Hadith: Equal to One Third of the Qur'an","description":"This hadith about Surah Ikhlas shows how a short surah can carry a very high value. A man heard another person repeating the words of Surah Al-Ikhlas. The next morning, he told the Messenger of Allah, and it seems he thought the surah was small because it is brief. The Prophet corrected that view with a strong statement: by the One in Whose Hand is his life, this surah is equal to a third of the Qur'an. The lesson is simple. Do not judge Qur'an recitation by length alone. Surah Ikhlas is short, easy to repeat, and full of meaning about Allah's oneness. This makes it a powerful part of Qur'an recitation and daily worship."},"teachings":["A short surah can have great value in the sight of Allah.","Surah Ikhlas should not be looked down upon because of its length.","Repeating Qur'an with care can be a meaningful act of worship.","The Prophet corrected weak assumptions about the Qur'an with clear guidance."],"related_hadiths":[{"id":"5013","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1464","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1468","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E280" s="4" t="n"/>
@@ -6921,7 +6925,7 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Best Two Surahs for Seeking Refuge","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Surah Al-Falaq and Surah An-Nas as two great surahs and recited them in Fajr prayer."},"heading":{"title":"Surah Falaq and Surah Nas Hadith: Two Best Surahs to Recite","description":"This hadith about Surah Falaq and Surah Nas shows the special place of these two surahs. Uqbah ibn Amir was with the Messenger of Allah during a journey when the Prophet offered to teach him two of the best surahs ever recited. He taught him Surah Al-Falaq and Surah An-Nas. At first, Uqbah did not show much joy, perhaps because the surahs are short. Later, the Prophet led the people in the morning prayer and recited these same two surahs. After the prayer, he turned to Uqbah and asked how he saw them. The message is clear: short surahs can hold deep value, and the Prophet showed their importance by reciting them in prayer."},"teachings":["Surah Al-Falaq and Surah An-Nas have a special value in recitation.","The Prophet taught important Qur'an lessons in simple moments, even during travel.","Short surahs should not be treated as less meaningful.","Reciting these surahs in prayer shows their respected place."],"related_hadiths":[{"id":"1463","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1468","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1464","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Best Two Surahs for Seeking Refuge","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Surah Al-Falaq and Surah An-Nas as two great surahs and recited them in Fajr prayer."},"heading":{"title":"Surah Falaq and Surah Nas Hadith: Two Best Surahs to Recite","description":"This hadith about Surah Falaq and Surah Nas shows the special place of these two surahs. Uqbah ibn Amir was with the Messenger of Allah during a journey when the Prophet offered to teach him two of the best surahs ever recited. He taught him Surah Al-Falaq and Surah An-Nas. At first, Uqbah did not show much joy, perhaps because the surahs are short. Later, the Prophet led the people in the morning prayer and recited these same two surahs. After the prayer, he turned to Uqbah and asked how he saw them. The message is clear: short surahs can hold deep value, and the Prophet showed their importance by reciting them in prayer."},"teachings":["Surah Al-Falaq and Surah An-Nas have a special value in recitation.","The Prophet taught important Qur'an lessons in simple moments, even during travel.","Short surahs should not be treated as less meaningful.","Reciting these surahs in prayer shows their respected place."],"related_hadiths":[{"id":"1463","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1468","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1464","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E281" s="4" t="n"/>
@@ -6944,7 +6948,7 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Refuge with Surah Falaq and Nas","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet used Surah Al-Falaq and Surah An-Nas to seek refuge during wind and darkness."},"heading":{"title":"Seeking Refuge with Surah Falaq and Surah Nas Hadith","description":"This hadith teaches a direct way to seek refuge in Allah through Surah Al-Falaq and Surah An-Nas. Uqbah ibn Amir was travelling with the Messenger of Allah between al-Juhfah and al-Abwa. A strong wind and deep darkness surrounded them. At that moment, the Prophet began seeking refuge by reciting these two surahs. He then told Uqbah to use them when seeking refuge in Allah, saying that no one could use anything like them for that purpose. Uqbah also heard the Prophet recite them while leading people in prayer. The hadith keeps the teaching simple: when fear, darkness, or harm is felt, these two surahs are a strong form of seeking protection from Allah."},"teachings":["Surah Al-Falaq and Surah An-Nas are used for seeking refuge in Allah.","The Prophet recited them during hardship, wind, and darkness.","A believer may turn to Qur'an when feeling fear or difficulty.","These two surahs were also recited by the Prophet while leading prayer."],"related_hadiths":[{"id":"1462","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1468","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1479","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seeking Refuge with Surah Falaq and Nas","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet used Surah Al-Falaq and Surah An-Nas to seek refuge during wind and darkness."},"heading":{"title":"Seeking Refuge with Surah Falaq and Surah Nas Hadith","description":"This hadith teaches a direct way to seek refuge in Allah through Surah Al-Falaq and Surah An-Nas. Uqbah ibn Amir was travelling with the Messenger of Allah between al-Juhfah and al-Abwa. A strong wind and deep darkness surrounded them. At that moment, the Prophet began seeking refuge by reciting these two surahs. He then told Uqbah to use them when seeking refuge in Allah, saying that no one could use anything like them for that purpose. Uqbah also heard the Prophet recite them while leading people in prayer. The hadith keeps the teaching simple: when fear, darkness, or harm is felt, these two surahs are a strong form of seeking protection from Allah."},"teachings":["Surah Al-Falaq and Surah An-Nas are used for seeking refuge in Allah.","The Prophet recited them during hardship, wind, and darkness.","A believer may turn to Qur'an when feeling fear or difficulty.","These two surahs were also recited by the Prophet while leading prayer."],"related_hadiths":[{"id":"1462","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1468","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1479","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E282" s="4" t="n"/>
@@ -6967,7 +6971,7 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Recite, Ascend, and Rise with the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. The devoted companion of the Qur'an is told to recite, ascend, and rise by the verses he recited."},"heading":{"title":"Companion of the Qur'an Hadith: Recite and Ascend","description":"This hadith about the companion of the Qur'an gives hope and also reminds us to stay close to recitation. The Messenger of Allah said that the one devoted to the Qur'an will be told to recite, ascend, and recite carefully, just as he used to recite carefully in the world. His place will be at the last verse he recites. The wording points to steady connection with the Qur'an, not rushed reading. It highlights careful recitation and a life shaped by the words of Allah. The hadith does not ask us to compare ourselves with others. It calls each person to build a real bond with the Qur'an through reading, care, and regular practice."},"teachings":["Being devoted to the Qur'an is linked with honor in the Hereafter.","Careful recitation matters, not only reading quickly.","A believer should build a lasting connection with the Qur'an.","The Qur'an can raise a person by Allah's permission."],"related_hadiths":[{"id":"1465","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1466","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1474","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Recite, Ascend, and Rise with the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. The devoted companion of the Qur'an is told to recite, ascend, and rise by the verses he recited."},"heading":{"title":"Companion of the Qur'an Hadith: Recite and Ascend","description":"This hadith about the companion of the Qur'an gives hope and also reminds us to stay close to recitation. The Messenger of Allah said that the one devoted to the Qur'an will be told to recite, ascend, and recite carefully, just as he used to recite carefully in the world. His place will be at the last verse he recites. The wording points to steady connection with the Qur'an, not rushed reading. It highlights careful recitation and a life shaped by the words of Allah. The hadith does not ask us to compare ourselves with others. It calls each person to build a real bond with the Qur'an through reading, care, and regular practice."},"teachings":["Being devoted to the Qur'an is linked with honor in the Hereafter.","Careful recitation matters, not only reading quickly.","A believer should build a lasting connection with the Qur'an.","The Qur'an can raise a person by Allah's permission."],"related_hadiths":[{"id":"1465","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1466","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1474","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E283" s="4" t="n"/>
@@ -6990,7 +6994,7 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Clear Qur'an Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas described the Prophet's Qur'an recitation as clear, with long accents expressed properly."},"heading":{"title":"Prophet's Qur'an Recitation Hadith: Clear and Measured Reading","description":"This hadith gives a small but useful picture of the Prophet's Qur'an recitation. Qatadah asked Anas about how the Prophet recited the Qur'an. Anas answered that he used to express the long accents clearly. The hadith focuses on the sound and care of recitation. It does not give a long description, but it teaches that Qur'an reading should not be careless or rushed. Clear recitation helps the words be heard properly. For anyone searching for a hadith about tajweed, madd, or the Prophet's recitation style, this narration points to careful pronunciation. The main lesson is to respect the Qur'an by reciting it with attention and clarity, as much as one is able."},"teachings":["The Prophet's recitation included clear lengthening of long accents.","Qur'an should be recited with attention, not carelessness.","Asking knowledgeable people about recitation is a useful way to learn.","Clear sound helps preserve the beauty of Qur'an recitation."],"related_hadiths":[{"id":"1466","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1468","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1469","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet's Clear Qur'an Recitation","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas described the Prophet's Qur'an recitation as clear, with long accents expressed properly."},"heading":{"title":"Prophet's Qur'an Recitation Hadith: Clear and Measured Reading","description":"This hadith gives a small but useful picture of the Prophet's Qur'an recitation. Qatadah asked Anas about how the Prophet recited the Qur'an. Anas answered that he used to express the long accents clearly. The hadith focuses on the sound and care of recitation. It does not give a long description, but it teaches that Qur'an reading should not be careless or rushed. Clear recitation helps the words be heard properly. For anyone searching for a hadith about tajweed, madd, or the Prophet's recitation style, this narration points to careful pronunciation. The main lesson is to respect the Qur'an by reciting it with attention and clarity, as much as one is able."},"teachings":["The Prophet's recitation included clear lengthening of long accents.","Qur'an should be recited with attention, not carelessness.","Asking knowledgeable people about recitation is a useful way to learn.","Clear sound helps preserve the beauty of Qur'an recitation."],"related_hadiths":[{"id":"1466","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1468","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1469","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E284" s="4" t="n"/>
@@ -7013,7 +7017,7 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reciting Surah Al-Fath on the Conquest Day","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited Surah Al-Fath on his she-camel on the day of the Conquest of Mecca."},"heading":{"title":"Surah Al-Fath Hadith: The Prophet Reciting on His She-Camel","description":"This hadith records a clear scene from the day of the Conquest of Mecca. Abdullah ibn Mughaffal said that he saw the Messenger of Allah riding his she-camel while reciting Surah Al-Fath. The narration also says he repeated each verse several times. The hadith is not giving a long ruling; it is showing an observed act of the Prophet. The main point is Qur'an recitation in a real moment of life, even while riding. For people searching for Surah Al-Fath hadith or Prophet recitation on the conquest of Mecca, this narration gives a direct report. It also connects careful recitation with a major event, without adding details beyond what the text itself says."},"teachings":["The Prophet recited Qur'an while riding his she-camel.","Surah Al-Fath was recited by the Prophet on the day of the Conquest of Mecca.","Repeating verses can be part of meaningful recitation.","A Companion carefully observed and reported the Prophet's recitation."],"related_hadiths":[{"id":"1465","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1466","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1468","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reciting Surah Al-Fath on the Conquest Day","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet recited Surah Al-Fath on his she-camel on the day of the Conquest of Mecca."},"heading":{"title":"Surah Al-Fath Hadith: The Prophet Reciting on His She-Camel","description":"This hadith records a clear scene from the day of the Conquest of Mecca. Abdullah ibn Mughaffal said that he saw the Messenger of Allah riding his she-camel while reciting Surah Al-Fath. The narration also says he repeated each verse several times. The hadith is not giving a long ruling; it is showing an observed act of the Prophet. The main point is Qur'an recitation in a real moment of life, even while riding. For people searching for Surah Al-Fath hadith or Prophet recitation on the conquest of Mecca, this narration gives a direct report. It also connects careful recitation with a major event, without adding details beyond what the text itself says."},"teachings":["The Prophet recited Qur'an while riding his she-camel.","Surah Al-Fath was recited by the Prophet on the day of the Conquest of Mecca.","Repeating verses can be part of meaningful recitation.","A Companion carefully observed and reported the Prophet's recitation."],"related_hadiths":[{"id":"1465","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1466","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1468","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E285" s="4" t="n"/>
@@ -7036,7 +7040,7 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Beautify the Qur'an with Your Voice","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught believers to beautify Qur'an recitation with their voices."},"heading":{"title":"Beautify the Qur'an with Your Voice Hadith","description":"This short hadith gives a direct teaching about Qur'an recitation. Al-Bara' ibn Azib narrated that the Prophet said to beautify the Qur'an with your voices. The wording is simple, but its message is strong. A believer should not treat recitation as dry reading. The voice should carry care, respect, and beauty, while still staying within proper recitation. This hadith is often searched as beautify the Quran with your voice hadith. It reminds readers that sound matters when reciting the words of Allah. The hadith does not demand a perfect voice from every person. It points to the effort of making recitation pleasant and respectful with the voice one has."},"teachings":["The Qur'an should be recited with a voice that shows care and respect.","Beautiful recitation is encouraged by the Prophet.","The aim is to beautify the Qur'an, not to show off the voice.","Every believer can try to improve recitation according to ability."],"related_hadiths":[{"id":"1469","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1471","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1473","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Beautify the Qur'an with Your Voice","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught believers to beautify Qur'an recitation with their voices."},"heading":{"title":"Beautify the Qur'an with Your Voice Hadith","description":"This short hadith gives a direct teaching about Qur'an recitation. Al-Bara' ibn Azib narrated that the Prophet said to beautify the Qur'an with your voices. The wording is simple, but its message is strong. A believer should not treat recitation as dry reading. The voice should carry care, respect, and beauty, while still staying within proper recitation. This hadith is often searched as beautify the Quran with your voice hadith. It reminds readers that sound matters when reciting the words of Allah. The hadith does not demand a perfect voice from every person. It points to the effort of making recitation pleasant and respectful with the voice one has."},"teachings":["The Qur'an should be recited with a voice that shows care and respect.","Beautiful recitation is encouraged by the Prophet.","The aim is to beautify the Qur'an, not to show off the voice.","Every believer can try to improve recitation according to ability."],"related_hadiths":[{"id":"1469","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1471","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1473","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E286" s="4" t="n"/>
@@ -7059,7 +7063,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Chanting the Qur'an with Care","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet warned against leaving the practice of chanting the Qur'an in recitation."},"heading":{"title":"He Who Does Not Chant the Qur'an Is Not One of Us Hadith","description":"This hadith about chanting the Qur'an carries a strong statement. Sa'd ibn Abu Waqqas narrated that the Messenger of Allah said that the one who does not chant the Qur'an is not one of us. The text points to giving the Qur'an a living voice in recitation, not reading it in a flat or careless way. The Arabic idea of taghanni is explained in nearby reports, so the safest lesson from this hadith is to recite with attention, beauty, and respect. The phrase should not be used to shame someone who is trying. Another report in this same group says a person should improve the voice as much as possible. So the focus is effort, not perfection."},"teachings":["Qur'an recitation should be done with care and a living voice.","The Prophet gave strong importance to chanting the Qur'an.","A believer should avoid careless or flat recitation when able.","Effort in improving recitation is part of honoring the Qur'an."],"related_hadiths":[{"id":"1470","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1471","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1472","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Chanting the Qur'an with Care","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet warned against leaving the practice of chanting the Qur'an in recitation."},"heading":{"title":"He Who Does Not Chant the Qur'an Is Not One of Us Hadith","description":"This hadith about chanting the Qur'an carries a strong statement. Sa'd ibn Abu Waqqas narrated that the Messenger of Allah said that the one who does not chant the Qur'an is not one of us. The text points to giving the Qur'an a living voice in recitation, not reading it in a flat or careless way. The Arabic idea of taghanni is explained in nearby reports, so the safest lesson from this hadith is to recite with attention, beauty, and respect. The phrase should not be used to shame someone who is trying. Another report in this same group says a person should improve the voice as much as possible. So the focus is effort, not perfection."},"teachings":["Qur'an recitation should be done with care and a living voice.","The Prophet gave strong importance to chanting the Qur'an.","A believer should avoid careless or flat recitation when able.","Effort in improving recitation is part of honoring the Qur'an."],"related_hadiths":[{"id":"1470","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1471","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1472","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E287" s="4" t="n"/>
@@ -7082,7 +7086,7 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping the Forelock Without Untying the Turban","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration describes wiping the forelock while wearing a turban without untying it."},"heading":{"title":"Hadith About Wiping Forelock in Wudu with a Turban","description":"This hadith about wiping the forelock in wudu gives a clear eye-witness report from Anas ibn Malik. He saw the Messenger of Allah (صلى الله عليه وسلم) performing ablution while wearing a Qutri turban. The Prophet inserted his hand under the turban, wiped over the front part of his head, and did not untie the turban. The core message is about how the wiping was done in that moment. The text does not say that he removed the turban, nor does it say he wiped the whole head in this specific report. It says he wiped the forelock and left the turban tied. For readers searching wiping over turban hadith, this narration gives a simple description of the Prophet’s action during wudu."},"teachings":["The Prophet (صلى الله عليه وسلم) wiped the front of his head while wearing a turban.","He did not untie the turban in this report.","The narration is based on what Anas ibn Malik saw.","Wudu practice should be described with the same care as the text."],"related_hadiths":[{"id":"204","book_id":"1","label":"Sahih Bukhari"},{"id":"561","book_id":"6","label":"Sunan Ibn Majah"},{"id":"203","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping the Forelock Without Untying the Turban","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration describes wiping the forelock while wearing a turban without untying it."},"heading":{"title":"Hadith About Wiping Forelock in Wudu with a Turban","description":"This hadith about wiping the forelock in wudu gives a clear eye-witness report from Anas ibn Malik. He saw the Messenger of Allah (صلى الله عليه وسلم) performing ablution while wearing a Qutri turban. The Prophet inserted his hand under the turban, wiped over the front part of his head, and did not untie the turban. The core message is about how the wiping was done in that moment. The text does not say that he removed the turban, nor does it say he wiped the whole head in this specific report. It says he wiped the forelock and left the turban tied. For readers searching wiping over turban hadith, this narration gives a simple description of the Prophet’s action during wudu."},"teachings":["The Prophet (صلى الله عليه وسلم) wiped the front of his head while wearing a turban.","He did not untie the turban in this report.","The narration is based on what Anas ibn Malik saw.","Wudu practice should be described with the same care as the text."],"related_hadiths":[{"id":"204","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"561","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"203","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E288" s="4" t="n"/>
@@ -7105,7 +7109,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Recite Beautifully as Much as Possible","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches chanting the Qur'an and improving the voice as much as one can."},"heading":{"title":"Chant the Qur'an as Much as You Can: Hadith on Voice and Effort","description":"This hadith adds a helpful balance to the topic of beautiful Qur'an recitation. Abu Lubabah narrated that he heard the Messenger of Allah say that the one who does not chant the Qur'an is not one of us. Then the narrator asked Ibn Abi Mulaykah about someone who does not have a pleasant voice. His answer was simple and kind: he should recite with a pleasant voice as much as possible. This is an important point for anyone worried about not having a naturally beautiful voice. The hadith points to effort, not showing off. The goal is to honor the Qur'an with the best voice one can manage, while accepting that people have different abilities."},"teachings":["Chanting the Qur'an is encouraged in recitation.","A person without a naturally pleasant voice should still try their best.","The focus is sincere effort, not perfect sound.","Improving one's recitation is a practical way to respect the Qur'an."],"related_hadiths":[{"id":"1469","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1470","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1473","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Recite Beautifully as Much as Possible","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches chanting the Qur'an and improving the voice as much as one can."},"heading":{"title":"Chant the Qur'an as Much as You Can: Hadith on Voice and Effort","description":"This hadith adds a helpful balance to the topic of beautiful Qur'an recitation. Abu Lubabah narrated that he heard the Messenger of Allah say that the one who does not chant the Qur'an is not one of us. Then the narrator asked Ibn Abi Mulaykah about someone who does not have a pleasant voice. His answer was simple and kind: he should recite with a pleasant voice as much as possible. This is an important point for anyone worried about not having a naturally beautiful voice. The hadith points to effort, not showing off. The goal is to honor the Qur'an with the best voice one can manage, while accepting that people have different abilities."},"teachings":["Chanting the Qur'an is encouraged in recitation.","A person without a naturally pleasant voice should still try their best.","The focus is sincere effort, not perfect sound.","Improving one's recitation is a practical way to respect the Qur'an."],"related_hadiths":[{"id":"1469","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1470","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1473","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E289" s="4" t="n"/>
@@ -7128,7 +7132,7 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Prophet Chanting the Qur'an Aloud","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah listens in a special way to a Prophet with a good voice chanting the Qur'an aloud."},"heading":{"title":"Allah Listens to a Prophet Chanting the Qur'an Aloud Hadith","description":"This hadith from Abu Hurairah speaks about the beauty of Qur'an recitation from a Prophet with a good voice. The Messenger of Allah said that Allah has not listened to anything as He does to a Prophet chanting the Qur'an with a loud voice. The wording is focused and should be read as it stands. It shows the high status of Qur'an recitation, a beautiful voice, and audible recitation when done in the right setting. The hadith is often searched with the phrase Allah listens to Quran recitation hadith. It does not tell ordinary readers to compete with others. Rather, it teaches respect for Qur'an recitation and shows that a good voice used for the Qur'an is a praised thing."},"teachings":["A good voice used for Qur'an recitation is praised in this hadith.","Audible Qur'an recitation has a special mention in the narration.","The hadith highlights the honor of a Prophet reciting the Qur'an.","Beautiful recitation should be connected to the Qur'an, not personal display."],"related_hadiths":[{"id":"1468","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1469","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1471","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Prophet Chanting the Qur'an Aloud","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah listens in a special way to a Prophet with a good voice chanting the Qur'an aloud."},"heading":{"title":"Allah Listens to a Prophet Chanting the Qur'an Aloud Hadith","description":"This hadith from Abu Hurairah speaks about the beauty of Qur'an recitation from a Prophet with a good voice. The Messenger of Allah said that Allah has not listened to anything as He does to a Prophet chanting the Qur'an with a loud voice. The wording is focused and should be read as it stands. It shows the high status of Qur'an recitation, a beautiful voice, and audible recitation when done in the right setting. The hadith is often searched with the phrase Allah listens to Quran recitation hadith. It does not tell ordinary readers to compete with others. Rather, it teaches respect for Qur'an recitation and shows that a good voice used for the Qur'an is a praised thing."},"teachings":["A good voice used for Qur'an recitation is praised in this hadith.","Audible Qur'an recitation has a special mention in the narration.","The hadith highlights the honor of a Prophet reciting the Qur'an.","Beautiful recitation should be connected to the Qur'an, not personal display."],"related_hadiths":[{"id":"1468","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1469","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1471","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E290" s="4" t="n"/>
@@ -7151,7 +7155,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning Against Forgetting the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith warns about reciting the Qur'an and then forgetting it."},"heading":{"title":"Forgetting the Qur'an Hadith: A Serious Warning","description":"This hadith gives a serious warning about forgetting the Qur'an after reciting it. Sa'd ibn Ubadah narrated that the Prophet said no person recites the Qur'an and then forgets it except that he will meet Allah on the Day of Judgment in a maimed condition, or as the translation notes, empty-handed or with no excuse. The wording is strong, so the explanation should stay careful and not soften it too much or add new details. The core teaching is that Qur'an recitation brings responsibility. A person who learns and recites should try to keep reviewing it. For searches like hadith about forgetting Quran, this narration reminds readers that the Qur'an should not be neglected after being learned."},"teachings":["Learning and reciting the Qur'an carries responsibility.","Forgetting the Qur'an after reciting it is treated seriously in this hadith.","Regular review helps a person avoid neglecting what they learned.","The warning should lead to care, not despair."],"related_hadiths":[{"id":"1464","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1465","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1466","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning Against Forgetting the Qur'an","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith warns about reciting the Qur'an and then forgetting it."},"heading":{"title":"Forgetting the Qur'an Hadith: A Serious Warning","description":"This hadith gives a serious warning about forgetting the Qur'an after reciting it. Sa'd ibn Ubadah narrated that the Prophet said no person recites the Qur'an and then forgets it except that he will meet Allah on the Day of Judgment in a maimed condition, or as the translation notes, empty-handed or with no excuse. The wording is strong, so the explanation should stay careful and not soften it too much or add new details. The core teaching is that Qur'an recitation brings responsibility. A person who learns and recites should try to keep reviewing it. For searches like hadith about forgetting Quran, this narration reminds readers that the Qur'an should not be neglected after being learned."},"teachings":["Learning and reciting the Qur'an carries responsibility.","Forgetting the Qur'an after reciting it is treated seriously in this hadith.","Regular review helps a person avoid neglecting what they learned.","The warning should lead to care, not despair."],"related_hadiths":[{"id":"1464","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1465","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1466","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E291" s="4" t="n"/>
@@ -7174,7 +7178,7 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Qur'an Revealed in Seven Modes","description":"$book_name$ $hadith_number$ - $chapter_name$. Umar learned that the Qur'an was sent down in seven modes and that ease was allowed in recitation."},"heading":{"title":"Seven Modes of Qur'an Recitation Hadith","description":"This hadith explains the seven modes of Qur'an recitation through an event involving Umar ibn al-Khattab and Hisham ibn Hakim. Umar heard Hisham reciting Surah Al-Furqan in a way different from what he had learned from the Messenger of Allah. He waited until Hisham finished, then brought him to the Prophet. The Prophet asked Hisham to recite and said that it was sent down that way. Then Umar recited, and the Prophet said the same about his recitation. He then explained that the Qur'an was sent down in seven modes, so people should recite what comes most easily. The hadith teaches care before judging another reciter and confirms allowed differences taught by the Prophet."},"teachings":["Allowed differences in recitation can exist within what the Prophet approved.","Umar waited until the recitation ended before taking action.","The Prophet checked both recitations before giving judgment.","The Qur'an was sent down in seven modes, with ease in recitation."],"related_hadiths":[{"id":"1476","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1477","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1478","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Qur'an Revealed in Seven Modes","description":"$book_name$ $hadith_number$ - $chapter_name$. Umar learned that the Qur'an was sent down in seven modes and that ease was allowed in recitation."},"heading":{"title":"Seven Modes of Qur'an Recitation Hadith","description":"This hadith explains the seven modes of Qur'an recitation through an event involving Umar ibn al-Khattab and Hisham ibn Hakim. Umar heard Hisham reciting Surah Al-Furqan in a way different from what he had learned from the Messenger of Allah. He waited until Hisham finished, then brought him to the Prophet. The Prophet asked Hisham to recite and said that it was sent down that way. Then Umar recited, and the Prophet said the same about his recitation. He then explained that the Qur'an was sent down in seven modes, so people should recite what comes most easily. The hadith teaches care before judging another reciter and confirms allowed differences taught by the Prophet."},"teachings":["Allowed differences in recitation can exist within what the Prophet approved.","Umar waited until the recitation ended before taking action.","The Prophet checked both recitations before giving judgment.","The Qur'an was sent down in seven modes, with ease in recitation."],"related_hadiths":[{"id":"1476","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1477","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1478","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E292" s="4" t="n"/>
@@ -7197,7 +7201,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seven Modes Share One Meaning","description":"$book_name$ $hadith_number$ - $chapter_name$. Al-Zuhri explained that the modes aimed at one point and did not differ in halal or haram."},"heading":{"title":"Seven Ahruf Meaning: Not Different in Halal and Haram","description":"This report gives a short explanation from Al-Zuhri about the seven modes of reciting the Qur'an. He said that these modes aimed at the same point and did not differ in matters of lawful and unlawful. This is important because it keeps the reader from thinking that the seven modes changed the religion's commands. The report is not a long study of the topic. It simply explains that the differences were within one matter and did not create a difference in halal and haram. For people searching seven ahruf meaning or seven modes Quran hadith, this narration gives a careful point: allowed recitation differences did not mean different religious rulings in lawful and unlawful matters."},"teachings":["The seven modes aimed at the same point in meaning.","They did not differ in matters of halal and haram according to Al-Zuhri.","Allowed recitation differences should not be treated as conflicting rulings.","Short explanatory reports can help clarify longer hadiths."],"related_hadiths":[{"id":"1475","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1477","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1478","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Seven Modes Share One Meaning","description":"$book_name$ $hadith_number$ - $chapter_name$. Al-Zuhri explained that the modes aimed at one point and did not differ in halal or haram."},"heading":{"title":"Seven Ahruf Meaning: Not Different in Halal and Haram","description":"This report gives a short explanation from Al-Zuhri about the seven modes of reciting the Qur'an. He said that these modes aimed at the same point and did not differ in matters of lawful and unlawful. This is important because it keeps the reader from thinking that the seven modes changed the religion's commands. The report is not a long study of the topic. It simply explains that the differences were within one matter and did not create a difference in halal and haram. For people searching seven ahruf meaning or seven modes Quran hadith, this narration gives a careful point: allowed recitation differences did not mean different religious rulings in lawful and unlawful matters."},"teachings":["The seven modes aimed at the same point in meaning.","They did not differ in matters of halal and haram according to Al-Zuhri.","Allowed recitation differences should not be treated as conflicting rulings.","Short explanatory reports can help clarify longer hadiths."],"related_hadiths":[{"id":"1475","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1477","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1478","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E293" s="4" t="n"/>
@@ -7220,7 +7224,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Each Qur'an Mode Is Sufficient","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet described the Qur'an being recited in up to seven modes, each sufficient."},"heading":{"title":"Seven Modes of the Qur'an: Each Mode Is Sufficient","description":"This hadith from Ubayy ibn Ka'b gives more detail about the Qur'an being recited in several modes. The Prophet said he was asked whether to recite in one mode or two. The angel with him told him to ask for two, then three, until the matter reached seven modes. The narration then says that each mode is sufficient and healing. It gives examples of endings such as all-hearing and all-knowing, or all-powerful and all-wise, while also setting a limit: one should not finish a verse of punishment with mercy or a verse of mercy with punishment. The hadith shows ease in recitation, but also keeps meaning and proper placement from being confused."},"teachings":["The seven modes were connected with ease for recitation.","Each mode is described as sufficient in the narration.","Meaning should not be changed by ending punishment with mercy or mercy with punishment.","The hadith balances ease with care in Qur'an recitation."],"related_hadiths":[{"id":"1475","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1476","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1478","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Each Qur'an Mode Is Sufficient","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet described the Qur'an being recited in up to seven modes, each sufficient."},"heading":{"title":"Seven Modes of the Qur'an: Each Mode Is Sufficient","description":"This hadith from Ubayy ibn Ka'b gives more detail about the Qur'an being recited in several modes. The Prophet said he was asked whether to recite in one mode or two. The angel with him told him to ask for two, then three, until the matter reached seven modes. The narration then says that each mode is sufficient and healing. It gives examples of endings such as all-hearing and all-knowing, or all-powerful and all-wise, while also setting a limit: one should not finish a verse of punishment with mercy or a verse of mercy with punishment. The hadith shows ease in recitation, but also keeps meaning and proper placement from being confused."},"teachings":["The seven modes were connected with ease for recitation.","Each mode is described as sufficient in the narration.","Meaning should not be changed by ending punishment with mercy or mercy with punishment.","The hadith balances ease with care in Qur'an recitation."],"related_hadiths":[{"id":"1475","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1476","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1478","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E294" s="4" t="n"/>
@@ -7243,7 +7247,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Ummah and the Seven Harfs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asked for ease for his community until recitation in seven harfs was allowed."},"heading":{"title":"Seven Harfs Hadith: Ease for the Ummah in Qur'an Recitation","description":"This hadith from Ubayy ibn Ka'b describes the Prophet at the pool of Banu Ghifar when Gabriel came to him. Gabriel said that Allah commanded him to make his community recite the Qur'an in one harf. The Prophet asked Allah for pardon and forgiveness, saying his community did not have the strength for that. The message came again, and the matter continued until it reached seven harfs. Finally, the Prophet was told that his community should recite in seven harfs, and whichever harf they read upon would be correct. The hadith highlights ease for the ummah in Qur'an recitation and shows the Prophet's concern for his community's ability."},"teachings":["The Prophet asked for ease for his community.","The recitation of the Qur'an was allowed in seven harfs in this narration.","The hadith shows concern for what the community could bear.","Whichever allowed harf they recited upon was described as correct."],"related_hadiths":[{"id":"1475","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1476","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1477","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Ummah and the Seven Harfs","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asked for ease for his community until recitation in seven harfs was allowed."},"heading":{"title":"Seven Harfs Hadith: Ease for the Ummah in Qur'an Recitation","description":"This hadith from Ubayy ibn Ka'b describes the Prophet at the pool of Banu Ghifar when Gabriel came to him. Gabriel said that Allah commanded him to make his community recite the Qur'an in one harf. The Prophet asked Allah for pardon and forgiveness, saying his community did not have the strength for that. The message came again, and the matter continued until it reached seven harfs. Finally, the Prophet was told that his community should recite in seven harfs, and whichever harf they read upon would be correct. The hadith highlights ease for the ummah in Qur'an recitation and shows the Prophet's concern for his community's ability."},"teachings":["The Prophet asked for ease for his community.","The recitation of the Qur'an was allowed in seven harfs in this narration.","The hadith shows concern for what the community could bear.","Whichever allowed harf they recited upon was described as correct."],"related_hadiths":[{"id":"1475","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1476","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1477","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E295" s="4" t="n"/>
@@ -7266,7 +7270,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Supplication Is Worship","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that supplication is worship and recited the verse calling people to invoke Allah."},"heading":{"title":"Supplication Is Worship Hadith: Du'a as an Act of Worship","description":"This hadith gives one of the clearest teachings about du'a. An-Nu'man ibn Bashir narrated that the Prophet said, supplication is itself worship. He then recited the verse in which the Lord says to call on Him and He will answer. The hadith connects du'a directly with worship, not just with asking for needs. When a person makes supplication, he is turning to Allah, showing need, and responding to the command to call upon Him. For searches like dua is worship hadith, this narration is central. The explanation should stay simple: du'a is not a side action with no weight. It is an act of worship taught by the Prophet and supported by the verse he recited."},"teachings":["Du'a is itself an act of worship.","Calling upon Allah is connected to the command in the Qur'an.","Supplication shows a person's need before Allah.","The Prophet taught du'a with a direct Qur'anic proof."],"related_hadiths":[{"id":"1480","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6304","book_id":"1","label":"Sahih Bukhari"},{"id":"6340","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Supplication Is Worship","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that supplication is worship and recited the verse calling people to invoke Allah."},"heading":{"title":"Supplication Is Worship Hadith: Du'a as an Act of Worship","description":"This hadith gives one of the clearest teachings about du'a. An-Nu'man ibn Bashir narrated that the Prophet said, supplication is itself worship. He then recited the verse in which the Lord says to call on Him and He will answer. The hadith connects du'a directly with worship, not just with asking for needs. When a person makes supplication, he is turning to Allah, showing need, and responding to the command to call upon Him. For searches like dua is worship hadith, this narration is central. The explanation should stay simple: du'a is not a side action with no weight. It is an act of worship taught by the Prophet and supported by the verse he recited."},"teachings":["Du'a is itself an act of worship.","Calling upon Allah is connected to the command in the Qur'an.","Supplication shows a person's need before Allah.","The Prophet taught du'a with a direct Qur'anic proof."],"related_hadiths":[{"id":"1480","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"6304","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6340","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E296" s="4" t="n"/>
@@ -7289,7 +7293,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rubbing the Toes in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows the Prophet rubbing his toes with his little finger during ablution."},"heading":{"title":"Hadith About Cleaning Toes in Wudu","description":"This hadith about cleaning toes in wudu is short but useful. Al-Mustawrid ibn Shaddad said that he saw the Messenger of Allah (صلى الله عليه وسلم) rubbing his toes with his little finger when he performed ablution. The text points to careful washing of the feet, especially between or around the toes. It does not describe a long method, but it gives one clear action: using the little finger to rub the toes. For someone searching how to wash feet in wudu or rubbing toes in wudu hadith, this narration highlights attention to parts that may be missed if a person rushes. The teaching is simple: wudu should be done with care, and the feet should not be treated as an afterthought."},"teachings":["The Prophet (صلى الله عليه وسلم) rubbed his toes during wudu.","The little finger is mentioned in the report.","Feet should be washed with care during ablution.","Small details in wudu can help prevent careless washing."],"related_hadiths":[{"id":"135","book_id":"4","label":"Sunan Abu Dawud"},{"id":"182","book_id":"1","label":"Sahih Bukhari"},{"id":"191","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rubbing the Toes in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows the Prophet rubbing his toes with his little finger during ablution."},"heading":{"title":"Hadith About Cleaning Toes in Wudu","description":"This hadith about cleaning toes in wudu is short but useful. Al-Mustawrid ibn Shaddad said that he saw the Messenger of Allah (صلى الله عليه وسلم) rubbing his toes with his little finger when he performed ablution. The text points to careful washing of the feet, especially between or around the toes. It does not describe a long method, but it gives one clear action: using the little finger to rub the toes. For someone searching how to wash feet in wudu or rubbing toes in wudu hadith, this narration highlights attention to parts that may be missed if a person rushes. The teaching is simple: wudu should be done with care, and the feet should not be treated as an afterthought."},"teachings":["The Prophet (صلى الله عليه وسلم) rubbed his toes during wudu.","The little finger is mentioned in the report.","Feet should be washed with care during ablution.","Small details in wudu can help prevent careless washing."],"related_hadiths":[{"id":"135","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"182","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"191","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E297" s="4" t="n"/>
@@ -7312,7 +7316,7 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoid Exaggeration in Supplication","description":"$book_name$ $hadith_number$ - $chapter_name$. Sa'd warned his son not to exaggerate in du'a and taught concise asking for Paradise and refuge from Hell."},"heading":{"title":"Avoid Exaggeration in Du'a Hadith","description":"This hadith teaches balance in supplication. A son of Sa'd was making a long du'a, asking for Paradise, its blessings, its pleasure, and many extra details. He also sought refuge from Hell, its chains, collars, and many extra details. His father Sa'd told him that he heard the Messenger of Allah say that people would exaggerate in supplication, and he warned him not to be among them. Sa'd then explained the simple point: if a person is granted Paradise, he is granted the good within it; and if he is protected from Hell, he is protected from its evil. The hadith does not stop a person from making du'a. It teaches concise, balanced, and meaningful supplication."},"teachings":["Du'a should be balanced and not exaggerated.","Asking for Paradise includes the good that is in it.","Seeking refuge from Hell includes protection from its evil.","A parent may correct a child's supplication with gentle teaching."],"related_hadiths":[{"id":"1479","book_id":"4","label":"Sunan Abu Dawud"},{"id":"6340","book_id":"1","label":"Sahih Bukhari"},{"id":"6304","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoid Exaggeration in Supplication","description":"$book_name$ $hadith_number$ - $chapter_name$. Sa'd warned his son not to exaggerate in du'a and taught concise asking for Paradise and refuge from Hell."},"heading":{"title":"Avoid Exaggeration in Du'a Hadith","description":"This hadith teaches balance in supplication. A son of Sa'd was making a long du'a, asking for Paradise, its blessings, its pleasure, and many extra details. He also sought refuge from Hell, its chains, collars, and many extra details. His father Sa'd told him that he heard the Messenger of Allah say that people would exaggerate in supplication, and he warned him not to be among them. Sa'd then explained the simple point: if a person is granted Paradise, he is granted the good within it; and if he is protected from Hell, he is protected from its evil. The hadith does not stop a person from making du'a. It teaches concise, balanced, and meaningful supplication."},"teachings":["Du'a should be balanced and not exaggerated.","Asking for Paradise includes the good that is in it.","Seeking refuge from Hell includes protection from its evil.","A parent may correct a child's supplication with gentle teaching."],"related_hadiths":[{"id":"1479","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"6340","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"6304","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E298" s="4" t="n"/>
@@ -7335,7 +7339,7 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Proper Way to Begin Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn to begin dua with praise of Allah and blessings upon the Prophet before asking."},"heading":{"title":"Hadith About the Proper Way to Make Dua in Prayer","description":"This hadith teaches a clear adab of dua in prayer. The Prophet (صلى الله عليه وسلم) heard a person making supplication, but the person did not first mention Allah’s greatness and did not send blessings upon the Prophet (صلى الله عليه وسلم). The Prophet (صلى الله عليه وسلم) said that he had made haste. Then he taught that when a person prays, he should begin by praising and exalting his Lord, then send blessings upon the Prophet (صلى الله عليه وسلم), and after that ask Allah for whatever he wishes. The main lesson is that dua is not only about asking. It is also about showing respect, praise, and love before asking. This makes the hadith important for anyone searching for the proper way to make dua, dua in salah, and sending salawat before dua."},"teachings":["Begin supplication by praising and exalting Allah.","Send blessings upon the Prophet (صلى الله عليه وسلم) before making personal requests.","Avoid rushing into dua without the manners taught in the hadith.","After praise and salawat, a person may ask Allah for what he wishes."],"related_hadiths":[{"id":"1483","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1484","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1493","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Proper Way to Begin Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn to begin dua with praise of Allah and blessings upon the Prophet before asking."},"heading":{"title":"Hadith About the Proper Way to Make Dua in Prayer","description":"This hadith teaches a clear adab of dua in prayer. The Prophet (صلى الله عليه وسلم) heard a person making supplication, but the person did not first mention Allah’s greatness and did not send blessings upon the Prophet (صلى الله عليه وسلم). The Prophet (صلى الله عليه وسلم) said that he had made haste. Then he taught that when a person prays, he should begin by praising and exalting his Lord, then send blessings upon the Prophet (صلى الله عليه وسلم), and after that ask Allah for whatever he wishes. The main lesson is that dua is not only about asking. It is also about showing respect, praise, and love before asking. This makes the hadith important for anyone searching for the proper way to make dua, dua in salah, and sending salawat before dua."},"teachings":["Begin supplication by praising and exalting Allah.","Send blessings upon the Prophet (صلى الله عليه وسلم) before making personal requests.","Avoid rushing into dua without the manners taught in the hadith.","After praise and salawat, a person may ask Allah for what he wishes."],"related_hadiths":[{"id":"1483","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1484","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1493","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E299" s="4" t="n"/>
@@ -7358,7 +7362,7 @@
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Comprehensive Supplication","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet loved comprehensive duas, teaching believers to ask with broad and meaningful words."},"heading":{"title":"Hadith About Comprehensive Dua and Simple Supplication","description":"This hadith from Aishah explains that the Messenger of Allah (صلى الله عليه وسلم) liked comprehensive supplication and left other kinds. A comprehensive dua is a supplication that carries wide meaning in a few words. The text does not list examples here, so the lesson should stay with what is stated: the Prophet (صلى الله عليه وسلم) preferred broad, meaningful supplication over other forms. This teaches a simple way to think about dua. A person does not always need long speech. Short and complete words can carry strong meaning when asking Allah. This hadith is useful for people searching for comprehensive dua, short duas in Islam, and prophetic supplication. It points to a balanced style: ask with words that are full, clear, and meaningful."},"teachings":["The Prophet (صلى الله عليه وسلم) liked supplications with broad meaning.","A dua does not need to be long to be meaningful.","Choosing complete and clear words in dua is a good practice.","The hadith encourages focused supplication rather than scattered wording."],"related_hadiths":[{"id":"1481","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1493","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1500","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Comprehensive Supplication","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet loved comprehensive duas, teaching believers to ask with broad and meaningful words."},"heading":{"title":"Hadith About Comprehensive Dua and Simple Supplication","description":"This hadith from Aishah explains that the Messenger of Allah (صلى الله عليه وسلم) liked comprehensive supplication and left other kinds. A comprehensive dua is a supplication that carries wide meaning in a few words. The text does not list examples here, so the lesson should stay with what is stated: the Prophet (صلى الله عليه وسلم) preferred broad, meaningful supplication over other forms. This teaches a simple way to think about dua. A person does not always need long speech. Short and complete words can carry strong meaning when asking Allah. This hadith is useful for people searching for comprehensive dua, short duas in Islam, and prophetic supplication. It points to a balanced style: ask with words that are full, clear, and meaningful."},"teachings":["The Prophet (صلى الله عليه وسلم) liked supplications with broad meaning.","A dua does not need to be long to be meaningful.","Choosing complete and clear words in dua is a good practice.","The hadith encourages focused supplication rather than scattered wording."],"related_hadiths":[{"id":"1481","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1493","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1500","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E300" s="4" t="n"/>
@@ -7381,7 +7385,7 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Be Firm When Asking Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ask Allah with firm hope, not with doubtful words, because no one can force Him."},"heading":{"title":"Hadith About Being Firm When Making Dua","description":"This hadith teaches believers how to speak when asking Allah. The Prophet (صلى الله عليه وسلم) said that a person should not say, “O Allah, forgive me if You please” or “show mercy to me if You please.” Instead, the person should be firm in asking. The reason given in the hadith is clear: no one can force Allah. This means the servant should ask with need, hope, and trust, not with wording that sounds unsure. The hadith is not telling a person to be proud or demanding. It is teaching proper wording in supplication. For people searching for hadith about dua, asking Allah firmly, or saying inshaAllah in dua, this narration gives direct guidance: ask Allah clearly and sincerely."},"teachings":["Do not phrase dua for forgiveness or mercy in a doubtful way.","Ask Allah with clear and firm wording.","No one can force Allah, so the servant asks with humility and trust.","The hadith teaches careful manners in the words of supplication."],"related_hadiths":[{"id":"1484","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1481","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1493","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Be Firm When Asking Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ask Allah with firm hope, not with doubtful words, because no one can force Him."},"heading":{"title":"Hadith About Being Firm When Making Dua","description":"This hadith teaches believers how to speak when asking Allah. The Prophet (صلى الله عليه وسلم) said that a person should not say, “O Allah, forgive me if You please” or “show mercy to me if You please.” Instead, the person should be firm in asking. The reason given in the hadith is clear: no one can force Allah. This means the servant should ask with need, hope, and trust, not with wording that sounds unsure. The hadith is not telling a person to be proud or demanding. It is teaching proper wording in supplication. For people searching for hadith about dua, asking Allah firmly, or saying inshaAllah in dua, this narration gives direct guidance: ask Allah clearly and sincerely."},"teachings":["Do not phrase dua for forgiveness or mercy in a doubtful way.","Ask Allah with clear and firm wording.","No one can force Allah, so the servant asks with humility and trust.","The hadith teaches careful manners in the words of supplication."],"related_hadiths":[{"id":"1484","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1481","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1493","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E301" s="4" t="n"/>
@@ -7404,7 +7408,7 @@
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Rush Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. A supplication is answered while a person avoids impatience and does not complain that it was unanswered."},"heading":{"title":"Hadith About Not Being Impatient With Dua","description":"This hadith teaches patience in supplication. The Messenger of Allah (صلى الله عليه وسلم) said that one of you is granted an answer to his supplication as long as he does not say, “I prayed but I was not granted an answer.” The hadith focuses on one clear mistake: becoming impatient and speaking as if dua has failed. It teaches a believer to keep asking Allah without turning the delay into complaint. The text does not explain the timing or form of the answer, so the explanation should remain simple: do not rush and do not give up with such words. This hadith is very relevant for searches like dua not answered, hadith about patience in dua, and not rushing supplication."},"teachings":["Avoid saying that your dua was not answered in a complaining way.","Patience is part of the manners of supplication.","A person should not rush the matter of dua.","The hadith encourages continued hope when asking Allah."],"related_hadiths":[{"id":"1483","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1481","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1488","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Rush Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. A supplication is answered while a person avoids impatience and does not complain that it was unanswered."},"heading":{"title":"Hadith About Not Being Impatient With Dua","description":"This hadith teaches patience in supplication. The Messenger of Allah (صلى الله عليه وسلم) said that one of you is granted an answer to his supplication as long as he does not say, “I prayed but I was not granted an answer.” The hadith focuses on one clear mistake: becoming impatient and speaking as if dua has failed. It teaches a believer to keep asking Allah without turning the delay into complaint. The text does not explain the timing or form of the answer, so the explanation should remain simple: do not rush and do not give up with such words. This hadith is very relevant for searches like dua not answered, hadith about patience in dua, and not rushing supplication."},"teachings":["Avoid saying that your dua was not answered in a complaining way.","Patience is part of the manners of supplication.","A person should not rush the matter of dua.","The hadith encourages continued hope when asking Allah."],"related_hadiths":[{"id":"1483","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1481","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1488","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E302" s="4" t="n"/>
@@ -7427,7 +7431,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Palms in Supplication","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions asking with palms raised, wiping the face, privacy, and Abu Dawud’s note on weakness."},"heading":{"title":"Hadith About Raising Palms in Dua and Respecting Privacy","description":"This narration contains several points. It says not to cover the walls, warns against looking into a brother’s letter without permission, and mentions supplicating to Allah with the palms of the hands rather than their backs. It also mentions wiping the face with the hands after finishing supplication. A key part of this entry is Abu Dawud’s own note: he said the tradition came through different chains from Muhammad ibn Ka'b, all of them weak, and that this chain is the best of them, though also weak. So the explanation must be careful. The hadith text points to dua hand position and respect for privacy, while the grading note reminds the reader that this report is weak according to Abu Dawud."},"teachings":["The narration mentions asking Allah with the palms of the hands.","It warns against looking at another person’s letter without permission.","It mentions wiping the face after supplication.","Abu Dawud clearly notes that this narration is weak."],"related_hadiths":[{"id":"1486","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1487","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1492","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Palms in Supplication","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions asking with palms raised, wiping the face, privacy, and Abu Dawud’s note on weakness."},"heading":{"title":"Hadith About Raising Palms in Dua and Respecting Privacy","description":"This narration contains several points. It says not to cover the walls, warns against looking into a brother’s letter without permission, and mentions supplicating to Allah with the palms of the hands rather than their backs. It also mentions wiping the face with the hands after finishing supplication. A key part of this entry is Abu Dawud’s own note: he said the tradition came through different chains from Muhammad ibn Ka'b, all of them weak, and that this chain is the best of them, though also weak. So the explanation must be careful. The hadith text points to dua hand position and respect for privacy, while the grading note reminds the reader that this report is weak according to Abu Dawud."},"teachings":["The narration mentions asking Allah with the palms of the hands.","It warns against looking at another person’s letter without permission.","It mentions wiping the face after supplication.","Abu Dawud clearly notes that this narration is weak."],"related_hadiths":[{"id":"1486","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1487","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1492","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E303" s="4" t="n"/>
@@ -7450,7 +7454,7 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ask With Palms Raised","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that requests to Allah should be made with palms raised, not with backs upward."},"heading":{"title":"Hadith About Making Dua With the Palms of the Hands","description":"This hadith gives a short instruction about the posture of the hands in supplication. The Prophet (صلى الله عليه وسلم) said that when people make requests to Allah, they should do so with the palms of their hands, not with the backs of the hands upward. The narration focuses on a physical manner connected to dua. It does not add a long explanation, so the main message is simple: when asking Allah, the palms are mentioned as the way of asking. Abu Dawud also includes a note from the narrator Sulaiman ibn Abd al-Hamid, saying that Malik ibn Yasar was regarded by them as a Companion of the Prophet (صلى الله عليه وسلم). This hadith is useful for people searching for raising hands in dua, palms up in dua, and dua hand position."},"teachings":["When asking Allah, the palms of the hands are mentioned in this narration.","The backs of the hands should not be used upward when making requests.","The hadith gives guidance on the outward manner of supplication.","Abu Dawud records a note about Malik ibn Yasar being regarded as a Companion."],"related_hadiths":[{"id":"1485","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1487","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1488","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ask With Palms Raised","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught that requests to Allah should be made with palms raised, not with backs upward."},"heading":{"title":"Hadith About Making Dua With the Palms of the Hands","description":"This hadith gives a short instruction about the posture of the hands in supplication. The Prophet (صلى الله عليه وسلم) said that when people make requests to Allah, they should do so with the palms of their hands, not with the backs of the hands upward. The narration focuses on a physical manner connected to dua. It does not add a long explanation, so the main message is simple: when asking Allah, the palms are mentioned as the way of asking. Abu Dawud also includes a note from the narrator Sulaiman ibn Abd al-Hamid, saying that Malik ibn Yasar was regarded by them as a Companion of the Prophet (صلى الله عليه وسلم). This hadith is useful for people searching for raising hands in dua, palms up in dua, and dua hand position."},"teachings":["When asking Allah, the palms of the hands are mentioned in this narration.","The backs of the hands should not be used upward when making requests.","The hadith gives guidance on the outward manner of supplication.","Abu Dawud records a note about Malik ibn Yasar being regarded as a Companion."],"related_hadiths":[{"id":"1485","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1487","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1488","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E304" s="4" t="n"/>
@@ -7473,7 +7477,7 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Palms and Backs in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas saw the Prophet supplicate using the palms of his hands and also their backs upward."},"heading":{"title":"Hadith About the Prophet’s Hand Position in Dua","description":"This narration from Anas ibn Malik describes what he saw from the Messenger of Allah (صلى الله عليه وسلم) during supplication. He said that he saw the Prophet (صلى الله عليه وسلم) supplicating in this manner with the palms of his hands and also with their backs upwards. The report is brief, so the explanation should remain close to its wording. It records an observed action of the Prophet (صلى الله عليه وسلم) in dua. Since other narrations in the same group mention asking with palms, this hadith adds that Anas saw both the palms and backs involved in the manner of supplication. This hadith is useful for users searching for dua hand position, raising hands in dua, and hadith about palms and backs in supplication."},"teachings":["Anas reported what he saw from the Prophet (صلى الله عليه وسلم) in supplication.","The narration mentions the palms of the hands in dua.","It also mentions the backs of the hands being used upward.","The hadith should be explained as an observed action, without adding extra details."],"related_hadiths":[{"id":"1486","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1488","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1490","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Palms and Backs in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas saw the Prophet supplicate using the palms of his hands and also their backs upward."},"heading":{"title":"Hadith About the Prophet’s Hand Position in Dua","description":"This narration from Anas ibn Malik describes what he saw from the Messenger of Allah (صلى الله عليه وسلم) during supplication. He said that he saw the Prophet (صلى الله عليه وسلم) supplicating in this manner with the palms of his hands and also with their backs upwards. The report is brief, so the explanation should remain close to its wording. It records an observed action of the Prophet (صلى الله عليه وسلم) in dua. Since other narrations in the same group mention asking with palms, this hadith adds that Anas saw both the palms and backs involved in the manner of supplication. This hadith is useful for users searching for dua hand position, raising hands in dua, and hadith about palms and backs in supplication."},"teachings":["Anas reported what he saw from the Prophet (صلى الله عليه وسلم) in supplication.","The narration mentions the palms of the hands in dua.","It also mentions the backs of the hands being used upward.","The hadith should be explained as an observed action, without adding extra details."],"related_hadiths":[{"id":"1486","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1488","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1490","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E305" s="4" t="n"/>
@@ -7496,7 +7500,7 @@
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Generosity in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah is generous and does not turn away empty the raised hands of His servant."},"heading":{"title":"Hadith About Raising Hands in Dua and Allah’s Generosity","description":"This hadith gives hope to the person making dua. The Prophet (صلى الله عليه وسلم) said that your Lord is munificent and generous, and He is ashamed to turn away empty the hands of His servant when he raises them to Him. The hadith joins two meanings: Allah’s generosity and the servant raising hands in supplication. It does not teach a person to demand from Allah. Rather, it gives comfort that Allah is generous to His servant. This narration is often searched by people looking for hadith about raising hands in dua, Allah’s generosity, and hope in supplication. The main message is simple and warm: when a servant raises his hands to Allah, he is asking a Lord described here as generous."},"teachings":["Allah is described in the hadith as munificent and generous.","Raising hands to Allah in dua is mentioned with honor.","The hadith gives hope to the servant who supplicates.","A believer should ask Allah while remembering His generosity."],"related_hadiths":[{"id":"1486","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1484","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1493","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Generosity in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Allah is generous and does not turn away empty the raised hands of His servant."},"heading":{"title":"Hadith About Raising Hands in Dua and Allah’s Generosity","description":"This hadith gives hope to the person making dua. The Prophet (صلى الله عليه وسلم) said that your Lord is munificent and generous, and He is ashamed to turn away empty the hands of His servant when he raises them to Him. The hadith joins two meanings: Allah’s generosity and the servant raising hands in supplication. It does not teach a person to demand from Allah. Rather, it gives comfort that Allah is generous to His servant. This narration is often searched by people looking for hadith about raising hands in dua, Allah’s generosity, and hope in supplication. The main message is simple and warm: when a servant raises his hands to Allah, he is asking a Lord described here as generous."},"teachings":["Allah is described in the hadith as munificent and generous.","Raising hands to Allah in dua is mentioned with honor.","The hadith gives hope to the servant who supplicates.","A believer should ask Allah while remembering His generosity."],"related_hadiths":[{"id":"1486","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1484","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1493","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E306" s="4" t="n"/>
@@ -7519,7 +7523,7 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hand Positions in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas described different hand positions for asking, seeking forgiveness, and earnest supplication."},"heading":{"title":"Hadith About Different Hand Positions for Dua","description":"This report from Ibn Abbas describes three manners connected to supplication. When asking for something, he said a person should raise the hands opposite the shoulders or near that level. When asking for forgiveness, he said one should point with one finger. When making earnest supplication, he said one should spread out both hands. The narration is specific and should not be expanded beyond these points. It gives a simple distinction between asking, seeking forgiveness, and earnest pleading. This makes it helpful for readers searching for hand positions in dua, pointing finger in istighfar, and how to raise hands in supplication. The main teaching is that the report describes different outward forms for different types of supplication."},"teachings":["For asking, the hands are described as raised near shoulder level.","For seeking forgiveness, the report mentions pointing with one finger.","For earnest supplication, the report mentions spreading both hands.","The narration separates different types of supplication by outward posture."],"related_hadiths":[{"id":"1490","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1491","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1499","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hand Positions in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas described different hand positions for asking, seeking forgiveness, and earnest supplication."},"heading":{"title":"Hadith About Different Hand Positions for Dua","description":"This report from Ibn Abbas describes three manners connected to supplication. When asking for something, he said a person should raise the hands opposite the shoulders or near that level. When asking for forgiveness, he said one should point with one finger. When making earnest supplication, he said one should spread out both hands. The narration is specific and should not be expanded beyond these points. It gives a simple distinction between asking, seeking forgiveness, and earnest pleading. This makes it helpful for readers searching for hand positions in dua, pointing finger in istighfar, and how to raise hands in supplication. The main teaching is that the report describes different outward forms for different types of supplication."},"teachings":["For asking, the hands are described as raised near shoulder level.","For seeking forgiveness, the report mentions pointing with one finger.","For earnest supplication, the report mentions spreading both hands.","The narration separates different types of supplication by outward posture."],"related_hadiths":[{"id":"1490","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1491","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1499","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E307" s="4" t="n"/>
@@ -7542,7 +7546,7 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu, Wiping Socks, and Prayer Behind an Imam","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports wudu on a journey, wiping over socks, and joining Fajr behind an imam."},"heading":{"title":"Hadith About Travel Wudu and Wiping Over Socks","description":"This hadith about travel wudu records a detailed event during the expedition of Tabuk. Al-Mughirah was with the Messenger of Allah (صلى الله عليه وسلم) before dawn. After the Prophet returned from relieving himself, water was poured for him. He washed his hands and face, worked around the tight sleeves of his gown, washed his forearms to the elbows, wiped his head, and wiped over his socks. The narration then moves to prayer. The people had already started Fajr with Abd al-Rahman ibn Awf leading them. The Prophet joined the row, prayed one rakah behind him, then stood to complete what he had missed. When the Muslims were worried, he said they had done right or done well. The hadith teaches careful wudu on a journey and respect for prayer time and congregation."},"teachings":["The Prophet (صلى الله عليه وسلم) performed wudu carefully even while traveling.","He wiped over his socks in this report.","He joined the congregation behind Abd al-Rahman ibn Awf.","The people were praised for praying on time instead of waiting."],"related_hadiths":[{"id":"182","book_id":"1","label":"Sahih Bukhari"},{"id":"206","book_id":"1","label":"Sahih Bukhari"},{"id":"274a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu, Wiping Socks, and Prayer Behind an Imam","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports wudu on a journey, wiping over socks, and joining Fajr behind an imam."},"heading":{"title":"Hadith About Travel Wudu and Wiping Over Socks","description":"This hadith about travel wudu records a detailed event during the expedition of Tabuk. Al-Mughirah was with the Messenger of Allah (صلى الله عليه وسلم) before dawn. After the Prophet returned from relieving himself, water was poured for him. He washed his hands and face, worked around the tight sleeves of his gown, washed his forearms to the elbows, wiped his head, and wiped over his socks. The narration then moves to prayer. The people had already started Fajr with Abd al-Rahman ibn Awf leading them. The Prophet joined the row, prayed one rakah behind him, then stood to complete what he had missed. When the Muslims were worried, he said they had done right or done well. The hadith teaches careful wudu on a journey and respect for prayer time and congregation."},"teachings":["The Prophet (صلى الله عليه وسلم) performed wudu carefully even while traveling.","He wiped over his socks in this report.","He joined the congregation behind Abd al-Rahman ibn Awf.","The people were praised for praying on time instead of waiting."],"related_hadiths":[{"id":"182","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"206","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E308" s="4" t="n"/>
@@ -7565,7 +7569,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Earnest Supplication Posture","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas described earnest supplication with raised hands and palms toward the face."},"heading":{"title":"Hadith About Earnest Supplication With Raised Hands","description":"This version continues the report from Ibn Abbas about the manner of earnest supplication. It says that earnest supplication should be made like this: he raised his hands and made his palms in the direction of his face. The hadith is short, so its teaching is also focused. It describes a particular hand position for ibtihal, or earnest supplication. The report does not add a separate dua phrase or promise. It simply shows how the hands were positioned. This is useful for people searching for earnest supplication hadith, palms toward face in dua, and raising hands in dua. The safest explanation is that this narration records a physical manner for intense asking, as described by Ibn Abbas in this version."},"teachings":["The report describes a manner of earnest supplication.","The hands are raised in this description.","The palms are placed in the direction of the face.","The narration focuses on posture, not on a specific wording of dua."],"related_hadiths":[{"id":"1489","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1491","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1487","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Earnest Supplication Posture","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas described earnest supplication with raised hands and palms toward the face."},"heading":{"title":"Hadith About Earnest Supplication With Raised Hands","description":"This version continues the report from Ibn Abbas about the manner of earnest supplication. It says that earnest supplication should be made like this: he raised his hands and made his palms in the direction of his face. The hadith is short, so its teaching is also focused. It describes a particular hand position for ibtihal, or earnest supplication. The report does not add a separate dua phrase or promise. It simply shows how the hands were positioned. This is useful for people searching for earnest supplication hadith, palms toward face in dua, and raising hands in dua. The safest explanation is that this narration records a physical manner for intense asking, as described by Ibn Abbas in this version."},"teachings":["The report describes a manner of earnest supplication.","The hands are raised in this description.","The palms are placed in the direction of the face.","The narration focuses on posture, not on a specific wording of dua."],"related_hadiths":[{"id":"1489","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1491","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1487","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E309" s="4" t="n"/>
@@ -7588,7 +7592,7 @@
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Similar Report on Dua Posture","description":"$book_name$ $hadith_number$ - $chapter_name$. This report transmits a similar narration from Ibn Abbas from the Messenger of Allah."},"heading":{"title":"Hadith About a Similar Narration on Dua Hand Position","description":"This entry states that the earlier mentioned tradition was also transmitted in a similar manner by Ibn Abbas from the Messenger of Allah (صلى الله عليه وسلم). It does not give a full new wording in the translation, but says that the narrator mentioned something similar. Because of that, the explanation should not add new details that are not in the text. The safest way to read it is as a supporting transmission connected to the previous report about manners of supplication and hand position. This hadith is useful for searches like Ibn Abbas dua posture, similar narration Abu Dawud 1491, and hand position in supplication. Its value in this batch is that it links the previous description to a report from the Prophet (صلى الله عليه وسلم)."},"teachings":["This entry reports a similar narration through Ibn Abbas.","It connects the topic to the Messenger of Allah (صلى الله عليه وسلم).","The text should be read with the earlier mentioned tradition in view.","No extra wording should be added beyond what is stated."],"related_hadiths":[{"id":"1489","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1490","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1486","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Similar Report on Dua Posture","description":"$book_name$ $hadith_number$ - $chapter_name$. This report transmits a similar narration from Ibn Abbas from the Messenger of Allah."},"heading":{"title":"Hadith About a Similar Narration on Dua Hand Position","description":"This entry states that the earlier mentioned tradition was also transmitted in a similar manner by Ibn Abbas from the Messenger of Allah (صلى الله عليه وسلم). It does not give a full new wording in the translation, but says that the narrator mentioned something similar. Because of that, the explanation should not add new details that are not in the text. The safest way to read it is as a supporting transmission connected to the previous report about manners of supplication and hand position. This hadith is useful for searches like Ibn Abbas dua posture, similar narration Abu Dawud 1491, and hand position in supplication. Its value in this batch is that it links the previous description to a report from the Prophet (صلى الله عليه وسلم)."},"teachings":["This entry reports a similar narration through Ibn Abbas.","It connects the topic to the Messenger of Allah (صلى الله عليه وسلم).","The text should be read with the earlier mentioned tradition in view.","No extra wording should be added beyond what is stated."],"related_hadiths":[{"id":"1489","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1490","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1486","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E310" s="4" t="n"/>
@@ -7611,7 +7615,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Face After Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions the Prophet raising his hands in dua and wiping his face afterward."},"heading":{"title":"Hadith About Raising Hands and Wiping the Face After Dua","description":"This narration from Yazid ibn Sa'id al-Kindi says that when the Prophet (صلى الله عليه وسلم) made supplication, he would raise his hands and wipe his face with his hands. The hadith focuses on two actions: raising the hands during dua and wiping the face afterward. The text does not give extra conditions or a specific dua to say. So the explanation should stay simple and close to the wording. It is commonly searched by people looking for wiping face after dua, raising hands in dua, and Sunan Abu Dawud 1492. Since another narration in this batch includes Abu Dawud’s note about weakness for a related report, readers should avoid building more than what this text directly says."},"teachings":["The narration mentions raising the hands when making dua.","It also mentions wiping the face with the hands after supplication.","The hadith does not mention a specific wording of dua.","The explanation should stay close to the reported action."],"related_hadiths":[{"id":"1485","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1486","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1488","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Face After Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration mentions the Prophet raising his hands in dua and wiping his face afterward."},"heading":{"title":"Hadith About Raising Hands and Wiping the Face After Dua","description":"This narration from Yazid ibn Sa'id al-Kindi says that when the Prophet (صلى الله عليه وسلم) made supplication, he would raise his hands and wipe his face with his hands. The hadith focuses on two actions: raising the hands during dua and wiping the face afterward. The text does not give extra conditions or a specific dua to say. So the explanation should stay simple and close to the wording. It is commonly searched by people looking for wiping face after dua, raising hands in dua, and Sunan Abu Dawud 1492. Since another narration in this batch includes Abu Dawud’s note about weakness for a related report, readers should avoid building more than what this text directly says."},"teachings":["The narration mentions raising the hands when making dua.","It also mentions wiping the face with the hands after supplication.","The hadith does not mention a specific wording of dua.","The explanation should stay close to the reported action."],"related_hadiths":[{"id":"1485","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1486","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1488","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E311" s="4" t="n"/>
@@ -7634,7 +7638,7 @@
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Greatest Name in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said this supplication used Allah’s Greatest Name, by which He gives and answers."},"heading":{"title":"Hadith About Allah’s Greatest Name in Supplication","description":"This hadith records a man making dua with words of tawhid: he bore witness that there is no god but Allah, the One, the Self-Sufficient, who neither begets nor is begotten, and to whom no one is equal. After hearing this, the Messenger of Allah (صلى الله عليه وسلم) said that the man had supplicated Allah using His Greatest Name. The hadith also says that when Allah is asked with this name, He gives, and when supplicated by this name, He answers. This narration is important for searches about Allah’s Greatest Name, Ism al-Azam dua, and dua with Surah Ikhlas meanings. The message stays centered on calling upon Allah with words that affirm His oneness and perfection."},"teachings":["The supplication begins with strong words of tawhid.","The Prophet (صلى الله عليه وسلم) identified this dua as using Allah’s Greatest Name.","The hadith links this Name with asking Allah and supplicating to Him.","The wording honors Allah as One and without equal."],"related_hadiths":[{"id":"1494","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1495","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1496","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Greatest Name in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said this supplication used Allah’s Greatest Name, by which He gives and answers."},"heading":{"title":"Hadith About Allah’s Greatest Name in Supplication","description":"This hadith records a man making dua with words of tawhid: he bore witness that there is no god but Allah, the One, the Self-Sufficient, who neither begets nor is begotten, and to whom no one is equal. After hearing this, the Messenger of Allah (صلى الله عليه وسلم) said that the man had supplicated Allah using His Greatest Name. The hadith also says that when Allah is asked with this name, He gives, and when supplicated by this name, He answers. This narration is important for searches about Allah’s Greatest Name, Ism al-Azam dua, and dua with Surah Ikhlas meanings. The message stays centered on calling upon Allah with words that affirm His oneness and perfection."},"teachings":["The supplication begins with strong words of tawhid.","The Prophet (صلى الله عليه وسلم) identified this dua as using Allah’s Greatest Name.","The hadith links this Name with asking Allah and supplicating to Him.","The wording honors Allah as One and without equal."],"related_hadiths":[{"id":"1494","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1495","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1496","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E312" s="4" t="n"/>
@@ -7657,7 +7661,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Asking by Allah’s Greatest Name","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that the man asked Allah using His Greatest Name."},"heading":{"title":"Hadith About Asking Allah by His Greatest Name","description":"This entry is another chain for the same report connected to Malik ibn Mighwal. Its added wording says, “He has asked Allah using His Greatest Name.” The hadith is brief, but its point is clear. It strengthens the focus on making dua by mentioning Allah in a way that the Prophet (صلى الله عليه وسلم) described as His Greatest Name. Since the translation does not repeat the full supplication here, the explanation should not pretend this version contains more than it states. It is related to the previous narration where the dua included testimony to Allah’s oneness and perfect uniqueness. This hadith is helpful for people searching for Ism al-Azam, Allah’s Greatest Name hadith, and asking Allah by His names."},"teachings":["This version highlights asking Allah using His Greatest Name.","It is transmitted through a different chain of narrators.","The wording is connected to the earlier report in the batch.","The hadith points to the honor of calling upon Allah by His names."],"related_hadiths":[{"id":"1493","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1495","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1496","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Asking by Allah’s Greatest Name","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that the man asked Allah using His Greatest Name."},"heading":{"title":"Hadith About Asking Allah by His Greatest Name","description":"This entry is another chain for the same report connected to Malik ibn Mighwal. Its added wording says, “He has asked Allah using His Greatest Name.” The hadith is brief, but its point is clear. It strengthens the focus on making dua by mentioning Allah in a way that the Prophet (صلى الله عليه وسلم) described as His Greatest Name. Since the translation does not repeat the full supplication here, the explanation should not pretend this version contains more than it states. It is related to the previous narration where the dua included testimony to Allah’s oneness and perfect uniqueness. This hadith is helpful for people searching for Ism al-Azam, Allah’s Greatest Name hadith, and asking Allah by His names."},"teachings":["This version highlights asking Allah using His Greatest Name.","It is transmitted through a different chain of narrators.","The wording is connected to the earlier report in the batch.","The hadith points to the honor of calling upon Allah by His names."],"related_hadiths":[{"id":"1493","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1495","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1496","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E313" s="4" t="n"/>
@@ -7680,7 +7684,7 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua With Allah’s Beautiful Names","description":"$book_name$ $hadith_number$ - $chapter_name$. A man called upon Allah with praise and names, and the Prophet said he used Allah’s Great Name."},"heading":{"title":"Hadith About Ism al-Azam and Calling Allah by His Names","description":"This hadith shows a man praying and then making dua with words of praise. He said that praise belongs to Allah, there is no deity but Him, the One who shows favor and beneficence, the Originator of the heavens and the earth, Lord of Majesty and Splendour, the Living One, and the Eternal One. The Prophet (صلى الله عليه وسلم) then said that he had supplicated Allah using His Great Name, by which He answers when called and gives when asked. The hadith teaches the beauty of making dua with praise and Allah’s names. It is highly relevant for people searching for Ism al-Azam dua, Ya Hayyu Ya Qayyum hadith, and dua with Allah’s names. The wording itself is the focus of the lesson."},"teachings":["The supplication begins with praise of Allah.","The man called upon Allah using names and attributes mentioned in the text.","The Prophet (صلى الله عليه وسلم) said he used Allah’s Great Name.","The hadith connects calling upon Allah with asking Him."],"related_hadiths":[{"id":"1493","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1494","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1496","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua With Allah’s Beautiful Names","description":"$book_name$ $hadith_number$ - $chapter_name$. A man called upon Allah with praise and names, and the Prophet said he used Allah’s Great Name."},"heading":{"title":"Hadith About Ism al-Azam and Calling Allah by His Names","description":"This hadith shows a man praying and then making dua with words of praise. He said that praise belongs to Allah, there is no deity but Him, the One who shows favor and beneficence, the Originator of the heavens and the earth, Lord of Majesty and Splendour, the Living One, and the Eternal One. The Prophet (صلى الله عليه وسلم) then said that he had supplicated Allah using His Great Name, by which He answers when called and gives when asked. The hadith teaches the beauty of making dua with praise and Allah’s names. It is highly relevant for people searching for Ism al-Azam dua, Ya Hayyu Ya Qayyum hadith, and dua with Allah’s names. The wording itself is the focus of the lesson."},"teachings":["The supplication begins with praise of Allah.","The man called upon Allah using names and attributes mentioned in the text.","The Prophet (صلى الله عليه وسلم) said he used Allah’s Great Name.","The hadith connects calling upon Allah with asking Him."],"related_hadiths":[{"id":"1493","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1494","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1496","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E314" s="4" t="n"/>
@@ -7703,7 +7707,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Greatest Name in Quranic Verses","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said Allah’s Greatest Name is in two verses about His oneness, mercy, life, and eternity."},"heading":{"title":"Hadith About Allah’s Greatest Name in Two Quranic Verses","description":"This hadith from Asma daughter of Yazid reports that the Prophet (صلى الله عليه وسلم) said Allah’s Greatest Name is in two verses. The first verse says that your God is One God, none has the right to be worshipped but Him, the Ever-Merciful, the Mercy-Giving. The second is the beginning of Surah Al Imran: “A.L.M. Allah, there is no deity but He, the Living, the Eternal.” The hadith points to Allah’s oneness, mercy, life, and eternal self-subsistence. The explanation should stay with what is given in the text. This narration is important for searches about Allah’s Greatest Name in the Quran, Ism al-Azam verses, and Ya Hayyu Ya Qayyum."},"teachings":["The hadith identifies two verses connected to Allah’s Greatest Name.","Both verses affirm that there is no deity but Allah.","The first verse mentions Allah’s mercy.","The beginning of Surah Al Imran mentions Allah as the Living and Eternal."],"related_hadiths":[{"id":"1493","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1494","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1495","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Allah’s Greatest Name in Quranic Verses","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said Allah’s Greatest Name is in two verses about His oneness, mercy, life, and eternity."},"heading":{"title":"Hadith About Allah’s Greatest Name in Two Quranic Verses","description":"This hadith from Asma daughter of Yazid reports that the Prophet (صلى الله عليه وسلم) said Allah’s Greatest Name is in two verses. The first verse says that your God is One God, none has the right to be worshipped but Him, the Ever-Merciful, the Mercy-Giving. The second is the beginning of Surah Al Imran: “A.L.M. Allah, there is no deity but He, the Living, the Eternal.” The hadith points to Allah’s oneness, mercy, life, and eternal self-subsistence. The explanation should stay with what is given in the text. This narration is important for searches about Allah’s Greatest Name in the Quran, Ism al-Azam verses, and Ya Hayyu Ya Qayyum."},"teachings":["The hadith identifies two verses connected to Allah’s Greatest Name.","Both verses affirm that there is no deity but Allah.","The first verse mentions Allah’s mercy.","The beginning of Surah Al Imran mentions Allah as the Living and Eternal."],"related_hadiths":[{"id":"1493","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1494","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1495","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E315" s="4" t="n"/>
@@ -7726,7 +7730,7 @@
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoid Lightening the Wrongdoer","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah cursed the thief of her quilt, and the Prophet told her not to lessen him."},"heading":{"title":"Hadith About Cursing a Thief and Restraining the Tongue","description":"This hadith tells that Aishah’s quilt was stolen, and she began to curse the person who had stolen it. The Prophet (صلى الله عليه وسلم) then told her, “Do not lighten him.” Abu Dawud explains that the phrase means “do not lessen him or lighten him.” The narration is brief and should be handled carefully. It does not give a long ruling about every case of theft or every kind of speech. It simply records this incident and the Prophet’s instruction to Aishah in that moment. The core topic is restraint in speech when wronged. It is useful for searches such as hadith about cursing, stolen property hadith, and controlling the tongue in Islam."},"teachings":["A person may feel upset when wronged, but speech still matters.","The Prophet (صلى الله عليه وسلم) corrected Aishah when she cursed the thief.","Abu Dawud explains the wording as not lessening or lightening him.","The narration teaches care with words after being harmed."],"related_hadiths":[{"id":"1483","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1484","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1498","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoid Lightening the Wrongdoer","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah cursed the thief of her quilt, and the Prophet told her not to lessen him."},"heading":{"title":"Hadith About Cursing a Thief and Restraining the Tongue","description":"This hadith tells that Aishah’s quilt was stolen, and she began to curse the person who had stolen it. The Prophet (صلى الله عليه وسلم) then told her, “Do not lighten him.” Abu Dawud explains that the phrase means “do not lessen him or lighten him.” The narration is brief and should be handled carefully. It does not give a long ruling about every case of theft or every kind of speech. It simply records this incident and the Prophet’s instruction to Aishah in that moment. The core topic is restraint in speech when wronged. It is useful for searches such as hadith about cursing, stolen property hadith, and controlling the tongue in Islam."},"teachings":["A person may feel upset when wronged, but speech still matters.","The Prophet (صلى الله عليه وسلم) corrected Aishah when she cursed the thief.","Abu Dawud explains the wording as not lessening or lightening him.","The narration teaches care with words after being harmed."],"related_hadiths":[{"id":"1483","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1484","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1498","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E316" s="4" t="n"/>
@@ -7749,7 +7753,7 @@
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Remember Others in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asked Umar to remember him and share him in his supplication during umrah."},"heading":{"title":"Hadith About Asking Others to Make Dua for You","description":"This hadith shows a warm moment between the Prophet (صلى الله عليه وسلم) and Umar ibn al-Khattab. Umar asked permission to perform umrah, and the Prophet (صلى الله عليه وسلم) gave permission. He then said, “My younger brother, do not forget me in your supplication.” Another wording says, “My younger brother, share me in your supplication.” Umar said this statement pleased him so much that he would not have been as pleased even if he had been given the whole world. The hadith teaches the value of remembering others in dua. It also shows that asking someone to include you in supplication is meaningful. This is relevant for searches about making dua for others, umrah dua, and Prophet asking Umar for dua."},"teachings":["The Prophet (صلى الله عليه وسلم) asked Umar to remember him in supplication.","A person may ask another believer to include him in dua.","Remembering others in supplication is shown as something valuable.","Umar deeply appreciated the Prophet’s words."],"related_hadiths":[{"id":"1481","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1484","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1488","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Remember Others in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet asked Umar to remember him and share him in his supplication during umrah."},"heading":{"title":"Hadith About Asking Others to Make Dua for You","description":"This hadith shows a warm moment between the Prophet (صلى الله عليه وسلم) and Umar ibn al-Khattab. Umar asked permission to perform umrah, and the Prophet (صلى الله عليه وسلم) gave permission. He then said, “My younger brother, do not forget me in your supplication.” Another wording says, “My younger brother, share me in your supplication.” Umar said this statement pleased him so much that he would not have been as pleased even if he had been given the whole world. The hadith teaches the value of remembering others in dua. It also shows that asking someone to include you in supplication is meaningful. This is relevant for searches about making dua for others, umrah dua, and Prophet asking Umar for dua."},"teachings":["The Prophet (صلى الله عليه وسلم) asked Umar to remember him in supplication.","A person may ask another believer to include him in dua.","Remembering others in supplication is shown as something valuable.","Umar deeply appreciated the Prophet’s words."],"related_hadiths":[{"id":"1481","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1484","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1488","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E317" s="4" t="n"/>
@@ -7772,7 +7776,7 @@
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Point With One Finger","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet corrected Sa'd in supplication and pointed with one forefinger."},"heading":{"title":"Hadith About Pointing With One Finger in Supplication","description":"This hadith reports that the Prophet (صلى الله عليه وسلم) passed by Sa'd ibn Abu Waqqas while Sa'd was supplicating by pointing with two fingers. The Prophet (صلى الله عليه وسلم) corrected him and said, “Point with one finger; point with one finger.” Then the Prophet himself pointed with the forefinger. The hadith is short and clear. It teaches a specific correction in the manner of pointing during supplication. The word “one” in the instruction gives the core meaning of singling out, and the action shown is the forefinger. The narration is useful for searches like pointing finger in dua, one finger in supplication, and Sa'd ibn Abu Waqqas dua hadith. The explanation should not add details beyond this correction."},"teachings":["The Prophet (صلى الله عليه وسلم) corrected pointing with two fingers in this supplication.","He instructed Sa'd to point with one finger.","The Prophet (صلى الله عليه وسلم) himself pointed with the forefinger.","The hadith teaches careful following even in small outward actions."],"related_hadiths":[{"id":"1489","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1490","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1491","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Point With One Finger","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet corrected Sa'd in supplication and pointed with one forefinger."},"heading":{"title":"Hadith About Pointing With One Finger in Supplication","description":"This hadith reports that the Prophet (صلى الله عليه وسلم) passed by Sa'd ibn Abu Waqqas while Sa'd was supplicating by pointing with two fingers. The Prophet (صلى الله عليه وسلم) corrected him and said, “Point with one finger; point with one finger.” Then the Prophet himself pointed with the forefinger. The hadith is short and clear. It teaches a specific correction in the manner of pointing during supplication. The word “one” in the instruction gives the core meaning of singling out, and the action shown is the forefinger. The narration is useful for searches like pointing finger in dua, one finger in supplication, and Sa'd ibn Abu Waqqas dua hadith. The explanation should not add details beyond this correction."},"teachings":["The Prophet (صلى الله عليه وسلم) corrected pointing with two fingers in this supplication.","He instructed Sa'd to point with one finger.","The Prophet (صلى الله عليه وسلم) himself pointed with the forefinger.","The hadith teaches careful following even in small outward actions."],"related_hadiths":[{"id":"1489","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1490","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1491","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E318" s="4" t="n"/>
@@ -7795,7 +7799,7 @@
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping the Forelock, Turban, and Socks","description":"$book_name$ $hadith_number$ - $chapter_name$. This report records wiping the forelock, turban, and socks during wudu in two narrated wordings."},"heading":{"title":"Hadith About Wiping Over Turban and Socks","description":"This hadith about wiping over turban and socks gives a brief report from Al-Mughirah ibn Shu’bah. One version says the Messenger of Allah (صلى الله عليه وسلم) performed ablution and wiped his forelock and turban. Another version adds that he wiped over his socks along with his forelock and turban. The core topic is wiping in wudu. The narration is useful for searches like masah over turban hadith and wiping over socks in wudu. It does not describe every step of ablution, but it records the parts wiped in this report. A careful explanation should keep the two versions clear: one mentions forelock and turban, while the other mentions socks as well. This helps readers understand the wording without mixing the reports."},"teachings":["The Prophet (صلى الله عليه وسلم) wiped his forelock and turban in this narration.","Another version also mentions wiping over the socks.","The hadith should be read with attention to its different wordings.","Wiping in wudu is reported through clear observed actions."],"related_hadiths":[{"id":"204","book_id":"1","label":"Sahih Bukhari"},{"id":"561","book_id":"6","label":"Sunan Ibn Majah"},{"id":"274a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping the Forelock, Turban, and Socks","description":"$book_name$ $hadith_number$ - $chapter_name$. This report records wiping the forelock, turban, and socks during wudu in two narrated wordings."},"heading":{"title":"Hadith About Wiping Over Turban and Socks","description":"This hadith about wiping over turban and socks gives a brief report from Al-Mughirah ibn Shu’bah. One version says the Messenger of Allah (صلى الله عليه وسلم) performed ablution and wiped his forelock and turban. Another version adds that he wiped over his socks along with his forelock and turban. The core topic is wiping in wudu. The narration is useful for searches like masah over turban hadith and wiping over socks in wudu. It does not describe every step of ablution, but it records the parts wiped in this report. A careful explanation should keep the two versions clear: one mentions forelock and turban, while the other mentions socks as well. This helps readers understand the wording without mixing the reports."},"teachings":["The Prophet (صلى الله عليه وسلم) wiped his forelock and turban in this narration.","Another version also mentions wiping over the socks.","The hadith should be read with attention to its different wordings.","Wiping in wudu is reported through clear observed actions."],"related_hadiths":[{"id":"204","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"561","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E319" s="4" t="n"/>
@@ -7818,7 +7822,7 @@
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Powerful Words of Dhikr","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught easier or better words of glorification than counting with date-stones or pebbles."},"heading":{"title":"Hadith About Dhikr Better or Easier Than Counting Pebbles","description":"This hadith describes a woman who had date-stones or pebbles in front of her and was using them as a rosary to glorify Allah. The Prophet (صلى الله عليه وسلم) said he would tell her something easier or more excellent than that. He then taught words of dhikr: “Glory be to Allah” as many times as what He created in the heaven, on the earth, between them, and what He is creating. He also mentioned saying “Allah is most great,” “Praise be to Allah,” “There is no god but Allah,” and “There is no might and no power except in Allah” in a similar number. The hadith teaches broad words of remembrance that connect praise to Allah’s creation and power."},"teachings":["The Prophet (صلى الله عليه وسلم) taught words of dhikr that were easier or more excellent for the woman.","The dhikr includes glorifying Allah by the number of what He created.","The narration includes tasbih, takbir, tahmid, tahlil, and hawqalah.","The hadith shows that meaningful words of remembrance can carry broad meaning."],"related_hadiths":[{"id":"1482","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1495","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1496","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Powerful Words of Dhikr","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught easier or better words of glorification than counting with date-stones or pebbles."},"heading":{"title":"Hadith About Dhikr Better or Easier Than Counting Pebbles","description":"This hadith describes a woman who had date-stones or pebbles in front of her and was using them as a rosary to glorify Allah. The Prophet (صلى الله عليه وسلم) said he would tell her something easier or more excellent than that. He then taught words of dhikr: “Glory be to Allah” as many times as what He created in the heaven, on the earth, between them, and what He is creating. He also mentioned saying “Allah is most great,” “Praise be to Allah,” “There is no god but Allah,” and “There is no might and no power except in Allah” in a similar number. The hadith teaches broad words of remembrance that connect praise to Allah’s creation and power."},"teachings":["The Prophet (صلى الله عليه وسلم) taught words of dhikr that were easier or more excellent for the woman.","The dhikr includes glorifying Allah by the number of what He created.","The narration includes tasbih, takbir, tahmid, tahlil, and hawqalah.","The hadith shows that meaningful words of remembrance can carry broad meaning."],"related_hadiths":[{"id":"1482","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1495","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1496","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E320" s="4" t="n"/>
@@ -7841,7 +7845,7 @@
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr on Fingers in Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the Prophet’s teaching on regular dhikr, takbir, tahlil, and counting remembrance on fingers."},"heading":{"title":"Hadith About Dhikr on Fingers: A Simple Sunnah of Remembrance","description":"This hadith teaches a clear and simple way to remember Allah. The Prophet صلى الله عليه وسلم told the women emigrants to be regular in saying words of dhikr: Allah is Most Great, Glory be to the King, the Holy, and there is no god but Allah. He also told them to count this remembrance on their fingers. The reason given in the hadith is powerful: the fingers will be questioned and asked to speak. So, this hadith about dhikr on fingers shows that remembrance is not only something said by the tongue. The body also takes part in worship. It points us to steady, mindful remembrance of Allah through simple words that can be repeated often."},"teachings":["Be regular in remembering Allah with takbir, tahlil, and words of glorification.","Counting dhikr on fingers is directly mentioned in this hadith.","Our body parts are connected to our deeds and may be questioned.","Simple words of remembrance can be part of daily worship."],"related_hadiths":[{"id":"2694","book_id":"2","label":"Sahih Muslim"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"},{"id":"2691","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr on Fingers in Islam","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the Prophet’s teaching on regular dhikr, takbir, tahlil, and counting remembrance on fingers."},"heading":{"title":"Hadith About Dhikr on Fingers: A Simple Sunnah of Remembrance","description":"This hadith teaches a clear and simple way to remember Allah. The Prophet صلى الله عليه وسلم told the women emigrants to be regular in saying words of dhikr: Allah is Most Great, Glory be to the King, the Holy, and there is no god but Allah. He also told them to count this remembrance on their fingers. The reason given in the hadith is powerful: the fingers will be questioned and asked to speak. So, this hadith about dhikr on fingers shows that remembrance is not only something said by the tongue. The body also takes part in worship. It points us to steady, mindful remembrance of Allah through simple words that can be repeated often."},"teachings":["Be regular in remembering Allah with takbir, tahlil, and words of glorification.","Counting dhikr on fingers is directly mentioned in this hadith.","Our body parts are connected to our deeds and may be questioned.","Simple words of remembrance can be part of daily worship."],"related_hadiths":[{"id":"2694","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2691","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E321" s="4" t="n"/>
@@ -7864,7 +7868,7 @@
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Powerful Words of Tasbih","description":"$book_name$ $hadith_number$ - $chapter_name$. Discover the short words of praise taught by the Prophet صلى الله عليه وسلم that carry great weight in remembrance of Allah."},"heading":{"title":"Subhan Allah Wa Bihamdihi: A Powerful Dhikr Hadith","description":"This hadith centers on a short but weighty form of dhikr. The Prophet صلى الله عليه وسلم left Juwayriyyah while she was in her place of worship, then returned and found her still there. When she said she had remained there, he taught her four phrases that he had said three times. He said that if those words were weighed against all that she had said during that time, they would be heavier. The phrase praises Allah by saying: Glory be to Allah and praise be to Him, by the number of His creatures, according to His pleasure, by the weight of His throne, and by the extent of His words. This hadith about Subhan Allah wa bihamdihi shows that short dhikr can carry deep praise when taught by the Prophet صلى الله عليه وسلم."},"teachings":["Short words of dhikr can hold great weight when taught by the Prophet صلى الله عليه وسلم.","The hadith highlights praising Allah with broad and rich meanings.","Worship includes both long devotion and concise remembrance.","The Prophet صلى الله عليه وسلم guided his family to words of remembrance."],"related_hadiths":[{"id":"2726a","book_id":"2","label":"Sahih Muslim"},{"id":"2694","book_id":"2","label":"Sahih Muslim"},{"id":"6406","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Powerful Words of Tasbih","description":"$book_name$ $hadith_number$ - $chapter_name$. Discover the short words of praise taught by the Prophet صلى الله عليه وسلم that carry great weight in remembrance of Allah."},"heading":{"title":"Subhan Allah Wa Bihamdihi: A Powerful Dhikr Hadith","description":"This hadith centers on a short but weighty form of dhikr. The Prophet صلى الله عليه وسلم left Juwayriyyah while she was in her place of worship, then returned and found her still there. When she said she had remained there, he taught her four phrases that he had said three times. He said that if those words were weighed against all that she had said during that time, they would be heavier. The phrase praises Allah by saying: Glory be to Allah and praise be to Him, by the number of His creatures, according to His pleasure, by the weight of His throne, and by the extent of His words. This hadith about Subhan Allah wa bihamdihi shows that short dhikr can carry deep praise when taught by the Prophet صلى الله عليه وسلم."},"teachings":["Short words of dhikr can hold great weight when taught by the Prophet صلى الله عليه وسلم.","The hadith highlights praising Allah with broad and rich meanings.","Worship includes both long devotion and concise remembrance.","The Prophet صلى الله عليه وسلم guided his family to words of remembrance."],"related_hadiths":[{"id":"2726a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2694","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"6406","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E322" s="4" t="n"/>
@@ -7887,7 +7891,7 @@
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr After Salah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the post-prayer dhikr taught to Abu Dharr: tasbih, tahmid, takbir, and tahlil after every prayer."},"heading":{"title":"Dhikr After Salah: Tasbih, Tahmid, Takbir, and Tahlil","description":"This hadith gives comfort to a person who feels left behind because he has less wealth. Abu Dharr said that wealthy people pray, fast, and also give charity from extra wealth, while he had no wealth to give. The Prophet صلى الله عليه وسلم taught him words to say after each prayer: say Allahu Akbar thirty-three times, Alhamdulillah thirty-three times, Subhan Allah thirty-three times, and end with the declaration that there is no god but Allah alone, with no partner. The hadith says sins will be forgiven, even if like the foam of the sea. This dhikr after salah is a way of worship open to people with or without wealth."},"teachings":["A person without wealth still has ways to seek reward through dhikr.","Post-prayer dhikr includes takbir, tahmid, tasbih, and tahlil.","The Prophet صلى الله عليه وسلم gave practical words to say after every prayer.","The hadith mentions forgiveness linked to this remembrance."],"related_hadiths":[{"id":"597a","book_id":"2","label":"Sahih Muslim"},{"id":"2691","book_id":"2","label":"Sahih Muslim"},{"id":"1006","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr After Salah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the post-prayer dhikr taught to Abu Dharr: tasbih, tahmid, takbir, and tahlil after every prayer."},"heading":{"title":"Dhikr After Salah: Tasbih, Tahmid, Takbir, and Tahlil","description":"This hadith gives comfort to a person who feels left behind because he has less wealth. Abu Dharr said that wealthy people pray, fast, and also give charity from extra wealth, while he had no wealth to give. The Prophet صلى الله عليه وسلم taught him words to say after each prayer: say Allahu Akbar thirty-three times, Alhamdulillah thirty-three times, Subhan Allah thirty-three times, and end with the declaration that there is no god but Allah alone, with no partner. The hadith says sins will be forgiven, even if like the foam of the sea. This dhikr after salah is a way of worship open to people with or without wealth."},"teachings":["A person without wealth still has ways to seek reward through dhikr.","Post-prayer dhikr includes takbir, tahmid, tasbih, and tahlil.","The Prophet صلى الله عليه وسلم gave practical words to say after every prayer.","The hadith mentions forgiveness linked to this remembrance."],"related_hadiths":[{"id":"597a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2691","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1006","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E323" s="4" t="n"/>
@@ -7910,7 +7914,7 @@
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua After Taslim","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the supplication the Prophet صلى الله عليه وسلم said after taslim, affirming Allah’s oneness, power, and control."},"heading":{"title":"Dua After Taslim: La Ilaha Illallah Wahdahu La Sharika Lah","description":"This hadith shows what the Messenger of Allah صلى الله عليه وسلم used to say after giving taslim in prayer. Al-Mughirah wrote that the Prophet صلى الله عليه وسلم would say there is no god but Allah alone, with no partner. To Him belongs the dominion, to Him is praise, and He has power over everything. Then he would say that no one can withhold what Allah gives, no one can give what Allah withholds, and no fortunate person benefits from fortune against Allah. The main lesson of this dua after taslim is dependence on Allah. It reminds the worshipper that prayer does not end with empty words. It ends with belief, praise, and trust in Allah’s control."},"teachings":["The Prophet صلى الله عليه وسلم said words of tawhid after taslim.","The supplication affirms that giving and withholding belong to Allah.","Worldly fortune does not benefit a person against Allah.","Post-prayer remembrance can strengthen trust in Allah."],"related_hadiths":[{"id":"593a","book_id":"2","label":"Sahih Muslim"},{"id":"593e","book_id":"2","label":"Sahih Muslim"},{"id":"6615","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua After Taslim","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the supplication the Prophet صلى الله عليه وسلم said after taslim, affirming Allah’s oneness, power, and control."},"heading":{"title":"Dua After Taslim: La Ilaha Illallah Wahdahu La Sharika Lah","description":"This hadith shows what the Messenger of Allah صلى الله عليه وسلم used to say after giving taslim in prayer. Al-Mughirah wrote that the Prophet صلى الله عليه وسلم would say there is no god but Allah alone, with no partner. To Him belongs the dominion, to Him is praise, and He has power over everything. Then he would say that no one can withhold what Allah gives, no one can give what Allah withholds, and no fortunate person benefits from fortune against Allah. The main lesson of this dua after taslim is dependence on Allah. It reminds the worshipper that prayer does not end with empty words. It ends with belief, praise, and trust in Allah’s control."},"teachings":["The Prophet صلى الله عليه وسلم said words of tawhid after taslim.","The supplication affirms that giving and withholding belong to Allah.","Worldly fortune does not benefit a person against Allah.","Post-prayer remembrance can strengthen trust in Allah."],"related_hadiths":[{"id":"593a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"593e","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"6615","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E324" s="4" t="n"/>
@@ -7933,7 +7937,7 @@
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tahlil After Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the Prophet’s post-prayer tahlil that affirms Allah’s oneness, praise, grace, and sincere devotion."},"heading":{"title":"Tahlil After Prayer: A Hadith on Sincere Devotion to Allah","description":"This hadith reports a supplication the Prophet صلى الله عليه وسلم used to say when he finished the prayer. The words begin with tahlil: there is no god but Allah alone, with no partner. The dua also says that to Allah belongs the kingdom, to Him belongs praise, and He has power over everything. It then repeats the message of sincere devotion to Allah, even if disbelievers dislike it. It mentions that to Him belongs wealth, grace, and good praise. This hadith about tahlil after prayer teaches the worshipper to leave prayer with tawhid on the tongue and sincerity in the heart. The focus is Allah alone, His praise, His power, and devotion to Him."},"teachings":["The Prophet صلى الله عليه وسلم recited tahlil after finishing prayer.","The dua repeats sincere devotion to Allah alone.","The hadith connects praise, kingdom, grace, and power to Allah.","A believer can end prayer by renewing tawhid and sincerity."],"related_hadiths":[{"id":"593a","book_id":"2","label":"Sahih Muslim"},{"id":"1218a","book_id":"2","label":"Sahih Muslim"},{"id":"1154","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tahlil After Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the Prophet’s post-prayer tahlil that affirms Allah’s oneness, praise, grace, and sincere devotion."},"heading":{"title":"Tahlil After Prayer: A Hadith on Sincere Devotion to Allah","description":"This hadith reports a supplication the Prophet صلى الله عليه وسلم used to say when he finished the prayer. The words begin with tahlil: there is no god but Allah alone, with no partner. The dua also says that to Allah belongs the kingdom, to Him belongs praise, and He has power over everything. It then repeats the message of sincere devotion to Allah, even if disbelievers dislike it. It mentions that to Him belongs wealth, grace, and good praise. This hadith about tahlil after prayer teaches the worshipper to leave prayer with tawhid on the tongue and sincerity in the heart. The focus is Allah alone, His praise, His power, and devotion to Him."},"teachings":["The Prophet صلى الله عليه وسلم recited tahlil after finishing prayer.","The dua repeats sincere devotion to Allah alone.","The hadith connects praise, kingdom, grace, and power to Allah.","A believer can end prayer by renewing tawhid and sincerity."],"related_hadiths":[{"id":"593a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1218a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1154","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E325" s="4" t="n"/>
@@ -7956,7 +7960,7 @@
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Post-Prayer Tahlil","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration adds words of reliance: no might and no power except with Allah, and worship for Him alone."},"heading":{"title":"Post-Prayer Tahlil: No Might and No Power Except with Allah","description":"This hadith continues the theme of remembrance after prayer. Abu al-Zubair reports that Abdullah ibn al-Zubair used to recite this supplication after each prescribed prayer. The narration mentions a similar dua and adds: there is no might and no power except in Allah; there is no god but Allah, Whom alone we worship; to Him belongs wealth. These words of post-prayer tahlil bring together tawhid, worship, and reliance. The phrase no might and no power except with Allah teaches the worshipper to remember human weakness and Allah’s full power. After salah, the heart is guided back to Allah alone as the One worshipped and the One who grants strength."},"teachings":["The narration shows regular supplication after each prescribed prayer.","The words affirm that might and power belong to Allah.","The supplication states that worship is for Allah alone.","Post-prayer dhikr can include tawhid and reliance on Allah."],"related_hadiths":[{"id":"593a","book_id":"2","label":"Sahih Muslim"},{"id":"1154","book_id":"1","label":"Sahih Bukhari"},{"id":"2691","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Post-Prayer Tahlil","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration adds words of reliance: no might and no power except with Allah, and worship for Him alone."},"heading":{"title":"Post-Prayer Tahlil: No Might and No Power Except with Allah","description":"This hadith continues the theme of remembrance after prayer. Abu al-Zubair reports that Abdullah ibn al-Zubair used to recite this supplication after each prescribed prayer. The narration mentions a similar dua and adds: there is no might and no power except in Allah; there is no god but Allah, Whom alone we worship; to Him belongs wealth. These words of post-prayer tahlil bring together tawhid, worship, and reliance. The phrase no might and no power except with Allah teaches the worshipper to remember human weakness and Allah’s full power. After salah, the heart is guided back to Allah alone as the One worshipped and the One who grants strength."},"teachings":["The narration shows regular supplication after each prescribed prayer.","The words affirm that might and power belong to Allah.","The supplication states that worship is for Allah alone.","Post-prayer dhikr can include tawhid and reliance on Allah."],"related_hadiths":[{"id":"593a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1154","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2691","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E326" s="4" t="n"/>
@@ -7979,7 +7983,7 @@
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sincerity in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Read a post-prayer supplication asking Allah for sincerity, faith, response, and reliance on Him."},"heading":{"title":"Sincerity in Dua: A Post-Prayer Supplication for Ikhlas","description":"This hadith records a long supplication the Prophet صلى الله عليه وسلم said after prayer. He bore witness that Allah is the Lord alone with no partner, that Muhammad صلى الله عليه وسلم is His servant and Messenger, and that all servants are brethren. He then asked Allah to make him and his family sincere to Him at every moment, in this world and the hereafter. The dua also includes calling upon Allah as Possessor of glory and honour, asking Him to hear and answer, saying Allah is incomparably great, and mentioning Allah as the Light or Lord of the heavens and earth. This hadith about sincerity in dua is focused on faith, family, brotherhood, and constant devotion to Allah."},"teachings":["The supplication begins with clear testimony to Allah’s oneness.","The Prophet صلى الله عليه وسلم asked for sincerity for himself and his family.","The hadith mentions the brotherhood of Allah’s servants.","The dua combines praise, testimony, request, and reliance."],"related_hadiths":[{"id":"2655","book_id":"2","label":"Sahih Muslim"},{"id":"769a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sincerity in Dua","description":"$book_name$ $hadith_number$ - $chapter_name$. Read a post-prayer supplication asking Allah for sincerity, faith, response, and reliance on Him."},"heading":{"title":"Sincerity in Dua: A Post-Prayer Supplication for Ikhlas","description":"This hadith records a long supplication the Prophet صلى الله عليه وسلم said after prayer. He bore witness that Allah is the Lord alone with no partner, that Muhammad صلى الله عليه وسلم is His servant and Messenger, and that all servants are brethren. He then asked Allah to make him and his family sincere to Him at every moment, in this world and the hereafter. The dua also includes calling upon Allah as Possessor of glory and honour, asking Him to hear and answer, saying Allah is incomparably great, and mentioning Allah as the Light or Lord of the heavens and earth. This hadith about sincerity in dua is focused on faith, family, brotherhood, and constant devotion to Allah."},"teachings":["The supplication begins with clear testimony to Allah’s oneness.","The Prophet صلى الله عليه وسلم asked for sincerity for himself and his family.","The hadith mentions the brotherhood of Allah’s servants.","The dua combines praise, testimony, request, and reliance."],"related_hadiths":[{"id":"2655","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"769a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr">
@@ -8006,7 +8010,7 @@
       </c>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Leave the Socks, They Were Put on Clean","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration teaches that the Prophet wiped over socks after saying his feet were clean when he wore them."},"heading":{"title":"Hadith About Wiping Over Socks After Wudu","description":"This hadith about wiping over socks after wudu gives an important detail in the Prophet’s own words. Al-Mughirah came with water and poured it for the Messenger of Allah (صلى الله عليه وسلم). The Prophet washed his hands and face. Because his Syrian woolen gown had tight sleeves, he brought his hands out from under the gown to wash his forearms. Al-Mughirah then bent down to remove the socks, but the Prophet told him to leave them, saying that his feet had been clean when he put them in. He then wiped over them. The core message is not just that he wiped over socks, but that the socks were worn while the feet were in a clean state. The narration is practical and easy to understand."},"teachings":["The Prophet (صلى الله عليه وسلم) wiped over his socks in this report.","He told Al-Mughirah not to remove them.","The reason given was that his feet were clean when he put them on.","The hadith shows careful service and clear instruction during wudu."],"related_hadiths":[{"id":"206","book_id":"1","label":"Sahih Bukhari"},{"id":"274a","book_id":"2","label":"Sahih Muslim"},{"id":"161","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Leave the Socks, They Were Put on Clean","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration teaches that the Prophet wiped over socks after saying his feet were clean when he wore them."},"heading":{"title":"Hadith About Wiping Over Socks After Wudu","description":"This hadith about wiping over socks after wudu gives an important detail in the Prophet’s own words. Al-Mughirah came with water and poured it for the Messenger of Allah (صلى الله عليه وسلم). The Prophet washed his hands and face. Because his Syrian woolen gown had tight sleeves, he brought his hands out from under the gown to wash his forearms. Al-Mughirah then bent down to remove the socks, but the Prophet told him to leave them, saying that his feet had been clean when he put them in. He then wiped over them. The core message is not just that he wiped over socks, but that the socks were worn while the feet were in a clean state. The narration is practical and easy to understand."},"teachings":["The Prophet (صلى الله عليه وسلم) wiped over his socks in this report.","He told Al-Mughirah not to remove them.","The reason given was that his feet were clean when he put them on.","The hadith shows careful service and clear instruction during wudu."],"related_hadiths":[{"id":"206","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"161","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E328" s="4" t="n"/>
@@ -8029,7 +8033,7 @@
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. Read a broad prophetic supplication for help, victory, gratitude, guidance, repentance, and a clean heart."},"heading":{"title":"Dua for Guidance: Help, Repentance, and a Sound Heart","description":"This hadith presents a broad supplication of the Prophet صلى الله عليه وسلم. He asked Allah for help, victory, good planning on his behalf, guidance, and ease in right guidance. He also asked Allah to make him grateful, mindful, fearful of Him, obedient, humble, and penitent. The dua continues with requests for accepted repentance, washing away sin, answered supplication, firm evidence, guidance of the heart, truthfulness of the tongue, and removal of malice from the chest. This hadith about dua for guidance is rich in personal requests. It teaches a person to ask Allah not only for outward success, but also for inner reform, clean speech, repentance, and a heart free from ill feeling."},"teachings":["The Prophet صلى الله عليه وسلم asked Allah for help, guidance, and victory.","The supplication includes gratitude, obedience, humility, and repentance.","The dua asks for a guided heart and truthful tongue.","The hadith mentions asking Allah to remove malice from the heart."],"related_hadiths":[{"id":"2655","book_id":"2","label":"Sahih Muslim"},{"id":"2697a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. Read a broad prophetic supplication for help, victory, gratitude, guidance, repentance, and a clean heart."},"heading":{"title":"Dua for Guidance: Help, Repentance, and a Sound Heart","description":"This hadith presents a broad supplication of the Prophet صلى الله عليه وسلم. He asked Allah for help, victory, good planning on his behalf, guidance, and ease in right guidance. He also asked Allah to make him grateful, mindful, fearful of Him, obedient, humble, and penitent. The dua continues with requests for accepted repentance, washing away sin, answered supplication, firm evidence, guidance of the heart, truthfulness of the tongue, and removal of malice from the chest. This hadith about dua for guidance is rich in personal requests. It teaches a person to ask Allah not only for outward success, but also for inner reform, clean speech, repentance, and a heart free from ill feeling."},"teachings":["The Prophet صلى الله عليه وسلم asked Allah for help, guidance, and victory.","The supplication includes gratitude, obedience, humility, and repentance.","The dua asks for a guided heart and truthful tongue.","The hadith mentions asking Allah to remove malice from the heart."],"related_hadiths":[{"id":"2655","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2697a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr">
@@ -8056,7 +8060,7 @@
       </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ease in Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. This version reports the same prophetic dua with the added wording: make right guidance easy for me."},"heading":{"title":"Ease in Guidance: A Hadith Version on Asking Allah for Hidayah","description":"This narration is connected to the previous supplication and reports it through another chain with the same meaning. The key added wording is: make right guidance easy for me. The narrator notes that this version did not say my right guidance, but simply right guidance. The hadith is short, yet the message is meaningful. Guidance is not only something a person needs to know; it is something a person needs Allah to make easy. A person may recognize the right path but still need help to follow it with steadiness. This hadith about ease in guidance keeps the focus on asking Allah to bring guidance near and make it manageable for the servant."},"teachings":["The narration supports asking Allah to make guidance easy.","Guidance is treated as a gift sought from Allah.","A slight wording difference is preserved in the report.","The hadith shows care in transmitting the wording of supplication."],"related_hadiths":[{"id":"2655","book_id":"2","label":"Sahih Muslim"},{"id":"2697a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ease in Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. This version reports the same prophetic dua with the added wording: make right guidance easy for me."},"heading":{"title":"Ease in Guidance: A Hadith Version on Asking Allah for Hidayah","description":"This narration is connected to the previous supplication and reports it through another chain with the same meaning. The key added wording is: make right guidance easy for me. The narrator notes that this version did not say my right guidance, but simply right guidance. The hadith is short, yet the message is meaningful. Guidance is not only something a person needs to know; it is something a person needs Allah to make easy. A person may recognize the right path but still need help to follow it with steadiness. This hadith about ease in guidance keeps the focus on asking Allah to bring guidance near and make it manageable for the servant."},"teachings":["The narration supports asking Allah to make guidance easy.","Guidance is treated as a gift sought from Allah.","A slight wording difference is preserved in the report.","The hadith shows care in transmitting the wording of supplication."],"related_hadiths":[{"id":"2655","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2697a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E330" s="4" t="inlineStr">
@@ -8083,7 +8087,7 @@
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Completing the Missed Rakah Behind an Imam","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows the Prophet joining Fajr behind Abd al-Rahman and completing the missed rakah."},"heading":{"title":"Hadith About Praying Behind Abd al-Rahman ibn Awf","description":"This hadith about praying behind Abd al-Rahman ibn Awf focuses on a prayer event after the Prophet (صلى الله عليه وسلم) lagged behind during a journey. When he and Al-Mughirah came to the people, Abd al-Rahman was leading the dawn prayer. When Abd al-Rahman noticed the Prophet, he wanted to step back, but the Prophet signaled for him to continue. The Prophet and Al-Mughirah prayed one rakah behind him. After Abd al-Rahman gave salam, the Prophet stood and completed the rakah he had missed, without adding anything else. The text also reports Abu Dawud’s note about some Companions’ view on prostrations of forgetfulness for one who catches an odd number of rakahs. The main lesson is to follow the prayer properly and complete what was missed."},"teachings":["The Prophet (صلى الله عليه وسلم) signaled the imam to continue leading.","He joined the congregation and prayed behind Abd al-Rahman ibn Awf.","He completed only the rakah that he had missed.","The narration shows order and calm in congregational prayer."],"related_hadiths":[{"id":"521","book_id":"1","label":"Sahih Bukhari"},{"id":"522","book_id":"1","label":"Sahih Bukhari"},{"id":"274a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Completing the Missed Rakah Behind an Imam","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows the Prophet joining Fajr behind Abd al-Rahman and completing the missed rakah."},"heading":{"title":"Hadith About Praying Behind Abd al-Rahman ibn Awf","description":"This hadith about praying behind Abd al-Rahman ibn Awf focuses on a prayer event after the Prophet (صلى الله عليه وسلم) lagged behind during a journey. When he and Al-Mughirah came to the people, Abd al-Rahman was leading the dawn prayer. When Abd al-Rahman noticed the Prophet, he wanted to step back, but the Prophet signaled for him to continue. The Prophet and Al-Mughirah prayed one rakah behind him. After Abd al-Rahman gave salam, the Prophet stood and completed the rakah he had missed, without adding anything else. The text also reports Abu Dawud’s note about some Companions’ view on prostrations of forgetfulness for one who catches an odd number of rakahs. The main lesson is to follow the prayer properly and complete what was missed."},"teachings":["The Prophet (صلى الله عليه وسلم) signaled the imam to continue leading.","He joined the congregation and prayed behind Abd al-Rahman ibn Awf.","He completed only the rakah that he had missed.","The narration shows order and calm in congregational prayer."],"related_hadiths":[{"id":"521","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"522","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E331" s="4" t="n"/>
@@ -8106,7 +8110,7 @@
       </c>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hadith About Repentance and Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear hadith about repentance, good ablution, two rak'ahs, and asking Allah for pardon after sin."},"heading":{"title":"Hadith About Repentance: Two Rak'ahs and Seeking Allah's Forgiveness","description":"This hadith about repentance shows a simple path back to Allah after a person falls into sin. The teaching is clear: a servant commits a sin, makes ablution well, stands for two rak'ahs, and asks Allah for pardon. The hadith then states that Allah pardons him. The report also shows Ali's care in accepting narrations from the Companions, and Abu Bakr is described as truthful in what he narrated. The core message is not to treat sin lightly, but also not to lose hope. When a believer remembers Allah after wronging the soul, turns to prayer, and asks forgiveness, the door of pardon is open by Allah's mercy as stated in this narration."},"teachings":["When a person sins, the hadith directs him to return to Allah through good ablution, prayer, and seeking pardon.","Two rak'ahs can be a sincere way to turn back to Allah after doing wrong.","The verse mentioned in the hadith links remembering Allah after sin with asking forgiveness."],"related_hadiths":[{"id":"1395","book_id":"6","label":"Sunan Ibn Majah"},{"id":"406","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"1524","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hadith About Repentance and Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear hadith about repentance, good ablution, two rak'ahs, and asking Allah for pardon after sin."},"heading":{"title":"Hadith About Repentance: Two Rak'ahs and Seeking Allah's Forgiveness","description":"This hadith about repentance shows a simple path back to Allah after a person falls into sin. The teaching is clear: a servant commits a sin, makes ablution well, stands for two rak'ahs, and asks Allah for pardon. The hadith then states that Allah pardons him. The report also shows Ali's care in accepting narrations from the Companions, and Abu Bakr is described as truthful in what he narrated. The core message is not to treat sin lightly, but also not to lose hope. When a believer remembers Allah after wronging the soul, turns to prayer, and asks forgiveness, the door of pardon is open by Allah's mercy as stated in this narration."},"teachings":["When a person sins, the hadith directs him to return to Allah through good ablution, prayer, and seeking pardon.","Two rak'ahs can be a sincere way to turn back to Allah after doing wrong.","The verse mentioned in the hadith links remembering Allah after sin with asking forgiveness."],"related_hadiths":[{"id":"1395","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"406","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"1524","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E332" s="4" t="n"/>
@@ -8129,7 +8133,7 @@
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua After Salah for Dhikr and Shukr","description":"$book_name$ $hadith_number$ - $chapter_name$. A loved companion is taught to ask Allah for help in remembrance, thanks, and worship after every prayer."},"heading":{"title":"Dua After Salah: Allahumma A'inni Ala Dhikrika Wa Shukrika","description":"This dua after salah was taught with warmth and love. The Prophet صلى الله عليه وسلم held Mu'adh's hand and told him that he loved him. Then he gave him a short but rich supplication to say after every prescribed prayer: asking Allah for help in remembering Him, thanking Him, and worshipping Him well. The hadith keeps the focus on dependence on Allah. Even acts like dhikr, gratitude, and good worship are things a believer asks Allah to help with. Mu'adh then passed this supplication on, and it was passed to others. The hadith teaches that regular prayer should lead to a heart that keeps asking Allah for better worship."},"teachings":["After prayer, a believer can ask Allah for help in remembering Him, thanking Him, and worshipping Him well.","The Prophet صلى الله عليه وسلم taught this dua with love and personal care for Mu'adh.","Good worship is something a person seeks help for from Allah, not just from personal effort."],"related_hadiths":[{"id":"1523","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1524","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1538","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua After Salah for Dhikr and Shukr","description":"$book_name$ $hadith_number$ - $chapter_name$. A loved companion is taught to ask Allah for help in remembrance, thanks, and worship after every prayer."},"heading":{"title":"Dua After Salah: Allahumma A'inni Ala Dhikrika Wa Shukrika","description":"This dua after salah was taught with warmth and love. The Prophet صلى الله عليه وسلم held Mu'adh's hand and told him that he loved him. Then he gave him a short but rich supplication to say after every prescribed prayer: asking Allah for help in remembering Him, thanking Him, and worshipping Him well. The hadith keeps the focus on dependence on Allah. Even acts like dhikr, gratitude, and good worship are things a believer asks Allah to help with. Mu'adh then passed this supplication on, and it was passed to others. The hadith teaches that regular prayer should lead to a heart that keeps asking Allah for better worship."},"teachings":["After prayer, a believer can ask Allah for help in remembering Him, thanking Him, and worshipping Him well.","The Prophet صلى الله عليه وسلم taught this dua with love and personal care for Mu'adh.","Good worship is something a person seeks help for from Allah, not just from personal effort."],"related_hadiths":[{"id":"1523","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1524","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1538","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E333" s="4" t="n"/>
@@ -8152,7 +8156,7 @@
       </c>
       <c r="D334" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reciting Mu'awwidhat After Every Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. A direct command to recite the Mu'awwidhat after every prayer as part of a steady prayer routine."},"heading":{"title":"Mu'awwidhat After Prayer: A Hadith on Reciting the Last Three Surahs","description":"This hadith about Mu'awwidhat after prayer is short and direct. Uqbah ibn Amir says that the Messenger of Allah صلى الله عليه وسلم commanded him to recite the Mu'awwidhatan, described in the provided translation as the last three surahs of the Qur'an, after every prayer. The teaching is easy to remember because the action is tied to a daily act that is already repeated: prayer. The hadith does not give a long explanation or list extra details. It simply shows that reciting these surahs after every prayer was something the Prophet صلى الله عليه وسلم instructed. The main focus is a regular habit of Qur'an recitation connected to salah."},"teachings":["The Prophet صلى الله عليه وسلم instructed Uqbah ibn Amir to recite the Mu'awwidhat after every prayer.","A small regular recitation can be tied to the daily prayer routine.","The hadith keeps the instruction simple and easy to practice."],"related_hadiths":[{"id":"1522","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1524","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1525","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reciting Mu'awwidhat After Every Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. A direct command to recite the Mu'awwidhat after every prayer as part of a steady prayer routine."},"heading":{"title":"Mu'awwidhat After Prayer: A Hadith on Reciting the Last Three Surahs","description":"This hadith about Mu'awwidhat after prayer is short and direct. Uqbah ibn Amir says that the Messenger of Allah صلى الله عليه وسلم commanded him to recite the Mu'awwidhatan, described in the provided translation as the last three surahs of the Qur'an, after every prayer. The teaching is easy to remember because the action is tied to a daily act that is already repeated: prayer. The hadith does not give a long explanation or list extra details. It simply shows that reciting these surahs after every prayer was something the Prophet صلى الله عليه وسلم instructed. The main focus is a regular habit of Qur'an recitation connected to salah."},"teachings":["The Prophet صلى الله عليه وسلم instructed Uqbah ibn Amir to recite the Mu'awwidhat after every prayer.","A small regular recitation can be tied to the daily prayer routine.","The hadith keeps the instruction simple and easy to practice."],"related_hadiths":[{"id":"1522","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1524","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1525","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E334" s="4" t="n"/>
@@ -8175,7 +8179,7 @@
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua in Distress and Pure Tawhid","description":"$book_name$ $hadith_number$ - $chapter_name$. A short supplication for distress that turns the heart to Allah alone without associating partners."},"heading":{"title":"Dua in Distress: Allah, Allah Is My Lord","description":"This hadith about dua in distress gives a very short phrase for hard moments. The Prophet صلى الله عليه وسلم asked Asma' bint Umays whether he should teach her words to say during distress. The words are: \"Allah, Allah is my Lord, I do not associate anything as partner with Him.\" The hadith does not list the type of distress, so the explanation should stay general. Its core message is to return to tawhid when the heart feels pressure. The phrase reminds a believer who the Lord is and that worship and reliance belong to Him alone. It is not a long dua, but it is full of faith, clarity, and calm trust in Allah."},"teachings":["In distress, the hadith teaches turning to Allah with words of tawhid.","The phrase affirms Allah as Lord and rejects associating partners with Him.","A short supplication can carry a clear and strong meaning."],"related_hadiths":[{"id":"1537","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1539","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1540","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua in Distress and Pure Tawhid","description":"$book_name$ $hadith_number$ - $chapter_name$. A short supplication for distress that turns the heart to Allah alone without associating partners."},"heading":{"title":"Dua in Distress: Allah, Allah Is My Lord","description":"This hadith about dua in distress gives a very short phrase for hard moments. The Prophet صلى الله عليه وسلم asked Asma' bint Umays whether he should teach her words to say during distress. The words are: \"Allah, Allah is my Lord, I do not associate anything as partner with Him.\" The hadith does not list the type of distress, so the explanation should stay general. Its core message is to return to tawhid when the heart feels pressure. The phrase reminds a believer who the Lord is and that worship and reliance belong to Him alone. It is not a long dua, but it is full of faith, clarity, and calm trust in Allah."},"teachings":["In distress, the hadith teaches turning to Allah with words of tawhid.","The phrase affirms Allah as Lord and rejects associating partners with Him.","A short supplication can carry a clear and strong meaning."],"related_hadiths":[{"id":"1537","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1539","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1540","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E335" s="4" t="n"/>
@@ -8198,7 +8202,7 @@
       </c>
       <c r="D336" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Hawla Wa La Quwwata and Quiet Supplication","description":"$book_name$ $hadith_number$ - $chapter_name$. A journey hadith teaching calm supplication and the treasure phrase: La hawla wa la quwwata illa billah."},"heading":{"title":"La Hawla Wa La Quwwata: A Treasure of Paradise and Calm Dhikr","description":"This hadith about La hawla wa la quwwata illa billah teaches two clear points. During a journey near Medina, some people raised their voices saying Allahu Akbar. The Prophet صلى الله عليه وسلم reminded them that they were not calling upon one who is deaf or absent. Allah is near, so supplication does not need loud strain. Then he told Abu Musa about one of the treasures of Paradise: \"There is no might and there is no power except in Allah.\" The hadith connects calm dhikr with deep reliance on Allah. It teaches that Allah hears, Allah is near, and real power belongs to Him alone."},"teachings":["The Prophet صلى الله عليه وسلم corrected raising the voice in supplication by reminding people that Allah is not deaf or absent.","The phrase La hawla wa la quwwata illa billah is called one of the treasures of Paradise in this hadith.","The hadith teaches calm remembrance and reliance on Allah's power."],"related_hadiths":[{"id":"1527","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1528","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1522","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | La Hawla Wa La Quwwata and Quiet Supplication","description":"$book_name$ $hadith_number$ - $chapter_name$. A journey hadith teaching calm supplication and the treasure phrase: La hawla wa la quwwata illa billah."},"heading":{"title":"La Hawla Wa La Quwwata: A Treasure of Paradise and Calm Dhikr","description":"This hadith about La hawla wa la quwwata illa billah teaches two clear points. During a journey near Medina, some people raised their voices saying Allahu Akbar. The Prophet صلى الله عليه وسلم reminded them that they were not calling upon one who is deaf or absent. Allah is near, so supplication does not need loud strain. Then he told Abu Musa about one of the treasures of Paradise: \"There is no might and there is no power except in Allah.\" The hadith connects calm dhikr with deep reliance on Allah. It teaches that Allah hears, Allah is near, and real power belongs to Him alone."},"teachings":["The Prophet صلى الله عليه وسلم corrected raising the voice in supplication by reminding people that Allah is not deaf or absent.","The phrase La hawla wa la quwwata illa billah is called one of the treasures of Paradise in this hadith.","The hadith teaches calm remembrance and reliance on Allah's power."],"related_hadiths":[{"id":"1527","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1528","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1522","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E336" s="4" t="n"/>
@@ -8221,7 +8225,7 @@
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Call Upon One Deaf or Absent","description":"$book_name$ $hadith_number$ - $chapter_name$. A hill-climb narration reminding believers that Allah hears and is not absent when they call on Him."},"heading":{"title":"Quiet Dhikr Hadith: You Are Not Calling One Deaf or Absent","description":"This hadith about quiet dhikr comes through Abu Musa al-Ash'ari. The Companions were with the Prophet صلى الله عليه وسلم while climbing the turn of a hill. A man raised his voice each time he ascended, saying, \"There is no god but Allah, and Allah is most great.\" The Prophet صلى الله عليه وسلم then said that they were not calling one who is deaf or absent. The report then continues in the same meaning as the related narration. The main lesson is not against remembering Allah, because the words of dhikr are good. The correction is about the manner: a person should remember that Allah hears and is near, so shouting is not needed."},"teachings":["The hadith teaches that Allah is not deaf or absent when a believer calls on Him.","Dhikr is good, but the manner of saying it should reflect awareness of Allah's nearness.","The Prophet صلى الله عليه وسلم corrected the Companions with a clear reminder about supplication."],"related_hadiths":[{"id":"1526","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1528","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1524","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Call Upon One Deaf or Absent","description":"$book_name$ $hadith_number$ - $chapter_name$. A hill-climb narration reminding believers that Allah hears and is not absent when they call on Him."},"heading":{"title":"Quiet Dhikr Hadith: You Are Not Calling One Deaf or Absent","description":"This hadith about quiet dhikr comes through Abu Musa al-Ash'ari. The Companions were with the Prophet صلى الله عليه وسلم while climbing the turn of a hill. A man raised his voice each time he ascended, saying, \"There is no god but Allah, and Allah is most great.\" The Prophet صلى الله عليه وسلم then said that they were not calling one who is deaf or absent. The report then continues in the same meaning as the related narration. The main lesson is not against remembering Allah, because the words of dhikr are good. The correction is about the manner: a person should remember that Allah hears and is near, so shouting is not needed."},"teachings":["The hadith teaches that Allah is not deaf or absent when a believer calls on Him.","Dhikr is good, but the manner of saying it should reflect awareness of Allah's nearness.","The Prophet صلى الله عليه وسلم corrected the Companions with a clear reminder about supplication."],"related_hadiths":[{"id":"1526","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1528","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1524","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E337" s="4" t="n"/>
@@ -8244,7 +8248,7 @@
       </c>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Be Lenient to Yourselves in Dhikr","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds a gentle command: be lenient to yourselves while calling upon Allah."},"heading":{"title":"Be Lenient to Yourselves: A Hadith on Gentle Dhikr","description":"This hadith is another version of the same report from Abu Musa al-Ash'ari. It adds the Prophet's صلى الله عليه وسلم words: \"Be lenient to yourselves, O people.\" In the surrounding narration, people had raised their voices in dhikr during travel, and the Prophet صلى الله عليه وسلم reminded them that Allah is not deaf or absent. This version highlights ease and gentleness in worship. The hadith about gentle dhikr does not cancel remembrance of Allah. Instead, it teaches that calling on Allah should not become hard on the self through unnecessary loudness or strain. The believer can remember Allah with a calm heart and a measured voice."},"teachings":["The Prophet صلى الله عليه وسلم told the people to be lenient to themselves.","The hadith points to ease and calmness in dhikr.","Calling upon Allah does not require unnecessary strain or loudness."],"related_hadiths":[{"id":"1526","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1527","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1525","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Be Lenient to Yourselves in Dhikr","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds a gentle command: be lenient to yourselves while calling upon Allah."},"heading":{"title":"Be Lenient to Yourselves: A Hadith on Gentle Dhikr","description":"This hadith is another version of the same report from Abu Musa al-Ash'ari. It adds the Prophet's صلى الله عليه وسلم words: \"Be lenient to yourselves, O people.\" In the surrounding narration, people had raised their voices in dhikr during travel, and the Prophet صلى الله عليه وسلم reminded them that Allah is not deaf or absent. This version highlights ease and gentleness in worship. The hadith about gentle dhikr does not cancel remembrance of Allah. Instead, it teaches that calling on Allah should not become hard on the self through unnecessary loudness or strain. The believer can remember Allah with a calm heart and a measured voice."},"teachings":["The Prophet صلى الله عليه وسلم told the people to be lenient to themselves.","The hadith points to ease and calmness in dhikr.","Calling upon Allah does not require unnecessary strain or loudness."],"related_hadiths":[{"id":"1526","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1527","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1525","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E338" s="4" t="n"/>
@@ -8267,7 +8271,7 @@
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | I Am Pleased With Allah as Lord","description":"$book_name$ $hadith_number$ - $chapter_name$. A powerful faith statement: being pleased with Allah as Lord, Islam as religion, and Muhammad صلى الله عليه وسلم as Messenger."},"heading":{"title":"I Am Pleased With Allah as Lord: A Hadith on Faith Declaration","description":"This hadith about being pleased with Allah as Lord teaches a short statement of faith and contentment. Abu Sa'id al-Khudri reported that the Messenger of Allah صلى الله عليه وسلم said that whoever says, \"I am pleased with Allah as Lord, with Islam as religion and with Muhammad صلى الله عليه وسلم as Apostle,\" Paradise will be his due. The hadith uses clear words: Lord, religion, and Messenger. It gathers the believer's loyalty and acceptance in one phrase. The explanation should stay close to the text: it is not about listing many actions or adding conditions not mentioned here. It is a declaration of faith, acceptance, and satisfaction with what Allah has chosen for the believer."},"teachings":["The hadith teaches a concise declaration of being pleased with Allah, Islam, and Muhammad صلى الله عليه وسلم.","The text states a great reward for the one who says this statement.","The phrase gathers faith in Allah, religion, and Messenger in simple words."],"related_hadiths":[{"id":"1525","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1530","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1522","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | I Am Pleased With Allah as Lord","description":"$book_name$ $hadith_number$ - $chapter_name$. A powerful faith statement: being pleased with Allah as Lord, Islam as religion, and Muhammad صلى الله عليه وسلم as Messenger."},"heading":{"title":"I Am Pleased With Allah as Lord: A Hadith on Faith Declaration","description":"This hadith about being pleased with Allah as Lord teaches a short statement of faith and contentment. Abu Sa'id al-Khudri reported that the Messenger of Allah صلى الله عليه وسلم said that whoever says, \"I am pleased with Allah as Lord, with Islam as religion and with Muhammad صلى الله عليه وسلم as Apostle,\" Paradise will be his due. The hadith uses clear words: Lord, religion, and Messenger. It gathers the believer's loyalty and acceptance in one phrase. The explanation should stay close to the text: it is not about listing many actions or adding conditions not mentioned here. It is a declaration of faith, acceptance, and satisfaction with what Allah has chosen for the believer."},"teachings":["The hadith teaches a concise declaration of being pleased with Allah, Islam, and Muhammad صلى الله عليه وسلم.","The text states a great reward for the one who says this statement.","The phrase gathers faith in Allah, religion, and Messenger in simple words."],"related_hadiths":[{"id":"1525","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1530","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1522","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E339" s="4" t="n"/>
@@ -8290,7 +8294,7 @@
       </c>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bilal Describes Wiping Over Turban and Socks","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration records Bilal describing the Prophet’s wudu with wiping over his turban and socks."},"heading":{"title":"Hadith About Bilal and the Prophet’s Wudu","description":"This hadith about Bilal and the Prophet’s wudu records a question asked by Abd al-Rahman ibn Awf. He asked Bilal about the ablution of the Messenger of Allah (صلى الله عليه وسلم). Bilal answered with a simple description: the Prophet would go out to relieve himself, then Bilal would bring him water. The Prophet would perform ablution and wipe over his turban and socks. The report is direct and practical. It does not give every step of wudu, but it highlights the part being asked about: wiping over a head covering and footwear. For readers searching Bilal wudu hadith or wiping over turban and socks hadith, this narration gives a clear Companion report tied to the Prophet’s regular practice as Bilal witnessed it."},"teachings":["Bilal was asked about the Prophet’s wudu.","He described bringing water after the Prophet relieved himself.","The Prophet (صلى الله عليه وسلم) wiped over his turban and socks in the report.","The narration gives a simple Companion account of wudu practice."],"related_hadiths":[{"id":"561","book_id":"6","label":"Sunan Ibn Majah"},{"id":"204","book_id":"1","label":"Sahih Bukhari"},{"id":"274a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bilal Describes Wiping Over Turban and Socks","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration records Bilal describing the Prophet’s wudu with wiping over his turban and socks."},"heading":{"title":"Hadith About Bilal and the Prophet’s Wudu","description":"This hadith about Bilal and the Prophet’s wudu records a question asked by Abd al-Rahman ibn Awf. He asked Bilal about the ablution of the Messenger of Allah (صلى الله عليه وسلم). Bilal answered with a simple description: the Prophet would go out to relieve himself, then Bilal would bring him water. The Prophet would perform ablution and wipe over his turban and socks. The report is direct and practical. It does not give every step of wudu, but it highlights the part being asked about: wiping over a head covering and footwear. For readers searching Bilal wudu hadith or wiping over turban and socks hadith, this narration gives a clear Companion report tied to the Prophet’s regular practice as Bilal witnessed it."},"teachings":["Bilal was asked about the Prophet’s wudu.","He described bringing water after the Prophet relieved himself.","The Prophet (صلى الله عليه وسلم) wiped over his turban and socks in the report.","The narration gives a simple Companion account of wudu practice."],"related_hadiths":[{"id":"561","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"204","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E340" s="4" t="n"/>
@@ -8313,7 +8317,7 @@
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Send Many Blessings on Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. A Friday hadith encouraging many blessings on the Prophet صلى الله عليه وسلم because they are submitted to him."},"heading":{"title":"Friday Salawat Hadith: Send Many Blessings on the Prophet صلى الله عليه وسلم","description":"This Friday salawat hadith teaches a special practice for Friday. Aws ibn Aws reported that the Prophet صلى الله عليه وسلم said Friday is among the most excellent of days, so believers should invoke many blessings on him on that day. The reason given in the hadith is that those blessings are submitted to him. When the Companions asked how this could happen after death, the Prophet صلى الله عليه وسلم said that Allah has prohibited the earth from consuming the bodies of the Prophets. The explanation should stay with the text: the hadith highlights Friday, frequent salawat, and the honored state of the Prophets' bodies as stated in the narration."},"teachings":["Friday is described in the hadith as among the most excellent days.","The Prophet صلى الله عليه وسلم instructed believers to send many blessings on him on Friday.","The hadith states that those blessings are submitted to him."],"related_hadiths":[{"id":"1530","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1533","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1524","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Send Many Blessings on Friday","description":"$book_name$ $hadith_number$ - $chapter_name$. A Friday hadith encouraging many blessings on the Prophet صلى الله عليه وسلم because they are submitted to him."},"heading":{"title":"Friday Salawat Hadith: Send Many Blessings on the Prophet صلى الله عليه وسلم","description":"This Friday salawat hadith teaches a special practice for Friday. Aws ibn Aws reported that the Prophet صلى الله عليه وسلم said Friday is among the most excellent of days, so believers should invoke many blessings on him on that day. The reason given in the hadith is that those blessings are submitted to him. When the Companions asked how this could happen after death, the Prophet صلى الله عليه وسلم said that Allah has prohibited the earth from consuming the bodies of the Prophets. The explanation should stay with the text: the hadith highlights Friday, frequent salawat, and the honored state of the Prophets' bodies as stated in the narration."},"teachings":["Friday is described in the hadith as among the most excellent days.","The Prophet صلى الله عليه وسلم instructed believers to send many blessings on him on Friday.","The hadith states that those blessings are submitted to him."],"related_hadiths":[{"id":"1530","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1533","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1524","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E341" s="4" t="n"/>
@@ -8336,7 +8340,7 @@
       </c>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Curse Yourself or Family","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning against harmful prayers on oneself, children, servants, or property at a time of answer."},"heading":{"title":"Do Not Curse Yourself: A Hadith on Guarding the Tongue in Dua","description":"This hadith about not cursing yourself is a strong reminder to guard the tongue during anger and stress. Jabir ibn Abdullah reported that the Prophet صلى الله عليه وسلم said not to invoke curse on yourselves, your children, your servants, or your property. The reason given is that a person may say such words at a time when Allah is asked and grants the request. The hadith does not tell us to stop making dua. It teaches us to avoid harmful dua. A believer should be careful with words, especially when upset, because supplication is serious. The safest path is to ask for good, mercy, and protection rather than harm."},"teachings":["The hadith forbids invoking curses on oneself, children, servants, or property.","Words said in anger can be dangerous when they take the form of harmful supplication.","The hadith directs believers to take dua seriously and guard the tongue."],"related_hadiths":[{"id":"1534","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1535","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1536","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Curse Yourself or Family","description":"$book_name$ $hadith_number$ - $chapter_name$. A warning against harmful prayers on oneself, children, servants, or property at a time of answer."},"heading":{"title":"Do Not Curse Yourself: A Hadith on Guarding the Tongue in Dua","description":"This hadith about not cursing yourself is a strong reminder to guard the tongue during anger and stress. Jabir ibn Abdullah reported that the Prophet صلى الله عليه وسلم said not to invoke curse on yourselves, your children, your servants, or your property. The reason given is that a person may say such words at a time when Allah is asked and grants the request. The hadith does not tell us to stop making dua. It teaches us to avoid harmful dua. A believer should be careful with words, especially when upset, because supplication is serious. The safest path is to ask for good, mercy, and protection rather than harm."},"teachings":["The hadith forbids invoking curses on oneself, children, servants, or property.","Words said in anger can be dangerous when they take the form of harmful supplication.","The hadith directs believers to take dua seriously and guard the tongue."],"related_hadiths":[{"id":"1534","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1535","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1536","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E342" s="4" t="n"/>
@@ -8359,7 +8363,7 @@
       </c>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for an Absent Brother","description":"$book_name$ $hadith_number$ - $chapter_name$. A hadith on praying for an absent Muslim brother while angels say Amin and ask the same for you."},"heading":{"title":"Dua for an Absent Brother: Angels Say Amin and the Like for You","description":"This hadith about dua for an absent brother teaches sincere care for another Muslim. Abu al-Darda' heard the Prophet صلى الله عليه وسلم say that when a Muslim supplicates for his absent brother, the angels say: Amin, and may you receive the like. The phrase \"absent brother\" shows that the prayer is made when the other person is not present. That makes the dua free from show and close to sincerity. The hadith also gives a beautiful response from the angels: they ask that the supplicating person receive the same. The main lesson is to make good dua for others, even when they do not hear it."},"teachings":["The hadith encourages making dua for a Muslim brother in his absence.","The angels say Amin to that supplication.","The angels also ask that the supplicating person receive the like."],"related_hadiths":[{"id":"1535","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1532","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1533","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for an Absent Brother","description":"$book_name$ $hadith_number$ - $chapter_name$. A hadith on praying for an absent Muslim brother while angels say Amin and ask the same for you."},"heading":{"title":"Dua for an Absent Brother: Angels Say Amin and the Like for You","description":"This hadith about dua for an absent brother teaches sincere care for another Muslim. Abu al-Darda' heard the Prophet صلى الله عليه وسلم say that when a Muslim supplicates for his absent brother, the angels say: Amin, and may you receive the like. The phrase \"absent brother\" shows that the prayer is made when the other person is not present. That makes the dua free from show and close to sincerity. The hadith also gives a beautiful response from the angels: they ask that the supplicating person receive the same. The main lesson is to make good dua for others, even when they do not hear it."},"teachings":["The hadith encourages making dua for a Muslim brother in his absence.","The angels say Amin to that supplication.","The angels also ask that the supplicating person receive the like."],"related_hadiths":[{"id":"1535","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1532","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1533","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E343" s="4" t="n"/>
@@ -8382,7 +8386,7 @@
       </c>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Quickest Answered Dua for Another Muslim","description":"$book_name$ $hadith_number$ - $chapter_name$. The quickest answered supplication is described as one distant Muslim praying for another."},"heading":{"title":"Answered Dua Hadith: A Distant Muslim Praying for Another","description":"This hadith about answered dua focuses on one special kind of supplication: a distant Muslim praying for another distant Muslim. Abdullah ibn Amr ibn al-As narrated that the Prophet صلى الله عليه وسلم said the supplication that gets the quickest answer is the dua made by one distant Muslim for another. The text highlights care that is not based on being seen, praised, or thanked in person. It is a prayer made from a distance, for someone else. This connects closely with the idea of sincere dua for an absent brother. The wording of the hadith gives a strong encouragement to remember others in private prayers."},"teachings":["The hadith praises supplication made by one distant Muslim for another.","It describes this kind of dua as the quickest in answer.","Praying for others from a distance points to sincerity and care."],"related_hadiths":[{"id":"1534","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1536","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1532","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Quickest Answered Dua for Another Muslim","description":"$book_name$ $hadith_number$ - $chapter_name$. The quickest answered supplication is described as one distant Muslim praying for another."},"heading":{"title":"Answered Dua Hadith: A Distant Muslim Praying for Another","description":"This hadith about answered dua focuses on one special kind of supplication: a distant Muslim praying for another distant Muslim. Abdullah ibn Amr ibn al-As narrated that the Prophet صلى الله عليه وسلم said the supplication that gets the quickest answer is the dua made by one distant Muslim for another. The text highlights care that is not based on being seen, praised, or thanked in person. It is a prayer made from a distance, for someone else. This connects closely with the idea of sincere dua for an absent brother. The wording of the hadith gives a strong encouragement to remember others in private prayers."},"teachings":["The hadith praises supplication made by one distant Muslim for another.","It describes this kind of dua as the quickest in answer.","Praying for others from a distance points to sincerity and care."],"related_hadiths":[{"id":"1534","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1536","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1532","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E344" s="4" t="n"/>
@@ -8405,7 +8409,7 @@
       </c>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Supplications That Are Answered","description":"$book_name$ $hadith_number$ - $chapter_name$. A hadith naming three answered supplications: a father, a traveller, and one who has been wronged."},"heading":{"title":"Three Supplications Are Answered: Father, Traveller, and the Wronged","description":"This hadith about three supplications that are answered names three people whose dua is answered without doubt in the wording of the narration: a father, a traveller, and one who has been wronged. Abu Hurayrah narrated this from the Prophet صلى الله عليه وسلم. The hadith teaches that certain states and relationships carry serious weight in supplication. A father's dua should not be treated lightly. A traveller's dua is also named. The dua of the wronged person is included, reminding believers to avoid oppression and harm. The explanation should not add extra categories here. The text gives these three, so the lesson stays with them."},"teachings":["The hadith names the supplication of a father as answered.","It also names the supplication of a traveller.","It warns by implication that the dua of one who has been wronged is serious."],"related_hadiths":[{"id":"1535","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1534","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1532","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Supplications That Are Answered","description":"$book_name$ $hadith_number$ - $chapter_name$. A hadith naming three answered supplications: a father, a traveller, and one who has been wronged."},"heading":{"title":"Three Supplications Are Answered: Father, Traveller, and the Wronged","description":"This hadith about three supplications that are answered names three people whose dua is answered without doubt in the wording of the narration: a father, a traveller, and one who has been wronged. Abu Hurayrah narrated this from the Prophet صلى الله عليه وسلم. The hadith teaches that certain states and relationships carry serious weight in supplication. A father's dua should not be treated lightly. A traveller's dua is also named. The dua of the wronged person is included, reminding believers to avoid oppression and harm. The explanation should not add extra categories here. The text gives these three, so the lesson stays with them."},"teachings":["The hadith names the supplication of a father as answered.","It also names the supplication of a traveller.","It warns by implication that the dua of one who has been wronged is serious."],"related_hadiths":[{"id":"1535","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1534","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1532","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E345" s="4" t="n"/>
@@ -8428,7 +8432,7 @@
       </c>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua When Fearing a People","description":"$book_name$ $hadith_number$ - $chapter_name$. A protection dua the Prophet صلى الله عليه وسلم said when he feared a group of people and sought refuge from their evil."},"heading":{"title":"Dua When Fearing People: Seeking Allah's Shield and Protection","description":"This hadith about dua when fearing people gives a short prayer of protection. Abu Musa al-Ash'ari narrated that when the Prophet صلى الله عليه وسلم feared a group of people, he would say: \"O Allah, we make Thee our shield against them, and take refuge in Thee from their evils.\" The hadith shows turning to Allah in a moment of fear. It does not give a long plan or a list of actions. The main act mentioned is supplication. The wording asks Allah to be a shield and seeks refuge from evil. This teaches that fear should lead the believer to seek Allah's help, protection, and safety."},"teachings":["When facing fear from people, the Prophet صلى الله عليه وسلم turned to Allah in supplication.","The dua asks Allah to be a shield against harm.","The hadith teaches seeking refuge in Allah from the evils of others."],"related_hadiths":[{"id":"1525","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1539","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1540","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua When Fearing a People","description":"$book_name$ $hadith_number$ - $chapter_name$. A protection dua the Prophet صلى الله عليه وسلم said when he feared a group of people and sought refuge from their evil."},"heading":{"title":"Dua When Fearing People: Seeking Allah's Shield and Protection","description":"This hadith about dua when fearing people gives a short prayer of protection. Abu Musa al-Ash'ari narrated that when the Prophet صلى الله عليه وسلم feared a group of people, he would say: \"O Allah, we make Thee our shield against them, and take refuge in Thee from their evils.\" The hadith shows turning to Allah in a moment of fear. It does not give a long plan or a list of actions. The main act mentioned is supplication. The wording asks Allah to be a shield and seeks refuge from evil. This teaches that fear should lead the believer to seek Allah's help, protection, and safety."},"teachings":["When facing fear from people, the Prophet صلى الله عليه وسلم turned to Allah in supplication.","The dua asks Allah to be a shield against harm.","The hadith teaches seeking refuge in Allah from the evils of others."],"related_hadiths":[{"id":"1525","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1539","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1540","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E346" s="4" t="n"/>
@@ -8451,7 +8455,7 @@
       </c>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istikhara Dua for Seeking Allah's Choice","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught istikhara with two voluntary rak'ahs and a dua asking Allah for the better choice."},"heading":{"title":"Istikhara Dua Hadith: Seeking Allah's Choice Before a Decision","description":"This istikhara dua hadith gives a detailed way to seek what is beneficial from Allah. Jabir ibn Abdullah said the Prophet صلى الله عليه وسلم taught them istikhara as he taught a surah from the Qur'an. When a person intends to do a matter, he should pray two voluntary rak'ahs and then ask Allah for the better choice through His knowledge and power. The dua asks that if the matter is good for one's religion, life, afterlife, and end result, Allah decree it, make it easy, and bless it. If it is bad, the dua asks Allah to turn it away and give good wherever it may be, then make the person content with it."},"teachings":["Istikhara is made when a person intends to do a matter.","The hadith mentions two voluntary rak'ahs before the supplication.","The dua asks Allah for what is good and for contentment with His decree."],"related_hadiths":[{"id":"1521","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1522","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1524","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istikhara Dua for Seeking Allah's Choice","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught istikhara with two voluntary rak'ahs and a dua asking Allah for the better choice."},"heading":{"title":"Istikhara Dua Hadith: Seeking Allah's Choice Before a Decision","description":"This istikhara dua hadith gives a detailed way to seek what is beneficial from Allah. Jabir ibn Abdullah said the Prophet صلى الله عليه وسلم taught them istikhara as he taught a surah from the Qur'an. When a person intends to do a matter, he should pray two voluntary rak'ahs and then ask Allah for the better choice through His knowledge and power. The dua asks that if the matter is good for one's religion, life, afterlife, and end result, Allah decree it, make it easy, and bless it. If it is bad, the dua asks Allah to turn it away and give good wherever it may be, then make the person content with it."},"teachings":["Istikhara is made when a person intends to do a matter.","The hadith mentions two voluntary rak'ahs before the supplication.","The dua asks Allah for what is good and for contentment with His decree."],"related_hadiths":[{"id":"1521","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1522","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1524","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E347" s="4" t="n"/>
@@ -8474,7 +8478,7 @@
       </c>
       <c r="D348" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Jarir’s Report After Surah al-Ma’idah","description":"$book_name$ $hadith_number$ - $chapter_name$. This report records Jarir wiping over socks and saying he saw the Messenger of Allah do it after al-Ma’idah."},"heading":{"title":"Hadith About Jarir Wiping Over Khuff After al-Ma’idah","description":"This hadith about Jarir wiping over khuff gives both an action and an answer to an objection. Jarir urinated, then performed wudu and wiped over his socks. When people questioned what he had done, he replied that he had seen the Messenger of Allah (صلى الله عليه وسلم) wiping. They suggested that this action might have been before the revelation of Surah al-Ma’idah. Jarir answered that he embraced Islam only after Surah al-Ma’idah was revealed. The text is important because it shows why the timing mattered to the people asking him. It also shows Jarir grounding his action in what he saw from the Prophet. For searches like wiping over khuff after Maidah hadith, this narration is a direct source."},"teachings":["Jarir wiped over his socks after performing wudu.","He based his action on seeing the Prophet (صلى الله عليه وسلم) do it.","The people raised a question about timing with Surah al-Ma’idah.","Jarir answered by mentioning when he embraced Islam."],"related_hadiths":[{"id":"272a","book_id":"2","label":"Sahih Muslim"},{"id":"94","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"543","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Jarir’s Report After Surah al-Ma’idah","description":"$book_name$ $hadith_number$ - $chapter_name$. This report records Jarir wiping over socks and saying he saw the Messenger of Allah do it after al-Ma’idah."},"heading":{"title":"Hadith About Jarir Wiping Over Khuff After al-Ma’idah","description":"This hadith about Jarir wiping over khuff gives both an action and an answer to an objection. Jarir urinated, then performed wudu and wiped over his socks. When people questioned what he had done, he replied that he had seen the Messenger of Allah (صلى الله عليه وسلم) wiping. They suggested that this action might have been before the revelation of Surah al-Ma’idah. Jarir answered that he embraced Islam only after Surah al-Ma’idah was revealed. The text is important because it shows why the timing mattered to the people asking him. It also shows Jarir grounding his action in what he saw from the Prophet. For searches like wiping over khuff after Maidah hadith, this narration is a direct source."},"teachings":["Jarir wiped over his socks after performing wudu.","He based his action on seeing the Prophet (صلى الله عليه وسلم) do it.","The people raised a question about timing with Surah al-Ma’idah.","Jarir answered by mentioning when he embraced Islam."],"related_hadiths":[{"id":"272a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"94","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"543","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E348" s="4" t="n"/>
@@ -8497,7 +8501,7 @@
       </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Against Weakness and Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. A refuge dua seeking protection from weakness, laziness, cowardice, old age, grave punishment, and trials."},"heading":{"title":"Dua Against Weakness and Laziness: Seeking Refuge From Life and Death Trials","description":"This hadith about dua against weakness and laziness records a supplication the Messenger of Allah صلى الله عليه وسلم used to say. Anas ibn Malik narrated that he sought refuge in Allah from weakness, laziness, cowardice, miserliness, and old age. He also sought refuge from the punishment of the grave and from the trials of life and death. The wording teaches a believer to ask Allah for protection from both personal weaknesses and serious trials. It is not only about outer problems. The dua also names qualities that can stop a person from doing good. The hadith gives a direct supplication for safety, strength, and protection from harm."},"teachings":["The Prophet صلى الله عليه وسلم sought refuge from weakness, laziness, cowardice, miserliness, and old age.","He sought refuge from punishment in the grave.","He also sought refuge from the trials of life and death."],"related_hadiths":[{"id":"1539","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1537","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1525","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Against Weakness and Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. A refuge dua seeking protection from weakness, laziness, cowardice, old age, grave punishment, and trials."},"heading":{"title":"Dua Against Weakness and Laziness: Seeking Refuge From Life and Death Trials","description":"This hadith about dua against weakness and laziness records a supplication the Messenger of Allah صلى الله عليه وسلم used to say. Anas ibn Malik narrated that he sought refuge in Allah from weakness, laziness, cowardice, miserliness, and old age. He also sought refuge from the punishment of the grave and from the trials of life and death. The wording teaches a believer to ask Allah for protection from both personal weaknesses and serious trials. It is not only about outer problems. The dua also names qualities that can stop a person from doing good. The hadith gives a direct supplication for safety, strength, and protection from harm."},"teachings":["The Prophet صلى الله عليه وسلم sought refuge from weakness, laziness, cowardice, miserliness, and old age.","He sought refuge from punishment in the grave.","He also sought refuge from the trials of life and death."],"related_hadiths":[{"id":"1539","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1537","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1525","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E349" s="4" t="n"/>
@@ -8520,7 +8524,7 @@
       </c>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Anxiety, Debt, and Grief","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn a Prophetic dua seeking Allah’s refuge from grief, anxiety, heavy debt, and being overpowered by people."},"heading":{"title":"Dua for Anxiety and Debt: Seeking Allah’s Protection","description":"This Hadith shares a simple but powerful dua for anxiety, grief, debt, and pressure from people. Anas b. Malik said that he served the Prophet (صلى الله عليه وسلم) and often heard him make this supplication. The words show that emotional pain and financial pressure are real struggles, and the Prophet (صلى الله عليه وسلم) turned to Allah for safety from them. The dua mentions grief and anxiety together, showing care for both sadness over what has happened and worry about what may come. It also asks protection from the hardship of debt and from being overpowered by men. The main lesson is clear: a believer should bring inner stress and outer pressure to Allah through sincere supplication."},"teachings":["The Prophet (صلى الله عليه وسلم) often sought refuge in Allah from grief and anxiety.","Debt can become a hardship, so asking Allah for relief from it is part of Prophetic guidance.","A believer may ask Allah for protection from being overpowered or pressured by others.","Serving and staying close to the Prophet (صلى الله عليه وسلم) allowed Anas to learn his regular supplications."],"related_hadiths":[{"id":"6369","book_id":"1","label":"Sahih Bukhari"},{"id":"5476","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Anxiety, Debt, and Grief","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn a Prophetic dua seeking Allah’s refuge from grief, anxiety, heavy debt, and being overpowered by people."},"heading":{"title":"Dua for Anxiety and Debt: Seeking Allah’s Protection","description":"This Hadith shares a simple but powerful dua for anxiety, grief, debt, and pressure from people. Anas b. Malik said that he served the Prophet (صلى الله عليه وسلم) and often heard him make this supplication. The words show that emotional pain and financial pressure are real struggles, and the Prophet (صلى الله عليه وسلم) turned to Allah for safety from them. The dua mentions grief and anxiety together, showing care for both sadness over what has happened and worry about what may come. It also asks protection from the hardship of debt and from being overpowered by men. The main lesson is clear: a believer should bring inner stress and outer pressure to Allah through sincere supplication."},"teachings":["The Prophet (صلى الله عليه وسلم) often sought refuge in Allah from grief and anxiety.","Debt can become a hardship, so asking Allah for relief from it is part of Prophetic guidance.","A believer may ask Allah for protection from being overpowered or pressured by others.","Serving and staying close to the Prophet (صلى الله عليه وسلم) allowed Anas to learn his regular supplications."],"related_hadiths":[{"id":"6369","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5476","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E350" s="4" t="n"/>
@@ -8543,7 +8547,7 @@
       </c>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Protection from Hell, Grave, and Dajjal","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear Prophetic dua seeking refuge from Hell, the grave, Dajjal, and the trials of life and death."},"heading":{"title":"Dua for Protection from the Grave, Hellfire, and Dajjal","description":"This Hadith teaches a dua for protection from major trials. Ibn Abbas said that the Messenger of Allah (صلى الله عليه وسلم) used to teach this supplication as he taught a surah from the Qur’an. This shows how important the words were in his teaching. The dua asks Allah for refuge from the punishment of Hell, the punishment of the grave, the trials of Al-Masihid-Dajjal, and the trials of life and death. The focus is not on a story or event, but on asking Allah for safety from harms that a person cannot face by personal strength alone. This Hadith is often searched as a dua for protection from Dajjal and punishment of the grave."},"teachings":["The Prophet (صلى الله عليه وسلم) taught this supplication with great care.","A believer should seek Allah’s refuge from the punishment of Hell and the grave.","The trials of Dajjal are specifically mentioned as something to seek protection from.","Life and death both contain trials, so a believer asks Allah for safety in both."],"related_hadiths":[{"id":"1377","book_id":"1","label":"Sahih Bukhari"},{"id":"588a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Protection from Hell, Grave, and Dajjal","description":"$book_name$ $hadith_number$ - $chapter_name$. A clear Prophetic dua seeking refuge from Hell, the grave, Dajjal, and the trials of life and death."},"heading":{"title":"Dua for Protection from the Grave, Hellfire, and Dajjal","description":"This Hadith teaches a dua for protection from major trials. Ibn Abbas said that the Messenger of Allah (صلى الله عليه وسلم) used to teach this supplication as he taught a surah from the Qur’an. This shows how important the words were in his teaching. The dua asks Allah for refuge from the punishment of Hell, the punishment of the grave, the trials of Al-Masihid-Dajjal, and the trials of life and death. The focus is not on a story or event, but on asking Allah for safety from harms that a person cannot face by personal strength alone. This Hadith is often searched as a dua for protection from Dajjal and punishment of the grave."},"teachings":["The Prophet (صلى الله عليه وسلم) taught this supplication with great care.","A believer should seek Allah’s refuge from the punishment of Hell and the grave.","The trials of Dajjal are specifically mentioned as something to seek protection from.","Life and death both contain trials, so a believer asks Allah for safety in both."],"related_hadiths":[{"id":"1377","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"588a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E351" s="4" t="n"/>
@@ -8566,7 +8570,7 @@
       </c>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Against Fire, Wealth, and Poverty Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. A concise dua seeking Allah’s refuge from the Fire and from the harms linked to richness and poverty."},"heading":{"title":"Dua Against the Trial of Fire, Wealth, and Poverty","description":"This Hadith gives a short supplication from the Prophet (صلى الله عليه وسلم), narrated by Aishah. He would seek refuge in Allah from the trials of the Fire, the punishment of the Fire, and from the evils of richness and poverty. The wording is balanced. It does not say wealth itself is evil, and it does not say poverty itself is blameworthy. Rather, the Prophet (صلى الله عليه وسلم) asked Allah for safety from the evil connected to both states. A person may be tested when having much, and may also be tested when having little. The Hadith teaches that a Muslim should ask Allah for protection in every condition, whether facing ease or hardship."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from both the trial and punishment of the Fire.","Richness can carry a trial, so a believer asks Allah for protection from its evil.","Poverty can also carry hardship, so a believer asks Allah for safety from its evil.","This dua teaches balance without blaming wealth or poverty in every case."],"related_hadiths":[{"id":"6376","book_id":"1","label":"Sahih Bukhari"},{"id":"5477","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Against Fire, Wealth, and Poverty Trials","description":"$book_name$ $hadith_number$ - $chapter_name$. A concise dua seeking Allah’s refuge from the Fire and from the harms linked to richness and poverty."},"heading":{"title":"Dua Against the Trial of Fire, Wealth, and Poverty","description":"This Hadith gives a short supplication from the Prophet (صلى الله عليه وسلم), narrated by Aishah. He would seek refuge in Allah from the trials of the Fire, the punishment of the Fire, and from the evils of richness and poverty. The wording is balanced. It does not say wealth itself is evil, and it does not say poverty itself is blameworthy. Rather, the Prophet (صلى الله عليه وسلم) asked Allah for safety from the evil connected to both states. A person may be tested when having much, and may also be tested when having little. The Hadith teaches that a Muslim should ask Allah for protection in every condition, whether facing ease or hardship."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from both the trial and punishment of the Fire.","Richness can carry a trial, so a believer asks Allah for protection from its evil.","Poverty can also carry hardship, so a believer asks Allah for safety from its evil.","This dua teaches balance without blaming wealth or poverty in every case."],"related_hadiths":[{"id":"6376","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5477","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E352" s="4" t="n"/>
@@ -8589,7 +8593,7 @@
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Against Poverty and Injustice","description":"$book_name$ $hadith_number$ - $chapter_name$. A Prophetic dua asking Allah for refuge from poverty, humiliation, and both causing or suffering wrong."},"heading":{"title":"Dua for Protection from Poverty, Humiliation, and Injustice","description":"This Hadith brings together two types of protection: personal hardship and moral safety. Abu Hurayrah narrated that the Prophet (صلى الله عليه وسلم) used to seek refuge in Allah from poverty, lack, and abasement. He also sought refuge from causing wrong or suffering wrong. The wording teaches a believer to care not only about being safe from hardship, but also about not becoming a source of harm to others. The dua against poverty and humiliation is direct, and the dua against injustice is balanced. It asks Allah to protect a person from being the wrongdoer and from being wronged. This makes it a strong daily supplication for dignity and fair conduct."},"teachings":["The Prophet (صلى الله عليه وسلم) sought Allah’s refuge from poverty, lack, and humiliation.","A believer should ask Allah not to become a person who wrongs others.","It is also valid to ask Allah for protection from being wronged.","This dua joins personal need with good character and justice."],"related_hadiths":[{"id":"3842","book_id":"6","label":"Sunan Ibn Majah"},{"id":"6376","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Against Poverty and Injustice","description":"$book_name$ $hadith_number$ - $chapter_name$. A Prophetic dua asking Allah for refuge from poverty, humiliation, and both causing or suffering wrong."},"heading":{"title":"Dua for Protection from Poverty, Humiliation, and Injustice","description":"This Hadith brings together two types of protection: personal hardship and moral safety. Abu Hurayrah narrated that the Prophet (صلى الله عليه وسلم) used to seek refuge in Allah from poverty, lack, and abasement. He also sought refuge from causing wrong or suffering wrong. The wording teaches a believer to care not only about being safe from hardship, but also about not becoming a source of harm to others. The dua against poverty and humiliation is direct, and the dua against injustice is balanced. It asks Allah to protect a person from being the wrongdoer and from being wronged. This makes it a strong daily supplication for dignity and fair conduct."},"teachings":["The Prophet (صلى الله عليه وسلم) sought Allah’s refuge from poverty, lack, and humiliation.","A believer should ask Allah not to become a person who wrongs others.","It is also valid to ask Allah for protection from being wronged.","This dua joins personal need with good character and justice."],"related_hadiths":[{"id":"3842","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"6376","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E353" s="4" t="n"/>
@@ -8612,7 +8616,7 @@
       </c>
       <c r="D354" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua to Protect Allah’s Blessings","description":"$book_name$ $hadith_number$ - $chapter_name$. A heartfelt dua asking Allah to protect His blessings, continued well-being, and safety from sudden punishment."},"heading":{"title":"Dua for Protection from Losing Allah’s Blessings","description":"This Hadith records one of the supplications of the Messenger of Allah (صلى الله عليه وسلم), narrated by Abdullah b. Umar. The Prophet (صلى الله عليه وسلم) sought refuge in Allah from the lifting of Allah’s blessings, the changing of His protection, the suddenness of His punishment, and all of His anger. The core message is gratitude with fear of losing what Allah has given. The dua does not list a single blessing. It speaks in a wide way, covering blessings, protection, punishment, and anger. This makes it a meaningful dua for anyone who knows that safety and ease are gifts from Allah. It teaches the heart to value blessings and ask Allah to keep them."},"teachings":["The Prophet (صلى الله عليه وسلم) asked Allah to protect him from the lifting of blessings.","Well-being and protection are gifts that can change, so they should be valued.","A believer may seek refuge from sudden punishment.","The dua teaches fear of Allah’s anger and hope in His protection."],"related_hadiths":[{"id":"2739","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua to Protect Allah’s Blessings","description":"$book_name$ $hadith_number$ - $chapter_name$. A heartfelt dua asking Allah to protect His blessings, continued well-being, and safety from sudden punishment."},"heading":{"title":"Dua for Protection from Losing Allah’s Blessings","description":"This Hadith records one of the supplications of the Messenger of Allah (صلى الله عليه وسلم), narrated by Abdullah b. Umar. The Prophet (صلى الله عليه وسلم) sought refuge in Allah from the lifting of Allah’s blessings, the changing of His protection, the suddenness of His punishment, and all of His anger. The core message is gratitude with fear of losing what Allah has given. The dua does not list a single blessing. It speaks in a wide way, covering blessings, protection, punishment, and anger. This makes it a meaningful dua for anyone who knows that safety and ease are gifts from Allah. It teaches the heart to value blessings and ask Allah to keep them."},"teachings":["The Prophet (صلى الله عليه وسلم) asked Allah to protect him from the lifting of blessings.","Well-being and protection are gifts that can change, so they should be valued.","A believer may seek refuge from sudden punishment.","The dua teaches fear of Allah’s anger and hope in His protection."],"related_hadiths":[{"id":"2739","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E354" s="4" t="inlineStr">
@@ -8639,7 +8643,7 @@
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Against Hypocrisy and Bad Character","description":"$book_name$ $hadith_number$ - $chapter_name$. A short Prophetic dua seeking Allah’s refuge from division, hypocrisy, and evil character."},"heading":{"title":"Dua for Protection from Hypocrisy and Bad Character","description":"This Hadith focuses on the inner and social dangers that can harm a believer. Abu Hurayrah narrated that the Messenger of Allah (صلى الله عليه وسلم) used to seek refuge in Allah from divisiveness, hypocrisy, and evil character. The dua is short, but its meaning is wide. Divisiveness harms relationships and community life. Hypocrisy harms sincerity and faith. Evil character harms the way a person deals with Allah’s servants. The Hadith does not give a long explanation, so the safest lesson is to stay close to its words: ask Allah to protect the heart, speech, and behavior from these harms. It is a strong dua for anyone trying to improve manners and sincerity."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from divisiveness.","Hypocrisy is serious enough to be named in a direct supplication.","Bad character is something a believer should ask Allah to be saved from.","The dua links personal faith with social conduct."],"related_hadiths":[{"id":"5471","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Against Hypocrisy and Bad Character","description":"$book_name$ $hadith_number$ - $chapter_name$. A short Prophetic dua seeking Allah’s refuge from division, hypocrisy, and evil character."},"heading":{"title":"Dua for Protection from Hypocrisy and Bad Character","description":"This Hadith focuses on the inner and social dangers that can harm a believer. Abu Hurayrah narrated that the Messenger of Allah (صلى الله عليه وسلم) used to seek refuge in Allah from divisiveness, hypocrisy, and evil character. The dua is short, but its meaning is wide. Divisiveness harms relationships and community life. Hypocrisy harms sincerity and faith. Evil character harms the way a person deals with Allah’s servants. The Hadith does not give a long explanation, so the safest lesson is to stay close to its words: ask Allah to protect the heart, speech, and behavior from these harms. It is a strong dua for anyone trying to improve manners and sincerity."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from divisiveness.","Hypocrisy is serious enough to be named in a direct supplication.","Bad character is something a believer should ask Allah to be saved from.","The dua links personal faith with social conduct."],"related_hadiths":[{"id":"5471","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr">
@@ -8666,7 +8670,7 @@
       </c>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Against Hunger and Treachery","description":"$book_name$ $hadith_number$ - $chapter_name$. A Prophetic dua seeking Allah’s refuge from hunger as a hard companion and treachery as a hidden evil."},"heading":{"title":"Dua for Protection from Hunger and Treachery","description":"This Hadith, narrated by Abu Hurayrah, records a dua in which the Messenger of Allah (صلى الله عليه وسلم) sought refuge from hunger and treachery. The Prophet (صلى الله عليه وسلم) described hunger as an evil bed-fellow and treachery as an evil hidden trait. The wording shows two different harms. Hunger is a hardship that stays close to a person, like something lying beside them. Treachery is hidden inside, like a bad inner quality. The Hadith teaches Muslims to ask Allah for protection from both outward pain and inward betrayal. It also reminds us that faith is not only about avoiding visible harm, but also about guarding the trust and honesty within the heart."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from hunger as a hard companion.","Treachery is described as an evil hidden trait.","A believer should ask Allah for protection from outer hardship and inner corruption.","The dua points to the value of trustworthiness."],"related_hadiths":[{"id":"5468","book_id":"3","label":"Sunan an-Nasai"},{"id":"3354","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua Against Hunger and Treachery","description":"$book_name$ $hadith_number$ - $chapter_name$. A Prophetic dua seeking Allah’s refuge from hunger as a hard companion and treachery as a hidden evil."},"heading":{"title":"Dua for Protection from Hunger and Treachery","description":"This Hadith, narrated by Abu Hurayrah, records a dua in which the Messenger of Allah (صلى الله عليه وسلم) sought refuge from hunger and treachery. The Prophet (صلى الله عليه وسلم) described hunger as an evil bed-fellow and treachery as an evil hidden trait. The wording shows two different harms. Hunger is a hardship that stays close to a person, like something lying beside them. Treachery is hidden inside, like a bad inner quality. The Hadith teaches Muslims to ask Allah for protection from both outward pain and inward betrayal. It also reminds us that faith is not only about avoiding visible harm, but also about guarding the trust and honesty within the heart."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from hunger as a hard companion.","Treachery is described as an evil hidden trait.","A believer should ask Allah for protection from outer hardship and inner corruption.","The dua points to the value of trustworthiness."],"related_hadiths":[{"id":"5468","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"3354","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E356" s="4" t="n"/>
@@ -8689,7 +8693,7 @@
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua from a Prayer with No Benefit","description":"$book_name$ $hadith_number$ - $chapter_name$. A brief Prophetic dua asking Allah for refuge from a prayer that brings no benefit."},"heading":{"title":"Dua from a Prayer That Does Not Benefit","description":"This Hadith is short and direct. Anas bin Malik narrated that the Prophet (صلى الله عليه وسلم) would say, “O Allah, I seek refuge in You from a prayer that is of no benefit.” The text does not explain the full meaning of a prayer without benefit, so the safest explanation is to stay with the wording itself. The Prophet (صلى الله عليه وسلم) asked Allah to protect him from a form of prayer that does not bring benefit. This shows that a believer should not treat prayer as empty movements or routine words. The Hadith encourages concern for the quality and outcome of prayer, while still leaving the full matter to Allah."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from a prayer that does not benefit.","A believer should care about the benefit and effect of prayer.","Even acts of worship are brought to Allah through dua.","Short supplications can carry deep reminders."],"related_hadiths":[{"id":"2722","book_id":"2","label":"Sahih Muslim"},{"id":"1548","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua from a Prayer with No Benefit","description":"$book_name$ $hadith_number$ - $chapter_name$. A brief Prophetic dua asking Allah for refuge from a prayer that brings no benefit."},"heading":{"title":"Dua from a Prayer That Does Not Benefit","description":"This Hadith is short and direct. Anas bin Malik narrated that the Prophet (صلى الله عليه وسلم) would say, “O Allah, I seek refuge in You from a prayer that is of no benefit.” The text does not explain the full meaning of a prayer without benefit, so the safest explanation is to stay with the wording itself. The Prophet (صلى الله عليه وسلم) asked Allah to protect him from a form of prayer that does not bring benefit. This shows that a believer should not treat prayer as empty movements or routine words. The Hadith encourages concern for the quality and outcome of prayer, while still leaving the full matter to Allah."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from a prayer that does not benefit.","A believer should care about the benefit and effect of prayer.","Even acts of worship are brought to Allah through dua.","Short supplications can carry deep reminders."],"related_hadiths":[{"id":"2722","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1548","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E357" s="4" t="n"/>
@@ -8712,7 +8716,7 @@
       </c>
       <c r="D358" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Najashi’s Gift and Wiping Over Socks","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports that the Prophet wore two black simple socks, made wudu, and wiped over them."},"heading":{"title":"Hadith About the Najashi Gift and Wiping Over Socks","description":"This hadith about the Najashi gift and wiping over socks reports that the Negus presented two black and simple socks to the Messenger of Allah (صلى الله عليه وسلم). The Prophet put them on, then performed ablution and wiped over them. The wording is short, but it gives a clear action: wearing the socks, making wudu, and wiping over them. It also includes Abu Dawud’s note that this tradition was narrated by the people of Basrah alone. A careful explanation should not add more than the text gives. It does not discuss the full conditions of wiping, the material in detail, or the length of time. It simply records the gift and the Prophet’s action. For searches like Najashi socks hadith or wiping over socks in wudu, this narration is directly related."},"teachings":["The Negus gifted the Prophet (صلى الله عليه وسلم) two black simple socks.","The Prophet wore them before performing wudu.","He wiped over the socks during ablution.","Abu Dawud notes how this report was transmitted."],"related_hadiths":[{"id":"549","book_id":"6","label":"Sunan Ibn Majah"},{"id":"204","book_id":"1","label":"Sahih Bukhari"},{"id":"274a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Najashi’s Gift and Wiping Over Socks","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports that the Prophet wore two black simple socks, made wudu, and wiped over them."},"heading":{"title":"Hadith About the Najashi Gift and Wiping Over Socks","description":"This hadith about the Najashi gift and wiping over socks reports that the Negus presented two black and simple socks to the Messenger of Allah (صلى الله عليه وسلم). The Prophet put them on, then performed ablution and wiped over them. The wording is short, but it gives a clear action: wearing the socks, making wudu, and wiping over them. It also includes Abu Dawud’s note that this tradition was narrated by the people of Basrah alone. A careful explanation should not add more than the text gives. It does not discuss the full conditions of wiping, the material in detail, or the length of time. It simply records the gift and the Prophet’s action. For searches like Najashi socks hadith or wiping over socks in wudu, this narration is directly related."},"teachings":["The Negus gifted the Prophet (صلى الله عليه وسلم) two black simple socks.","The Prophet wore them before performing wudu.","He wiped over the socks during ablution.","Abu Dawud notes how this report was transmitted."],"related_hadiths":[{"id":"549","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"204","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"274a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E358" s="4" t="n"/>
@@ -8735,7 +8739,7 @@
       </c>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua from Evil of Past and Future Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. A concise dua seeking refuge from the evil of what one has done and what one has not done."},"heading":{"title":"Dua for Protection from the Evil of What I Have Done and Not Done","description":"This Hadith records a question asked to Aishah, the Mother of the Believers, about the supplication of the Messenger of Allah (صلى الله عليه وسلم). She replied that he would say, “O Allah, I seek refuge in You from the evil of what I have done, and from the evil of what I have not done.” The wording is simple and very wide. It covers actions already done and matters not yet done. The Hadith teaches a believer to ask Allah for protection from the harm tied to personal actions and possible future actions. It is a dua about accountability, caution, and neediness before Allah."},"teachings":["Aishah was asked about the supplication of the Prophet (صلى الله عليه وسلم).","The Prophet (صلى الله عليه وسلم) sought refuge from the evil of what had already been done.","He also sought refuge from the evil of what had not yet been done.","A believer should ask Allah for safety regarding both past and future actions."],"related_hadiths":[{"id":"2716a","book_id":"2","label":"Sahih Muslim"},{"id":"3839","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5526","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua from Evil of Past and Future Deeds","description":"$book_name$ $hadith_number$ - $chapter_name$. A concise dua seeking refuge from the evil of what one has done and what one has not done."},"heading":{"title":"Dua for Protection from the Evil of What I Have Done and Not Done","description":"This Hadith records a question asked to Aishah, the Mother of the Believers, about the supplication of the Messenger of Allah (صلى الله عليه وسلم). She replied that he would say, “O Allah, I seek refuge in You from the evil of what I have done, and from the evil of what I have not done.” The wording is simple and very wide. It covers actions already done and matters not yet done. The Hadith teaches a believer to ask Allah for protection from the harm tied to personal actions and possible future actions. It is a dua about accountability, caution, and neediness before Allah."},"teachings":["Aishah was asked about the supplication of the Prophet (صلى الله عليه وسلم).","The Prophet (صلى الله عليه وسلم) sought refuge from the evil of what had already been done.","He also sought refuge from the evil of what had not yet been done.","A believer should ask Allah for safety regarding both past and future actions."],"related_hadiths":[{"id":"2716a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"3839","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"5526","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E359" s="4" t="n"/>
@@ -8758,7 +8762,7 @@
       </c>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua to Guard Hearing, Sight, Tongue, Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. A taught dua seeking refuge from the evil of hearing, sight, tongue, heart, and sexual passion."},"heading":{"title":"Dua for Guarding the Hearing, Sight, Tongue, Heart, and Desires","description":"This Hadith begins with a request: Shakl ibn Humayd asked the Messenger of Allah (صلى الله عليه وسلم) to teach him a supplication. The Prophet (صلى الله عليه وسلم) taught him to seek refuge in Allah from the evil of what he hears, sees, speaks, thinks, and from the evil of his semen, explained in the translation as sexual passion. The dua is very personal. It names the senses, speech, heart or thought, and desire. It teaches that a believer needs Allah’s help to use these gifts safely. The Hadith does not list examples of sins, so the explanation should remain close to the text: ask Allah to protect every inner and outer part of the self from evil."},"teachings":["A companion asked the Prophet (صلى الله عليه وسلم) to teach him a supplication.","The dua asks protection from the evil connected to hearing and seeing.","It also asks protection from harmful speech and inner thoughts.","The wording includes protection from sexual passion."],"related_hadiths":[{"id":"3492","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"5455","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua to Guard Hearing, Sight, Tongue, Heart","description":"$book_name$ $hadith_number$ - $chapter_name$. A taught dua seeking refuge from the evil of hearing, sight, tongue, heart, and sexual passion."},"heading":{"title":"Dua for Guarding the Hearing, Sight, Tongue, Heart, and Desires","description":"This Hadith begins with a request: Shakl ibn Humayd asked the Messenger of Allah (صلى الله عليه وسلم) to teach him a supplication. The Prophet (صلى الله عليه وسلم) taught him to seek refuge in Allah from the evil of what he hears, sees, speaks, thinks, and from the evil of his semen, explained in the translation as sexual passion. The dua is very personal. It names the senses, speech, heart or thought, and desire. It teaches that a believer needs Allah’s help to use these gifts safely. The Hadith does not list examples of sins, so the explanation should remain close to the text: ask Allah to protect every inner and outer part of the self from evil."},"teachings":["A companion asked the Prophet (صلى الله عليه وسلم) to teach him a supplication.","The dua asks protection from the evil connected to hearing and seeing.","It also asks protection from harmful speech and inner thoughts.","The wording includes protection from sexual passion."],"related_hadiths":[{"id":"3492","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"5455","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E360" s="4" t="n"/>
@@ -8781,7 +8785,7 @@
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Safety from Calamity and Bad Death","description":"$book_name$ $hadith_number$ - $chapter_name$. A detailed dua seeking refuge from collapse, falling, drowning, burning, old age, and harmful death moments."},"heading":{"title":"Dua for Safety from Calamities and Harm at Death","description":"This Hadith contains a detailed supplication of the Messenger of Allah (صلى الله عليه وسلم), narrated by AbulYusr. The Prophet (صلى الله عليه وسلم) sought refuge from his house falling on him, falling into an abyss, drowning, burning, and decrepitude. He also sought refuge from the devil harming him at the time of death, from dying in Allah’s path while retreating, and from dying by the sting of a poisonous creature. The text names physical dangers, the weakness of old age, and fears connected to the moment of death. The Hadith teaches believers to ask Allah for safety in worldly dangers and in the final moments of life."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from several physical calamities.","He asked Allah for protection from the devil at the time of death.","The dua includes concern about how a person dies.","A believer may ask Allah for safety from both sudden harm and final trials."],"related_hadiths":[{"id":"5531","book_id":"3","label":"Sunan an-Nasai"},{"id":"1553","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Safety from Calamity and Bad Death","description":"$book_name$ $hadith_number$ - $chapter_name$. A detailed dua seeking refuge from collapse, falling, drowning, burning, old age, and harmful death moments."},"heading":{"title":"Dua for Safety from Calamities and Harm at Death","description":"This Hadith contains a detailed supplication of the Messenger of Allah (صلى الله عليه وسلم), narrated by AbulYusr. The Prophet (صلى الله عليه وسلم) sought refuge from his house falling on him, falling into an abyss, drowning, burning, and decrepitude. He also sought refuge from the devil harming him at the time of death, from dying in Allah’s path while retreating, and from dying by the sting of a poisonous creature. The text names physical dangers, the weakness of old age, and fears connected to the moment of death. The Hadith teaches believers to ask Allah for safety in worldly dangers and in the final moments of life."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from several physical calamities.","He asked Allah for protection from the devil at the time of death.","The dua includes concern about how a person dies.","A believer may ask Allah for safety from both sudden harm and final trials."],"related_hadiths":[{"id":"5531","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"1553","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E361" s="4" t="n"/>
@@ -8804,7 +8808,7 @@
       </c>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Added Refuge from Sorrow","description":"$book_name$ $hadith_number$ - $chapter_name$. A related report of Abu al-Yusr’s supplication that adds seeking refuge from sorrow."},"heading":{"title":"Seeking Refuge from Sorrow in the Prophetic Supplication","description":"This Hadith is a brief report connected to the previous tradition of Abu al-Yusr. It says that the same tradition was transmitted through a different chain of narrators, and this version adds the words “and from sorrow.” Because the text is short, the explanation should not add extra details beyond what is given. The main point is that another narration of the supplication includes seeking Allah’s refuge from sorrow. In the wider wording of the previous report, many dangers were named, and this version adds an emotional hardship. The Hadith reminds us that sorrow is also something a believer can bring to Allah in supplication."},"teachings":["This report is linked to the previous narration of Abu al-Yusr.","A different chain includes an added phrase.","The added wording seeks refuge from sorrow.","Emotional distress can be included in a believer’s supplication to Allah."],"related_hadiths":[{"id":"1552","book_id":"4","label":"Sunan Abu Dawud"},{"id":"5531","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Added Refuge from Sorrow","description":"$book_name$ $hadith_number$ - $chapter_name$. A related report of Abu al-Yusr’s supplication that adds seeking refuge from sorrow."},"heading":{"title":"Seeking Refuge from Sorrow in the Prophetic Supplication","description":"This Hadith is a brief report connected to the previous tradition of Abu al-Yusr. It says that the same tradition was transmitted through a different chain of narrators, and this version adds the words “and from sorrow.” Because the text is short, the explanation should not add extra details beyond what is given. The main point is that another narration of the supplication includes seeking Allah’s refuge from sorrow. In the wider wording of the previous report, many dangers were named, and this version adds an emotional hardship. The Hadith reminds us that sorrow is also something a believer can bring to Allah in supplication."},"teachings":["This report is linked to the previous narration of Abu al-Yusr.","A different chain includes an added phrase.","The added wording seeks refuge from sorrow.","Emotional distress can be included in a believer’s supplication to Allah."],"related_hadiths":[{"id":"1552","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"5531","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E362" s="4" t="n"/>
@@ -8827,7 +8831,7 @@
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Protection from Harmful Diseases","description":"$book_name$ $hadith_number$ - $chapter_name$. A Prophetic dua seeking Allah’s refuge from leprosy, madness, elephantiasis, and evil diseases."},"heading":{"title":"Dua for Protection from Leprosy, Madness, Elephantiasis, and Evil Diseases","description":"This Hadith, narrated by Anas ibn Malik, records a dua in which the Prophet (صلى الله عليه وسلم) sought refuge in Allah from leprosy, madness, elephantiasis, and evil diseases. The Hadith is clear and does not need added stories or medical detail to explain its core message. The Prophet (صلى الله عليه وسلم) named certain serious diseases and then used a wider phrase: evil diseases. This teaches a believer to ask Allah for protection from harmful illness and distressing conditions. The dua also shows that health is a blessing and that seeking Allah’s refuge from disease is part of Prophetic supplication. It is often searched as a dua for protection from illness."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from named diseases.","The dua also includes a general request for protection from evil diseases.","A believer may ask Allah for health and safety from illness.","The wording teaches reliance on Allah in matters of bodily well-being."],"related_hadiths":[{"id":"5452","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua for Protection from Harmful Diseases","description":"$book_name$ $hadith_number$ - $chapter_name$. A Prophetic dua seeking Allah’s refuge from leprosy, madness, elephantiasis, and evil diseases."},"heading":{"title":"Dua for Protection from Leprosy, Madness, Elephantiasis, and Evil Diseases","description":"This Hadith, narrated by Anas ibn Malik, records a dua in which the Prophet (صلى الله عليه وسلم) sought refuge in Allah from leprosy, madness, elephantiasis, and evil diseases. The Hadith is clear and does not need added stories or medical detail to explain its core message. The Prophet (صلى الله عليه وسلم) named certain serious diseases and then used a wider phrase: evil diseases. This teaches a believer to ask Allah for protection from harmful illness and distressing conditions. The dua also shows that health is a blessing and that seeking Allah’s refuge from disease is part of Prophetic supplication. It is often searched as a dua for protection from illness."},"teachings":["The Prophet (صلى الله عليه وسلم) sought refuge from named diseases.","The dua also includes a general request for protection from evil diseases.","A believer may ask Allah for health and safety from illness.","The wording teaches reliance on Allah in matters of bodily well-being."],"related_hadiths":[{"id":"5452","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
@@ -8854,7 +8858,7 @@
       </c>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Morning and Evening Dua for Debt and Worry","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Abu Umamah a morning and evening dua for care, grief, weakness, debt, and pressure."},"heading":{"title":"Morning and Evening Dua for Debt, Worry, and Grief","description":"This Hadith gives a full setting for a well-known dua for debt and worry. Abu Sa'id al-Khudri narrated that the Messenger of Allah (صلى الله عليه وسلم) entered the mosque and saw Abu Umamah sitting there outside the time of prayer. Abu Umamah said that cares and debts had held him down. The Prophet (صلى الله عليه وسلم) taught him words to say in the morning and evening: seeking refuge from care and grief, incapacity and slackness, cowardice and miserliness, and from being overcome by debt and subdued by men. The report ends with Abu Umamah saying that when he did it, Allah removed his care and settled his debt. The wording teaches regular dua in times of pressure."},"teachings":["The Prophet (صلى الله عليه وسلم) noticed Abu Umamah’s distress and asked about it.","The dua was taught for morning and evening use.","It asks refuge from emotional, personal, and financial hardship.","Abu Umamah reported relief after practicing what he was taught."],"related_hadiths":[{"id":"6369","book_id":"1","label":"Sahih Bukhari"},{"id":"5476","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Morning and Evening Dua for Debt and Worry","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Abu Umamah a morning and evening dua for care, grief, weakness, debt, and pressure."},"heading":{"title":"Morning and Evening Dua for Debt, Worry, and Grief","description":"This Hadith gives a full setting for a well-known dua for debt and worry. Abu Sa'id al-Khudri narrated that the Messenger of Allah (صلى الله عليه وسلم) entered the mosque and saw Abu Umamah sitting there outside the time of prayer. Abu Umamah said that cares and debts had held him down. The Prophet (صلى الله عليه وسلم) taught him words to say in the morning and evening: seeking refuge from care and grief, incapacity and slackness, cowardice and miserliness, and from being overcome by debt and subdued by men. The report ends with Abu Umamah saying that when he did it, Allah removed his care and settled his debt. The wording teaches regular dua in times of pressure."},"teachings":["The Prophet (صلى الله عليه وسلم) noticed Abu Umamah’s distress and asked about it.","The dua was taught for morning and evening use.","It asks refuge from emotional, personal, and financial hardship.","Abu Umamah reported relief after practicing what he was taught."],"related_hadiths":[{"id":"6369","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5476","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E364" s="4" t="n"/>
@@ -8877,7 +8881,7 @@
       </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr on Prayer and Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. A report on Abu Bakr’s stand that prayer and zakat must not be separated after the Prophet’s death."},"heading":{"title":"Zakat Obligation: Abu Bakr’s Stand on Prayer and Zakat","description":"This Hadith is about zakat obligation and the early Muslim community after the death of the Messenger of Allah (صلى الله عليه وسلم). Abu Hurairah reported that when Abu Bakr became the successor, some Arab clans apostatized. Umar questioned how Abu Bakr could fight people when the Prophet (صلى الله عليه وسلم) had said that whoever says “There is no God but Allah” protects his life and property except for what is due. Abu Bakr replied that he would fight those who separated prayer and zakat, because zakat is what is due from property. Umar then recognized that Abu Bakr’s view was right. The Hadith centers on the duty of zakat and its connection to prayer."},"teachings":["The report shows a discussion between Umar and Abu Bakr after the Prophet’s death.","Abu Bakr refused to separate prayer from zakat.","The Hadith states that zakat is due from property.","Umar later recognized Abu Bakr’s position as right."],"related_hadiths":[{"id":"1399","book_id":"1","label":"Sahih Bukhari"},{"id":"1400","book_id":"1","label":"Sahih Bukhari"},{"id":"20","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Bakr on Prayer and Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. A report on Abu Bakr’s stand that prayer and zakat must not be separated after the Prophet’s death."},"heading":{"title":"Zakat Obligation: Abu Bakr’s Stand on Prayer and Zakat","description":"This Hadith is about zakat obligation and the early Muslim community after the death of the Messenger of Allah (صلى الله عليه وسلم). Abu Hurairah reported that when Abu Bakr became the successor, some Arab clans apostatized. Umar questioned how Abu Bakr could fight people when the Prophet (صلى الله عليه وسلم) had said that whoever says “There is no God but Allah” protects his life and property except for what is due. Abu Bakr replied that he would fight those who separated prayer and zakat, because zakat is what is due from property. Umar then recognized that Abu Bakr’s view was right. The Hadith centers on the duty of zakat and its connection to prayer."},"teachings":["The report shows a discussion between Umar and Abu Bakr after the Prophet’s death.","Abu Bakr refused to separate prayer from zakat.","The Hadith states that zakat is due from property.","Umar later recognized Abu Bakr’s position as right."],"related_hadiths":[{"id":"1399","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1400","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"20","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E365" s="4" t="n"/>
@@ -8900,7 +8904,7 @@
       </c>
       <c r="D366" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat as the Right Due from Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. A brief supporting report that Abu Bakr called zakat the due right of wealth."},"heading":{"title":"Zakat Is the Due Right of Wealth","description":"This Hadith is a shorter version of the previous report about Abu Bakr and zakat. It says that the tradition was also transmitted by Al-Zuhri through a different chain. In this version, Abu Bakr said that its due is the payment of zakat, and he used the wording “a rope of a camel.” Since the text is brief, the main teaching should stay brief too: zakat is treated as a due right connected to wealth, not as an optional gift. The report supports the wording in the longer narration and keeps the focus on Abu Bakr’s statement about paying zakat. It is useful for searches about zakat obligation and the right of wealth."},"teachings":["This report supports the previous narration through another chain.","Abu Bakr described zakat as the due right connected to wealth.","The wording includes the mention of a camel rope.","The Hadith keeps the focus on the obligation of paying zakat."],"related_hadiths":[{"id":"1399","book_id":"1","label":"Sahih Bukhari"},{"id":"1400","book_id":"1","label":"Sahih Bukhari"},{"id":"20","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat as the Right Due from Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. A brief supporting report that Abu Bakr called zakat the due right of wealth."},"heading":{"title":"Zakat Is the Due Right of Wealth","description":"This Hadith is a shorter version of the previous report about Abu Bakr and zakat. It says that the tradition was also transmitted by Al-Zuhri through a different chain. In this version, Abu Bakr said that its due is the payment of zakat, and he used the wording “a rope of a camel.” Since the text is brief, the main teaching should stay brief too: zakat is treated as a due right connected to wealth, not as an optional gift. The report supports the wording in the longer narration and keeps the focus on Abu Bakr’s statement about paying zakat. It is useful for searches about zakat obligation and the right of wealth."},"teachings":["This report supports the previous narration through another chain.","Abu Bakr described zakat as the due right connected to wealth.","The wording includes the mention of a camel rope.","The Hadith keeps the focus on the obligation of paying zakat."],"related_hadiths":[{"id":"1399","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1400","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"20","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E366" s="4" t="n"/>
@@ -8923,7 +8927,7 @@
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat Nisab for Camels, Silver, and Crops","description":"$book_name$ $hadith_number$ - $chapter_name$. A key zakat nisab Hadith stating no zakat below five camels, five ounces of silver, and five wasq."},"heading":{"title":"Zakat Nisab Hadith: Five Camels, Five Ounces, and Five Wasq","description":"This Hadith gives clear zakat nisab limits for three types of property. Abu Sa'id al-Khudri reported that the Messenger of Allah (صلى الله عليه وسلم) said no sadaqah, meaning zakat in this context, is payable on less than five camels, less than five ounces of silver, and less than five camel loads, or wasq. The wording teaches that zakat has thresholds and is not due below these amounts. The Hadith is often searched by people looking for zakat nisab in hadith, especially for camels, silver, dates, grain, and wasq. The explanation should not add later calculations beyond the text, because the Hadith itself only gives the named measures."},"teachings":["No zakat is payable on less than five camels in this report.","No zakat is payable on less than five ounces of silver.","No zakat is payable on less than five wasq.","The Hadith shows that zakat is tied to set thresholds."],"related_hadiths":[{"id":"1458","book_id":"1","label":"Sahih Bukhari"},{"id":"1484","book_id":"1","label":"Sahih Bukhari"},{"id":"2478","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat Nisab for Camels, Silver, and Crops","description":"$book_name$ $hadith_number$ - $chapter_name$. A key zakat nisab Hadith stating no zakat below five camels, five ounces of silver, and five wasq."},"heading":{"title":"Zakat Nisab Hadith: Five Camels, Five Ounces, and Five Wasq","description":"This Hadith gives clear zakat nisab limits for three types of property. Abu Sa'id al-Khudri reported that the Messenger of Allah (صلى الله عليه وسلم) said no sadaqah, meaning zakat in this context, is payable on less than five camels, less than five ounces of silver, and less than five camel loads, or wasq. The wording teaches that zakat has thresholds and is not due below these amounts. The Hadith is often searched by people looking for zakat nisab in hadith, especially for camels, silver, dates, grain, and wasq. The explanation should not add later calculations beyond the text, because the Hadith itself only gives the named measures."},"teachings":["No zakat is payable on less than five camels in this report.","No zakat is payable on less than five ounces of silver.","No zakat is payable on less than five wasq.","The Hadith shows that zakat is tied to set thresholds."],"related_hadiths":[{"id":"1458","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1484","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2478","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E367" s="4" t="n"/>
@@ -8946,7 +8950,7 @@
       </c>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Five Wasq Zakat Threshold","description":"$book_name$ $hadith_number$ - $chapter_name$. A zakat report stating no zakat is due on grain or dates below five wasq, with one wasq as sixty sa'."},"heading":{"title":"Five Wasq Zakat Threshold for Grain and Dates","description":"This Hadith focuses on the zakat threshold for grain or dates. Abu Sa'id al-Khudri narrated that the Prophet (صلى الله عليه وسلم) said there is no zakat payable on less than five camel-loads. The report then states that one wasq measures sixty sa' in weight. This makes the Hadith useful for people searching for five wasq zakat threshold or wasq meaning in zakat. The wording is narrower than the previous Hadith because it centers on grain or dates and the measure of wasq. The text also includes Abu Dawud’s note that Abu al-Bakhtari did not hear from Abu Sa'id, but the core content presented is about the zakat threshold."},"teachings":["The Hadith states no zakat is payable below five wasq for grain or dates.","It defines one wasq as sixty sa' in this report.","The focus is on measured produce, not every type of wealth.","The report includes a note about the chain from Abu Dawud."],"related_hadiths":[{"id":"1484","book_id":"1","label":"Sahih Bukhari"},{"id":"2478","book_id":"3","label":"Sunan an-Nasai"},{"id":"1558","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Five Wasq Zakat Threshold","description":"$book_name$ $hadith_number$ - $chapter_name$. A zakat report stating no zakat is due on grain or dates below five wasq, with one wasq as sixty sa'."},"heading":{"title":"Five Wasq Zakat Threshold for Grain and Dates","description":"This Hadith focuses on the zakat threshold for grain or dates. Abu Sa'id al-Khudri narrated that the Prophet (صلى الله عليه وسلم) said there is no zakat payable on less than five camel-loads. The report then states that one wasq measures sixty sa' in weight. This makes the Hadith useful for people searching for five wasq zakat threshold or wasq meaning in zakat. The wording is narrower than the previous Hadith because it centers on grain or dates and the measure of wasq. The text also includes Abu Dawud’s note that Abu al-Bakhtari did not hear from Abu Sa'id, but the core content presented is about the zakat threshold."},"teachings":["The Hadith states no zakat is payable below five wasq for grain or dates.","It defines one wasq as sixty sa' in this report.","The focus is on measured produce, not every type of wealth.","The report includes a note about the chain from Abu Dawud."],"related_hadiths":[{"id":"1484","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2478","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"1558","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E368" s="4" t="n"/>
@@ -8969,7 +8973,7 @@
       </c>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | My Lord Commanded Me to Wipe","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows the Prophet answering that wiping over the socks was by the command of his Lord."},"heading":{"title":"Hadith About Wiping Over Socks by Allah’s Command","description":"This hadith about wiping over socks by Allah’s command gives a clear exchange between Al-Mughirah ibn Shu’bah and the Messenger of Allah (صلى الله عليه وسلم). Al-Mughirah saw the Prophet wiping over the socks and asked, “Messenger of Allah, have you forgotten?” The Prophet answered that Al-Mughirah had forgotten, and said, “My Lord has commanded me to do this.” The narration shows that the action was not presented as forgetfulness. It was explained as a commanded act. For readers searching my Lord commanded me to wipe over socks hadith, the key point is this answer. The text should be handled carefully: it does not list the wider rules of wiping, but it strongly links this action to the Prophet’s stated obedience to Allah."},"teachings":["The Prophet (صلى الله عليه وسلم) wiped over the socks in this report.","Al-Mughirah asked if he had forgotten.","The Prophet rejected that idea and gave a clear answer.","The hadith connects the action to the command of Allah."],"related_hadiths":[{"id":"161","book_id":"4","label":"Sunan Abu Dawud"},{"id":"206","book_id":"1","label":"Sahih Bukhari"},{"id":"551","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | My Lord Commanded Me to Wipe","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows the Prophet answering that wiping over the socks was by the command of his Lord."},"heading":{"title":"Hadith About Wiping Over Socks by Allah’s Command","description":"This hadith about wiping over socks by Allah’s command gives a clear exchange between Al-Mughirah ibn Shu’bah and the Messenger of Allah (صلى الله عليه وسلم). Al-Mughirah saw the Prophet wiping over the socks and asked, “Messenger of Allah, have you forgotten?” The Prophet answered that Al-Mughirah had forgotten, and said, “My Lord has commanded me to do this.” The narration shows that the action was not presented as forgetfulness. It was explained as a commanded act. For readers searching my Lord commanded me to wipe over socks hadith, the key point is this answer. The text should be handled carefully: it does not list the wider rules of wiping, but it strongly links this action to the Prophet’s stated obedience to Allah."},"teachings":["The Prophet (صلى الله عليه وسلم) wiped over the socks in this report.","Al-Mughirah asked if he had forgotten.","The Prophet rejected that idea and gave a clear answer.","The hadith connects the action to the command of Allah."],"related_hadiths":[{"id":"161","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"206","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"551","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E369" s="4" t="n"/>
@@ -8992,7 +8996,7 @@
       </c>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wasq Measurement in Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibrahim explains that one wasq contained sixty stamped sa' according to the measure mentioned."},"heading":{"title":"Wasq Measurement: Sixty Sa' in the Zakat Discussion","description":"This report is not a direct Prophetic statement in the translation. It records that Ibrahim said the wasq contained sixty sa's stamped with the stamp of Al-Hajjaj. The core topic is measurement, especially the meaning of wasq in the zakat discussion. It is connected to the previous Hadith about no zakat being payable below five wasq. The text helps readers understand the measure mentioned in that zakat threshold. Since the report only gives the measure and mentions the stamp of Al-Hajjaj, the explanation should not go beyond that. It is best used for searches about wasq, sa', and zakat measurement terms."},"teachings":["This report explains a measurement term used in zakat discussions.","Ibrahim stated that one wasq contained sixty sa's.","The report mentions the stamp of Al-Hajjaj in relation to the measure.","It supports understanding of the five wasq threshold mentioned nearby."],"related_hadiths":[{"id":"1559","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1484","book_id":"1","label":"Sahih Bukhari"},{"id":"2478","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wasq Measurement in Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibrahim explains that one wasq contained sixty stamped sa' according to the measure mentioned."},"heading":{"title":"Wasq Measurement: Sixty Sa' in the Zakat Discussion","description":"This report is not a direct Prophetic statement in the translation. It records that Ibrahim said the wasq contained sixty sa's stamped with the stamp of Al-Hajjaj. The core topic is measurement, especially the meaning of wasq in the zakat discussion. It is connected to the previous Hadith about no zakat being payable below five wasq. The text helps readers understand the measure mentioned in that zakat threshold. Since the report only gives the measure and mentions the stamp of Al-Hajjaj, the explanation should not go beyond that. It is best used for searches about wasq, sa', and zakat measurement terms."},"teachings":["This report explains a measurement term used in zakat discussions.","Ibrahim stated that one wasq contained sixty sa's.","The report mentions the stamp of Al-Hajjaj in relation to the measure.","It supports understanding of the five wasq threshold mentioned nearby."],"related_hadiths":[{"id":"1559","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1484","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2478","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E370" s="4" t="n"/>
@@ -9015,7 +9019,7 @@
       </c>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Socks: Traveller and Resident Time Limits","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith gives the time limit for wiping over socks: three days for a traveller and one day for a resident."},"heading":{"title":"Hadith About Wiping Over Socks Time Limit","description":"This hadith about wiping over socks time limit gives a direct rule in the wording of the Prophet (صلى الله عليه وسلم). Khuzaymah ibn Thabit narrated that the time limit for wiping over the socks is three days and nights for a traveller, and one day and one night for a resident. Abu Dawud also mentions another version that says if they had requested an extension, he would have extended it. The main teaching is the time difference between travel and residence. For people searching how long can you wipe over socks in wudu, this narration gives the exact periods stated in the text. A safe explanation should not go beyond those words. It should simply show the two categories: traveller and resident, with their stated time limits."},"teachings":["A traveller is given three days and nights for wiping over socks.","A resident is given one day and one night.","The hadith states a clear difference between travel and residence.","The added version mentions a possible extension if it had been requested."],"related_hadiths":[{"id":"276a","book_id":"2","label":"Sahih Muslim"},{"id":"552","book_id":"6","label":"Sunan Ibn Majah"},{"id":"95","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Socks: Traveller and Resident Time Limits","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith gives the time limit for wiping over socks: three days for a traveller and one day for a resident."},"heading":{"title":"Hadith About Wiping Over Socks Time Limit","description":"This hadith about wiping over socks time limit gives a direct rule in the wording of the Prophet (صلى الله عليه وسلم). Khuzaymah ibn Thabit narrated that the time limit for wiping over the socks is three days and nights for a traveller, and one day and one night for a resident. Abu Dawud also mentions another version that says if they had requested an extension, he would have extended it. The main teaching is the time difference between travel and residence. For people searching how long can you wipe over socks in wudu, this narration gives the exact periods stated in the text. A safe explanation should not go beyond those words. It should simply show the two categories: traveller and resident, with their stated time limits."},"teachings":["A traveller is given three days and nights for wiping over socks.","A resident is given one day and one night.","The hadith states a clear difference between travel and residence.","The added version mentions a possible extension if it had been requested."],"related_hadiths":[{"id":"276a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"552","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"95","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E371" s="4" t="n"/>
@@ -9038,7 +9042,7 @@
       </c>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ubayy ibn Umarah Asks About Wiping Period","description":"$book_name$ $hadith_number$ - $chapter_name$. This report records repeated questions about wiping over socks and Abu Dawud’s note on the chain."},"heading":{"title":"Hadith About Ubayy ibn Umarah and Wiping Over Socks","description":"This hadith about Ubayy ibn Umarah and wiping over socks records a question-and-answer exchange. Ubayy asked the Messenger of Allah (صلى الله عليه وسلم) if he could wipe over the socks, and the answer was yes. He then asked about one day, two days, and three days, and the Prophet answered in the affirmative. The version quoted then says, “as long as you wish.” Abu Dawud adds important notes: another version reaches seven days, and he says there is variance in the chain and that the chain is not strong. Because the text itself includes that note, the explanation should be careful. This narration shows the question being asked, but it also shows Abu Dawud’s caution about its strength. It should not be used to ignore clearer time-limit reports without scholarly care."},"teachings":["Ubayy ibn Umarah asked about wiping over socks.","The report mentions one day, two days, and three days.","Abu Dawud records differences in the chain.","The text itself warns that the chain is not strong."],"related_hadiths":[{"id":"557","book_id":"6","label":"Sunan Ibn Majah"},{"id":"276a","book_id":"2","label":"Sahih Muslim"},{"id":"552","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ubayy ibn Umarah Asks About Wiping Period","description":"$book_name$ $hadith_number$ - $chapter_name$. This report records repeated questions about wiping over socks and Abu Dawud’s note on the chain."},"heading":{"title":"Hadith About Ubayy ibn Umarah and Wiping Over Socks","description":"This hadith about Ubayy ibn Umarah and wiping over socks records a question-and-answer exchange. Ubayy asked the Messenger of Allah (صلى الله عليه وسلم) if he could wipe over the socks, and the answer was yes. He then asked about one day, two days, and three days, and the Prophet answered in the affirmative. The version quoted then says, “as long as you wish.” Abu Dawud adds important notes: another version reaches seven days, and he says there is variance in the chain and that the chain is not strong. Because the text itself includes that note, the explanation should be careful. This narration shows the question being asked, but it also shows Abu Dawud’s caution about its strength. It should not be used to ignore clearer time-limit reports without scholarly care."},"teachings":["Ubayy ibn Umarah asked about wiping over socks.","The report mentions one day, two days, and three days.","Abu Dawud records differences in the chain.","The text itself warns that the chain is not strong."],"related_hadiths":[{"id":"557","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"276a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"552","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E372" s="4" t="n"/>
@@ -9061,7 +9065,7 @@
       </c>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fair Zakat on Livestock","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how zakat collectors were told to avoid taking pregnant animals and collect fairly from livestock."},"heading":{"title":"Hadith About Fair Zakat Collection on Livestock","description":"This Hadith teaches fairness in zakat collection, especially when taking zakat from sheep. The man first offered a goat that was full of milk and fat, but the messengers of the Prophet صلى الله عليه وسلم refused it because it was pregnant. They said the Messenger of Allah صلى الله عليه وسلم had prohibited them from accepting such an animal. Instead, they asked for a goat in its second or third year. The clear message is that zakat collectors should not simply choose the best-looking animal or take what may harm the owner. Zakat on livestock should be handled with care, honesty, and balance. This Hadith about zakat collection shows that Islamic giving is not meant to be unfair to the giver."},"teachings":["Zakat collectors should follow the limits they were given.","Pregnant animals were not accepted in this report as zakat.","Fairness matters when collecting zakat from livestock."],"related_hadiths":[{"id":"1582","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1583","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fair Zakat on Livestock","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how zakat collectors were told to avoid taking pregnant animals and collect fairly from livestock."},"heading":{"title":"Hadith About Fair Zakat Collection on Livestock","description":"This Hadith teaches fairness in zakat collection, especially when taking zakat from sheep. The man first offered a goat that was full of milk and fat, but the messengers of the Prophet صلى الله عليه وسلم refused it because it was pregnant. They said the Messenger of Allah صلى الله عليه وسلم had prohibited them from accepting such an animal. Instead, they asked for a goat in its second or third year. The clear message is that zakat collectors should not simply choose the best-looking animal or take what may harm the owner. Zakat on livestock should be handled with care, honesty, and balance. This Hadith about zakat collection shows that Islamic giving is not meant to be unfair to the giver."},"teachings":["Zakat collectors should follow the limits they were given.","Pregnant animals were not accepted in this report as zakat.","Fairness matters when collecting zakat from livestock."],"related_hadiths":[{"id":"1582","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1583","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E373" s="4" t="n"/>
@@ -9084,7 +9088,7 @@
       </c>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Voluntary Better Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows that giving more than the required zakat can be accepted when done willingly."},"heading":{"title":"Hadith About Voluntarily Giving Better Zakat","description":"This Hadith gives a clear picture of zakat duty and voluntary goodness. Ubayy ibn Ka'b was sent as a zakat collector. He found that a she-camel in her second year was due from the man. The man wanted to give a better, young, large, and fat she-camel instead. Ubayy did not take it on his own because he had not been ordered to take that type. He brought the matter to the Prophet صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم said that the required animal was what was due, but if the man gave something better by choice, Allah would reward him for it and it would be accepted. This Hadith about voluntary zakat shows both rule-following and generous giving."},"teachings":["A zakat collector should not take beyond what he is allowed to take.","A person may give better than what is due if it is voluntary.","The Prophet صلى الله عليه وسلم prayed for blessing in the giver’s property."],"related_hadiths":[{"id":"1581","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1582","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1584","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Voluntary Better Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows that giving more than the required zakat can be accepted when done willingly."},"heading":{"title":"Hadith About Voluntarily Giving Better Zakat","description":"This Hadith gives a clear picture of zakat duty and voluntary goodness. Ubayy ibn Ka'b was sent as a zakat collector. He found that a she-camel in her second year was due from the man. The man wanted to give a better, young, large, and fat she-camel instead. Ubayy did not take it on his own because he had not been ordered to take that type. He brought the matter to the Prophet صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم said that the required animal was what was due, but if the man gave something better by choice, Allah would reward him for it and it would be accepted. This Hadith about voluntary zakat shows both rule-following and generous giving."},"teachings":["A zakat collector should not take beyond what he is allowed to take.","A person may give better than what is due if it is voluntary.","The Prophet صلى الله عليه وسلم prayed for blessing in the giver’s property."],"related_hadiths":[{"id":"1581","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1582","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1584","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E374" s="4" t="n"/>
@@ -9107,7 +9111,7 @@
       </c>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat, Prayer, and Justice","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught Mu'adh to call people to faith, prayer, zakat, and justice."},"heading":{"title":"Hadith About Zakat Taken from the Rich and Given to the Poor","description":"This well-known Hadith about zakat shows the order in which Mu'adh was told to teach the people of Yemen. The Prophet صلى الله عليه وسلم first told him to call them to testify that there is no deity but Allah and that Muhammad صلى الله عليه وسلم is the Messenger of Allah. If they accepted that, he should tell them about the five daily prayers. If they obeyed that, he should tell them that Allah prescribed zakat on their property, taken from their rich and returned to their poor. The Prophet صلى الله عليه وسلم also warned him not to take the best of their wealth and to fear the curse of the oppressed. The message is faith, worship, fair zakat, and avoiding injustice."},"teachings":["Calling to Allah begins with belief in Allah and His Messenger صلى الله عليه وسلم.","Zakat is taken from the wealthy and returned to the poor.","Taking the best property unfairly is warned against in this Hadith."],"related_hadiths":[{"id":"1395","book_id":"1","label":"Sahih Bukhari"},{"id":"1582","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1585","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat, Prayer, and Justice","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught Mu'adh to call people to faith, prayer, zakat, and justice."},"heading":{"title":"Hadith About Zakat Taken from the Rich and Given to the Poor","description":"This well-known Hadith about zakat shows the order in which Mu'adh was told to teach the people of Yemen. The Prophet صلى الله عليه وسلم first told him to call them to testify that there is no deity but Allah and that Muhammad صلى الله عليه وسلم is the Messenger of Allah. If they accepted that, he should tell them about the five daily prayers. If they obeyed that, he should tell them that Allah prescribed zakat on their property, taken from their rich and returned to their poor. The Prophet صلى الله عليه وسلم also warned him not to take the best of their wealth and to fear the curse of the oppressed. The message is faith, worship, fair zakat, and avoiding injustice."},"teachings":["Calling to Allah begins with belief in Allah and His Messenger صلى الله عليه وسلم.","Zakat is taken from the wealthy and returned to the poor.","Taking the best property unfairly is warned against in this Hadith."],"related_hadiths":[{"id":"1395","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1582","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1585","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E375" s="4" t="n"/>
@@ -9130,7 +9134,7 @@
       </c>
       <c r="D376" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Honesty During Zakat Disputes","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that unfair collection does not allow people to hide wealth."},"heading":{"title":"Hadith About Not Hiding Wealth from Zakat Collectors","description":"In this Hadith, people asked the Messenger of Allah صلى الله عليه وسلم about a hard situation. They said that sadaqah collectors were taking more than was due. They asked if they could hide part of their property equal to the extra amount being taken. The Prophet صلى الله عليه وسلم answered with one clear word: No. This Hadith about zakat and honesty teaches that the wrong action of another person does not make hiding wealth acceptable in this case. The text does not give a long discussion; it gives a direct answer. The lesson is to keep one’s own duty clean, even when dealing with unfair treatment from zakat collectors."},"teachings":["A person should not hide wealth from zakat collectors in this case.","Another person’s unfairness does not permit dishonesty here.","The Prophet صلى الله عليه وسلم gave a clear answer without allowing retaliation."],"related_hadiths":[{"id":"1585","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1587","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1589","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Honesty During Zakat Disputes","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that unfair collection does not allow people to hide wealth."},"heading":{"title":"Hadith About Not Hiding Wealth from Zakat Collectors","description":"In this Hadith, people asked the Messenger of Allah صلى الله عليه وسلم about a hard situation. They said that sadaqah collectors were taking more than was due. They asked if they could hide part of their property equal to the extra amount being taken. The Prophet صلى الله عليه وسلم answered with one clear word: No. This Hadith about zakat and honesty teaches that the wrong action of another person does not make hiding wealth acceptable in this case. The text does not give a long discussion; it gives a direct answer. The lesson is to keep one’s own duty clean, even when dealing with unfair treatment from zakat collectors."},"teachings":["A person should not hide wealth from zakat collectors in this case.","Another person’s unfairness does not permit dishonesty here.","The Prophet صلى الله عليه وسلم gave a clear answer without allowing retaliation."],"related_hadiths":[{"id":"1585","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1587","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1589","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E376" s="4" t="n"/>
@@ -9153,7 +9157,7 @@
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Unfair Collectors and Zakat Honesty","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration repeats the concern about zakat collectors taking more than what is due."},"heading":{"title":"Hadith About Zakat Collectors Who Go Beyond the Limit","description":"This narration supports the earlier report about people complaining that sadaqah collectors were acting beyond the proper limit. The added wording says that they told the Messenger of Allah صلى الله عليه وسلم, “The collectors of sadaqah collect more than is due from us.” The report is tied to the same meaning as the previous narration. The core topic is zakat honesty under pressure. It reminds the reader that people may face unfair treatment, but the answer in the connected narration did not allow them to hide their property. This Hadith about unfair zakat collectors keeps the focus on staying upright while also showing that over-collection was recognized as a problem."},"teachings":["People raised concerns about zakat collectors taking more than due.","The narration supports the same meaning as the previous report.","The text keeps attention on proper conduct even during unfair treatment."],"related_hadiths":[{"id":"1585","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1586","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1588","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Unfair Collectors and Zakat Honesty","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration repeats the concern about zakat collectors taking more than what is due."},"heading":{"title":"Hadith About Zakat Collectors Who Go Beyond the Limit","description":"This narration supports the earlier report about people complaining that sadaqah collectors were acting beyond the proper limit. The added wording says that they told the Messenger of Allah صلى الله عليه وسلم, “The collectors of sadaqah collect more than is due from us.” The report is tied to the same meaning as the previous narration. The core topic is zakat honesty under pressure. It reminds the reader that people may face unfair treatment, but the answer in the connected narration did not allow them to hide their property. This Hadith about unfair zakat collectors keeps the focus on staying upright while also showing that over-collection was recognized as a problem."},"teachings":["People raised concerns about zakat collectors taking more than due.","The narration supports the same meaning as the previous report.","The text keeps attention on proper conduct even during unfair treatment."],"related_hadiths":[{"id":"1585","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1586","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1588","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E377" s="4" t="n"/>
@@ -9176,7 +9180,7 @@
       </c>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Patience with Zakat Collectors","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches welcoming zakat collectors while their justice or injustice remains on them."},"heading":{"title":"Hadith About Welcoming Zakat Collectors with Patience","description":"This Hadith speaks about riders who would come to collect zakat, even though people might dislike their arrival. The Prophet صلى الله عليه وسلم told the people to welcome them and give them room to do what they came for. If the collectors acted justly, that would be for their own good. If they acted unjustly, the burden would be on them. The Hadith also says to please them, because the completion of the people’s zakat was linked here with the collectors’ satisfaction, and they should ask blessings for the people. This Hadith about zakat collectors teaches calm conduct, patience, and leaving the matter of injustice to the one who commits it."},"teachings":["People were told to welcome the zakat collectors when they came.","The justice or injustice of collectors would return to them.","Collectors were to ask blessing for those who paid zakat."],"related_hadiths":[{"id":"1589","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1590","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1585","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Patience with Zakat Collectors","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches welcoming zakat collectors while their justice or injustice remains on them."},"heading":{"title":"Hadith About Welcoming Zakat Collectors with Patience","description":"This Hadith speaks about riders who would come to collect zakat, even though people might dislike their arrival. The Prophet صلى الله عليه وسلم told the people to welcome them and give them room to do what they came for. If the collectors acted justly, that would be for their own good. If they acted unjustly, the burden would be on them. The Hadith also says to please them, because the completion of the people’s zakat was linked here with the collectors’ satisfaction, and they should ask blessings for the people. This Hadith about zakat collectors teaches calm conduct, patience, and leaving the matter of injustice to the one who commits it."},"teachings":["People were told to welcome the zakat collectors when they came.","The justice or injustice of collectors would return to them.","Collectors were to ask blessing for those who paid zakat."],"related_hadiths":[{"id":"1589","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1590","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1585","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E378" s="4" t="n"/>
@@ -9199,7 +9203,7 @@
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Please Your Zakat Collectors","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم told people to keep good conduct with zakat collectors, even when wronged."},"heading":{"title":"Hadith About Pleasing Zakat Collectors Even When Wronged","description":"In this Hadith, some nomadic Arabs came to the Messenger of Allah صلى الله عليه وسلم and complained that zakat collectors were acting unjustly toward them. The Prophet صلى الله عليه وسلم told them to please those who collected sadaqah from them. They asked again, even if the collectors wronged them. He repeated the command to please the collectors. One version adds, “even if you are wronged.” The report ends with Jarir saying that after hearing this from the Messenger of Allah صلى الله عليه وسلم, no zakat collector left him except pleased with him. This Hadith about dealing with zakat collectors teaches restraint, calm behavior, and avoiding a hostile response during collection."},"teachings":["The people complained about unjust behavior from some collectors.","The Prophet صلى الله عليه وسلم still told them to keep the collectors pleased.","Jarir applied this teaching in his own dealings afterward."],"related_hadiths":[{"id":"1588","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1590","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1586","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Please Your Zakat Collectors","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم told people to keep good conduct with zakat collectors, even when wronged."},"heading":{"title":"Hadith About Pleasing Zakat Collectors Even When Wronged","description":"In this Hadith, some nomadic Arabs came to the Messenger of Allah صلى الله عليه وسلم and complained that zakat collectors were acting unjustly toward them. The Prophet صلى الله عليه وسلم told them to please those who collected sadaqah from them. They asked again, even if the collectors wronged them. He repeated the command to please the collectors. One version adds, “even if you are wronged.” The report ends with Jarir saying that after hearing this from the Messenger of Allah صلى الله عليه وسلم, no zakat collector left him except pleased with him. This Hadith about dealing with zakat collectors teaches restraint, calm behavior, and avoiding a hostile response during collection."},"teachings":["The people complained about unjust behavior from some collectors.","The Prophet صلى الله عليه وسلم still told them to keep the collectors pleased.","Jarir applied this teaching in his own dealings afterward."],"related_hadiths":[{"id":"1588","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1590","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1586","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E379" s="4" t="n"/>
@@ -9222,7 +9226,7 @@
       </c>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Over Stockings and Shoes","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports wiping over stockings and shoes, along with Abu Dawud’s notes on transmission."},"heading":{"title":"Hadith About Wiping Over Stockings and Shoes","description":"This hadith about wiping over stockings and shoes reports from Al-Mughirah ibn Shu’bah that the Messenger of Allah (صلى الله عليه وسلم) performed ablution and wiped over the stockings and shoes. The report also includes Abu Dawud’s careful comments. He says Abd al-Rahman ibn Mahdi did not narrate it because the familiar version from Al-Mughirah says the Prophet wiped over the socks. Abu Dawud also mentions a report from Abu Musa about wiping over stockings, but says its chain is not continuous or strong. Then he lists Companions who wiped over stockings. This narration is useful for searches like wiping over jawrabayn hadith, but the explanation must keep Abu Dawud’s notes in view. The text contains both the report and caution about transmission."},"teachings":["The report mentions wiping over stockings and shoes.","Abu Dawud notes that the familiar version mentions socks.","A related Abu Musa report is described as not continuous or strong.","The text also lists Companions who wiped over stockings."],"related_hadiths":[{"id":"559","book_id":"6","label":"Sunan Ibn Majah"},{"id":"99","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"124","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Over Stockings and Shoes","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports wiping over stockings and shoes, along with Abu Dawud’s notes on transmission."},"heading":{"title":"Hadith About Wiping Over Stockings and Shoes","description":"This hadith about wiping over stockings and shoes reports from Al-Mughirah ibn Shu’bah that the Messenger of Allah (صلى الله عليه وسلم) performed ablution and wiped over the stockings and shoes. The report also includes Abu Dawud’s careful comments. He says Abd al-Rahman ibn Mahdi did not narrate it because the familiar version from Al-Mughirah says the Prophet wiped over the socks. Abu Dawud also mentions a report from Abu Musa about wiping over stockings, but says its chain is not continuous or strong. Then he lists Companions who wiped over stockings. This narration is useful for searches like wiping over jawrabayn hadith, but the explanation must keep Abu Dawud’s notes in view. The text contains both the report and caution about transmission."},"teachings":["The report mentions wiping over stockings and shoes.","Abu Dawud notes that the familiar version mentions socks.","A related Abu Musa report is described as not continuous or strong.","The text also lists Companions who wiped over stockings."],"related_hadiths":[{"id":"559","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"99","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"124","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E380" s="4" t="n"/>
@@ -9245,7 +9249,7 @@
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blessing for Zakat Payers","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows the Prophet صلى الله عليه وسلم praying for families who brought their sadaqah."},"heading":{"title":"Hadith About Praying for Those Who Give Zakat","description":"This Hadith shows a beautiful practice of the Prophet صلى الله عليه وسلم when people brought their sadaqah. Abdullah bin Abi Awfa said that when a group brought their sadaqah, the Prophet صلى الله عليه وسلم would say, “O Allah, bless the family of so and so.” When Abu Awfa brought his sadaqah, the Prophet صلى الله عليه وسلم prayed, “O Allah, bless the family of Abu Awfa.” The main topic is blessing for zakat payers. The text does not speak about rates or types of property. It focuses on a simple act: making dua for those who fulfilled their sadaqah. This Hadith about zakat reminds us that giving was met with kindness, prayer, and good words."},"teachings":["The Prophet صلى الله عليه وسلم prayed for people who brought their sadaqah.","Good words may be given to those who fulfill zakat.","The family of Abu Awfa received a specific prayer in this narration."],"related_hadiths":[{"id":"1588","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1589","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1583","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blessing for Zakat Payers","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith shows the Prophet صلى الله عليه وسلم praying for families who brought their sadaqah."},"heading":{"title":"Hadith About Praying for Those Who Give Zakat","description":"This Hadith shows a beautiful practice of the Prophet صلى الله عليه وسلم when people brought their sadaqah. Abdullah bin Abi Awfa said that when a group brought their sadaqah, the Prophet صلى الله عليه وسلم would say, “O Allah, bless the family of so and so.” When Abu Awfa brought his sadaqah, the Prophet صلى الله عليه وسلم prayed, “O Allah, bless the family of Abu Awfa.” The main topic is blessing for zakat payers. The text does not speak about rates or types of property. It focuses on a simple act: making dua for those who fulfilled their sadaqah. This Hadith about zakat reminds us that giving was met with kindness, prayer, and good words."},"teachings":["The Prophet صلى الله عليه وسلم prayed for people who brought their sadaqah.","Good words may be given to those who fulfill zakat.","The family of Abu Awfa received a specific prayer in this narration."],"related_hadiths":[{"id":"1588","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1589","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1583","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E381" s="4" t="n"/>
@@ -9268,7 +9272,7 @@
       </c>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat Collected at Dwellings","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that zakat should be received from people at their own places."},"heading":{"title":"Hadith About Collecting Zakat at People’s Dwellings","description":"This Hadith gives a rule about where sadaqah or zakat should be collected. The Prophet صلى الله عليه وسلم said there should be no collecting from a distance, and property owners should not move their property far away. Their sadaqah should be received in their dwellings. The core topic is fair zakat collection. The Hadith keeps both sides balanced. Collectors should not make people bring their animals from far away, and owners should not move their animals away from the collector. This Hadith about zakat collection in dwellings shows that Islamic instructions care about fairness, ease, and proper process in collecting what is due."},"teachings":["Zakat should be received at the people’s own dwellings.","Collectors should not demand collection from a far place.","Owners should not move property away to avoid proper collection."],"related_hadiths":[{"id":"1592","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1588","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1585","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat Collected at Dwellings","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches that zakat should be received from people at their own places."},"heading":{"title":"Hadith About Collecting Zakat at People’s Dwellings","description":"This Hadith gives a rule about where sadaqah or zakat should be collected. The Prophet صلى الله عليه وسلم said there should be no collecting from a distance, and property owners should not move their property far away. Their sadaqah should be received in their dwellings. The core topic is fair zakat collection. The Hadith keeps both sides balanced. Collectors should not make people bring their animals from far away, and owners should not move their animals away from the collector. This Hadith about zakat collection in dwellings shows that Islamic instructions care about fairness, ease, and proper process in collecting what is due."},"teachings":["Zakat should be received at the people’s own dwellings.","Collectors should not demand collection from a far place.","Owners should not move property away to avoid proper collection."],"related_hadiths":[{"id":"1592","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1588","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1585","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E382" s="4" t="n"/>
@@ -9291,7 +9295,7 @@
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Take Back Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches not to buy back or take back something already given as charity."},"heading":{"title":"Hadith About Not Taking Back Your Sadaqah","description":"This Hadith teaches a clear lesson about sadaqah after it has been given. Umar ibn al-Khattab gave a horse as alms in the way of Allah. Later, he found that same horse being sold and wanted to buy it. He asked the Messenger of Allah صلى الله عليه وسلم about it. The Prophet صلى الله عليه وسلم told him not to buy it and not to return to his sadaqah. The core topic is taking back charity. The Hadith does not discuss every possible case of ownership. It speaks directly about this act: giving something in charity and then trying to buy it back. This Hadith about sadaqah encourages the giver to let the charity remain given."},"teachings":["A person should not buy back what he has given as charity.","The Prophet صلى الله عليه وسلم described buying it back as returning to sadaqah.","Charity should be treated as something given for Allah’s sake."],"related_hadiths":[{"id":"1490","book_id":"1","label":"Sahih Bukhari"},{"id":"1594","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1595","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Take Back Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith teaches not to buy back or take back something already given as charity."},"heading":{"title":"Hadith About Not Taking Back Your Sadaqah","description":"This Hadith teaches a clear lesson about sadaqah after it has been given. Umar ibn al-Khattab gave a horse as alms in the way of Allah. Later, he found that same horse being sold and wanted to buy it. He asked the Messenger of Allah صلى الله عليه وسلم about it. The Prophet صلى الله عليه وسلم told him not to buy it and not to return to his sadaqah. The core topic is taking back charity. The Hadith does not discuss every possible case of ownership. It speaks directly about this act: giving something in charity and then trying to buy it back. This Hadith about sadaqah encourages the giver to let the charity remain given."},"teachings":["A person should not buy back what he has given as charity.","The Prophet صلى الله عليه وسلم described buying it back as returning to sadaqah.","Charity should be treated as something given for Allah’s sake."],"related_hadiths":[{"id":"1490","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1594","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1595","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E383" s="4" t="n"/>
@@ -9314,7 +9318,7 @@
       </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Horse and Slave","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith states that no sadaqah is due on a horse or slave except fitr for the slave."},"heading":{"title":"Hadith About No Zakat on Horse or Slave Except Zakat al-Fitr","description":"This Hadith states a specific point about sadaqah due on certain possessions. Abu Hurairah narrated that the Prophet صلى الله عليه وسلم said no sadaqah is due on a horse or a slave, except that which is given at the breaking of the fast at the end of Ramadan. The core topic is zakat exemption. The Hadith is short and focused. It does not speak about all types of wealth. It only mentions the horse and the slave, and then makes an exception for zakat al-fitr in relation to the slave. This Hadith about zakat on horses and slaves is useful for people searching for clear wording on this specific issue."},"teachings":["No sadaqah is due on a horse in this narration.","No sadaqah is due on a slave except the stated fitr exception.","The Hadith gives a specific rule without a long explanation."],"related_hadiths":[{"id":"1595","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1593","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1596","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat on Horse and Slave","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith states that no sadaqah is due on a horse or slave except fitr for the slave."},"heading":{"title":"Hadith About No Zakat on Horse or Slave Except Zakat al-Fitr","description":"This Hadith states a specific point about sadaqah due on certain possessions. Abu Hurairah narrated that the Prophet صلى الله عليه وسلم said no sadaqah is due on a horse or a slave, except that which is given at the breaking of the fast at the end of Ramadan. The core topic is zakat exemption. The Hadith is short and focused. It does not speak about all types of wealth. It only mentions the horse and the slave, and then makes an exception for zakat al-fitr in relation to the slave. This Hadith about zakat on horses and slaves is useful for people searching for clear wording on this specific issue."},"teachings":["No sadaqah is due on a horse in this narration.","No sadaqah is due on a slave except the stated fitr exception.","The Hadith gives a specific rule without a long explanation."],"related_hadiths":[{"id":"1595","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1593","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1596","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E384" s="4" t="n"/>
@@ -9337,7 +9341,7 @@
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat from Each Wealth Type","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith tells Mu'adh to collect each zakat type from the same type of property."},"heading":{"title":"Hadith About Taking Zakat from the Same Type of Wealth","description":"This Hadith reports the instruction given to Mu'adh ibn Jabal when the Messenger of Allah صلى الله عليه وسلم sent him to Yemen. He told him to collect corn from corn, sheep from sheep, camels from camels, and cows from cows. The core topic is zakat collection by wealth type. The wording is simple and practical. It shows that the collected zakat should match the kind of property being assessed in the examples given. The Hadith about zakat types does not list every form of wealth. It mentions these categories clearly: grain, sheep, camels, and cows. Abu Dawud also added his own observation about large produce, but the prophetic instruction remains focused on taking from the same type."},"teachings":["Corn is to be taken from corn in this instruction.","Livestock examples are matched with their own kind.","The Hadith gives practical guidance for zakat collection."],"related_hadiths":[{"id":"1596","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1597","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1600","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat from Each Wealth Type","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith tells Mu'adh to collect each zakat type from the same type of property."},"heading":{"title":"Hadith About Taking Zakat from the Same Type of Wealth","description":"This Hadith reports the instruction given to Mu'adh ibn Jabal when the Messenger of Allah صلى الله عليه وسلم sent him to Yemen. He told him to collect corn from corn, sheep from sheep, camels from camels, and cows from cows. The core topic is zakat collection by wealth type. The wording is simple and practical. It shows that the collected zakat should match the kind of property being assessed in the examples given. The Hadith about zakat types does not list every form of wealth. It mentions these categories clearly: grain, sheep, camels, and cows. Abu Dawud also added his own observation about large produce, but the prophetic instruction remains focused on taking from the same type."},"teachings":["Corn is to be taken from corn in this instruction.","Livestock examples are matched with their own kind.","The Hadith gives practical guidance for zakat collection."],"related_hadiths":[{"id":"1596","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1597","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1600","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E385" s="4" t="n"/>
@@ -9360,7 +9364,7 @@
       </c>
       <c r="D386" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Over Shoes and Feet","description":"$book_name$ $hadith_number$ - $chapter_name$. This report records the Prophet performing wudu and wiping over his shoes and feet."},"heading":{"title":"Hadith About Wiping Over Shoes and Feet in Wudu","description":"This hadith about wiping over shoes and feet in wudu reports from Aws ibn Abu Aws ath-Thaqafi that the Messenger of Allah (صلى الله عليه وسلم) performed ablution and wiped over his shoes and feet. The narration also preserves a small wording detail from Abbad, who said the Prophet came to the well of a people. The text notes that Musaddad did not mention the words for the ablution place and well, but both narrators agreed on the key wording: he performed wudu and wiped over his shoes and feet. The core message is the action reported during ablution. A careful explanation should not turn this short narration into a broad ruling by itself. It simply records what was seen and how the wording was transmitted."},"teachings":["The Prophet (صلى الله عليه وسلم) performed wudu in this report.","He wiped over his shoes and feet according to the wording given.","The narration preserves a difference about the place description.","Both narrators agree on the key wiping wording."],"related_hadiths":[{"id":"559","book_id":"6","label":"Sunan Ibn Majah"},{"id":"161","book_id":"4","label":"Sunan Abu Dawud"},{"id":"203","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Over Shoes and Feet","description":"$book_name$ $hadith_number$ - $chapter_name$. This report records the Prophet performing wudu and wiping over his shoes and feet."},"heading":{"title":"Hadith About Wiping Over Shoes and Feet in Wudu","description":"This hadith about wiping over shoes and feet in wudu reports from Aws ibn Abu Aws ath-Thaqafi that the Messenger of Allah (صلى الله عليه وسلم) performed ablution and wiped over his shoes and feet. The narration also preserves a small wording detail from Abbad, who said the Prophet came to the well of a people. The text notes that Musaddad did not mention the words for the ablution place and well, but both narrators agreed on the key wording: he performed wudu and wiped over his shoes and feet. The core message is the action reported during ablution. A careful explanation should not turn this short narration into a broad ruling by itself. It simply records what was seen and how the wording was transmitted."},"teachings":["The Prophet (صلى الله عليه وسلم) performed wudu in this report.","He wiped over his shoes and feet according to the wording given.","The narration preserves a difference about the place description.","Both narrators agree on the key wiping wording."],"related_hadiths":[{"id":"559","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"161","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"203","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E386" s="4" t="n"/>
@@ -9383,7 +9387,7 @@
       </c>
       <c r="D387" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Honey Tithe and Protected Land","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions a tithe on honey and the protected valley of Salabah."},"heading":{"title":"Hadith About Honey Tithe and the Valley of Salabah","description":"This Hadith tells the story of Hilal from Banu Mat'an, who brought a tenth of honey from his beehives to the Messenger of Allah صلى الله عليه وسلم. He also asked for a wood or valley called Salabah to be protected for him, and the Messenger of Allah صلى الله عليه وسلم granted it. Later, during the time of Umar ibn al-Khattab, Sufyan ibn Wahb asked about that protected land. Umar wrote that if Hilal continued paying the tithe on honey as he used to pay to the Messenger of Allah صلى الله عليه وسلم, then Salabah should remain protected for him. If not, the bees would be like those of any open wood. The core topic is honey tithe and protected land."},"teachings":["Hilal brought a tenth of honey from his beehives.","The protected land was tied to continuing the payment mentioned in the report.","Umar referred back to what had been paid during the Prophet’s time."],"related_hadiths":[{"id":"1599","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1596","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1597","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Honey Tithe and Protected Land","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions a tithe on honey and the protected valley of Salabah."},"heading":{"title":"Hadith About Honey Tithe and the Valley of Salabah","description":"This Hadith tells the story of Hilal from Banu Mat'an, who brought a tenth of honey from his beehives to the Messenger of Allah صلى الله عليه وسلم. He also asked for a wood or valley called Salabah to be protected for him, and the Messenger of Allah صلى الله عليه وسلم granted it. Later, during the time of Umar ibn al-Khattab, Sufyan ibn Wahb asked about that protected land. Umar wrote that if Hilal continued paying the tithe on honey as he used to pay to the Messenger of Allah صلى الله عليه وسلم, then Salabah should remain protected for him. If not, the bees would be like those of any open wood. The core topic is honey tithe and protected land."},"teachings":["Hilal brought a tenth of honey from his beehives.","The protected land was tied to continuing the payment mentioned in the report.","Umar referred back to what had been paid during the Prophet’s time."],"related_hadiths":[{"id":"1599","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1596","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1597","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E387" s="4" t="n"/>
@@ -9406,7 +9410,7 @@
       </c>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Over Socks in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم wiped over socks in wudu, with a report mentioning the upper part of the socks."},"heading":{"title":"Wiping Over Socks in Wudu: A Simple Sunnah Report","description":"This Hadith is about wiping over socks in wudu, often searched as wiping over khuffain or masah over socks. Al-Mughirah ibn Shu'bah narrates that the Messenger of Allah صلى الله عليه وسلم wiped over the socks. Another version adds a clear detail: the wiping was on the back, or upper part, of the socks. The wording is short, but it gives a direct picture of an action done by the Prophet صلى الله عليه وسلم during purification. The main lesson here is to follow the reported Sunnah as it is stated. The text does not give extra conditions, timings, or a full method, so the explanation should stay close to what is mentioned: wiping over the socks, with the added version pointing to the upper part."},"teachings":["The Prophet صلى الله عليه وسلم is reported to have wiped over socks during wudu.","One version mentions the upper part of the socks.","The Hadith teaches careful attention to the exact wording of worship reports."],"related_hadiths":[{"id":"203","book_id":"1","label":"Sahih Bukhari"},{"id":"274c","book_id":"2","label":"Sahih Muslim"},{"id":"276a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Over Socks in Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم wiped over socks in wudu, with a report mentioning the upper part of the socks."},"heading":{"title":"Wiping Over Socks in Wudu: A Simple Sunnah Report","description":"This Hadith is about wiping over socks in wudu, often searched as wiping over khuffain or masah over socks. Al-Mughirah ibn Shu'bah narrates that the Messenger of Allah صلى الله عليه وسلم wiped over the socks. Another version adds a clear detail: the wiping was on the back, or upper part, of the socks. The wording is short, but it gives a direct picture of an action done by the Prophet صلى الله عليه وسلم during purification. The main lesson here is to follow the reported Sunnah as it is stated. The text does not give extra conditions, timings, or a full method, so the explanation should stay close to what is mentioned: wiping over the socks, with the added version pointing to the upper part."},"teachings":["The Prophet صلى الله عليه وسلم is reported to have wiped over socks during wudu.","One version mentions the upper part of the socks.","The Hadith teaches careful attention to the exact wording of worship reports."],"related_hadiths":[{"id":"203","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"274c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"276a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E388" s="4" t="n"/>
@@ -9429,7 +9433,7 @@
       </c>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sunnah Over Personal Opinion","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali explains that the Prophet صلى الله عليه وسلم wiped the upper part of his shoes, showing worship follows reported practice, not opinion."},"heading":{"title":"Wiping Over Khuffain: Following the Sunnah Over Opinion","description":"This Hadith centers on wiping over khuffain in wudu and the place of Sunnah over personal opinion. Ali ibn Abu Talib says that if religion were based only on opinion, wiping the under part of the shoe would seem more fitting than wiping the upper part. But he then says he saw the Messenger of Allah صلى الله عليه وسلم wiping over the upper part of his shoes. The meaning is simple and strong: in acts of worship, the Prophet's صلى الله عليه وسلم action is followed even when human reasoning might expect something else. This Hadith is often searched as hadith about religion and opinion, wiping over leather socks, or wiping upper part of khuffain. It keeps the focus on what Ali directly witnessed from the Prophet صلى الله عليه وسلم."},"teachings":["Acts of worship are learned from the Prophet's صلى الله عليه وسلم practice.","Ali compared opinion with what he saw from the Messenger صلى الله عليه وسلم.","The report points to wiping the upper part of the shoes, not the underside."],"related_hadiths":[{"id":"274i","book_id":"2","label":"Sahih Muslim"},{"id":"203","book_id":"1","label":"Sahih Bukhari"},{"id":"276a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sunnah Over Personal Opinion","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali explains that the Prophet صلى الله عليه وسلم wiped the upper part of his shoes, showing worship follows reported practice, not opinion."},"heading":{"title":"Wiping Over Khuffain: Following the Sunnah Over Opinion","description":"This Hadith centers on wiping over khuffain in wudu and the place of Sunnah over personal opinion. Ali ibn Abu Talib says that if religion were based only on opinion, wiping the under part of the shoe would seem more fitting than wiping the upper part. But he then says he saw the Messenger of Allah صلى الله عليه وسلم wiping over the upper part of his shoes. The meaning is simple and strong: in acts of worship, the Prophet's صلى الله عليه وسلم action is followed even when human reasoning might expect something else. This Hadith is often searched as hadith about religion and opinion, wiping over leather socks, or wiping upper part of khuffain. It keeps the focus on what Ali directly witnessed from the Prophet صلى الله عليه وسلم."},"teachings":["Acts of worship are learned from the Prophet's صلى الله عليه وسلم practice.","Ali compared opinion with what he saw from the Messenger صلى الله عليه وسلم.","The report points to wiping the upper part of the shoes, not the underside."],"related_hadiths":[{"id":"274i","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"203","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"276a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E389" s="4" t="n"/>
@@ -9452,7 +9456,7 @@
       </c>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Who Must Pay Zakat al-Fitr","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas taught that sadaqah of the fast is due at Ramadan’s end for free and slave, male and female, young and old."},"heading":{"title":"Zakat al-Fitr Hadith: Who Pays and What Is Given","description":"This zakat al fitr hadith gives clear details about the sadaqah linked to the fast. Ibn Abbas spoke near the end of Ramadan and told the people to bring out the sadaqah of their fast. When some did not understand, he asked the people of Medina to stand and teach them. The narration says the Messenger of Allah صلى الله عليه وسلم prescribed it as one sa' of dried dates or barley, or half a sa' of wheat, for every freeman or slave, male or female, young or old. It also mentions Ali’s advice when prices fell: give one sa' of everything. This makes the hadith a key text for searches like “zakat al fitr amount hadith” and “who must pay sadaqatul fitr.”"},"teachings":["Zakat al-Fitr was taught near the end of Ramadan.","People who know should help teach those who do not know.","The narration includes free and slave, male and female, young and old.","The text mentions measured food amounts, not vague giving."],"related_hadiths":[{"id":"1620","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1621","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Who Must Pay Zakat al-Fitr","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas taught that sadaqah of the fast is due at Ramadan’s end for free and slave, male and female, young and old."},"heading":{"title":"Zakat al-Fitr Hadith: Who Pays and What Is Given","description":"This zakat al fitr hadith gives clear details about the sadaqah linked to the fast. Ibn Abbas spoke near the end of Ramadan and told the people to bring out the sadaqah of their fast. When some did not understand, he asked the people of Medina to stand and teach them. The narration says the Messenger of Allah صلى الله عليه وسلم prescribed it as one sa' of dried dates or barley, or half a sa' of wheat, for every freeman or slave, male or female, young or old. It also mentions Ali’s advice when prices fell: give one sa' of everything. This makes the hadith a key text for searches like “zakat al fitr amount hadith” and “who must pay sadaqatul fitr.”"},"teachings":["Zakat al-Fitr was taught near the end of Ramadan.","People who know should help teach those who do not know.","The narration includes free and slave, male and female, young and old.","The text mentions measured food amounts, not vague giving."],"related_hadiths":[{"id":"1620","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1621","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E390" s="4" t="n"/>
@@ -9475,7 +9479,7 @@
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat, Fair Judgment, and Family Honor","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم explained cases involving withheld zakat, defended Khalid, and took responsibility for al-Abbas."},"heading":{"title":"Zakat Hadith: Fairness When Collecting Sadaqah","description":"This zakat hadith shows a careful response when some people were reported as not giving sadaqah. The Prophet صلى الله عليه وسلم sent Umar to collect it, and the names of Ibn Jamil, Khalid ibn al-Walid, and al-Abbas were mentioned. The Prophet صلى الله عليه وسلم answered each case differently. About Ibn Jamil, he reminded that he had been poor and Allah enriched him. About Khalid, he said people were wronging him, because he had kept his armor and weapons for the path of Allah. About al-Abbas, he said he would be responsible for it and an equal amount with it. For readers searching “hadith about zakat collection” or “Khalid ibn Walid zakat hadith,” this narration teaches that claims about people must be handled with care and fairness."},"teachings":["Reports about unpaid zakat should be judged carefully.","A person’s situation may explain what appears to be refusal.","The Prophet صلى الله عليه وسلم defended Khalid when people misunderstood his case.","Family ties were honored, as shown in the words about the paternal uncle."],"related_hadiths":[{"id":"1624","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1625","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Zakat, Fair Judgment, and Family Honor","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم explained cases involving withheld zakat, defended Khalid, and took responsibility for al-Abbas."},"heading":{"title":"Zakat Hadith: Fairness When Collecting Sadaqah","description":"This zakat hadith shows a careful response when some people were reported as not giving sadaqah. The Prophet صلى الله عليه وسلم sent Umar to collect it, and the names of Ibn Jamil, Khalid ibn al-Walid, and al-Abbas were mentioned. The Prophet صلى الله عليه وسلم answered each case differently. About Ibn Jamil, he reminded that he had been poor and Allah enriched him. About Khalid, he said people were wronging him, because he had kept his armor and weapons for the path of Allah. About al-Abbas, he said he would be responsible for it and an equal amount with it. For readers searching “hadith about zakat collection” or “Khalid ibn Walid zakat hadith,” this narration teaches that claims about people must be handled with care and fairness."},"teachings":["Reports about unpaid zakat should be judged carefully.","A person’s situation may explain what appears to be refusal.","The Prophet صلى الله عليه وسلم defended Khalid when people misunderstood his case.","Family ties were honored, as shown in the words about the paternal uncle."],"related_hadiths":[{"id":"1624","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1625","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E391" s="4" t="n"/>
@@ -9498,7 +9502,7 @@
       </c>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Collecting and Spending Zakat Correctly","description":"$book_name$ $hadith_number$ - $chapter_name$. Imran ibn Husayn said zakat was collected and spent as it had been during the lifetime of the Prophet صلى الله عليه وسلم."},"heading":{"title":"Zakat Distribution Hadith: Collect It and Spend It in the Right Place","description":"This zakat distribution hadith highlights trust in collecting and spending sadaqah. A governor sent Imran ibn Husayn to collect zakat. When Imran returned, he was asked, “Where is the property?” His answer is the heart of the narration. He said they collected it from where they used to collect it in the lifetime of the Messenger of Allah صلى الله عليه وسلم, and they spent it where they used to spend it during his time. The hadith does not give a long list of categories here. It points to a method: take it from the proper place and put it in the proper place. People searching “hadith about zakat distribution” can see that zakat is not personal wealth for collectors or rulers."},"teachings":["Zakat collection is a trust, not a private gain.","Collected sadaqah should be placed where it belongs.","Imran referred back to the practice during the Prophet’s صلى الله عليه وسلم lifetime.","A collector may be questioned, and he should answer with honesty."],"related_hadiths":[{"id":"1623","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1630","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Collecting and Spending Zakat Correctly","description":"$book_name$ $hadith_number$ - $chapter_name$. Imran ibn Husayn said zakat was collected and spent as it had been during the lifetime of the Prophet صلى الله عليه وسلم."},"heading":{"title":"Zakat Distribution Hadith: Collect It and Spend It in the Right Place","description":"This zakat distribution hadith highlights trust in collecting and spending sadaqah. A governor sent Imran ibn Husayn to collect zakat. When Imran returned, he was asked, “Where is the property?” His answer is the heart of the narration. He said they collected it from where they used to collect it in the lifetime of the Messenger of Allah صلى الله عليه وسلم, and they spent it where they used to spend it during his time. The hadith does not give a long list of categories here. It points to a method: take it from the proper place and put it in the proper place. People searching “hadith about zakat distribution” can see that zakat is not personal wealth for collectors or rulers."},"teachings":["Zakat collection is a trust, not a private gain.","Collected sadaqah should be placed where it belongs.","Imran referred back to the practice during the Prophet’s صلى الله عليه وسلم lifetime.","A collector may be questioned, and he should answer with honesty."],"related_hadiths":[{"id":"1623","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1630","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E392" s="4" t="n"/>
@@ -9521,7 +9525,7 @@
       </c>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning Against Begging While Affluent","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم warned against begging while having enough, and named fifty dirhams or its value in gold as affluence."},"heading":{"title":"Begging in Islam Hadith: When a Person Has Enough","description":"This begging in Islam hadith gives a serious warning about asking people when one already has enough. Abdullah ibn Mas'ud narrates that the Prophet صلى الله عليه وسلم said whoever begs while having what suffices him will come on the Day of Resurrection with marks on his face, described as scrapes, scratches, or lacerations. When asked what counts as affluence, the Prophet صلى الله عليه وسلم replied: fifty dirhams or its value in gold. The hadith is direct, so the explanation should stay direct too. It is not attacking the needy. It is warning against asking without need. For search terms like “hadith about begging with enough wealth” and “fifty dirhams hadith,” this narration gives both the warning and the stated measure."},"teachings":["Begging while having enough is strongly warned against.","The narration gives a stated measure: fifty dirhams or its value in gold.","The warning is about needless asking, not real hardship.","A person should check his own means before asking others."],"related_hadiths":[{"id":"1627","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1628","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1629","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning Against Begging While Affluent","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم warned against begging while having enough, and named fifty dirhams or its value in gold as affluence."},"heading":{"title":"Begging in Islam Hadith: When a Person Has Enough","description":"This begging in Islam hadith gives a serious warning about asking people when one already has enough. Abdullah ibn Mas'ud narrates that the Prophet صلى الله عليه وسلم said whoever begs while having what suffices him will come on the Day of Resurrection with marks on his face, described as scrapes, scratches, or lacerations. When asked what counts as affluence, the Prophet صلى الله عليه وسلم replied: fifty dirhams or its value in gold. The hadith is direct, so the explanation should stay direct too. It is not attacking the needy. It is warning against asking without need. For search terms like “hadith about begging with enough wealth” and “fifty dirhams hadith,” this narration gives both the warning and the stated measure."},"teachings":["Begging while having enough is strongly warned against.","The narration gives a stated measure: fifty dirhams or its value in gold.","The warning is about needless asking, not real hardship.","A person should check his own means before asking others."],"related_hadiths":[{"id":"1627","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1628","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1629","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E393" s="4" t="n"/>
@@ -9544,7 +9548,7 @@
       </c>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stopping Yourself from Asking Without Need","description":"$book_name$ $hadith_number$ - $chapter_name$. A man turned back from asking when he realized his she-camel was better than an uqiyah."},"heading":{"title":"Hadith About Begging: Self-Respect When You Have Enough","description":"This hadith about begging tells a very human story. A man from Banu Asad went to ask the Messenger of Allah صلى الله عليه وسلم for food because his family mentioned their need. He reached the Prophet صلى الله عليه وسلم and found another man asking, while the Prophet صلى الله عليه وسلم said he had nothing to give. That man became angry. Then the Prophet صلى الله عليه وسلم explained that whoever asks while having an uqiyah or its equivalent has asked with insistence beyond measure. The man from Banu Asad thought about his own she-camel and realized it was better than an uqiyah, which was forty dirhams. So he went back and did not ask. Later, food came to the Prophet صلى الله عليه وسلم, and the man’s family received a share until Allah made them self-sufficient."},"teachings":["A person should think about what he already owns before asking.","The Prophet صلى الله عليه وسلم did not give what he did not have.","Needless insistence in asking is discouraged in the text.","Provision later came without the man begging at that moment."],"related_hadiths":[{"id":"1626","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1628","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1639","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stopping Yourself from Asking Without Need","description":"$book_name$ $hadith_number$ - $chapter_name$. A man turned back from asking when he realized his she-camel was better than an uqiyah."},"heading":{"title":"Hadith About Begging: Self-Respect When You Have Enough","description":"This hadith about begging tells a very human story. A man from Banu Asad went to ask the Messenger of Allah صلى الله عليه وسلم for food because his family mentioned their need. He reached the Prophet صلى الله عليه وسلم and found another man asking, while the Prophet صلى الله عليه وسلم said he had nothing to give. That man became angry. Then the Prophet صلى الله عليه وسلم explained that whoever asks while having an uqiyah or its equivalent has asked with insistence beyond measure. The man from Banu Asad thought about his own she-camel and realized it was better than an uqiyah, which was forty dirhams. So he went back and did not ask. Later, food came to the Prophet صلى الله عليه وسلم, and the man’s family received a share until Allah made them self-sufficient."},"teachings":["A person should think about what he already owns before asking.","The Prophet صلى الله عليه وسلم did not give what he did not have.","Needless insistence in asking is discouraged in the text.","Provision later came without the man begging at that moment."],"related_hadiths":[{"id":"1626","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1628","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1639","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E394" s="4" t="n"/>
@@ -9567,7 +9571,7 @@
       </c>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | An Uqiyah and Immoderate Begging","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said begging while owning the value of an uqiyah is immoderate, and Abu Sa'id did not ask."},"heading":{"title":"Uqiyah Hadith: Begging When You Already Have Enough","description":"This uqiyah hadith repeats the same clear meaning in a shorter form. Abu Sa'id al-Khudri narrates that the Prophet صلى الله عليه وسلم said whoever begs while having something equal to an uqiyah in value has begged immoderately. Abu Sa'id then looked at his own situation and said his she-camel was better than an uqiyah. In Hisham’s version, it says better than forty dirhams, and he returned without asking anything. The narration also states that an uqiyah in the time of the Messenger of Allah صلى الله عليه وسلم was forty dirhams. This makes the hadith useful for people searching “uqiyah meaning in hadith,” “forty dirhams begging hadith,” and “hadith about not begging when you have enough.”"},"teachings":["An uqiyah is linked here with forty dirhams.","Abu Sa'id applied the Prophet’s صلى الله عليه وسلم words to his own case.","The narration discourages asking while owning enough value.","The hadith connects self-checking with self-restraint."],"related_hadiths":[{"id":"1626","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1627","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1629","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | An Uqiyah and Immoderate Begging","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said begging while owning the value of an uqiyah is immoderate, and Abu Sa'id did not ask."},"heading":{"title":"Uqiyah Hadith: Begging When You Already Have Enough","description":"This uqiyah hadith repeats the same clear meaning in a shorter form. Abu Sa'id al-Khudri narrates that the Prophet صلى الله عليه وسلم said whoever begs while having something equal to an uqiyah in value has begged immoderately. Abu Sa'id then looked at his own situation and said his she-camel was better than an uqiyah. In Hisham’s version, it says better than forty dirhams, and he returned without asking anything. The narration also states that an uqiyah in the time of the Messenger of Allah صلى الله عليه وسلم was forty dirhams. This makes the hadith useful for people searching “uqiyah meaning in hadith,” “forty dirhams begging hadith,” and “hadith about not begging when you have enough.”"},"teachings":["An uqiyah is linked here with forty dirhams.","Abu Sa'id applied the Prophet’s صلى الله عليه وسلم words to his own case.","The narration discourages asking while owning enough value.","The hadith connects self-checking with self-restraint."],"related_hadiths":[{"id":"1626","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1627","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1629","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E395" s="4" t="n"/>
@@ -9590,7 +9594,7 @@
       </c>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Following What the Prophet صلى الله عليه وسلم Did","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows Ali changed his preference after seeing the Prophet صلى الله عليه وسلم wipe the upper part of his socks."},"heading":{"title":"Wudu and Wiping the Upper Part of Socks","description":"This narration gives another wording on the same core topic: wiping over socks in wudu. The speaker says he used to think that the under part of the feet was more deserving of washing until he saw the Messenger of Allah صلى الله عليه وسلم wiping the upper part of his socks. The Hadith is useful because it shows a person leaving his own first thought when a clear Prophetic action is known. The focus is not on debate or extra rulings. It is about seeing the Prophet صلى الله عليه وسلم perform an act and then accepting that practice. For people searching for masah over socks hadith, upper part of khuffain, or wudu Sunnah, this text gives a direct and easy lesson."},"teachings":["A person may change his view when a Prophetic practice becomes clear.","The narration mentions wiping the upper part of the socks.","The text keeps worship tied to what was seen from the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"274i","book_id":"2","label":"Sahih Muslim"},{"id":"274c","book_id":"2","label":"Sahih Muslim"},{"id":"203","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Following What the Prophet صلى الله عليه وسلم Did","description":"$book_name$ $hadith_number$ - $chapter_name$. This report shows Ali changed his preference after seeing the Prophet صلى الله عليه وسلم wipe the upper part of his socks."},"heading":{"title":"Wudu and Wiping the Upper Part of Socks","description":"This narration gives another wording on the same core topic: wiping over socks in wudu. The speaker says he used to think that the under part of the feet was more deserving of washing until he saw the Messenger of Allah صلى الله عليه وسلم wiping the upper part of his socks. The Hadith is useful because it shows a person leaving his own first thought when a clear Prophetic action is known. The focus is not on debate or extra rulings. It is about seeing the Prophet صلى الله عليه وسلم perform an act and then accepting that practice. For people searching for masah over socks hadith, upper part of khuffain, or wudu Sunnah, this text gives a direct and easy lesson."},"teachings":["A person may change his view when a Prophetic practice becomes clear.","The narration mentions wiping the upper part of the socks.","The text keeps worship tied to what was seen from the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"274i","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"274c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"203","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E396" s="4" t="n"/>
@@ -9613,7 +9617,7 @@
       </c>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Deprived Poor Person","description":"$book_name$ $hadith_number$ - $chapter_name$. The narration describes the poor person who avoids begging, lacks enough, and whose need is not known to people."},"heading":{"title":"Miskin Hadith: The One Who Avoids Begging","description":"This miskin hadith builds on the previous report and adds more detail. It describes the poor person as one who abstains from begging. In the added wording, he does not have enough to be free of need, yet he does not ask people, and his need is not known so that sadaqah may be given to him. The report also mentions the word “deprived,” while Abu Dawud notes that this wording is more sound as a statement of al-Zuhri. The message for everyday readers is clear: hidden need can be easy to miss. People searching “hadith about poor who avoid begging” or “miskin muta'affif hadith” will find here a reminder to look beyond loud requests."},"teachings":["Some poor people avoid asking even when they lack enough.","A person’s need may remain unknown to others.","Giving sadaqah requires care for quiet hardship.","The narration records a note about which wording belongs to al-Zuhri."],"related_hadiths":[{"id":"1631","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1633","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1640","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Deprived Poor Person","description":"$book_name$ $hadith_number$ - $chapter_name$. The narration describes the poor person who avoids begging, lacks enough, and whose need is not known to people."},"heading":{"title":"Miskin Hadith: The One Who Avoids Begging","description":"This miskin hadith builds on the previous report and adds more detail. It describes the poor person as one who abstains from begging. In the added wording, he does not have enough to be free of need, yet he does not ask people, and his need is not known so that sadaqah may be given to him. The report also mentions the word “deprived,” while Abu Dawud notes that this wording is more sound as a statement of al-Zuhri. The message for everyday readers is clear: hidden need can be easy to miss. People searching “hadith about poor who avoid begging” or “miskin muta'affif hadith” will find here a reminder to look beyond loud requests."},"teachings":["Some poor people avoid asking even when they lack enough.","A person’s need may remain unknown to others.","Giving sadaqah requires care for quiet hardship.","The narration records a note about which wording belongs to al-Zuhri."],"related_hadiths":[{"id":"1631","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1633","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1640","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E397" s="4" t="n"/>
@@ -9636,7 +9640,7 @@
       </c>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sadaqah Is Not for the Rich and Strong","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said sadaqah is not lawful for a rich person or one with strength and sound limbs."},"heading":{"title":"Sadaqah Eligibility Hadith: Not for the Rich or Strong","description":"This sadaqah eligibility hadith is short and firm. Abdullah ibn Amr narrates that the Prophet صلى الله عليه وسلم said sadaqah is not lawful for a rich person or for one who has strength and is sound in limbs. Abu Dawud then records wording differences, such as “strong” and “sound in limbs,” and also mentions a related statement from Abdullah ibn Amr. The core meaning stays the same: sadaqah has limits. It is not a general gift for anyone who asks. For people searching “sadaqah not lawful for rich hadith” or “zakat not for able person hadith,” this narration gives a clear rule from the provided text. It also fits closely with the report about the two strong men who asked during the Farewell Pilgrimage."},"teachings":["Sadaqah is not lawful for a rich person in this narration.","Strength and ability are part of the eligibility discussion.","The report preserves wording differences without changing the main meaning.","Charity distribution should consider need and ability."],"related_hadiths":[{"id":"1633","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1635","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1630","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sadaqah Is Not for the Rich and Strong","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said sadaqah is not lawful for a rich person or one with strength and sound limbs."},"heading":{"title":"Sadaqah Eligibility Hadith: Not for the Rich or Strong","description":"This sadaqah eligibility hadith is short and firm. Abdullah ibn Amr narrates that the Prophet صلى الله عليه وسلم said sadaqah is not lawful for a rich person or for one who has strength and is sound in limbs. Abu Dawud then records wording differences, such as “strong” and “sound in limbs,” and also mentions a related statement from Abdullah ibn Amr. The core meaning stays the same: sadaqah has limits. It is not a general gift for anyone who asks. For people searching “sadaqah not lawful for rich hadith” or “zakat not for able person hadith,” this narration gives a clear rule from the provided text. It also fits closely with the report about the two strong men who asked during the Farewell Pilgrimage."},"teachings":["Sadaqah is not lawful for a rich person in this narration.","Strength and ability are part of the eligibility discussion.","The report preserves wording differences without changing the main meaning.","Charity distribution should consider need and ability."],"related_hadiths":[{"id":"1633","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1635","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1630","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E398" s="4" t="n"/>
@@ -9659,7 +9663,7 @@
       </c>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Five Cases Where a Rich Person May Receive","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم named five exceptions in which sadaqah may reach a rich person."},"heading":{"title":"Sadaqah for a Rich Person Hadith: Five Exceptions","description":"This sadaqah for a rich person hadith gives five listed exceptions. The Prophet صلى الله عليه وسلم said sadaqah is not lawful for a rich man except in five cases: one who fights in Allah’s path, one who collects it, a debtor, a man who buys it with his own money, or a man whose poor neighbor receives sadaqah and then gifts it to the rich man. The wording is practical and exact. It does not remove the main rule that sadaqah is not for the rich. It explains named cases where it may reach him. Readers searching “five exceptions zakat rich hadith” or “can a rich person receive sadaqah hadith” should notice each exception as stated, without adding more."},"teachings":["The main rule remains that sadaqah is not for the rich.","The hadith lists five stated exceptions.","A worker who collects sadaqah is included in the exceptions.","A poor neighbor’s gift can make sadaqah reach a rich person as a gift."],"related_hadiths":[{"id":"1636","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1637","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1634","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Five Cases Where a Rich Person May Receive","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم named five exceptions in which sadaqah may reach a rich person."},"heading":{"title":"Sadaqah for a Rich Person Hadith: Five Exceptions","description":"This sadaqah for a rich person hadith gives five listed exceptions. The Prophet صلى الله عليه وسلم said sadaqah is not lawful for a rich man except in five cases: one who fights in Allah’s path, one who collects it, a debtor, a man who buys it with his own money, or a man whose poor neighbor receives sadaqah and then gifts it to the rich man. The wording is practical and exact. It does not remove the main rule that sadaqah is not for the rich. It explains named cases where it may reach him. Readers searching “five exceptions zakat rich hadith” or “can a rich person receive sadaqah hadith” should notice each exception as stated, without adding more."},"teachings":["The main rule remains that sadaqah is not for the rich.","The hadith lists five stated exceptions.","A worker who collects sadaqah is included in the exceptions.","A poor neighbor’s gift can make sadaqah reach a rich person as a gift."],"related_hadiths":[{"id":"1636","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1637","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1634","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E399" s="4" t="n"/>
@@ -9682,7 +9686,7 @@
       </c>
       <c r="D400" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | When Sadaqah May Reach a Rich Person","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم mentioned cases such as Allah’s path, traveler, and a poor neighbor who gifts or invites."},"heading":{"title":"Sadaqah for the Rich Hadith: Gift, Travel, and Allah’s Path","description":"This sadaqah for the rich hadith gives a related wording with named situations. Abu Sa'id reports that the Messenger of Allah صلى الله عليه وسلم said sadaqah is not lawful for a rich person except in Allah’s path, or for the wayfarer, or when a poor neighbor receives sadaqah and then gives it to you as a gift or invites you. The teaching is exact and should not be stretched. It is not saying that rich people normally take zakat. It is listing cases where sadaqah may reach them in a different way. For search intent like “poor neighbor gives sadaqah as gift hadith” or “sadaqah for traveler hadith,” this narration gives clear wording."},"teachings":["The general rule is that sadaqah is not lawful for the rich.","The narration names specific exceptions.","A poor neighbor may gift or invite from what he received.","The wayfarer is mentioned in this wording."],"related_hadiths":[{"id":"1635","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1636","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1630","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | When Sadaqah May Reach a Rich Person","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم mentioned cases such as Allah’s path, traveler, and a poor neighbor who gifts or invites."},"heading":{"title":"Sadaqah for the Rich Hadith: Gift, Travel, and Allah’s Path","description":"This sadaqah for the rich hadith gives a related wording with named situations. Abu Sa'id reports that the Messenger of Allah صلى الله عليه وسلم said sadaqah is not lawful for a rich person except in Allah’s path, or for the wayfarer, or when a poor neighbor receives sadaqah and then gives it to you as a gift or invites you. The teaching is exact and should not be stretched. It is not saying that rich people normally take zakat. It is listing cases where sadaqah may reach them in a different way. For search intent like “poor neighbor gives sadaqah as gift hadith” or “sadaqah for traveler hadith,” this narration gives clear wording."},"teachings":["The general rule is that sadaqah is not lawful for the rich.","The narration names specific exceptions.","A poor neighbor may gift or invite from what he received.","The wayfarer is mentioned in this wording."],"related_hadiths":[{"id":"1635","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1636","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1630","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E400" s="4" t="n"/>
@@ -9705,7 +9709,7 @@
       </c>
       <c r="D401" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blood-Wit Paid from Sadaqah Camels","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم gave one hundred camels from the sadaqah camels as blood-wit for the Ansari killed at Khaibar."},"heading":{"title":"Blood-Wit Hadith: Sadaqah Camels Used for a Diyyah","description":"This blood-wit hadith mentions a specific case. A man from the Ansar, Sahl ibn Abu Hathmah, reported that the Prophet صلى الله عليه وسلم gave him one hundred camels as blood-wit from the camels of sadaqah. The text explains that this was the blood-wit for the Ansari who was killed at Khaibar. The narration is not a general discussion of zakat categories or legal detail. It records one action: a diyyah was paid with one hundred camels from sadaqah camels. For readers searching “blood money from zakat hadith,” “diyyah camels hadith,” or “Ansari killed at Khaibar hadith,” the safest explanation is to stay close to this event and not add rulings that the text itself does not state."},"teachings":["The narration records a specific payment of blood-wit.","The amount mentioned is one hundred camels.","The camels are described as being from the sadaqah camels.","The case relates to an Ansari killed at Khaibar."],"related_hadiths":[{"id":"1625","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1630","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Blood-Wit Paid from Sadaqah Camels","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم gave one hundred camels from the sadaqah camels as blood-wit for the Ansari killed at Khaibar."},"heading":{"title":"Blood-Wit Hadith: Sadaqah Camels Used for a Diyyah","description":"This blood-wit hadith mentions a specific case. A man from the Ansar, Sahl ibn Abu Hathmah, reported that the Prophet صلى الله عليه وسلم gave him one hundred camels as blood-wit from the camels of sadaqah. The text explains that this was the blood-wit for the Ansari who was killed at Khaibar. The narration is not a general discussion of zakat categories or legal detail. It records one action: a diyyah was paid with one hundred camels from sadaqah camels. For readers searching “blood money from zakat hadith,” “diyyah camels hadith,” or “Ansari killed at Khaibar hadith,” the safest explanation is to stay close to this event and not add rulings that the text itself does not state."},"teachings":["The narration records a specific payment of blood-wit.","The amount mentioned is one hundred camels.","The camels are described as being from the sadaqah camels.","The case relates to an Ansari killed at Khaibar."],"related_hadiths":[{"id":"1625","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1630","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E401" s="4" t="n"/>
@@ -9728,7 +9732,7 @@
       </c>
       <c r="D402" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Begging and Self-Respect","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم described begging as marks on a person’s face, except when asking a ruler or facing necessity."},"heading":{"title":"Begging and Self-Respect Hadith: When Asking Is Excused","description":"This begging and self-respect hadith gives a strong image. The Prophet صلى الله عليه وسلم said acts of begging are lacerations by which a man disfigures his face. Then he said that whoever wishes may preserve his face, and whoever wishes may leave it. But the hadith also gives exceptions: asking a ruler, or asking in a matter from which a person finds no escape. That balance matters. The narration discourages casual begging and repeated asking, but it does not close the door on need. For search terms such as “hadith about begging and self respect,” “begging from ruler hadith,” and “asking in necessity Islam,” this text gives both warning and allowance in one short report."},"teachings":["Begging without need harms a person’s dignity in this wording.","The hadith makes an exception for asking a ruler.","It also allows asking in a matter of real necessity.","The text balances self-restraint with genuine need."],"related_hadiths":[{"id":"1626","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1629","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1640","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Begging and Self-Respect","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم described begging as marks on a person’s face, except when asking a ruler or facing necessity."},"heading":{"title":"Begging and Self-Respect Hadith: When Asking Is Excused","description":"This begging and self-respect hadith gives a strong image. The Prophet صلى الله عليه وسلم said acts of begging are lacerations by which a man disfigures his face. Then he said that whoever wishes may preserve his face, and whoever wishes may leave it. But the hadith also gives exceptions: asking a ruler, or asking in a matter from which a person finds no escape. That balance matters. The narration discourages casual begging and repeated asking, but it does not close the door on need. For search terms such as “hadith about begging and self respect,” “begging from ruler hadith,” and “asking in necessity Islam,” this text gives both warning and allowance in one short report."},"teachings":["Begging without need harms a person’s dignity in this wording.","The hadith makes an exception for asking a ruler.","It also allows asking in a matter of real necessity.","The text balances self-restraint with genuine need."],"related_hadiths":[{"id":"1626","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1629","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1640","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E402" s="4" t="n"/>
@@ -9751,7 +9755,7 @@
       </c>
       <c r="D403" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Cases Where Begging Is Allowed","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم allowed begging for three cases: a guarantor payment, destroyed wealth, or confirmed poverty."},"heading":{"title":"Begging Is Allowed in Three Cases Hadith","description":"This hadith about begging allowed in three cases is one of the clearest texts in the batch. Qabisah came to the Prophet صلى الله عليه وسلم because he had become a guarantor for a payment. The Prophet صلى الله عليه وسلم told him to wait until sadaqah came so it could be ordered for him. Then he explained that begging is allowed only for three types: a man who has taken on a guarantor payment until he receives enough to cover it, a man whose property is destroyed by a calamity until he gets basic support, and a man struck by poverty when three sensible people from his people confirm it. After each case, the person must stop once his need is met. Any other begging is described as forbidden consumption."},"teachings":["Begging is allowed for a guarantor payment until it is covered.","A calamity that destroys wealth is named as a valid case.","Confirmed poverty is named as a valid case.","After getting enough support, the person must stop asking."],"related_hadiths":[{"id":"1629","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1639","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1633","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Cases Where Begging Is Allowed","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم allowed begging for three cases: a guarantor payment, destroyed wealth, or confirmed poverty."},"heading":{"title":"Begging Is Allowed in Three Cases Hadith","description":"This hadith about begging allowed in three cases is one of the clearest texts in the batch. Qabisah came to the Prophet صلى الله عليه وسلم because he had become a guarantor for a payment. The Prophet صلى الله عليه وسلم told him to wait until sadaqah came so it could be ordered for him. Then he explained that begging is allowed only for three types: a man who has taken on a guarantor payment until he receives enough to cover it, a man whose property is destroyed by a calamity until he gets basic support, and a man struck by poverty when three sensible people from his people confirm it. After each case, the person must stop once his need is met. Any other begging is described as forbidden consumption."},"teachings":["Begging is allowed for a guarantor payment until it is covered.","A calamity that destroys wealth is named as a valid case.","Confirmed poverty is named as a valid case.","After getting enough support, the person must stop asking."],"related_hadiths":[{"id":"1629","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1639","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1633","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E403" s="4" t="n"/>
@@ -9774,7 +9778,7 @@
       </c>
       <c r="D404" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Work Is Better Than Begging","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم guides a needy man toward work, showing when begging is allowed and why earning with effort is better."},"heading":{"title":"Hadith About Begging and Self-Reliance in Islam","description":"This Hadith about begging teaches a clear path from need to honest work. A man from the Ansar asked the Prophet صلى الله عليه وسلم for help. Instead of only giving him something for the moment, the Prophet صلى الله عليه وسلم looked at what he had, sold his simple items, and helped him buy food and an axe. Then he fixed the axe handle with his own hands and told him to gather firewood and sell it. The man returned with earnings, clothing, and food. The lesson is simple: when a person can work, earning through halal effort is better than asking people. The Hadith also gives limits: begging is right only for severe poverty, heavy debt, or hard compensation."},"teachings":["Seeking work is better than asking people when a person is able to earn.","Immediate family needs should be handled with care, such as food before other plans.","Begging is only allowed in the hard cases named in the Hadith."],"related_hadiths":[{"id":"1471","book_id":"1","label":"Sahih Bukhari"},{"id":"1469","book_id":"1","label":"Sahih Bukhari"},{"id":"1427","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Work Is Better Than Begging","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم guides a needy man toward work, showing when begging is allowed and why earning with effort is better."},"heading":{"title":"Hadith About Begging and Self-Reliance in Islam","description":"This Hadith about begging teaches a clear path from need to honest work. A man from the Ansar asked the Prophet صلى الله عليه وسلم for help. Instead of only giving him something for the moment, the Prophet صلى الله عليه وسلم looked at what he had, sold his simple items, and helped him buy food and an axe. Then he fixed the axe handle with his own hands and told him to gather firewood and sell it. The man returned with earnings, clothing, and food. The lesson is simple: when a person can work, earning through halal effort is better than asking people. The Hadith also gives limits: begging is right only for severe poverty, heavy debt, or hard compensation."},"teachings":["Seeking work is better than asking people when a person is able to earn.","Immediate family needs should be handled with care, such as food before other plans.","Begging is only allowed in the hard cases named in the Hadith."],"related_hadiths":[{"id":"1471","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1469","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1427","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E404" s="4" t="n"/>
@@ -9797,7 +9801,7 @@
       </c>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Promise for Avoiding Begging","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم gives a strong promise to the one who leaves begging, and Thawban applies it in daily life."},"heading":{"title":"Hadith About Avoiding Begging and Paradise","description":"This Hadith about avoiding begging is short, but its message is powerful. The Prophet صلى الله عليه وسلم asked who would guarantee that he would not beg from people, and he promised Paradise for that person. Thawban accepted this promise and lived by it. The report says he never asked anyone for anything. The Hadith points to a high level of self-control and trust in Allah. It does not describe every case of need, so it should be read together with the text that allows asking in severe hardship. Here, the focus is on a person who chooses not to make asking people his way of life. It teaches dignity, restraint, and strong faith."},"teachings":["Avoiding begging is praised when a person can bear it.","A promise made for Allah’s sake should be taken seriously.","Thawban’s response shows practical commitment, not only words."],"related_hadiths":[{"id":"1471","book_id":"1","label":"Sahih Bukhari"},{"id":"1469","book_id":"1","label":"Sahih Bukhari"},{"id":"1427","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Promise for Avoiding Begging","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم gives a strong promise to the one who leaves begging, and Thawban applies it in daily life."},"heading":{"title":"Hadith About Avoiding Begging and Paradise","description":"This Hadith about avoiding begging is short, but its message is powerful. The Prophet صلى الله عليه وسلم asked who would guarantee that he would not beg from people, and he promised Paradise for that person. Thawban accepted this promise and lived by it. The report says he never asked anyone for anything. The Hadith points to a high level of self-control and trust in Allah. It does not describe every case of need, so it should be read together with the text that allows asking in severe hardship. Here, the focus is on a person who chooses not to make asking people his way of life. It teaches dignity, restraint, and strong faith."},"teachings":["Avoiding begging is praised when a person can bear it.","A promise made for Allah’s sake should be taken seriously.","Thawban’s response shows practical commitment, not only words."],"related_hadiths":[{"id":"1471","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1469","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1427","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E405" s="4" t="n"/>
@@ -9820,7 +9824,7 @@
       </c>
       <c r="D406" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Patience Is a Wide Gift","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم teaches restraint, contentment, and patience after giving what he had to those who asked."},"heading":{"title":"Hadith About Patience and Contentment in Islam","description":"This Hadith about patience and contentment begins with people from the Ansar asking the Prophet صلى الله عليه وسلم for help. He gave them until what he had was gone. Then he explained a lasting lesson: whatever good he had, he would not keep it away from them. But the person who seeks to abstain, Allah strengthens his abstinence. The one who seeks satisfaction, Allah gives him satisfaction. The one who shows patience, Allah strengthens his patience. The Hadith closes by saying that no one has been given a gift wider than patience. The teaching is not coldness toward the needy. It joins generosity with inner strength, asking less, and learning to carry hardship with sabr."},"teachings":["The Prophet صلى الله عليه وسلم gave from what he had and did not hide good from people.","A person who tries to abstain from asking is helped toward restraint.","Patience is described as a wide and valuable gift."],"related_hadiths":[{"id":"1469","book_id":"1","label":"Sahih Bukhari"},{"id":"1053a","book_id":"2","label":"Sahih Muslim"},{"id":"1427","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Patience Is a Wide Gift","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم teaches restraint, contentment, and patience after giving what he had to those who asked."},"heading":{"title":"Hadith About Patience and Contentment in Islam","description":"This Hadith about patience and contentment begins with people from the Ansar asking the Prophet صلى الله عليه وسلم for help. He gave them until what he had was gone. Then he explained a lasting lesson: whatever good he had, he would not keep it away from them. But the person who seeks to abstain, Allah strengthens his abstinence. The one who seeks satisfaction, Allah gives him satisfaction. The one who shows patience, Allah strengthens his patience. The Hadith closes by saying that no one has been given a gift wider than patience. The teaching is not coldness toward the needy. It joins generosity with inner strength, asking less, and learning to carry hardship with sabr."},"teachings":["The Prophet صلى الله عليه وسلم gave from what he had and did not hide good from people.","A person who tries to abstain from asking is helped toward restraint.","Patience is described as a wide and valuable gift."],"related_hadiths":[{"id":"1469","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1053a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1427","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E406" s="4" t="n"/>
@@ -9843,7 +9847,7 @@
       </c>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ask Only When There Is No Escape","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم discourages begging and, if it cannot be avoided, directs the person to ask the upright."},"heading":{"title":"Hadith About Begging Only When Necessary","description":"This Hadith about begging gives a simple and balanced answer. Al-Firasi asked the Messenger of Allah صلى الله عليه وسلم if he may beg. The Prophet صلى الله عليه وسلم said no. Then he added that if there is no escape from asking, the person should ask from the upright. The wording keeps two points together. First, begging is not something to choose without need. Second, if a person is trapped by a hard situation and must ask, he should choose people of goodness and honesty. The Hadith does not list every type of need, so the explanation should stay close to its wording. It teaches restraint, careful choice, and respect for one’s dignity while facing hardship."},"teachings":["Begging should not be a first choice.","If asking becomes unavoidable, the Hadith points to upright people.","A believer should protect dignity while dealing with real need."],"related_hadiths":[{"id":"1471","book_id":"1","label":"Sahih Bukhari"},{"id":"1469","book_id":"1","label":"Sahih Bukhari"},{"id":"1053a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ask Only When There Is No Escape","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم discourages begging and, if it cannot be avoided, directs the person to ask the upright."},"heading":{"title":"Hadith About Begging Only When Necessary","description":"This Hadith about begging gives a simple and balanced answer. Al-Firasi asked the Messenger of Allah صلى الله عليه وسلم if he may beg. The Prophet صلى الله عليه وسلم said no. Then he added that if there is no escape from asking, the person should ask from the upright. The wording keeps two points together. First, begging is not something to choose without need. Second, if a person is trapped by a hard situation and must ask, he should choose people of goodness and honesty. The Hadith does not list every type of need, so the explanation should stay close to its wording. It teaches restraint, careful choice, and respect for one’s dignity while facing hardship."},"teachings":["Begging should not be a first choice.","If asking becomes unavoidable, the Hadith points to upright people.","A believer should protect dignity while dealing with real need."],"related_hadiths":[{"id":"1471","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1469","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1053a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E407" s="4" t="n"/>
@@ -9866,7 +9870,7 @@
       </c>
       <c r="D408" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Accept What Comes Without Asking","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم teaches that payment or gifts received without asking may be used and also given in charity."},"heading":{"title":"Hadith About Accepting Gifts Without Asking","description":"This Hadith about accepting gifts without asking deals with a worker who collected sadaqah. Ibn al-Saidi says Umar employed him to collect it. When the work was finished, Umar ordered payment for him. Ibn al-Saidi felt he had worked only for Allah and wanted his reward from Allah. Umar then shared that he had once said the same to the Messenger of Allah صلى الله عليه وسلم when he was given payment for similar work. The Prophet صلى الله عليه وسلم told him that when he is given something without asking for it, he may use it for himself and give from it as sadaqah. The Hadith teaches that refusing pay is not the only way to be sincere."},"teachings":["A person may receive what is given without asking for it.","Sincerity for Allah can remain even when lawful payment is accepted.","What is received can be used personally and also shared as sadaqah."],"related_hadiths":[{"id":"1045b","book_id":"2","label":"Sahih Muslim"},{"id":"1045d","book_id":"2","label":"Sahih Muslim"},{"id":"1045e","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Accept What Comes Without Asking","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم teaches that payment or gifts received without asking may be used and also given in charity."},"heading":{"title":"Hadith About Accepting Gifts Without Asking","description":"This Hadith about accepting gifts without asking deals with a worker who collected sadaqah. Ibn al-Saidi says Umar employed him to collect it. When the work was finished, Umar ordered payment for him. Ibn al-Saidi felt he had worked only for Allah and wanted his reward from Allah. Umar then shared that he had once said the same to the Messenger of Allah صلى الله عليه وسلم when he was given payment for similar work. The Prophet صلى الله عليه وسلم told him that when he is given something without asking for it, he may use it for himself and give from it as sadaqah. The Hadith teaches that refusing pay is not the only way to be sincere."},"teachings":["A person may receive what is given without asking for it.","Sincerity for Allah can remain even when lawful payment is accepted.","What is received can be used personally and also shared as sadaqah."],"related_hadiths":[{"id":"1045b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1045d","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1045e","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E408" s="4" t="n"/>
@@ -9889,7 +9893,7 @@
       </c>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Give From What Is Surplus","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم describes three hands and tells believers to give surplus without being overcome by the soul’s demands."},"heading":{"title":"Hadith About Giving Surplus Charity in Islam","description":"This Hadith about giving surplus charity explains hands in three levels. Allah’s hand is the upper one. The hand of the giver comes near it. The hand of the beggar is the lower one. Then the Prophet صلى الله عليه وسلم gives a direct instruction: give what is surplus, and do not submit yourself to the demand of your soul. The teaching is practical. It does not call a person to harm his own needs, because it mentions surplus. At the same time, it warns the person not to let the inner pull for more stop him from giving. The Hadith joins generosity with self-control and makes charity a way to rise above selfish desire."},"teachings":["Giving from surplus is praised in the Hadith.","A person should not let inner desire stop needed generosity.","The giver’s hand is honored above the hand that asks."],"related_hadiths":[{"id":"1427","book_id":"1","label":"Sahih Bukhari"},{"id":"1429","book_id":"1","label":"Sahih Bukhari"},{"id":"2590","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Give From What Is Surplus","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم describes three hands and tells believers to give surplus without being overcome by the soul’s demands."},"heading":{"title":"Hadith About Giving Surplus Charity in Islam","description":"This Hadith about giving surplus charity explains hands in three levels. Allah’s hand is the upper one. The hand of the giver comes near it. The hand of the beggar is the lower one. Then the Prophet صلى الله عليه وسلم gives a direct instruction: give what is surplus, and do not submit yourself to the demand of your soul. The teaching is practical. It does not call a person to harm his own needs, because it mentions surplus. At the same time, it warns the person not to let the inner pull for more stop him from giving. The Hadith joins generosity with self-control and makes charity a way to rise above selfish desire."},"teachings":["Giving from surplus is praised in the Hadith.","A person should not let inner desire stop needed generosity.","The giver’s hand is honored above the hand that asks."],"related_hadiths":[{"id":"1427","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1429","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2590","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E409" s="4" t="n"/>
@@ -9912,7 +9916,7 @@
       </c>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sadaqah Is Not Lawful for the Prophet’s Household","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم explains that sadaqah is not lawful for his household, and a client belongs with his people."},"heading":{"title":"Hadith About Sadaqah Not Lawful for Ahl al-Bayt","description":"This Hadith about sadaqah not being lawful for the Prophet’s household begins with a man from Banu Makhzum being sent to collect sadaqah. He asked Abu Rafi to come with him so he might receive some of it. Abu Rafi did not decide by himself. He went to the Prophet صلى الله عليه وسلم and asked. The answer was clear: sadaqah is not lawful for us, and the client of a people is treated as one of them. The Hadith shows careful religious practice. Abu Rafi paused before taking anything linked to sadaqah. The Prophet صلى الله عليه وسلم then explained that the ruling covered him because of his connection to the Prophet’s people."},"teachings":["Abu Rafi asked before taking from something doubtful to him.","The Prophet صلى الله عليه وسلم stated that sadaqah was not lawful for his household.","A client is treated as connected to the people he belongs to."],"related_hadiths":[{"id":"2431","book_id":"1","label":"Sahih Bukhari"},{"id":"1074a","book_id":"2","label":"Sahih Muslim"},{"id":"2578","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sadaqah Is Not Lawful for the Prophet’s Household","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم explains that sadaqah is not lawful for his household, and a client belongs with his people."},"heading":{"title":"Hadith About Sadaqah Not Lawful for Ahl al-Bayt","description":"This Hadith about sadaqah not being lawful for the Prophet’s household begins with a man from Banu Makhzum being sent to collect sadaqah. He asked Abu Rafi to come with him so he might receive some of it. Abu Rafi did not decide by himself. He went to the Prophet صلى الله عليه وسلم and asked. The answer was clear: sadaqah is not lawful for us, and the client of a people is treated as one of them. The Hadith shows careful religious practice. Abu Rafi paused before taking anything linked to sadaqah. The Prophet صلى الله عليه وسلم then explained that the ruling covered him because of his connection to the Prophet’s people."},"teachings":["Abu Rafi asked before taking from something doubtful to him.","The Prophet صلى الله عليه وسلم stated that sadaqah was not lawful for his household.","A client is treated as connected to the people he belongs to."],"related_hadiths":[{"id":"2431","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1074a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2578","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E410" s="4" t="n"/>
@@ -9935,7 +9939,7 @@
       </c>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Leaving a Date Out of Caution","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم avoided taking a fallen date because it might have been sadaqah, showing carefulness in doubtful matters."},"heading":{"title":"Hadith About Avoiding Doubtful Sadaqah","description":"This Hadith about avoiding doubtful sadaqah is very brief, but it teaches carefulness. Anas reports that the Messenger of Allah صلى الله عليه وسلم passed by a date lying on the road. He did not take it only because he feared it might be from sadaqah. The text does not say the date was certainly sadaqah. It says the Prophet صلى الله عليه وسلم avoided it because of that possibility. This gives a simple example of staying away from something when there is a religious concern tied to it. The lesson is not about being wasteful. It is about caution when a matter may fall under something not allowed for him. The focus is clean conduct and careful eating."},"teachings":["The Prophet صلى الله عليه وسلم avoided what might be sadaqah for him.","Caution can be practiced even in small matters.","A person should pause when a matter may be religiously sensitive."],"related_hadiths":[{"id":"2431","book_id":"1","label":"Sahih Bukhari"},{"id":"1074a","book_id":"2","label":"Sahih Muslim"},{"id":"2578","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Leaving a Date Out of Caution","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم avoided taking a fallen date because it might have been sadaqah, showing carefulness in doubtful matters."},"heading":{"title":"Hadith About Avoiding Doubtful Sadaqah","description":"This Hadith about avoiding doubtful sadaqah is very brief, but it teaches carefulness. Anas reports that the Messenger of Allah صلى الله عليه وسلم passed by a date lying on the road. He did not take it only because he feared it might be from sadaqah. The text does not say the date was certainly sadaqah. It says the Prophet صلى الله عليه وسلم avoided it because of that possibility. This gives a simple example of staying away from something when there is a religious concern tied to it. The lesson is not about being wasteful. It is about caution when a matter may fall under something not allowed for him. The focus is clean conduct and careful eating."},"teachings":["The Prophet صلى الله عليه وسلم avoided what might be sadaqah for him.","Caution can be practiced even in small matters.","A person should pause when a matter may be religiously sensitive."],"related_hadiths":[{"id":"2431","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1074a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2578","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E411" s="4" t="n"/>
@@ -9958,7 +9962,7 @@
       </c>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fear It May Be Sadaqah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم says he would eat a found date if not for fear that it might be from sadaqah."},"heading":{"title":"Hadith About a Found Date and Sadaqah Caution","description":"This Hadith about a found date gives the same careful lesson in direct words. Anas reports that the Messenger of Allah صلى الله عليه وسلم found a date and said that if he did not fear it might be from sadaqah, he would eat it. The meaning stays close to the wording: the date itself was small, but the concern was serious because it might belong to a category not lawful for him. This Hadith is often searched as the Prophet صلى الله عليه وسلم found a date hadith. It teaches that a believer should not treat small things as meaningless when halal and haram may be involved. Care in small matters can protect a person’s conduct."},"teachings":["The Prophet صلى الله عليه وسلم considered the possibility that the date was sadaqah.","Small items can still require care when lawful use is unclear.","Avoiding doubtful benefit can be part of clean religious practice."],"related_hadiths":[{"id":"2431","book_id":"1","label":"Sahih Bukhari"},{"id":"1074a","book_id":"2","label":"Sahih Muslim"},{"id":"2578","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fear It May Be Sadaqah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم says he would eat a found date if not for fear that it might be from sadaqah."},"heading":{"title":"Hadith About a Found Date and Sadaqah Caution","description":"This Hadith about a found date gives the same careful lesson in direct words. Anas reports that the Messenger of Allah صلى الله عليه وسلم found a date and said that if he did not fear it might be from sadaqah, he would eat it. The meaning stays close to the wording: the date itself was small, but the concern was serious because it might belong to a category not lawful for him. This Hadith is often searched as the Prophet صلى الله عليه وسلم found a date hadith. It teaches that a believer should not treat small things as meaningless when halal and haram may be involved. Care in small matters can protect a person’s conduct."},"teachings":["The Prophet صلى الله عليه وسلم considered the possibility that the date was sadaqah.","Small items can still require care when lawful use is unclear.","Avoiding doubtful benefit can be part of clean religious practice."],"related_hadiths":[{"id":"2431","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1074a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2578","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E412" s="4" t="n"/>
@@ -9981,7 +9985,7 @@
       </c>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Exchanging Sadaqah Camels","description":"$book_name$ $hadith_number$ - $chapter_name$. A second chain reports the same event and adds that the father exchanged the camels for him."},"heading":{"title":"Hadith About Exchanging Camels From Sadaqah","description":"This Hadith about exchanging camels from sadaqah is another narration of the previous report. The wording says it was transmitted from Ibn Abbas through a different chain in a similar manner, and this version adds: my father exchanged them for him. Because the text is brief, the explanation should not add details that are not stated. What it clearly shows is that the same sadaqah-related camels were part of a handled transaction, and the added phrase mentions an exchange made by Ibn Abbas’s father. The Hadith is useful for readers searching for sadaqah property, zakat camels, and the careful transfer of charity goods in early Muslim practice."},"teachings":["The report confirms the same account through another chain.","This version adds that Ibn Abbas’s father exchanged the camels.","Charity-linked property is shown as something handled with clear action."],"related_hadiths":[{"id":"2578","book_id":"1","label":"Sahih Bukhari"},{"id":"1074a","book_id":"2","label":"Sahih Muslim"},{"id":"1493","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Exchanging Sadaqah Camels","description":"$book_name$ $hadith_number$ - $chapter_name$. A second chain reports the same event and adds that the father exchanged the camels for him."},"heading":{"title":"Hadith About Exchanging Camels From Sadaqah","description":"This Hadith about exchanging camels from sadaqah is another narration of the previous report. The wording says it was transmitted from Ibn Abbas through a different chain in a similar manner, and this version adds: my father exchanged them for him. Because the text is brief, the explanation should not add details that are not stated. What it clearly shows is that the same sadaqah-related camels were part of a handled transaction, and the added phrase mentions an exchange made by Ibn Abbas’s father. The Hadith is useful for readers searching for sadaqah property, zakat camels, and the careful transfer of charity goods in early Muslim practice."},"teachings":["The report confirms the same account through another chain.","This version adds that Ibn Abbas’s father exchanged the camels.","Charity-linked property is shown as something handled with clear action."],"related_hadiths":[{"id":"2578","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1074a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1493","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E413" s="4" t="n"/>
@@ -10004,7 +10008,7 @@
       </c>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward Remains and Inheritance Returns","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم tells a woman that her sadaqah reward remains, while inheritance returned the slave girl to her."},"heading":{"title":"Hadith About Charity Reward and Inheritance","description":"This Hadith about charity reward and inheritance answers a personal question. A woman told the Messenger of Allah صلى الله عليه وسلم that she had given a slave girl as sadaqah to her mother. Her mother then died and left that slave girl behind. The Prophet صلى الله عليه وسلم said that her reward was sure and the inheritance had returned the slave girl to her. The Hadith separates two matters. The reward for giving had already been earned, and the later return came through inheritance. It is not saying every gift will come back. It speaks about this stated case. For readers, the key terms are sadaqah to parents, reward for charity, and inheritance returning property."},"teachings":["A charitable act can have its reward even if the item later returns by inheritance.","The woman asked about her real situation instead of guessing.","The Prophet صلى الله عليه وسلم answered both the reward and ownership parts of the case."],"related_hadiths":[{"id":"2762","book_id":"1","label":"Sahih Bukhari"},{"id":"2760","book_id":"1","label":"Sahih Bukhari"},{"id":"1004c","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward Remains and Inheritance Returns","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم tells a woman that her sadaqah reward remains, while inheritance returned the slave girl to her."},"heading":{"title":"Hadith About Charity Reward and Inheritance","description":"This Hadith about charity reward and inheritance answers a personal question. A woman told the Messenger of Allah صلى الله عليه وسلم that she had given a slave girl as sadaqah to her mother. Her mother then died and left that slave girl behind. The Prophet صلى الله عليه وسلم said that her reward was sure and the inheritance had returned the slave girl to her. The Hadith separates two matters. The reward for giving had already been earned, and the later return came through inheritance. It is not saying every gift will come back. It speaks about this stated case. For readers, the key terms are sadaqah to parents, reward for charity, and inheritance returning property."},"teachings":["A charitable act can have its reward even if the item later returns by inheritance.","The woman asked about her real situation instead of guessing.","The Prophet صلى الله عليه وسلم answered both the reward and ownership parts of the case."],"related_hadiths":[{"id":"2762","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2760","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1004c","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E414" s="4" t="n"/>
@@ -10027,7 +10031,7 @@
       </c>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lending Daily Use Items","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Mas‘ud explains that ma‘un was understood as lending useful items like a bucket and cooking pot."},"heading":{"title":"Hadith About Ma'un and Lending Daily Items","description":"This Hadith about ma'un and lending daily items is simple and practical. Abdullah ibn Mas'ud says that during the time of the Messenger of Allah صلى الله عليه وسلم, they used to consider ma'un to be lending a bucket and a cooking pot. The report points to small acts of help that people may need in normal life. It is not about large gifts or public charity only. A bucket and pot are basic tools for water and food. Lending them makes life easier for others without needing a big cost. The Hadith teaches that everyday help matters. It also helps readers understand ma'un as useful support shared between people."},"teachings":["Small useful items can be part of helping others.","Lending a bucket or cooking pot was counted as ma'un in this report.","Daily kindness is not limited to large acts of charity."],"related_hadiths":[{"id":"1416","book_id":"1","label":"Sahih Bukhari"},{"id":"2590","book_id":"1","label":"Sahih Bukhari"},{"id":"1017a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lending Daily Use Items","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Mas‘ud explains that ma‘un was understood as lending useful items like a bucket and cooking pot."},"heading":{"title":"Hadith About Ma'un and Lending Daily Items","description":"This Hadith about ma'un and lending daily items is simple and practical. Abdullah ibn Mas'ud says that during the time of the Messenger of Allah صلى الله عليه وسلم, they used to consider ma'un to be lending a bucket and a cooking pot. The report points to small acts of help that people may need in normal life. It is not about large gifts or public charity only. A bucket and pot are basic tools for water and food. Lending them makes life easier for others without needing a big cost. The Hadith teaches that everyday help matters. It also helps readers understand ma'un as useful support shared between people."},"teachings":["Small useful items can be part of helping others.","Lending a bucket or cooking pot was counted as ma'un in this report.","Daily kindness is not limited to large acts of charity."],"related_hadiths":[{"id":"1416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2590","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1017a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E415" s="4" t="n"/>
@@ -10050,7 +10054,7 @@
       </c>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning for Withholding Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم warns owners of treasure, sheep, and camels who do not pay what is due on them."},"heading":{"title":"Hadith About Not Paying Zakat on Wealth and Livestock","description":"This Hadith about not paying zakat gives a serious warning. Abu Hurairah reports that owners of treasure who do not pay what is due on it will face punishment with it on the Day of Judgment. Their side, forehead, and back are mentioned. The Hadith then speaks about owners of sheep and camels who do not pay what is due on them. Those animals appear strong and many, and the owner is trampled or struck until Allah judges between people. The wording is strong because withholding zakat is not a small matter. The Hadith focuses on wealth, sheep, camels, the Day of Judgment, and the duty to give what is due."},"teachings":["Wealth has a due right that must not be withheld.","Livestock owners are also warned about failing to pay what is due.","The Day of Judgment is used in the Hadith to show the seriousness of unpaid zakat."],"related_hadiths":[{"id":"987a","book_id":"2","label":"Sahih Muslim"},{"id":"987c","book_id":"2","label":"Sahih Muslim"},{"id":"1402","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warning for Withholding Zakat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم warns owners of treasure, sheep, and camels who do not pay what is due on them."},"heading":{"title":"Hadith About Not Paying Zakat on Wealth and Livestock","description":"This Hadith about not paying zakat gives a serious warning. Abu Hurairah reports that owners of treasure who do not pay what is due on it will face punishment with it on the Day of Judgment. Their side, forehead, and back are mentioned. The Hadith then speaks about owners of sheep and camels who do not pay what is due on them. Those animals appear strong and many, and the owner is trampled or struck until Allah judges between people. The wording is strong because withholding zakat is not a small matter. The Hadith focuses on wealth, sheep, camels, the Day of Judgment, and the duty to give what is due."},"teachings":["Wealth has a due right that must not be withheld.","Livestock owners are also warned about failing to pay what is due.","The Day of Judgment is used in the Hadith to show the seriousness of unpaid zakat."],"related_hadiths":[{"id":"987a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"987c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1402","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E416" s="4" t="n"/>
@@ -10073,7 +10077,7 @@
       </c>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Right of Camels","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that one right of camels is milking them for others when they come to drink water."},"heading":{"title":"Hadith About the Rights of Camels in Zakat","description":"This Hadith about the rights of camels adds one detail to the previous warning. Abu Hurairah narrates the same general report about owners who do not pay what is due on their property. In the part about camels, this version adds that one of their rights is to milk them on the day they come down to drink water. The wording shows that the right connected to camels is not only a number or payment. It also includes sharing milk in that stated setting. The Hadith teaches care for what Allah has placed in a person’s hands. It links livestock, zakat duty, and practical benefit for others."},"teachings":["Camels have rights that owners should not ignore.","This version mentions giving milk when the camels come to drink water.","The report connects property ownership with responsibility toward others."],"related_hadiths":[{"id":"987c","book_id":"2","label":"Sahih Muslim"},{"id":"990a","book_id":"2","label":"Sahih Muslim"},{"id":"2371","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Right of Camels","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that one right of camels is milking them for others when they come to drink water."},"heading":{"title":"Hadith About the Rights of Camels in Zakat","description":"This Hadith about the rights of camels adds one detail to the previous warning. Abu Hurairah narrates the same general report about owners who do not pay what is due on their property. In the part about camels, this version adds that one of their rights is to milk them on the day they come down to drink water. The wording shows that the right connected to camels is not only a number or payment. It also includes sharing milk in that stated setting. The Hadith teaches care for what Allah has placed in a person’s hands. It links livestock, zakat duty, and practical benefit for others."},"teachings":["Camels have rights that owners should not ignore.","This version mentions giving milk when the camels come to drink water.","The report connects property ownership with responsibility toward others."],"related_hadiths":[{"id":"987c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"990a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2371","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E417" s="4" t="n"/>
@@ -10096,7 +10100,7 @@
       </c>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sprinkling Water After Urination","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم performed ablution after urinating and sprinkled water on the private parts, as this report states."},"heading":{"title":"Sprinkling Water After Urination and Wudu","description":"This Hadith speaks about purification after urination and wudu. Hakam ibn Sufyan ath-Thaqafi reports that when the Messenger of Allah صلى الله عليه وسلم urinated, he performed ablution and sprinkled water on the private parts of the body. The wording is simple, and the teaching should stay simple too. It describes an action connected to cleanliness after relieving oneself. Abu Dawud also adds a note about the chain, saying a group of scholars agreed with Sufyan on this chain, while some differed over the narrator's name: Sufyan ibn al-Hakam or al-Hakam ibn Sufyan. So the Hadith includes both a purification practice and a narrator-name note. Common searches include sprinkling water after urination hadith, wudu after urinating, and nadh water hadith."},"teachings":["The Prophet صلى الله عليه وسلم is reported to have performed wudu after urinating.","The narration mentions sprinkling water on the private parts.","Abu Dawud notes a difference in the narrator's name."],"related_hadiths":[{"id":"135","book_id":"3","label":"Sunan an-Nasai"},{"id":"461","book_id":"6","label":"Sunan Ibn Majah"},{"id":"222","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sprinkling Water After Urination","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم performed ablution after urinating and sprinkled water on the private parts, as this report states."},"heading":{"title":"Sprinkling Water After Urination and Wudu","description":"This Hadith speaks about purification after urination and wudu. Hakam ibn Sufyan ath-Thaqafi reports that when the Messenger of Allah صلى الله عليه وسلم urinated, he performed ablution and sprinkled water on the private parts of the body. The wording is simple, and the teaching should stay simple too. It describes an action connected to cleanliness after relieving oneself. Abu Dawud also adds a note about the chain, saying a group of scholars agreed with Sufyan on this chain, while some differed over the narrator's name: Sufyan ibn al-Hakam or al-Hakam ibn Sufyan. So the Hadith includes both a purification practice and a narrator-name note. Common searches include sprinkling water after urination hadith, wudu after urinating, and nadh water hadith."},"teachings":["The Prophet صلى الله عليه وسلم is reported to have performed wudu after urinating.","The narration mentions sprinkling water on the private parts.","Abu Dawud notes a difference in the narrator's name."],"related_hadiths":[{"id":"135","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"461","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"222","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E418" s="4" t="n"/>
@@ -10119,7 +10123,7 @@
       </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Give, Lend, and Share Milk","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah explains the due rights of camels: giving, lending, offering mounts, breeding service, and milk."},"heading":{"title":"Hadith About the Rights of Camels in Islam","description":"This Hadith about the rights of camels explains what is due on them. Abu Hurairah heard the Messenger of Allah صلى الله عليه وسلم say something like the earlier warning. When asked what is due on camels, Abu Hurairah listed practical duties: give the best of the camels in Allah’s path, lend a milch she-camel, lend a mount for riding, lend the stallion for covering, and give milk to people for drinking. The report turns livestock ownership into responsibility. Camels are not only private wealth. They can serve others through transport, milk, breeding, and giving. The Hadith teaches generosity with useful property and warns against treating blessings as only personal gain."},"teachings":["Owners should recognize practical rights attached to their camels.","Sharing milk, mounts, and breeding service are named in the report.","Useful property can become a way to benefit others."],"related_hadiths":[{"id":"987c","book_id":"2","label":"Sahih Muslim"},{"id":"990a","book_id":"2","label":"Sahih Muslim"},{"id":"2371","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Give, Lend, and Share Milk","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Hurairah explains the due rights of camels: giving, lending, offering mounts, breeding service, and milk."},"heading":{"title":"Hadith About the Rights of Camels in Islam","description":"This Hadith about the rights of camels explains what is due on them. Abu Hurairah heard the Messenger of Allah صلى الله عليه وسلم say something like the earlier warning. When asked what is due on camels, Abu Hurairah listed practical duties: give the best of the camels in Allah’s path, lend a milch she-camel, lend a mount for riding, lend the stallion for covering, and give milk to people for drinking. The report turns livestock ownership into responsibility. Camels are not only private wealth. They can serve others through transport, milk, breeding, and giving. The Hadith teaches generosity with useful property and warns against treating blessings as only personal gain."},"teachings":["Owners should recognize practical rights attached to their camels.","Sharing milk, mounts, and breeding service are named in the report.","Useful property can become a way to benefit others."],"related_hadiths":[{"id":"987c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"990a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"2371","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E419" s="4" t="n"/>
@@ -10142,7 +10146,7 @@
       </c>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sprinkling Water for Cleanliness","description":"$book_name$ $hadith_number$ - $chapter_name$. A man from Thaqif reports seeing the Prophet صلى الله عليه وسلم urinate and then sprinkle water on his private parts."},"heading":{"title":"Sprinkling Water After Urination: A Report from Thaqif","description":"This Hadith is another short report on sprinkling water after urination. A man from Thaqif narrates from his father that he saw the Messenger of Allah صلى الله عليه وسلم urinate, then sprinkle water on the private parts of his body. The report does not add a long explanation, a full wudu sequence, or a separate ruling. It simply records an observed action. For readers searching for hadith about sprinkling water after urinating, nadh after wudu, or purification after urine in Islam, the key point is that the text connects the Prophet's صلى الله عليه وسلم action with cleanliness after urination. Since the Hadith is brief, the safest explanation is also brief and exact: after urinating, water was sprinkled on the private area."},"teachings":["The report describes an action seen from the Prophet صلى الله عليه وسلم.","It connects urination with sprinkling water afterward.","The text does not add extra details beyond the observed act."],"related_hadiths":[{"id":"135","book_id":"3","label":"Sunan an-Nasai"},{"id":"461","book_id":"6","label":"Sunan Ibn Majah"},{"id":"222","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sprinkling Water for Cleanliness","description":"$book_name$ $hadith_number$ - $chapter_name$. A man from Thaqif reports seeing the Prophet صلى الله عليه وسلم urinate and then sprinkle water on his private parts."},"heading":{"title":"Sprinkling Water After Urination: A Report from Thaqif","description":"This Hadith is another short report on sprinkling water after urination. A man from Thaqif narrates from his father that he saw the Messenger of Allah صلى الله عليه وسلم urinate, then sprinkle water on the private parts of his body. The report does not add a long explanation, a full wudu sequence, or a separate ruling. It simply records an observed action. For readers searching for hadith about sprinkling water after urinating, nadh after wudu, or purification after urine in Islam, the key point is that the text connects the Prophet's صلى الله عليه وسلم action with cleanliness after urination. Since the Hadith is brief, the safest explanation is also brief and exact: after urinating, water was sprinkled on the private area."},"teachings":["The report describes an action seen from the Prophet صلى الله عليه وسلم.","It connects urination with sprinkling water afterward.","The text does not add extra details beyond the observed act."],"related_hadiths":[{"id":"135","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"461","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"222","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E420" s="4" t="n"/>
@@ -10165,7 +10169,7 @@
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu and Sprinkling Water","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports that the Prophet صلى الله عليه وسلم urinated, performed ablution, and sprinkled water on the private parts."},"heading":{"title":"Wudu After Urination and Sprinkling Water","description":"This Hadith clearly joins three actions in order: the Prophet صلى الله عليه وسلم urinated, then performed ablution, and then sprinkled water on the private parts of his body. The core topic is purification after urination. It is a direct text for people searching wudu after urinating hadith, sprinkling water after urine, or nadh in Islam. The narration does not discuss doubt, prayer, or a wider method of washing; it only states what happened. That is why the explanation should not go beyond the wording. It shows care for cleanliness after relieving oneself and links that care with ablution. The narrator is named as Hakam or Ibn al-Hakam on the authority of his father, as stated in the report."},"teachings":["The report mentions urination followed by ablution.","It states that water was sprinkled on the private parts.","The narration keeps the focus on practical cleanliness."],"related_hadiths":[{"id":"135","book_id":"3","label":"Sunan an-Nasai"},{"id":"461","book_id":"6","label":"Sunan Ibn Majah"},{"id":"224","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu and Sprinkling Water","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports that the Prophet صلى الله عليه وسلم urinated, performed ablution, and sprinkled water on the private parts."},"heading":{"title":"Wudu After Urination and Sprinkling Water","description":"This Hadith clearly joins three actions in order: the Prophet صلى الله عليه وسلم urinated, then performed ablution, and then sprinkled water on the private parts of his body. The core topic is purification after urination. It is a direct text for people searching wudu after urinating hadith, sprinkling water after urine, or nadh in Islam. The narration does not discuss doubt, prayer, or a wider method of washing; it only states what happened. That is why the explanation should not go beyond the wording. It shows care for cleanliness after relieving oneself and links that care with ablution. The narrator is named as Hakam or Ibn al-Hakam on the authority of his father, as stated in the report."},"teachings":["The report mentions urination followed by ablution.","It states that water was sprinkled on the private parts.","The narration keeps the focus on practical cleanliness."],"related_hadiths":[{"id":"135","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"461","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"224","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E421" s="4" t="n"/>
@@ -10188,7 +10192,7 @@
       </c>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Charity Is Giving Water","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how giving water as sadaqah became a lasting charity done for Umm Sa'd after her death."},"heading":{"title":"Hadith About Best Charity: Giving Water as Sadaqah","description":"This hadith about giving water shows a simple but deep act of sadaqah. Sa'd ibn Ubadah asked the Messenger of Allah صلى الله عليه وسلم what form of charity was best after his mother, Umm Sa'd, had died. The Prophet صلى الله عليه وسلم answered with one word: water. Sa'd then dug a well and dedicated it for Umm Sa'd. The message is clear from the text: giving water can be a strong form of charity, especially when it helps people meet a real need. The hadith also shows that a person may give sadaqah with the intention of benefit for a deceased loved one. It is a practical lesson in turning grief into service."},"teachings":["Giving water is mentioned here as a best form of sadaqah.","A person can dedicate charity for a deceased loved one.","Useful charity can take a practical form, such as digging a well."],"related_hadiths":[{"id":"1679","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1680","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1682","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Best Charity Is Giving Water","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how giving water as sadaqah became a lasting charity done for Umm Sa'd after her death."},"heading":{"title":"Hadith About Best Charity: Giving Water as Sadaqah","description":"This hadith about giving water shows a simple but deep act of sadaqah. Sa'd ibn Ubadah asked the Messenger of Allah صلى الله عليه وسلم what form of charity was best after his mother, Umm Sa'd, had died. The Prophet صلى الله عليه وسلم answered with one word: water. Sa'd then dug a well and dedicated it for Umm Sa'd. The message is clear from the text: giving water can be a strong form of charity, especially when it helps people meet a real need. The hadith also shows that a person may give sadaqah with the intention of benefit for a deceased loved one. It is a practical lesson in turning grief into service."},"teachings":["Giving water is mentioned here as a best form of sadaqah.","A person can dedicate charity for a deceased loved one.","Useful charity can take a practical form, such as digging a well."],"related_hadiths":[{"id":"1679","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1680","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1682","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E422" s="4" t="n"/>
@@ -10211,7 +10215,7 @@
       </c>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Feeding, Clothing and Giving Drink","description":"$book_name$ $hadith_number$ - $chapter_name$. See the reward mentioned for clothing, feeding, and giving drink to Muslims in need."},"heading":{"title":"Hadith About Feeding the Hungry and Giving Drink","description":"This hadith about feeding the hungry, clothing the needy, and giving drink to the thirsty speaks about care in very direct terms. The Prophet صلى الله عليه وسلم mentions three types of help: clothing a Muslim who lacks clothing, feeding a Muslim who is hungry, and giving drink to a Muslim who is thirsty. For each act, the hadith mentions a reward from Paradise. The focus is not on large public acts. It is on seeing a real need and meeting it. The search phrase “hadith about helping the needy” fits this narration well because the text joins faith with practical kindness. It teaches that sadaqah can be food, clothing, or water when someone needs them."},"teachings":["Helping people with basic needs is praised in this narration.","Food, clothing, and drink are all forms of charity in the text.","The hadith links kind action toward Muslims in need with reward from Allah."],"related_hadiths":[{"id":"1681","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1675","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1676","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Feeding, Clothing and Giving Drink","description":"$book_name$ $hadith_number$ - $chapter_name$. See the reward mentioned for clothing, feeding, and giving drink to Muslims in need."},"heading":{"title":"Hadith About Feeding the Hungry and Giving Drink","description":"This hadith about feeding the hungry, clothing the needy, and giving drink to the thirsty speaks about care in very direct terms. The Prophet صلى الله عليه وسلم mentions three types of help: clothing a Muslim who lacks clothing, feeding a Muslim who is hungry, and giving drink to a Muslim who is thirsty. For each act, the hadith mentions a reward from Paradise. The focus is not on large public acts. It is on seeing a real need and meeting it. The search phrase “hadith about helping the needy” fits this narration well because the text joins faith with practical kindness. It teaches that sadaqah can be food, clothing, or water when someone needs them."},"teachings":["Helping people with basic needs is praised in this narration.","Food, clothing, and drink are all forms of charity in the text.","The hadith links kind action toward Muslims in need with reward from Allah."],"related_hadiths":[{"id":"1681","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1675","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1676","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E423" s="4" t="n"/>
@@ -10234,7 +10238,7 @@
       </c>
       <c r="D424" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward of the Faithful Trustee","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how an honest trustee who delivers charity fully can share in the reward of sadaqah."},"heading":{"title":"Hadith About the Faithful Trustee and Sadaqah","description":"This hadith about the faithful trustee teaches that honesty in handling charity matters. The Prophet صلى الله عليه وسلم describes a trustee who gives exactly what he is commanded to give, gives it completely, gives it with a willing heart, and delivers it to the person named for it. Such a trustee is called one of the two who gives sadaqah. The main lesson is simple: even when a person is not the original owner of the wealth, his faithful delivery has value. The search phrase “trustee reward in Islam” fits this hadith because the text is about trust, full delivery, and good will. Charity work needs honesty, care, and a clean heart."},"teachings":["A trustee should deliver what he is told to give in full.","Good will matters when carrying out a charitable duty.","A faithful helper in charity can share in the reward of sadaqah."],"related_hadiths":[{"id":"1685","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1688","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1683","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reward of the Faithful Trustee","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how an honest trustee who delivers charity fully can share in the reward of sadaqah."},"heading":{"title":"Hadith About the Faithful Trustee and Sadaqah","description":"This hadith about the faithful trustee teaches that honesty in handling charity matters. The Prophet صلى الله عليه وسلم describes a trustee who gives exactly what he is commanded to give, gives it completely, gives it with a willing heart, and delivers it to the person named for it. Such a trustee is called one of the two who gives sadaqah. The main lesson is simple: even when a person is not the original owner of the wealth, his faithful delivery has value. The search phrase “trustee reward in Islam” fits this hadith because the text is about trust, full delivery, and good will. Charity work needs honesty, care, and a clean heart."},"teachings":["A trustee should deliver what he is told to give in full.","Good will matters when carrying out a charitable duty.","A faithful helper in charity can share in the reward of sadaqah."],"related_hadiths":[{"id":"1685","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1688","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1683","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E424" s="4" t="n"/>
@@ -10257,7 +10261,7 @@
       </c>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua After Wudu and Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Ablution done well, focused prayer, and the shahadah after wudu are linked here with great reward."},"heading":{"title":"Dua After Wudu: Shahadah, Focused Prayer, and Hope","description":"This Hadith is rich in meaning for anyone searching dua after wudu, shahadah after wudu, or two rak'ahs after ablution. Uqbah ibn Amir describes joining the Messenger of Allah صلى الله عليه وسلم while he was addressing people. He heard that whoever performs ablution well, then stands and offers two rak'ahs with heart and body turned toward them, is promised Paradise in the wording of the report. Umar then tells him of an earlier statement: whoever performs ablution well and then says the testimony of faith after finishing wudu will have the eight doors of Paradise opened for him. The Hadith keeps two connected lessons together: doing wudu well, praying with attention, and ending wudu with words of faith."},"teachings":["Performing wudu well is strongly emphasized.","The report links two rak'ahs after wudu with focused heart and body.","The shahadah after wudu is mentioned with the opening of the eight doors of Paradise."],"related_hadiths":[{"id":"234a","book_id":"2","label":"Sahih Muslim"},{"id":"159","book_id":"1","label":"Sahih Bukhari"},{"id":"244","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dua After Wudu and Two Rak'ahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Ablution done well, focused prayer, and the shahadah after wudu are linked here with great reward."},"heading":{"title":"Dua After Wudu: Shahadah, Focused Prayer, and Hope","description":"This Hadith is rich in meaning for anyone searching dua after wudu, shahadah after wudu, or two rak'ahs after ablution. Uqbah ibn Amir describes joining the Messenger of Allah صلى الله عليه وسلم while he was addressing people. He heard that whoever performs ablution well, then stands and offers two rak'ahs with heart and body turned toward them, is promised Paradise in the wording of the report. Umar then tells him of an earlier statement: whoever performs ablution well and then says the testimony of faith after finishing wudu will have the eight doors of Paradise opened for him. The Hadith keeps two connected lessons together: doing wudu well, praying with attention, and ending wudu with words of faith."},"teachings":["Performing wudu well is strongly emphasized.","The report links two rak'ahs after wudu with focused heart and body.","The shahadah after wudu is mentioned with the opening of the eight doors of Paradise."],"related_hadiths":[{"id":"234a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"159","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"244","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E425" s="4" t="n"/>
@@ -10280,7 +10284,7 @@
       </c>
       <c r="D426" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Raising Eyes and Saying Dua After Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This version mentions performing wudu well, raising the eyes toward the sky, and conveying the same meaning as the prior report."},"heading":{"title":"Dua After Wudu and Raising the Eyes Toward the Sky","description":"This Hadith reports the same meaning as the previous narration about what to say after finishing wudu. It does not mention tending camels, but it adds a detail after the words 'he performed ablution well': the person then raises his eyes toward the sky. The core topic is dua after wudu and the shahadah after ablution. Since the report says it conveys the same meaning as Mu'awiyah's narration, the focus remains on performing wudu well and saying the words of testimony after finishing. The Hadith is useful for searches like what to say after wudu, dua after ablution, and raising eyes to sky after wudu. The explanation should not add more than the narration gives."},"teachings":["This version omits the camel-tending part.","It adds raising the eyes toward the sky after performing wudu well.","It conveys the same meaning as the earlier report about words after wudu."],"related_hadiths":[{"id":"234a","book_id":"2","label":"Sahih Muslim"},{"id":"55","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"244","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Raising Eyes and Saying Dua After Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This version mentions performing wudu well, raising the eyes toward the sky, and conveying the same meaning as the prior report."},"heading":{"title":"Dua After Wudu and Raising the Eyes Toward the Sky","description":"This Hadith reports the same meaning as the previous narration about what to say after finishing wudu. It does not mention tending camels, but it adds a detail after the words 'he performed ablution well': the person then raises his eyes toward the sky. The core topic is dua after wudu and the shahadah after ablution. Since the report says it conveys the same meaning as Mu'awiyah's narration, the focus remains on performing wudu well and saying the words of testimony after finishing. The Hadith is useful for searches like what to say after wudu, dua after ablution, and raising eyes to sky after wudu. The explanation should not add more than the narration gives."},"teachings":["This version omits the camel-tending part.","It adds raising the eyes toward the sky after performing wudu well.","It conveys the same meaning as the earlier report about words after wudu."],"related_hadiths":[{"id":"234a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"55","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"244","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E426" s="4" t="n"/>
@@ -10303,7 +10307,7 @@
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lost Property and Honest Return","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how found wealth should be announced, recorded, and returned if its owner later appears."},"heading":{"title":"Hadith About Lost Property: Announce It and Protect the Owner’s Right","description":"This hadith about lost property teaches careful honesty when a person finds something that belongs to someone else. Ubayy ibn Ka'b found a purse containing one hundred dinars and asked the Prophet صلى الله عليه وسلم what to do. The instruction was to make the matter known for a year, and the narration mentions this being repeated. The finder was also told to remember the number, container, and tie of the purse. This shows that found wealth is not treated like ordinary personal property right away. The owner’s right stays important. If the owner comes, the item must be returned. If no owner is found after the required announcement, the finder may use it, while still knowing its signs. The core lesson is trust, record-keeping, and respect for people’s property."},"teachings":["A person who finds valuable property should not rush to use it without trying to find its owner.","The details of the lost item, such as number, container, and tie, should be remembered.","If the rightful owner appears, the item should be given back to him.","Asking knowledgeable people about unclear matters is a good step."],"related_hadiths":[{"id":"1704","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1709","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lost Property and Honest Return","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how found wealth should be announced, recorded, and returned if its owner later appears."},"heading":{"title":"Hadith About Lost Property: Announce It and Protect the Owner’s Right","description":"This hadith about lost property teaches careful honesty when a person finds something that belongs to someone else. Ubayy ibn Ka'b found a purse containing one hundred dinars and asked the Prophet صلى الله عليه وسلم what to do. The instruction was to make the matter known for a year, and the narration mentions this being repeated. The finder was also told to remember the number, container, and tie of the purse. This shows that found wealth is not treated like ordinary personal property right away. The owner’s right stays important. If the owner comes, the item must be returned. If no owner is found after the required announcement, the finder may use it, while still knowing its signs. The core lesson is trust, record-keeping, and respect for people’s property."},"teachings":["A person who finds valuable property should not rush to use it without trying to find its owner.","The details of the lost item, such as number, container, and tie, should be remembered.","If the rightful owner appears, the item should be given back to him.","Asking knowledgeable people about unclear matters is a good step."],"related_hadiths":[{"id":"1704","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1709","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E427" s="4" t="n"/>
@@ -10326,7 +10330,7 @@
       </c>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Identifying Found Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith teaches keeping clear details of found wealth before returning it to a claimant."},"heading":{"title":"Hadith About Identifying Lost Property Before Returning It","description":"This hadith about identifying lost property focuses on knowing the signs of the item. The narration mentions making the matter known for two or three years, and then remembering its number, container, and string. It also adds that if the owner comes and tells its number and string, it should be given to him. The important message is that found wealth should be handled with care. A person should not simply hand it to anyone who claims it without checking clear signs. At the same time, the finder must not hide it or treat it as his own from the start. This hadith gives a balanced lesson: protect the lost item, announce it, record its marks, and return it when the owner is known through proper signs."},"teachings":["The finder should learn and preserve the signs of the lost item.","Claims of ownership should be checked through clear details mentioned in the hadith.","Found property should be announced before being used.","The rightful owner should receive the item when his claim is recognized."],"related_hadiths":[{"id":"1701","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1708","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Identifying Found Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith teaches keeping clear details of found wealth before returning it to a claimant."},"heading":{"title":"Hadith About Identifying Lost Property Before Returning It","description":"This hadith about identifying lost property focuses on knowing the signs of the item. The narration mentions making the matter known for two or three years, and then remembering its number, container, and string. It also adds that if the owner comes and tells its number and string, it should be given to him. The important message is that found wealth should be handled with care. A person should not simply hand it to anyone who claims it without checking clear signs. At the same time, the finder must not hide it or treat it as his own from the start. This hadith gives a balanced lesson: protect the lost item, announce it, record its marks, and return it when the owner is known through proper signs."},"teachings":["The finder should learn and preserve the signs of the lost item.","Claims of ownership should be checked through clear details mentioned in the hadith.","Found property should be announced before being used.","The rightful owner should receive the item when his claim is recognized."],"related_hadiths":[{"id":"1701","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1708","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E428" s="4" t="n"/>
@@ -10349,7 +10353,7 @@
       </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lost Items and Stray Animals","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains found property, stray sheep, and why stray camels are treated differently."},"heading":{"title":"Hadith About Lost Property, Stray Sheep, and Stray Camels","description":"This hadith about lost property and stray animals gives clear guidance for different cases. For a found item, the Prophet صلى الله عليه وسلم said to make it known for a year, note its string and container, and then use it if no owner appears. If the owner later comes, it must be returned. About a stray sheep, he said it may be taken because it is either for the finder, for another person, or for the wolf. This shows the sheep is in danger if left alone. But when asked about stray camels, the Prophet صلى الله عليه وسلم became angry and said the camel has its feet and its stomach for drink until its owner comes. The lesson is that not every lost animal is treated the same. The condition and safety of the animal matter."},"teachings":["A found item should be announced for a year before use.","The details of the item, such as its string and container, should be recorded.","A stray sheep may be taken because it may be exposed to harm.","A stray camel should not be taken when it can survive until its owner comes."],"related_hadiths":[{"id":"1705","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1718","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lost Items and Stray Animals","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains found property, stray sheep, and why stray camels are treated differently."},"heading":{"title":"Hadith About Lost Property, Stray Sheep, and Stray Camels","description":"This hadith about lost property and stray animals gives clear guidance for different cases. For a found item, the Prophet صلى الله عليه وسلم said to make it known for a year, note its string and container, and then use it if no owner appears. If the owner later comes, it must be returned. About a stray sheep, he said it may be taken because it is either for the finder, for another person, or for the wolf. This shows the sheep is in danger if left alone. But when asked about stray camels, the Prophet صلى الله عليه وسلم became angry and said the camel has its feet and its stomach for drink until its owner comes. The lesson is that not every lost animal is treated the same. The condition and safety of the animal matter."},"teachings":["A found item should be announced for a year before use.","The details of the item, such as its string and container, should be recorded.","A stray sheep may be taken because it may be exposed to harm.","A stray camel should not be taken when it can survive until its owner comes."],"related_hadiths":[{"id":"1705","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1718","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E429" s="4" t="n"/>
@@ -10372,7 +10376,7 @@
       </c>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stray Camels and Found Items","description":"$book_name$ $hadith_number$ - $chapter_name$. This report explains found items and notes how camels can reach water and eat trees."},"heading":{"title":"Hadith About Stray Camels and Found Property in Islam","description":"This hadith about stray camels and found property supports the meaning of the earlier narration. It says that a found item should be made known for a year. If its owner comes, it should be given back. If the owner does not come, the finder may use it. The narration also adds a point about stray camels: they have their stomachs, can go down to water, and eat trees. This explains why they are not treated like weak or exposed animals. A camel can move, drink, and feed itself until its owner finds it. The hadith gives a simple rule of fairness. Found property needs announcement, and stray animals are judged by their situation. A stronger animal is not to be taken like one that may be harmed quickly."},"teachings":["Found property should be announced for a year.","If the owner comes, the item should be returned.","Stray camels are left because they can reach water and eat trees.","Different lost animals may need different treatment."],"related_hadiths":[{"id":"1704","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1718","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1720","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stray Camels and Found Items","description":"$book_name$ $hadith_number$ - $chapter_name$. This report explains found items and notes how camels can reach water and eat trees."},"heading":{"title":"Hadith About Stray Camels and Found Property in Islam","description":"This hadith about stray camels and found property supports the meaning of the earlier narration. It says that a found item should be made known for a year. If its owner comes, it should be given back. If the owner does not come, the finder may use it. The narration also adds a point about stray camels: they have their stomachs, can go down to water, and eat trees. This explains why they are not treated like weak or exposed animals. A camel can move, drink, and feed itself until its owner finds it. The hadith gives a simple rule of fairness. Found property needs announcement, and stray animals are judged by their situation. A stronger animal is not to be taken like one that may be harmed quickly."},"teachings":["Found property should be announced for a year.","If the owner comes, the item should be returned.","Stray camels are left because they can reach water and eat trees.","Different lost animals may need different treatment."],"related_hadiths":[{"id":"1704","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1718","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1720","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E430" s="4" t="n"/>
@@ -10395,7 +10399,7 @@
       </c>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Returning a Found Item","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches announcing a found item and returning it whenever its seeker appears."},"heading":{"title":"Hadith About Returning Lost Property to Its Seeker","description":"This hadith about returning lost property gives a short and clear process. The Prophet صلى الله عليه وسلم was asked about a find. He said to make it known for a year. If the seeker comes, the item should be delivered to him. If no seeker comes, the finder should note its container and string, then may use it. But even after using it, the duty is not forgotten. If the seeker comes later, it must still be delivered to him. This makes the teaching very practical. The finder is allowed to benefit after the announcement period, but the owner’s right is still respected. The hadith is a strong reminder that found property in Islam is not a free gain without responsibility."},"teachings":["A found item should be announced for a year.","If the seeker appears, the item should be returned.","The container and string should be noted before use.","Using the item later does not cancel the duty to return it if the owner appears."],"related_hadiths":[{"id":"1701","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1704","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1707","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Returning a Found Item","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches announcing a found item and returning it whenever its seeker appears."},"heading":{"title":"Hadith About Returning Lost Property to Its Seeker","description":"This hadith about returning lost property gives a short and clear process. The Prophet صلى الله عليه وسلم was asked about a find. He said to make it known for a year. If the seeker comes, the item should be delivered to him. If no seeker comes, the finder should note its container and string, then may use it. But even after using it, the duty is not forgotten. If the seeker comes later, it must still be delivered to him. This makes the teaching very practical. The finder is allowed to benefit after the announcement period, but the owner’s right is still respected. The hadith is a strong reminder that found property in Islam is not a free gain without responsibility."},"teachings":["A found item should be announced for a year.","If the seeker appears, the item should be returned.","The container and string should be noted before use.","Using the item later does not cancel the duty to return it if the owner appears."],"related_hadiths":[{"id":"1701","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1704","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1707","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E431" s="4" t="n"/>
@@ -10418,7 +10422,7 @@
       </c>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mixing Found Property with Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith explains announcing found property, then keeping it ready for its owner."},"heading":{"title":"Hadith About Found Property and Returning It After Use","description":"This hadith about found property explains that a person should announce a lost item for a year. If the owner comes, it must be handed over. If the owner does not come, the finder should know its string and container and may then place it with his own property. Yet this permission does not remove the owner’s right. The hadith ends by repeating that if the owner later comes, it should be delivered to him. This is a clear lesson in trust. Found property may enter someone’s use only after the proper steps. The finder should not hide it, ignore its signs, or forget the person who lost it. The hadith teaches care, patience, and readiness to return what belongs to another person."},"teachings":["Found property should be announced for a full year.","The finder should remember the item’s string and container.","The item may be kept with one’s property after the required announcement.","If the owner later comes, the item should still be returned."],"related_hadiths":[{"id":"1704","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1709","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mixing Found Property with Wealth","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith explains announcing found property, then keeping it ready for its owner."},"heading":{"title":"Hadith About Found Property and Returning It After Use","description":"This hadith about found property explains that a person should announce a lost item for a year. If the owner comes, it must be handed over. If the owner does not come, the finder should know its string and container and may then place it with his own property. Yet this permission does not remove the owner’s right. The hadith ends by repeating that if the owner later comes, it should be delivered to him. This is a clear lesson in trust. Found property may enter someone’s use only after the proper steps. The finder should not hide it, ignore its signs, or forget the person who lost it. The hadith teaches care, patience, and readiness to return what belongs to another person."},"teachings":["Found property should be announced for a full year.","The finder should remember the item’s string and container.","The item may be kept with one’s property after the required announcement.","If the owner later comes, the item should still be returned."],"related_hadiths":[{"id":"1704","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1709","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E432" s="4" t="n"/>
@@ -10441,7 +10445,7 @@
       </c>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witnesses for Found Property","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith teaches witnesses, openness, and returning a found item to its owner."},"heading":{"title":"Hadith About Witnesses When Finding Lost Property","description":"This hadith about witnesses for lost property gives a strong lesson in honesty. The Prophet صلى الله عليه وسلم said that whoever finds something should call one or two trustworthy people as witnesses. The finder should not conceal it or cover it up. If the owner is found, the item must be returned. If the owner is not found, the hadith describes it as Allah’s property which He gives to whom He wills. The main message is open and clean behavior. A found item should not become a secret. Calling witnesses protects the finder from blame and helps protect the owner’s right. The hadith also warns against hiding what was found. It teaches that lost property in Islam is linked to trust, public honesty, and returning rights when the owner is known."},"teachings":["The finder should call one or two trustworthy witnesses.","A found item should not be concealed or hidden.","If the owner is found, the property should be returned.","Honesty protects both the finder and the owner."],"related_hadiths":[{"id":"1701","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1707","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Witnesses for Found Property","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith teaches witnesses, openness, and returning a found item to its owner."},"heading":{"title":"Hadith About Witnesses When Finding Lost Property","description":"This hadith about witnesses for lost property gives a strong lesson in honesty. The Prophet صلى الله عليه وسلم said that whoever finds something should call one or two trustworthy people as witnesses. The finder should not conceal it or cover it up. If the owner is found, the item must be returned. If the owner is not found, the hadith describes it as Allah’s property which He gives to whom He wills. The main message is open and clean behavior. A found item should not become a secret. Calling witnesses protects the finder from blame and helps protect the owner’s right. The hadith also warns against hiding what was found. It teaches that lost property in Islam is linked to trust, public honesty, and returning rights when the owner is known."},"teachings":["The finder should call one or two trustworthy witnesses.","A found item should not be concealed or hidden.","If the owner is found, the property should be returned.","Honesty protects both the finder and the owner."],"related_hadiths":[{"id":"1701","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1707","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E433" s="4" t="n"/>
@@ -10464,7 +10468,7 @@
       </c>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Wudu for Many Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas says the Prophet صلى الله عليه وسلم performed ablution for each prayer, while the companions prayed many prayers with one ablution."},"heading":{"title":"One Wudu for Multiple Prayers: What Anas Reported","description":"This Hadith answers a common question: can you pray multiple prayers with one wudu? Abu Asad ibn Amr asked Anas ibn Malik about ablution. Anas replied that the Prophet صلى الله عليه وسلم performed ablution for each prayer, while they offered many prayers with the same ablution. The report gives two pieces of information without turning them into a long debate. First, it describes the Prophet's صلى الله عليه وسلم regular practice as performing wudu for each prayer. Second, it says the companions prayed more than one prayer with one ablution. The wording is balanced, so the explanation should stay balanced. It is useful for searches like same wudu for multiple prayers, wudu for every salah, and Anas wudu hadith."},"teachings":["The Prophet صلى الله عليه وسلم is described as performing wudu for each prayer.","The companions are described as praying many prayers with one wudu.","The report gives a practical answer without adding extra conditions."],"related_hadiths":[{"id":"214","book_id":"1","label":"Sahih Bukhari"},{"id":"58","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"60","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Wudu for Many Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas says the Prophet صلى الله عليه وسلم performed ablution for each prayer, while the companions prayed many prayers with one ablution."},"heading":{"title":"One Wudu for Multiple Prayers: What Anas Reported","description":"This Hadith answers a common question: can you pray multiple prayers with one wudu? Abu Asad ibn Amr asked Anas ibn Malik about ablution. Anas replied that the Prophet صلى الله عليه وسلم performed ablution for each prayer, while they offered many prayers with the same ablution. The report gives two pieces of information without turning them into a long debate. First, it describes the Prophet's صلى الله عليه وسلم regular practice as performing wudu for each prayer. Second, it says the companions prayed more than one prayer with one ablution. The wording is balanced, so the explanation should stay balanced. It is useful for searches like same wudu for multiple prayers, wudu for every salah, and Anas wudu hadith."},"teachings":["The Prophet صلى الله عليه وسلم is described as performing wudu for each prayer.","The companions are described as praying many prayers with one wudu.","The report gives a practical answer without adding extra conditions."],"related_hadiths":[{"id":"214","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"58","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"60","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E434" s="4" t="n"/>
@@ -10487,7 +10491,7 @@
       </c>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fruit, Finds, and Public Property Rules","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains need, taking fruit, lost items, and treasure with clear limits."},"heading":{"title":"Hadith About Hanging Fruit, Lost Property, and Hidden Treasure","description":"This hadith about property rights covers several cases in one report. The Prophet صلى الله عليه وسلم was asked about hanging fruit. He said that a needy person who eats some without carrying a supply away in his garment is not blamed. But the one who carries it away faces payment and punishment. If the fruit has been stored in the drying place and its value reaches the price of a shield, theft has a stronger legal result mentioned in the hadith. The report also repeats the rules of stray camels and sheep, and then explains found property. If a lost item is found on a frequented road or in a large town, it should be announced for a year. If no owner comes, it belongs to the finder. If it is in ancient waste land or is hidden treasure, one fifth is due."},"teachings":["A needy person eating some hanging fruit is treated differently from someone carrying it away.","Found property in a road or town should be announced for a year.","If the owner comes, the found item should be returned.","Hidden treasure mentioned in the hadith is subject to one fifth."],"related_hadiths":[{"id":"1704","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1712","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fruit, Finds, and Public Property Rules","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith explains need, taking fruit, lost items, and treasure with clear limits."},"heading":{"title":"Hadith About Hanging Fruit, Lost Property, and Hidden Treasure","description":"This hadith about property rights covers several cases in one report. The Prophet صلى الله عليه وسلم was asked about hanging fruit. He said that a needy person who eats some without carrying a supply away in his garment is not blamed. But the one who carries it away faces payment and punishment. If the fruit has been stored in the drying place and its value reaches the price of a shield, theft has a stronger legal result mentioned in the hadith. The report also repeats the rules of stray camels and sheep, and then explains found property. If a lost item is found on a frequented road or in a large town, it should be announced for a year. If no owner comes, it belongs to the finder. If it is in ancient waste land or is hidden treasure, one fifth is due."},"teachings":["A needy person eating some hanging fruit is treated differently from someone carrying it away.","Found property in a road or town should be announced for a year.","If the owner comes, the found item should be returned.","Hidden treasure mentioned in the hadith is subject to one fifth."],"related_hadiths":[{"id":"1704","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1712","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E435" s="4" t="n"/>
@@ -10510,7 +10514,7 @@
       </c>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Taking a Stray Sheep","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration adds that a stray sheep may be gathered and protected."},"heading":{"title":"Hadith About Taking a Stray Sheep in Islam","description":"This hadith about a stray sheep is a short supporting narration of the earlier report. It adds that regarding the stray sheep, the wording was “gather it.” The teaching is simple but important. A stray sheep is not like a strong camel that can reach water and eat on its own. A sheep may be exposed to danger, loss, or attack. So the instruction here points to gathering it rather than leaving it unattended. The hadith is closely tied to the rules of lost property and stray animals. It shows that Islam teaches care for property and care for animals, while also respecting the right of the owner. The finder’s action should not be based on greed, but on protection and proper handling."},"teachings":["A stray sheep may be gathered instead of being left exposed.","The finder should act with care, not with greed.","The owner’s right remains connected to the animal.","Different animals may have different treatment based on their condition."],"related_hadiths":[{"id":"1704","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1712","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1713","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Taking a Stray Sheep","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration adds that a stray sheep may be gathered and protected."},"heading":{"title":"Hadith About Taking a Stray Sheep in Islam","description":"This hadith about a stray sheep is a short supporting narration of the earlier report. It adds that regarding the stray sheep, the wording was “gather it.” The teaching is simple but important. A stray sheep is not like a strong camel that can reach water and eat on its own. A sheep may be exposed to danger, loss, or attack. So the instruction here points to gathering it rather than leaving it unattended. The hadith is closely tied to the rules of lost property and stray animals. It shows that Islam teaches care for property and care for animals, while also respecting the right of the owner. The finder’s action should not be based on greed, but on protection and proper handling."},"teachings":["A stray sheep may be gathered instead of being left exposed.","The finder should act with care, not with greed.","The owner’s right remains connected to the animal.","Different animals may have different treatment based on their condition."],"related_hadiths":[{"id":"1704","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1712","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1713","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E436" s="4" t="n"/>
@@ -10533,7 +10537,7 @@
       </c>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Keep a Stray Sheep Until Claimed","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says to gather a stray sheep until its seeker comes for it."},"heading":{"title":"Hadith About Keeping a Stray Sheep Until Its Owner Comes","description":"This hadith about keeping a stray sheep gives a careful form of the instruction. It says to gather the sheep until its seeker comes to it. This wording helps show the purpose of taking it. The sheep is gathered for care and protection, not to erase the right of the owner. The hadith also fits with other reports in the same topic, where a stray sheep is described as being at risk if left alone. Here, the focus is on holding it until the person seeking it arrives. This makes the teaching easy to understand: when a vulnerable animal is found, the finder may protect it, but should stay ready to return it. The hadith is a practical lesson in trust and responsibility."},"teachings":["A stray sheep may be gathered for protection.","The animal should be kept until its seeker comes.","The finder should not treat the animal as ownerless without care.","Protecting lost property includes being ready to return it."],"related_hadiths":[{"id":"1704","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1711","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1712","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Keep a Stray Sheep Until Claimed","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith says to gather a stray sheep until its seeker comes for it."},"heading":{"title":"Hadith About Keeping a Stray Sheep Until Its Owner Comes","description":"This hadith about keeping a stray sheep gives a careful form of the instruction. It says to gather the sheep until its seeker comes to it. This wording helps show the purpose of taking it. The sheep is gathered for care and protection, not to erase the right of the owner. The hadith also fits with other reports in the same topic, where a stray sheep is described as being at risk if left alone. Here, the focus is on holding it until the person seeking it arrives. This makes the teaching easy to understand: when a vulnerable animal is found, the finder may protect it, but should stay ready to return it. The hadith is a practical lesson in trust and responsibility."},"teachings":["A stray sheep may be gathered for protection.","The animal should be kept until its seeker comes.","The finder should not treat the animal as ownerless without care.","Protecting lost property includes being ready to return it."],"related_hadiths":[{"id":"1704","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1711","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1712","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E437" s="4" t="n"/>
@@ -10556,7 +10560,7 @@
       </c>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Returning a Found Dinar","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows a found dinar being returned when its owner came asking for it."},"heading":{"title":"Hadith About a Found Dinar and Returning It to the Owner","description":"This hadith about a found dinar shows the duty to return lost wealth when the owner appears. Ali ibn Abi Talib found a dinar and brought it to Fatimah. She asked the Messenger of Allah صلى الله عليه وسلم about it, and he said it was Allah’s provision. Food was bought from it, and the Prophet صلى الله عليه وسلم, Ali, and Fatimah ate from that food. Later, a woman came crying out about the dinar. At that point, the Prophet صلى الله عليه وسلم said, “Pay the dinar, Ali.” The hadith is simple and direct. Even when a found item has been used, the owner’s claim matters when she comes asking for it. The teaching is not to ignore the owner once known. It points to fairness, return of rights, and honest response when lost wealth is claimed."},"teachings":["A found dinar was returned when its owner came asking for it.","The owner’s claim was not ignored after the item had been used.","Ali was instructed to pay the dinar back.","Lost wealth should be handled with fairness when the owner appears."],"related_hadiths":[{"id":"1715","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1716","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1709","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Returning a Found Dinar","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith shows a found dinar being returned when its owner came asking for it."},"heading":{"title":"Hadith About a Found Dinar and Returning It to the Owner","description":"This hadith about a found dinar shows the duty to return lost wealth when the owner appears. Ali ibn Abi Talib found a dinar and brought it to Fatimah. She asked the Messenger of Allah صلى الله عليه وسلم about it, and he said it was Allah’s provision. Food was bought from it, and the Prophet صلى الله عليه وسلم, Ali, and Fatimah ate from that food. Later, a woman came crying out about the dinar. At that point, the Prophet صلى الله عليه وسلم said, “Pay the dinar, Ali.” The hadith is simple and direct. Even when a found item has been used, the owner’s claim matters when she comes asking for it. The teaching is not to ignore the owner once known. It points to fairness, return of rights, and honest response when lost wealth is claimed."},"teachings":["A found dinar was returned when its owner came asking for it.","The owner’s claim was not ignored after the item had been used.","Ali was instructed to pay the dinar back.","Lost wealth should be handled with fairness when the owner appears."],"related_hadiths":[{"id":"1715","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1716","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1709","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E438" s="4" t="n"/>
@@ -10579,7 +10583,7 @@
       </c>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali and the Found Dinar","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports Ali finding a dinar and using it in a measured way."},"heading":{"title":"Hadith Report About Ali Finding a Dinar","description":"This report about Ali finding a dinar gives a brief account of found money being used in a specific situation. Ali found a dinar and bought flour with it. The flour seller recognized him and returned the dinar to him. Ali then took it, cut two qirat from it, and bought meat with it. The hadith text is short, so the explanation should stay close to what it says. It shows a found dinar, a purchase of flour, the seller returning the coin, and then part of it being used for meat. Since the text does not give a full legal discussion on its own, we should not add extra rulings beyond the report. The main searchable topic is the found dinar narration involving Ali, flour, and meat."},"teachings":["The narration reports Ali finding a dinar and buying flour with it.","The seller recognized him and returned the dinar.","Ali later used part of the dinar to buy meat.","Short reports should be explained without adding claims beyond the text."],"related_hadiths":[{"id":"1714","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1716","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1701","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali and the Found Dinar","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports Ali finding a dinar and using it in a measured way."},"heading":{"title":"Hadith Report About Ali Finding a Dinar","description":"This report about Ali finding a dinar gives a brief account of found money being used in a specific situation. Ali found a dinar and bought flour with it. The flour seller recognized him and returned the dinar to him. Ali then took it, cut two qirat from it, and bought meat with it. The hadith text is short, so the explanation should stay close to what it says. It shows a found dinar, a purchase of flour, the seller returning the coin, and then part of it being used for meat. Since the text does not give a full legal discussion on its own, we should not add extra rulings beyond the report. The main searchable topic is the found dinar narration involving Ali, flour, and meat."},"teachings":["The narration reports Ali finding a dinar and buying flour with it.","The seller recognized him and returned the dinar.","Ali later used part of the dinar to buy meat.","Short reports should be explained without adding claims beyond the text."],"related_hadiths":[{"id":"1714","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1716","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1701","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E439" s="4" t="n"/>
@@ -10602,7 +10606,7 @@
       </c>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Found Dinar and Its Owner","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows food bought with a found dinar and the coin returned to its owner."},"heading":{"title":"Hadith About the Found Dinar, Hunger, and Returning the Owner’s Right","description":"This hadith about the found dinar tells a longer story. Hasan and Husain were crying from hunger. Ali went out and found a dinar in the market. Flour was bought, then the dinar came back to him, and meat was obtained through a pledge. Fatimah explained the matter to the Prophet صلى الله عليه وسلم and asked if they could eat. He said, “Eat in the name of Allah,” so they ate. While they were eating, a boy called out looking for the dinar. The Prophet صلى الله عليه وسلم asked him, and the boy said he had lost it in the market. The Prophet صلى الله عليه وسلم then instructed Ali to get the dinar from the butcher, with the dirham due upon the Prophet صلى الله عليه وسلم, and the dinar was handed to the boy. The clear lesson is that when the owner appeared, the dinar was returned."},"teachings":["Ali found a dinar in the market during a time of hunger.","Fatimah openly told the Prophet صلى الله عليه وسلم the matter before eating.","When the boy claimed the dinar, he was asked about it.","The dinar was returned to the boy after his loss was known."],"related_hadiths":[{"id":"1714","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1715","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1709","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Found Dinar and Its Owner","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows food bought with a found dinar and the coin returned to its owner."},"heading":{"title":"Hadith About the Found Dinar, Hunger, and Returning the Owner’s Right","description":"This hadith about the found dinar tells a longer story. Hasan and Husain were crying from hunger. Ali went out and found a dinar in the market. Flour was bought, then the dinar came back to him, and meat was obtained through a pledge. Fatimah explained the matter to the Prophet صلى الله عليه وسلم and asked if they could eat. He said, “Eat in the name of Allah,” so they ate. While they were eating, a boy called out looking for the dinar. The Prophet صلى الله عليه وسلم asked him, and the boy said he had lost it in the market. The Prophet صلى الله عليه وسلم then instructed Ali to get the dinar from the butcher, with the dirham due upon the Prophet صلى الله عليه وسلم, and the dinar was handed to the boy. The clear lesson is that when the owner appeared, the dinar was returned."},"teachings":["Ali found a dinar in the market during a time of hunger.","Fatimah openly told the Prophet صلى الله عليه وسلم the matter before eating.","When the boy claimed the dinar, he was asked about it.","The dinar was returned to the boy after his loss was known."],"related_hadiths":[{"id":"1714","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1715","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1709","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E440" s="4" t="n"/>
@@ -10625,7 +10629,7 @@
       </c>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Small Found Items","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions permission to benefit from simple found items like a stick or rope."},"heading":{"title":"Hadith About Benefiting from Small Found Items","description":"This hadith about small found items mentions a stick, a rope, a whip, and similar things. Jabir ibn Abdullah said the Messenger of Allah صلى الله عليه وسلم gave license for a person who picked up such items to benefit from them. The wording is limited to simple items of that type, so the explanation should not stretch it to all found wealth. Other reports in this same topic speak about announcing valuable finds, but this narration focuses on items like a stick, rope, or whip. The likely main search term is hadith about small found items in Islam. The practical message is that not every found object has the same treatment. Small, ordinary items mentioned in the text may be used by the person who picks them up."},"teachings":["The hadith mentions permission to benefit from a stick, rope, whip, and similar items.","The wording is about simple found objects, not every type of wealth.","A person may benefit from the small items named in the narration.","Different kinds of found property may have different treatment."],"related_hadiths":[{"id":"1701","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1704","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Small Found Items","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions permission to benefit from simple found items like a stick or rope."},"heading":{"title":"Hadith About Benefiting from Small Found Items","description":"This hadith about small found items mentions a stick, a rope, a whip, and similar things. Jabir ibn Abdullah said the Messenger of Allah صلى الله عليه وسلم gave license for a person who picked up such items to benefit from them. The wording is limited to simple items of that type, so the explanation should not stretch it to all found wealth. Other reports in this same topic speak about announcing valuable finds, but this narration focuses on items like a stick, rope, or whip. The likely main search term is hadith about small found items in Islam. The practical message is that not every found object has the same treatment. Small, ordinary items mentioned in the text may be used by the person who picks them up."},"teachings":["The hadith mentions permission to benefit from a stick, rope, whip, and similar items.","The wording is about simple found objects, not every type of wealth.","A person may benefit from the small items named in the narration.","Different kinds of found property may have different treatment."],"related_hadiths":[{"id":"1701","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1704","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1706","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E441" s="4" t="n"/>
@@ -10648,7 +10652,7 @@
       </c>
       <c r="D442" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hiding a Stray Camel","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith warns that hiding a stray camel brings a fine and similar compensation."},"heading":{"title":"Hadith About Hiding a Stray Camel and Paying Compensation","description":"This hadith about hiding a stray camel is short and serious. The Prophet صلى الله عليه وسلم said that whoever hides a stray camel shall pay a fine and a like compensation with it. The main message is that a stray camel should not be concealed. This connects closely with other narrations where stray camels are not to be taken like stray sheep, because camels have the ability to move, drink, and feed until their owner comes. Here, the focus is on the wrong act of hiding the animal. Concealing a stray animal can harm the owner and block the animal from being found. The hadith teaches that dealing with stray animals must be honest and open. A camel that strays is not a secret gain for the finder."},"teachings":["A stray camel should not be hidden.","The hadith mentions a fine and similar compensation for hiding it.","Concealing a stray animal harms the owner’s right.","Handling stray animals requires honesty."],"related_hadiths":[{"id":"1704","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1705","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1720","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hiding a Stray Camel","description":"$book_name$ $hadith_number$ - $chapter_name$. The hadith warns that hiding a stray camel brings a fine and similar compensation."},"heading":{"title":"Hadith About Hiding a Stray Camel and Paying Compensation","description":"This hadith about hiding a stray camel is short and serious. The Prophet صلى الله عليه وسلم said that whoever hides a stray camel shall pay a fine and a like compensation with it. The main message is that a stray camel should not be concealed. This connects closely with other narrations where stray camels are not to be taken like stray sheep, because camels have the ability to move, drink, and feed until their owner comes. Here, the focus is on the wrong act of hiding the animal. Concealing a stray animal can harm the owner and block the animal from being found. The hadith teaches that dealing with stray animals must be honest and open. A camel that strays is not a secret gain for the finder."},"teachings":["A stray camel should not be hidden.","The hadith mentions a fine and similar compensation for hiding it.","Concealing a stray animal harms the owner’s right.","Handling stray animals requires honesty."],"related_hadiths":[{"id":"1704","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1705","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1720","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E442" s="4" t="n"/>
@@ -10671,7 +10675,7 @@
       </c>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Five Prayers With One Ablution","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed five prayers with one ablution on the day of the conquest of Mecca and said he did it deliberately."},"heading":{"title":"Five Prayers With One Wudu on the Day of Conquest","description":"This Hadith is a direct report about praying five prayers with one wudu. Buraidah narrates from his father that the Messenger of Allah صلى الله عليه وسلم performed five prayers with the same ablution on the occasion of the capture of Mecca, and he wiped over his socks. Umar noticed that this was something he had not seen the Prophet صلى الله عليه وسلم do before. The Prophet صلى الله عليه وسلم replied that he did it deliberately. The wording matters because it shows the action was intentional in that event, not accidental. For people searching can I pray multiple prayers with one wudu, five prayers one ablution hadith, or wiping over socks hadith, this narration gives a clear event-based example."},"teachings":["The Prophet صلى الله عليه وسلم prayed five prayers with one ablution on that occasion.","Umar noticed the action because it was different from what he had seen before.","The Prophet صلى الله عليه وسلم said he did it deliberately."],"related_hadiths":[{"id":"277","book_id":"2","label":"Sahih Muslim"},{"id":"61","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"214","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Five Prayers With One Ablution","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed five prayers with one ablution on the day of the conquest of Mecca and said he did it deliberately."},"heading":{"title":"Five Prayers With One Wudu on the Day of Conquest","description":"This Hadith is a direct report about praying five prayers with one wudu. Buraidah narrates from his father that the Messenger of Allah صلى الله عليه وسلم performed five prayers with the same ablution on the occasion of the capture of Mecca, and he wiped over his socks. Umar noticed that this was something he had not seen the Prophet صلى الله عليه وسلم do before. The Prophet صلى الله عليه وسلم replied that he did it deliberately. The wording matters because it shows the action was intentional in that event, not accidental. For people searching can I pray multiple prayers with one wudu, five prayers one ablution hadith, or wiping over socks hadith, this narration gives a clear event-based example."},"teachings":["The Prophet صلى الله عليه وسلم prayed five prayers with one ablution on that occasion.","Umar noticed the action because it was different from what he had seen before.","The Prophet صلى الله عليه وسلم said he did it deliberately."],"related_hadiths":[{"id":"277","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"61","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"214","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E443" s="4" t="n"/>
@@ -10694,7 +10698,7 @@
       </c>
       <c r="D444" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Mix a Stray Animal","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against mixing a stray animal with one’s own animals."},"heading":{"title":"Hadith About Mixing a Stray Animal with Your Animals","description":"This hadith about mixing a stray animal gives a strong warning. Al-Mundhir ibn Jarir said he was with Jarir when the shepherd brought cows. Among them was a cow that was not one of their cows. The shepherd said it had mixed with the herd and they did not know whose it was. Jarir told him to take it out. He then quoted the Messenger of Allah صلى الله عليه وسلم: no one mixes a stray animal with his animals except a person who strays from the right path. The teaching is clear. A stray animal should not be absorbed into one’s own herd as if it belongs there. Mixing it can hide it from its owner and make return harder. The hadith calls for separation, honesty, and respect for the owner’s property."},"teachings":["A stray animal should not be mixed into one’s own herd.","Jarir ordered the unknown cow to be taken out.","Mixing a stray animal can hide it from its owner.","The hadith strongly links this behavior with straying from the right path."],"related_hadiths":[{"id":"1704","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1718","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1709","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Mix a Stray Animal","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against mixing a stray animal with one’s own animals."},"heading":{"title":"Hadith About Mixing a Stray Animal with Your Animals","description":"This hadith about mixing a stray animal gives a strong warning. Al-Mundhir ibn Jarir said he was with Jarir when the shepherd brought cows. Among them was a cow that was not one of their cows. The shepherd said it had mixed with the herd and they did not know whose it was. Jarir told him to take it out. He then quoted the Messenger of Allah صلى الله عليه وسلم: no one mixes a stray animal with his animals except a person who strays from the right path. The teaching is clear. A stray animal should not be absorbed into one’s own herd as if it belongs there. Mixing it can hide it from its owner and make return harder. The hadith calls for separation, honesty, and respect for the owner’s property."},"teachings":["A stray animal should not be mixed into one’s own herd.","Jarir ordered the unknown cow to be taken out.","Mixing a stray animal can hide it from its owner.","The hadith strongly links this behavior with straying from the right path."],"related_hadiths":[{"id":"1704","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1718","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1709","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E444" s="4" t="n"/>
@@ -10717,7 +10721,7 @@
       </c>
       <c r="D445" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Guidance for the Prophet’s Wives","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions the Prophet’s words to his wives during the Farewell Pilgrimage."},"heading":{"title":"Hadith About the Prophet’s Wives During Hajj","description":"This Hadith about the Prophet’s wives during Hajj records a short statement from the Farewell Pilgrimage. Abu Waqid al-Laythi heard the Messenger of Allah صلى الله عليه وسلم speak to his wives and say, “This,” then after that to remain at home. The wording in the translation explains the phrase as sticking to the surface of the mats, meaning staying at home. The core topic is women and Hajj, especially the special instruction given to the wives of the Prophet صلى الله عليه وسلم in this text. A careful reading should not turn this into a broad statement beyond what is given here. The Hadith focuses on the Prophet’s direct words to his own wives during that specific pilgrimage."},"teachings":["The Hadith records a special instruction given to the Prophet’s wives.","The statement was made during the Farewell Pilgrimage.","The text connects this instruction with remaining at home afterward.","The wording should be read carefully without adding extra details."],"related_hadiths":[{"id":"1723","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1726","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1728","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Guidance for the Prophet’s Wives","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith mentions the Prophet’s words to his wives during the Farewell Pilgrimage."},"heading":{"title":"Hadith About the Prophet’s Wives During Hajj","description":"This Hadith about the Prophet’s wives during Hajj records a short statement from the Farewell Pilgrimage. Abu Waqid al-Laythi heard the Messenger of Allah صلى الله عليه وسلم speak to his wives and say, “This,” then after that to remain at home. The wording in the translation explains the phrase as sticking to the surface of the mats, meaning staying at home. The core topic is women and Hajj, especially the special instruction given to the wives of the Prophet صلى الله عليه وسلم in this text. A careful reading should not turn this into a broad statement beyond what is given here. The Hadith focuses on the Prophet’s direct words to his own wives during that specific pilgrimage."},"teachings":["The Hadith records a special instruction given to the Prophet’s wives.","The statement was made during the Farewell Pilgrimage.","The text connects this instruction with remaining at home afterward.","The wording should be read carefully without adding extra details."],"related_hadiths":[{"id":"1723","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1726","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1728","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E445" s="4" t="n"/>
@@ -10740,7 +10744,7 @@
       </c>
       <c r="D446" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Perform Ablution Well","description":"$book_name$ $hadith_number$ - $chapter_name$. A man left a tiny part of his foot unwashed, so the Prophet صلى الله عليه وسلم told him to go back and perform wudu well."},"heading":{"title":"Complete Wudu Properly: Do Not Leave Dry Spots","description":"This Hadith is about complete wudu and paying attention to the feet. Anas reports that a person came to the Messenger of Allah صلى الله عليه وسلم after performing ablution, but he had left a small part on his foot equal to the space of a nail. The Prophet صلى الله عليه وسلم told him to go back and perform his ablution well. The text is clear and practical. Wudu is not only about doing the actions quickly; the water must reach the parts being washed. The report does not mention a long warning or a separate story, so the explanation should stay with the point: a small missed spot mattered enough that the man was told to repeat the wudu properly. This is a key search topic for dry spot in wudu hadith."},"teachings":["A small unwashed place on the foot was noticed.","The Prophet صلى الله عليه وسلم told the man to go back and improve his wudu.","The Hadith teaches care and completeness in ablution."],"related_hadiths":[{"id":"243","book_id":"2","label":"Sahih Muslim"},{"id":"165","book_id":"1","label":"Sahih Bukhari"},{"id":"242c","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Perform Ablution Well","description":"$book_name$ $hadith_number$ - $chapter_name$. A man left a tiny part of his foot unwashed, so the Prophet صلى الله عليه وسلم told him to go back and perform wudu well."},"heading":{"title":"Complete Wudu Properly: Do Not Leave Dry Spots","description":"This Hadith is about complete wudu and paying attention to the feet. Anas reports that a person came to the Messenger of Allah صلى الله عليه وسلم after performing ablution, but he had left a small part on his foot equal to the space of a nail. The Prophet صلى الله عليه وسلم told him to go back and perform his ablution well. The text is clear and practical. Wudu is not only about doing the actions quickly; the water must reach the parts being washed. The report does not mention a long warning or a separate story, so the explanation should stay with the point: a small missed spot mattered enough that the man was told to repeat the wudu properly. This is a key search topic for dry spot in wudu hadith."},"teachings":["A small unwashed place on the foot was noticed.","The Prophet صلى الله عليه وسلم told the man to go back and improve his wudu.","The Hadith teaches care and completeness in ablution."],"related_hadiths":[{"id":"243","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"165","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"242c","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E446" s="4" t="n"/>
@@ -10763,7 +10767,7 @@
       </c>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Leave Prayer for Doubt Alone","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught that doubt about passing wind should not make a person leave prayer unless there is sound or smell."},"heading":{"title":"Doubt About Breaking Wudu: Sound or Smell","description":"This Hadith addresses a common worry: doubt about breaking wudu during prayer. A person complained to the Prophet صلى الله عليه وسلم that he felt as if something had happened to him that would invalidate ablution. The Prophet صلى الله عليه وسلم said he should not cease praying unless he hears a sound or perceives a smell. The wording gives a clear way to deal with uncertainty in this case. It does not tell the person to leave prayer for every feeling or thought. It sets a simple sign: sound or smell. For people searching does doubt break wudu, passing wind doubt in salah, or hadith hears sound or smells odor, this narration is direct and calming while staying tied to the text."},"teachings":["A mere feeling or doubt is not treated like certainty in this report.","The Prophet صلى الله عليه وسلم mentioned sound or smell as signs in this case.","The instruction was given about a person experiencing doubt during prayer."],"related_hadiths":[{"id":"177","book_id":"1","label":"Sahih Bukhari"},{"id":"361","book_id":"2","label":"Sahih Muslim"},{"id":"75","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Leave Prayer for Doubt Alone","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught that doubt about passing wind should not make a person leave prayer unless there is sound or smell."},"heading":{"title":"Doubt About Breaking Wudu: Sound or Smell","description":"This Hadith addresses a common worry: doubt about breaking wudu during prayer. A person complained to the Prophet صلى الله عليه وسلم that he felt as if something had happened to him that would invalidate ablution. The Prophet صلى الله عليه وسلم said he should not cease praying unless he hears a sound or perceives a smell. The wording gives a clear way to deal with uncertainty in this case. It does not tell the person to leave prayer for every feeling or thought. It sets a simple sign: sound or smell. For people searching does doubt break wudu, passing wind doubt in salah, or hadith hears sound or smells odor, this narration is direct and calming while staying tied to the text."},"teachings":["A mere feeling or doubt is not treated like certainty in this report.","The Prophet صلى الله عليه وسلم mentioned sound or smell as signs in this case.","The instruction was given about a person experiencing doubt during prayer."],"related_hadiths":[{"id":"177","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"361","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"75","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E447" s="4" t="n"/>
@@ -10786,7 +10790,7 @@
       </c>
       <c r="D448" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | What to Do if a Sacrificial Camel Becomes Fatigued","description":"$book_name$ $hadith_number$ - $chapter_name$. See what the Prophet صلى الله عليه وسلم taught when a sacrificial camel becomes too weak on the way to the Ka'bah."},"heading":{"title":"Hadith About a Fatigued Sacrificial Camel in Hajj","description":"This Hadith about a fatigued sacrificial camel explains what should be done if a Hajj offering cannot continue. Najiyah al-Aslami was sent with sacrificial camels as an offering to the Ka'bah. The Messenger of Allah (صلى الله عليه وسلم) told him that if any one of them became fatigued, he should slaughter it, dip its shoes in its blood, and leave it for the people to eat. The focus is on handling the offering properly when it can no longer travel. The animal is not ignored, and the food is not wasted. The narration also points to clear marking, because the shoes were dipped in blood and left with it. For searches about hady rules in Hajj, this Hadith gives a direct instruction from the Prophet (صلى الله عليه وسلم)."},"teachings":["A sacrificial camel that becomes too weak should be dealt with in a clear and proper way.","The meat was to be left for the people to eat, not wasted.","The instruction included marking the animal by dipping its shoes in its blood.","The Hadith teaches care for offerings that cannot complete the journey."],"related_hadiths":[{"id":"1763","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1761","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1769","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | What to Do if a Sacrificial Camel Becomes Fatigued","description":"$book_name$ $hadith_number$ - $chapter_name$. See what the Prophet صلى الله عليه وسلم taught when a sacrificial camel becomes too weak on the way to the Ka'bah."},"heading":{"title":"Hadith About a Fatigued Sacrificial Camel in Hajj","description":"This Hadith about a fatigued sacrificial camel explains what should be done if a Hajj offering cannot continue. Najiyah al-Aslami was sent with sacrificial camels as an offering to the Ka'bah. The Messenger of Allah (صلى الله عليه وسلم) told him that if any one of them became fatigued, he should slaughter it, dip its shoes in its blood, and leave it for the people to eat. The focus is on handling the offering properly when it can no longer travel. The animal is not ignored, and the food is not wasted. The narration also points to clear marking, because the shoes were dipped in blood and left with it. For searches about hady rules in Hajj, this Hadith gives a direct instruction from the Prophet (صلى الله عليه وسلم)."},"teachings":["A sacrificial camel that becomes too weak should be dealt with in a clear and proper way.","The meat was to be left for the people to eat, not wasted.","The instruction included marking the animal by dipping its shoes in its blood.","The Hadith teaches care for offerings that cannot complete the journey."],"related_hadiths":[{"id":"1763","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1761","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1769","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E448" s="4" t="n"/>
@@ -10809,7 +10813,7 @@
       </c>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet صلى الله عليه وسلم Sacrificed Camels by His Hand","description":"$book_name$ $hadith_number$ - $chapter_name$. Read how the Prophet صلى الله عليه وسلم sacrificed thirty camels himself and then asked Ali to complete the rest."},"heading":{"title":"Hadith About the Prophet Sacrificing Camels by His Own Hand","description":"This Hadith about the Prophet sacrificing camels shows a direct scene from the Hajj sacrifice. Ali ibn Abu Talib narrated that when the Messenger of Allah (صلى الله عليه وسلم) sacrificed his camels, he sacrificed thirty with his own hand. Then he commanded Ali, and Ali sacrificed the rest. The report is brief, but it clearly shows action, leadership, and trust. The Prophet (صلى الله عليه وسلم) personally carried out part of the sacrifice, and then assigned the remaining work to Ali. For readers looking for a Hadith about Qurbani camels or Hajj sacrifice, this narration is focused on who performed the slaughter and how Ali was involved. The text does not add more rulings, so the lesson remains simple and close to the wording."},"teachings":["The Prophet (صلى الله عليه وسلم) personally sacrificed thirty camels with his own hand.","Ali was commanded to sacrifice the remaining camels.","The narration shows delegation after direct personal action.","The text keeps the focus on the act of sacrifice itself."],"related_hadiths":[{"id":"1766","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1765","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1767","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet صلى الله عليه وسلم Sacrificed Camels by His Hand","description":"$book_name$ $hadith_number$ - $chapter_name$. Read how the Prophet صلى الله عليه وسلم sacrificed thirty camels himself and then asked Ali to complete the rest."},"heading":{"title":"Hadith About the Prophet Sacrificing Camels by His Own Hand","description":"This Hadith about the Prophet sacrificing camels shows a direct scene from the Hajj sacrifice. Ali ibn Abu Talib narrated that when the Messenger of Allah (صلى الله عليه وسلم) sacrificed his camels, he sacrificed thirty with his own hand. Then he commanded Ali, and Ali sacrificed the rest. The report is brief, but it clearly shows action, leadership, and trust. The Prophet (صلى الله عليه وسلم) personally carried out part of the sacrifice, and then assigned the remaining work to Ali. For readers looking for a Hadith about Qurbani camels or Hajj sacrifice, this narration is focused on who performed the slaughter and how Ali was involved. The text does not add more rulings, so the lesson remains simple and close to the wording."},"teachings":["The Prophet (صلى الله عليه وسلم) personally sacrificed thirty camels with his own hand.","Ali was commanded to sacrifice the remaining camels.","The narration shows delegation after direct personal action.","The text keeps the focus on the act of sacrifice itself."],"related_hadiths":[{"id":"1766","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1765","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1767","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E449" s="4" t="n"/>
@@ -10832,7 +10836,7 @@
       </c>
       <c r="D450" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali Helped the Prophet صلى الله عليه وسلم Sacrifice Camels","description":"$book_name$ $hadith_number$ - $chapter_name$. See how the Prophet صلى الله عليه وسلم and Ali handled the lance together while sacrificing camels at the Farewell Hajj."},"heading":{"title":"Hadith About Ali Helping the Prophet Sacrifice Camels","description":"This Hadith about sacrificing camels at the Farewell Pilgrimage gives a close picture of the act. Arfah ibn al-Harith said he was present with the Messenger of Allah (صلى الله عليه وسلم) during the Farewell Hajj. When the sacrificial camels were brought, the Prophet (صلى الله عليه وسلم) called for Abul Hasan, meaning Ali. Ali was told to hold the lower end of the lance, while the Messenger of Allah (صلى الله عليه وسلم) held the upper end. Then he pierced the camels with it. After finishing, he rode his mule and mounted Ali behind him. The narration is about cooperation in the sacrifice and the specific way Ali assisted. It does not add extra rulings beyond what is stated."},"teachings":["Ali assisted the Messenger of Allah (صلى الله عليه وسلم) during the camel sacrifice.","The Prophet (صلى الله عليه وسلم) held the upper end of the lance and Ali held the lower end.","The event took place during the Farewell Pilgrimage.","After the sacrifice, the Prophet (صلى الله عليه وسلم) rode his mule and seated Ali behind him."],"related_hadiths":[{"id":"1764","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1767","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1768","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ali Helped the Prophet صلى الله عليه وسلم Sacrifice Camels","description":"$book_name$ $hadith_number$ - $chapter_name$. See how the Prophet صلى الله عليه وسلم and Ali handled the lance together while sacrificing camels at the Farewell Hajj."},"heading":{"title":"Hadith About Ali Helping the Prophet Sacrifice Camels","description":"This Hadith about sacrificing camels at the Farewell Pilgrimage gives a close picture of the act. Arfah ibn al-Harith said he was present with the Messenger of Allah (صلى الله عليه وسلم) during the Farewell Hajj. When the sacrificial camels were brought, the Prophet (صلى الله عليه وسلم) called for Abul Hasan, meaning Ali. Ali was told to hold the lower end of the lance, while the Messenger of Allah (صلى الله عليه وسلم) held the upper end. Then he pierced the camels with it. After finishing, he rode his mule and mounted Ali behind him. The narration is about cooperation in the sacrifice and the specific way Ali assisted. It does not add extra rulings beyond what is stated."},"teachings":["Ali assisted the Messenger of Allah (صلى الله عليه وسلم) during the camel sacrifice.","The Prophet (صلى الله عليه وسلم) held the upper end of the lance and Ali held the lower end.","The event took place during the Farewell Pilgrimage.","After the sacrifice, the Prophet (صلى الله عليه وسلم) rode his mule and seated Ali behind him."],"related_hadiths":[{"id":"1764","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1767","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1768","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E450" s="4" t="n"/>
@@ -10855,7 +10859,7 @@
       </c>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing Camel Sacrifice in the Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the reported practice of sacrificing a camel while standing with its left leg tied."},"heading":{"title":"Hadith About Sacrificing a Camel While Standing","description":"This Hadith about sacrificing a camel while standing describes the practice of the Prophet (صلى الله عليه وسلم) and his companions. Abd al-Rahman bin Thabit reported that they used to sacrifice the camel with its left leg tied, while it remained standing on the rest of its legs. The wording is short, but it gives a clear image of the method mentioned in the narration. For people searching for the Sunnah way to sacrifice a camel, this report points to standing the camel and tying the left leg. The explanation should not go beyond the text by adding details not mentioned here. Its main point is the form in which the camel was kept at the time of sacrifice."},"teachings":["The narration describes sacrificing the camel while it is standing.","The left leg was tied according to the wording of the report.","The camel remained on the rest of its legs.","The practice is linked to the Prophet (صلى الله عليه وسلم) and his companions in the text."],"related_hadiths":[{"id":"1768","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1766","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1764","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Standing Camel Sacrifice in the Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the reported practice of sacrificing a camel while standing with its left leg tied."},"heading":{"title":"Hadith About Sacrificing a Camel While Standing","description":"This Hadith about sacrificing a camel while standing describes the practice of the Prophet (صلى الله عليه وسلم) and his companions. Abd al-Rahman bin Thabit reported that they used to sacrifice the camel with its left leg tied, while it remained standing on the rest of its legs. The wording is short, but it gives a clear image of the method mentioned in the narration. For people searching for the Sunnah way to sacrifice a camel, this report points to standing the camel and tying the left leg. The explanation should not go beyond the text by adding details not mentioned here. Its main point is the form in which the camel was kept at the time of sacrifice."},"teachings":["The narration describes sacrificing the camel while it is standing.","The left leg was tied according to the wording of the report.","The camel remained on the rest of its legs.","The practice is linked to the Prophet (صلى الله عليه وسلم) and his companions in the text."],"related_hadiths":[{"id":"1768","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1766","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1764","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E451" s="4" t="n"/>
@@ -10878,7 +10882,7 @@
       </c>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Distributing Skins and Saddle Cloths as Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how Ali was told to distribute skins and saddle cloths and not pay the butcher from them."},"heading":{"title":"Hadith About Giving Sacrificial Camel Skins as Sadaqah","description":"This Hadith about sacrificial camel skins explains how the Prophet (صلى الله عليه وسلم) instructed Ali after the sacrifice. Ali said the Messenger of Allah (صلى الله عليه وسلم) commanded him to take charge of the sacrificial camels and to distribute their skins and saddle cloths as sadaqah. He also commanded him not to give any part of them to the butcher as payment. Ali said they used to give the butcher his wage from their own wealth. The message is clear and focused: parts connected to the sacrificial camels were distributed as charity, and the worker's payment was kept separate. For people searching for hadith about paying the butcher from Qurbani meat or skins, this narration gives a direct answer from the text."},"teachings":["Ali was placed in charge of the sacrificial camels.","The skins and saddle cloths were to be distributed as sadaqah.","The butcher was not to be paid from those items.","The butcher's wage was given separately from their own wealth."],"related_hadiths":[{"id":"1762","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1763","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1765","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Distributing Skins and Saddle Cloths as Charity","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how Ali was told to distribute skins and saddle cloths and not pay the butcher from them."},"heading":{"title":"Hadith About Giving Sacrificial Camel Skins as Sadaqah","description":"This Hadith about sacrificial camel skins explains how the Prophet (صلى الله عليه وسلم) instructed Ali after the sacrifice. Ali said the Messenger of Allah (صلى الله عليه وسلم) commanded him to take charge of the sacrificial camels and to distribute their skins and saddle cloths as sadaqah. He also commanded him not to give any part of them to the butcher as payment. Ali said they used to give the butcher his wage from their own wealth. The message is clear and focused: parts connected to the sacrificial camels were distributed as charity, and the worker's payment was kept separate. For people searching for hadith about paying the butcher from Qurbani meat or skins, this narration gives a direct answer from the text."},"teachings":["Ali was placed in charge of the sacrificial camels.","The skins and saddle cloths were to be distributed as sadaqah.","The butcher was not to be paid from those items.","The butcher's wage was given separately from their own wealth."],"related_hadiths":[{"id":"1762","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1763","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1765","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E452" s="4" t="n"/>
@@ -10901,7 +10905,7 @@
       </c>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Talbiyah from the Mosque of Dhul-Hulayfah","description":"$book_name$ $hadith_number$ - $chapter_name$. Read Ibn Umar's statement that the Prophet صلى الله عليه وسلم raised Talbiyah from the mosque at Dhul-Hulayfah."},"heading":{"title":"Hadith About Talbiyah from Dhul-Hulayfah Mosque","description":"This Hadith about Talbiyah from Dhul-Hulayfah records a strong statement from Ibn Umar. He said that al-Bayda was being used to ascribe something false to the Messenger of Allah (صلى الله عليه وسلم). According to his report, the Prophet (صلى الله عليه وسلم) did not raise his voice in Talbiyah except from the mosque, meaning the mosque of Dhul-Hulayfah. The core topic is Talbiyah timing. The narration is short, but it matters because it shows Ibn Umar's care in linking a practice only to what he knew from the Prophet (صلى الله عليه وسلم). For readers searching for the Talbiyah at Dhul-Hulayfah hadith, this text gives one clear report: the starting place named here is the mosque, not al-Bayda."},"teachings":["Ibn Umar connected the Prophet's Talbiyah to the mosque of Dhul-Hulayfah.","He rejected attributing the act to al-Bayda in this report.","The narration shows care in reporting the Prophet's practice accurately.","The main point is the stated location of raising Talbiyah."],"related_hadiths":[{"id":"1770","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1773","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1774","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Talbiyah from the Mosque of Dhul-Hulayfah","description":"$book_name$ $hadith_number$ - $chapter_name$. Read Ibn Umar's statement that the Prophet صلى الله عليه وسلم raised Talbiyah from the mosque at Dhul-Hulayfah."},"heading":{"title":"Hadith About Talbiyah from Dhul-Hulayfah Mosque","description":"This Hadith about Talbiyah from Dhul-Hulayfah records a strong statement from Ibn Umar. He said that al-Bayda was being used to ascribe something false to the Messenger of Allah (صلى الله عليه وسلم). According to his report, the Prophet (صلى الله عليه وسلم) did not raise his voice in Talbiyah except from the mosque, meaning the mosque of Dhul-Hulayfah. The core topic is Talbiyah timing. The narration is short, but it matters because it shows Ibn Umar's care in linking a practice only to what he knew from the Prophet (صلى الله عليه وسلم). For readers searching for the Talbiyah at Dhul-Hulayfah hadith, this text gives one clear report: the starting place named here is the mosque, not al-Bayda."},"teachings":["Ibn Umar connected the Prophet's Talbiyah to the mosque of Dhul-Hulayfah.","He rejected attributing the act to al-Bayda in this report.","The narration shows care in reporting the Prophet's practice accurately.","The main point is the stated location of raising Talbiyah."],"related_hadiths":[{"id":"1770","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1773","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1774","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E453" s="4" t="n"/>
@@ -10924,7 +10928,7 @@
       </c>
       <c r="D454" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Umar Following What He Saw from the Prophet صلى الله عليه وسلم","description":"$book_name$ $hadith_number$ - $chapter_name$. See how Ibn Umar explained his Hajj practices by pointing to what he saw from the Prophet صلى الله عليه وسلم."},"heading":{"title":"Hadith About Ibn Umar Following the Prophet's Practice","description":"This Hadith about following the Prophet's practice shows how Ibn Umar explained four actions. Ubayd ibn Jurayj asked why he touched only the two Yamani corners, wore tanned leather shoes, used yellow dye, and delayed raising Talbiyah until the eighth of Dhul-Hijjah. Ibn Umar answered each point by saying he saw the Messenger of Allah (صلى الله عليه وسلم) do it or did not see him do otherwise. He saw the Prophet (صلى الله عليه وسلم) touch only the two Yamani corners, wear tanned leather shoes and make ablution in them, use yellow dye, and raise Talbiyah when his she-camel stood with him on its back. The narration is a clear lesson in loving and following what one has learned from the Prophet (صلى الله عليه وسلم)."},"teachings":["Ibn Umar based his actions on what he saw from the Messenger of Allah (صلى الله عليه وسلم).","He touched only the two Yamani corners because that is what he had seen.","He liked wearing tanned leather shoes and using yellow dye due to the Prophet's example.","He linked Talbiyah to the moment the mount stood with the Prophet (صلى الله عليه وسلم)."],"related_hadiths":[{"id":"1770","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1773","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1771","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Umar Following What He Saw from the Prophet صلى الله عليه وسلم","description":"$book_name$ $hadith_number$ - $chapter_name$. See how Ibn Umar explained his Hajj practices by pointing to what he saw from the Prophet صلى الله عليه وسلم."},"heading":{"title":"Hadith About Ibn Umar Following the Prophet's Practice","description":"This Hadith about following the Prophet's practice shows how Ibn Umar explained four actions. Ubayd ibn Jurayj asked why he touched only the two Yamani corners, wore tanned leather shoes, used yellow dye, and delayed raising Talbiyah until the eighth of Dhul-Hijjah. Ibn Umar answered each point by saying he saw the Messenger of Allah (صلى الله عليه وسلم) do it or did not see him do otherwise. He saw the Prophet (صلى الله عليه وسلم) touch only the two Yamani corners, wear tanned leather shoes and make ablution in them, use yellow dye, and raise Talbiyah when his she-camel stood with him on its back. The narration is a clear lesson in loving and following what one has learned from the Prophet (صلى الله عليه وسلم)."},"teachings":["Ibn Umar based his actions on what he saw from the Messenger of Allah (صلى الله عليه وسلم).","He touched only the two Yamani corners because that is what he had seen.","He liked wearing tanned leather shoes and using yellow dye due to the Prophet's example.","He linked Talbiyah to the moment the mount stood with the Prophet (صلى الله عليه وسلم)."],"related_hadiths":[{"id":"1770","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1773","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1771","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E454" s="4" t="n"/>
@@ -10947,7 +10951,7 @@
       </c>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Talbiyah After Mounting at Dhul-Hulayfah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn Anas's report that the Prophet صلى الله عليه وسلم raised Talbiyah after mounting at Dhul-Hulayfah."},"heading":{"title":"Hadith About Talbiyah After Mounting the Ride","description":"This Hadith about Talbiyah after mounting gives Anas's report of the Prophet's journey. The Messenger of Allah (صلى الله عليه وسلم) prayed four rak'ahs at Madinah and then prayed two rak'ahs of the afternoon prayer at Dhul-Hulayfah. He spent the night there until morning. When he mounted his ride and it stood up with him, he raised his voice in Talbiyah. The report is useful for anyone searching for when the Prophet said Talbiyah in Hajj because it gives a simple order of events: prayer in Madinah, prayer at Dhul-Hulayfah, staying overnight, then Talbiyah after the mount stood. The text does not speak about every possible case. It records what Anas saw or reported in this journey."},"teachings":["The Prophet (صلى الله عليه وسلم) prayed four rak'ahs in Madinah and two at Dhul-Hulayfah.","He stayed at Dhul-Hulayfah until morning.","Anas reported Talbiyah after the Prophet's ride stood with him.","The narration gives a clear sequence of events in the Hajj journey."],"related_hadiths":[{"id":"1772","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1774","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1770","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Talbiyah After Mounting at Dhul-Hulayfah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn Anas's report that the Prophet صلى الله عليه وسلم raised Talbiyah after mounting at Dhul-Hulayfah."},"heading":{"title":"Hadith About Talbiyah After Mounting the Ride","description":"This Hadith about Talbiyah after mounting gives Anas's report of the Prophet's journey. The Messenger of Allah (صلى الله عليه وسلم) prayed four rak'ahs at Madinah and then prayed two rak'ahs of the afternoon prayer at Dhul-Hulayfah. He spent the night there until morning. When he mounted his ride and it stood up with him, he raised his voice in Talbiyah. The report is useful for anyone searching for when the Prophet said Talbiyah in Hajj because it gives a simple order of events: prayer in Madinah, prayer at Dhul-Hulayfah, staying overnight, then Talbiyah after the mount stood. The text does not speak about every possible case. It records what Anas saw or reported in this journey."},"teachings":["The Prophet (صلى الله عليه وسلم) prayed four rak'ahs in Madinah and two at Dhul-Hulayfah.","He stayed at Dhul-Hulayfah until morning.","Anas reported Talbiyah after the Prophet's ride stood with him.","The narration gives a clear sequence of events in the Hajj journey."],"related_hadiths":[{"id":"1772","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1774","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1770","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E455" s="4" t="n"/>
@@ -10970,7 +10974,7 @@
       </c>
       <c r="D456" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Talbiyah at the Hill of al-Bayda","description":"$book_name$ $hadith_number$ - $chapter_name$. Read Anas ibn Malik's report that the Prophet صلى الله عليه وسلم raised Talbiyah when reaching al-Bayda."},"heading":{"title":"Hadith About Talbiyah at al-Bayda in Hajj","description":"This Hadith about Talbiyah at al-Bayda gives another report from Anas ibn Malik. He narrated that the Prophet (صلى الله عليه وسلم) offered the noon prayer and then rode his mount. When he came to the hill of al-Bayda, he raised his voice in Talbiyah. The core point is the place and moment mentioned in this narration. It does not deny other reports in this same collection, but this text itself names al-Bayda after the noon prayer and mounting the ride. For people searching for the al-Bayda Talbiyah hadith, the wording is simple: prayer came first, then riding, then raising the voice in Talbiyah at the hill. Staying close to the text keeps the meaning clear."},"teachings":["Anas reported that the Prophet (صلى الله عليه وسلم) raised Talbiyah at al-Bayda.","The noon prayer is mentioned before mounting the ride.","The narration focuses on a specific place and moment.","The report should be read as the wording states, without adding extra details."],"related_hadiths":[{"id":"1775","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1773","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1770","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Talbiyah at the Hill of al-Bayda","description":"$book_name$ $hadith_number$ - $chapter_name$. Read Anas ibn Malik's report that the Prophet صلى الله عليه وسلم raised Talbiyah when reaching al-Bayda."},"heading":{"title":"Hadith About Talbiyah at al-Bayda in Hajj","description":"This Hadith about Talbiyah at al-Bayda gives another report from Anas ibn Malik. He narrated that the Prophet (صلى الله عليه وسلم) offered the noon prayer and then rode his mount. When he came to the hill of al-Bayda, he raised his voice in Talbiyah. The core point is the place and moment mentioned in this narration. It does not deny other reports in this same collection, but this text itself names al-Bayda after the noon prayer and mounting the ride. For people searching for the al-Bayda Talbiyah hadith, the wording is simple: prayer came first, then riding, then raising the voice in Talbiyah at the hill. Staying close to the text keeps the meaning clear."},"teachings":["Anas reported that the Prophet (صلى الله عليه وسلم) raised Talbiyah at al-Bayda.","The noon prayer is mentioned before mounting the ride.","The narration focuses on a specific place and moment.","The report should be read as the wording states, without adding extra details."],"related_hadiths":[{"id":"1775","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1773","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1770","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E456" s="4" t="n"/>
@@ -10993,7 +10997,7 @@
       </c>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Talbiyah Timing on Different Routes","description":"$book_name$ $hadith_number$ - $chapter_name$. See Sa'd ibn Abi Waqqas's report about Talbiyah timing on the routes of al-Far' and Uhud."},"heading":{"title":"Hadith About Talbiyah Timing on Different Hajj Routes","description":"This Hadith about Talbiyah timing on different routes reports the words of Sa'd ibn Abi Waqqas. He said that when the Prophet of Allah (صلى الله عليه وسلم) traveled by the way of al-Far, he raised Talbiyah when his mount stood up with him on its back. But when he traveled by the way of Uhud, he raised Talbiyah when he ascended the hill of al-Bayda. The main lesson is that the narration links the timing to the route mentioned. It does not give a broad rule in every setting. It records two route-based moments: the mount standing on one route and reaching al-Bayda on another. For readers asking about when to say Talbiyah, this report helps explain why different moments are reported."},"teachings":["The report mentions two different routes: al-Far and Uhud.","On the route of al-Far, Talbiyah was raised when the mount stood.","On the route of Uhud, Talbiyah was raised at the hill of al-Bayda.","The narration helps explain route-based reports about Talbiyah timing."],"related_hadiths":[{"id":"1774","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1773","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1770","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Talbiyah Timing on Different Routes","description":"$book_name$ $hadith_number$ - $chapter_name$. See Sa'd ibn Abi Waqqas's report about Talbiyah timing on the routes of al-Far' and Uhud."},"heading":{"title":"Hadith About Talbiyah Timing on Different Hajj Routes","description":"This Hadith about Talbiyah timing on different routes reports the words of Sa'd ibn Abi Waqqas. He said that when the Prophet of Allah (صلى الله عليه وسلم) traveled by the way of al-Far, he raised Talbiyah when his mount stood up with him on its back. But when he traveled by the way of Uhud, he raised Talbiyah when he ascended the hill of al-Bayda. The main lesson is that the narration links the timing to the route mentioned. It does not give a broad rule in every setting. It records two route-based moments: the mount standing on one route and reaching al-Bayda on another. For readers asking about when to say Talbiyah, this report helps explain why different moments are reported."},"teachings":["The report mentions two different routes: al-Far and Uhud.","On the route of al-Far, Talbiyah was raised when the mount stood.","On the route of Uhud, Talbiyah was raised at the hill of al-Bayda.","The narration helps explain route-based reports about Talbiyah timing."],"related_hadiths":[{"id":"1774","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1773","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1770","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E457" s="4" t="n"/>
@@ -11016,7 +11020,7 @@
       </c>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Making a Condition in Hajj Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the supplication taught to Duba'ah when she wanted to make a condition for Hajj."},"heading":{"title":"Hadith About Making a Condition in Ihram for Hajj","description":"This Hadith about making a condition in Ihram records the question of Duba'ah bint al-Zubair. She came to the Messenger of Allah (صلى الله عليه وسلم) and said that she wanted to perform Hajj and asked whether she could make a condition. He said yes. When she asked what to say, he taught her to say the Talbiyah and add that her place of leaving Ihram would be where Allah restrained her. The report is direct and personal. It does not list every reason a person may be stopped, but it clearly gives the wording taught to her. For searches like condition in Ihram Hadith or Duba'ah Hajj condition, this narration is the key text in this batch."},"teachings":["Duba'ah asked before acting, and the Prophet (صلى الله عليه وسلم) answered her question.","The Prophet (صلى الله عليه وسلم) allowed her to make a condition for Hajj.","He taught her specific wording connected to Talbiyah and being restrained.","The narration shows a simple way to state a condition in Ihram as given in the text."],"related_hadiths":[{"id":"1778","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1779","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1780","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Making a Condition in Hajj Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the supplication taught to Duba'ah when she wanted to make a condition for Hajj."},"heading":{"title":"Hadith About Making a Condition in Ihram for Hajj","description":"This Hadith about making a condition in Ihram records the question of Duba'ah bint al-Zubair. She came to the Messenger of Allah (صلى الله عليه وسلم) and said that she wanted to perform Hajj and asked whether she could make a condition. He said yes. When she asked what to say, he taught her to say the Talbiyah and add that her place of leaving Ihram would be where Allah restrained her. The report is direct and personal. It does not list every reason a person may be stopped, but it clearly gives the wording taught to her. For searches like condition in Ihram Hadith or Duba'ah Hajj condition, this narration is the key text in this batch."},"teachings":["Duba'ah asked before acting, and the Prophet (صلى الله عليه وسلم) answered her question.","The Prophet (صلى الله عليه وسلم) allowed her to make a condition for Hajj.","He taught her specific wording connected to Talbiyah and being restrained.","The narration shows a simple way to state a condition in Ihram as given in the text."],"related_hadiths":[{"id":"1778","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1779","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1780","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E458" s="4" t="n"/>
@@ -11039,7 +11043,7 @@
       </c>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Kissing and Ablution Report","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports the Prophet صلى الله عليه وسلم kissed her and did not perform ablution, while Abu Dawud notes the report is mursal."},"heading":{"title":"Does Kissing Break Wudu? A Report with Abu Dawud's Note","description":"This Hadith is often searched under does kissing break wudu or Prophet kissed Aishah and did not make wudu. The translation reports from Aishah, the Mother of the Believers, that the Prophet صلى الله عليه وسلم kissed her and did not perform ablution. The important part is that Abu Dawud adds a clear note: this tradition is mursal, meaning the Companion link is missing in this chain, and Ibrahim at-Taimi did not hear anything from Aishah. So the content mentions an action, but the Hadith itself also records a chain concern. A careful explanation should include both, without turning the report into a broad ruling. The text teaches us to read the narration and the scholar's note together."},"teachings":["The report says the Prophet صلى الله عليه وسلم kissed Aishah and did not perform ablution.","Abu Dawud states that this tradition is mursal.","The chain note is part of the provided Hadith and should not be ignored."],"related_hadiths":[{"id":"86","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"502","book_id":"6","label":"Sunan Ibn Majah"},{"id":"503","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Kissing and Ablution Report","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports the Prophet صلى الله عليه وسلم kissed her and did not perform ablution, while Abu Dawud notes the report is mursal."},"heading":{"title":"Does Kissing Break Wudu? A Report with Abu Dawud's Note","description":"This Hadith is often searched under does kissing break wudu or Prophet kissed Aishah and did not make wudu. The translation reports from Aishah, the Mother of the Believers, that the Prophet صلى الله عليه وسلم kissed her and did not perform ablution. The important part is that Abu Dawud adds a clear note: this tradition is mursal, meaning the Companion link is missing in this chain, and Ibrahim at-Taimi did not hear anything from Aishah. So the content mentions an action, but the Hadith itself also records a chain concern. A careful explanation should include both, without turning the report into a broad ruling. The text teaches us to read the narration and the scholar's note together."},"teachings":["The report says the Prophet صلى الله عليه وسلم kissed Aishah and did not perform ablution.","Abu Dawud states that this tradition is mursal.","The chain note is part of the provided Hadith and should not be ignored."],"related_hadiths":[{"id":"86","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"502","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"503","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E459" s="4" t="n"/>
@@ -11062,7 +11066,7 @@
       </c>
       <c r="D460" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Leaving Ihram After Umrah","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the added wording that whoever raised Talbiyah for Umrah came out of Ihram after performing it."},"heading":{"title":"Hadith About Leaving Ihram After Performing Umrah","description":"This Hadith about leaving Ihram after Umrah is a related version of the previous report through another chain. It adds a clear point: the one who raises his voice in Talbiyah for Umrah, and wears Ihram for it, should put off Ihram after performing Umrah. The narration is short, so the meaning should not be stretched. It speaks about the person whose intention and Talbiyah were for Umrah. After the Umrah is done, that person leaves Ihram. For readers searching for when to remove Ihram after Umrah, this report gives the direct wording found in the translation. It is also closely tied to the Farewell Hajj reports about people entering Ihram for different rites."},"teachings":["This version adds wording about the person who entered Ihram for Umrah.","A person who raised Talbiyah for Umrah put off Ihram after performing Umrah.","The report is tied to the earlier narration through another chain.","The main point is the timing of leaving Ihram after Umrah."],"related_hadiths":[{"id":"1779","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1778","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1777","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Leaving Ihram After Umrah","description":"$book_name$ $hadith_number$ - $chapter_name$. Read the added wording that whoever raised Talbiyah for Umrah came out of Ihram after performing it."},"heading":{"title":"Hadith About Leaving Ihram After Performing Umrah","description":"This Hadith about leaving Ihram after Umrah is a related version of the previous report through another chain. It adds a clear point: the one who raises his voice in Talbiyah for Umrah, and wears Ihram for it, should put off Ihram after performing Umrah. The narration is short, so the meaning should not be stretched. It speaks about the person whose intention and Talbiyah were for Umrah. After the Umrah is done, that person leaves Ihram. For readers searching for when to remove Ihram after Umrah, this report gives the direct wording found in the translation. It is also closely tied to the Farewell Hajj reports about people entering Ihram for different rites."},"teachings":["This version adds wording about the person who entered Ihram for Umrah.","A person who raised Talbiyah for Umrah put off Ihram after performing Umrah.","The report is tied to the earlier narration through another chain.","The main point is the timing of leaving Ihram after Umrah."],"related_hadiths":[{"id":"1779","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1778","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1777","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E460" s="4" t="n"/>
@@ -11085,7 +11089,7 @@
       </c>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hajj Umrah Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how Aishah was guided during Hajj and how missed Umrah was replaced after purification."},"heading":{"title":"Aisha Hajj Umrah Hadith: Hajj Umrah Lessons","description":"This Hadith about Aisha Hajj Umrah hadith centers on how the Prophet صلى الله عليه وسلم guided Aishah during the Farewell Hajj. She had intended Umrah, but when menstruation began, she could not perform Tawaf of the Ka'bah or Sa'i between Safa and Marwah at that time. The Prophet صلى الله عليه وسلم told her to undo and comb her hair, enter talbiyah for Hajj, and leave that Umrah. After Hajj was completed, he sent her with Abd al-Rahman to al-Tan'im so she could perform Umrah in place of the one she missed. The report also shows a clear difference between pilgrims doing Umrah first and those combining Hajj and Umrah with sacrificial animals."},"teachings":["A missed Umrah in this case was replaced after Hajj from al-Tan'im.","Menstruation prevented Tawaf and Sa'i at that time, but guidance was given.","Pilgrims with sacrificial animals did not leave ihram until both rites were complete."],"related_hadiths":[{"id":"1782","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1785","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1786","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hajj Umrah Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how Aishah was guided during Hajj and how missed Umrah was replaced after purification."},"heading":{"title":"Aisha Hajj Umrah Hadith: Hajj Umrah Lessons","description":"This Hadith about Aisha Hajj Umrah hadith centers on how the Prophet صلى الله عليه وسلم guided Aishah during the Farewell Hajj. She had intended Umrah, but when menstruation began, she could not perform Tawaf of the Ka'bah or Sa'i between Safa and Marwah at that time. The Prophet صلى الله عليه وسلم told her to undo and comb her hair, enter talbiyah for Hajj, and leave that Umrah. After Hajj was completed, he sent her with Abd al-Rahman to al-Tan'im so she could perform Umrah in place of the one she missed. The report also shows a clear difference between pilgrims doing Umrah first and those combining Hajj and Umrah with sacrificial animals."},"teachings":["A missed Umrah in this case was replaced after Hajj from al-Tan'im.","Menstruation prevented Tawaf and Sa'i at that time, but guidance was given.","Pilgrims with sacrificial animals did not leave ihram until both rites were complete."],"related_hadiths":[{"id":"1782","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1785","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1786","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E461" s="4" t="n"/>
@@ -11108,7 +11112,7 @@
       </c>
       <c r="D462" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hajj Menstruation Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah was told to complete Hajj rites while avoiding Tawaf until purified, then perform Umrah from Tan'im."},"heading":{"title":"Menstruation During Hajj Hadith: Hajj Menstruation Lessons","description":"This menstruation during Hajj hadith gives a calm and caring lesson from the Prophet صلى الله عليه وسلم. Aishah cried when she menstruated at Sarif because she feared missing her pilgrimage acts. The Prophet صلى الله عليه وسلم told her that menstruation is something Allah has written for the daughters of Adam. He then guided her to do all the rites of Hajj, except Tawaf around the House until she became pure. Later, after she was purified, he arranged for her to go to al-Tan'im and begin Umrah. The Hadith teaches that Hajj worship has clear limits, but it also has ease and guidance when a pilgrim faces a real condition."},"teachings":["A menstruating pilgrim was told to do Hajj rites except Tawaf until purified.","The Prophet صلى الله عليه وسلم comforted Aishah instead of blaming her.","Aishah was later taken to al-Tan'im to begin Umrah."],"related_hadiths":[{"id":"1781","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1785","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1786","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hajj Menstruation Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah was told to complete Hajj rites while avoiding Tawaf until purified, then perform Umrah from Tan'im."},"heading":{"title":"Menstruation During Hajj Hadith: Hajj Menstruation Lessons","description":"This menstruation during Hajj hadith gives a calm and caring lesson from the Prophet صلى الله عليه وسلم. Aishah cried when she menstruated at Sarif because she feared missing her pilgrimage acts. The Prophet صلى الله عليه وسلم told her that menstruation is something Allah has written for the daughters of Adam. He then guided her to do all the rites of Hajj, except Tawaf around the House until she became pure. Later, after she was purified, he arranged for her to go to al-Tan'im and begin Umrah. The Hadith teaches that Hajj worship has clear limits, but it also has ease and guidance when a pilgrim faces a real condition."},"teachings":["A menstruating pilgrim was told to do Hajj rites except Tawaf until purified.","The Prophet صلى الله عليه وسلم comforted Aishah instead of blaming her.","Aishah was later taken to al-Tan'im to begin Umrah."],"related_hadiths":[{"id":"1781","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1785","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1786","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E462" s="4" t="n"/>
@@ -11131,7 +11135,7 @@
       </c>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ihram Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet instructed pilgrims without sacrificial animals to leave ihram after Tawaf and Sa'i."},"heading":{"title":"Taking Off Ihram After Umrah: Ihram Lessons","description":"This taking off ihram after Umrah Hadith focuses on a simple order during the Prophet's Hajj journey. Aishah said they went out thinking only of Hajj. When they arrived in Makkah, they performed Tawaf around the Ka'bah. Then the Prophet صلى الله عليه وسلم ordered those who had not brought sacrificial animals to leave ihram. So the people who had no hady came out of ihram after their rites. The key point is the difference made by bringing sacrificial animals. Those without them were allowed to end ihram, while this report does not mention the same for those who had brought hady. It is a focused Hajj and Umrah ruling from the text."},"teachings":["Those without sacrificial animals were ordered to leave ihram after Tawaf.","The ruling in the report is linked to whether hady was brought.","The Companions followed the Prophet's instruction in their pilgrimage."],"related_hadiths":[{"id":"1788","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1791","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1792","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ihram Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet instructed pilgrims without sacrificial animals to leave ihram after Tawaf and Sa'i."},"heading":{"title":"Taking Off Ihram After Umrah: Ihram Lessons","description":"This taking off ihram after Umrah Hadith focuses on a simple order during the Prophet's Hajj journey. Aishah said they went out thinking only of Hajj. When they arrived in Makkah, they performed Tawaf around the Ka'bah. Then the Prophet صلى الله عليه وسلم ordered those who had not brought sacrificial animals to leave ihram. So the people who had no hady came out of ihram after their rites. The key point is the difference made by bringing sacrificial animals. Those without them were allowed to end ihram, while this report does not mention the same for those who had brought hady. It is a focused Hajj and Umrah ruling from the text."},"teachings":["Those without sacrificial animals were ordered to leave ihram after Tawaf.","The ruling in the report is linked to whether hady was brought.","The Companions followed the Prophet's instruction in their pilgrimage."],"related_hadiths":[{"id":"1788","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1791","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1792","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E463" s="4" t="n"/>
@@ -11154,7 +11158,7 @@
       </c>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tamattu Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah was guided through Hajj during menstruation, then completed Tawaf, Sa'i, and Umrah from Tan'im."},"heading":{"title":"Aisha Menstruation Hajj Umrah Hadith: Tamattu Lessons","description":"This Aisha menstruation Hajj Umrah hadith gives a fuller picture of Hajj rites during a real difficulty. Jabir reports that many pilgrims came for Hajj, while Aishah came for Umrah and then menstruated at Sarif. The Prophet صلى الله عليه وسلم told those without sacrificial animals to leave ihram after Tawaf and Sa'i, and he explained that normal lawful acts became allowed. When Aishah cried because she had not done Tawaf, he told her that menstruation was written for the daughters of Adam, then instructed her to bathe and raise talbiyah for Hajj. After purification, she performed Tawaf and Sa'i, and later an Umrah from al-Tan'im was arranged for her."},"teachings":["Aishah continued Hajj rites while avoiding Tawaf until purification.","Those without hady left ihram after completing Umrah rites.","The Prophet صلى الله عليه وسلم arranged an Umrah for Aishah from al-Tan'im."],"related_hadiths":[{"id":"1781","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1782","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1786","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tamattu Guidance","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah was guided through Hajj during menstruation, then completed Tawaf, Sa'i, and Umrah from Tan'im."},"heading":{"title":"Aisha Menstruation Hajj Umrah Hadith: Tamattu Lessons","description":"This Aisha menstruation Hajj Umrah hadith gives a fuller picture of Hajj rites during a real difficulty. Jabir reports that many pilgrims came for Hajj, while Aishah came for Umrah and then menstruated at Sarif. The Prophet صلى الله عليه وسلم told those without sacrificial animals to leave ihram after Tawaf and Sa'i, and he explained that normal lawful acts became allowed. When Aishah cried because she had not done Tawaf, he told her that menstruation was written for the daughters of Adam, then instructed her to bathe and raise talbiyah for Hajj. After purification, she performed Tawaf and Sa'i, and later an Umrah from al-Tan'im was arranged for her."},"teachings":["Aishah continued Hajj rites while avoiding Tawaf until purification.","Those without hady left ihram after completing Umrah rites.","The Prophet صلى الله عليه وسلم arranged an Umrah for Aishah from al-Tan'im."],"related_hadiths":[{"id":"1781","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1782","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1786","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E464" s="4" t="n"/>
@@ -11177,7 +11181,7 @@
       </c>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Chain Notes on Kissing and Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This report records Abu Dawud's chain discussion about the kissing-and-wudu narration and related weak chains."},"heading":{"title":"Weak Chain Notes on the Kissing and Wudu Hadith","description":"This Hadith is mainly about hadith chain analysis connected to the report on kissing and wudu. It says the tradition was reported through another chain on the authority of Aishah. Abu Dawud then quotes Yahya ibn Sa'id al-Qattan, who told a person to narrate from him that two traditions were weak in respect of their chains: the narration of al-A'mash from Habib about kissing, and another through the same chain about a woman with prolonged bleeding being told to perform ablution for every prayer. Abu Dawud also records a statement from al-Thawri about Habib's narration and then says Hamzah al-Zayyat reported a sound tradition from Habib, from Urwah ibn al-Zubair, from Aishah. The key topic is not just kissing; it is careful checking of transmission."},"teachings":["The narration focuses on the chains of related reports.","Yahya ibn Sa'id al-Qattan is quoted as weakening two chains.","Abu Dawud also mentions a sound report through Hamzah al-Zayyat."],"related_hadiths":[{"id":"86","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"502","book_id":"6","label":"Sunan Ibn Majah"},{"id":"503","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Chain Notes on Kissing and Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. This report records Abu Dawud's chain discussion about the kissing-and-wudu narration and related weak chains."},"heading":{"title":"Weak Chain Notes on the Kissing and Wudu Hadith","description":"This Hadith is mainly about hadith chain analysis connected to the report on kissing and wudu. It says the tradition was reported through another chain on the authority of Aishah. Abu Dawud then quotes Yahya ibn Sa'id al-Qattan, who told a person to narrate from him that two traditions were weak in respect of their chains: the narration of al-A'mash from Habib about kissing, and another through the same chain about a woman with prolonged bleeding being told to perform ablution for every prayer. Abu Dawud also records a statement from al-Thawri about Habib's narration and then says Hamzah al-Zayyat reported a sound tradition from Habib, from Urwah ibn al-Zubair, from Aishah. The key topic is not just kissing; it is careful checking of transmission."},"teachings":["The narration focuses on the chains of related reports.","Yahya ibn Sa'id al-Qattan is quoted as weakening two chains.","Abu Dawud also mentions a sound report through Hamzah al-Zayyat."],"related_hadiths":[{"id":"86","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"502","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"503","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E465" s="4" t="n"/>
@@ -11200,7 +11204,7 @@
       </c>
       <c r="D466" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hair Clipping at Marwah","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions the Prophet’s hair being clipped at Marwah with a broad iron arrowhead."},"heading":{"title":"Hadith About Hair Clipping at Marwah","description":"This hadith focuses on hair clipping at Marwah during the rites of Hajj or Umrah. Mu’awiyah reported, or according to one wording saw, that the hair of the Prophet صلى الله عليه وسلم was clipped at al-Marwah with a broad iron arrowhead. The report is short, but it gives a clear detail connected to ending a state of ihram. Many people search for this as hadith about clipping hair in Umrah, hair cutting after Safa Marwah, or the Prophet’s hair clipped at Marwah. The wording also shows careful narration, because the narrator mentions a difference in how the report was phrased. The teaching should stay within the text: it records an act of clipping hair at Marwah."},"teachings":["Hair clipping is mentioned in connection with the rites at al-Marwah.","The report preserves a specific detail about the tool used.","The narrators carefully noted differences in wording."],"related_hadiths":[{"id":"1803","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1805","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1801","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hair Clipping at Marwah","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith mentions the Prophet’s hair being clipped at Marwah with a broad iron arrowhead."},"heading":{"title":"Hadith About Hair Clipping at Marwah","description":"This hadith focuses on hair clipping at Marwah during the rites of Hajj or Umrah. Mu’awiyah reported, or according to one wording saw, that the hair of the Prophet صلى الله عليه وسلم was clipped at al-Marwah with a broad iron arrowhead. The report is short, but it gives a clear detail connected to ending a state of ihram. Many people search for this as hadith about clipping hair in Umrah, hair cutting after Safa Marwah, or the Prophet’s hair clipped at Marwah. The wording also shows careful narration, because the narrator mentions a difference in how the report was phrased. The teaching should stay within the text: it records an act of clipping hair at Marwah."},"teachings":["Hair clipping is mentioned in connection with the rites at al-Marwah.","The report preserves a specific detail about the tool used.","The narrators carefully noted differences in wording."],"related_hadiths":[{"id":"1803","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1805","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1801","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E466" s="4" t="n"/>
@@ -11223,7 +11227,7 @@
       </c>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hair Clipping During Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. Mu’awiyah mentions clipping the Prophet’s hair at Marwah during his Hajj."},"heading":{"title":"Hadith About Clipping Hair During Hajj at Marwah","description":"This hadith is another report about clipping the hair of the Messenger of Allah صلى الله عليه وسلم at al-Marwah. Mu’awiyah told Ibn Abbas that he clipped the Prophet’s hair with a broad iron arrowhead. One version adds that this happened during his Hajj. The core topic is hair clipping in Hajj, especially at Marwah. People may search for it as clipping hair after Umrah hadith, hair cutting in Hajj, or Mu’awiyah clipped the Prophet’s hair. The hadith does not give a long explanation, so the safest reading is to stay with what it says: a specific act of clipping took place at Marwah, and one narration connects it to the Prophet’s Hajj."},"teachings":["The hadith records hair clipping as part of the pilgrimage rites.","Al-Marwah is mentioned as the place where the clipping occurred.","The narration gives a specific witness report from Mu’awiyah."],"related_hadiths":[{"id":"1802","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1805","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1806","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hair Clipping During Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. Mu’awiyah mentions clipping the Prophet’s hair at Marwah during his Hajj."},"heading":{"title":"Hadith About Clipping Hair During Hajj at Marwah","description":"This hadith is another report about clipping the hair of the Messenger of Allah صلى الله عليه وسلم at al-Marwah. Mu’awiyah told Ibn Abbas that he clipped the Prophet’s hair with a broad iron arrowhead. One version adds that this happened during his Hajj. The core topic is hair clipping in Hajj, especially at Marwah. People may search for it as clipping hair after Umrah hadith, hair cutting in Hajj, or Mu’awiyah clipped the Prophet’s hair. The hadith does not give a long explanation, so the safest reading is to stay with what it says: a specific act of clipping took place at Marwah, and one narration connects it to the Prophet’s Hajj."},"teachings":["The hadith records hair clipping as part of the pilgrimage rites.","Al-Marwah is mentioned as the place where the clipping occurred.","The narration gives a specific witness report from Mu’awiyah."],"related_hadiths":[{"id":"1802","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1805","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1806","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E467" s="4" t="n"/>
@@ -11246,7 +11250,7 @@
       </c>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hajj Tamattu Guide","description":"$book_name$ $hadith_number$ - $chapter_name$. This detailed hadith explains Umrah with Hajj, ihram, tawaf, sa’i, sacrifice, and fasting."},"heading":{"title":"Hajj Tamattu Hadith: Umrah, Ihram, Tawaf, Sa’i, and Sacrifice","description":"This hadith gives a detailed picture of the Prophet’s صلى الله عليه وسلم pilgrimage at the Farewell Pilgrimage. The main topic is Hajj Tamattu, meaning Umrah joined with Hajj as described in the text. The Prophet صلى الله عليه وسلم began with Umrah, then Hajj, and brought sacrificial animals from Dhu al-Hulaifah. When he reached Makkah, he explained two cases. Those who brought sacrificial animals stayed in ihram until completing Hajj. Those who did not bring them performed tawaf, sa’i between Safa and Marwah, clipped their hair, left ihram, then entered Hajj again later. The hadith also mentions fasting three days during Hajj and seven after returning for those unable to find sacrificial animals. It is a key hadith about Hajj Tamattu, tawaf and sa’i, and sacrifice in Hajj."},"teachings":["Pilgrims with sacrificial animals remained in ihram until Hajj was completed.","Pilgrims without sacrificial animals were told to perform tawaf, sa’i, clip hair, and leave ihram.","Fasting is mentioned for those who could not find sacrificial animals.","The Prophet صلى الله عليه وسلم performed tawaf, prayed two rak’ahs at Maqam Ibrahim, and did sa’i."],"related_hadiths":[{"id":"1801","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1806","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1808","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hajj Tamattu Guide","description":"$book_name$ $hadith_number$ - $chapter_name$. This detailed hadith explains Umrah with Hajj, ihram, tawaf, sa’i, sacrifice, and fasting."},"heading":{"title":"Hajj Tamattu Hadith: Umrah, Ihram, Tawaf, Sa’i, and Sacrifice","description":"This hadith gives a detailed picture of the Prophet’s صلى الله عليه وسلم pilgrimage at the Farewell Pilgrimage. The main topic is Hajj Tamattu, meaning Umrah joined with Hajj as described in the text. The Prophet صلى الله عليه وسلم began with Umrah, then Hajj, and brought sacrificial animals from Dhu al-Hulaifah. When he reached Makkah, he explained two cases. Those who brought sacrificial animals stayed in ihram until completing Hajj. Those who did not bring them performed tawaf, sa’i between Safa and Marwah, clipped their hair, left ihram, then entered Hajj again later. The hadith also mentions fasting three days during Hajj and seven after returning for those unable to find sacrificial animals. It is a key hadith about Hajj Tamattu, tawaf and sa’i, and sacrifice in Hajj."},"teachings":["Pilgrims with sacrificial animals remained in ihram until Hajj was completed.","Pilgrims without sacrificial animals were told to perform tawaf, sa’i, clip hair, and leave ihram.","Fasting is mentioned for those who could not find sacrificial animals.","The Prophet صلى الله عليه وسلم performed tawaf, prayed two rak’ahs at Maqam Ibrahim, and did sa’i."],"related_hadiths":[{"id":"1801","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1806","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1808","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E468" s="4" t="n"/>
@@ -11269,7 +11273,7 @@
       </c>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu After Touching the Private Part","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the teaching on renewing wudu after touching the private part and how Busrah reported it from the Prophet صلى الله عليه وسلم."},"heading":{"title":"Hadith About Wudu After Touching the Private Part","description":"This hadith centers on wudu after touching the private part. The report begins with a discussion about matters that make ablution void. Marwan asks whether touching the penis is included. Urwah says he does not know that ruling. Marwan then shares what Busrah daughter of Safwan heard from the Messenger of Allah صلى الله عليه وسلم: “He who touches his penis should perform ablution.” The teaching is short and direct. It shows that questions about purity were discussed with care, and that a clear prophetic statement was used when there was uncertainty. For readers searching for hadith about touching private part and wudu, the main point in this text is renewal of ablution after that touch."},"teachings":["When a ruling is unclear, one should refer back to the words of the Prophet صلى الله عليه وسلم.","The hadith links touching the private part with performing wudu.","Knowledge was shared carefully through named narrators.","Matters of purification should be treated with seriousness."],"related_hadiths":[{"id":"82","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"84","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"47","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu After Touching the Private Part","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn the teaching on renewing wudu after touching the private part and how Busrah reported it from the Prophet صلى الله عليه وسلم."},"heading":{"title":"Hadith About Wudu After Touching the Private Part","description":"This hadith centers on wudu after touching the private part. The report begins with a discussion about matters that make ablution void. Marwan asks whether touching the penis is included. Urwah says he does not know that ruling. Marwan then shares what Busrah daughter of Safwan heard from the Messenger of Allah صلى الله عليه وسلم: “He who touches his penis should perform ablution.” The teaching is short and direct. It shows that questions about purity were discussed with care, and that a clear prophetic statement was used when there was uncertainty. For readers searching for hadith about touching private part and wudu, the main point in this text is renewal of ablution after that touch."},"teachings":["When a ruling is unclear, one should refer back to the words of the Prophet صلى الله عليه وسلم.","The hadith links touching the private part with performing wudu.","Knowledge was shared carefully through named narrators.","Matters of purification should be treated with seriousness."],"related_hadiths":[{"id":"82","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"84","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"47","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E469" s="4" t="n"/>
@@ -11292,7 +11296,7 @@
       </c>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Touching Private Part After Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. A Bedouin asks about touching the private part after wudu, and the Prophet صلى الله عليه وسلم answers with a simple comparison."},"heading":{"title":"Touching the Private Part After Wudu: A Simple Hadith Explanation","description":"This hadith is about touching the private part after wudu. A man, described as appearing to be a Bedouin, asks the Prophet صلى الله عليه وسلم what should be thought about a man who touches his penis after performing ablution. The Prophet صلى الله عليه وسلم replies that it is only a part of his body, or a piece of him. The wording is brief, so the explanation should stay close to the text. The hadith shows that people asked direct questions about purification, even about private matters. It also shows the Prophet صلى الله عليه وسلم answered in a clear and simple way. For searches like touching private part after wudu hadith, the core point here is the answer given in this specific report."},"teachings":["People may ask honest questions about purification without shame.","The Prophet صلى الله عليه وسلم answered the question with simple words.","The report treats the private part as a part of the body in this wording.","Different narrations on a topic should be read with care."],"related_hadiths":[{"id":"85","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Touching Private Part After Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. A Bedouin asks about touching the private part after wudu, and the Prophet صلى الله عليه وسلم answers with a simple comparison."},"heading":{"title":"Touching the Private Part After Wudu: A Simple Hadith Explanation","description":"This hadith is about touching the private part after wudu. A man, described as appearing to be a Bedouin, asks the Prophet صلى الله عليه وسلم what should be thought about a man who touches his penis after performing ablution. The Prophet صلى الله عليه وسلم replies that it is only a part of his body, or a piece of him. The wording is brief, so the explanation should stay close to the text. The hadith shows that people asked direct questions about purification, even about private matters. It also shows the Prophet صلى الله عليه وسلم answered in a clear and simple way. For searches like touching private part after wudu hadith, the core point here is the answer given in this specific report."},"teachings":["People may ask honest questions about purification without shame.","The Prophet صلى الله عليه وسلم answered the question with simple words.","The report treats the private part as a part of the body in this wording.","Different narrations on a topic should be read with care."],"related_hadiths":[{"id":"85","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E470" s="4" t="inlineStr">
@@ -11319,7 +11323,7 @@
       </c>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Touching Private Part During Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This short report adds the words “during the prayer” to the narration about touching the private part."},"heading":{"title":"Touching the Private Part During Prayer: Hadith and Wudu Context","description":"This hadith is a short follow-up to the previous report from Qais bin Talq. It says the same meaning came through another chain, with the added wording “during the prayer.” That small addition matters because it places the question inside the setting of salah. The report does not give a long ruling by itself; it simply notes the added phrase in this version. A careful explanation should not add more than the text says. For someone searching touching private part during prayer hadith, the key point is that this narration preserves a specific wording linked to prayer. It also reminds us that hadith wording can be reported through different chains, and small wording details are noted by scholars."},"teachings":["Small wording differences in hadith reports are important.","This version specifically mentions the setting of prayer.","The report connects purification questions with salah.","Care is needed when explaining brief narrations."],"related_hadiths":[{"id":"85","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Touching Private Part During Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This short report adds the words “during the prayer” to the narration about touching the private part."},"heading":{"title":"Touching the Private Part During Prayer: Hadith and Wudu Context","description":"This hadith is a short follow-up to the previous report from Qais bin Talq. It says the same meaning came through another chain, with the added wording “during the prayer.” That small addition matters because it places the question inside the setting of salah. The report does not give a long ruling by itself; it simply notes the added phrase in this version. A careful explanation should not add more than the text says. For someone searching touching private part during prayer hadith, the key point is that this narration preserves a specific wording linked to prayer. It also reminds us that hadith wording can be reported through different chains, and small wording details are noted by scholars."},"teachings":["Small wording differences in hadith reports are important.","This version specifically mentions the setting of prayer.","The report connects purification questions with salah.","Care is needed when explaining brief narrations."],"related_hadiths":[{"id":"85","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E471" s="4" t="inlineStr">
@@ -11346,7 +11350,7 @@
       </c>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu After Eating Camel Meat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم teaches wudu after camel meat, no wudu after sheep meat, and guidance on prayer places."},"heading":{"title":"Wudu After Eating Camel Meat Hadith: Prayer Places and Purity","description":"This hadith covers wudu after eating camel meat and prayer in animal resting places. The Messenger of Allah صلى الله عليه وسلم was asked about ablution after eating camel flesh, and he said to perform ablution after it. He was also asked about sheep meat, and he said not to perform ablution after it. The hadith then moves to prayer places. He said not to pray where camels lie down, calling them places of Satan in the wording of the report. He allowed prayer in sheepfolds and called them places of blessing. The text gives a clear difference between camel meat and sheep meat, and also between camel resting places and sheepfolds. The explanation should keep these points separate and not mix them."},"teachings":["The hadith specifically mentions wudu after eating camel meat.","It distinguishes camel meat from sheep meat.","The Prophet صلى الله عليه وسلم gave guidance about where not to pray.","The text allows prayer in sheepfolds and describes them as blessed places."],"related_hadiths":[{"id":"79","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"360b","book_id":"2","label":"Sahih Muslim"},{"id":"494","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu After Eating Camel Meat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم teaches wudu after camel meat, no wudu after sheep meat, and guidance on prayer places."},"heading":{"title":"Wudu After Eating Camel Meat Hadith: Prayer Places and Purity","description":"This hadith covers wudu after eating camel meat and prayer in animal resting places. The Messenger of Allah صلى الله عليه وسلم was asked about ablution after eating camel flesh, and he said to perform ablution after it. He was also asked about sheep meat, and he said not to perform ablution after it. The hadith then moves to prayer places. He said not to pray where camels lie down, calling them places of Satan in the wording of the report. He allowed prayer in sheepfolds and called them places of blessing. The text gives a clear difference between camel meat and sheep meat, and also between camel resting places and sheepfolds. The explanation should keep these points separate and not mix them."},"teachings":["The hadith specifically mentions wudu after eating camel meat.","It distinguishes camel meat from sheep meat.","The Prophet صلى الله عليه وسلم gave guidance about where not to pray.","The text allows prayer in sheepfolds and describes them as blessed places."],"related_hadiths":[{"id":"79","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"360b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"494","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E472" s="4" t="n"/>
@@ -11369,7 +11373,7 @@
       </c>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Betrothal During Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration adds that a pilgrim in ihram should not make a betrothal."},"heading":{"title":"Hadith About Betrothal During Ihram","description":"This hadith continues the teaching about marriage during ihram. It reports the same meaning as the previous narration from Uthman, from the Messenger of Allah صلى الله عليه وسلم, and adds an important detail: the person in ihram should not make a betrothal. The core topic is the conduct of a pilgrim while wearing ihram. The hadith does not only mention the final marriage contract. It also mentions the step of proposing or arranging engagement. This gives the reader a simple lesson: while in ihram, the pilgrim should stay away from marriage-related actions mentioned in the text. The sacred state has its own limits, and the believer treats those limits with care."},"teachings":["A pilgrim in ihram should not make a betrothal.","Ihram affects marriage-related actions mentioned in the hadith.","Small steps leading to marriage are also treated seriously here."],"related_hadiths":[{"id":"1841","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1843","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1845","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Betrothal During Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration adds that a pilgrim in ihram should not make a betrothal."},"heading":{"title":"Hadith About Betrothal During Ihram","description":"This hadith continues the teaching about marriage during ihram. It reports the same meaning as the previous narration from Uthman, from the Messenger of Allah صلى الله عليه وسلم, and adds an important detail: the person in ihram should not make a betrothal. The core topic is the conduct of a pilgrim while wearing ihram. The hadith does not only mention the final marriage contract. It also mentions the step of proposing or arranging engagement. This gives the reader a simple lesson: while in ihram, the pilgrim should stay away from marriage-related actions mentioned in the text. The sacred state has its own limits, and the believer treats those limits with care."},"teachings":["A pilgrim in ihram should not make a betrothal.","Ihram affects marriage-related actions mentioned in the hadith.","Small steps leading to marriage are also treated seriously here."],"related_hadiths":[{"id":"1841","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1843","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1845","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E473" s="4" t="n"/>
@@ -11392,7 +11396,7 @@
       </c>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Maimunah and Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم married Maimunah while in ihram."},"heading":{"title":"Hadith on the Prophet’s Marriage to Maimunah in Ihram","description":"This hadith gives Ibn Abbas’s report about the Prophet’s صلى الله عليه وسلم marriage to Maimunah. In this narration, Ibn Abbas said that the Prophet صلى الله عليه وسلم married her while he was in the sacred state. The core topic is marriage during ihram, and the report is short and focused. It does not add extra details about the event, the place, or any ruling beyond the statement itself. When reading this hadith, it is important to stay with the wording given. The text presents Ibn Abbas’s statement as a report. It is closely connected to other narrations in the same batch that discuss whether the marriage happened during ihram or outside ihram."},"teachings":["Ibn Abbas reported this marriage as happening during ihram.","The hadith is brief and should not be expanded beyond its wording.","Related narrations should be read carefully when studying this topic."],"related_hadiths":[{"id":"1843","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1845","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1841","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Maimunah and Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم married Maimunah while in ihram."},"heading":{"title":"Hadith on the Prophet’s Marriage to Maimunah in Ihram","description":"This hadith gives Ibn Abbas’s report about the Prophet’s صلى الله عليه وسلم marriage to Maimunah. In this narration, Ibn Abbas said that the Prophet صلى الله عليه وسلم married her while he was in the sacred state. The core topic is marriage during ihram, and the report is short and focused. It does not add extra details about the event, the place, or any ruling beyond the statement itself. When reading this hadith, it is important to stay with the wording given. The text presents Ibn Abbas’s statement as a report. It is closely connected to other narrations in the same batch that discuss whether the marriage happened during ihram or outside ihram."},"teachings":["Ibn Abbas reported this marriage as happening during ihram.","The hadith is brief and should not be expanded beyond its wording.","Related narrations should be read carefully when studying this topic."],"related_hadiths":[{"id":"1843","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1845","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1841","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E474" s="4" t="n"/>
@@ -11415,7 +11419,7 @@
       </c>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Clarifying Maimunah Marriage","description":"$book_name$ $hadith_number$ - $chapter_name$. Sa'id bin Al Musayyib says Ibn Abbas misunderstood the marriage report about Maimunah."},"heading":{"title":"Clarification Hadith on Maimunah’s Marriage and Ihram","description":"This narration gives Sa’id bin Al Musayyib’s comment on the report that the Prophet صلى الله عليه وسلم married Maimunah while in ihram. He said that Ibn Abbas was mistaken about this matter. The core topic is clarification of a marriage report during ihram. The wording is very brief, but it matters because it directly addresses the earlier report. It does not give a long explanation or a new story. It only states that there was a misunderstanding regarding the marriage of Maimunah while in the sacred state. This hadith is helpful for readers searching the Maimunah marriage hadith because it shows that the narrations in this topic were discussed carefully."},"teachings":["A report may be clarified by another narration or statement.","The topic of Maimunah’s marriage was discussed with care.","Readers should avoid adding claims not stated in the narration."],"related_hadiths":[{"id":"1843","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1844","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1841","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Clarifying Maimunah Marriage","description":"$book_name$ $hadith_number$ - $chapter_name$. Sa'id bin Al Musayyib says Ibn Abbas misunderstood the marriage report about Maimunah."},"heading":{"title":"Clarification Hadith on Maimunah’s Marriage and Ihram","description":"This narration gives Sa’id bin Al Musayyib’s comment on the report that the Prophet صلى الله عليه وسلم married Maimunah while in ihram. He said that Ibn Abbas was mistaken about this matter. The core topic is clarification of a marriage report during ihram. The wording is very brief, but it matters because it directly addresses the earlier report. It does not give a long explanation or a new story. It only states that there was a misunderstanding regarding the marriage of Maimunah while in the sacred state. This hadith is helpful for readers searching the Maimunah marriage hadith because it shows that the narrations in this topic were discussed carefully."},"teachings":["A report may be clarified by another narration or statement.","The topic of Maimunah’s marriage was discussed with care.","Readers should avoid adding claims not stated in the narration."],"related_hadiths":[{"id":"1843","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1844","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1841","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E475" s="4" t="n"/>
@@ -11438,7 +11442,7 @@
       </c>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Animals Killed in Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم named five harmful creatures that may be killed in and outside the sacred area."},"heading":{"title":"Hadith About Animals a Pilgrim May Kill in Ihram","description":"This hadith answers a practical question about what a pilgrim in ihram may kill from creatures. The Prophet صلى الله عليه وسلم named five: the scorpion, the crow, the rat, the kite, and the biting dog. The narration says there is no sin for killing them, whether outside or inside the sacred area. The core topic is harmful animals in ihram. The hadith does not give a general permission to kill any animal. It names specific creatures in the text. This makes the teaching easy to understand: ihram has limits, but the hadith also mentions cases where harm-related creatures are treated differently."},"teachings":["The hadith names specific creatures that may be killed.","The ruling is mentioned for both sacred and non-sacred areas.","The text does not give a broad rule for all animals."],"related_hadiths":[{"id":"1847","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1848","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Animals Killed in Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم named five harmful creatures that may be killed in and outside the sacred area."},"heading":{"title":"Hadith About Animals a Pilgrim May Kill in Ihram","description":"This hadith answers a practical question about what a pilgrim in ihram may kill from creatures. The Prophet صلى الله عليه وسلم named five: the scorpion, the crow, the rat, the kite, and the biting dog. The narration says there is no sin for killing them, whether outside or inside the sacred area. The core topic is harmful animals in ihram. The hadith does not give a general permission to kill any animal. It names specific creatures in the text. This makes the teaching easy to understand: ihram has limits, but the hadith also mentions cases where harm-related creatures are treated differently."},"teachings":["The hadith names specific creatures that may be killed.","The ruling is mentioned for both sacred and non-sacred areas.","The text does not give a broad rule for all animals."],"related_hadiths":[{"id":"1847","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1848","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E476" s="4" t="n"/>
@@ -11461,7 +11465,7 @@
       </c>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Harmful Creatures in Haram","description":"$book_name$ $hadith_number$ - $chapter_name$. Five harmful creatures are named as lawful to kill in the sacred territory."},"heading":{"title":"Hadith About Killing Harmful Creatures in the Sacred Territory","description":"This hadith reports that five creatures may be killed in the sacred territory: the snake, the scorpion, the kite, the rat, and the biting dog. The core topic is harmful creatures in the Haram. The narration is short and clear. It does not speak about hunting for food or killing animals in general. It points to certain creatures named in the text. This is important for anyone searching for hadith about animals in ihram or the sacred territory. The wording shows that even in a sacred place, the hadith makes mention of harmful creatures that are treated differently from normal game animals."},"teachings":["The hadith names five creatures linked with harm.","The sacred territory has limits, yet this exception is stated.","The ruling should be kept to what the text mentions."],"related_hadiths":[{"id":"1846","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1848","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Harmful Creatures in Haram","description":"$book_name$ $hadith_number$ - $chapter_name$. Five harmful creatures are named as lawful to kill in the sacred territory."},"heading":{"title":"Hadith About Killing Harmful Creatures in the Sacred Territory","description":"This hadith reports that five creatures may be killed in the sacred territory: the snake, the scorpion, the kite, the rat, and the biting dog. The core topic is harmful creatures in the Haram. The narration is short and clear. It does not speak about hunting for food or killing animals in general. It points to certain creatures named in the text. This is important for anyone searching for hadith about animals in ihram or the sacred territory. The wording shows that even in a sacred place, the hadith makes mention of harmful creatures that are treated differently from normal game animals."},"teachings":["The hadith names five creatures linked with harm.","The sacred territory has limits, yet this exception is stated.","The ruling should be kept to what the text mentions."],"related_hadiths":[{"id":"1846","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1848","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E477" s="4" t="n"/>
@@ -11484,7 +11488,7 @@
       </c>
       <c r="D478" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dangerous Animals in Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم named creatures a pilgrim may kill and said the pied crow should be driven away."},"heading":{"title":"Hadith About Dangerous Animals a Muhrim May Kill","description":"This hadith gives a detailed answer about creatures a pilgrim in ihram may kill. The Prophet صلى الله عليه وسلم mentioned the snake, scorpion, rat, biting dog, kite, and any wild animal that attacks a person. The narration also adds a special point about the pied crow: it should be driven away, but not killed. The core topic is dangerous animals in ihram. This hadith is useful because it separates different cases instead of treating all creatures the same. It shows that the sacred state of ihram has rules, and the text also mentions protection from creatures that attack or cause harm."},"teachings":["Some harmful creatures are named as exceptions during ihram.","The pied crow is treated differently in this narration.","An attacking wild animal is mentioned as a serious case."],"related_hadiths":[{"id":"1846","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1847","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dangerous Animals in Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم named creatures a pilgrim may kill and said the pied crow should be driven away."},"heading":{"title":"Hadith About Dangerous Animals a Muhrim May Kill","description":"This hadith gives a detailed answer about creatures a pilgrim in ihram may kill. The Prophet صلى الله عليه وسلم mentioned the snake, scorpion, rat, biting dog, kite, and any wild animal that attacks a person. The narration also adds a special point about the pied crow: it should be driven away, but not killed. The core topic is dangerous animals in ihram. This hadith is useful because it separates different cases instead of treating all creatures the same. It shows that the sacred state of ihram has rules, and the text also mentions protection from creatures that attack or cause harm."},"teachings":["Some harmful creatures are named as exceptions during ihram.","The pied crow is treated differently in this narration.","An attacking wild animal is mentioned as a serious case."],"related_hadiths":[{"id":"1846","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1847","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E478" s="4" t="n"/>
@@ -11507,7 +11511,7 @@
       </c>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Game Meat During Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali refused wild ass meat while in ihram and recalled the Prophet صلى الله عليه وسلم refusing such a gift."},"heading":{"title":"Hadith About Game Meat While Wearing Ihram","description":"This hadith discusses game meat during ihram through the action of Ali. Food was prepared containing birds and wild animal meat, and Ali was invited to eat. He refused and said it should be given to people who were not in ihram, because he and his companions were wearing ihram. He then asked those present whether they knew that a wild ass had been presented to the Messenger of Allah صلى الله عليه وسلم while he was in ihram, and that he refused to eat it. They confirmed it. The core topic is game meat in ihram. The hadith shows careful restraint when a person is in the sacred state."},"teachings":["Ali avoided eating game meat while in ihram.","He referred to the Prophet’s صلى الله عليه وسلم refusal of a wild ass gift.","The food was directed to people who were not in ihram."],"related_hadiths":[{"id":"1850","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1852","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Game Meat During Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali refused wild ass meat while in ihram and recalled the Prophet صلى الله عليه وسلم refusing such a gift."},"heading":{"title":"Hadith About Game Meat While Wearing Ihram","description":"This hadith discusses game meat during ihram through the action of Ali. Food was prepared containing birds and wild animal meat, and Ali was invited to eat. He refused and said it should be given to people who were not in ihram, because he and his companions were wearing ihram. He then asked those present whether they knew that a wild ass had been presented to the Messenger of Allah صلى الله عليه وسلم while he was in ihram, and that he refused to eat it. They confirmed it. The core topic is game meat in ihram. The hadith shows careful restraint when a person is in the sacred state."},"teachings":["Ali avoided eating game meat while in ihram.","He referred to the Prophet’s صلى الله عليه وسلم refusal of a wild ass gift.","The food was directed to people who were not in ihram."],"related_hadiths":[{"id":"1850","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1852","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E479" s="4" t="n"/>
@@ -11530,7 +11534,7 @@
       </c>
       <c r="D480" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Skinning a Goat Without Renewing Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم showed how to skin a goat, then led prayer without performing ablution or touching water."},"heading":{"title":"Hadith About Skinning a Goat and Praying Without New Wudu","description":"This hadith is about skinning a goat and praying without new wudu. The Prophet صلى الله عليه وسلم passed by a boy who was skinning a goat and told him to leave it until he showed him. He placed his hand between the skin and the flesh until it reached the armpit. After that, he went away and led the people in prayer without performing ablution. One version adds that he did not touch water. The report is practical and visual. It shows the Prophet صلى الله عليه وسلم teaching by action, not only by speech. For readers searching hadith about touching meat and wudu, the point here is that this action was followed by prayer without a fresh ablution in this narration."},"teachings":["The Prophet صلى الله عليه وسلم sometimes taught practical skills by showing them.","In this report, skinning the goat was followed by prayer without new wudu.","The added wording says he did not touch water.","The narration should be understood only within the action it describes."],"related_hadiths":[{"id":"207","book_id":"1","label":"Sahih Bukhari"},{"id":"354a","book_id":"2","label":"Sahih Muslim"},{"id":"210","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Skinning a Goat Without Renewing Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم showed how to skin a goat, then led prayer without performing ablution or touching water."},"heading":{"title":"Hadith About Skinning a Goat and Praying Without New Wudu","description":"This hadith is about skinning a goat and praying without new wudu. The Prophet صلى الله عليه وسلم passed by a boy who was skinning a goat and told him to leave it until he showed him. He placed his hand between the skin and the flesh until it reached the armpit. After that, he went away and led the people in prayer without performing ablution. One version adds that he did not touch water. The report is practical and visual. It shows the Prophet صلى الله عليه وسلم teaching by action, not only by speech. For readers searching hadith about touching meat and wudu, the point here is that this action was followed by prayer without a fresh ablution in this narration."},"teachings":["The Prophet صلى الله عليه وسلم sometimes taught practical skills by showing them.","In this report, skinning the goat was followed by prayer without new wudu.","The added wording says he did not touch water.","The narration should be understood only within the action it describes."],"related_hadiths":[{"id":"207","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"354a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"210","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E480" s="4" t="n"/>
@@ -11553,7 +11557,7 @@
       </c>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Land Game for Pilgrims","description":"$book_name$ $hadith_number$ - $chapter_name$. Land game is lawful if the pilgrim did not hunt it or have it hunted for him."},"heading":{"title":"Hadith About Land Game Being Lawful in Ihram","description":"This hadith gives an important condition about land game for someone in ihram. The Messenger of Allah صلى الله عليه وسلم said that land game is lawful for you as long as you do not hunt it or have it hunted on your behalf. The core topic is land game in ihram. The wording is careful and conditional. It does not allow the pilgrim to hunt. It also does not allow the pilgrim to arrange for the animal to be hunted for him. The narration then includes Abu Dawud’s note that when two reports from the Prophet صلى الله عليه وسلم appear to conflict, one should look at what his Companions followed."},"teachings":["Land game is mentioned as lawful under stated conditions.","A pilgrim should not hunt it himself.","A pilgrim should not have it hunted on his behalf."],"related_hadiths":[{"id":"1849","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1850","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1852","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Land Game for Pilgrims","description":"$book_name$ $hadith_number$ - $chapter_name$. Land game is lawful if the pilgrim did not hunt it or have it hunted for him."},"heading":{"title":"Hadith About Land Game Being Lawful in Ihram","description":"This hadith gives an important condition about land game for someone in ihram. The Messenger of Allah صلى الله عليه وسلم said that land game is lawful for you as long as you do not hunt it or have it hunted on your behalf. The core topic is land game in ihram. The wording is careful and conditional. It does not allow the pilgrim to hunt. It also does not allow the pilgrim to arrange for the animal to be hunted for him. The narration then includes Abu Dawud’s note that when two reports from the Prophet صلى الله عليه وسلم appear to conflict, one should look at what his Companions followed."},"teachings":["Land game is mentioned as lawful under stated conditions.","A pilgrim should not hunt it himself.","A pilgrim should not have it hunted on his behalf."],"related_hadiths":[{"id":"1849","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1850","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1852","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E481" s="4" t="n"/>
@@ -11576,7 +11580,7 @@
       </c>
       <c r="D482" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Qatadah’s Hunt","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Qatadah hunted while not in ihram, and the Prophet صلى الله عليه وسلم allowed the companions to eat it."},"heading":{"title":"Abu Qatadah Wild Ass Hadith and Ihram","description":"This hadith tells the story of Abu Qatadah and a wild ass during the journey to Makkah. Abu Qatadah was not in ihram, while some of his companions were. When he saw the wild ass, he asked them to hand him his whip and lance, but they refused. He then took the lance himself, hunted the animal, and killed it. Some companions ate from it, while others refused. When they asked the Messenger of Allah صلى الله عليه وسلم, he said it was food Allah had provided for them. The core topic is game meat in ihram. The hadith clearly notes that Abu Qatadah himself was not in ihram."},"teachings":["Abu Qatadah hunted while he was not in ihram.","The companions in ihram did not help by handing him the tools.","The Prophet صلى الله عليه وسلم described the food as provision from Allah."],"related_hadiths":[{"id":"1851","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1849","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1850","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Abu Qatadah’s Hunt","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Qatadah hunted while not in ihram, and the Prophet صلى الله عليه وسلم allowed the companions to eat it."},"heading":{"title":"Abu Qatadah Wild Ass Hadith and Ihram","description":"This hadith tells the story of Abu Qatadah and a wild ass during the journey to Makkah. Abu Qatadah was not in ihram, while some of his companions were. When he saw the wild ass, he asked them to hand him his whip and lance, but they refused. He then took the lance himself, hunted the animal, and killed it. Some companions ate from it, while others refused. When they asked the Messenger of Allah صلى الله عليه وسلم, he said it was food Allah had provided for them. The core topic is game meat in ihram. The hadith clearly notes that Abu Qatadah himself was not in ihram."},"teachings":["Abu Qatadah hunted while he was not in ihram.","The companions in ihram did not help by handing him the tools.","The Prophet صلى الله عليه وسلم described the food as provision from Allah."],"related_hadiths":[{"id":"1851","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1849","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1850","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E482" s="4" t="n"/>
@@ -11599,7 +11603,7 @@
       </c>
       <c r="D483" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Locusts and Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. A report mentions locusts as sea game, while Abu Dawud notes weakness and misunderstanding."},"heading":{"title":"Hadith Report About Locusts During Ihram","description":"This narration mentions a group finding a swarm of locusts. A man in ihram began striking them with his whip, and someone objected. When the matter was mentioned to the Prophet صلى الله عليه وسلم, the report says he described it as being from the game of the sea. The core topic is locusts during ihram. The narration also includes Abu Dawud’s important comment: Abu Al Muhzim is weak, and he said both traditions are based on misunderstanding. Because that note is part of the supplied text, it should be included when explaining this hadith. The safe way to read it is to present the report and Abu Dawud’s caution together."},"teachings":["The report mentions locusts in relation to sea game.","A man in ihram striking locusts was questioned.","Abu Dawud notes weakness and misunderstanding in the report."],"related_hadiths":[{"id":"1853","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1855","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Locusts and Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. A report mentions locusts as sea game, while Abu Dawud notes weakness and misunderstanding."},"heading":{"title":"Hadith Report About Locusts During Ihram","description":"This narration mentions a group finding a swarm of locusts. A man in ihram began striking them with his whip, and someone objected. When the matter was mentioned to the Prophet صلى الله عليه وسلم, the report says he described it as being from the game of the sea. The core topic is locusts during ihram. The narration also includes Abu Dawud’s important comment: Abu Al Muhzim is weak, and he said both traditions are based on misunderstanding. Because that note is part of the supplied text, it should be included when explaining this hadith. The safe way to read it is to present the report and Abu Dawud’s caution together."},"teachings":["The report mentions locusts in relation to sea game.","A man in ihram striking locusts was questioned.","Abu Dawud notes weakness and misunderstanding in the report."],"related_hadiths":[{"id":"1853","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1855","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E483" s="4" t="n"/>
@@ -11622,7 +11626,7 @@
       </c>
       <c r="D484" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ka'ab on Locusts","description":"$book_name$ $hadith_number$ - $chapter_name$. Ka'ab states that locusts are counted along with the game of the sea."},"heading":{"title":"Ka'ab’s Report About Locusts as Sea Game","description":"This narration gives a statement from Ka’ab: locusts are counted along with the game of the sea. The core topic is locusts and sea game. It is not worded here as a long story, nor does it describe a detailed ruling with many conditions. It is a short statement that connects locusts to the same category mentioned in nearby reports. Readers searching for locusts hadith or sea game hadith will find that this narration is focused on classification. The best explanation is simple: the report says locusts belong with sea game, and no extra details should be added beyond the text supplied."},"teachings":["Ka’ab stated that locusts are counted with sea game.","The narration is short and focused on classification.","The text does not add further conditions or details."],"related_hadiths":[{"id":"1853","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1854","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ka'ab on Locusts","description":"$book_name$ $hadith_number$ - $chapter_name$. Ka'ab states that locusts are counted along with the game of the sea."},"heading":{"title":"Ka'ab’s Report About Locusts as Sea Game","description":"This narration gives a statement from Ka’ab: locusts are counted along with the game of the sea. The core topic is locusts and sea game. It is not worded here as a long story, nor does it describe a detailed ruling with many conditions. It is a short statement that connects locusts to the same category mentioned in nearby reports. Readers searching for locusts hadith or sea game hadith will find that this narration is focused on classification. The best explanation is simple: the report says locusts belong with sea game, and no extra details should be added beyond the text supplied."},"teachings":["Ka’ab stated that locusts are counted with sea game.","The narration is short and focused on classification.","The text does not add further conditions or details."],"related_hadiths":[{"id":"1853","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1854","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1851","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E484" s="4" t="n"/>
@@ -11645,7 +11649,7 @@
       </c>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shaving Head in Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. Ka'b was allowed to shave due to lice and was given ransom options."},"heading":{"title":"Hadith About Shaving the Head in Ihram Due to Lice","description":"This hadith tells the case of Ka’ab bin Ujrah at Al Hudaibiyyah. The Messenger of Allah صلى الله عليه وسلم saw his condition and asked if the insects of his head were troubling him. Ka’ab said yes. The Prophet صلى الله عليه وسلم then told him to shave his head and gave options: sacrifice a sheep, fast three days, or give three sa’s of dates to six poor people. The core topic is shaving in ihram due to harm. The hadith shows that the instruction came after real hardship was present. It also gives clear ransom choices in the wording, without making the matter sound harder than the text says."},"teachings":["Ka’ab was allowed to shave because of harm from lice.","The Prophet صلى الله عليه وسلم gave three ransom options.","The options mentioned were sacrifice, fasting, or feeding poor people."],"related_hadiths":[{"id":"1857","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1858","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1860","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shaving Head in Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. Ka'b was allowed to shave due to lice and was given ransom options."},"heading":{"title":"Hadith About Shaving the Head in Ihram Due to Lice","description":"This hadith tells the case of Ka’ab bin Ujrah at Al Hudaibiyyah. The Messenger of Allah صلى الله عليه وسلم saw his condition and asked if the insects of his head were troubling him. Ka’ab said yes. The Prophet صلى الله عليه وسلم then told him to shave his head and gave options: sacrifice a sheep, fast three days, or give three sa’s of dates to six poor people. The core topic is shaving in ihram due to harm. The hadith shows that the instruction came after real hardship was present. It also gives clear ransom choices in the wording, without making the matter sound harder than the text says."},"teachings":["Ka’ab was allowed to shave because of harm from lice.","The Prophet صلى الله عليه وسلم gave three ransom options.","The options mentioned were sacrifice, fasting, or feeding poor people."],"related_hadiths":[{"id":"1857","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1858","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1860","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E485" s="4" t="n"/>
@@ -11668,7 +11672,7 @@
       </c>
       <c r="D486" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fidyah Options in Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم gave Ka'b a choice: sacrifice, fast three days, or feed six poor people."},"heading":{"title":"Hadith About Fidyah Options for Ka'b bin Ujrah","description":"This hadith gives the ransom options mentioned to Ka’ab bin Ujrah. The Messenger of Allah صلى الله عليه وسلم said that if he wished, he could sacrifice an animal; if he wished, he could fast three days; and if he wished, he could give three sa’s of dates to six poor people. The core topic is fidyah in ihram. The wording is clear because it presents choices. It does not add extra cases or different amounts beyond what is stated. For someone searching for fidyah for shaving head in ihram, this hadith is direct and practical. It shows the options given in simple terms."},"teachings":["Ka’ab was given more than one ransom option.","The options included sacrifice, fasting, or feeding.","The feeding amount mentioned was three sa’s for six poor people."],"related_hadiths":[{"id":"1856","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1858","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1860","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Fidyah Options in Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم gave Ka'b a choice: sacrifice, fast three days, or feed six poor people."},"heading":{"title":"Hadith About Fidyah Options for Ka'b bin Ujrah","description":"This hadith gives the ransom options mentioned to Ka’ab bin Ujrah. The Messenger of Allah صلى الله عليه وسلم said that if he wished, he could sacrifice an animal; if he wished, he could fast three days; and if he wished, he could give three sa’s of dates to six poor people. The core topic is fidyah in ihram. The wording is clear because it presents choices. It does not add extra cases or different amounts beyond what is stated. For someone searching for fidyah for shaving head in ihram, this hadith is direct and practical. It shows the options given in simple terms."},"teachings":["Ka’ab was given more than one ransom option.","The options included sacrifice, fasting, or feeding.","The feeding amount mentioned was three sa’s for six poor people."],"related_hadiths":[{"id":"1856","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1858","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1860","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E486" s="4" t="n"/>
@@ -11691,7 +11695,7 @@
       </c>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Feeding Six Poor People","description":"$book_name$ $hadith_number$ - $chapter_name$. Ka'b had no sacrificial animal, so fasting or feeding six poor people was mentioned."},"heading":{"title":"Hadith About Feeding Six Poor People as Fidyah","description":"This hadith continues the story of Ka’ab bin Ujrah at Al Hudaibiyyah. The Prophet صلى الله عليه وسلم asked him whether he had a sacrificial animal. Ka’ab replied that he did not. The Prophet صلى الله عليه وسلم then told him to fast three days or give three sa’s of dates to six poor people, with one sa’ shared by every two persons. The core topic is feeding six poor people as fidyah. The hadith is useful because it gives a detail about the amount and how it was divided. It stays connected to Ka’ab’s specific situation and the hardship mentioned in the related narrations."},"teachings":["Ka’ab was asked if he had a sacrificial animal.","When he did not, fasting or feeding was mentioned.","The narration explains the feeding amount for six poor people."],"related_hadiths":[{"id":"1856","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1857","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1860","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Feeding Six Poor People","description":"$book_name$ $hadith_number$ - $chapter_name$. Ka'b had no sacrificial animal, so fasting or feeding six poor people was mentioned."},"heading":{"title":"Hadith About Feeding Six Poor People as Fidyah","description":"This hadith continues the story of Ka’ab bin Ujrah at Al Hudaibiyyah. The Prophet صلى الله عليه وسلم asked him whether he had a sacrificial animal. Ka’ab replied that he did not. The Prophet صلى الله عليه وسلم then told him to fast three days or give three sa’s of dates to six poor people, with one sa’ shared by every two persons. The core topic is feeding six poor people as fidyah. The hadith is useful because it gives a detail about the amount and how it was divided. It stays connected to Ka’ab’s specific situation and the hardship mentioned in the related narrations."},"teachings":["Ka’ab was asked if he had a sacrificial animal.","When he did not, fasting or feeding was mentioned.","The narration explains the feeding amount for six poor people."],"related_hadiths":[{"id":"1856","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1857","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1860","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E487" s="4" t="n"/>
@@ -11714,7 +11718,7 @@
       </c>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Offering After Shaving","description":"$book_name$ $hadith_number$ - $chapter_name$. Ka'b shaved due to head pain, and the Prophet صلى الله عليه وسلم ordered an offering of a cow."},"heading":{"title":"Hadith About Offering After Shaving the Head in Ihram","description":"This narration reports that Ka’ab bin Ujrah had pain in his head due to lice, so he shaved his head. The Prophet صلى الله عليه وسلم then ordered him to give an offering, described here as a cow. The core topic is offering after shaving in ihram. The text is brief and does not mention the other options found in nearby narrations. So the explanation should stay with this report: there was harm in the head, shaving took place, and an offering was ordered. For readers searching for Ka’ab bin Ujrah shaving hadith, this narration highlights one version of the response after shaving due to difficulty."},"teachings":["Ka’ab shaved because of harm in his head.","The Prophet صلى الله عليه وسلم ordered an offering in this narration.","The offering mentioned here is a cow."],"related_hadiths":[{"id":"1856","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1857","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1860","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Offering After Shaving","description":"$book_name$ $hadith_number$ - $chapter_name$. Ka'b shaved due to head pain, and the Prophet صلى الله عليه وسلم ordered an offering of a cow."},"heading":{"title":"Hadith About Offering After Shaving the Head in Ihram","description":"This narration reports that Ka’ab bin Ujrah had pain in his head due to lice, so he shaved his head. The Prophet صلى الله عليه وسلم then ordered him to give an offering, described here as a cow. The core topic is offering after shaving in ihram. The text is brief and does not mention the other options found in nearby narrations. So the explanation should stay with this report: there was harm in the head, shaving took place, and an offering was ordered. For readers searching for Ka’ab bin Ujrah shaving hadith, this narration highlights one version of the response after shaving due to difficulty."},"teachings":["Ka’ab shaved because of harm in his head.","The Prophet صلى الله عليه وسلم ordered an offering in this narration.","The offering mentioned here is a cow."],"related_hadiths":[{"id":"1856","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1857","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1860","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E488" s="4" t="n"/>
@@ -11737,7 +11741,7 @@
       </c>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Dead Kid and the Value of Things","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم passed a dead kid in the market and used it to ask who would like to take it."},"heading":{"title":"Dead Kid in the Market Hadith: A Lesson on Value","description":"This hadith mentions the Prophet صلى الله عليه وسلم passing through the market while people were on both sides of him. He found a dead kid whose ears were joined together, held it by the ear, and asked, “Which of you likes to take it?” The provided text says the narrator transmitted the tradition in full, but the full wording is not included here. So the safest explanation is to stay with what is present: the Prophet صلى الله عليه وسلم used a real object in front of the people to make them think about value and desire. For searches like dead goat hadith or dead kid market hadith, this report is often recognized by that scene. The text shows a direct teaching moment in a public place."},"teachings":["The Prophet صلى الله عليه وسلم used everyday scenes to teach people.","The question made listeners think before receiving the full lesson.","The report takes place in a market, where people often think about value.","The provided text is abridged, so the explanation should not overstate details."],"related_hadiths":[{"id":"2957","book_id":"2","label":"Sahih Muslim"},{"id":"6416","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Dead Kid and the Value of Things","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم passed a dead kid in the market and used it to ask who would like to take it."},"heading":{"title":"Dead Kid in the Market Hadith: A Lesson on Value","description":"This hadith mentions the Prophet صلى الله عليه وسلم passing through the market while people were on both sides of him. He found a dead kid whose ears were joined together, held it by the ear, and asked, “Which of you likes to take it?” The provided text says the narrator transmitted the tradition in full, but the full wording is not included here. So the safest explanation is to stay with what is present: the Prophet صلى الله عليه وسلم used a real object in front of the people to make them think about value and desire. For searches like dead goat hadith or dead kid market hadith, this report is often recognized by that scene. The text shows a direct teaching moment in a public place."},"teachings":["The Prophet صلى الله عليه وسلم used everyday scenes to teach people.","The question made listeners think before receiving the full lesson.","The report takes place in a market, where people often think about value.","The provided text is abridged, so the explanation should not overstate details."],"related_hadiths":[{"id":"2957","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"6416","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E489" s="4" t="n"/>
@@ -11760,7 +11764,7 @@
       </c>
       <c r="D490" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ka'b bin Ujrah Fidyah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ka'b’s head ailment led to shaving and a choice of fasting, feeding, or sacrifice."},"heading":{"title":"Ka'b bin Ujrah Hadith About Fidyah for Head Ailment","description":"This hadith gives Ka’ab bin Ujrah’s own account from the year of Al Hudaibiyyah. He had many lice in his head, to the point that he feared for his eyesight. He said that Allah revealed the verse about being sick or having an ailment of the head in relation to his case. The Messenger of Allah صلى الله عليه وسلم then called him and told him to shave his head and choose one of the mentioned actions: fast three days, feed six poor people with a faraq of raisins, or sacrifice a goat. Ka’ab said he shaved his head and sacrificed. The core topic is fidyah for a head ailment in ihram."},"teachings":["Ka’ab’s hardship was serious enough that he feared for his eyesight.","He was told to shave his head and give fidyah.","The options mentioned were fasting, feeding, or sacrificing a goat."],"related_hadiths":[{"id":"1856","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1857","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1858","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ka'b bin Ujrah Fidyah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ka'b’s head ailment led to shaving and a choice of fasting, feeding, or sacrifice."},"heading":{"title":"Ka'b bin Ujrah Hadith About Fidyah for Head Ailment","description":"This hadith gives Ka’ab bin Ujrah’s own account from the year of Al Hudaibiyyah. He had many lice in his head, to the point that he feared for his eyesight. He said that Allah revealed the verse about being sick or having an ailment of the head in relation to his case. The Messenger of Allah صلى الله عليه وسلم then called him and told him to shave his head and choose one of the mentioned actions: fast three days, feed six poor people with a faraq of raisins, or sacrifice a goat. Ka’ab said he shaved his head and sacrificed. The core topic is fidyah for a head ailment in ihram."},"teachings":["Ka’ab’s hardship was serious enough that he feared for his eyesight.","He was told to shave his head and give fidyah.","The options mentioned were fasting, feeding, or sacrificing a goat."],"related_hadiths":[{"id":"1856","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1857","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1858","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E490" s="4" t="n"/>
@@ -11783,7 +11787,7 @@
       </c>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Illness During Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration adds illness to the case of a pilgrim unable to continue Hajj."},"heading":{"title":"Hadith About Illness During Hajj","description":"This Hadith gives the same meaning as the previous report but adds the case of illness. It mentions a person who breaks a leg, becomes lame, or falls ill. The core topic is Hajj interrupted by hardship. The wording helps people searching for hadith about illness during Hajj, injury in ihram, or being unable to complete pilgrimage. The Hadith does not add long details here, so the safest understanding is to stay with what is clearly stated: these conditions are treated as reasons connected to leaving the sacred state, with the meaning already mentioned in the related report."},"teachings":["Illness is mentioned along with injury and lameness.","The Hadith keeps the ruling tied to real inability.","The narration supports the same meaning as the previous report."],"related_hadiths":[{"id":"1862","book_id":"4","label":"Sunan Abu Dawud"},{"id":"940","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Illness During Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration adds illness to the case of a pilgrim unable to continue Hajj."},"heading":{"title":"Hadith About Illness During Hajj","description":"This Hadith gives the same meaning as the previous report but adds the case of illness. It mentions a person who breaks a leg, becomes lame, or falls ill. The core topic is Hajj interrupted by hardship. The wording helps people searching for hadith about illness during Hajj, injury in ihram, or being unable to complete pilgrimage. The Hadith does not add long details here, so the safest understanding is to stay with what is clearly stated: these conditions are treated as reasons connected to leaving the sacred state, with the meaning already mentioned in the related report."},"teachings":["Illness is mentioned along with injury and lameness.","The Hadith keeps the ruling tied to real inability.","The narration supports the same meaning as the previous report."],"related_hadiths":[{"id":"1862","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"940","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E491" s="4" t="n"/>
@@ -11806,7 +11810,7 @@
       </c>
       <c r="D492" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Entering Makkah with Preparation","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar followed the Prophet’s practice of bathing and entering Makkah by day."},"heading":{"title":"Hadith About Entering Makkah by Day","description":"This Hadith shows the practice of Ibn ‘Umar when he came to Makkah. He would spend the night at Dhu Tuwa, bathe in the morning, and enter Makkah during the daytime. He mentioned that the Prophet صلى الله عليه وسلم had done the same. The core topic is entering Makkah with preparation. For people looking for hadith about entering Makkah, Dhu Tuwa, or bathing before entering Makkah, this narration gives a clear practice linked to the Prophet صلى الله عليه وسلم. The text is about this specific action and does not make wider claims beyond that practice."},"teachings":["Ibn ‘Umar carefully followed what he knew from the Prophet صلى الله عليه وسلم.","Bathing before entering Makkah is mentioned in this report.","The narration highlights calm preparation before entering Makkah."],"related_hadiths":[{"id":"1573","book_id":"1","label":"Sahih Bukhari"},{"id":"1259","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Entering Makkah with Preparation","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar followed the Prophet’s practice of bathing and entering Makkah by day."},"heading":{"title":"Hadith About Entering Makkah by Day","description":"This Hadith shows the practice of Ibn ‘Umar when he came to Makkah. He would spend the night at Dhu Tuwa, bathe in the morning, and enter Makkah during the daytime. He mentioned that the Prophet صلى الله عليه وسلم had done the same. The core topic is entering Makkah with preparation. For people looking for hadith about entering Makkah, Dhu Tuwa, or bathing before entering Makkah, this narration gives a clear practice linked to the Prophet صلى الله عليه وسلم. The text is about this specific action and does not make wider claims beyond that practice."},"teachings":["Ibn ‘Umar carefully followed what he knew from the Prophet صلى الله عليه وسلم.","Bathing before entering Makkah is mentioned in this report.","The narration highlights calm preparation before entering Makkah."],"related_hadiths":[{"id":"1573","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1259","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E492" s="4" t="n"/>
@@ -11829,7 +11833,7 @@
       </c>
       <c r="D493" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Route of Entering Makkah","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes the Prophet’s entry and exit routes in Makkah."},"heading":{"title":"Hadith About the Prophet’s Route into Makkah","description":"This Hadith describes how the Prophet صلى الله عليه وسلم used to enter Makkah from the upper hillock and leave from the lower hillock. One version names Kuda’ from the hillock of Batha’. The core topic is the route of entering Makkah. For searches like hadith about entering Makkah from Kuda, upper hill of Makkah, or Prophet’s route into Makkah, this narration gives the route in simple terms. The report is descriptive, so the explanation should stay close to the text: it records where the Prophet صلى الله عليه وسلم entered and where he came out."},"teachings":["The Prophet صلى الله عليه وسلم had a known route for entering and leaving Makkah.","The narration preserves details of place and movement.","Ibn ‘Umar reported this practice with care."],"related_hadiths":[{"id":"1575","book_id":"1","label":"Sahih Bukhari"},{"id":"1257","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Route of Entering Makkah","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith describes the Prophet’s entry and exit routes in Makkah."},"heading":{"title":"Hadith About the Prophet’s Route into Makkah","description":"This Hadith describes how the Prophet صلى الله عليه وسلم used to enter Makkah from the upper hillock and leave from the lower hillock. One version names Kuda’ from the hillock of Batha’. The core topic is the route of entering Makkah. For searches like hadith about entering Makkah from Kuda, upper hill of Makkah, or Prophet’s route into Makkah, this narration gives the route in simple terms. The report is descriptive, so the explanation should stay close to the text: it records where the Prophet صلى الله عليه وسلم entered and where he came out."},"teachings":["The Prophet صلى الله عليه وسلم had a known route for entering and leaving Makkah.","The narration preserves details of place and movement.","Ibn ‘Umar reported this practice with care."],"related_hadiths":[{"id":"1575","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1257","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E493" s="4" t="n"/>
@@ -11852,7 +11856,7 @@
       </c>
       <c r="D494" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Entering Makkah from Kuda","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports the Prophet’s entry routes during the Conquest and during Umrah."},"heading":{"title":"Hadith About Entering Makkah from Kuda","description":"This Hadith mentions two entries into Makkah. ‘Aishah said the Messenger of Allah صلى الله عليه وسلم entered from Kuda’, the upper side of Makkah, in the year of the conquest. She also said he entered from Kuda when he performed umrah. The report adds that ‘Urwah entered from both sides and often used the side nearer to his house. The core topic is entering Makkah by route. For search terms like Kuda Makkah hadith, Prophet entered Makkah conquest, or umrah route hadith, this narration gives the route details without adding more than the text states."},"teachings":["The Hadith records different entry routes into Makkah.","The Prophet صلى الله عليه وسلم entered from the upper side during the conquest.","‘Urwah’s practice shows he used both routes, often choosing the nearer one."],"related_hadiths":[{"id":"1575","book_id":"1","label":"Sahih Bukhari"},{"id":"1258","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Entering Makkah from Kuda","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports the Prophet’s entry routes during the Conquest and during Umrah."},"heading":{"title":"Hadith About Entering Makkah from Kuda","description":"This Hadith mentions two entries into Makkah. ‘Aishah said the Messenger of Allah صلى الله عليه وسلم entered from Kuda’, the upper side of Makkah, in the year of the conquest. She also said he entered from Kuda when he performed umrah. The report adds that ‘Urwah entered from both sides and often used the side nearer to his house. The core topic is entering Makkah by route. For search terms like Kuda Makkah hadith, Prophet entered Makkah conquest, or umrah route hadith, this narration gives the route details without adding more than the text states."},"teachings":["The Hadith records different entry routes into Makkah.","The Prophet صلى الله عليه وسلم entered from the upper side during the conquest.","‘Urwah’s practice shows he used both routes, often choosing the nearer one."],"related_hadiths":[{"id":"1575","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1258","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E494" s="4" t="n"/>
@@ -11875,7 +11879,7 @@
       </c>
       <c r="D495" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Entering and Leaving Makkah","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports the Prophet entering Makkah from the upper side and leaving from below."},"heading":{"title":"Hadith About Entering and Leaving Makkah","description":"This Hadith gives a short and clear report from ‘Aishah. When the Prophet صلى الله عليه وسلم entered Makkah, he entered from its upper side, and when he left, he went out from its lower side. The core topic is the Prophet’s route in Makkah. People looking for hadith about entering Makkah from upper side, leaving Makkah from lower side, or Makkah route Sunnah will find this narration directly related. The text is simple and specific. It does not discuss other acts of Hajj or umrah, so the explanation should stay focused on the route described."},"teachings":["The Prophet’s entry and exit routes were remembered by the companions.","The Hadith gives a clear place-based description.","It teaches respect for reported practice without adding extra details."],"related_hadiths":[{"id":"1575","book_id":"1","label":"Sahih Bukhari"},{"id":"1258","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Entering and Leaving Makkah","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports the Prophet entering Makkah from the upper side and leaving from below."},"heading":{"title":"Hadith About Entering and Leaving Makkah","description":"This Hadith gives a short and clear report from ‘Aishah. When the Prophet صلى الله عليه وسلم entered Makkah, he entered from its upper side, and when he left, he went out from its lower side. The core topic is the Prophet’s route in Makkah. People looking for hadith about entering Makkah from upper side, leaving Makkah from lower side, or Makkah route Sunnah will find this narration directly related. The text is simple and specific. It does not discuss other acts of Hajj or umrah, so the explanation should stay focused on the route described."},"teachings":["The Prophet’s entry and exit routes were remembered by the companions.","The Hadith gives a clear place-based description.","It teaches respect for reported practice without adding extra details."],"related_hadiths":[{"id":"1575","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1258","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E495" s="4" t="n"/>
@@ -11898,7 +11902,7 @@
       </c>
       <c r="D496" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eating Goat Shoulder Without New Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم ate from a goat shoulder, prayed, and did not perform ablution."},"heading":{"title":"Eating Goat Shoulder and Praying Without Renewing Wudu","description":"This hadith is short and clear. Ibn Abbas says the Messenger of Allah صلى الله عليه وسلم took meat from a goat’s shoulder, offered prayer, and did not perform ablution. The core topic is wudu after eating meat, especially goat or sheep meat. The report does not mention camel meat, cooked fire, or any other condition, so the explanation should not add those details. It simply shows that in this narration, eating from a goat’s shoulder was followed by prayer without a new ablution. For readers searching hadith about eating meat without wudu, this is a direct text. It also shows that actions of the Prophet صلى الله عليه وسلم were carefully observed and passed on as guidance."},"teachings":["The Prophet صلى الله عليه وسلم ate goat shoulder and then prayed.","In this report, he did not renew ablution after eating it.","The action was observed and narrated by Ibn Abbas.","The hadith should not be stretched beyond the meat and prayer mentioned."],"related_hadiths":[{"id":"207","book_id":"1","label":"Sahih Bukhari"},{"id":"210","book_id":"1","label":"Sahih Bukhari"},{"id":"354a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eating Goat Shoulder Without New Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم ate from a goat shoulder, prayed, and did not perform ablution."},"heading":{"title":"Eating Goat Shoulder and Praying Without Renewing Wudu","description":"This hadith is short and clear. Ibn Abbas says the Messenger of Allah صلى الله عليه وسلم took meat from a goat’s shoulder, offered prayer, and did not perform ablution. The core topic is wudu after eating meat, especially goat or sheep meat. The report does not mention camel meat, cooked fire, or any other condition, so the explanation should not add those details. It simply shows that in this narration, eating from a goat’s shoulder was followed by prayer without a new ablution. For readers searching hadith about eating meat without wudu, this is a direct text. It also shows that actions of the Prophet صلى الله عليه وسلم were carefully observed and passed on as guidance."},"teachings":["The Prophet صلى الله عليه وسلم ate goat shoulder and then prayed.","In this report, he did not renew ablution after eating it.","The action was observed and narrated by Ibn Abbas.","The hadith should not be stretched beyond the meat and prayer mentioned."],"related_hadiths":[{"id":"207","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"210","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"354a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E496" s="4" t="n"/>
@@ -11921,7 +11925,7 @@
       </c>
       <c r="D497" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Unreported Acts","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir says the Prophet did not raise his hands on first seeing the Ka‘bah."},"heading":{"title":"Hadith About Raising Hands When Seeing the Ka‘bah","description":"This Hadith is about a man who sees the Ka‘bah and raises his hands for prayer. Jabir ibn Abdullah replied that he did not find anyone doing this except the Jews, and he added that they performed Hajj with the Messenger of Allah صلى الله عليه وسلم, but he did not do so. The core topic is avoiding an act not reported from the Prophet صلى الله عليه وسلم in this setting. For searches like hadith about raising hands when seeing Kaaba or dua when seeing Kaaba, this narration gives Jabir’s direct answer. The meaning should stay limited to the action mentioned in the text."},"teachings":["Jabir compared the action with what he saw during Hajj with the Prophet صلى الله عليه وسلم.","The Prophet صلى الله عليه وسلم did not do this specific act in the report.","Worship practices should be checked against reported prophetic practice."],"related_hadiths":[{"id":"1568","book_id":"1","label":"Sahih Bukhari"},{"id":"1218","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Unreported Acts","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir says the Prophet did not raise his hands on first seeing the Ka‘bah."},"heading":{"title":"Hadith About Raising Hands When Seeing the Ka‘bah","description":"This Hadith is about a man who sees the Ka‘bah and raises his hands for prayer. Jabir ibn Abdullah replied that he did not find anyone doing this except the Jews, and he added that they performed Hajj with the Messenger of Allah صلى الله عليه وسلم, but he did not do so. The core topic is avoiding an act not reported from the Prophet صلى الله عليه وسلم in this setting. For searches like hadith about raising hands when seeing Kaaba or dua when seeing Kaaba, this narration gives Jabir’s direct answer. The meaning should stay limited to the action mentioned in the text."},"teachings":["Jabir compared the action with what he saw during Hajj with the Prophet صلى الله عليه وسلم.","The Prophet صلى الله عليه وسلم did not do this specific act in the report.","Worship practices should be checked against reported prophetic practice."],"related_hadiths":[{"id":"1568","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1218","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E497" s="4" t="n"/>
@@ -11944,7 +11948,7 @@
       </c>
       <c r="D498" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf and Prayer Behind Maqam","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet entered Makkah, made tawaf, and prayed two rak‘ahs behind the Maqam."},"heading":{"title":"Hadith About Tawaf and Two Rak‘ahs Behind Maqam","description":"This Hadith describes what the Prophet صلى الله عليه وسلم did when he entered Makkah on the day of the Conquest. He circumambulated the House and offered two rak‘ahs behind the Station of Ibrahim. The core topic is tawaf and prayer behind Maqam Ibrahim. For users searching for hadith about tawaf prayer, two rakahs after tawaf, or prayer behind Maqam Ibrahim, this narration gives a direct report. The Hadith does not expand into all rules of tawaf. It simply records that the Prophet صلى الله عليه وسلم entered Makkah, made tawaf, and prayed behind the Maqam."},"teachings":["The Prophet صلى الله عليه وسلم performed tawaf after entering Makkah in this report.","He prayed two rak‘ahs behind the Station.","The narration links tawaf with prayer behind Maqam Ibrahim."],"related_hadiths":[{"id":"395","book_id":"1","label":"Sahih Bukhari"},{"id":"1218","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf and Prayer Behind Maqam","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet entered Makkah, made tawaf, and prayed two rak‘ahs behind the Maqam."},"heading":{"title":"Hadith About Tawaf and Two Rak‘ahs Behind Maqam","description":"This Hadith describes what the Prophet صلى الله عليه وسلم did when he entered Makkah on the day of the Conquest. He circumambulated the House and offered two rak‘ahs behind the Station of Ibrahim. The core topic is tawaf and prayer behind Maqam Ibrahim. For users searching for hadith about tawaf prayer, two rakahs after tawaf, or prayer behind Maqam Ibrahim, this narration gives a direct report. The Hadith does not expand into all rules of tawaf. It simply records that the Prophet صلى الله عليه وسلم entered Makkah, made tawaf, and prayed behind the Maqam."},"teachings":["The Prophet صلى الله عليه وسلم performed tawaf after entering Makkah in this report.","He prayed two rak‘ahs behind the Station.","The narration links tawaf with prayer behind Maqam Ibrahim."],"related_hadiths":[{"id":"395","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1218","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E498" s="4" t="n"/>
@@ -11967,7 +11971,7 @@
       </c>
       <c r="D499" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr and Dua at Safa","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet touched the Stone, made tawaf, then remembered Allah and supplicated at Safa."},"heading":{"title":"Hadith About Dhikr and Dua at Safa","description":"This Hadith describes several actions after the Prophet صلى الله عليه وسلم entered Makkah. He went to the Stone, touched it, went around the Ka‘bah, then went to as-Safa and mounted it so he could look at the House. There he raised his hands, remembered Allah as much as he wished, praised Allah, and made supplication. The core topic is dhikr and dua at Safa. People search for hadith about dua at Safa, raising hands at Safa, or Prophet making dhikr after tawaf. This report gives those actions clearly and in order."},"teachings":["The Prophet صلى الله عليه وسلم touched the Stone before making tawaf in this report.","He remembered Allah and made dua at Safa.","He raised his hands at Safa, as stated in the narration."],"related_hadiths":[{"id":"1218","book_id":"2","label":"Sahih Muslim"},{"id":"1643","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dhikr and Dua at Safa","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet touched the Stone, made tawaf, then remembered Allah and supplicated at Safa."},"heading":{"title":"Hadith About Dhikr and Dua at Safa","description":"This Hadith describes several actions after the Prophet صلى الله عليه وسلم entered Makkah. He went to the Stone, touched it, went around the Ka‘bah, then went to as-Safa and mounted it so he could look at the House. There he raised his hands, remembered Allah as much as he wished, praised Allah, and made supplication. The core topic is dhikr and dua at Safa. People search for hadith about dua at Safa, raising hands at Safa, or Prophet making dhikr after tawaf. This report gives those actions clearly and in order."},"teachings":["The Prophet صلى الله عليه وسلم touched the Stone before making tawaf in this report.","He remembered Allah and made dua at Safa.","He raised his hands at Safa, as stated in the narration."],"related_hadiths":[{"id":"1218","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1643","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E499" s="4" t="n"/>
@@ -11990,7 +11994,7 @@
       </c>
       <c r="D500" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Kissing the Black Stone","description":"$book_name$ $hadith_number$ - $chapter_name$. Umar explains that kissing the Black Stone is done because the Prophet did it."},"heading":{"title":"Hadith About Kissing the Black Stone","description":"This Hadith gives a powerful statement from ‘Umar at the Black Stone. He said that he knew the Stone was only a stone and that it could neither benefit nor harm. He then said that if he had not seen the Messenger of Allah صلى الله عليه وسلم kissing it, he would not have kissed it. The core topic is following the Prophet صلى الله عليه وسلم in worship. For searches like hadith about Black Stone, Umar kissing Black Stone, or Black Stone cannot benefit or harm, this narration is very direct. It teaches that the act is followed because of the Prophet’s example, not because the stone itself has power."},"teachings":["The Black Stone itself does not benefit or harm.","‘Umar kissed it because he saw the Prophet صلى الله عليه وسلم do so.","The Hadith teaches following the Prophet صلى الله عليه وسلم without false beliefs about objects."],"related_hadiths":[{"id":"1597","book_id":"1","label":"Sahih Bukhari"},{"id":"1270","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Kissing the Black Stone","description":"$book_name$ $hadith_number$ - $chapter_name$. Umar explains that kissing the Black Stone is done because the Prophet did it."},"heading":{"title":"Hadith About Kissing the Black Stone","description":"This Hadith gives a powerful statement from ‘Umar at the Black Stone. He said that he knew the Stone was only a stone and that it could neither benefit nor harm. He then said that if he had not seen the Messenger of Allah صلى الله عليه وسلم kissing it, he would not have kissed it. The core topic is following the Prophet صلى الله عليه وسلم in worship. For searches like hadith about Black Stone, Umar kissing Black Stone, or Black Stone cannot benefit or harm, this narration is very direct. It teaches that the act is followed because of the Prophet’s example, not because the stone itself has power."},"teachings":["The Black Stone itself does not benefit or harm.","‘Umar kissed it because he saw the Prophet صلى الله عليه وسلم do so.","The Hadith teaches following the Prophet صلى الله عليه وسلم without false beliefs about objects."],"related_hadiths":[{"id":"1597","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1270","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E500" s="4" t="n"/>
@@ -12013,7 +12017,7 @@
       </c>
       <c r="D501" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Touching the Yamani Corners","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar says the Prophet touched only the two Yamani corners of the Ka‘bah."},"heading":{"title":"Hadith About Touching the Yamani Corners","description":"This Hadith records Ibn ‘Umar’s observation of the Prophet صلى الله عليه وسلم during tawaf. He said that he did not see the Messenger of Allah صلى الله عليه وسلم touching anything of the House except the two Yamani corners. The core topic is touching the corners of the Ka‘bah. For searches like Yamani corners hadith, touching Kaaba during tawaf, or which corners of Kaaba to touch, this narration gives a direct answer from what Ibn ‘Umar saw. The Hadith is specific and should not be stretched beyond its wording. It names only the two Yamani corners as touched in this report."},"teachings":["Ibn ‘Umar reported what he personally saw from the Prophet صلى الله عليه وسلم.","The Prophet صلى الله عليه وسلم touched only the two Yamani corners in this narration.","The Hadith helps keep tawaf actions tied to reported practice."],"related_hadiths":[{"id":"1609","book_id":"1","label":"Sahih Bukhari"},{"id":"1267","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Touching the Yamani Corners","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar says the Prophet touched only the two Yamani corners of the Ka‘bah."},"heading":{"title":"Hadith About Touching the Yamani Corners","description":"This Hadith records Ibn ‘Umar’s observation of the Prophet صلى الله عليه وسلم during tawaf. He said that he did not see the Messenger of Allah صلى الله عليه وسلم touching anything of the House except the two Yamani corners. The core topic is touching the corners of the Ka‘bah. For searches like Yamani corners hadith, touching Kaaba during tawaf, or which corners of Kaaba to touch, this narration gives a direct answer from what Ibn ‘Umar saw. The Hadith is specific and should not be stretched beyond its wording. It names only the two Yamani corners as touched in this report."},"teachings":["Ibn ‘Umar reported what he personally saw from the Prophet صلى الله عليه وسلم.","The Prophet صلى الله عليه وسلم touched only the two Yamani corners in this narration.","The Hadith helps keep tawaf actions tied to reported practice."],"related_hadiths":[{"id":"1609","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1267","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E501" s="4" t="n"/>
@@ -12036,7 +12040,7 @@
       </c>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Al-Hijr and the Ka‘bah Foundation","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar connects al-Hijr and the untouched corners to the Ka‘bah’s foundations."},"heading":{"title":"Hadith About Al-Hijr and the Ka‘bah","description":"This Hadith discusses a statement from ‘Aishah that part of al-Hijr is included in the Ka‘bah. Ibn ‘Umar said he thought she must have heard it from the Messenger of Allah صلى الله عليه وسلم. He then reasoned that the Prophet صلى الله عليه وسلم did not touch two corners because they were not on the foundations of the House, and that people did not make tawaf beyond al-Hijr for this reason. The core topic is al-Hijr and the Ka‘bah foundation. For searches like al-Hijr part of Kaaba hadith or why not touch all Kaaba corners, this report is closely related."},"teachings":["Ibn ‘Umar respected ‘Aishah’s report and linked it to prophetic knowledge.","The narration connects al-Hijr with the structure of the Ka‘bah.","It explains why some corners were not touched in tawaf."],"related_hadiths":[{"id":"1586","book_id":"1","label":"Sahih Bukhari"},{"id":"1333","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Al-Hijr and the Ka‘bah Foundation","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar connects al-Hijr and the untouched corners to the Ka‘bah’s foundations."},"heading":{"title":"Hadith About Al-Hijr and the Ka‘bah","description":"This Hadith discusses a statement from ‘Aishah that part of al-Hijr is included in the Ka‘bah. Ibn ‘Umar said he thought she must have heard it from the Messenger of Allah صلى الله عليه وسلم. He then reasoned that the Prophet صلى الله عليه وسلم did not touch two corners because they were not on the foundations of the House, and that people did not make tawaf beyond al-Hijr for this reason. The core topic is al-Hijr and the Ka‘bah foundation. For searches like al-Hijr part of Kaaba hadith or why not touch all Kaaba corners, this report is closely related."},"teachings":["Ibn ‘Umar respected ‘Aishah’s report and linked it to prophetic knowledge.","The narration connects al-Hijr with the structure of the Ka‘bah.","It explains why some corners were not touched in tawaf."],"related_hadiths":[{"id":"1586","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1333","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E502" s="4" t="n"/>
@@ -12059,7 +12063,7 @@
       </c>
       <c r="D503" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Touching the Black Stone and Yamani Corner","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet touched the Yamani Corner and Black Stone in each circuit of tawaf."},"heading":{"title":"Hadith About Touching the Black Stone and Yamani Corner","description":"This Hadith reports that the Messenger of Allah صلى الله عليه وسلم did not leave touching the Yamani corner and the Black Stone in each circuit of tawaf. It also says that Ibn ‘Umar used to do the same. The core topic is tawaf practice at the Ka‘bah. For people searching for touching Black Stone during tawaf, Rukn Yamani hadith, or tawaf each round hadith, this narration gives a clear practice. The text does not mention touching every part of the Ka‘bah. It names the Yamani corner and the Black Stone as the places touched in each circuit."},"teachings":["The Prophet صلى الله عليه وسلم touched the Yamani corner and Black Stone in each circuit.","Ibn ‘Umar followed this practice.","The narration keeps the action limited to the places named."],"related_hadiths":[{"id":"1609","book_id":"1","label":"Sahih Bukhari"},{"id":"1267","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Touching the Black Stone and Yamani Corner","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet touched the Yamani Corner and Black Stone in each circuit of tawaf."},"heading":{"title":"Hadith About Touching the Black Stone and Yamani Corner","description":"This Hadith reports that the Messenger of Allah صلى الله عليه وسلم did not leave touching the Yamani corner and the Black Stone in each circuit of tawaf. It also says that Ibn ‘Umar used to do the same. The core topic is tawaf practice at the Ka‘bah. For people searching for touching Black Stone during tawaf, Rukn Yamani hadith, or tawaf each round hadith, this narration gives a clear practice. The text does not mention touching every part of the Ka‘bah. It names the Yamani corner and the Black Stone as the places touched in each circuit."},"teachings":["The Prophet صلى الله عليه وسلم touched the Yamani corner and Black Stone in each circuit.","Ibn ‘Umar followed this practice.","The narration keeps the action limited to the places named."],"related_hadiths":[{"id":"1609","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1267","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E503" s="4" t="n"/>
@@ -12082,7 +12086,7 @@
       </c>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf on a Camel","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet made tawaf on a camel and touched the corner with a stick."},"heading":{"title":"Hadith About Tawaf on a Camel","description":"This Hadith reports that during the Farewell Pilgrimage, the Messenger of Allah صلى الله عليه وسلم performed tawaf on a camel and touched the corner with a crooked stick. The core topic is tawaf on a mount. For search terms like Prophet tawaf on camel, touching Black Stone with stick, or Farewell Hajj tawaf hadith, this narration is directly related. The Hadith shows the action as it happened in that setting. It does not give a long reason here, so the explanation should stay close: the Prophet صلى الله عليه وسلم made tawaf while mounted and used a stick to touch the corner."},"teachings":["The Prophet صلى الله عليه وسلم performed tawaf on a camel in this report.","He touched the corner with a crooked stick.","The narration records a practice from the Farewell Pilgrimage."],"related_hadiths":[{"id":"1612","book_id":"1","label":"Sahih Bukhari"},{"id":"1272","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf on a Camel","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet made tawaf on a camel and touched the corner with a stick."},"heading":{"title":"Hadith About Tawaf on a Camel","description":"This Hadith reports that during the Farewell Pilgrimage, the Messenger of Allah صلى الله عليه وسلم performed tawaf on a camel and touched the corner with a crooked stick. The core topic is tawaf on a mount. For search terms like Prophet tawaf on camel, touching Black Stone with stick, or Farewell Hajj tawaf hadith, this narration is directly related. The Hadith shows the action as it happened in that setting. It does not give a long reason here, so the explanation should stay close: the Prophet صلى الله عليه وسلم made tawaf while mounted and used a stick to touch the corner."},"teachings":["The Prophet صلى الله عليه وسلم performed tawaf on a camel in this report.","He touched the corner with a crooked stick.","The narration records a practice from the Farewell Pilgrimage."],"related_hadiths":[{"id":"1612","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1272","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E504" s="4" t="n"/>
@@ -12105,7 +12109,7 @@
       </c>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf During the Conquest","description":"$book_name$ $hadith_number$ - $chapter_name$. Safiyyah saw the Prophet make tawaf on a camel and touch the corner with a stick."},"heading":{"title":"Hadith About Tawaf on a Camel During the Conquest","description":"This Hadith reports what Safiyyah bint Shaybah saw in Makkah during the year of the Conquest. After the Messenger of Allah صلى الله عليه وسلم had some rest, he performed tawaf on a camel and touched the corner with a crooked stick in his hand. The core topic is tawaf on a camel. For searches like Safiyyah bint Shaybah tawaf hadith, Prophet tawaf on camel, or touching the corner with a stick, this narration gives an eyewitness report. The words “I was looking at him” make the report very direct, but the explanation should remain tied to this action."},"teachings":["Safiyyah bint Shaybah witnessed the Prophet صلى الله عليه وسلم making tawaf.","The Prophet صلى الله عليه وسلم performed tawaf on a camel in this report.","He touched the corner with a crooked stick."],"related_hadiths":[{"id":"1612","book_id":"1","label":"Sahih Bukhari"},{"id":"1272","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf During the Conquest","description":"$book_name$ $hadith_number$ - $chapter_name$. Safiyyah saw the Prophet make tawaf on a camel and touch the corner with a stick."},"heading":{"title":"Hadith About Tawaf on a Camel During the Conquest","description":"This Hadith reports what Safiyyah bint Shaybah saw in Makkah during the year of the Conquest. After the Messenger of Allah صلى الله عليه وسلم had some rest, he performed tawaf on a camel and touched the corner with a crooked stick in his hand. The core topic is tawaf on a camel. For searches like Safiyyah bint Shaybah tawaf hadith, Prophet tawaf on camel, or touching the corner with a stick, this narration gives an eyewitness report. The words “I was looking at him” make the report very direct, but the explanation should remain tied to this action."},"teachings":["Safiyyah bint Shaybah witnessed the Prophet صلى الله عليه وسلم making tawaf.","The Prophet صلى الله عليه وسلم performed tawaf on a camel in this report.","He touched the corner with a crooked stick."],"related_hadiths":[{"id":"1612","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1272","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E505" s="4" t="n"/>
@@ -12128,7 +12132,7 @@
       </c>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf and Sa‘i on a Mount","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports tawaf on a camel, touching the corner with a stick, and sa‘i on a mount."},"heading":{"title":"Hadith About Tawaf and Sa‘i on a Camel","description":"This Hadith reports that Abu al-Tufail saw the Prophet صلى الله عليه وسلم making tawaf around the House on his riding animal. He touched the corner with his crooked stick and then kissed the stick. The added wording says he then went to al-Safa and al-Marwah and completed seven rounds on his riding animal. The core topic is tawaf and sa‘i on a mount. For searches like Prophet did sa‘i on camel, tawaf on camel hadith, or kissed the stick after touching Black Stone, this narration gives a clear description of what was seen."},"teachings":["The Prophet صلى الله عليه وسلم made tawaf on his riding animal in this report.","He touched the corner with a stick and kissed the stick.","The added report mentions seven rounds between Safa and Marwah on his mount."],"related_hadiths":[{"id":"1612","book_id":"1","label":"Sahih Bukhari"},{"id":"1272","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf and Sa‘i on a Mount","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports tawaf on a camel, touching the corner with a stick, and sa‘i on a mount."},"heading":{"title":"Hadith About Tawaf and Sa‘i on a Camel","description":"This Hadith reports that Abu al-Tufail saw the Prophet صلى الله عليه وسلم making tawaf around the House on his riding animal. He touched the corner with his crooked stick and then kissed the stick. The added wording says he then went to al-Safa and al-Marwah and completed seven rounds on his riding animal. The core topic is tawaf and sa‘i on a mount. For searches like Prophet did sa‘i on camel, tawaf on camel hadith, or kissed the stick after touching Black Stone, this narration gives a clear description of what was seen."},"teachings":["The Prophet صلى الله عليه وسلم made tawaf on his riding animal in this report.","He touched the corner with a stick and kissed the stick.","The added report mentions seven rounds between Safa and Marwah on his mount."],"related_hadiths":[{"id":"1612","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1272","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E506" s="4" t="n"/>
@@ -12151,7 +12155,7 @@
       </c>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mutton, Adhan, and Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم cut roasted mutton for his guest, then rose for prayer when Bilal called him."},"heading":{"title":"Mutton and Prayer Hadith: Responding When Salah Is Called","description":"This hadith describes a night when Al-Mughirah ibn Shu'bah was the Prophet’s guest. The Prophet صلى الله عليه وسلم ordered a piece of mutton to be roasted and cut it with a knife for him. Then Bilal came and called him to prayer. The Prophet صلى الله عليه وسلم threw the knife aside, made a brief remark, and stood for prayer. The report also includes an added note about trimming a long moustache using a tooth-stick. The main searchable topic is eating meat and prayer, because the Prophet صلى الله عليه وسلم moved from the meal setting to salah. The text does not explicitly say he performed wudu at that moment, so the explanation should avoid adding that. It shows readiness to answer the call to prayer."},"teachings":["The Prophet صلى الله عليه وسلم honored his guest by serving him food.","When Bilal called for prayer, the Prophet صلى الله عليه وسلم stood for salah.","The report shows movement from food to worship.","The added note mentions trimming a long moustache with a tooth-stick."],"related_hadiths":[{"id":"675","book_id":"1","label":"Sahih Bukhari"},{"id":"207","book_id":"1","label":"Sahih Bukhari"},{"id":"354a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mutton, Adhan, and Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم cut roasted mutton for his guest, then rose for prayer when Bilal called him."},"heading":{"title":"Mutton and Prayer Hadith: Responding When Salah Is Called","description":"This hadith describes a night when Al-Mughirah ibn Shu'bah was the Prophet’s guest. The Prophet صلى الله عليه وسلم ordered a piece of mutton to be roasted and cut it with a knife for him. Then Bilal came and called him to prayer. The Prophet صلى الله عليه وسلم threw the knife aside, made a brief remark, and stood for prayer. The report also includes an added note about trimming a long moustache using a tooth-stick. The main searchable topic is eating meat and prayer, because the Prophet صلى الله عليه وسلم moved from the meal setting to salah. The text does not explicitly say he performed wudu at that moment, so the explanation should avoid adding that. It shows readiness to answer the call to prayer."},"teachings":["The Prophet صلى الله عليه وسلم honored his guest by serving him food.","When Bilal called for prayer, the Prophet صلى الله عليه وسلم stood for salah.","The report shows movement from food to worship.","The added note mentions trimming a long moustache with a tooth-stick."],"related_hadiths":[{"id":"675","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"207","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"354a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E507" s="4" t="n"/>
@@ -12174,7 +12178,7 @@
       </c>
       <c r="D508" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf While Ill","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet performed tawaf while ill, touched the Black Stone with a stick, then prayed two rak’ahs."},"heading":{"title":"Tawaf While Ill: A Clear Hadith About Ease in Worship","description":"This hadith about tawaf while ill shows a simple and practical scene from the Prophet’s pilgrimage practice. When the Messenger of Allah صلى الله عليه وسلم came to Makkah while unwell, he performed circumambulation on his camel. Each time he reached the corner of the Black Stone, he touched it with a crooked stick. After finishing tawaf, he made his camel kneel and prayed two rak’ahs. The core message is that worship is still honored even when a person is facing weakness. The text also shows care for the rites of tawaf, touching the Black Stone, and praying after tawaf, without adding hardship beyond the situation."},"teachings":["Illness did not stop the Prophet صلى الله عليه وسلم from completing tawaf when he was able to do it.","The Black Stone was touched with a stick when direct contact was not described.","Two rak’ahs were prayed after the circumambulation was completed."],"related_hadiths":[{"id":"1633","book_id":"1","label":"Sahih Bukhari"},{"id":"1616","book_id":"1","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf While Ill","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet performed tawaf while ill, touched the Black Stone with a stick, then prayed two rak’ahs."},"heading":{"title":"Tawaf While Ill: A Clear Hadith About Ease in Worship","description":"This hadith about tawaf while ill shows a simple and practical scene from the Prophet’s pilgrimage practice. When the Messenger of Allah صلى الله عليه وسلم came to Makkah while unwell, he performed circumambulation on his camel. Each time he reached the corner of the Black Stone, he touched it with a crooked stick. After finishing tawaf, he made his camel kneel and prayed two rak’ahs. The core message is that worship is still honored even when a person is facing weakness. The text also shows care for the rites of tawaf, touching the Black Stone, and praying after tawaf, without adding hardship beyond the situation."},"teachings":["Illness did not stop the Prophet صلى الله عليه وسلم from completing tawaf when he was able to do it.","The Black Stone was touched with a stick when direct contact was not described.","Two rak’ahs were prayed after the circumambulation was completed."],"related_hadiths":[{"id":"1633","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1616","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E508" s="4" t="n"/>
@@ -12197,7 +12201,7 @@
       </c>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Understanding Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas explains ramal and sa’i on a camel, separating what happened from what was called Sunnah."},"heading":{"title":"Understanding Sunnah: Ibn Abbas on Ramal and Sa’i on a Camel","description":"This hadith about understanding Sunnah is important because Ibn Abbas separates an event from a general practice. Abu al-Tufail asked him about people saying that the Prophet صلى الله عليه وسلم did ramal around the Ka’bah and that it was Sunnah. Ibn Abbas said they were partly right and partly wrong. He confirmed that the Prophet صلى الله عليه وسلم did ramal, but explained that it was done in a specific situation connected to Quraysh and the treaty period. He also explained that the Prophet صلى الله عليه وسلم did sa’i on a camel so people could hear him and see him, and so their hands would not reach him. The main lesson is to be careful when calling something Sunnah without understanding the report."},"teachings":["Ibn Abbas confirmed that the Prophet صلى الله عليه وسلم did ramal, but discussed its specific setting.","He explained that sa’i on a camel helped people hear and see the Prophet صلى الله عليه وسلم.","The hadith teaches caution before turning every reported action into a general claim."],"related_hadiths":[{"id":"1602","book_id":"1","label":"Sahih Bukhari"},{"id":"1616","book_id":"1","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Understanding Sunnah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas explains ramal and sa’i on a camel, separating what happened from what was called Sunnah."},"heading":{"title":"Understanding Sunnah: Ibn Abbas on Ramal and Sa’i on a Camel","description":"This hadith about understanding Sunnah is important because Ibn Abbas separates an event from a general practice. Abu al-Tufail asked him about people saying that the Prophet صلى الله عليه وسلم did ramal around the Ka’bah and that it was Sunnah. Ibn Abbas said they were partly right and partly wrong. He confirmed that the Prophet صلى الله عليه وسلم did ramal, but explained that it was done in a specific situation connected to Quraysh and the treaty period. He also explained that the Prophet صلى الله عليه وسلم did sa’i on a camel so people could hear him and see him, and so their hands would not reach him. The main lesson is to be careful when calling something Sunnah without understanding the report."},"teachings":["Ibn Abbas confirmed that the Prophet صلى الله عليه وسلم did ramal, but discussed its specific setting.","He explained that sa’i on a camel helped people hear and see the Prophet صلى الله عليه وسلم.","The hadith teaches caution before turning every reported action into a general claim."],"related_hadiths":[{"id":"1602","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1616","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E509" s="4" t="n"/>
@@ -12220,7 +12224,7 @@
       </c>
       <c r="D510" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ramal and Mercy","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet ordered ramal in three circuits while showing mercy by not ordering it in all circuits."},"heading":{"title":"Ramal and Mercy: A Hadith About Strength and Ease in Tawaf","description":"This hadith about ramal and mercy explains why the Companions were told to walk proudly with a swift pace in the first three circuits. Ibn Abbas said the Prophet صلى الله عليه وسلم came to Makkah when the fever of Yathrib had weakened them. The disbelievers said these people had been weakened by fever. Allah informed His Prophet صلى الله عليه وسلم of what they said, so he ordered the Companions to perform ramal in three circuits and walk normally between the two corners. When the disbelievers saw them, they said they were stronger than expected. Ibn Abbas also said the Prophet صلى الله عليه وسلم did not order ramal in all circuits out of mercy for them."},"teachings":["Ramal was ordered in three circuits in response to what the disbelievers had said.","The Companions walked normally between the two corners in this report.","Ibn Abbas linked the limited number of circuits to mercy for the Companions."],"related_hadiths":[{"id":"1602","book_id":"1","label":"Sahih Bukhari"},{"id":"1616","book_id":"1","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ramal and Mercy","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet ordered ramal in three circuits while showing mercy by not ordering it in all circuits."},"heading":{"title":"Ramal and Mercy: A Hadith About Strength and Ease in Tawaf","description":"This hadith about ramal and mercy explains why the Companions were told to walk proudly with a swift pace in the first three circuits. Ibn Abbas said the Prophet صلى الله عليه وسلم came to Makkah when the fever of Yathrib had weakened them. The disbelievers said these people had been weakened by fever. Allah informed His Prophet صلى الله عليه وسلم of what they said, so he ordered the Companions to perform ramal in three circuits and walk normally between the two corners. When the disbelievers saw them, they said they were stronger than expected. Ibn Abbas also said the Prophet صلى الله عليه وسلم did not order ramal in all circuits out of mercy for them."},"teachings":["Ramal was ordered in three circuits in response to what the disbelievers had said.","The Companions walked normally between the two corners in this report.","Ibn Abbas linked the limited number of circuits to mercy for the Companions."],"related_hadiths":[{"id":"1602","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1616","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E510" s="4" t="n"/>
@@ -12243,7 +12247,7 @@
       </c>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Remembrance of Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. Tawaf, sa’i, and stoning the pillars are meant for establishing the remembrance of Allah."},"heading":{"title":"Remembrance of Allah: The Purpose of Tawaf, Sa’i, and Jamarat","description":"This hadith about remembrance of Allah gives a clear purpose for major pilgrimage actions. The Messenger of Allah صلى الله عليه وسلم said that going round the House, running between Safa and Marwah, and throwing pebbles at the pillars were made for establishing the remembrance of Allah. The hadith keeps the focus of Hajj and Umrah rituals on dhikr, not just movement. Tawaf around the Ka’bah, sa’i between Safa and Marwah, and ramy of the jamarat are physical acts, but this report points to their inner meaning: remembering Allah. A simple reading of the hadith teaches that these rites should not become empty motions. They are acts tied to worship and remembrance."},"teachings":["Tawaf is connected to the remembrance of Allah.","Sa’i between Safa and Marwah is also linked to remembering Allah.","Throwing pebbles at the pillars is described as being for Allah’s remembrance."],"related_hadiths":[{"id":"1616","book_id":"1","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","label":"Sahih Bukhari"},{"id":"1633","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Remembrance of Allah","description":"$book_name$ $hadith_number$ - $chapter_name$. Tawaf, sa’i, and stoning the pillars are meant for establishing the remembrance of Allah."},"heading":{"title":"Remembrance of Allah: The Purpose of Tawaf, Sa’i, and Jamarat","description":"This hadith about remembrance of Allah gives a clear purpose for major pilgrimage actions. The Messenger of Allah صلى الله عليه وسلم said that going round the House, running between Safa and Marwah, and throwing pebbles at the pillars were made for establishing the remembrance of Allah. The hadith keeps the focus of Hajj and Umrah rituals on dhikr, not just movement. Tawaf around the Ka’bah, sa’i between Safa and Marwah, and ramy of the jamarat are physical acts, but this report points to their inner meaning: remembering Allah. A simple reading of the hadith teaches that these rites should not become empty motions. They are acts tied to worship and remembrance."},"teachings":["Tawaf is connected to the remembrance of Allah.","Sa’i between Safa and Marwah is also linked to remembering Allah.","Throwing pebbles at the pillars is described as being for Allah’s remembrance."],"related_hadiths":[{"id":"1616","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1633","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E511" s="4" t="n"/>
@@ -12266,7 +12270,7 @@
       </c>
       <c r="D512" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ramal in Tawaf","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet touched the Black Stone, said Allahu Akbar, and did ramal in three circuits."},"heading":{"title":"Ramal in Tawaf: Touching the Black Stone and Saying Allahu Akbar","description":"This hadith about ramal in tawaf describes several actions together. Ibn Abbas reported that the Prophet صلى الله عليه وسلم wore the mantle under his right armpit with the end over his left shoulder. He touched the corner, said “Allah is most great,” and then walked proudly in three circuits of tawaf. The report also says that when the Companions were hidden from the Quraysh near the Yamani corner, they walked normally, and when they appeared, they did ramal. Quraysh compared them to deer. Ibn Abbas said this became Sunnah. The hadith is strongly linked to ramal, idtiba, touching the Black Stone, and takbeer during tawaf."},"teachings":["The Prophet صلى الله عليه وسلم touched the corner and said Allahu Akbar.","Ramal was done in three circuits in this report.","The Companions alternated between normal walking and ramal based on visibility to Quraysh."],"related_hadiths":[{"id":"1602","book_id":"1","label":"Sahih Bukhari"},{"id":"1616","book_id":"1","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ramal in Tawaf","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet touched the Black Stone, said Allahu Akbar, and did ramal in three circuits."},"heading":{"title":"Ramal in Tawaf: Touching the Black Stone and Saying Allahu Akbar","description":"This hadith about ramal in tawaf describes several actions together. Ibn Abbas reported that the Prophet صلى الله عليه وسلم wore the mantle under his right armpit with the end over his left shoulder. He touched the corner, said “Allah is most great,” and then walked proudly in three circuits of tawaf. The report also says that when the Companions were hidden from the Quraysh near the Yamani corner, they walked normally, and when they appeared, they did ramal. Quraysh compared them to deer. Ibn Abbas said this became Sunnah. The hadith is strongly linked to ramal, idtiba, touching the Black Stone, and takbeer during tawaf."},"teachings":["The Prophet صلى الله عليه وسلم touched the corner and said Allahu Akbar.","Ramal was done in three circuits in this report.","The Companions alternated between normal walking and ramal based on visibility to Quraysh."],"related_hadiths":[{"id":"1602","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1616","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E512" s="4" t="n"/>
@@ -12289,7 +12293,7 @@
       </c>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Hands After Eating Meat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم ate from a shoulder, wiped his hand on a cloth, then stood and prayed."},"heading":{"title":"Wiping Hands After Eating Meat Before Prayer","description":"This hadith reports that the Messenger of Allah صلى الله عليه وسلم ate from a shoulder, wiped his hand with a cloth that was under him, then got up and prayed. The main topic is eating meat and prayer without mention of a fresh wudu. The report focuses on wiping the hand before standing for prayer. It does not say that he washed with water or renewed ablution. For searches like wiping hands after eating meat hadith, the teaching is simple: the action described was eating, wiping the hand, and then praying. A careful reader should notice what is stated and what is not stated. The narration gives a small but useful detail about cleanliness before prayer."},"teachings":["The Prophet صلى الله عليه وسلم wiped his hand after eating.","He then stood and prayed in this report.","The text does not mention a fresh ablution.","Small actions of cleanliness were observed and narrated."],"related_hadiths":[{"id":"207","book_id":"1","label":"Sahih Bukhari"},{"id":"210","book_id":"1","label":"Sahih Bukhari"},{"id":"354a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Hands After Eating Meat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم ate from a shoulder, wiped his hand on a cloth, then stood and prayed."},"heading":{"title":"Wiping Hands After Eating Meat Before Prayer","description":"This hadith reports that the Messenger of Allah صلى الله عليه وسلم ate from a shoulder, wiped his hand with a cloth that was under him, then got up and prayed. The main topic is eating meat and prayer without mention of a fresh wudu. The report focuses on wiping the hand before standing for prayer. It does not say that he washed with water or renewed ablution. For searches like wiping hands after eating meat hadith, the teaching is simple: the action described was eating, wiping the hand, and then praying. A careful reader should notice what is stated and what is not stated. The narration gives a small but useful detail about cleanliness before prayer."},"teachings":["The Prophet صلى الله عليه وسلم wiped his hand after eating.","He then stood and prayed in this report.","The text does not mention a fresh ablution.","Small actions of cleanliness were observed and narrated."],"related_hadiths":[{"id":"207","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"210","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"354a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E513" s="4" t="n"/>
@@ -12312,7 +12316,7 @@
       </c>
       <c r="D514" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ramal from Stone to Stone","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar performed ramal from the Black Stone to the Black Stone and linked it to the Prophet."},"heading":{"title":"Ramal from Stone to Stone: Ibn Umar’s Report on Tawaf","description":"This hadith about ramal from stone to stone is a brief report from Nafi’. He said Ibn Umar did ramal from the corner of the Black Stone back to the corner of the Black Stone. Ibn Umar also mentioned that the Messenger of Allah صلى الله عليه وسلم had done that. The hadith focuses on the full circuit from the Black Stone to the Black Stone. It does not give extra details about the number of rounds in this wording, so the explanation should not add more than the text states. The related search terms are ramal in tawaf, Black Stone to Black Stone, and Ibn Umar tawaf hadith."},"teachings":["Ibn Umar performed ramal from the Black Stone back to the Black Stone.","He connected this action to what the Prophet صلى الله عليه وسلم had done.","The hadith preserves a specific way of moving during tawaf."],"related_hadiths":[{"id":"1602","book_id":"1","label":"Sahih Bukhari"},{"id":"1616","book_id":"1","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ramal from Stone to Stone","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar performed ramal from the Black Stone to the Black Stone and linked it to the Prophet."},"heading":{"title":"Ramal from Stone to Stone: Ibn Umar’s Report on Tawaf","description":"This hadith about ramal from stone to stone is a brief report from Nafi’. He said Ibn Umar did ramal from the corner of the Black Stone back to the corner of the Black Stone. Ibn Umar also mentioned that the Messenger of Allah صلى الله عليه وسلم had done that. The hadith focuses on the full circuit from the Black Stone to the Black Stone. It does not give extra details about the number of rounds in this wording, so the explanation should not add more than the text states. The related search terms are ramal in tawaf, Black Stone to Black Stone, and Ibn Umar tawaf hadith."},"teachings":["Ibn Umar performed ramal from the Black Stone back to the Black Stone.","He connected this action to what the Prophet صلى الله عليه وسلم had done.","The hadith preserves a specific way of moving during tawaf."],"related_hadiths":[{"id":"1602","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1616","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E514" s="4" t="n"/>
@@ -12335,7 +12339,7 @@
       </c>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sa’i Between Safa and Marwah","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir said the Prophet and his Companions ran between Safa and Marwah only once."},"heading":{"title":"Sa’i Between Safa and Marwah: Jabir’s Report on One Running","description":"This hadith about sa’i between Safa and Marwah reports the statement of Jabir ibn Abdullah. He said that neither the Prophet صلى الله عليه وسلم nor his Companions ran between Safa and Marwah except once, and that was his first running. The main focus is the number of times this running occurred in the report. The wording does not give a full step-by-step guide to sa’i, nor does it discuss other details of Hajj or Umrah. So the explanation stays close to the text: Jabir is describing the Prophet صلى الله عليه وسلم and the Companions, and he limits the running between Safa and Marwah to the first running mentioned here."},"teachings":["Jabir reported that the Prophet صلى الله عليه وسلم ran between Safa and Marwah once.","He included the Companions in this description.","The report identifies that running as the first running."],"related_hadiths":[{"id":"1643","book_id":"1","label":"Sahih Bukhari"},{"id":"1644","book_id":"1","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sa’i Between Safa and Marwah","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir said the Prophet and his Companions ran between Safa and Marwah only once."},"heading":{"title":"Sa’i Between Safa and Marwah: Jabir’s Report on One Running","description":"This hadith about sa’i between Safa and Marwah reports the statement of Jabir ibn Abdullah. He said that neither the Prophet صلى الله عليه وسلم nor his Companions ran between Safa and Marwah except once, and that was his first running. The main focus is the number of times this running occurred in the report. The wording does not give a full step-by-step guide to sa’i, nor does it discuss other details of Hajj or Umrah. So the explanation stays close to the text: Jabir is describing the Prophet صلى الله عليه وسلم and the Companions, and he limits the running between Safa and Marwah to the first running mentioned here."},"teachings":["Jabir reported that the Prophet صلى الله عليه وسلم ran between Safa and Marwah once.","He included the Companions in this description.","The report identifies that running as the first running."],"related_hadiths":[{"id":"1643","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1644","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1691","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E515" s="4" t="n"/>
@@ -12358,7 +12362,7 @@
       </c>
       <c r="D516" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Order of Hajj Rites","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah said the Companions did not perform tawaf until they threw pebbles at the Jamrah."},"heading":{"title":"Order of Hajj Rites: Throwing Pebbles Before Tawaf","description":"This hadith about the order of Hajj rites is reported from Aishah, the Mother of the Believers. She said that the Companions of the Messenger of Allah صلى الله عليه وسلم who were with him did not go round the Ka’bah until they threw pebbles at the Jamrah. The text is brief but clear. It connects two Hajj actions: throwing pebbles at the pillar in Mina and then performing tawaf. The hadith does not add all details of the Hajj schedule, so the explanation should not expand beyond the given wording. Its main value is showing the order mentioned in this report."},"teachings":["The Companions with the Prophet صلى الله عليه وسلم threw pebbles before performing tawaf in this report.","The hadith connects Jamrah with tawaf during Hajj.","Aishah’s statement preserves the sequence of these actions."],"related_hadiths":[{"id":"1732","book_id":"1","label":"Sahih Bukhari"},{"id":"1733","book_id":"1","label":"Sahih Bukhari"},{"id":"1751","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Order of Hajj Rites","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah said the Companions did not perform tawaf until they threw pebbles at the Jamrah."},"heading":{"title":"Order of Hajj Rites: Throwing Pebbles Before Tawaf","description":"This hadith about the order of Hajj rites is reported from Aishah, the Mother of the Believers. She said that the Companions of the Messenger of Allah صلى الله عليه وسلم who were with him did not go round the Ka’bah until they threw pebbles at the Jamrah. The text is brief but clear. It connects two Hajj actions: throwing pebbles at the pillar in Mina and then performing tawaf. The hadith does not add all details of the Hajj schedule, so the explanation should not expand beyond the given wording. Its main value is showing the order mentioned in this report."},"teachings":["The Companions with the Prophet صلى الله عليه وسلم threw pebbles before performing tawaf in this report.","The hadith connects Jamrah with tawaf during Hajj.","Aishah’s statement preserves the sequence of these actions."],"related_hadiths":[{"id":"1732","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1733","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1751","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E516" s="4" t="n"/>
@@ -12381,7 +12385,7 @@
       </c>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf and Sa’i Sufficiency","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet told Aishah her tawaf and sa’i were sufficient for her Hajj and Umrah."},"heading":{"title":"Tawaf and Sa’i Sufficiency: A Hadith About Hajj and Umrah","description":"This hadith about tawaf and sa’i sufficiency reports that the Prophet صلى الله عليه وسلم told Aishah: “Your tawaf of the House and between Safa and Marwah is sufficient for your Hajj and your Umrah.” The wording centers on two acts: circumambulation of the Ka’bah and going between Safa and Marwah. It also mentions that al-Shafi’i discussed how Sufyan narrated the report, sometimes through Aishah and sometimes as a statement to Aishah. The main teaching from the text is that, in this report, the Prophet صلى الله عليه وسلم linked her tawaf and sa’i to sufficiency for both Hajj and Umrah."},"teachings":["The Prophet صلى الله عليه وسلم mentioned tawaf of the House and sa’i between Safa and Marwah.","He said these were sufficient for Aishah’s Hajj and Umrah.","The report also notes a narration detail mentioned by al-Shafi’i."],"related_hadiths":[{"id":"1785","book_id":"1","label":"Sahih Bukhari"},{"id":"1786","book_id":"1","label":"Sahih Bukhari"},{"id":"1643","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf and Sa’i Sufficiency","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet told Aishah her tawaf and sa’i were sufficient for her Hajj and Umrah."},"heading":{"title":"Tawaf and Sa’i Sufficiency: A Hadith About Hajj and Umrah","description":"This hadith about tawaf and sa’i sufficiency reports that the Prophet صلى الله عليه وسلم told Aishah: “Your tawaf of the House and between Safa and Marwah is sufficient for your Hajj and your Umrah.” The wording centers on two acts: circumambulation of the Ka’bah and going between Safa and Marwah. It also mentions that al-Shafi’i discussed how Sufyan narrated the report, sometimes through Aishah and sometimes as a statement to Aishah. The main teaching from the text is that, in this report, the Prophet صلى الله عليه وسلم linked her tawaf and sa’i to sufficiency for both Hajj and Umrah."},"teachings":["The Prophet صلى الله عليه وسلم mentioned tawaf of the House and sa’i between Safa and Marwah.","He said these were sufficient for Aishah’s Hajj and Umrah.","The report also notes a narration detail mentioned by al-Shafi’i."],"related_hadiths":[{"id":"1785","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1786","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1643","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E517" s="4" t="n"/>
@@ -12404,7 +12408,7 @@
       </c>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Embracing the Ka’bah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet and his Companions placed their cheeks on the House from the door to al-Hatim."},"heading":{"title":"Embracing the Ka’bah: A Report from the Conquest of Makkah","description":"This hadith about embracing the Ka’bah reports what AbdurRahman ibn Safwan saw when the Messenger of Allah صلى الله عليه وسلم conquered Makkah. He went out to watch how the Prophet صلى الله عليه وسلم would act. He saw the Prophet صلى الله عليه وسلم and his Companions coming out from the Ka’bah. They embraced the House from its entrance to al-Hatim and placed their cheeks on the House, while the Messenger of Allah صلى الله عليه وسلم was among them. The report gives a vivid description of their closeness to the Ka’bah at that moment. It does not add a general command, so the explanation stays with what was seen and reported."},"teachings":["The narrator wanted to observe how the Prophet صلى الله عليه وسلم behaved after the conquest of Makkah.","The Prophet صلى الله عليه وسلم and his Companions embraced the House from the door to al-Hatim.","They placed their cheeks on the House in this report."],"related_hadiths":[{"id":"1598","book_id":"1","label":"Sahih Bukhari"},{"id":"1601","book_id":"1","label":"Sahih Bukhari"},{"id":"4288","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Embracing the Ka’bah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet and his Companions placed their cheeks on the House from the door to al-Hatim."},"heading":{"title":"Embracing the Ka’bah: A Report from the Conquest of Makkah","description":"This hadith about embracing the Ka’bah reports what AbdurRahman ibn Safwan saw when the Messenger of Allah صلى الله عليه وسلم conquered Makkah. He went out to watch how the Prophet صلى الله عليه وسلم would act. He saw the Prophet صلى الله عليه وسلم and his Companions coming out from the Ka’bah. They embraced the House from its entrance to al-Hatim and placed their cheeks on the House, while the Messenger of Allah صلى الله عليه وسلم was among them. The report gives a vivid description of their closeness to the Ka’bah at that moment. It does not add a general command, so the explanation stays with what was seen and reported."},"teachings":["The narrator wanted to observe how the Prophet صلى الله عليه وسلم behaved after the conquest of Makkah.","The Prophet صلى الله عليه وسلم and his Companions embraced the House from the door to al-Hatim.","They placed their cheeks on the House in this report."],"related_hadiths":[{"id":"1598","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1601","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4288","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E518" s="4" t="n"/>
@@ -12427,7 +12431,7 @@
       </c>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Hajj Journey","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir gives a detailed report of the Prophet’s صلى الله عليه وسلم Hajj, including tawaf, Arafah, Muzdalifah, Mina, and the sermon."},"heading":{"title":"Complete Hadith About the Prophet’s Hajj Journey","description":"This long hadith is one of the clearest reports about the Prophet’s صلى الله عليه وسلم Hajj. Jabir describes how the Prophet صلى الله عليه وسلم set out, entered ihram, recited the talbiyah, made tawaf, prayed behind Maqam Ibrahim, went to Safa and Marwa, stood at Arafah, moved to Muzdalifah, went to Mina, threw pebbles, sacrificed, and returned to the House. The hadith also records parts of the sermon at Arafah. In it, the Prophet صلى الله عليه وسلم spoke about the safety of life and property, ending old blood claims and usury, treating women with care, and holding firmly to Allah’s Book. The report is detailed, but its heart is following the Prophet صلى الله عليه وسلم in Hajj with care and calm obedience."},"teachings":["The Prophet’s صلى الله عليه وسلم Hajj was followed closely by the Companions.","The talbiyah declares Allah’s oneness and rejects partners.","The sermon emphasized respect for life, property, and women’s rights.","The Prophet صلى الله عليه وسلم taught calmness and clear order in Hajj rites."],"related_hadiths":[{"id":"1218a","book_id":"2","label":"Sahih Muslim"},{"id":"1651","book_id":"1","label":"Sahih Bukhari"},{"id":"1920","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | The Prophet’s Hajj Journey","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir gives a detailed report of the Prophet’s صلى الله عليه وسلم Hajj, including tawaf, Arafah, Muzdalifah, Mina, and the sermon."},"heading":{"title":"Complete Hadith About the Prophet’s Hajj Journey","description":"This long hadith is one of the clearest reports about the Prophet’s صلى الله عليه وسلم Hajj. Jabir describes how the Prophet صلى الله عليه وسلم set out, entered ihram, recited the talbiyah, made tawaf, prayed behind Maqam Ibrahim, went to Safa and Marwa, stood at Arafah, moved to Muzdalifah, went to Mina, threw pebbles, sacrificed, and returned to the House. The hadith also records parts of the sermon at Arafah. In it, the Prophet صلى الله عليه وسلم spoke about the safety of life and property, ending old blood claims and usury, treating women with care, and holding firmly to Allah’s Book. The report is detailed, but its heart is following the Prophet صلى الله عليه وسلم in Hajj with care and calm obedience."},"teachings":["The Prophet’s صلى الله عليه وسلم Hajj was followed closely by the Companions.","The talbiyah declares Allah’s oneness and rejects partners.","The sermon emphasized respect for life, property, and women’s rights.","The Prophet صلى الله عليه وسلم taught calmness and clear order in Hajj rites."],"related_hadiths":[{"id":"1218a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1651","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1920","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E519" s="4" t="n"/>
@@ -12450,7 +12454,7 @@
       </c>
       <c r="D520" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Combining Prayers in Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم combined prayers at Arafah and Muzdalifah without extra prayers between them."},"heading":{"title":"Hadith About Combining Prayers at Arafah and Muzdalifah","description":"This hadith focuses on prayer during Hajj. It says that the Prophet صلى الله عليه وسلم prayed Dhuhr and Asr at Arafah with one adhan and two iqamahs, and he did not pray extra prayers between them. It also says that he prayed Maghrib and Isha at Muzdalifah with one adhan and two iqamahs, again without extra prayers between them. Abu Dawud then notes a related version that mentions one adhan and one iqamah for Maghrib and Isha. The main teaching is the described prayer arrangement during these Hajj locations, without adding wider rulings beyond the text."},"teachings":["Dhuhr and Asr were combined at Arafah in this report.","Maghrib and Isha were combined at Muzdalifah in this report.","No extra prayers between the combined prayers are mentioned.","Hadith narrators preserved wording differences carefully."],"related_hadiths":[{"id":"1218a","book_id":"2","label":"Sahih Muslim"},{"id":"1674","book_id":"1","label":"Sahih Bukhari"},{"id":"1913","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Combining Prayers in Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم combined prayers at Arafah and Muzdalifah without extra prayers between them."},"heading":{"title":"Hadith About Combining Prayers at Arafah and Muzdalifah","description":"This hadith focuses on prayer during Hajj. It says that the Prophet صلى الله عليه وسلم prayed Dhuhr and Asr at Arafah with one adhan and two iqamahs, and he did not pray extra prayers between them. It also says that he prayed Maghrib and Isha at Muzdalifah with one adhan and two iqamahs, again without extra prayers between them. Abu Dawud then notes a related version that mentions one adhan and one iqamah for Maghrib and Isha. The main teaching is the described prayer arrangement during these Hajj locations, without adding wider rulings beyond the text."},"teachings":["Dhuhr and Asr were combined at Arafah in this report.","Maghrib and Isha were combined at Muzdalifah in this report.","No extra prayers between the combined prayers are mentioned.","Hadith narrators preserved wording differences carefully."],"related_hadiths":[{"id":"1218a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1674","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1913","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E520" s="4" t="n"/>
@@ -12473,7 +12477,7 @@
       </c>
       <c r="D521" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mina Arafah and Muzdalifah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught that Mina, Arafah, and Muzdalifah each have broad places for their Hajj rites."},"heading":{"title":"Hadith About Mina, Arafah, and Muzdalifah as Hajj Places","description":"This hadith gives a clear and practical teaching about Hajj locations. The Prophet صلى الله عليه وسلم said that he sacrificed at one place, but all of Mina is a place of sacrifice. He stood at Arafah and said all of Arafah is a place of standing. He also stood at Muzdalifah and said all of Muzdalifah is a place of standing. The message is easy to understand: the Prophet صلى الله عليه وسلم named the wider valid areas for these rites. The hadith helps pilgrims see that these acts are not limited only to the exact spot where the Prophet صلى الله عليه وسلم stood or sacrificed."},"teachings":["All of Mina is described as a place of sacrifice.","All of Arafah is described as a place of standing.","All of Muzdalifah is described as a place of standing.","The Prophet صلى الله عليه وسلم taught Hajj in a way people could follow."],"related_hadiths":[{"id":"1218a","book_id":"2","label":"Sahih Muslim"},{"id":"1908","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1919","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mina Arafah and Muzdalifah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught that Mina, Arafah, and Muzdalifah each have broad places for their Hajj rites."},"heading":{"title":"Hadith About Mina, Arafah, and Muzdalifah as Hajj Places","description":"This hadith gives a clear and practical teaching about Hajj locations. The Prophet صلى الله عليه وسلم said that he sacrificed at one place, but all of Mina is a place of sacrifice. He stood at Arafah and said all of Arafah is a place of standing. He also stood at Muzdalifah and said all of Muzdalifah is a place of standing. The message is easy to understand: the Prophet صلى الله عليه وسلم named the wider valid areas for these rites. The hadith helps pilgrims see that these acts are not limited only to the exact spot where the Prophet صلى الله عليه وسلم stood or sacrificed."},"teachings":["All of Mina is described as a place of sacrifice.","All of Arafah is described as a place of standing.","All of Muzdalifah is described as a place of standing.","The Prophet صلى الله عليه وسلم taught Hajj in a way people could follow."],"related_hadiths":[{"id":"1218a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1908","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1919","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E521" s="4" t="n"/>
@@ -12496,7 +12500,7 @@
       </c>
       <c r="D522" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Remaining Food and Prayer Without New Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir reports that the Prophet صلى الله عليه وسلم ate, made wudu for Dhuhr, ate again, then prayed without new wudu."},"heading":{"title":"Eating Remaining Food and Praying Without New Wudu","description":"This hadith gives a detailed sequence. Jabir says he presented bread and meat to the Prophet صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم ate, called for ablution water, performed wudu, and prayed Dhuhr. Then he called for the remaining food and ate it. After that, he stood for prayer and did not perform ablution. The main topic is wudu after eating cooked food or meat. The hadith is helpful because it shows two moments: wudu before Dhuhr after eating, and then no new wudu after eating the remaining food. The explanation should stay with that sequence. For users searching did the Prophet make wudu after eating, this narration shows both action and non-renewal in one report."},"teachings":["The Prophet صلى الله عليه وسلم ate bread and meat before Dhuhr.","He performed wudu and prayed Dhuhr.","He later ate the remaining food and prayed without new wudu.","The sequence helps readers avoid oversimplifying the report."],"related_hadiths":[{"id":"356a","book_id":"2","label":"Sahih Muslim"},{"id":"354b","book_id":"2","label":"Sahih Muslim"},{"id":"207","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Remaining Food and Prayer Without New Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Jabir reports that the Prophet صلى الله عليه وسلم ate, made wudu for Dhuhr, ate again, then prayed without new wudu."},"heading":{"title":"Eating Remaining Food and Praying Without New Wudu","description":"This hadith gives a detailed sequence. Jabir says he presented bread and meat to the Prophet صلى الله عليه وسلم. The Prophet صلى الله عليه وسلم ate, called for ablution water, performed wudu, and prayed Dhuhr. Then he called for the remaining food and ate it. After that, he stood for prayer and did not perform ablution. The main topic is wudu after eating cooked food or meat. The hadith is helpful because it shows two moments: wudu before Dhuhr after eating, and then no new wudu after eating the remaining food. The explanation should stay with that sequence. For users searching did the Prophet make wudu after eating, this narration shows both action and non-renewal in one report."},"teachings":["The Prophet صلى الله عليه وسلم ate bread and meat before Dhuhr.","He performed wudu and prayed Dhuhr.","He later ate the remaining food and prayed without new wudu.","The sequence helps readers avoid oversimplifying the report."],"related_hadiths":[{"id":"356a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"354b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"207","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E522" s="4" t="n"/>
@@ -12519,7 +12523,7 @@
       </c>
       <c r="D523" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mina Prayers Before Arafah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم prayed Dhuhr on Tarwiyah and Fajr on Arafah day in Mina."},"heading":{"title":"Hadith About Praying in Mina on Tarwiyah and Arafah Day","description":"This hadith gives a short detail about the Prophet’s صلى الله عليه وسلم Hajj schedule. Ibn Abbas reports that the Messenger of Allah صلى الله عليه وسلم offered the noon prayer on the 8th of Dhul-Hijjah, known as Yawm at-Tarwiyah, in Mina. He also prayed the dawn prayer on the 9th of Dhul-Hijjah, known as Yawm al-Arafah, in Mina. The report is brief and focused. It does not describe the whole Hajj journey. It simply preserves where these two prayers were offered before going to Arafah. This makes it useful for people searching for Mina prayers during Hajj."},"teachings":["The Prophet صلى الله عليه وسلم prayed Dhuhr on Yawm at-Tarwiyah in Mina.","He prayed Fajr on Yawm al-Arafah in Mina.","The Companions preserved specific prayer locations.","Hajj includes ordered movement between sacred places."],"related_hadiths":[{"id":"1218a","book_id":"2","label":"Sahih Muslim"},{"id":"1912","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1913","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mina Prayers Before Arafah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم prayed Dhuhr on Tarwiyah and Fajr on Arafah day in Mina."},"heading":{"title":"Hadith About Praying in Mina on Tarwiyah and Arafah Day","description":"This hadith gives a short detail about the Prophet’s صلى الله عليه وسلم Hajj schedule. Ibn Abbas reports that the Messenger of Allah صلى الله عليه وسلم offered the noon prayer on the 8th of Dhul-Hijjah, known as Yawm at-Tarwiyah, in Mina. He also prayed the dawn prayer on the 9th of Dhul-Hijjah, known as Yawm al-Arafah, in Mina. The report is brief and focused. It does not describe the whole Hajj journey. It simply preserves where these two prayers were offered before going to Arafah. This makes it useful for people searching for Mina prayers during Hajj."},"teachings":["The Prophet صلى الله عليه وسلم prayed Dhuhr on Yawm at-Tarwiyah in Mina.","He prayed Fajr on Yawm al-Arafah in Mina.","The Companions preserved specific prayer locations.","Hajj includes ordered movement between sacred places."],"related_hadiths":[{"id":"1218a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1912","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1913","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E523" s="4" t="n"/>
@@ -12542,7 +12546,7 @@
       </c>
       <c r="D524" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mina and Abtah Prayer Locations","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas reports where the Prophet صلى الله عليه وسلم prayed on Tarwiyah and where he prayed Asr on the day of departure."},"heading":{"title":"Hadith About Prayer Locations in Mina and Al-Abtah","description":"In this hadith, ‘Abd al-‘Aziz bin Rufai‘ asked Anas bin Malik about something he knew from the Messenger of Allah صلى الله عليه وسلم. He asked where the Prophet صلى الله عليه وسلم prayed Dhuhr on Yawm at-Tarwiyah, and Anas answered, “In Mina.” He then asked where he prayed Asr on Yawm an-Nafr, and Anas answered, “In al-Abtah.” Anas then said, “Do as your commanders do.” The main point is the reported prayer locations during Hajj. The last statement also shows a practical concern for order and group conduct, as stated in the text."},"teachings":["The Prophet صلى الله عليه وسلم prayed Dhuhr on Tarwiyah in Mina.","He prayed Asr on Yawm an-Nafr in al-Abtah.","Anas answered from what he remembered of the Prophet صلى الله عليه وسلم.","The report ends with advice to follow the commanders in that setting."],"related_hadiths":[{"id":"1218a","book_id":"2","label":"Sahih Muslim"},{"id":"1911","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1913","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mina and Abtah Prayer Locations","description":"$book_name$ $hadith_number$ - $chapter_name$. Anas reports where the Prophet صلى الله عليه وسلم prayed on Tarwiyah and where he prayed Asr on the day of departure."},"heading":{"title":"Hadith About Prayer Locations in Mina and Al-Abtah","description":"In this hadith, ‘Abd al-‘Aziz bin Rufai‘ asked Anas bin Malik about something he knew from the Messenger of Allah صلى الله عليه وسلم. He asked where the Prophet صلى الله عليه وسلم prayed Dhuhr on Yawm at-Tarwiyah, and Anas answered, “In Mina.” He then asked where he prayed Asr on Yawm an-Nafr, and Anas answered, “In al-Abtah.” Anas then said, “Do as your commanders do.” The main point is the reported prayer locations during Hajj. The last statement also shows a practical concern for order and group conduct, as stated in the text."},"teachings":["The Prophet صلى الله عليه وسلم prayed Dhuhr on Tarwiyah in Mina.","He prayed Asr on Yawm an-Nafr in al-Abtah.","Anas answered from what he remembered of the Prophet صلى الله عليه وسلم.","The report ends with advice to follow the commanders in that setting."],"related_hadiths":[{"id":"1218a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1911","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1913","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E524" s="4" t="n"/>
@@ -12565,7 +12569,7 @@
       </c>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Moving to Arafah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar describes the Prophet’s صلى الله عليه وسلم movement from Mina to Arafah, prayer combining, sermon, and standing."},"heading":{"title":"Hadith About Moving from Mina to Arafah on Hajj","description":"This hadith describes the Prophet’s صلى الله عليه وسلم movement on the morning of Arafah day. Ibn Umar said that the Messenger of Allah صلى الله عليه وسلم left Mina after praying Fajr and went to Arafah. He stopped at Namirah, which the report describes as the place where the imam stays at Arafah. When Dhuhr time came, the Prophet صلى الله عليه وسلم moved, combined Dhuhr and Asr, addressed the people, and then went to the standing place in Arafah. The hadith is useful for understanding the order: Mina, Namirah, combined prayer, sermon, and standing at Arafah."},"teachings":["The Prophet صلى الله عليه وسلم left Mina after Fajr on Arafah day.","He stopped at Namirah before the standing.","He combined Dhuhr and Asr before addressing and standing.","The report preserves the order of Hajj actions at Arafah."],"related_hadiths":[{"id":"1218a","book_id":"2","label":"Sahih Muslim"},{"id":"1906","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1914","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Moving to Arafah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar describes the Prophet’s صلى الله عليه وسلم movement from Mina to Arafah, prayer combining, sermon, and standing."},"heading":{"title":"Hadith About Moving from Mina to Arafah on Hajj","description":"This hadith describes the Prophet’s صلى الله عليه وسلم movement on the morning of Arafah day. Ibn Umar said that the Messenger of Allah صلى الله عليه وسلم left Mina after praying Fajr and went to Arafah. He stopped at Namirah, which the report describes as the place where the imam stays at Arafah. When Dhuhr time came, the Prophet صلى الله عليه وسلم moved, combined Dhuhr and Asr, addressed the people, and then went to the standing place in Arafah. The hadith is useful for understanding the order: Mina, Namirah, combined prayer, sermon, and standing at Arafah."},"teachings":["The Prophet صلى الله عليه وسلم left Mina after Fajr on Arafah day.","He stopped at Namirah before the standing.","He combined Dhuhr and Asr before addressing and standing.","The report preserves the order of Hajj actions at Arafah."],"related_hadiths":[{"id":"1218a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1906","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1914","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E525" s="4" t="n"/>
@@ -12588,7 +12592,7 @@
       </c>
       <c r="D526" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sermon at Arafah","description":"$book_name$ $hadith_number$ - $chapter_name$. A man from Banu Damrah reports seeing the Prophet صلى الله عليه وسلم on the pulpit at Arafah."},"heading":{"title":"Hadith About the Prophet صلى الله عليه وسلم on the Pulpit at Arafah","description":"This hadith is very brief. A man from Banu Damrah reports from his father or uncle that he saw the Messenger of Allah صلى الله عليه وسلم on the pulpit in Arafah. The report does not give the sermon text. It simply records the sight of the Prophet صلى الله عليه وسلم in that place and setting. Because the narration is short, we should not add details beyond it. The core topic is the Arafah sermon scene. It supports the fact that the Prophet صلى الله عليه وسلم addressed people at Arafah, as also described in longer reports about the Hajj."},"teachings":["The Prophet صلى الله عليه وسلم was seen on the pulpit at Arafah.","The report preserves a direct observation.","Short narrations may confirm a setting without giving full details.","Arafah was a place where the Prophet صلى الله عليه وسلم addressed people."],"related_hadiths":[{"id":"1218a","book_id":"2","label":"Sahih Muslim"},{"id":"1916","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1917","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sermon at Arafah","description":"$book_name$ $hadith_number$ - $chapter_name$. A man from Banu Damrah reports seeing the Prophet صلى الله عليه وسلم on the pulpit at Arafah."},"heading":{"title":"Hadith About the Prophet صلى الله عليه وسلم on the Pulpit at Arafah","description":"This hadith is very brief. A man from Banu Damrah reports from his father or uncle that he saw the Messenger of Allah صلى الله عليه وسلم on the pulpit in Arafah. The report does not give the sermon text. It simply records the sight of the Prophet صلى الله عليه وسلم in that place and setting. Because the narration is short, we should not add details beyond it. The core topic is the Arafah sermon scene. It supports the fact that the Prophet صلى الله عليه وسلم addressed people at Arafah, as also described in longer reports about the Hajj."},"teachings":["The Prophet صلى الله عليه وسلم was seen on the pulpit at Arafah.","The report preserves a direct observation.","Short narrations may confirm a setting without giving full details.","Arafah was a place where the Prophet صلى الله عليه وسلم addressed people."],"related_hadiths":[{"id":"1218a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1916","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1917","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E526" s="4" t="n"/>
@@ -12611,7 +12615,7 @@
       </c>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet صلى الله عليه وسلم Standing at Arafah","description":"$book_name$ $hadith_number$ - $chapter_name$. Nubayt reports seeing the Prophet صلى الله عليه وسلم standing at Arafah on a red camel while giving a sermon."},"heading":{"title":"Hadith About the Prophet صلى الله عليه وسلم Standing at Arafah on a Camel","description":"This hadith reports that Nubayt saw the Prophet صلى الله عليه وسلم in Arafat. The Arabic text adds that he saw the Prophet صلى الله عليه وسلم standing at Arafah on a red camel while delivering a sermon. The narration is short and visual. It does not provide the sermon wording, but it gives a clear scene: the Prophet صلى الله عليه وسلم at Arafah, mounted, and addressing people. The main topic is the Arafah sermon and standing. This hadith should be explained as a witness report, not as a full legal discussion. It helps readers picture the setting without adding details not found in the text."},"teachings":["Nubayt saw the Prophet صلى الله عليه وسلم at Arafah.","The report mentions the Prophet صلى الله عليه وسلم giving a sermon.","The Prophet صلى الله عليه وسلم was seen on a red camel in this narration.","Eyewitness reports preserved scenes from the Hajj."],"related_hadiths":[{"id":"1218a","book_id":"2","label":"Sahih Muslim"},{"id":"1915","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1917","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet صلى الله عليه وسلم Standing at Arafah","description":"$book_name$ $hadith_number$ - $chapter_name$. Nubayt reports seeing the Prophet صلى الله عليه وسلم standing at Arafah on a red camel while giving a sermon."},"heading":{"title":"Hadith About the Prophet صلى الله عليه وسلم Standing at Arafah on a Camel","description":"This hadith reports that Nubayt saw the Prophet صلى الله عليه وسلم in Arafat. The Arabic text adds that he saw the Prophet صلى الله عليه وسلم standing at Arafah on a red camel while delivering a sermon. The narration is short and visual. It does not provide the sermon wording, but it gives a clear scene: the Prophet صلى الله عليه وسلم at Arafah, mounted, and addressing people. The main topic is the Arafah sermon and standing. This hadith should be explained as a witness report, not as a full legal discussion. It helps readers picture the setting without adding details not found in the text."},"teachings":["Nubayt saw the Prophet صلى الله عليه وسلم at Arafah.","The report mentions the Prophet صلى الله عليه وسلم giving a sermon.","The Prophet صلى الله عليه وسلم was seen on a red camel in this narration.","Eyewitness reports preserved scenes from the Hajj."],"related_hadiths":[{"id":"1218a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1915","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1917","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E527" s="4" t="n"/>
@@ -12634,7 +12638,7 @@
       </c>
       <c r="D528" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Same Arafah Sermon Report","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration transmits the same Arafah sermon report from Al-Adda’ through another chain."},"heading":{"title":"Hadith About the Arafah Sermon Through Another Chain","description":"This hadith is very short. It says that the same report was transmitted from Al-Adda’ bin Khalid through a different chain of narrators, with the same meaning. The main topic is hadith transmission related to the Prophet’s صلى الله عليه وسلم address at Arafah. It does not add a new scene or new wording to the previous report. Its value is in showing that the narration came through another route. For readers, the easy takeaway is that scholars and narrators preserved not only the text, but also the chains through which reports were passed down."},"teachings":["This report carries the same meaning as the previous narration.","It came through a different chain of narrators.","Hadith transmission includes attention to chains.","The report remains linked to the Prophet’s صلى الله عليه وسلم address at Arafah."],"related_hadiths":[{"id":"1218a","book_id":"2","label":"Sahih Muslim"},{"id":"1917","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1915","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Same Arafah Sermon Report","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration transmits the same Arafah sermon report from Al-Adda’ through another chain."},"heading":{"title":"Hadith About the Arafah Sermon Through Another Chain","description":"This hadith is very short. It says that the same report was transmitted from Al-Adda’ bin Khalid through a different chain of narrators, with the same meaning. The main topic is hadith transmission related to the Prophet’s صلى الله عليه وسلم address at Arafah. It does not add a new scene or new wording to the previous report. Its value is in showing that the narration came through another route. For readers, the easy takeaway is that scholars and narrators preserved not only the text, but also the chains through which reports were passed down."},"teachings":["This report carries the same meaning as the previous narration.","It came through a different chain of narrators.","Hadith transmission includes attention to chains.","The report remains linked to the Prophet’s صلى الله عليه وسلم address at Arafah."],"related_hadiths":[{"id":"1218a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1917","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1915","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E528" s="4" t="n"/>
@@ -12657,7 +12661,7 @@
       </c>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer at Muzdalifah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم delayed prayer until Muzdalifah and prayed Maghrib and Isha there."},"heading":{"title":"Hadith About Prayer at Muzdalifah During Hajj","description":"This hadith focuses on prayer at Muzdalifah during Hajj. Usamah bin Zaid describes the Prophet صلى الله عليه وسلم leaving Arafah, stopping briefly, making a light ablution, and saying, “Prayer ahead of you.” The prayer was not offered at that stopping place. It was offered after reaching Muzdalifah. The hadith also shows order and calm during travel. The people did not unload their camels until after the Prophet صلى الله عليه وسلم prayed Maghrib and Isha. So the main lesson is simple: during this part of Hajj, the Prophet صلى الله عليه وسلم kept moving toward Muzdalifah and prayed there. The report also shows care in following the Prophet’s actual practice step by step."},"teachings":["The Prophet صلى الله عليه وسلم delayed the prayer until reaching Muzdalifah.","A light ablution was made before continuing the journey.","The pilgrims followed the Prophet’s order before unloading their camels."],"related_hadiths":[{"id":"1941","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1945","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer at Muzdalifah","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet صلى الله عليه وسلم delayed prayer until Muzdalifah and prayed Maghrib and Isha there."},"heading":{"title":"Hadith About Prayer at Muzdalifah During Hajj","description":"This hadith focuses on prayer at Muzdalifah during Hajj. Usamah bin Zaid describes the Prophet صلى الله عليه وسلم leaving Arafah, stopping briefly, making a light ablution, and saying, “Prayer ahead of you.” The prayer was not offered at that stopping place. It was offered after reaching Muzdalifah. The hadith also shows order and calm during travel. The people did not unload their camels until after the Prophet صلى الله عليه وسلم prayed Maghrib and Isha. So the main lesson is simple: during this part of Hajj, the Prophet صلى الله عليه وسلم kept moving toward Muzdalifah and prayed there. The report also shows care in following the Prophet’s actual practice step by step."},"teachings":["The Prophet صلى الله عليه وسلم delayed the prayer until reaching Muzdalifah.","A light ablution was made before continuing the journey.","The pilgrims followed the Prophet’s order before unloading their camels."],"related_hadiths":[{"id":"1941","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1945","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E529" s="4" t="n"/>
@@ -12680,7 +12684,7 @@
       </c>
       <c r="D530" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eating Cooked Food Before Takbir","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم took a piece from a fire-pan and kept chewing it until he began the prayer."},"heading":{"title":"Eating Cooked Food Until the Opening Takbir Hadith","description":"This hadith describes the Prophet صلى الله عليه وسلم coming out after Bilal called him for prayer. On the way, he passed a man whose fire-pan was on the fire and asked whether the food had been cooked. When the man said yes, the Prophet صلى الله عليه وسلم took a piece from it and kept chewing until he uttered the first takbir of the prayer. The narrator says he was looking at him. The main searchable topic is eating cooked food before prayer. The report does not mention renewed wudu in this wording. It simply gives a close observation of eating from cooked food right before the prayer began. The teaching should be kept to that clear scene."},"teachings":["The Prophet صلى الله عليه وسلم responded to the call for prayer.","He ate from food that had been cooked in the fire-pan.","He continued chewing until the opening takbir.","The narrator carefully watched and preserved the detail."],"related_hadiths":[{"id":"356a","book_id":"2","label":"Sahih Muslim"},{"id":"354b","book_id":"2","label":"Sahih Muslim"},{"id":"207","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Eating Cooked Food Before Takbir","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم took a piece from a fire-pan and kept chewing it until he began the prayer."},"heading":{"title":"Eating Cooked Food Until the Opening Takbir Hadith","description":"This hadith describes the Prophet صلى الله عليه وسلم coming out after Bilal called him for prayer. On the way, he passed a man whose fire-pan was on the fire and asked whether the food had been cooked. When the man said yes, the Prophet صلى الله عليه وسلم took a piece from it and kept chewing until he uttered the first takbir of the prayer. The narrator says he was looking at him. The main searchable topic is eating cooked food before prayer. The report does not mention renewed wudu in this wording. It simply gives a close observation of eating from cooked food right before the prayer began. The teaching should be kept to that clear scene."},"teachings":["The Prophet صلى الله عليه وسلم responded to the call for prayer.","He ate from food that had been cooked in the fire-pan.","He continued chewing until the opening takbir.","The narrator carefully watched and preserved the detail."],"related_hadiths":[{"id":"356a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"354b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"207","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E530" s="4" t="n"/>
@@ -12703,7 +12707,7 @@
       </c>
       <c r="D531" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hajj Rami for the Weak","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet guided weak family members in Mina with care, timing, and order during stoning."},"heading":{"title":"Hadith About Stoning the Jamrah After Sunrise During Hajj","description":"This Hadith teaches a clear point about Hajj rami and care for weak pilgrims. Abdullah ibn Abbas reports that the Messenger of Allah (صلى الله عليه وسلم) sent the weak members of his family ahead in darkness toward Mina. At the same time, he told them not to throw pebbles at the jamrah until the sun had risen. The main lesson is balance. The weak were given ease in movement, but the act of stoning the jamrah still had a set time in this report. For anyone searching for hadith about stoning the jamrah, this narration shows mercy, order, and attention to people’s ability during Hajj rituals."},"teachings":["The Prophet (صلى الله عليه وسلم) showed care for weak family members during Hajj travel.","Ease was given in moving early, while the timing of rami was still respected.","Hajj rituals include both mercy for people and clear instructions.","The weak were not ignored in the planning of the pilgrimage."],"related_hadiths":[{"id":"1942","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1943","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1944","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hajj Rami for the Weak","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how the Prophet guided weak family members in Mina with care, timing, and order during stoning."},"heading":{"title":"Hadith About Stoning the Jamrah After Sunrise During Hajj","description":"This Hadith teaches a clear point about Hajj rami and care for weak pilgrims. Abdullah ibn Abbas reports that the Messenger of Allah (صلى الله عليه وسلم) sent the weak members of his family ahead in darkness toward Mina. At the same time, he told them not to throw pebbles at the jamrah until the sun had risen. The main lesson is balance. The weak were given ease in movement, but the act of stoning the jamrah still had a set time in this report. For anyone searching for hadith about stoning the jamrah, this narration shows mercy, order, and attention to people’s ability during Hajj rituals."},"teachings":["The Prophet (صلى الله عليه وسلم) showed care for weak family members during Hajj travel.","Ease was given in moving early, while the timing of rami was still respected.","Hajj rituals include both mercy for people and clear instructions.","The weak were not ignored in the planning of the pilgrimage."],"related_hadiths":[{"id":"1942","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1943","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1944","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E531" s="4" t="n"/>
@@ -12726,7 +12730,7 @@
       </c>
       <c r="D532" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umm Salamah and Rami","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith reports Umm Salamah throwing pebbles before dawn and then performing tawaf on the day of sacrifice."},"heading":{"title":"Hadith About Umm Salamah Throwing Pebbles Before Dawn","description":"This Hadith focuses on Umm Salamah and the Hajj rites on the night before the day of sacrifice. Aisha reports that the Prophet (صلى الله عليه وسلم) sent Umm Salamah that night, and she threw pebbles at the jamrah before dawn. She then went on quickly to Mecca and performed the circumambulation. The narration also notes that this was the day the Messenger of Allah (صلى الله عليه وسلم) spent with her. For readers searching for hadith about rami before dawn, this report is directly about the timing of throwing pebbles and moving on to tawaf. It shows that this specific action took place with the Prophet’s knowledge and instruction."},"teachings":["Umm Salamah was sent on the night before the day of sacrifice.","The Hadith reports rami before dawn in this specific case.","After throwing pebbles, she went on to perform tawaf.","The narration connects Hajj movement, rami, and circumambulation."],"related_hadiths":[{"id":"1941","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1943","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1944","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umm Salamah and Rami","description":"$book_name$ $hadith_number$ - $chapter_name$. This Hadith reports Umm Salamah throwing pebbles before dawn and then performing tawaf on the day of sacrifice."},"heading":{"title":"Hadith About Umm Salamah Throwing Pebbles Before Dawn","description":"This Hadith focuses on Umm Salamah and the Hajj rites on the night before the day of sacrifice. Aisha reports that the Prophet (صلى الله عليه وسلم) sent Umm Salamah that night, and she threw pebbles at the jamrah before dawn. She then went on quickly to Mecca and performed the circumambulation. The narration also notes that this was the day the Messenger of Allah (صلى الله عليه وسلم) spent with her. For readers searching for hadith about rami before dawn, this report is directly about the timing of throwing pebbles and moving on to tawaf. It shows that this specific action took place with the Prophet’s knowledge and instruction."},"teachings":["Umm Salamah was sent on the night before the day of sacrifice.","The Hadith reports rami before dawn in this specific case.","After throwing pebbles, she went on to perform tawaf.","The narration connects Hajj movement, rami, and circumambulation."],"related_hadiths":[{"id":"1941","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1943","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1944","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E532" s="4" t="n"/>
@@ -12749,7 +12753,7 @@
       </c>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rami at Night","description":"$book_name$ $hadith_number$ - $chapter_name$. Asma reports that throwing pebbles at night was practiced during the lifetime of the Messenger of Allah."},"heading":{"title":"Hadith About Throwing Pebbles at Night During Hajj","description":"This Hadith speaks about rami at night during Hajj. Ata reports that he heard about Asma throwing pebbles at the jamrah at night. When he mentioned that they had thrown pebbles at night, she replied that they used to do this during the lifetime of the Messenger of Allah (صلى الله عليه وسلم). The focus of this narration is simple and direct: throwing pebbles at night was not described here as a new practice by Asma. It was something she connected to the Prophet’s time. For people searching for hadith about stoning the jamrah at night, this report gives a short but important statement on that practice."},"teachings":["Asma connected night-time rami to the lifetime of the Prophet (صلى الله عليه وسلم).","The Hadith directly mentions throwing pebbles at the jamrah at night.","A Companion’s report can preserve practical details of Hajj rites.","The narration stays focused on the timing of rami."],"related_hadiths":[{"id":"1941","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1942","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1944","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rami at Night","description":"$book_name$ $hadith_number$ - $chapter_name$. Asma reports that throwing pebbles at night was practiced during the lifetime of the Messenger of Allah."},"heading":{"title":"Hadith About Throwing Pebbles at Night During Hajj","description":"This Hadith speaks about rami at night during Hajj. Ata reports that he heard about Asma throwing pebbles at the jamrah at night. When he mentioned that they had thrown pebbles at night, she replied that they used to do this during the lifetime of the Messenger of Allah (صلى الله عليه وسلم). The focus of this narration is simple and direct: throwing pebbles at night was not described here as a new practice by Asma. It was something she connected to the Prophet’s time. For people searching for hadith about stoning the jamrah at night, this report gives a short but important statement on that practice."},"teachings":["Asma connected night-time rami to the lifetime of the Prophet (صلى الله عليه وسلم).","The Hadith directly mentions throwing pebbles at the jamrah at night.","A Companion’s report can preserve practical details of Hajj rites.","The narration stays focused on the timing of rami."],"related_hadiths":[{"id":"1941","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1942","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1944","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E533" s="4" t="n"/>
@@ -12772,7 +12776,7 @@
       </c>
       <c r="D534" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Day of Greater Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet identified the day of sacrifice as the day of greater Hajj during his pilgrimage."},"heading":{"title":"Hadith About the Day of Greater Hajj and the Day of Sacrifice","description":"This Hadith explains the meaning of the day of greater Hajj in a very direct way. Abdullah ibn Umar reports that the Messenger of Allah (صلى الله عليه وسلم) stood on the day of sacrifice between the jamrahs during the Hajj he performed. He asked the people which day it was. They replied that it was the day of sacrifice. The Prophet (صلى الله عليه وسلم) then said, “This is the day of greater hajj.” For anyone searching for day of greater Hajj hadith, this narration links that phrase with the day of sacrifice. The report is brief, but it clearly names the day and places the statement in Mina between the jamrahs."},"teachings":["The Prophet (صلى الله عليه وسلم) identified the day of sacrifice as the day of greater Hajj.","The statement was made during his Hajj between the jamrahs.","The Companions answered the Prophet’s question before he explained the day’s status.","The narration gives a clear label for an important Hajj day."],"related_hadiths":[{"id":"1946","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1954","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1955","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Day of Greater Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet identified the day of sacrifice as the day of greater Hajj during his pilgrimage."},"heading":{"title":"Hadith About the Day of Greater Hajj and the Day of Sacrifice","description":"This Hadith explains the meaning of the day of greater Hajj in a very direct way. Abdullah ibn Umar reports that the Messenger of Allah (صلى الله عليه وسلم) stood on the day of sacrifice between the jamrahs during the Hajj he performed. He asked the people which day it was. They replied that it was the day of sacrifice. The Prophet (صلى الله عليه وسلم) then said, “This is the day of greater hajj.” For anyone searching for day of greater Hajj hadith, this narration links that phrase with the day of sacrifice. The report is brief, but it clearly names the day and places the statement in Mina between the jamrahs."},"teachings":["The Prophet (صلى الله عليه وسلم) identified the day of sacrifice as the day of greater Hajj.","The statement was made during his Hajj between the jamrahs.","The Companions answered the Prophet’s question before he explained the day’s status.","The narration gives a clear label for an important Hajj day."],"related_hadiths":[{"id":"1946","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1954","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1955","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E534" s="4" t="n"/>
@@ -12795,7 +12799,7 @@
       </c>
       <c r="D535" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Greater Hajj Announcement","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr sent Abu Hurairah to announce Hajj rulings at Mina on the day of sacrifice."},"heading":{"title":"Hadith About the Greater Hajj Announcement at Mina","description":"This Hadith reports a public announcement made at Mina. Abu Hurairah says that Abu Bakr sent him among those who proclaimed on the day of sacrifice that no polytheist should perform Hajj after that year, no naked person should go around the House, and that the day of greater Hajj is the day of sacrifice. The narration also states that the greater Hajj is the Hajj. For users searching for hadith about greater Hajj, this report is closely tied to Mina, the day of sacrifice, and public guidance about pilgrimage practice. It is a direct narration about what was announced to the people at that time."},"teachings":["A public announcement was made at Mina on the day of sacrifice.","The day of greater Hajj is identified as the day of sacrifice.","The announcement included rules about who may perform Hajj after that year.","The narration also mentions that naked tawaf around the House was prohibited."],"related_hadiths":[{"id":"1945","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1954","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1955","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Greater Hajj Announcement","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Bakr sent Abu Hurairah to announce Hajj rulings at Mina on the day of sacrifice."},"heading":{"title":"Hadith About the Greater Hajj Announcement at Mina","description":"This Hadith reports a public announcement made at Mina. Abu Hurairah says that Abu Bakr sent him among those who proclaimed on the day of sacrifice that no polytheist should perform Hajj after that year, no naked person should go around the House, and that the day of greater Hajj is the day of sacrifice. The narration also states that the greater Hajj is the Hajj. For users searching for hadith about greater Hajj, this report is closely tied to Mina, the day of sacrifice, and public guidance about pilgrimage practice. It is a direct narration about what was announced to the people at that time."},"teachings":["A public announcement was made at Mina on the day of sacrifice.","The day of greater Hajj is identified as the day of sacrifice.","The announcement included rules about who may perform Hajj after that year.","The narration also mentions that naked tawaf around the House was prohibited."],"related_hadiths":[{"id":"1945","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1954","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1955","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E535" s="4" t="n"/>
@@ -12818,7 +12822,7 @@
       </c>
       <c r="D536" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mina Camping Order","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet arranged the Muhajirun, Ansar, and others in their places at Mina."},"heading":{"title":"Hadith About Staying in Assigned Places at Mina","description":"This Hadith describes how the Prophet (صلى الله عليه وسلم) organized people at Mina. A Companion reports that the Prophet addressed the people and made them stay in their dwellings. He directed the Muhajirun to one side, pointing to the right side of the qiblah, and the Ansar to another side, pointing to the left side of the qiblah. Then he said the people should stay around them. The main topic is Mina camping and order during Hajj. The Hadith does not give a long ruling discussion. It simply shows that during the Hajj stay at Mina, the Prophet (صلى الله عليه وسلم) gave people clear places and arranged the groups in an orderly way."},"teachings":["The Prophet (صلى الله عليه وسلم) arranged people’s places at Mina.","The Muhajirun and Ansar were given distinct areas.","The wider group of people stayed around them.","Order and clear placement mattered during the Mina stay."],"related_hadiths":[{"id":"1957","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1958","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1959","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mina Camping Order","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet arranged the Muhajirun, Ansar, and others in their places at Mina."},"heading":{"title":"Hadith About Staying in Assigned Places at Mina","description":"This Hadith describes how the Prophet (صلى الله عليه وسلم) organized people at Mina. A Companion reports that the Prophet addressed the people and made them stay in their dwellings. He directed the Muhajirun to one side, pointing to the right side of the qiblah, and the Ansar to another side, pointing to the left side of the qiblah. Then he said the people should stay around them. The main topic is Mina camping and order during Hajj. The Hadith does not give a long ruling discussion. It simply shows that during the Hajj stay at Mina, the Prophet (صلى الله عليه وسلم) gave people clear places and arranged the groups in an orderly way."},"teachings":["The Prophet (صلى الله عليه وسلم) arranged people’s places at Mina.","The Muhajirun and Ansar were given distinct areas.","The wider group of people stayed around them.","Order and clear placement mattered during the Mina stay."],"related_hadiths":[{"id":"1957","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1958","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1959","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E536" s="4" t="n"/>
@@ -12841,7 +12845,7 @@
       </c>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mina Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. Two men from Banu Bakr saw the Prophet giving his Mina sermon during the middle Tashriq days."},"heading":{"title":"Hadith About the Prophet’s Sermon at Mina During Tashriq","description":"This Hadith reports that the Messenger of Allah (صلى الله عليه وسلم) addressed the people at Mina during the middle of the days of Tashriq. Two men from Banu Bakr said they saw him giving the sermon while they were staying near his mount. The narration identifies this as the address of the Messenger of Allah (صلى الله عليه وسلم) that he gave at Mina. The core topic is the Mina sermon. For readers searching for hadith about the Prophet’s khutbah at Mina, this report gives the setting, the time, and the witness statement. It does not quote the sermon content here, so the explanation should stay with what the text says."},"teachings":["The Prophet (صلى الله عليه وسلم) addressed the people at Mina.","The sermon took place during the middle days of Tashriq.","Two men from Banu Bakr witnessed this address.","The narration identifies the event as the Prophet’s Mina sermon."],"related_hadiths":[{"id":"1953","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1954","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1955","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mina Sermon","description":"$book_name$ $hadith_number$ - $chapter_name$. Two men from Banu Bakr saw the Prophet giving his Mina sermon during the middle Tashriq days."},"heading":{"title":"Hadith About the Prophet’s Sermon at Mina During Tashriq","description":"This Hadith reports that the Messenger of Allah (صلى الله عليه وسلم) addressed the people at Mina during the middle of the days of Tashriq. Two men from Banu Bakr said they saw him giving the sermon while they were staying near his mount. The narration identifies this as the address of the Messenger of Allah (صلى الله عليه وسلم) that he gave at Mina. The core topic is the Mina sermon. For readers searching for hadith about the Prophet’s khutbah at Mina, this report gives the setting, the time, and the witness statement. It does not quote the sermon content here, so the explanation should stay with what the text says."},"teachings":["The Prophet (صلى الله عليه وسلم) addressed the people at Mina.","The sermon took place during the middle days of Tashriq.","Two men from Banu Bakr witnessed this address.","The narration identifies the event as the Prophet’s Mina sermon."],"related_hadiths":[{"id":"1953","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1954","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1955","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E537" s="4" t="n"/>
@@ -12864,7 +12868,7 @@
       </c>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Khutbah on Al-Adba","description":"$book_name$ $hadith_number$ - $chapter_name$. Harmas saw the Prophet addressing the people on his she-camel al-Adba at Mina on Eid."},"heading":{"title":"Hadith About the Prophet’s Khutbah on His She-Camel at Mina","description":"This Hadith gives a direct eyewitness report from Harmas ibn Ziyad al-Bahili. He says that he saw the Prophet (صلى الله عليه وسلم) addressing the people on his she-camel al-Adba’ on the day of sacrifice at Mina. The core topic is the Prophet’s Mina khutbah. The report does not give the words of the sermon, but it gives the place, day, and manner in which Harmas saw it. For people searching for hadith about the Prophet’s sermon at Mina, this narration is important because it confirms that the address took place on the day of sacrifice and that the Prophet (صلى الله عليه وسلم) delivered it while mounted."},"teachings":["Harmas ibn Ziyad personally saw the Prophet (صلى الله عليه وسلم) giving the address.","The sermon took place at Mina on the day of sacrifice.","The Prophet (صلى الله عليه وسلم) addressed people while on his she-camel al-Adba’.","The narration preserves a clear eyewitness detail from Hajj."],"related_hadiths":[{"id":"1952","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1955","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1956","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Khutbah on Al-Adba","description":"$book_name$ $hadith_number$ - $chapter_name$. Harmas saw the Prophet addressing the people on his she-camel al-Adba at Mina on Eid."},"heading":{"title":"Hadith About the Prophet’s Khutbah on His She-Camel at Mina","description":"This Hadith gives a direct eyewitness report from Harmas ibn Ziyad al-Bahili. He says that he saw the Prophet (صلى الله عليه وسلم) addressing the people on his she-camel al-Adba’ on the day of sacrifice at Mina. The core topic is the Prophet’s Mina khutbah. The report does not give the words of the sermon, but it gives the place, day, and manner in which Harmas saw it. For people searching for hadith about the Prophet’s sermon at Mina, this narration is important because it confirms that the address took place on the day of sacrifice and that the Prophet (صلى الله عليه وسلم) delivered it while mounted."},"teachings":["Harmas ibn Ziyad personally saw the Prophet (صلى الله عليه وسلم) giving the address.","The sermon took place at Mina on the day of sacrifice.","The Prophet (صلى الله عليه وسلم) addressed people while on his she-camel al-Adba’.","The narration preserves a clear eyewitness detail from Hajj."],"related_hadiths":[{"id":"1952","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1955","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1956","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E538" s="4" t="n"/>
@@ -12887,7 +12891,7 @@
       </c>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rinsing the Mouth After Milk","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم drank milk, rinsed his mouth, and said that milk contains greasiness."},"heading":{"title":"Rinsing Mouth After Drinking Milk Hadith","description":"This hadith is about rinsing the mouth after drinking milk. Ibn Abbas reports that the Prophet صلى الله عليه وسلم drank some milk, called for water, rinsed his mouth, and said that it contains greasiness. The teaching is simple and easy to understand. Milk can leave a fatty feel in the mouth, so rinsing clears it before prayer or speech. The text does not say that milk requires a full wudu. It only mentions rinsing the mouth and gives the reason: greasiness. For readers searching hadith about rinsing mouth after milk, this narration gives both the action and the explanation in the Prophet’s own words. It is a small act of cleanliness preserved in a clear report."},"teachings":["The Prophet صلى الله عليه وسلم rinsed his mouth after drinking milk.","He gave the reason: milk contains greasiness.","The report mentions rinsing the mouth, not a full wudu.","Small acts of cleanliness matter in daily worship."],"related_hadiths":[{"id":"211","book_id":"1","label":"Sahih Bukhari"},{"id":"358a","book_id":"2","label":"Sahih Muslim"},{"id":"498","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Rinsing the Mouth After Milk","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم drank milk, rinsed his mouth, and said that milk contains greasiness."},"heading":{"title":"Rinsing Mouth After Drinking Milk Hadith","description":"This hadith is about rinsing the mouth after drinking milk. Ibn Abbas reports that the Prophet صلى الله عليه وسلم drank some milk, called for water, rinsed his mouth, and said that it contains greasiness. The teaching is simple and easy to understand. Milk can leave a fatty feel in the mouth, so rinsing clears it before prayer or speech. The text does not say that milk requires a full wudu. It only mentions rinsing the mouth and gives the reason: greasiness. For readers searching hadith about rinsing mouth after milk, this narration gives both the action and the explanation in the Prophet’s own words. It is a small act of cleanliness preserved in a clear report."},"teachings":["The Prophet صلى الله عليه وسلم rinsed his mouth after drinking milk.","He gave the reason: milk contains greasiness.","The report mentions rinsing the mouth, not a full wudu.","Small acts of cleanliness matter in daily worship."],"related_hadiths":[{"id":"211","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"358a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"498","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E539" s="4" t="n"/>
@@ -12910,7 +12914,7 @@
       </c>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer at Mina","description":"$book_name$ $hadith_number$ - $chapter_name$. Uthman prayed four rak'ahs at Mina because he intended to stay there after Hajj."},"heading":{"title":"Hadith About Prayer at Mina and Intending to Stay","description":"This hadith explains a clear reason given for Uthman praying four rak'ahs at Mina. The main point is prayer at Mina when a person has resolved to stay after Hajj. The narration does not discuss every rule of travel prayer. It simply says Uthman prayed four rak'ahs because he had made a firm intention to remain there after Hajj. For someone searching for hadith about prayer at Mina or Uthman praying four rak'ahs, this report shows how intention to settle or stay was linked to completing the prayer in this case."},"teachings":["A stated intention to stay can affect how prayer is performed.","The narration gives a specific reason for Uthman's action at Mina.","The report should be understood within its own wording, without adding extra cases."],"related_hadiths":[{"id":"1082","book_id":"1","label":"Sahih Bukhari"},{"id":"694a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer at Mina","description":"$book_name$ $hadith_number$ - $chapter_name$. Uthman prayed four rak'ahs at Mina because he intended to stay there after Hajj."},"heading":{"title":"Hadith About Prayer at Mina and Intending to Stay","description":"This hadith explains a clear reason given for Uthman praying four rak'ahs at Mina. The main point is prayer at Mina when a person has resolved to stay after Hajj. The narration does not discuss every rule of travel prayer. It simply says Uthman prayed four rak'ahs because he had made a firm intention to remain there after Hajj. For someone searching for hadith about prayer at Mina or Uthman praying four rak'ahs, this report shows how intention to settle or stay was linked to completing the prayer in this case."},"teachings":["A stated intention to stay can affect how prayer is performed.","The narration gives a specific reason for Uthman's action at Mina.","The report should be understood within its own wording, without adding extra cases."],"related_hadiths":[{"id":"1082","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"694a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E540" s="4" t="n"/>
@@ -12933,7 +12937,7 @@
       </c>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Settling at Mina","description":"$book_name$ $hadith_number$ - $chapter_name$. Uthman prayed four rak'ahs at Mina because he had taken it as a place of settlement."},"heading":{"title":"Hadith About Uthman Praying Four Rak'ahs at Mina","description":"This narration gives another short explanation for Uthman's complete prayer at Mina. It says he prayed four rak'ahs because he made Mina his home for settlement. The core topic is residence and prayer during Hajj. The hadith does not give a long legal discussion. It records Ibrahim's explanation that Uthman's status was not being treated like someone merely passing through. People searching for Uthman four rak'ahs at Mina or hadith about settling during Hajj can understand that the report connects complete prayer with taking a place as home."},"teachings":["Residence or settlement is presented here as the reason for complete prayer.","The report focuses on Uthman's specific situation at Mina.","Short narrations should be read carefully without adding unrelated rulings."],"related_hadiths":[{"id":"1082","book_id":"1","label":"Sahih Bukhari"},{"id":"694a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Settling at Mina","description":"$book_name$ $hadith_number$ - $chapter_name$. Uthman prayed four rak'ahs at Mina because he had taken it as a place of settlement."},"heading":{"title":"Hadith About Uthman Praying Four Rak'ahs at Mina","description":"This narration gives another short explanation for Uthman's complete prayer at Mina. It says he prayed four rak'ahs because he made Mina his home for settlement. The core topic is residence and prayer during Hajj. The hadith does not give a long legal discussion. It records Ibrahim's explanation that Uthman's status was not being treated like someone merely passing through. People searching for Uthman four rak'ahs at Mina or hadith about settling during Hajj can understand that the report connects complete prayer with taking a place as home."},"teachings":["Residence or settlement is presented here as the reason for complete prayer.","The report focuses on Uthman's specific situation at Mina.","Short narrations should be read carefully without adding unrelated rulings."],"related_hadiths":[{"id":"1082","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"694a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E541" s="4" t="n"/>
@@ -12956,7 +12960,7 @@
       </c>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer at Mina","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم led two rak'ahs at Mina during the Farewell Pilgrimage despite a large gathering."},"heading":{"title":"Hadith About the Prophet صلى الله عليه وسلم Praying Two Rak'ahs at Mina","description":"This hadith reports that Harithah ibn Wahb prayed behind the Messenger of Allah صلى الله عليه وسلم at Mina during the Farewell Pilgrimage. Even though the people were gathered in large numbers, the Prophet صلى الله عليه وسلم led them in two rak'ahs. The core topic is prayer at Mina during Hajj. The text also includes Abu Dawud's note that Harithah was from Khuza'ah and their houses were in Mecca. For users searching for hadith about two rak'ahs at Mina, this narration gives a direct report from the Farewell Pilgrimage."},"teachings":["The Prophet صلى الله عليه وسلم led two rak'ahs at Mina during the Farewell Pilgrimage.","A large crowd is mentioned, yet the prayer described was two rak'ahs.","The narrator personally prayed behind the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"1082","book_id":"1","label":"Sahih Bukhari"},{"id":"694a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer at Mina","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم led two rak'ahs at Mina during the Farewell Pilgrimage despite a large gathering."},"heading":{"title":"Hadith About the Prophet صلى الله عليه وسلم Praying Two Rak'ahs at Mina","description":"This hadith reports that Harithah ibn Wahb prayed behind the Messenger of Allah صلى الله عليه وسلم at Mina during the Farewell Pilgrimage. Even though the people were gathered in large numbers, the Prophet صلى الله عليه وسلم led them in two rak'ahs. The core topic is prayer at Mina during Hajj. The text also includes Abu Dawud's note that Harithah was from Khuza'ah and their houses were in Mecca. For users searching for hadith about two rak'ahs at Mina, this narration gives a direct report from the Farewell Pilgrimage."},"teachings":["The Prophet صلى الله عليه وسلم led two rak'ahs at Mina during the Farewell Pilgrimage.","A large crowd is mentioned, yet the prayer described was two rak'ahs.","The narrator personally prayed behind the Prophet صلى الله عليه وسلم."],"related_hadiths":[{"id":"1082","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"694a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E542" s="4" t="n"/>
@@ -12979,7 +12983,7 @@
       </c>
       <c r="D543" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stoning Jamarat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم threw small pebbles at the jamrah and warned people not to harm each other."},"heading":{"title":"Hadith About Stoning the Jamarat Safely","description":"This hadith describes the Messenger of Allah صلى الله عليه وسلم throwing pebbles at the jamrah from the bottom of the valley while riding. He said takbir with each pebble. When people crowded, he told them not to kill one another and instructed them to throw small pebbles. The core topic is stoning Jamarat with safety. The hadith is very practical. It shows that the act of ramy in Hajj should not become a cause of harm. People searching for hadith about throwing pebbles at Jamarat will find both the method and the warning in this report."},"teachings":["Takbir was said with each pebble.","Small pebbles were instructed for the jamrah.","Crowding and harming others were directly warned against."],"related_hadiths":[{"id":"1297","book_id":"2","label":"Sahih Muslim"},{"id":"1751","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Stoning Jamarat","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم threw small pebbles at the jamrah and warned people not to harm each other."},"heading":{"title":"Hadith About Stoning the Jamarat Safely","description":"This hadith describes the Messenger of Allah صلى الله عليه وسلم throwing pebbles at the jamrah from the bottom of the valley while riding. He said takbir with each pebble. When people crowded, he told them not to kill one another and instructed them to throw small pebbles. The core topic is stoning Jamarat with safety. The hadith is very practical. It shows that the act of ramy in Hajj should not become a cause of harm. People searching for hadith about throwing pebbles at Jamarat will find both the method and the warning in this report."},"teachings":["Takbir was said with each pebble.","Small pebbles were instructed for the jamrah.","Crowding and harming others were directly warned against."],"related_hadiths":[{"id":"1297","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1751","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E543" s="4" t="n"/>
@@ -13002,7 +13006,7 @@
       </c>
       <c r="D544" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Standing at Jamrah","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that the Prophet صلى الله عليه وسلم did not stand near that jamrah after throwing."},"heading":{"title":"Hadith About Not Standing Near the Jamrah","description":"This report is a shorter version connected to the narration about throwing pebbles at the jamrah. Its added point is that the Prophet صلى الله عليه وسلم did not stand near it after throwing. The core topic is the action after stoning. The wording is limited, so the explanation should stay limited too. It does not describe every jamrah or every day of Hajj. It only adds that in this report, after that throwing, he did not remain standing there. This is useful for searches about standing after Jamarat and Jamrat al-Aqabah hadith."},"teachings":["The added wording says he did not stand near that jamrah.","The narration focuses on what happened after throwing.","The report should not be stretched beyond the action it mentions."],"related_hadiths":[{"id":"1751","book_id":"1","label":"Sahih Bukhari"},{"id":"1297","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Standing at Jamrah","description":"$book_name$ $hadith_number$ - $chapter_name$. This version adds that the Prophet صلى الله عليه وسلم did not stand near that jamrah after throwing."},"heading":{"title":"Hadith About Not Standing Near the Jamrah","description":"This report is a shorter version connected to the narration about throwing pebbles at the jamrah. Its added point is that the Prophet صلى الله عليه وسلم did not stand near it after throwing. The core topic is the action after stoning. The wording is limited, so the explanation should stay limited too. It does not describe every jamrah or every day of Hajj. It only adds that in this report, after that throwing, he did not remain standing there. This is useful for searches about standing after Jamarat and Jamrat al-Aqabah hadith."},"teachings":["The added wording says he did not stand near that jamrah.","The narration focuses on what happened after throwing.","The report should not be stretched beyond the action it mentions."],"related_hadiths":[{"id":"1751","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1297","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E544" s="4" t="n"/>
@@ -13025,7 +13029,7 @@
       </c>
       <c r="D545" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Walking to Jamarat","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar walked to and from the Jamarat during the three days after sacrifice."},"heading":{"title":"Hadith About Walking to the Jamarat","description":"This hadith reports Ibn Umar's practice during the three days after the day of sacrifice. He would come to the Jamarat walking and return walking. He also reported that the Prophet صلى الله عليه وسلم used to do this. The core topic is walking to Jamarat. The narration is simple and practical. It does not discuss riding in other situations. It only mentions this practice for the three days after sacrifice. People searching for hadith about walking to Jamarat or Prophet's practice in Mina will find a clear report here."},"teachings":["Ibn Umar walked to the Jamarat and returned walking.","He connected this practice to the Prophet صلى الله عليه وسلم.","The report refers to the three days after the day of sacrifice."],"related_hadiths":[{"id":"1751","book_id":"1","label":"Sahih Bukhari"},{"id":"1297","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Walking to Jamarat","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar walked to and from the Jamarat during the three days after sacrifice."},"heading":{"title":"Hadith About Walking to the Jamarat","description":"This hadith reports Ibn Umar's practice during the three days after the day of sacrifice. He would come to the Jamarat walking and return walking. He also reported that the Prophet صلى الله عليه وسلم used to do this. The core topic is walking to Jamarat. The narration is simple and practical. It does not discuss riding in other situations. It only mentions this practice for the three days after sacrifice. People searching for hadith about walking to Jamarat or Prophet's practice in Mina will find a clear report here."},"teachings":["Ibn Umar walked to the Jamarat and returned walking.","He connected this practice to the Prophet صلى الله عليه وسلم.","The report refers to the three days after the day of sacrifice."],"related_hadiths":[{"id":"1751","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1297","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E545" s="4" t="n"/>
@@ -13048,7 +13052,7 @@
       </c>
       <c r="D546" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learn Hajj Rites","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم told people to learn their Hajj rites as he threw pebbles on the day of sacrifice."},"heading":{"title":"Hadith About Learning the Rites of Hajj","description":"This hadith carries a powerful teaching from the Farewell Pilgrimage. Jabir saw the Messenger of Allah صلى الله عليه وسلم throwing pebbles on the day of sacrifice while riding. The Prophet صلى الله عليه وسلم said, “Learn your rites,” and mentioned that he did not know whether he would perform Hajj after that occasion. The core topic is learning Hajj rites from the Prophet صلى الله عليه وسلم. The narration directly ties the act of ramy to learning by watching his practice. For searches like learn your Hajj rites hadith or Prophet's Hajj method, this report is very important."},"teachings":["Hajj rites should be learned from the Prophet's صلى الله عليه وسلم practice.","The Prophet صلى الله عليه وسلم taught while performing the rite.","The statement shows the importance of paying attention during worship."],"related_hadiths":[{"id":"1297","book_id":"2","label":"Sahih Muslim"},{"id":"1653","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Learn Hajj Rites","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم told people to learn their Hajj rites as he threw pebbles on the day of sacrifice."},"heading":{"title":"Hadith About Learning the Rites of Hajj","description":"This hadith carries a powerful teaching from the Farewell Pilgrimage. Jabir saw the Messenger of Allah صلى الله عليه وسلم throwing pebbles on the day of sacrifice while riding. The Prophet صلى الله عليه وسلم said, “Learn your rites,” and mentioned that he did not know whether he would perform Hajj after that occasion. The core topic is learning Hajj rites from the Prophet صلى الله عليه وسلم. The narration directly ties the act of ramy to learning by watching his practice. For searches like learn your Hajj rites hadith or Prophet's Hajj method, this report is very important."},"teachings":["Hajj rites should be learned from the Prophet's صلى الله عليه وسلم practice.","The Prophet صلى الله عليه وسلم taught while performing the rite.","The statement shows the importance of paying attention during worship."],"related_hadiths":[{"id":"1297","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1653","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E546" s="4" t="n"/>
@@ -13071,7 +13075,7 @@
       </c>
       <c r="D547" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | After Zawal","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar said they waited until the sun declined, then threw the pebbles."},"heading":{"title":"Hadith About Throwing Jamarat After Zawal","description":"This hadith answers a direct question: when should pebbles be thrown at the jamrah? Ibn Umar first said to throw when the imam throws. When asked again, he explained that they used to wait until the sun passed the meridian. When the sun declined, they threw the pebbles. The core topic is throwing Jamarat after zawal. The narration shows both following the Hajj leader and observing the time. It is useful for searches like when to throw Jamarat after noon and Ibn Umar Jamarat timing hadith."},"teachings":["Ibn Umar advised throwing when the imam throws.","He described waiting until the sun declined.","The report connects the act of throwing with a known time."],"related_hadiths":[{"id":"1746","book_id":"1","label":"Sahih Bukhari"},{"id":"1297","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | After Zawal","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar said they waited until the sun declined, then threw the pebbles."},"heading":{"title":"Hadith About Throwing Jamarat After Zawal","description":"This hadith answers a direct question: when should pebbles be thrown at the jamrah? Ibn Umar first said to throw when the imam throws. When asked again, he explained that they used to wait until the sun passed the meridian. When the sun declined, they threw the pebbles. The core topic is throwing Jamarat after zawal. The narration shows both following the Hajj leader and observing the time. It is useful for searches like when to throw Jamarat after noon and Ibn Umar Jamarat timing hadith."},"teachings":["Ibn Umar advised throwing when the imam throws.","He described waiting until the sun declined.","The report connects the act of throwing with a known time."],"related_hadiths":[{"id":"1746","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1297","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E547" s="4" t="n"/>
@@ -13094,7 +13098,7 @@
       </c>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Herdsmen Concession","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم allowed camel herdsmen a concession about staying in Mina and throwing pebbles."},"heading":{"title":"Hadith About the Herdsmen's Concession in Hajj","description":"This hadith describes a concession given by the Messenger of Allah صلى الله عليه وسلم to camel herdsmen. They were allowed not to spend the night at Mina. The report also mentions their throwing on the day of sacrifice, then on the next day and the following two days, and on the day of return. The core topic is concession in Hajj. The narration is about a specific group with a specific duty: herdsmen of camels. It should not be turned into a broad claim for every pilgrim. It shows ease where the text mentions ease."},"teachings":["The Prophet صلى الله عليه وسلم gave a concession to camel herdsmen.","The concession included not spending the night at Mina.","The report gives a specific schedule for their throwing."],"related_hadiths":[{"id":"955","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"3069","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Herdsmen Concession","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم allowed camel herdsmen a concession about staying in Mina and throwing pebbles."},"heading":{"title":"Hadith About the Herdsmen's Concession in Hajj","description":"This hadith describes a concession given by the Messenger of Allah صلى الله عليه وسلم to camel herdsmen. They were allowed not to spend the night at Mina. The report also mentions their throwing on the day of sacrifice, then on the next day and the following two days, and on the day of return. The core topic is concession in Hajj. The narration is about a specific group with a specific duty: herdsmen of camels. It should not be turned into a broad claim for every pilgrim. It shows ease where the text mentions ease."},"teachings":["The Prophet صلى الله عليه وسلم gave a concession to camel herdsmen.","The concession included not spending the night at Mina.","The report gives a specific schedule for their throwing."],"related_hadiths":[{"id":"955","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"3069","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E548" s="4" t="n"/>
@@ -13117,7 +13121,7 @@
       </c>
       <c r="D549" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Scholarly Caution","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas answered with caution, saying he did not know whether six or seven pebbles were thrown."},"heading":{"title":"Hadith About Caution When Answering Hajj Questions","description":"This narration shows Abu Mijlaz asking Ibn Abbas about a matter related to throwing stones at the jamrahs. Ibn Abbas replied that he did not know whether the Messenger of Allah صلى الله عليه وسلم threw six or seven pebbles. The core topic is scholarly caution. The hadith is not mainly giving a final ruling on the number. It records Ibn Abbas being careful with what he did not know. For searches like Ibn Abbas six or seven pebbles hadith, this report teaches honesty in religious answers and care when speaking about the Prophet's صلى الله عليه وسلم practice."},"teachings":["Ibn Abbas openly said he did not know in this matter.","Care is needed when reporting details of worship.","A respected companion did not answer beyond what he was sure about."],"related_hadiths":[{"id":"1751","book_id":"1","label":"Sahih Bukhari"},{"id":"1297","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Scholarly Caution","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas answered with caution, saying he did not know whether six or seven pebbles were thrown."},"heading":{"title":"Hadith About Caution When Answering Hajj Questions","description":"This narration shows Abu Mijlaz asking Ibn Abbas about a matter related to throwing stones at the jamrahs. Ibn Abbas replied that he did not know whether the Messenger of Allah صلى الله عليه وسلم threw six or seven pebbles. The core topic is scholarly caution. The hadith is not mainly giving a final ruling on the number. It records Ibn Abbas being careful with what he did not know. For searches like Ibn Abbas six or seven pebbles hadith, this report teaches honesty in religious answers and care when speaking about the Prophet's صلى الله عليه وسلم practice."},"teachings":["Ibn Abbas openly said he did not know in this matter.","Care is needed when reporting details of worship.","A respected companion did not answer beyond what he was sure about."],"related_hadiths":[{"id":"1751","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1297","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E549" s="4" t="n"/>
@@ -13140,7 +13144,7 @@
       </c>
       <c r="D550" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ending Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. This weak report says things become lawful after Jamrat al-Aqabah except women."},"heading":{"title":"Hadith About Jamrat al-Aqabah and Ending Ihram","description":"This narration states that when a person throws pebbles at the last jamrah, Jamrat al-Aqabah, everything becomes lawful except women, meaning sexual intercourse. The core topic is ending ihram. However, the text itself includes Abu Dawud's note that this is a weak tradition. He says the narrator al-Hajjaj neither saw al-Zuhri nor heard hadith from him. So the explanation must include that caution. People searching for hadith about Jamrat al-Aqabah and ihram should know both the wording of the report and Abu Dawud's grading note."},"teachings":["The report discusses what becomes lawful after Jamrat al-Aqabah.","The text itself says the tradition is weak.","Hadith grading notes should be noticed when studying a narration."],"related_hadiths":[{"id":"1754","book_id":"1","label":"Sahih Bukhari"},{"id":"1218a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ending Ihram","description":"$book_name$ $hadith_number$ - $chapter_name$. This weak report says things become lawful after Jamrat al-Aqabah except women."},"heading":{"title":"Hadith About Jamrat al-Aqabah and Ending Ihram","description":"This narration states that when a person throws pebbles at the last jamrah, Jamrat al-Aqabah, everything becomes lawful except women, meaning sexual intercourse. The core topic is ending ihram. However, the text itself includes Abu Dawud's note that this is a weak tradition. He says the narrator al-Hajjaj neither saw al-Zuhri nor heard hadith from him. So the explanation must include that caution. People searching for hadith about Jamrat al-Aqabah and ihram should know both the wording of the report and Abu Dawud's grading note."},"teachings":["The report discusses what becomes lawful after Jamrat al-Aqabah.","The text itself says the tradition is weak.","Hadith grading notes should be noticed when studying a narration."],"related_hadiths":[{"id":"1754","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1218a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E550" s="4" t="n"/>
@@ -13163,7 +13167,7 @@
       </c>
       <c r="D551" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shaving in Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed for mercy for those who shaved and then included those who clipped."},"heading":{"title":"Hadith About Shaving or Clipping Hair After Hajj","description":"This hadith reports the Prophet's صلى الله عليه وسلم supplication for those who shave their heads after Hajj. He said, “O Allah, have mercy on those who have themselves shaved.” The people asked about those who clip their hair. He repeated the prayer for those who shaved, and then included those who clip their hair. The core topic is shaving in Hajj. The text shows special mention of shaving and also mention of clipping. For searches like hadith about shaving hair in Hajj or Allah have mercy on those who shaved, this narration is direct and easy to understand."},"teachings":["The Prophet صلى الله عليه وسلم prayed for mercy for those who shaved their heads.","Those who clipped their hair were also included.","The narration shows both shaving and clipping in the Hajj context."],"related_hadiths":[{"id":"1728","book_id":"1","label":"Sahih Bukhari"},{"id":"1301","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Shaving in Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prayed for mercy for those who shaved and then included those who clipped."},"heading":{"title":"Hadith About Shaving or Clipping Hair After Hajj","description":"This hadith reports the Prophet's صلى الله عليه وسلم supplication for those who shave their heads after Hajj. He said, “O Allah, have mercy on those who have themselves shaved.” The people asked about those who clip their hair. He repeated the prayer for those who shaved, and then included those who clip their hair. The core topic is shaving in Hajj. The text shows special mention of shaving and also mention of clipping. For searches like hadith about shaving hair in Hajj or Allah have mercy on those who shaved, this narration is direct and easy to understand."},"teachings":["The Prophet صلى الله عليه وسلم prayed for mercy for those who shaved their heads.","Those who clipped their hair were also included.","The narration shows both shaving and clipping in the Hajj context."],"related_hadiths":[{"id":"1728","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1301","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E551" s="4" t="n"/>
@@ -13186,7 +13190,7 @@
       </c>
       <c r="D552" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Quran Recitation During Guard Duty","description":"$book_name$ $hadith_number$ - $chapter_name$. An Ansari continued reciting in prayer while wounded, then woke his companion after bowing and prostrating."},"heading":{"title":"Quran Recitation During Guard Duty: The Ansari Who Kept Praying","description":"This hadith tells a powerful scene from the journey to Dhat ar-Riqa. The Prophet صلى الله عليه وسلم asked who would keep watch, and one Muhajir and one Ansari went to the mouth of the mountain-pass. The Muhajir lay down, while the Ansari stood in prayer. An enemy saw him, recognized him as a guard, and shot arrows at him. The Ansari removed the arrows and continued until three arrows had struck him. Then he bowed, prostrated, and woke his companion. When asked why he did not wake him earlier, he said he was reciting a chapter of the Qur’an and did not like to cut it off. The main lesson in the text is love for recitation while still guarding the group."},"teachings":["The companions took turns guarding the Muslims.","The Ansari was praying while keeping watch.","He valued the Qur’an recitation and did not like to cut it short.","He still woke his companion after bowing and prostrating."],"related_hadiths":[{"id":"4129","book_id":"1","label":"Sahih Bukhari"},{"id":"4126","book_id":"1","label":"Sahih Bukhari"},{"id":"843a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Quran Recitation During Guard Duty","description":"$book_name$ $hadith_number$ - $chapter_name$. An Ansari continued reciting in prayer while wounded, then woke his companion after bowing and prostrating."},"heading":{"title":"Quran Recitation During Guard Duty: The Ansari Who Kept Praying","description":"This hadith tells a powerful scene from the journey to Dhat ar-Riqa. The Prophet صلى الله عليه وسلم asked who would keep watch, and one Muhajir and one Ansari went to the mouth of the mountain-pass. The Muhajir lay down, while the Ansari stood in prayer. An enemy saw him, recognized him as a guard, and shot arrows at him. The Ansari removed the arrows and continued until three arrows had struck him. Then he bowed, prostrated, and woke his companion. When asked why he did not wake him earlier, he said he was reciting a chapter of the Qur’an and did not like to cut it off. The main lesson in the text is love for recitation while still guarding the group."},"teachings":["The companions took turns guarding the Muslims.","The Ansari was praying while keeping watch.","He valued the Qur’an recitation and did not like to cut it short.","He still woke his companion after bowing and prostrating."],"related_hadiths":[{"id":"4129","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4126","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"843a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E552" s="4" t="n"/>
@@ -13209,7 +13213,7 @@
       </c>
       <c r="D553" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet's Shaving","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reported that the Messenger of Allah صلى الله عليه وسلم shaved his head during the Farewell Pilgrimage."},"heading":{"title":"Hadith About the Prophet صلى الله عليه وسلم Shaving His Head in Hajj","description":"This hadith gives a short and clear report from Ibn Umar: the Messenger of Allah صلى الله عليه وسلم had his head shaved during the Farewell Pilgrimage. The core topic is shaving in Hajj. The narration does not give a long explanation or compare different actions. It simply records what the Prophet صلى الله عليه وسلم did. This makes it useful for users searching for Prophet shaved head in Hajj hadith or Farewell Pilgrimage shaving hadith. The report also connects the action to the Farewell Pilgrimage, which is a key setting for learning the Prophet's صلى الله عليه وسلم Hajj practice."},"teachings":["The Prophet صلى الله عليه وسلم shaved his head in the Farewell Pilgrimage.","Ibn Umar directly reported this action.","The narration preserves a simple detail from the Prophet's صلى الله عليه وسلم Hajj."],"related_hadiths":[{"id":"1728","book_id":"1","label":"Sahih Bukhari"},{"id":"1301","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet's Shaving","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reported that the Messenger of Allah صلى الله عليه وسلم shaved his head during the Farewell Pilgrimage."},"heading":{"title":"Hadith About the Prophet صلى الله عليه وسلم Shaving His Head in Hajj","description":"This hadith gives a short and clear report from Ibn Umar: the Messenger of Allah صلى الله عليه وسلم had his head shaved during the Farewell Pilgrimage. The core topic is shaving in Hajj. The narration does not give a long explanation or compare different actions. It simply records what the Prophet صلى الله عليه وسلم did. This makes it useful for users searching for Prophet shaved head in Hajj hadith or Farewell Pilgrimage shaving hadith. The report also connects the action to the Farewell Pilgrimage, which is a key setting for learning the Prophet's صلى الله عليه وسلم Hajj practice."},"teachings":["The Prophet صلى الله عليه وسلم shaved his head in the Farewell Pilgrimage.","Ibn Umar directly reported this action.","The narration preserves a simple detail from the Prophet's صلى الله عليه وسلم Hajj."],"related_hadiths":[{"id":"1728","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1301","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E553" s="4" t="n"/>
@@ -13232,7 +13236,7 @@
       </c>
       <c r="D554" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women and Hair Clipping","description":"$book_name$ $hadith_number$ - $chapter_name$. Women are not required to shave; the Hadith states that clipping is for them."},"heading":{"title":"Hadith on Women Clipping Hair After Hajj or Umrah","description":"This narration repeats the teaching that shaving is not for women, while clipping is for them. The message is direct and easy to understand. It focuses on the hair rite after Hajj or Umrah and explains that women complete this part by clipping, not shaving. The Hadith does not discuss other details, so the meaning should not be stretched beyond the words given. For searches like women hair clipping after Umrah hadith, this narration is a clear source. It also shows that the Prophet صلى الله عليه وسلم gave guidance specific to women in this act of worship."},"teachings":["Women complete this hair rite by clipping.","Shaving is not placed upon women in this Hadith.","The Prophet صلى الله عليه وسلم gave clear guidance for women’s practice."],"related_hadiths":[{"id":"1984","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1305c","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Women and Hair Clipping","description":"$book_name$ $hadith_number$ - $chapter_name$. Women are not required to shave; the Hadith states that clipping is for them."},"heading":{"title":"Hadith on Women Clipping Hair After Hajj or Umrah","description":"This narration repeats the teaching that shaving is not for women, while clipping is for them. The message is direct and easy to understand. It focuses on the hair rite after Hajj or Umrah and explains that women complete this part by clipping, not shaving. The Hadith does not discuss other details, so the meaning should not be stretched beyond the words given. For searches like women hair clipping after Umrah hadith, this narration is a clear source. It also shows that the Prophet صلى الله عليه وسلم gave guidance specific to women in this act of worship."},"teachings":["Women complete this hair rite by clipping.","Shaving is not placed upon women in this Hadith.","The Prophet صلى الله عليه وسلم gave clear guidance for women’s practice."],"related_hadiths":[{"id":"1984","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1305c","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E554" s="4" t="n"/>
@@ -13255,7 +13259,7 @@
       </c>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umrah Before Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports that the Prophet صلى الله عليه وسلم performed Umrah before performing Hajj."},"heading":{"title":"The Prophet صلى الله عليه وسلم Performed Umrah Before Hajj","description":"This short Hadith tells us that the Messenger of Allah صلى الله عليه وسلم performed Umrah before performing Hajj. The core topic is Umrah before Hajj. The report does not list the dates, places, or number of Umrahs, so the explanation should stay with the simple point it gives. For people searching for did the Prophet perform Umrah before Hajj, this narration answers that question directly. It shows that Umrah was part of the Prophet’s صلى الله عليه وسلم practice before his Hajj. The Hadith is brief, but it is useful for understanding the link between Umrah and Hajj in his life."},"teachings":["The Prophet صلى الله عليه وسلم performed Umrah before Hajj.","Umrah was part of his practice before the Hajj mentioned here.","Short narrations can still give clear religious information."],"related_hadiths":[{"id":"1775","book_id":"1","label":"Sahih Bukhari"},{"id":"1253a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umrah Before Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Umar reports that the Prophet صلى الله عليه وسلم performed Umrah before performing Hajj."},"heading":{"title":"The Prophet صلى الله عليه وسلم Performed Umrah Before Hajj","description":"This short Hadith tells us that the Messenger of Allah صلى الله عليه وسلم performed Umrah before performing Hajj. The core topic is Umrah before Hajj. The report does not list the dates, places, or number of Umrahs, so the explanation should stay with the simple point it gives. For people searching for did the Prophet perform Umrah before Hajj, this narration answers that question directly. It shows that Umrah was part of the Prophet’s صلى الله عليه وسلم practice before his Hajj. The Hadith is brief, but it is useful for understanding the link between Umrah and Hajj in his life."},"teachings":["The Prophet صلى الله عليه وسلم performed Umrah before Hajj.","Umrah was part of his practice before the Hajj mentioned here.","Short narrations can still give clear religious information."],"related_hadiths":[{"id":"1775","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1253a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E555" s="4" t="n"/>
@@ -13278,7 +13282,7 @@
       </c>
       <c r="D556" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umrah in Dhul-Hijjah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas explains that Aisha’s Umrah in Dhul-Hijjah ended a pre-Islamic restriction."},"heading":{"title":"Umrah in Dhul-Hijjah and Ending False Restrictions","description":"This Hadith explains why the Messenger of Allah صلى الله عليه وسلم had Aisha perform Umrah in Dhul-Hijjah. Ibn Abbas says it was done to cut off the practice of the idolaters before Islam. They used to claim that Umrah was not allowed until Dhul-Hijjah and Muharram had passed and Safar had begun. The core topic is Umrah in Dhul-Hijjah. The Hadith directly shows that this old restriction was rejected. For people searching for Umrah in Dhul Hijjah hadith, this narration is important because it links Aisha’s Umrah with ending a false belief about when Umrah becomes lawful."},"teachings":["Aisha’s Umrah in Dhul-Hijjah opposed a pre-Islamic restriction.","The old claim that Umrah was unlawful until Safar was rejected.","Acts of worship should follow prophetic guidance, not inherited false customs."],"related_hadiths":[{"id":"1240a","book_id":"2","label":"Sahih Muslim"},{"id":"1778","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umrah in Dhul-Hijjah","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas explains that Aisha’s Umrah in Dhul-Hijjah ended a pre-Islamic restriction."},"heading":{"title":"Umrah in Dhul-Hijjah and Ending False Restrictions","description":"This Hadith explains why the Messenger of Allah صلى الله عليه وسلم had Aisha perform Umrah in Dhul-Hijjah. Ibn Abbas says it was done to cut off the practice of the idolaters before Islam. They used to claim that Umrah was not allowed until Dhul-Hijjah and Muharram had passed and Safar had begun. The core topic is Umrah in Dhul-Hijjah. The Hadith directly shows that this old restriction was rejected. For people searching for Umrah in Dhul Hijjah hadith, this narration is important because it links Aisha’s Umrah with ending a false belief about when Umrah becomes lawful."},"teachings":["Aisha’s Umrah in Dhul-Hijjah opposed a pre-Islamic restriction.","The old claim that Umrah was unlawful until Safar was rejected.","Acts of worship should follow prophetic guidance, not inherited false customs."],"related_hadiths":[{"id":"1240a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1778","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E556" s="4" t="n"/>
@@ -13301,7 +13305,7 @@
       </c>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ramadan Umrah Like Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Ma'qil was told to perform Umrah in Ramadan after missing Hajj with the Prophet صلى الله عليه وسلم."},"heading":{"title":"Umrah in Ramadan After Missing Hajj","description":"This Hadith gives another report about Umm Ma'qil. She missed Hajj with the Messenger of Allah صلى الله عليه وسلم because Abu Ma'qil died and their camel had been dedicated to the cause of Allah. The Prophet صلى الله عليه وسلم asked why she had not used it, saying that Hajj is in the cause of Allah. Since she missed that Hajj, he told her to perform Umrah in Ramadan, saying it is like Hajj. The narration also includes her own careful statement: Hajj is Hajj and Umrah is Umrah, and she did not know whether this was special to her. This makes the explanation balanced and faithful to the text."},"teachings":["The Prophet صلى الله عليه وسلم described Hajj as being in the cause of Allah.","Umm Ma'qil was guided to perform Umrah in Ramadan after missing Hajj.","The narrator’s caution reminds us not to overstate beyond the report."],"related_hadiths":[{"id":"1255b","book_id":"2","label":"Sahih Muslim"},{"id":"1782","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ramadan Umrah Like Hajj","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Ma'qil was told to perform Umrah in Ramadan after missing Hajj with the Prophet صلى الله عليه وسلم."},"heading":{"title":"Umrah in Ramadan After Missing Hajj","description":"This Hadith gives another report about Umm Ma'qil. She missed Hajj with the Messenger of Allah صلى الله عليه وسلم because Abu Ma'qil died and their camel had been dedicated to the cause of Allah. The Prophet صلى الله عليه وسلم asked why she had not used it, saying that Hajj is in the cause of Allah. Since she missed that Hajj, he told her to perform Umrah in Ramadan, saying it is like Hajj. The narration also includes her own careful statement: Hajj is Hajj and Umrah is Umrah, and she did not know whether this was special to her. This makes the explanation balanced and faithful to the text."},"teachings":["The Prophet صلى الله عليه وسلم described Hajj as being in the cause of Allah.","Umm Ma'qil was guided to perform Umrah in Ramadan after missing Hajj.","The narrator’s caution reminds us not to overstate beyond the report."],"related_hadiths":[{"id":"1255b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1782","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E557" s="4" t="n"/>
@@ -13324,7 +13328,7 @@
       </c>
       <c r="D558" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ramadan Umrah with Hajj Reward","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said Umrah in Ramadan was equivalent to Hajj with him."},"heading":{"title":"Umrah in Ramadan Equivalent to Hajj with the Prophet صلى الله عليه وسلم","description":"This Hadith reports a woman who wanted to perform Hajj with the Messenger of Allah صلى الله عليه وسلم. Her husband said he had no mount for her, because a certain camel was dedicated to the cause of Allah. When he asked the Prophet صلى الله عليه وسلم, he was told that letting her perform Hajj on that camel would also be in the cause of Allah. The woman also asked what action would equal Hajj with the Prophet صلى الله عليه وسلم. He told her that Umrah in Ramadan was equivalent to performing Hajj with him. The main focus is Ramadan Umrah and its special value in this report."},"teachings":["Helping someone perform Hajj can be part of the cause of Allah.","The Prophet صلى الله عليه وسلم replied to the woman’s question with kindness.","Umrah in Ramadan was described here as equal to Hajj with him."],"related_hadiths":[{"id":"1255b","book_id":"2","label":"Sahih Muslim"},{"id":"1782","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ramadan Umrah with Hajj Reward","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said Umrah in Ramadan was equivalent to Hajj with him."},"heading":{"title":"Umrah in Ramadan Equivalent to Hajj with the Prophet صلى الله عليه وسلم","description":"This Hadith reports a woman who wanted to perform Hajj with the Messenger of Allah صلى الله عليه وسلم. Her husband said he had no mount for her, because a certain camel was dedicated to the cause of Allah. When he asked the Prophet صلى الله عليه وسلم, he was told that letting her perform Hajj on that camel would also be in the cause of Allah. The woman also asked what action would equal Hajj with the Prophet صلى الله عليه وسلم. He told her that Umrah in Ramadan was equivalent to performing Hajj with him. The main focus is Ramadan Umrah and its special value in this report."},"teachings":["Helping someone perform Hajj can be part of the cause of Allah.","The Prophet صلى الله عليه وسلم replied to the woman’s question with kindness.","Umrah in Ramadan was described here as equal to Hajj with him."],"related_hadiths":[{"id":"1255b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1782","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E558" s="4" t="n"/>
@@ -13347,7 +13351,7 @@
       </c>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet’s Umrahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Aisha reports two Umrahs of the Prophet صلى الله عليه وسلم, one in Dhul-Qa'dah and one in Shawwal."},"heading":{"title":"The Prophet’s صلى الله عليه وسلم Umrahs in Dhul-Qa'dah and Shawwal","description":"This Hadith reports from Aisha, Mother of the Believers, that the Messenger of Allah صلى الله عليه وسلم performed two Umrahs: one in Dhul-Qa'dah and one in Shawwal. The core topic is the timing of the Prophet’s Umrahs. The narration is brief and does not explain other Umrahs or compare reports, so the explanation should remain tied to the given wording. For people searching for the Prophet’s Umrah in Dhul Qa'dah or Shawwal, this Hadith gives a direct report. It shows that these two months are mentioned in connection with his Umrah practice in this narration."},"teachings":["Aisha reported two Umrahs of the Prophet صلى الله عليه وسلم in this narration.","One Umrah is mentioned in Dhul-Qa'dah.","One Umrah is mentioned in Shawwal."],"related_hadiths":[{"id":"1253a","book_id":"2","label":"Sahih Muslim"},{"id":"1775","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prophet’s Umrahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Aisha reports two Umrahs of the Prophet صلى الله عليه وسلم, one in Dhul-Qa'dah and one in Shawwal."},"heading":{"title":"The Prophet’s صلى الله عليه وسلم Umrahs in Dhul-Qa'dah and Shawwal","description":"This Hadith reports from Aisha, Mother of the Believers, that the Messenger of Allah صلى الله عليه وسلم performed two Umrahs: one in Dhul-Qa'dah and one in Shawwal. The core topic is the timing of the Prophet’s Umrahs. The narration is brief and does not explain other Umrahs or compare reports, so the explanation should remain tied to the given wording. For people searching for the Prophet’s Umrah in Dhul Qa'dah or Shawwal, this Hadith gives a direct report. It shows that these two months are mentioned in connection with his Umrah practice in this narration."},"teachings":["Aisha reported two Umrahs of the Prophet صلى الله عليه وسلم in this narration.","One Umrah is mentioned in Dhul-Qa'dah.","One Umrah is mentioned in Shawwal."],"related_hadiths":[{"id":"1253a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1775","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E559" s="4" t="n"/>
@@ -13370,7 +13374,7 @@
       </c>
       <c r="D560" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Number of Prophet’s Umrahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Aisha corrected the count of the Prophet’s صلى الله عليه وسلم Umrahs beyond the Farewell Hajj."},"heading":{"title":"How Many Umrahs Did the Prophet صلى الله عليه وسلم Perform?","description":"This Hadith records a discussion about the number of Umrahs performed by the Messenger of Allah صلى الله عليه وسلم. Ibn Umar was asked and answered that he performed two. Aisha then said that Ibn Umar knew the Prophet صلى الله عليه وسلم performed three Umrahs besides the one he combined with the Farewell Pilgrimage. The core topic is the number of Prophet’s Umrahs. The Hadith is useful because it shows a report, a correction, and a count connected to the Farewell Hajj. For searchers asking how many Umrahs did the Prophet perform, this narration provides Aisha’s statement in clear terms."},"teachings":["The Companions discussed the number of the Prophet’s صلى الله عليه وسلم Umrahs.","Aisha mentioned three Umrahs besides the one joined with the Farewell Hajj.","The Farewell Pilgrimage included an Umrah according to this report."],"related_hadiths":[{"id":"1253a","book_id":"2","label":"Sahih Muslim"},{"id":"1775","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Number of Prophet’s Umrahs","description":"$book_name$ $hadith_number$ - $chapter_name$. Aisha corrected the count of the Prophet’s صلى الله عليه وسلم Umrahs beyond the Farewell Hajj."},"heading":{"title":"How Many Umrahs Did the Prophet صلى الله عليه وسلم Perform?","description":"This Hadith records a discussion about the number of Umrahs performed by the Messenger of Allah صلى الله عليه وسلم. Ibn Umar was asked and answered that he performed two. Aisha then said that Ibn Umar knew the Prophet صلى الله عليه وسلم performed three Umrahs besides the one he combined with the Farewell Pilgrimage. The core topic is the number of Prophet’s Umrahs. The Hadith is useful because it shows a report, a correction, and a count connected to the Farewell Hajj. For searchers asking how many Umrahs did the Prophet perform, this narration provides Aisha’s statement in clear terms."},"teachings":["The Companions discussed the number of the Prophet’s صلى الله عليه وسلم Umrahs.","Aisha mentioned three Umrahs besides the one joined with the Farewell Hajj.","The Farewell Pilgrimage included an Umrah according to this report."],"related_hadiths":[{"id":"1253a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1775","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E560" s="4" t="n"/>
@@ -13393,7 +13397,7 @@
       </c>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Umrahs of the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas lists the four Umrahs performed by the Messenger of Allah صلى الله عليه وسلم."},"heading":{"title":"Four Umrahs of the Prophet صلى الله عليه وسلم Listed by Ibn Abbas","description":"This Hadith gives a clear list of four Umrahs performed by the Messenger of Allah صلى الله عليه وسلم. Ibn Abbas names the Umrah of al-Hudaybiyyah, the next year’s Umrah that was agreed upon, the Umrah from al-Ji'ranah, and the Umrah combined with his Hajj. The core topic is four Umrahs of the Prophet. This narration is especially useful for people searching for a list of the Prophet’s Umrahs. It does not add details about each journey, so the explanation should stay focused on the names and count given in the text."},"teachings":["Ibn Abbas listed four Umrahs of the Prophet صلى الله عليه وسلم.","One Umrah was connected to al-Hudaybiyyah.","One Umrah was combined with his Hajj."],"related_hadiths":[{"id":"1253a","book_id":"2","label":"Sahih Muslim"},{"id":"1775","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Four Umrahs of the Prophet","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas lists the four Umrahs performed by the Messenger of Allah صلى الله عليه وسلم."},"heading":{"title":"Four Umrahs of the Prophet صلى الله عليه وسلم Listed by Ibn Abbas","description":"This Hadith gives a clear list of four Umrahs performed by the Messenger of Allah صلى الله عليه وسلم. Ibn Abbas names the Umrah of al-Hudaybiyyah, the next year’s Umrah that was agreed upon, the Umrah from al-Ji'ranah, and the Umrah combined with his Hajj. The core topic is four Umrahs of the Prophet. This narration is especially useful for people searching for a list of the Prophet’s Umrahs. It does not add details about each journey, so the explanation should stay focused on the names and count given in the text."},"teachings":["Ibn Abbas listed four Umrahs of the Prophet صلى الله عليه وسلم.","One Umrah was connected to al-Hudaybiyyah.","One Umrah was combined with his Hajj."],"related_hadiths":[{"id":"1253a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1775","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E561" s="4" t="n"/>
@@ -13416,7 +13420,7 @@
       </c>
       <c r="D562" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aisha’s Umrah from Tan'im","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم instructed AbdurRahman to take Aisha for Umrah from at-Tan'im."},"heading":{"title":"Aisha’s Umrah from at-Tan'im","description":"This Hadith reports that the Messenger of Allah صلى الله عليه وسلم told AbdurRahman to place his sister Aisha behind him on the camel and make her perform Umrah from at-Tan'im. He also instructed that when they came down from the hillock, she should enter ihram for Umrah. The core topic is Aisha’s Umrah from Tan'im. The Hadith gives a specific instruction, route, and action. It also includes the Prophet’s صلى الله عليه وسلم statement that it was an accepted Umrah. For people searching for Aisha Umrah from Tan'im hadith, this narration is directly about that event."},"teachings":["The Prophet صلى الله عليه وسلم instructed AbdurRahman to help Aisha perform Umrah.","Aisha was to enter ihram from at-Tan'im.","The narration describes this Umrah as accepted."],"related_hadiths":[{"id":"1778","book_id":"4","label":"Sunan Abu Dawud"},{"id":"1788","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aisha’s Umrah from Tan'im","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم instructed AbdurRahman to take Aisha for Umrah from at-Tan'im."},"heading":{"title":"Aisha’s Umrah from at-Tan'im","description":"This Hadith reports that the Messenger of Allah صلى الله عليه وسلم told AbdurRahman to place his sister Aisha behind him on the camel and make her perform Umrah from at-Tan'im. He also instructed that when they came down from the hillock, she should enter ihram for Umrah. The core topic is Aisha’s Umrah from Tan'im. The Hadith gives a specific instruction, route, and action. It also includes the Prophet’s صلى الله عليه وسلم statement that it was an accepted Umrah. For people searching for Aisha Umrah from Tan'im hadith, this narration is directly about that event."},"teachings":["The Prophet صلى الله عليه وسلم instructed AbdurRahman to help Aisha perform Umrah.","Aisha was to enter ihram from at-Tan'im.","The narration describes this Umrah as accepted."],"related_hadiths":[{"id":"1778","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"1788","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E562" s="4" t="n"/>
@@ -13439,7 +13443,7 @@
       </c>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ihram from al-Ji'ranah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم entered al-Ji'ranah, prayed, wore ihram, and travelled toward Makkah."},"heading":{"title":"The Prophet صلى الله عليه وسلم Wore Ihram at al-Ji'ranah","description":"This Hadith describes the Prophet’s صلى الله عليه وسلم entry into al-Ji'ranah. He came to the mosque there and prayed as long as Allah wished. Then he wore ihram, mounted his camel, and faced Batn Sarif until he reached the road leading to Madinah. The report says he returned from Makkah at night to al-Ji'ranah as if he had spent the night at Makkah. The core topic is ihram from al-Ji'ranah. The narration gives a route and a sequence: entering, praying, wearing ihram, riding, and travelling. It is useful for searches about the Prophet’s Umrah from Ji'ranah."},"teachings":["The Prophet صلى الله عليه وسلم prayed at the mosque in al-Ji'ranah.","He wore ihram after that prayer.","The narration records his movement from al-Ji'ranah toward Makkah."],"related_hadiths":[{"id":"1253a","book_id":"2","label":"Sahih Muslim"},{"id":"1775","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ihram from al-Ji'ranah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم entered al-Ji'ranah, prayed, wore ihram, and travelled toward Makkah."},"heading":{"title":"The Prophet صلى الله عليه وسلم Wore Ihram at al-Ji'ranah","description":"This Hadith describes the Prophet’s صلى الله عليه وسلم entry into al-Ji'ranah. He came to the mosque there and prayed as long as Allah wished. Then he wore ihram, mounted his camel, and faced Batn Sarif until he reached the road leading to Madinah. The report says he returned from Makkah at night to al-Ji'ranah as if he had spent the night at Makkah. The core topic is ihram from al-Ji'ranah. The narration gives a route and a sequence: entering, praying, wearing ihram, riding, and travelling. It is useful for searches about the Prophet’s Umrah from Ji'ranah."},"teachings":["The Prophet صلى الله عليه وسلم prayed at the mosque in al-Ji'ranah.","He wore ihram after that prayer.","The narration records his movement from al-Ji'ranah toward Makkah."],"related_hadiths":[{"id":"1253a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1775","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E563" s="4" t="n"/>
@@ -13462,7 +13466,7 @@
       </c>
       <c r="D564" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umrat al-Qada Stay","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم stayed three days during Umrat al-Qada."},"heading":{"title":"The Prophet’s صلى الله عليه وسلم Three-Day Stay During Umrat al-Qada","description":"This short Hadith reports from Ibn Abbas that the Messenger of Allah صلى الله عليه وسلم stayed for three days during Umrat al-Qada. The core topic is Umrat al-Qada. The narration does not give extra detail about what happened during those days, so the explanation should remain limited to the statement itself. For users searching for how long the Prophet stayed in Makkah during Umrat al-Qada, this Hadith gives a direct answer: three days. Its value is in the clear time detail preserved in the report."},"teachings":["The Prophet صلى الله عليه وسلم stayed three days during Umrat al-Qada.","The Hadith gives a clear time detail.","The report focuses on the length of stay, not extra events."],"related_hadiths":[{"id":"4251","book_id":"1","label":"Sahih Bukhari"},{"id":"1783","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umrat al-Qada Stay","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports that the Prophet صلى الله عليه وسلم stayed three days during Umrat al-Qada."},"heading":{"title":"The Prophet’s صلى الله عليه وسلم Three-Day Stay During Umrat al-Qada","description":"This short Hadith reports from Ibn Abbas that the Messenger of Allah صلى الله عليه وسلم stayed for three days during Umrat al-Qada. The core topic is Umrat al-Qada. The narration does not give extra detail about what happened during those days, so the explanation should remain limited to the statement itself. For users searching for how long the Prophet stayed in Makkah during Umrat al-Qada, this Hadith gives a direct answer: three days. Its value is in the clear time detail preserved in the report."},"teachings":["The Prophet صلى الله عليه وسلم stayed three days during Umrat al-Qada.","The Hadith gives a clear time detail.","The report focuses on the length of stay, not extra events."],"related_hadiths":[{"id":"4251","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1783","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E564" s="4" t="n"/>
@@ -13485,7 +13489,7 @@
       </c>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf al-Ziyarah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم performed Tawaf al-Ziyarah on the day of sacrifice, then prayed Dhuhr at Mina."},"heading":{"title":"Tawaf al-Ziyarah on the Day of Sacrifice","description":"This Hadith reports from Ibn Umar that the Prophet صلى الله عليه وسلم performed the obligatory circumambulation, known as Tawaf al-Ziyarah, on the day of sacrifice. After that, he returned and offered the noon prayer at Mina. The core topic is Tawaf al-Ziyarah. The narration gives a simple order: Tawaf on the day of sacrifice, then Dhuhr prayer at Mina after returning. For people searching for Tawaf al-Ziyarah hadith or when the Prophet performed Tawaf al-Ifadah, this report gives a clear action and timing from the Hajj journey."},"teachings":["The Prophet صلى الله عليه وسلم performed Tawaf al-Ziyarah on the day of sacrifice.","He returned to Mina after the Tawaf.","He offered the noon prayer at Mina after returning."],"related_hadiths":[{"id":"1308a","book_id":"2","label":"Sahih Muslim"},{"id":"1732","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tawaf al-Ziyarah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم performed Tawaf al-Ziyarah on the day of sacrifice, then prayed Dhuhr at Mina."},"heading":{"title":"Tawaf al-Ziyarah on the Day of Sacrifice","description":"This Hadith reports from Ibn Umar that the Prophet صلى الله عليه وسلم performed the obligatory circumambulation, known as Tawaf al-Ziyarah, on the day of sacrifice. After that, he returned and offered the noon prayer at Mina. The core topic is Tawaf al-Ziyarah. The narration gives a simple order: Tawaf on the day of sacrifice, then Dhuhr prayer at Mina after returning. For people searching for Tawaf al-Ziyarah hadith or when the Prophet performed Tawaf al-Ifadah, this report gives a clear action and timing from the Hajj journey."},"teachings":["The Prophet صلى الله عليه وسلم performed Tawaf al-Ziyarah on the day of sacrifice.","He returned to Mina after the Tawaf.","He offered the noon prayer at Mina after returning."],"related_hadiths":[{"id":"1308a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1732","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E565" s="4" t="n"/>
@@ -13508,7 +13512,7 @@
       </c>
       <c r="D566" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ihram and Tawaf al-Ziyarah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم explained what remains restricted before Tawaf al-Ziyarah is performed."},"heading":{"title":"Ihram Restrictions Before Tawaf al-Ziyarah","description":"This Hadith explains a detailed point about Hajj after stoning the jamrah on the day of sacrifice. Wahb ibn Zam'ah had not performed the obligatory circumambulation, Tawaf al-Ziyarah, and was wearing a shirt. The Prophet صلى الله عليه وسلم told him to remove it. He explained that after throwing the stones, people were allowed to leave ihram restrictions except regarding women. But if evening came before they performed Tawaf of the House, they would return to the sacred state as before stoning, until they completed the Tawaf. The core topic is ihram and Tawaf al-Ziyarah. The Hadith should be read carefully because it gives a specific condition."},"teachings":["Stoning the jamrah allowed some ihram restrictions to be lifted in this report.","Intercourse with women remained excluded from that allowance.","Tawaf al-Ziyarah was required before fully moving beyond the condition described."],"related_hadiths":[{"id":"1308a","book_id":"2","label":"Sahih Muslim"},{"id":"1732","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ihram and Tawaf al-Ziyarah","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم explained what remains restricted before Tawaf al-Ziyarah is performed."},"heading":{"title":"Ihram Restrictions Before Tawaf al-Ziyarah","description":"This Hadith explains a detailed point about Hajj after stoning the jamrah on the day of sacrifice. Wahb ibn Zam'ah had not performed the obligatory circumambulation, Tawaf al-Ziyarah, and was wearing a shirt. The Prophet صلى الله عليه وسلم told him to remove it. He explained that after throwing the stones, people were allowed to leave ihram restrictions except regarding women. But if evening came before they performed Tawaf of the House, they would return to the sacred state as before stoning, until they completed the Tawaf. The core topic is ihram and Tawaf al-Ziyarah. The Hadith should be read carefully because it gives a specific condition."},"teachings":["Stoning the jamrah allowed some ihram restrictions to be lifted in this report.","Intercourse with women remained excluded from that allowance.","Tawaf al-Ziyarah was required before fully moving beyond the condition described."],"related_hadiths":[{"id":"1308a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"1732","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E566" s="4" t="n"/>
@@ -13531,7 +13535,7 @@
       </c>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dozing Before Prayer and Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. A man spoke privately with the Prophet before prayer; some people dozed, then he led them without mention of ablution."},"heading":{"title":"Hadith About Isha Prayer, Dozing, and Ablution","description":"This hadith is often searched as a hadith about dozing before prayer and wudu. The report says the people stood for the night prayer, then a man said he had something to tell the Messenger of Allah. The Prophet listened to him privately until the people, or some of them, dozed off. After that, he led them in prayer. The key point in the wording is simple: Thabit al-Bunani did not mention ablution. So the lesson should stay close to the text. It shows the Prophet giving time to someone’s need before prayer, and it notes that dozing happened before the prayer was led."},"teachings":["The Prophet gave attention to a person who had a need before the prayer.","Some people dozed while waiting, and the prayer was still led afterward.","The narrator carefully noted that ablution was not mentioned in this report."],"related_hadiths":[{"id":"761a","book_id":"2","label":"Sahih Muslim"},{"id":"761b","book_id":"2","label":"Sahih Muslim"},{"id":"763f","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Dozing Before Prayer and Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. A man spoke privately with the Prophet before prayer; some people dozed, then he led them without mention of ablution."},"heading":{"title":"Hadith About Isha Prayer, Dozing, and Ablution","description":"This hadith is often searched as a hadith about dozing before prayer and wudu. The report says the people stood for the night prayer, then a man said he had something to tell the Messenger of Allah. The Prophet listened to him privately until the people, or some of them, dozed off. After that, he led them in prayer. The key point in the wording is simple: Thabit al-Bunani did not mention ablution. So the lesson should stay close to the text. It shows the Prophet giving time to someone’s need before prayer, and it notes that dozing happened before the prayer was led."},"teachings":["The Prophet gave attention to a person who had a need before the prayer.","Some people dozed while waiting, and the prayer was still led afterward.","The narrator carefully noted that ablution was not mentioned in this report."],"related_hadiths":[{"id":"761a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"761b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"763f","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E567" s="4" t="n"/>
@@ -13554,7 +13558,7 @@
       </c>
       <c r="D568" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sleep in Prostration and Ablution","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet sleeping in prostration, then praying without ablution; Abu Dawud flags part of the wording as rejected."},"heading":{"title":"Sleep in Prostration and Wudu Hadith Explained","description":"This hadith is searched by many people as the sleep in prostration wudu hadith. The report says the Messenger of Allah would prostrate, sleep, and make puffing sounds, then stand and pray without performing ablution. Ibn Abbas asked about that, and the answer in this narration links ablution to sleeping while lying down. The text also includes a very important note from Abu Dawud: the wording about ablution being necessary for one who sleeps lying down is called munkar, meaning rejected. So the explanation must be careful. The report itself also says the Prophet was protected, and Aishah reported that his eyes slept but his heart did not sleep."},"teachings":["The report describes the Prophet sleeping in prostration, then praying without ablution.","Abu Dawud clearly notes weakness in the added wording about lying down.","The text points to the special state of the Prophet: his eyes slept, but his heart did not."],"related_hadiths":[{"id":"1147","book_id":"1","label":"Sahih Bukhari"},{"id":"2013","book_id":"1","label":"Sahih Bukhari"},{"id":"763f","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Sleep in Prostration and Ablution","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas reports the Prophet sleeping in prostration, then praying without ablution; Abu Dawud flags part of the wording as rejected."},"heading":{"title":"Sleep in Prostration and Wudu Hadith Explained","description":"This hadith is searched by many people as the sleep in prostration wudu hadith. The report says the Messenger of Allah would prostrate, sleep, and make puffing sounds, then stand and pray without performing ablution. Ibn Abbas asked about that, and the answer in this narration links ablution to sleeping while lying down. The text also includes a very important note from Abu Dawud: the wording about ablution being necessary for one who sleeps lying down is called munkar, meaning rejected. So the explanation must be careful. The report itself also says the Prophet was protected, and Aishah reported that his eyes slept but his heart did not sleep."},"teachings":["The report describes the Prophet sleeping in prostration, then praying without ablution.","Abu Dawud clearly notes weakness in the added wording about lying down.","The text points to the special state of the Prophet: his eyes slept, but his heart did not."],"related_hadiths":[{"id":"1147","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2013","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"763f","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E568" s="4" t="n"/>
@@ -13577,7 +13581,7 @@
       </c>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Madhi Requires Wudu, Not Ghusl","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali was told not to bathe repeatedly for madhi; he should wash his penis and perform prayer ablution, while semen requires ghusl."},"heading":{"title":"Madhi and Wudu: When Ghusl Is Not Required","description":"This hadith is one of the key texts people search for as the madhi wudu hadith. Ali said he had excessive prostatic fluid and used to bathe so often that his back cracked. When the matter was mentioned to the Prophet, he said, “Do not do so.” The instruction was clear: when madhi is found, wash the penis and perform ablution as done for prayer. But when seminal emission occurs, then take a bath. The hadith teaches a balanced response. It does not treat every fluid the same way. It also shows that hardship from repeated bathing was corrected by a simpler act based on the type of discharge."},"teachings":["Madhi is treated with washing the private part and performing wudu.","Repeated ghusl for madhi was corrected in this report.","Seminal emission is mentioned separately as requiring a bath."],"related_hadiths":[{"id":"269","book_id":"1","label":"Sahih Bukhari"},{"id":"303c","book_id":"2","label":"Sahih Muslim"},{"id":"346a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Madhi Requires Wudu, Not Ghusl","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali was told not to bathe repeatedly for madhi; he should wash his penis and perform prayer ablution, while semen requires ghusl."},"heading":{"title":"Madhi and Wudu: When Ghusl Is Not Required","description":"This hadith is one of the key texts people search for as the madhi wudu hadith. Ali said he had excessive prostatic fluid and used to bathe so often that his back cracked. When the matter was mentioned to the Prophet, he said, “Do not do so.” The instruction was clear: when madhi is found, wash the penis and perform ablution as done for prayer. But when seminal emission occurs, then take a bath. The hadith teaches a balanced response. It does not treat every fluid the same way. It also shows that hardship from repeated bathing was corrected by a simpler act based on the type of discharge."},"teachings":["Madhi is treated with washing the private part and performing wudu.","Repeated ghusl for madhi was corrected in this report.","Seminal emission is mentioned separately as requiring a bath."],"related_hadiths":[{"id":"269","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"303c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"346a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E569" s="4" t="n"/>
@@ -13600,7 +13604,7 @@
       </c>
       <c r="D570" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Madhi Before Intercourse","description":"$book_name$ $hadith_number$ - $chapter_name$. Al-Miqdad asked about madhi for Ali, and the Prophet instructed washing the private part and performing ablution for prayer."},"heading":{"title":"Madhi Before Intercourse: Wudu Hadith Explained","description":"This hadith is closely searched as madhi before intercourse wudu hadith. Ali asked al-Miqdad to ask the Messenger of Allah because he felt shy due to the Prophet’s daughter being his wife. The question was about a man who approaches his wife and prostatic fluid comes out. The Prophet’s answer was practical and direct: when any of you finds that, he should wash his private part and perform ablution as he does for prayer. The report teaches that honest questions about purity are part of religious life. It also shows a respectful way of asking through someone else when a person feels shy."},"teachings":["A person may ask a sensitive purity question in a respectful way.","For madhi, the instruction is washing the private part and performing wudu.","The Prophet’s answer was simple and practical."],"related_hadiths":[{"id":"269","book_id":"1","label":"Sahih Bukhari"},{"id":"303c","book_id":"2","label":"Sahih Muslim"},{"id":"346a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Madhi Before Intercourse","description":"$book_name$ $hadith_number$ - $chapter_name$. Al-Miqdad asked about madhi for Ali, and the Prophet instructed washing the private part and performing ablution for prayer."},"heading":{"title":"Madhi Before Intercourse: Wudu Hadith Explained","description":"This hadith is closely searched as madhi before intercourse wudu hadith. Ali asked al-Miqdad to ask the Messenger of Allah because he felt shy due to the Prophet’s daughter being his wife. The question was about a man who approaches his wife and prostatic fluid comes out. The Prophet’s answer was practical and direct: when any of you finds that, he should wash his private part and perform ablution as he does for prayer. The report teaches that honest questions about purity are part of religious life. It also shows a respectful way of asking through someone else when a person feels shy."},"teachings":["A person may ask a sensitive purity question in a respectful way.","For madhi, the instruction is washing the private part and performing wudu.","The Prophet’s answer was simple and practical."],"related_hadiths":[{"id":"269","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"303c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"346a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E570" s="4" t="n"/>
@@ -13623,7 +13627,7 @@
       </c>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Safeguarding from Urine Impurity","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn why guarding oneself from urine impurity is a serious part of cleanliness and personal worship."},"heading":{"title":"Hadith About Safeguarding from Urine Impurity","description":"This hadith about safeguarding from urine impurity teaches a simple but serious rule of taharah. The report from Ibn Abbas says the wording is about a person who did not cover himself while urinating, or did not safeguard himself from urine. The core lesson is not about shame or hardship. It is about being careful with urine so it does not soil the body or clothes. In everyday words, Islamic cleanliness is not only about looking clean. It also includes private habits that protect purity before prayer and daily worship. The related search intent behind this hadith is usually “hadith about urine impurity” or “protect yourself from urine hadith.” The message stays clear: a believer should take care while relieving himself."},"teachings":["Safeguarding from urine is part of personal purity.","Small private habits can affect a person’s cleanliness.","Care during urination helps protect the body and clothes from impurity."],"related_hadiths":[{"id":"216","book_id":"1","label":"Sahih Bukhari"},{"id":"292a","book_id":"2","label":"Sahih Muslim"},{"id":"226","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Safeguarding from Urine Impurity","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn why guarding oneself from urine impurity is a serious part of cleanliness and personal worship."},"heading":{"title":"Hadith About Safeguarding from Urine Impurity","description":"This hadith about safeguarding from urine impurity teaches a simple but serious rule of taharah. The report from Ibn Abbas says the wording is about a person who did not cover himself while urinating, or did not safeguard himself from urine. The core lesson is not about shame or hardship. It is about being careful with urine so it does not soil the body or clothes. In everyday words, Islamic cleanliness is not only about looking clean. It also includes private habits that protect purity before prayer and daily worship. The related search intent behind this hadith is usually “hadith about urine impurity” or “protect yourself from urine hadith.” The message stays clear: a believer should take care while relieving himself."},"teachings":["Safeguarding from urine is part of personal purity.","Small private habits can affect a person’s cleanliness.","Care during urination helps protect the body and clothes from impurity."],"related_hadiths":[{"id":"216","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"292a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"226","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E571" s="4" t="n"/>
@@ -13646,7 +13650,7 @@
       </c>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Madhi on Clothes","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet told Sahl that ablution is enough for madhi and that water may be sprinkled where it touches clothing."},"heading":{"title":"Madhi on Clothes: Sprinkle Water and Perform Wudu","description":"This hadith answers two common searches: does madhi require ghusl and what to do if madhi gets on clothes. Sahl ibn Hunayf said he suffered greatly from frequent prostatic fluid and used to bathe very often. When he asked the Messenger of Allah, the answer was that ablution was sufficient for him because of it. Then he asked about his clothes. The Prophet said it was enough to take a handful of water and sprinkle it on the clothing where he thought it had smeared it. The hadith gives ease without ignoring cleanliness. It tells the person what to do and removes the burden of repeated bathing."},"teachings":["For madhi, ablution is described as sufficient in this report.","If madhi smears clothing, water may be sprinkled where it is seen or thought to have touched.","The answer reduced hardship from frequent bathing."],"related_hadiths":[{"id":"269","book_id":"1","label":"Sahih Bukhari"},{"id":"303c","book_id":"2","label":"Sahih Muslim"},{"id":"346a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Madhi on Clothes","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet told Sahl that ablution is enough for madhi and that water may be sprinkled where it touches clothing."},"heading":{"title":"Madhi on Clothes: Sprinkle Water and Perform Wudu","description":"This hadith answers two common searches: does madhi require ghusl and what to do if madhi gets on clothes. Sahl ibn Hunayf said he suffered greatly from frequent prostatic fluid and used to bathe very often. When he asked the Messenger of Allah, the answer was that ablution was sufficient for him because of it. Then he asked about his clothes. The Prophet said it was enough to take a handful of water and sprinkle it on the clothing where he thought it had smeared it. The hadith gives ease without ignoring cleanliness. It tells the person what to do and removes the burden of repeated bathing."},"teachings":["For madhi, ablution is described as sufficient in this report.","If madhi smears clothing, water may be sprinkled where it is seen or thought to have touched.","The answer reduced hardship from frequent bathing."],"related_hadiths":[{"id":"269","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"303c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"346a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E572" s="4" t="n"/>
@@ -13669,7 +13673,7 @@
       </c>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ghusl Becomes Obligatory","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said that when the circumcised parts meet in intercourse, bath becomes obligatory."},"heading":{"title":"When Does Ghusl Become Obligatory? Hadith Explained","description":"This hadith gives a direct answer to one of the most searched purity questions: when does ghusl become obligatory. Abu Hurairah reported that the Prophet said when a man sits between the four parts of a woman and the circumcised parts join together, then bath becomes obligatory. The wording is about intercourse and the duty of ghusl. It does not depend in this wording on a separate mention of emission. The explanation should stay with the text and avoid adding a long legal discussion. The key message is clear: the meeting of the circumcised parts in intercourse is stated as a cause for ghusl becoming required."},"teachings":["The hadith states that ghusl becomes obligatory in the described case.","The wording links the obligation to intercourse.","The report gives a clear purity instruction after marital relations."],"related_hadiths":[{"id":"291","book_id":"1","label":"Sahih Bukhari"},{"id":"349","book_id":"2","label":"Sahih Muslim"},{"id":"191","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ghusl Becomes Obligatory","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet said that when the circumcised parts meet in intercourse, bath becomes obligatory."},"heading":{"title":"When Does Ghusl Become Obligatory? Hadith Explained","description":"This hadith gives a direct answer to one of the most searched purity questions: when does ghusl become obligatory. Abu Hurairah reported that the Prophet said when a man sits between the four parts of a woman and the circumcised parts join together, then bath becomes obligatory. The wording is about intercourse and the duty of ghusl. It does not depend in this wording on a separate mention of emission. The explanation should stay with the text and avoid adding a long legal discussion. The key message is clear: the meeting of the circumcised parts in intercourse is stated as a cause for ghusl becoming required."},"teachings":["The hadith states that ghusl becomes obligatory in the described case.","The wording links the obligation to intercourse.","The report gives a clear purity instruction after marital relations."],"related_hadiths":[{"id":"291","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"349","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"191","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E573" s="4" t="n"/>
@@ -13692,7 +13696,7 @@
       </c>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Covering While Relieving Oneself","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم covered himself while urinating and taught care, modesty, and balance in matters of purification."},"heading":{"title":"Hadith About Covering While Relieving Oneself","description":"This hadith about covering while relieving oneself gives a clear picture of modesty and purity. The Prophet صلى الله عليه وسلم came out with a leather shield, covered himself with it, and urinated. Some people made a comment, saying he was urinating as a woman does. The Prophet صلى الله عليه وسلم answered by reminding them of what happened to a man from Banu Isra’il, where strict handling of urine had become extreme, and a person who stopped them was punished in his grave. The hadith keeps two points together: covering oneself is proper manners, and speech about the Prophet’s action should be careful. It also points to the seriousness of urine impurity without turning the matter into harshness beyond what the text says."},"teachings":["Covering oneself while relieving is a part of modest conduct.","People should avoid careless comments about prophetic actions.","Purification should be taken seriously without turning it into needless hardship."],"related_hadiths":[{"id":"226","book_id":"1","label":"Sahih Bukhari"},{"id":"224","book_id":"1","label":"Sahih Bukhari"},{"id":"292a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Covering While Relieving Oneself","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم covered himself while urinating and taught care, modesty, and balance in matters of purification."},"heading":{"title":"Hadith About Covering While Relieving Oneself","description":"This hadith about covering while relieving oneself gives a clear picture of modesty and purity. The Prophet صلى الله عليه وسلم came out with a leather shield, covered himself with it, and urinated. Some people made a comment, saying he was urinating as a woman does. The Prophet صلى الله عليه وسلم answered by reminding them of what happened to a man from Banu Isra’il, where strict handling of urine had become extreme, and a person who stopped them was punished in his grave. The hadith keeps two points together: covering oneself is proper manners, and speech about the Prophet’s action should be careful. It also points to the seriousness of urine impurity without turning the matter into harshness beyond what the text says."},"teachings":["Covering oneself while relieving is a part of modest conduct.","People should avoid careless comments about prophetic actions.","Purification should be taken seriously without turning it into needless hardship."],"related_hadiths":[{"id":"226","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"224","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"292a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E574" s="4" t="n"/>
@@ -13715,7 +13719,7 @@
       </c>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ghusl with Plaited Hair","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how Aisha described ghusl, wudu before washing, and extra water for plaited hair."},"heading":{"title":"Hadith About Ghusl and Plaited Hair: Aisha’s Clear Description","description":"This hadith focuses on ghusl, especially how water was poured over the head. Aisha was asked how they used to bathe, and she gave a clear answer from what she knew. She said the Messenger of Allah صلى الله عليه وسلم began with ablution like the ablution for prayer, then poured water over his head three times. She also explained that they poured water over their heads five times because of plaits. So the main lesson is practical and simple: ghusl is done with care, and the condition of the hair may require more attention. The hadith about ghusl with plaited hair shows that purification is not rushed. The goal is to wash properly, while keeping the action tied to what was reported."},"teachings":["Ghusl may begin with ablution like the ablution for prayer.","The Prophet صلى الله عليه وسلم poured water over his head three times in this report.","Aisha mentioned extra pouring because of plaited hair.","Questions about purification were answered with practical detail."],"related_hadiths":[{"id":"248","book_id":"1","label":"Sahih Bukhari"},{"id":"254","book_id":"1","label":"Sahih Bukhari"},{"id":"330a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ghusl with Plaited Hair","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how Aisha described ghusl, wudu before washing, and extra water for plaited hair."},"heading":{"title":"Hadith About Ghusl and Plaited Hair: Aisha’s Clear Description","description":"This hadith focuses on ghusl, especially how water was poured over the head. Aisha was asked how they used to bathe, and she gave a clear answer from what she knew. She said the Messenger of Allah صلى الله عليه وسلم began with ablution like the ablution for prayer, then poured water over his head three times. She also explained that they poured water over their heads five times because of plaits. So the main lesson is practical and simple: ghusl is done with care, and the condition of the hair may require more attention. The hadith about ghusl with plaited hair shows that purification is not rushed. The goal is to wash properly, while keeping the action tied to what was reported."},"teachings":["Ghusl may begin with ablution like the ablution for prayer.","The Prophet صلى الله عليه وسلم poured water over his head three times in this report.","Aisha mentioned extra pouring because of plaited hair.","Questions about purification were answered with practical detail."],"related_hadiths":[{"id":"248","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"254","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"330a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E575" s="4" t="n"/>
@@ -13738,7 +13742,7 @@
       </c>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Cleaning Hands in Ghusl","description":"$book_name$ $hadith_number$ - $chapter_name$. Aisha reports that the Prophet صلى الله عليه وسلم began ghusl by washing his hands, cleaning them well, then making wudu."},"heading":{"title":"Hadith About Cleaning the Hands Before Ghusl","description":"This hadith explains part of the ghusl after janabah by showing how the Messenger of Allah صلى الله عليه وسلم began. Aisha said that when he intended to bathe, he started with his hands and washed them. He then washed the joints of his limbs and poured water. After cleansing his hands, he rubbed them on the wall so they would be clean with dust, then he performed ablution and poured water over his head. The key point is the careful order of purification. The hadith about cleaning hands before ghusl is not a broad ruling on every detail of ghusl; it simply reports how he washed and cleaned before moving to wudu and washing the head."},"teachings":["The Prophet صلى الله عليه وسلم began this ghusl by washing his hands.","He cleaned the hands carefully before continuing.","He performed ablution after washing and cleaning.","He poured water over his head as part of the bath."],"related_hadiths":[{"id":"260","book_id":"1","label":"Sahih Bukhari"},{"id":"262","book_id":"1","label":"Sahih Bukhari"},{"id":"265","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Cleaning Hands in Ghusl","description":"$book_name$ $hadith_number$ - $chapter_name$. Aisha reports that the Prophet صلى الله عليه وسلم began ghusl by washing his hands, cleaning them well, then making wudu."},"heading":{"title":"Hadith About Cleaning the Hands Before Ghusl","description":"This hadith explains part of the ghusl after janabah by showing how the Messenger of Allah صلى الله عليه وسلم began. Aisha said that when he intended to bathe, he started with his hands and washed them. He then washed the joints of his limbs and poured water. After cleansing his hands, he rubbed them on the wall so they would be clean with dust, then he performed ablution and poured water over his head. The key point is the careful order of purification. The hadith about cleaning hands before ghusl is not a broad ruling on every detail of ghusl; it simply reports how he washed and cleaned before moving to wudu and washing the head."},"teachings":["The Prophet صلى الله عليه وسلم began this ghusl by washing his hands.","He cleaned the hands carefully before continuing.","He performed ablution after washing and cleaning.","He poured water over his head as part of the bath."],"related_hadiths":[{"id":"260","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"262","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"265","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E576" s="4" t="n"/>
@@ -13761,7 +13765,7 @@
       </c>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Complete Ghusl After Janabah","description":"$book_name$ $hadith_number$ - $chapter_name$. Maimunah describes the Prophet’s ghusl, from washing hands and private parts to washing head, body, and feet."},"heading":{"title":"Complete Sunnah Ghusl After Janabah from Maimunah’s Hadith","description":"This hadith gives a detailed report from Maimunah about ghusl after sexual intercourse. She placed water for the Prophet صلى الله عليه وسلم. He poured water on his right hand and washed it two or three times. Then he washed his private parts with the left hand, wiped the hand on the ground, rinsed the mouth, snuffed water, washed the face and hands, poured water over the head and body, then moved aside and washed the feet. A garment was offered, but he shook water from his body instead. Ibrahim’s comment says they saw no harm in using a garment, but disliked making it a habit. This is a rich hadith for people searching how to perform ghusl correctly according to Sunnah."},"teachings":["Maimunah carefully described the order of the Prophet’s ghusl.","The report includes washing hands, private parts, mouth, nose, face, body, and feet.","The Prophet صلى الله عليه وسلم moved aside before washing his feet.","Using a garment to dry was not treated as harmful in Ibrahim’s comment, though habit was disliked."],"related_hadiths":[{"id":"257","book_id":"1","label":"Sahih Bukhari"},{"id":"259","book_id":"1","label":"Sahih Bukhari"},{"id":"266","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Complete Ghusl After Janabah","description":"$book_name$ $hadith_number$ - $chapter_name$. Maimunah describes the Prophet’s ghusl, from washing hands and private parts to washing head, body, and feet."},"heading":{"title":"Complete Sunnah Ghusl After Janabah from Maimunah’s Hadith","description":"This hadith gives a detailed report from Maimunah about ghusl after sexual intercourse. She placed water for the Prophet صلى الله عليه وسلم. He poured water on his right hand and washed it two or three times. Then he washed his private parts with the left hand, wiped the hand on the ground, rinsed the mouth, snuffed water, washed the face and hands, poured water over the head and body, then moved aside and washed the feet. A garment was offered, but he shook water from his body instead. Ibrahim’s comment says they saw no harm in using a garment, but disliked making it a habit. This is a rich hadith for people searching how to perform ghusl correctly according to Sunnah."},"teachings":["Maimunah carefully described the order of the Prophet’s ghusl.","The report includes washing hands, private parts, mouth, nose, face, body, and feet.","The Prophet صلى الله عليه وسلم moved aside before washing his feet.","Using a garment to dry was not treated as harmful in Ibrahim’s comment, though habit was disliked."],"related_hadiths":[{"id":"257","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"259","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"266","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E577" s="4" t="n"/>
@@ -13784,7 +13788,7 @@
       </c>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Abbas on Purification","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas shows ghusl after janabah with washing the hand, making wudu, and pouring water over the body."},"heading":{"title":"Ibn Abbas Hadith on Ghusl After Janabah and Purification","description":"This hadith reports how Ibn Abbas performed ghusl because of sexual defilement. He poured water over his left hand with his right hand seven times, then washed his private part. One time he forgot the number and asked Shu’bah, who did not know. Ibn Abbas then performed ablution as he did for prayer and poured water over his skin. He said this was how the Messenger of Allah صلى الله عليه وسلم purified himself. The focus is ghusl after janabah and careful purification. The narration also shows attention to number and order. It does not say every person must use the exact same wording in every case, but it reports a remembered way of purification."},"teachings":["Ibn Abbas paid attention to the number of times he poured water.","He washed the private part before performing ablution.","He performed ablution like the ablution for prayer.","He connected this method to the purification of the Messenger of Allah صلى الله عليه وسلم."],"related_hadiths":[{"id":"249","book_id":"1","label":"Sahih Bukhari"},{"id":"265","book_id":"1","label":"Sahih Bukhari"},{"id":"281","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ibn Abbas on Purification","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas shows ghusl after janabah with washing the hand, making wudu, and pouring water over the body."},"heading":{"title":"Ibn Abbas Hadith on Ghusl After Janabah and Purification","description":"This hadith reports how Ibn Abbas performed ghusl because of sexual defilement. He poured water over his left hand with his right hand seven times, then washed his private part. One time he forgot the number and asked Shu’bah, who did not know. Ibn Abbas then performed ablution as he did for prayer and poured water over his skin. He said this was how the Messenger of Allah صلى الله عليه وسلم purified himself. The focus is ghusl after janabah and careful purification. The narration also shows attention to number and order. It does not say every person must use the exact same wording in every case, but it reports a remembered way of purification."},"teachings":["Ibn Abbas paid attention to the number of times he poured water.","He washed the private part before performing ablution.","He performed ablution like the ablution for prayer.","He connected this method to the purification of the Messenger of Allah صلى الله عليه وسلم."],"related_hadiths":[{"id":"249","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"265","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"281","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E578" s="4" t="n"/>
@@ -13807,7 +13811,7 @@
       </c>
       <c r="D579" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Washing Hair in Ghusl","description":"$book_name$ $hadith_number$ - $chapter_name$. This report mentions washing the hair and skin in ghusl, with Abu Dawud noting weakness in its chain."},"heading":{"title":"Hadith About Washing Hair and Skin in Ghusl","description":"This report says that there is sexual defilement under every hair, so the hair should be washed and the skin cleansed. The hadith is about washing hair in ghusl and making sure the skin is clean. At the same time, the text itself includes an important note from Abu Dawud: he said the narration of Harith ibn Wajih is rejected, and that he is weak in transmission. So this hadith must be handled carefully. The wording points to the idea of careful washing, but the grading note stops us from treating this report as strong on its own. A balanced explanation should mention both parts: the instruction in the wording and the weakness stated by Abu Dawud."},"teachings":["The wording mentions washing the hair during ghusl.","The wording also mentions cleansing the skin.","Abu Dawud states that the narrator Harith ibn Wajih is weak.","The grading note teaches care when using a hadith as evidence."],"related_hadiths":[{"id":"248","book_id":"1","label":"Sahih Bukhari"},{"id":"256","book_id":"1","label":"Sahih Bukhari"},{"id":"272","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Washing Hair in Ghusl","description":"$book_name$ $hadith_number$ - $chapter_name$. This report mentions washing the hair and skin in ghusl, with Abu Dawud noting weakness in its chain."},"heading":{"title":"Hadith About Washing Hair and Skin in Ghusl","description":"This report says that there is sexual defilement under every hair, so the hair should be washed and the skin cleansed. The hadith is about washing hair in ghusl and making sure the skin is clean. At the same time, the text itself includes an important note from Abu Dawud: he said the narration of Harith ibn Wajih is rejected, and that he is weak in transmission. So this hadith must be handled carefully. The wording points to the idea of careful washing, but the grading note stops us from treating this report as strong on its own. A balanced explanation should mention both parts: the instruction in the wording and the weakness stated by Abu Dawud."},"teachings":["The wording mentions washing the hair during ghusl.","The wording also mentions cleansing the skin.","Abu Dawud states that the narrator Harith ibn Wajih is weak.","The grading note teaches care when using a hadith as evidence."],"related_hadiths":[{"id":"248","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"256","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"272","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E579" s="4" t="n"/>
@@ -13830,7 +13834,7 @@
       </c>
       <c r="D580" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Not Leaving Any Spot in Ghusl","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali reports a warning about leaving even a hair-width spot unwashed during ghusl after janabah."},"heading":{"title":"Hadith About Not Leaving Any Spot Unwashed in Ghusl","description":"This hadith gives a serious warning about ghusl after janabah. Ali ibn Abi Talib narrated that the Messenger of Allah صلى الله عليه وسلم said that if someone in a state of sexual defilement leaves a spot equal to the breadth of a hair without washing, punishment will follow. Ali then said that because of this he treated his head as an enemy, meaning he cut his hair, and he used to cut it. The core topic is complete ghusl and careful washing. The explanation should not go beyond the report or invent extra rulings. The hadith simply stresses not leaving an unwashed place when purification is required, especially when hair can make washing more difficult."},"teachings":["Ghusl should be done carefully, without leaving unwashed spots.","The report uses the width of a hair to stress attention to detail.","Ali took the warning seriously in how he dealt with his hair.","The hadith focuses on washing after janabah, not on unrelated matters."],"related_hadiths":[{"id":"248","book_id":"1","label":"Sahih Bukhari"},{"id":"256","book_id":"1","label":"Sahih Bukhari"},{"id":"272","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Not Leaving Any Spot in Ghusl","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali reports a warning about leaving even a hair-width spot unwashed during ghusl after janabah."},"heading":{"title":"Hadith About Not Leaving Any Spot Unwashed in Ghusl","description":"This hadith gives a serious warning about ghusl after janabah. Ali ibn Abi Talib narrated that the Messenger of Allah صلى الله عليه وسلم said that if someone in a state of sexual defilement leaves a spot equal to the breadth of a hair without washing, punishment will follow. Ali then said that because of this he treated his head as an enemy, meaning he cut his hair, and he used to cut it. The core topic is complete ghusl and careful washing. The explanation should not go beyond the report or invent extra rulings. The hadith simply stresses not leaving an unwashed place when purification is required, especially when hair can make washing more difficult."},"teachings":["Ghusl should be done carefully, without leaving unwashed spots.","The report uses the width of a hair to stress attention to detail.","Ali took the warning seriously in how he dealt with his hair.","The hadith focuses on washing after janabah, not on unrelated matters."],"related_hadiths":[{"id":"248","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"256","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"272","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E580" s="4" t="n"/>
@@ -13853,7 +13857,7 @@
       </c>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Harm in Roads and Shade","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم warned against relieving oneself where people walk or rest, protecting public cleanliness and comfort."},"heading":{"title":"Hadith About Public Hygiene in Roads and Shade","description":"This hadith about public hygiene teaches Muslims to avoid actions that harm people in shared places. Abu Hurairah reports that the Prophet صلى الله عليه وسلم said to beware of two things that provoke cursing. When asked what they were, he said: relieving oneself in people’s roads or in their shade. The wording is direct and very practical. Roads are used for walking, and shade is used for rest. So the hadith teaches respect for public spaces. A person should not make people’s paths or resting places dirty or difficult to use. The popular search terms for this report are “hadith about cleanliness of roads” and “hadith about relieving in shade.” The message is public manners, cleanliness, and avoiding harm."},"teachings":["Do not relieve yourself where people walk.","Do not spoil places where people take shade and rest.","Public cleanliness is part of good Islamic manners."],"related_hadiths":[{"id":"269","book_id":"2","label":"Sahih Muslim"},{"id":"328","book_id":"6","label":"Sunan Ibn Majah"},{"id":"262a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Avoiding Harm in Roads and Shade","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم warned against relieving oneself where people walk or rest, protecting public cleanliness and comfort."},"heading":{"title":"Hadith About Public Hygiene in Roads and Shade","description":"This hadith about public hygiene teaches Muslims to avoid actions that harm people in shared places. Abu Hurairah reports that the Prophet صلى الله عليه وسلم said to beware of two things that provoke cursing. When asked what they were, he said: relieving oneself in people’s roads or in their shade. The wording is direct and very practical. Roads are used for walking, and shade is used for rest. So the hadith teaches respect for public spaces. A person should not make people’s paths or resting places dirty or difficult to use. The popular search terms for this report are “hadith about cleanliness of roads” and “hadith about relieving in shade.” The message is public manners, cleanliness, and avoiding harm."},"teachings":["Do not relieve yourself where people walk.","Do not spoil places where people take shade and rest.","Public cleanliness is part of good Islamic manners."],"related_hadiths":[{"id":"269","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"328","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"262a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E581" s="4" t="n"/>
@@ -13876,7 +13880,7 @@
       </c>
       <c r="D582" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Places to Avoid","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against relieving oneself at water sources, roads, and shade used by people."},"heading":{"title":"Hadith About Three Places to Avoid When Relieving Oneself","description":"This hadith about three places to avoid gives a clear public hygiene lesson. Mu’adh ibn Jabal reports that the Messenger of Allah صلى الله عليه وسلم warned against three things that provoke cursing: relieving oneself in watering places, on thoroughfares, and in shade. The teaching is easy to apply. Do not spoil water sources, do not make roads dirty, and do not disturb shaded places where people may rest. The hadith does not need a long outside story to be understood. It speaks directly about care for shared places. Searchers often look for “three things that provoke curses hadith” or “hadith about water places road shade.” The core topic is public manners, because one person’s careless act can trouble many others."},"teachings":["Watering places should be kept clean for others.","Roads should not be used as toilet areas.","Shade used by people deserves respect and cleanliness."],"related_hadiths":[{"id":"328","book_id":"6","label":"Sunan Ibn Majah"},{"id":"269","book_id":"2","label":"Sahih Muslim"},{"id":"262b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Three Places to Avoid","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith warns against relieving oneself at water sources, roads, and shade used by people."},"heading":{"title":"Hadith About Three Places to Avoid When Relieving Oneself","description":"This hadith about three places to avoid gives a clear public hygiene lesson. Mu’adh ibn Jabal reports that the Messenger of Allah صلى الله عليه وسلم warned against three things that provoke cursing: relieving oneself in watering places, on thoroughfares, and in shade. The teaching is easy to apply. Do not spoil water sources, do not make roads dirty, and do not disturb shaded places where people may rest. The hadith does not need a long outside story to be understood. It speaks directly about care for shared places. Searchers often look for “three things that provoke curses hadith” or “hadith about water places road shade.” The core topic is public manners, because one person’s careless act can trouble many others."},"teachings":["Watering places should be kept clean for others.","Roads should not be used as toilet areas.","Shade used by people deserves respect and cleanliness."],"related_hadiths":[{"id":"328","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"269","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"262b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E582" s="4" t="n"/>
@@ -13899,7 +13903,7 @@
       </c>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Menstruation Is Not in the Hand","description":"$book_name$ $hadith_number$ - $chapter_name$. A gentle lesson that menstruation does not make the hand unable to pass an item from the mosque when needed."},"heading":{"title":"Hadith About Menstruation: Your Menstruation Is Not in Your Hand","description":"This hadith about menstruation shows a simple and gentle teaching. Aishah said the Messenger of Allah صلى الله عليه وسلم asked her to get the mat from the mosque. She mentioned that she was menstruating, likely thinking this affected the request. The Prophet صلى الله عليه وسلم replied, “Your menstruation is not in your hand.” The main message is clear from the text: menstruation did not stop her hand from passing the mat. This hadith is often searched as “your menstruation is not in your hand hadith” and “menstruating woman mosque hadith.” It teaches calmness, ease, and a careful difference between a person and the state of menstruation."},"teachings":["Menstruation did not stop Aishah from handing over the mat.","The Prophet صلى الله عليه وسلم corrected her concern with a short and gentle answer.","The hadith separates the hand from the state of menstruation in this situation."],"related_hadiths":[{"id":"298a","book_id":"2","label":"Sahih Muslim"},{"id":"298b","book_id":"2","label":"Sahih Muslim"},{"id":"333","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Menstruation Is Not in the Hand","description":"$book_name$ $hadith_number$ - $chapter_name$. A gentle lesson that menstruation does not make the hand unable to pass an item from the mosque when needed."},"heading":{"title":"Hadith About Menstruation: Your Menstruation Is Not in Your Hand","description":"This hadith about menstruation shows a simple and gentle teaching. Aishah said the Messenger of Allah صلى الله عليه وسلم asked her to get the mat from the mosque. She mentioned that she was menstruating, likely thinking this affected the request. The Prophet صلى الله عليه وسلم replied, “Your menstruation is not in your hand.” The main message is clear from the text: menstruation did not stop her hand from passing the mat. This hadith is often searched as “your menstruation is not in your hand hadith” and “menstruating woman mosque hadith.” It teaches calmness, ease, and a careful difference between a person and the state of menstruation."},"teachings":["Menstruation did not stop Aishah from handing over the mat.","The Prophet صلى الله عليه وسلم corrected her concern with a short and gentle answer.","The hadith separates the hand from the state of menstruation in this situation."],"related_hadiths":[{"id":"298a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"298b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"333","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E583" s="4" t="n"/>
@@ -13922,7 +13926,7 @@
       </c>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Missed Prayers During Menstruation","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah explains that women in the Prophet’s time did not make up prayers missed during menstruation."},"heading":{"title":"Menstruating Woman Make Up Prayers Hadith: Aishah’s Clear Answer","description":"This hadith focuses on the question many people search for: “does a menstruating woman make up prayers?” A woman asked Aishah whether a menstruating woman should complete the prayers left during menses. Aishah answered by recalling what happened in the time of the Messenger of Allah صلى الله عليه وسلم. She said they menstruated then, and they did not make up those prayers, nor were they commanded to make them up. The explanation should stay close to the text. The hadith does not give a long speech; it gives a direct report from Aishah about practice and command. It teaches that worship is followed as taught, not by personal pressure or guesswork."},"teachings":["Aishah answered the question by referring to the Prophet’s time.","The women did not make up prayers missed during menstruation.","The hadith points to following the command that was actually given."],"related_hadiths":[{"id":"335b","book_id":"2","label":"Sahih Muslim"},{"id":"335c","book_id":"2","label":"Sahih Muslim"},{"id":"130","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Missed Prayers During Menstruation","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah explains that women in the Prophet’s time did not make up prayers missed during menstruation."},"heading":{"title":"Menstruating Woman Make Up Prayers Hadith: Aishah’s Clear Answer","description":"This hadith focuses on the question many people search for: “does a menstruating woman make up prayers?” A woman asked Aishah whether a menstruating woman should complete the prayers left during menses. Aishah answered by recalling what happened in the time of the Messenger of Allah صلى الله عليه وسلم. She said they menstruated then, and they did not make up those prayers, nor were they commanded to make them up. The explanation should stay close to the text. The hadith does not give a long speech; it gives a direct report from Aishah about practice and command. It teaches that worship is followed as taught, not by personal pressure or guesswork."},"teachings":["Aishah answered the question by referring to the Prophet’s time.","The women did not make up prayers missed during menstruation.","The hadith points to following the command that was actually given."],"related_hadiths":[{"id":"335b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"335c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"130","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E584" s="4" t="n"/>
@@ -13945,7 +13949,7 @@
       </c>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Make Up Fasts but Not Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah’s report states that missed fasts were made up, while missed prayers during menstruation were not."},"heading":{"title":"Hadith About Making Up Fasts but Not Prayers During Menstruation","description":"This narration adds an important detail to the same issue of menstruation, fasting, and prayer. It reports from Aishah that women were commanded to make up the fast that was left during menstruation, but they were not commanded to make up the prayer. People often search for this as “menstruating woman make up fasts not prayers hadith.” The wording matters. The hadith speaks about two acts of worship separately: fasting and prayer. It does not mix them into one rule. The lesson is that a Muslim follows the teaching as it came, even when two matters may look similar at first. The text gives a clear difference between missed fasts and missed prayers."},"teachings":["Missed fasts during menstruation were to be made up.","Missed prayers during menstruation were not commanded to be made up.","The hadith treats fasting and prayer as separate matters in this case."],"related_hadiths":[{"id":"335b","book_id":"2","label":"Sahih Muslim"},{"id":"335c","book_id":"2","label":"Sahih Muslim"},{"id":"130","book_id":"5","label":"Jami at-Tirmidhi"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Make Up Fasts but Not Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah’s report states that missed fasts were made up, while missed prayers during menstruation were not."},"heading":{"title":"Hadith About Making Up Fasts but Not Prayers During Menstruation","description":"This narration adds an important detail to the same issue of menstruation, fasting, and prayer. It reports from Aishah that women were commanded to make up the fast that was left during menstruation, but they were not commanded to make up the prayer. People often search for this as “menstruating woman make up fasts not prayers hadith.” The wording matters. The hadith speaks about two acts of worship separately: fasting and prayer. It does not mix them into one rule. The lesson is that a Muslim follows the teaching as it came, even when two matters may look similar at first. The text gives a clear difference between missed fasts and missed prayers."},"teachings":["Missed fasts during menstruation were to be made up.","Missed prayers during menstruation were not commanded to be made up.","The hadith treats fasting and prayer as separate matters in this case."],"related_hadiths":[{"id":"335b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"335c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"130","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"}]}</t>
         </is>
       </c>
       <c r="E585" s="4" t="n"/>
@@ -13968,7 +13972,7 @@
       </c>
       <c r="D586" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Dinar or Half a Dinar","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas distinguishes between the beginning and end of menses for the amount given in alms."},"heading":{"title":"Hadith on Intercourse During Menses: Beginning and End of Menstruation","description":"This report from Ibn Abbas gives a more detailed wording about alms after intercourse during menses. It says that if intercourse happens at the beginning of the menses, one dinar should be given. If it happens toward the end of the menses, half a dinar should be given. Many users search this topic as “one dinar or half dinar menstruation hadith.” The text itself is short, so the explanation should stay short in meaning too. It points to a difference between the beginning of the blood and the time when the blood is ending. It also keeps the focus on giving alms, not on unrelated details."},"teachings":["The beginning of menses is linked with one dinar in this report.","The end of menses is linked with half a dinar in this report.","The narration keeps the response tied to alms."],"related_hadiths":[{"id":"370","book_id":"3","label":"Sunan an-Nasai"},{"id":"640","book_id":"6","label":"Sunan Ibn Majah"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Dinar or Half a Dinar","description":"$book_name$ $hadith_number$ - $chapter_name$. Ibn Abbas distinguishes between the beginning and end of menses for the amount given in alms."},"heading":{"title":"Hadith on Intercourse During Menses: Beginning and End of Menstruation","description":"This report from Ibn Abbas gives a more detailed wording about alms after intercourse during menses. It says that if intercourse happens at the beginning of the menses, one dinar should be given. If it happens toward the end of the menses, half a dinar should be given. Many users search this topic as “one dinar or half dinar menstruation hadith.” The text itself is short, so the explanation should stay short in meaning too. It points to a difference between the beginning of the blood and the time when the blood is ending. It also keeps the focus on giving alms, not on unrelated details."},"teachings":["The beginning of menses is linked with one dinar in this report.","The end of menses is linked with half a dinar in this report.","The narration keeps the response tied to alms."],"related_hadiths":[{"id":"370","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"640","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"}]}</t>
         </is>
       </c>
       <c r="E586" s="4" t="n"/>
@@ -13991,7 +13995,7 @@
       </c>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mercy and Boundaries During Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم would embrace a menstruating wife while she wore a wrapper covering the stated area."},"heading":{"title":"Hadith About Intimacy During Menstruation With a Waist Wrapper","description":"This hadith about intimacy during menstruation is narrated by Maimunah. She says the Prophet صلى الله عليه وسلم would contact and embrace one of his wives while she was menstruating, and she would wear a wrapper up to half the thighs or covering the knees. The text gives both closeness and a boundary. It does not describe full intercourse. It describes contact, embrace, and the use of a wrapper. People often search for “hadith about intimacy during menstruation” or “menstruating wife waist wrapper hadith.” The simple lesson is that menstruation did not remove kindness or closeness between spouses, while the report also mentions covering in a clear way."},"teachings":["The Prophet صلى الله عليه وسلم maintained closeness with a menstruating wife.","The narration mentions a wrapper covering the thighs or knees.","The hadith describes contact and embrace, not intercourse."],"related_hadiths":[{"id":"293a","book_id":"2","label":"Sahih Muslim"},{"id":"293b","book_id":"2","label":"Sahih Muslim"},{"id":"374","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Mercy and Boundaries During Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم would embrace a menstruating wife while she wore a wrapper covering the stated area."},"heading":{"title":"Hadith About Intimacy During Menstruation With a Waist Wrapper","description":"This hadith about intimacy during menstruation is narrated by Maimunah. She says the Prophet صلى الله عليه وسلم would contact and embrace one of his wives while she was menstruating, and she would wear a wrapper up to half the thighs or covering the knees. The text gives both closeness and a boundary. It does not describe full intercourse. It describes contact, embrace, and the use of a wrapper. People often search for “hadith about intimacy during menstruation” or “menstruating wife waist wrapper hadith.” The simple lesson is that menstruation did not remove kindness or closeness between spouses, while the report also mentions covering in a clear way."},"teachings":["The Prophet صلى الله عليه وسلم maintained closeness with a menstruating wife.","The narration mentions a wrapper covering the thighs or knees.","The hadith describes contact and embrace, not intercourse."],"related_hadiths":[{"id":"293a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"293b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"374","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E587" s="4" t="n"/>
@@ -14014,7 +14018,7 @@
       </c>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lying With a Menstruating Wife","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports that a waist wrapper was tied before the husband lay with or embraced his menstruating wife."},"heading":{"title":"Menstruating Wife Waist Wrapper Hadith: Lying Together With Care","description":"Aishah reports that when one of the wives of the Prophet صلى الله عليه وسلم menstruated, he asked her to tie a waist wrapper. Then her husband lay with her, or, in another wording from the narrator, embraced her. This hadith is often searched as “menstruating wife waist wrapper hadith” and “can husband lie with wife during period hadith.” The wording is careful, and the explanation should be careful too. The narration shows closeness within a named boundary: the waist wrapper is mentioned first, then lying together or embracing. It teaches that the Prophet’s household dealt with menses with calm instruction, not harsh distance or careless behavior."},"teachings":["The waist wrapper is mentioned before lying together or embracing.","The hadith shows calm instruction during menstruation.","The wording keeps closeness within a stated boundary."],"related_hadiths":[{"id":"293a","book_id":"2","label":"Sahih Muslim"},{"id":"293b","book_id":"2","label":"Sahih Muslim"},{"id":"302","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Lying With a Menstruating Wife","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports that a waist wrapper was tied before the husband lay with or embraced his menstruating wife."},"heading":{"title":"Menstruating Wife Waist Wrapper Hadith: Lying Together With Care","description":"Aishah reports that when one of the wives of the Prophet صلى الله عليه وسلم menstruated, he asked her to tie a waist wrapper. Then her husband lay with her, or, in another wording from the narrator, embraced her. This hadith is often searched as “menstruating wife waist wrapper hadith” and “can husband lie with wife during period hadith.” The wording is careful, and the explanation should be careful too. The narration shows closeness within a named boundary: the waist wrapper is mentioned first, then lying together or embracing. It teaches that the Prophet’s household dealt with menses with calm instruction, not harsh distance or careless behavior."},"teachings":["The waist wrapper is mentioned before lying together or embracing.","The hadith shows calm instruction during menstruation.","The wording keeps closeness within a stated boundary."],"related_hadiths":[{"id":"293a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"293b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"302","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E588" s="4" t="n"/>
@@ -14037,7 +14041,7 @@
       </c>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Washing the Spot of Blood","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports that when menstrual blood touched the body or cloth, only that spot was washed before prayer."},"heading":{"title":"Menstrual Blood on Clothes Hadith: Wash the Spot and Pray","description":"This hadith gives a practical report about menstrual blood touching the Prophet صلى الله عليه وسلم or his cloth. Aishah says they would pass the night in one cloth while she was menstruating heavily. If anything from her touched his body, he washed that spot and did not go beyond it, then he prayed. If it touched his garment, he washed that spot and prayed in it. The main search term is “menstrual blood on clothes hadith.” The message is simple and measured: the washing described in the hadith was limited to the affected place. The text does not say the whole body or whole garment was washed in this situation."},"teachings":["When blood touched a place, that place was washed.","The report says he did not go beyond the affected spot.","After washing the spot, he prayed in the garment."],"related_hadiths":[{"id":"293a","book_id":"2","label":"Sahih Muslim"},{"id":"302","book_id":"1","label":"Sahih Bukhari"},{"id":"374","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Washing the Spot of Blood","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports that when menstrual blood touched the body or cloth, only that spot was washed before prayer."},"heading":{"title":"Menstrual Blood on Clothes Hadith: Wash the Spot and Pray","description":"This hadith gives a practical report about menstrual blood touching the Prophet صلى الله عليه وسلم or his cloth. Aishah says they would pass the night in one cloth while she was menstruating heavily. If anything from her touched his body, he washed that spot and did not go beyond it, then he prayed. If it touched his garment, he washed that spot and prayed in it. The main search term is “menstrual blood on clothes hadith.” The message is simple and measured: the washing described in the hadith was limited to the affected place. The text does not say the whole body or whole garment was washed in this situation."},"teachings":["When blood touched a place, that place was washed.","The report says he did not go beyond the affected spot.","After washing the spot, he prayed in the garment."],"related_hadiths":[{"id":"293a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"302","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"374","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E589" s="4" t="n"/>
@@ -14060,7 +14064,7 @@
       </c>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warmth and Care During Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet صلى الله عليه وسلم seeking warmth and closeness while she was menstruating."},"heading":{"title":"Sleeping With a Menstruating Wife Hadith: Care, Warmth, and Closeness","description":"This narration answers a personal question: what if a woman menstruates and she and her husband have only one bed? Aishah shares what happened with the Messenger of Allah صلى الله عليه وسلم. He was cold, asked her to come near, and when she mentioned menstruation, he still asked her to uncover her thighs. He then placed his cheek and chest on her thighs, and she leaned over him until he became warm and slept. This hadith is often searched as “sleeping with menstruating wife hadith.” The text shows care, warmth, and closeness in a specific situation. It should not be turned into a wider claim beyond what Aishah described."},"teachings":["Aishah answered by narrating a direct example from her life.","The Prophet صلى الله عليه وسلم sought warmth and closeness while she was menstruating.","The report describes one specific situation with one shared bed."],"related_hadiths":[{"id":"293a","book_id":"2","label":"Sahih Muslim"},{"id":"293b","book_id":"2","label":"Sahih Muslim"},{"id":"302","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Warmth and Care During Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah describes the Prophet صلى الله عليه وسلم seeking warmth and closeness while she was menstruating."},"heading":{"title":"Sleeping With a Menstruating Wife Hadith: Care, Warmth, and Closeness","description":"This narration answers a personal question: what if a woman menstruates and she and her husband have only one bed? Aishah shares what happened with the Messenger of Allah صلى الله عليه وسلم. He was cold, asked her to come near, and when she mentioned menstruation, he still asked her to uncover her thighs. He then placed his cheek and chest on her thighs, and she leaned over him until he became warm and slept. This hadith is often searched as “sleeping with menstruating wife hadith.” The text shows care, warmth, and closeness in a specific situation. It should not be turned into a wider claim beyond what Aishah described."},"teachings":["Aishah answered by narrating a direct example from her life.","The Prophet صلى الله عليه وسلم sought warmth and closeness while she was menstruating.","The report describes one specific situation with one shared bed."],"related_hadiths":[{"id":"293a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"293b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"302","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E590" s="4" t="n"/>
@@ -14083,7 +14087,7 @@
       </c>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aishah’s Caution During Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports that during menstruation she stayed away from the bed until purification."},"heading":{"title":"Aishah Menstruation Bed Hadith: Staying Apart Until Purified","description":"This hadith gives a different report from Aishah about her own action during menstruation. She says that when she menstruated, she left the bed and lay on the reed-mat. She also says she did not approach or come near the Messenger of Allah صلى الله عليه وسلم until they were purified. The main search phrase is “Aishah menstruation bed hadith.” The wording here is about caution and separation until purification. It should be explained as this report states it, without forcing it to say more than it says. The hadith reminds readers that narrations may describe specific actions and settings, and each text should be read carefully on its own terms."},"teachings":["Aishah describes leaving the bed during menstruation in this report.","She mentions waiting until purification before coming near.","The hadith should be understood from its own wording."],"related_hadiths":[{"id":"293a","book_id":"2","label":"Sahih Muslim"},{"id":"293b","book_id":"2","label":"Sahih Muslim"},{"id":"302","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Aishah’s Caution During Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports that during menstruation she stayed away from the bed until purification."},"heading":{"title":"Aishah Menstruation Bed Hadith: Staying Apart Until Purified","description":"This hadith gives a different report from Aishah about her own action during menstruation. She says that when she menstruated, she left the bed and lay on the reed-mat. She also says she did not approach or come near the Messenger of Allah صلى الله عليه وسلم until they were purified. The main search phrase is “Aishah menstruation bed hadith.” The wording here is about caution and separation until purification. It should be explained as this report states it, without forcing it to say more than it says. The hadith reminds readers that narrations may describe specific actions and settings, and each text should be read carefully on its own terms."},"teachings":["Aishah describes leaving the bed during menstruation in this report.","She mentions waiting until purification before coming near.","The hadith should be understood from its own wording."],"related_hadiths":[{"id":"293a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"293b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"302","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E591" s="4" t="n"/>
@@ -14106,7 +14110,7 @@
       </c>
       <c r="D592" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Control and Boundaries During Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports the waist-wrapper instruction and notes the Prophet’s صلى الله عليه وسلم strong control over desire."},"heading":{"title":"Hadith About Intimacy During Menstruation and Control of Desire","description":"Aishah says the Messenger of Allah صلى الله عليه وسلم would ask them at the beginning of menstruation to tie the waist-wrapper, and then he would embrace them. She then adds a clear reminder: who among you can control his desire as the Messenger of Allah صلى الله عليه وسلم controlled his desire? This hadith is searched as “control desire menstruation hadith” and “waist wrapper menstruation hadith.” The teaching is balanced. The narration mentions affection and embrace, but it also warns readers not to ignore self-control. The beginning of menstruation is named, the waist-wrapper is named, and the Prophet’s control is named. These are the points the explanation should stay with."},"teachings":["The waist-wrapper was tied at the beginning of menstruation.","The Prophet صلى الله عليه وسلم embraced, while keeping control.","Aishah reminds others not to assume they have the same level of control."],"related_hadiths":[{"id":"293b","book_id":"2","label":"Sahih Muslim"},{"id":"302","book_id":"1","label":"Sahih Bukhari"},{"id":"1106c","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Control and Boundaries During Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah reports the waist-wrapper instruction and notes the Prophet’s صلى الله عليه وسلم strong control over desire."},"heading":{"title":"Hadith About Intimacy During Menstruation and Control of Desire","description":"Aishah says the Messenger of Allah صلى الله عليه وسلم would ask them at the beginning of menstruation to tie the waist-wrapper, and then he would embrace them. She then adds a clear reminder: who among you can control his desire as the Messenger of Allah صلى الله عليه وسلم controlled his desire? This hadith is searched as “control desire menstruation hadith” and “waist wrapper menstruation hadith.” The teaching is balanced. The narration mentions affection and embrace, but it also warns readers not to ignore self-control. The beginning of menstruation is named, the waist-wrapper is named, and the Prophet’s control is named. These are the points the explanation should stay with."},"teachings":["The waist-wrapper was tied at the beginning of menstruation.","The Prophet صلى الله عليه وسلم embraced, while keeping control.","Aishah reminds others not to assume they have the same level of control."],"related_hadiths":[{"id":"293b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"302","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1106c","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E592" s="4" t="n"/>
@@ -14129,7 +14133,7 @@
       </c>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Usual Period and Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم told the woman with bleeding to count her usual menstrual days, then bathe, bind a cloth, and pray."},"heading":{"title":"Istihadah Hadith: Count the Usual Menses Days Then Pray","description":"This hadith is about a woman who had an issue of blood in the time of the Messenger of Allah صلى الله عليه وسلم. Umm Salamah asked him for a decision about her. The Prophet صلى الله عليه وسلم told her to consider the number of nights and days she used to menstruate each month before the problem began. During that usual period, she should leave prayer. When those days and nights were over, she should bathe, tie a cloth over her private parts, and pray. The main search phrase is “istihadah hadith.” The teaching is practical and direct: the woman looks back to her known habit, then follows the steps mentioned in the hadith."},"teachings":["The woman should count the days and nights of her usual menses.","She should leave prayer during that usual period.","After that time, she should bathe, bind a cloth, and pray."],"related_hadiths":[{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","label":"Sahih Muslim"},{"id":"217","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Usual Period and Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم told the woman with bleeding to count her usual menstrual days, then bathe, bind a cloth, and pray."},"heading":{"title":"Istihadah Hadith: Count the Usual Menses Days Then Pray","description":"This hadith is about a woman who had an issue of blood in the time of the Messenger of Allah صلى الله عليه وسلم. Umm Salamah asked him for a decision about her. The Prophet صلى الله عليه وسلم told her to consider the number of nights and days she used to menstruate each month before the problem began. During that usual period, she should leave prayer. When those days and nights were over, she should bathe, tie a cloth over her private parts, and pray. The main search phrase is “istihadah hadith.” The teaching is practical and direct: the woman looks back to her known habit, then follows the steps mentioned in the hadith."},"teachings":["The woman should count the days and nights of her usual menses.","She should leave prayer during that usual period.","After that time, she should bathe, bind a cloth, and pray."],"related_hadiths":[{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"217","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E593" s="4" t="n"/>
@@ -14152,7 +14156,7 @@
       </c>
       <c r="D594" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Outside the Menses Period","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said she should leave prayer, bathe outside that period, bind a cloth, and pray."},"heading":{"title":"Fatimah bint Abi Hubaish Istihadah Hadith: Bathe and Pray Outside Menses","description":"This narration continues the story of a woman with prolonged bleeding. It says she should leave prayer, and outside that period she should take a bath, bind a cloth, and pray. Abu Dawud adds that Hammad b. Zaid named the woman in this hadith as Fatimah daughter of Abu Hubaish. The main search phrase is “Fatimah bint Abi Hubaish istihadah hadith.” The text is useful because it separates the menstrual period from the time outside it. During the period, she leaves prayer. Outside it, the report mentions bathing, binding a cloth, and praying. The explanation should not move beyond that sequence."},"teachings":["The narration separates the menstrual period from the time outside it.","Outside that period, bathing and prayer are mentioned.","Abu Dawud notes the named woman as Fatimah daughter of Abu Hubaish."],"related_hadiths":[{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","label":"Sahih Muslim"},{"id":"217","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer Outside the Menses Period","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم said she should leave prayer, bathe outside that period, bind a cloth, and pray."},"heading":{"title":"Fatimah bint Abi Hubaish Istihadah Hadith: Bathe and Pray Outside Menses","description":"This narration continues the story of a woman with prolonged bleeding. It says she should leave prayer, and outside that period she should take a bath, bind a cloth, and pray. Abu Dawud adds that Hammad b. Zaid named the woman in this hadith as Fatimah daughter of Abu Hubaish. The main search phrase is “Fatimah bint Abi Hubaish istihadah hadith.” The text is useful because it separates the menstrual period from the time outside it. During the period, she leaves prayer. Outside it, the report mentions bathing, binding a cloth, and praying. The explanation should not move beyond that sequence."},"teachings":["The narration separates the menstrual period from the time outside it.","Outside that period, bathing and prayer are mentioned.","Abu Dawud notes the named woman as Fatimah daughter of Abu Hubaish."],"related_hadiths":[{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"217","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E594" s="4" t="n"/>
@@ -14175,7 +14179,7 @@
       </c>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Simple Grooming and Bathing Etiquette","description":"$book_name$ $hadith_number$ - $chapter_name$. This report mentions two manners: not combing every day and not urinating in the bathing place."},"heading":{"title":"Hadith About Simple Grooming and Bathing Etiquette","description":"This hadith about simple grooming and bathing etiquette comes through a man from the Companions. He said the Messenger of Allah صلى الله عليه وسلم forbade that anyone among them should comb his hair every day or urinate in the place where he takes a bath. The report joins two daily habits: personal grooming and bathroom cleanliness. The wording does not say a person must neglect appearance. It says not to comb every day, while also warning against urinating in the bathing place. So the safest explanation is to keep the teaching close to the text: do not become excessive in daily grooming, and do not make the washing place impure. Searchers may look for “hadith comb hair every day” or “urinate in bathing place hadith.”"},"teachings":["Daily grooming should stay simple and balanced.","A bathing place should not be used for urination.","The hadith links personal care with clean bathroom manners."],"related_hadiths":[{"id":"36","book_id":"3","label":"Sunan an-Nasai"},{"id":"5376","book_id":"1","label":"Sahih Bukhari"},{"id":"262b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Simple Grooming and Bathing Etiquette","description":"$book_name$ $hadith_number$ - $chapter_name$. This report mentions two manners: not combing every day and not urinating in the bathing place."},"heading":{"title":"Hadith About Simple Grooming and Bathing Etiquette","description":"This hadith about simple grooming and bathing etiquette comes through a man from the Companions. He said the Messenger of Allah صلى الله عليه وسلم forbade that anyone among them should comb his hair every day or urinate in the place where he takes a bath. The report joins two daily habits: personal grooming and bathroom cleanliness. The wording does not say a person must neglect appearance. It says not to comb every day, while also warning against urinating in the bathing place. So the safest explanation is to keep the teaching close to the text: do not become excessive in daily grooming, and do not make the washing place impure. Searchers may look for “hadith comb hair every day” or “urinate in bathing place hadith.”"},"teachings":["Daily grooming should stay simple and balanced.","A bathing place should not be used for urination.","The hadith links personal care with clean bathroom manners."],"related_hadiths":[{"id":"36","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"5376","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"262b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E595" s="4" t="n"/>
@@ -14198,7 +14202,7 @@
       </c>
       <c r="D596" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Vein, Not Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم told Fatimah that the flowing blood was from a vein, and to stop prayer only when menses comes."},"heading":{"title":"Fatimah bint Abu Hubaish Hadith: Blood From a Vein and Prayer","description":"Fatimah daughter of Abu Hubaish complained to the Messenger of Allah صلى الله عليه وسلم about the flowing of her blood. He told her that it was only due to a vein. Then he gave a clear instruction: when her menstruation comes, she should not pray; when her menstruation ends, she should wash herself and pray during the time between one menstruation and the next. This is a key “istihadah hadith” and is often searched as “blood vessel not menses hadith.” The teaching is easy to follow from the text. Not every flowing blood in this case was treated as menses. The sign used in the hadith is the arrival and passing of her menstruation."},"teachings":["The Prophet صلى الله عليه وسلم described the bleeding as due to a vein.","She was told not to pray when menstruation came.","When menstruation ended, she was told to wash and pray between periods."],"related_hadiths":[{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"320","book_id":"1","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | A Vein, Not Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم told Fatimah that the flowing blood was from a vein, and to stop prayer only when menses comes."},"heading":{"title":"Fatimah bint Abu Hubaish Hadith: Blood From a Vein and Prayer","description":"Fatimah daughter of Abu Hubaish complained to the Messenger of Allah صلى الله عليه وسلم about the flowing of her blood. He told her that it was only due to a vein. Then he gave a clear instruction: when her menstruation comes, she should not pray; when her menstruation ends, she should wash herself and pray during the time between one menstruation and the next. This is a key “istihadah hadith” and is often searched as “blood vessel not menses hadith.” The teaching is easy to follow from the text. Not every flowing blood in this case was treated as menses. The sign used in the hadith is the arrival and passing of her menstruation."},"teachings":["The Prophet صلى الله عليه وسلم described the bleeding as due to a vein.","She was told not to pray when menstruation came.","When menstruation ended, she was told to wash and pray between periods."],"related_hadiths":[{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"320","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E596" s="4" t="n"/>
@@ -14221,7 +14225,7 @@
       </c>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istihadah and Prayer During Prolonged Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how a woman with prolonged bleeding pauses prayer for her usual menses, then bathes and prays."},"heading":{"title":"Istihadah Hadith: Prayer Guidance During Prolonged Bleeding","description":"This istihadah hadith gives clear guidance about prolonged bleeding in Islam. Fatimah daughter of Abu Hubaish asked about her condition, and the Prophet صلى الله عليه وسلم advised that she should refrain from prayer for the same number of days she previously used to refrain. After that, she should wash herself. The repeated reports in this narration point to the same core teaching: a woman with prolonged flow of blood should leave prayer during her known menstrual days, then take a bath and return to prayer. The text also shows Abu Dawud discussing different chains and wording, which helps readers see how carefully this ruling was transmitted. The main lesson is simple: prolonged bleeding is treated differently from the known menstrual period."},"teachings":["A woman with prolonged bleeding should use her known menstrual days as a guide.","Prayer is left during the usual menses, not for the whole prolonged bleeding period.","After the menstrual period ends, washing and returning to prayer are mentioned clearly.","The narration shows care in checking the wording and chains of reports."],"related_hadiths":[{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","label":"Sahih Muslim"},{"id":"354","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istihadah and Prayer During Prolonged Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how a woman with prolonged bleeding pauses prayer for her usual menses, then bathes and prays."},"heading":{"title":"Istihadah Hadith: Prayer Guidance During Prolonged Bleeding","description":"This istihadah hadith gives clear guidance about prolonged bleeding in Islam. Fatimah daughter of Abu Hubaish asked about her condition, and the Prophet صلى الله عليه وسلم advised that she should refrain from prayer for the same number of days she previously used to refrain. After that, she should wash herself. The repeated reports in this narration point to the same core teaching: a woman with prolonged flow of blood should leave prayer during her known menstrual days, then take a bath and return to prayer. The text also shows Abu Dawud discussing different chains and wording, which helps readers see how carefully this ruling was transmitted. The main lesson is simple: prolonged bleeding is treated differently from the known menstrual period."},"teachings":["A woman with prolonged bleeding should use her known menstrual days as a guide.","Prayer is left during the usual menses, not for the whole prolonged bleeding period.","After the menstrual period ends, washing and returning to prayer are mentioned clearly.","The narration shows care in checking the wording and chains of reports."],"related_hadiths":[{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"354","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E597" s="4" t="n"/>
@@ -14244,7 +14248,7 @@
       </c>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istihadah Is Not Menstruation","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that prolonged bleeding is not menses; prayer resumes after menses ends and blood is washed."},"heading":{"title":"Istihadah Hadith: Prolonged Bleeding Is Not Menstruation","description":"This hadith about istihadah answers a direct question from Fatimah daughter of Abu Hubaish. She told the Messenger of Allah صلى الله عليه وسلم that she had prolonged bleeding and did not become purified, so she asked whether she should abandon prayer. The Prophet صلى الله عليه وسلم explained that this was due to a vein and was not menstruation. He then gave a clear guide: when menstruation begins, she should leave prayer; when it ends, she should wash away the blood and pray. The teaching is focused and practical. It separates menstrual blood from prolonged bleeding and shows that prayer is not stopped without limit. For people searching for a hadith about menstruation and prayer, this narration is one of the key texts on the subject."},"teachings":["Prolonged bleeding is described here as a vein, not menstruation.","Prayer is left when the actual menstruation begins.","When menstruation ends, the blood is washed away and prayer resumes.","The woman asked clearly, and the Prophet صلى الله عليه وسلم gave a clear answer."],"related_hadiths":[{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"320","book_id":"1","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istihadah Is Not Menstruation","description":"$book_name$ $hadith_number$ - $chapter_name$. This hadith teaches that prolonged bleeding is not menses; prayer resumes after menses ends and blood is washed."},"heading":{"title":"Istihadah Hadith: Prolonged Bleeding Is Not Menstruation","description":"This hadith about istihadah answers a direct question from Fatimah daughter of Abu Hubaish. She told the Messenger of Allah صلى الله عليه وسلم that she had prolonged bleeding and did not become purified, so she asked whether she should abandon prayer. The Prophet صلى الله عليه وسلم explained that this was due to a vein and was not menstruation. He then gave a clear guide: when menstruation begins, she should leave prayer; when it ends, she should wash away the blood and pray. The teaching is focused and practical. It separates menstrual blood from prolonged bleeding and shows that prayer is not stopped without limit. For people searching for a hadith about menstruation and prayer, this narration is one of the key texts on the subject."},"teachings":["Prolonged bleeding is described here as a vein, not menstruation.","Prayer is left when the actual menstruation begins.","When menstruation ends, the blood is washed away and prayer resumes.","The woman asked clearly, and the Prophet صلى الله عليه وسلم gave a clear answer."],"related_hadiths":[{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"320","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E598" s="4" t="n"/>
@@ -14267,7 +14271,7 @@
       </c>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer After the Usual Menstrual Period","description":"$book_name$ $hadith_number$ - $chapter_name$. This report explains leaving prayer during menses, then washing away the blood and praying afterward."},"heading":{"title":"Istihadah Hadith: Wash and Pray After the Menstrual Period Ends","description":"This narration repeats the same core ruling about istihadah and prayer through another chain. The wording says that when menstruation begins, prayer should be left. Then, when the period equal to its usual length has passed, the woman should wash away the blood and pray. The focus is the known time of menstruation, not the full time of prolonged bleeding. This makes the hadith easy to understand for anyone searching for guidance on prolonged bleeding in Islam. It teaches that the usual menstrual period has a special ruling, while bleeding beyond that is handled differently. The instruction is not vague: stop during the menstrual time, wash afterward, and return to prayer."},"teachings":["The usual length of menses is used as the measure.","Prayer is paused during the menstrual period.","After that period passes, washing away the blood is mentioned before prayer.","A different chain supports the same basic meaning."],"related_hadiths":[{"id":"320","book_id":"1","label":"Sahih Bukhari"},{"id":"325","book_id":"1","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Prayer After the Usual Menstrual Period","description":"$book_name$ $hadith_number$ - $chapter_name$. This report explains leaving prayer during menses, then washing away the blood and praying afterward."},"heading":{"title":"Istihadah Hadith: Wash and Pray After the Menstrual Period Ends","description":"This narration repeats the same core ruling about istihadah and prayer through another chain. The wording says that when menstruation begins, prayer should be left. Then, when the period equal to its usual length has passed, the woman should wash away the blood and pray. The focus is the known time of menstruation, not the full time of prolonged bleeding. This makes the hadith easy to understand for anyone searching for guidance on prolonged bleeding in Islam. It teaches that the usual menstrual period has a special ruling, while bleeding beyond that is handled differently. The instruction is not vague: stop during the menstrual time, wash afterward, and return to prayer."},"teachings":["The usual length of menses is used as the measure.","Prayer is paused during the menstrual period.","After that period passes, washing away the blood is mentioned before prayer.","A different chain supports the same basic meaning."],"related_hadiths":[{"id":"320","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"325","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E599" s="4" t="n"/>
@@ -14290,7 +14294,7 @@
       </c>
       <c r="D600" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Counting Normal Menstrual Days","description":"$book_name$ $hadith_number$ - $chapter_name$. A woman with abnormal bleeding counts her normal menses, leaves prayer, bathes, uses cloth, and prays."},"heading":{"title":"Istihadah Hadith: Count Normal Menstrual Days Before Prayer","description":"This hadith about abnormal menses gives a practical method for a woman whose bleeding changed and became continuous. A woman asked Aishah about this condition, and Aishah said the Messenger of Allah صلى الله عليه وسلم told her to advise the woman to look at the period in which she used to menstruate each month when her cycle was normal. She should count the same number of days, leave prayer during that time, then take a bath, tie a cloth, and pray. This istihadah hadith is especially useful because it gives step-by-step guidance from the text itself. It does not tell her to stop prayer forever. It points her back to her regular menstrual pattern, then to purification and prayer."},"teachings":["A woman with changed bleeding may look back to her normal monthly menses.","Prayer is left for the number of days equal to that known period.","Taking a bath is mentioned before returning to prayer.","Using a cloth is mentioned as a practical step before praying."],"related_hadiths":[{"id":"354","book_id":"3","label":"Sunan an-Nasai"},{"id":"355","book_id":"3","label":"Sunan an-Nasai"},{"id":"334f","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Counting Normal Menstrual Days","description":"$book_name$ $hadith_number$ - $chapter_name$. A woman with abnormal bleeding counts her normal menses, leaves prayer, bathes, uses cloth, and prays."},"heading":{"title":"Istihadah Hadith: Count Normal Menstrual Days Before Prayer","description":"This hadith about abnormal menses gives a practical method for a woman whose bleeding changed and became continuous. A woman asked Aishah about this condition, and Aishah said the Messenger of Allah صلى الله عليه وسلم told her to advise the woman to look at the period in which she used to menstruate each month when her cycle was normal. She should count the same number of days, leave prayer during that time, then take a bath, tie a cloth, and pray. This istihadah hadith is especially useful because it gives step-by-step guidance from the text itself. It does not tell her to stop prayer forever. It points her back to her regular menstrual pattern, then to purification and prayer."},"teachings":["A woman with changed bleeding may look back to her normal monthly menses.","Prayer is left for the number of days equal to that known period.","Taking a bath is mentioned before returning to prayer.","Using a cloth is mentioned as a practical step before praying."],"related_hadiths":[{"id":"354","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"355","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"334f","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E600" s="4" t="n"/>
@@ -14313,7 +14317,7 @@
       </c>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umm Habibah and Prolonged Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Habibah had long bleeding; the Prophet صلى الله عليه وسلم said it was not menses but a vein, so she should bathe and pray."},"heading":{"title":"Umm Habibah Istihadah Hadith: Not Menses but a Vein","description":"This narration focuses on Umm Habibah daughter of Jahsh, who had prolonged bleeding for seven years. She asked the Messenger of Allah صلى الله عليه وسلم about it. He said that it was not menstruation, but due to a vein, and told her to wash herself and pray. The report also records Abu Dawud’s notes about extra wording in some chains, including wording about leaving prayer when menstruation begins and bathing when it ends. The main message from the hadith text is that prolonged bleeding is not treated as menstruation in every moment. For readers searching for Umm Habibah istihadah hadith, this narration shows both the ruling and the care of hadith scholars in preserving exact wording."},"teachings":["Umm Habibah sought guidance for prolonged bleeding instead of guessing.","The Prophet صلى الله عليه وسلم described the condition as not menstruation but a vein.","Washing and praying are directly mentioned in the answer.","The narration includes careful notes about differences in transmitted wording."],"related_hadiths":[{"id":"334a","book_id":"2","label":"Sahih Muslim"},{"id":"334b","book_id":"2","label":"Sahih Muslim"},{"id":"327","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umm Habibah and Prolonged Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Habibah had long bleeding; the Prophet صلى الله عليه وسلم said it was not menses but a vein, so she should bathe and pray."},"heading":{"title":"Umm Habibah Istihadah Hadith: Not Menses but a Vein","description":"This narration focuses on Umm Habibah daughter of Jahsh, who had prolonged bleeding for seven years. She asked the Messenger of Allah صلى الله عليه وسلم about it. He said that it was not menstruation, but due to a vein, and told her to wash herself and pray. The report also records Abu Dawud’s notes about extra wording in some chains, including wording about leaving prayer when menstruation begins and bathing when it ends. The main message from the hadith text is that prolonged bleeding is not treated as menstruation in every moment. For readers searching for Umm Habibah istihadah hadith, this narration shows both the ruling and the care of hadith scholars in preserving exact wording."},"teachings":["Umm Habibah sought guidance for prolonged bleeding instead of guessing.","The Prophet صلى الله عليه وسلم described the condition as not menstruation but a vein.","Washing and praying are directly mentioned in the answer.","The narration includes careful notes about differences in transmitted wording."],"related_hadiths":[{"id":"334a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"334b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"327","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E601" s="4" t="n"/>
@@ -14336,7 +14340,7 @@
       </c>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Recognizing Menstrual Blood","description":"$book_name$ $hadith_number$ - $chapter_name$. Menstrual blood is described as black and recognizable; other bleeding requires ablution and prayer."},"heading":{"title":"Istihadah Hadith: Recognizing Menstrual Blood and Praying","description":"This hadith gives a sign-based answer about istihadah and menstrual blood. Fatimah daughter of Abu Hubaish had continuing bleeding, and the Prophet صلى الله عليه وسلم said that when the blood is menstrual blood, it is black blood that can be recognized. When that appears, she should refrain from prayer. When the blood is different, she should perform ablution and pray, because it is due only to a vein. The narration also mentions comments from others about thick black blood and different blood after that, but the core Prophetic wording is simple. This hadith is often searched by people looking for the difference between menstrual blood and istihadah. The text links recognition of the blood with the prayer ruling."},"teachings":["Menstrual blood is described as black and recognizable in this narration.","Prayer is left when that recognized menstrual blood appears.","When the bleeding is different, ablution and prayer are mentioned.","The hadith connects physical signs with the prayer decision."],"related_hadiths":[{"id":"362","book_id":"3","label":"Sunan an-Nasai"},{"id":"363","book_id":"3","label":"Sunan an-Nasai"},{"id":"306","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Recognizing Menstrual Blood","description":"$book_name$ $hadith_number$ - $chapter_name$. Menstrual blood is described as black and recognizable; other bleeding requires ablution and prayer."},"heading":{"title":"Istihadah Hadith: Recognizing Menstrual Blood and Praying","description":"This hadith gives a sign-based answer about istihadah and menstrual blood. Fatimah daughter of Abu Hubaish had continuing bleeding, and the Prophet صلى الله عليه وسلم said that when the blood is menstrual blood, it is black blood that can be recognized. When that appears, she should refrain from prayer. When the blood is different, she should perform ablution and pray, because it is due only to a vein. The narration also mentions comments from others about thick black blood and different blood after that, but the core Prophetic wording is simple. This hadith is often searched by people looking for the difference between menstrual blood and istihadah. The text links recognition of the blood with the prayer ruling."},"teachings":["Menstrual blood is described as black and recognizable in this narration.","Prayer is left when that recognized menstrual blood appears.","When the bleeding is different, ablution and prayer are mentioned.","The hadith connects physical signs with the prayer decision."],"related_hadiths":[{"id":"362","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"363","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E602" s="4" t="n"/>
@@ -14359,7 +14363,7 @@
       </c>
       <c r="D603" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hamnah bint Jahsh and Severe Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Hamnah asked about severe bleeding, and was guided on menses days, bathing, prayer, and fasting."},"heading":{"title":"Hamnah bint Jahsh Hadith: Severe Istihadah and Prayer","description":"This hadith describes Hamnah daughter of Jahsh, who had severe and heavy bleeding. She came to the Messenger of Allah صلى الله عليه وسلم because the bleeding had kept her from prayer and fasting. The Prophet صلى الله عليه وسلم first suggested cotton, then a cloth, but she explained that the bleeding was too much. He then gave her guidance: she should treat six or seven days as menses, according to what Allah knows, then wash. When she sees that she is clean, she should pray and fast for the remaining days of the month. The narration also mentions another option involving bathing and combining certain prayers if she is strong enough. This is a detailed istihadah hadith about hardship, prayer, fasting, and practical ease."},"teachings":["Hamnah asked for guidance when severe bleeding affected worship.","The hadith mentions practical means like cotton and cloth for heavy bleeding.","Six or seven days are mentioned as the menses period in this case.","Prayer and fasting continue after washing when cleanliness is seen."],"related_hadiths":[{"id":"361","book_id":"3","label":"Sunan an-Nasai"},{"id":"356","book_id":"3","label":"Sunan an-Nasai"},{"id":"357","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hamnah bint Jahsh and Severe Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Hamnah asked about severe bleeding, and was guided on menses days, bathing, prayer, and fasting."},"heading":{"title":"Hamnah bint Jahsh Hadith: Severe Istihadah and Prayer","description":"This hadith describes Hamnah daughter of Jahsh, who had severe and heavy bleeding. She came to the Messenger of Allah صلى الله عليه وسلم because the bleeding had kept her from prayer and fasting. The Prophet صلى الله عليه وسلم first suggested cotton, then a cloth, but she explained that the bleeding was too much. He then gave her guidance: she should treat six or seven days as menses, according to what Allah knows, then wash. When she sees that she is clean, she should pray and fast for the remaining days of the month. The narration also mentions another option involving bathing and combining certain prayers if she is strong enough. This is a detailed istihadah hadith about hardship, prayer, fasting, and practical ease."},"teachings":["Hamnah asked for guidance when severe bleeding affected worship.","The hadith mentions practical means like cotton and cloth for heavy bleeding.","Six or seven days are mentioned as the menses period in this case.","Prayer and fasting continue after washing when cleanliness is seen."],"related_hadiths":[{"id":"361","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"356","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"357","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E603" s="4" t="n"/>
@@ -14382,7 +14386,7 @@
       </c>
       <c r="D604" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bathing and Prayer During Istihadah","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Habibah’s prolonged bleeding is described as a vein; she was told to bathe and pray."},"heading":{"title":"Umm Habibah Hadith: Ghusl and Prayer During Prolonged Bleeding","description":"This narration again mentions Umm Habibah daughter of Jahsh, who had bleeding for seven years. She asked the Messenger of Allah صلى الله عليه وسلم about it, and he said that it was not menstruation, but a vein. He told her to take a bath and pray. Aishah then described that Umm Habibah used to bathe in a wash-tub in the room of her sister Zainab, and the redness of the blood would dominate the water. The hadith gives a strong picture of how serious the bleeding was, yet the instruction still included prayer after bathing. For anyone searching for prolonged bleeding in Islam, this narration shows that a difficult condition did not remove prayer after the menses ruling was handled."},"teachings":["The bleeding lasted a long time, yet it was not treated as menses the whole time.","The Prophet صلى الله عليه وسلم described it as a vein, not menstruation.","Taking a bath and praying are directly mentioned.","Aishah’s description shows the bleeding was real and heavy."],"related_hadiths":[{"id":"334b","book_id":"2","label":"Sahih Muslim"},{"id":"327","book_id":"1","label":"Sahih Bukhari"},{"id":"351","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bathing and Prayer During Istihadah","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Habibah’s prolonged bleeding is described as a vein; she was told to bathe and pray."},"heading":{"title":"Umm Habibah Hadith: Ghusl and Prayer During Prolonged Bleeding","description":"This narration again mentions Umm Habibah daughter of Jahsh, who had bleeding for seven years. She asked the Messenger of Allah صلى الله عليه وسلم about it, and he said that it was not menstruation, but a vein. He told her to take a bath and pray. Aishah then described that Umm Habibah used to bathe in a wash-tub in the room of her sister Zainab, and the redness of the blood would dominate the water. The hadith gives a strong picture of how serious the bleeding was, yet the instruction still included prayer after bathing. For anyone searching for prolonged bleeding in Islam, this narration shows that a difficult condition did not remove prayer after the menses ruling was handled."},"teachings":["The bleeding lasted a long time, yet it was not treated as menses the whole time.","The Prophet صلى الله عليه وسلم described it as a vein, not menstruation.","Taking a bath and praying are directly mentioned.","Aishah’s description shows the bleeding was real and heavy."],"related_hadiths":[{"id":"334b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"327","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"351","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E604" s="4" t="n"/>
@@ -14405,7 +14409,7 @@
       </c>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Urinate in a Hole","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prohibited urinating in a hole, and Qatadah said such holes were said to be dwellings of jinn."},"heading":{"title":"Hadith About Not Urinating in a Hole","description":"This hadith about not urinating in a hole is a short warning with a clear action: avoid it. Abdullah ibn Sarjis reports that the Prophet صلى الله عليه وسلم prohibited urinating in a hole. Qatadah was asked why this was disliked, and he replied that it was said these holes are the habitats of the jinn. The hadith itself gives the prohibition, and the explanation from Qatadah gives the stated reason found in the report. We should not add extra claims beyond that. In everyday terms, the hadith teaches caution about places that are hidden, unknown, or possibly inhabited. Searchers often type “hadith do not urinate in a hole” or “jinn live in holes hadith.” The main lesson is careful toilet manners and respect for unseen or hidden spaces."},"teachings":["Do not urinate in holes.","Be careful with hidden places whose contents are unknown.","The report links this act with a reason mentioned by Qatadah."],"related_hadiths":[{"id":"328","book_id":"6","label":"Sunan Ibn Majah"},{"id":"36","book_id":"3","label":"Sunan an-Nasai"},{"id":"155","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Urinate in a Hole","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم prohibited urinating in a hole, and Qatadah said such holes were said to be dwellings of jinn."},"heading":{"title":"Hadith About Not Urinating in a Hole","description":"This hadith about not urinating in a hole is a short warning with a clear action: avoid it. Abdullah ibn Sarjis reports that the Prophet صلى الله عليه وسلم prohibited urinating in a hole. Qatadah was asked why this was disliked, and he replied that it was said these holes are the habitats of the jinn. The hadith itself gives the prohibition, and the explanation from Qatadah gives the stated reason found in the report. We should not add extra claims beyond that. In everyday terms, the hadith teaches caution about places that are hidden, unknown, or possibly inhabited. Searchers often type “hadith do not urinate in a hole” or “jinn live in holes hadith.” The main lesson is careful toilet manners and respect for unseen or hidden spaces."},"teachings":["Do not urinate in holes.","Be careful with hidden places whose contents are unknown.","The report links this act with a reason mentioned by Qatadah."],"related_hadiths":[{"id":"328","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"36","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"155","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E605" s="4" t="n"/>
@@ -14428,7 +14432,7 @@
       </c>
       <c r="D606" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reports on Bathing for Every Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration preserves reports that Umm Habibah used to bathe for every prayer during istihadah."},"heading":{"title":"Istihadah Hadith: Reports About Bathing for Every Prayer","description":"This narration discusses the wording that Umm Habibah used to take a bath for every prayer. It comes through another chain from Aishah and includes Abu Dawud’s comments about different transmitters. He notes that some versions say she used to take a bath for every prayer, while Ibn Uyainah said that al-Zuhri did not say the Prophet صلى الله عليه وسلم commanded her to take bath. The main point for readers is that this hadith is about preserving exact wording in the issue of istihadah and ghusl. It records the practice of bathing for every prayer, while also showing careful attention to whether the wording was a direct command or a reported action."},"teachings":["The report preserves the wording that she bathed for every prayer.","Abu Dawud notes differences between transmitters.","The narration shows care in separating a command from a reported practice.","The topic remains connected to istihadah, ghusl, and prayer."],"related_hadiths":[{"id":"334a","book_id":"2","label":"Sahih Muslim"},{"id":"334b","book_id":"2","label":"Sahih Muslim"},{"id":"327","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Reports on Bathing for Every Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration preserves reports that Umm Habibah used to bathe for every prayer during istihadah."},"heading":{"title":"Istihadah Hadith: Reports About Bathing for Every Prayer","description":"This narration discusses the wording that Umm Habibah used to take a bath for every prayer. It comes through another chain from Aishah and includes Abu Dawud’s comments about different transmitters. He notes that some versions say she used to take a bath for every prayer, while Ibn Uyainah said that al-Zuhri did not say the Prophet صلى الله عليه وسلم commanded her to take bath. The main point for readers is that this hadith is about preserving exact wording in the issue of istihadah and ghusl. It records the practice of bathing for every prayer, while also showing careful attention to whether the wording was a direct command or a reported action."},"teachings":["The report preserves the wording that she bathed for every prayer.","Abu Dawud notes differences between transmitters.","The narration shows care in separating a command from a reported practice.","The topic remains connected to istihadah, ghusl, and prayer."],"related_hadiths":[{"id":"334a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"334b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"327","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E606" s="4" t="n"/>
@@ -14451,7 +14455,7 @@
       </c>
       <c r="D607" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umm Habibah Bathing for Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Habibah had prolonged bleeding for seven years and used to bathe for every prayer."},"heading":{"title":"Umm Habibah Hadith: Bathing for Every Prayer During Istihadah","description":"This narration is clear and direct. Aishah said that Umm Habibah had prolonged bleeding for seven years. The Messenger of Allah صلى الله عليه وسلم commanded her to take bath, and she used to take bath for every prayer. The hadith is tied to the topic of istihadah, a condition where bleeding continues beyond the usual menstrual period. The wording highlights both the length of her hardship and her care for prayer. For someone searching for ghusl for every prayer during istihadah, this report is highly relevant. It does not add a long discussion. It simply records the condition, the command to bathe, and the practice of bathing for each prayer."},"teachings":["Umm Habibah experienced prolonged bleeding for seven years.","The Messenger of Allah صلى الله عليه وسلم commanded her to take a bath.","She used to bathe for every prayer in this report.","The narration connects purification with continuing prayer."],"related_hadiths":[{"id":"334a","book_id":"2","label":"Sahih Muslim"},{"id":"334b","book_id":"2","label":"Sahih Muslim"},{"id":"357","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Umm Habibah Bathing for Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Habibah had prolonged bleeding for seven years and used to bathe for every prayer."},"heading":{"title":"Umm Habibah Hadith: Bathing for Every Prayer During Istihadah","description":"This narration is clear and direct. Aishah said that Umm Habibah had prolonged bleeding for seven years. The Messenger of Allah صلى الله عليه وسلم commanded her to take bath, and she used to take bath for every prayer. The hadith is tied to the topic of istihadah, a condition where bleeding continues beyond the usual menstrual period. The wording highlights both the length of her hardship and her care for prayer. For someone searching for ghusl for every prayer during istihadah, this report is highly relevant. It does not add a long discussion. It simply records the condition, the command to bathe, and the practice of bathing for each prayer."},"teachings":["Umm Habibah experienced prolonged bleeding for seven years.","The Messenger of Allah صلى الله عليه وسلم commanded her to take a bath.","She used to bathe for every prayer in this report.","The narration connects purification with continuing prayer."],"related_hadiths":[{"id":"334a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"334b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"357","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E607" s="4" t="n"/>
@@ -14474,7 +14478,7 @@
       </c>
       <c r="D608" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bathing or Ablution Reports","description":"$book_name$ $hadith_number$ - $chapter_name$. This report mentions bathing for every prayer and notes Abu Dawud’s correction of a wording difference."},"heading":{"title":"Istihadah Hadith: Bathing for Every Prayer and Wording Care","description":"This narration mentions that Umm Habibah had prolonged bleeding during the time of the Messenger of Allah صلى الله عليه وسلم, and that he commanded her to take bath for every prayer. It then records Abu Dawud’s note about another narration involving Zainab daughter of Jahsh, with the wording to take bath for every prayer. Abu Dawud also explains that one version said ablution for every prayer, but he judged that wording to be a misunderstanding and said the correct version was bathing. This hadith is important for readers searching for istihadah ghusl and wudu because it shows how closely scholars looked at the exact words. The core text keeps the topic focused on purification before prayer during prolonged bleeding."},"teachings":["The report mentions bathing for every prayer during prolonged bleeding.","A similar report is connected to Zainab daughter of Jahsh.","Abu Dawud points out a wording difference between bathing and ablution.","The narration shows care in identifying the stronger wording."],"related_hadiths":[{"id":"334b","book_id":"2","label":"Sahih Muslim"},{"id":"351","book_id":"3","label":"Sunan an-Nasai"},{"id":"357","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Bathing or Ablution Reports","description":"$book_name$ $hadith_number$ - $chapter_name$. This report mentions bathing for every prayer and notes Abu Dawud’s correction of a wording difference."},"heading":{"title":"Istihadah Hadith: Bathing for Every Prayer and Wording Care","description":"This narration mentions that Umm Habibah had prolonged bleeding during the time of the Messenger of Allah صلى الله عليه وسلم, and that he commanded her to take bath for every prayer. It then records Abu Dawud’s note about another narration involving Zainab daughter of Jahsh, with the wording to take bath for every prayer. Abu Dawud also explains that one version said ablution for every prayer, but he judged that wording to be a misunderstanding and said the correct version was bathing. This hadith is important for readers searching for istihadah ghusl and wudu because it shows how closely scholars looked at the exact words. The core text keeps the topic focused on purification before prayer during prolonged bleeding."},"teachings":["The report mentions bathing for every prayer during prolonged bleeding.","A similar report is connected to Zainab daughter of Jahsh.","Abu Dawud points out a wording difference between bathing and ablution.","The narration shows care in identifying the stronger wording."],"related_hadiths":[{"id":"334b","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"351","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"357","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E608" s="4" t="n"/>
@@ -14497,7 +14501,7 @@
       </c>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Combining Prayers During Istihadah","description":"$book_name$ $hadith_number$ - $chapter_name$. A woman with prolonged bleeding was guided to combine prayer times with baths for paired prayers."},"heading":{"title":"Combining Prayers During Istihadah: Bathing for Paired Prayers","description":"This hadith describes a woman with prolonged bleeding during the time of the Messenger of Allah صلى الله عليه وسلم. She was commanded to advance Asr and delay Zuhr, then take one bath for both. She was also told to delay Maghrib and advance Isha, then take one bath for both. For the dawn prayer, she would take a separate bath. The narration is a key text for people searching about combining prayers during istihadah. Its wording focuses on managing prayer times and purification when bleeding continues. It does not say to leave prayer entirely. Instead, it shows an organized way to pray while dealing with a difficult bleeding condition."},"teachings":["Zuhr and Asr are mentioned together with one bath.","Maghrib and Isha are mentioned together with one bath.","Fajr has a separate bath in this report.","The narration presents a structured way to pray during prolonged bleeding."],"related_hadiths":[{"id":"361","book_id":"3","label":"Sunan an-Nasai"},{"id":"356","book_id":"3","label":"Sunan an-Nasai"},{"id":"357","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Combining Prayers During Istihadah","description":"$book_name$ $hadith_number$ - $chapter_name$. A woman with prolonged bleeding was guided to combine prayer times with baths for paired prayers."},"heading":{"title":"Combining Prayers During Istihadah: Bathing for Paired Prayers","description":"This hadith describes a woman with prolonged bleeding during the time of the Messenger of Allah صلى الله عليه وسلم. She was commanded to advance Asr and delay Zuhr, then take one bath for both. She was also told to delay Maghrib and advance Isha, then take one bath for both. For the dawn prayer, she would take a separate bath. The narration is a key text for people searching about combining prayers during istihadah. Its wording focuses on managing prayer times and purification when bleeding continues. It does not say to leave prayer entirely. Instead, it shows an organized way to pray while dealing with a difficult bleeding condition."},"teachings":["Zuhr and Asr are mentioned together with one bath.","Maghrib and Isha are mentioned together with one bath.","Fajr has a separate bath in this report.","The narration presents a structured way to pray during prolonged bleeding."],"related_hadiths":[{"id":"361","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"356","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"357","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E609" s="4" t="n"/>
@@ -14520,7 +14524,7 @@
       </c>
       <c r="D610" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ease When Bathing Became Hard","description":"$book_name$ $hadith_number$ - $chapter_name$. Sahlah was first told to bathe for every prayer, then to combine prayers when that became hard."},"heading":{"title":"Sahlah bint Suhayl Hadith: Ease in Istihadah Prayer","description":"This narration mentions Sahlah daughter of Suhayl, who had prolonged bleeding. She came to the Prophet صلى الله عليه وسلم, and he first commanded her to take a bath for every prayer. When that became hard for her, he commanded her to combine Zuhr and Asr with one bath, Maghrib and Isha with one bath, and to take a separate bath for the dawn prayer. This hadith is useful for searches about istihadah and hardship because it shows a move from a harder practice to an easier arrangement when bathing for every prayer became difficult. The text is direct and balanced. It keeps prayer in place while giving a practical way to handle purification."},"teachings":["Sahlah asked the Prophet صلى الله عليه وسلم about her prolonged bleeding.","Bathing for every prayer was first mentioned.","When it became hard, combining paired prayers with one bath was mentioned.","The dawn prayer still had a separate bath in this report."],"related_hadiths":[{"id":"361","book_id":"3","label":"Sunan an-Nasai"},{"id":"334f","book_id":"2","label":"Sahih Muslim"},{"id":"355","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ease When Bathing Became Hard","description":"$book_name$ $hadith_number$ - $chapter_name$. Sahlah was first told to bathe for every prayer, then to combine prayers when that became hard."},"heading":{"title":"Sahlah bint Suhayl Hadith: Ease in Istihadah Prayer","description":"This narration mentions Sahlah daughter of Suhayl, who had prolonged bleeding. She came to the Prophet صلى الله عليه وسلم, and he first commanded her to take a bath for every prayer. When that became hard for her, he commanded her to combine Zuhr and Asr with one bath, Maghrib and Isha with one bath, and to take a separate bath for the dawn prayer. This hadith is useful for searches about istihadah and hardship because it shows a move from a harder practice to an easier arrangement when bathing for every prayer became difficult. The text is direct and balanced. It keeps prayer in place while giving a practical way to handle purification."},"teachings":["Sahlah asked the Prophet صلى الله عليه وسلم about her prolonged bleeding.","Bathing for every prayer was first mentioned.","When it became hard, combining paired prayers with one bath was mentioned.","The dawn prayer still had a separate bath in this report."],"related_hadiths":[{"id":"361","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"334f","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"355","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E610" s="4" t="n"/>
@@ -14543,7 +14547,7 @@
       </c>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ghusl and Wudu Between Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. Fatimah was guided to bathe for paired prayers and perform ablution between them."},"heading":{"title":"Istihadah Hadith: Bathing for Paired Prayers and Wudu Between Them","description":"This hadith reports that Asma daughter of Umays spoke to the Messenger of Allah صلى الله عليه وسلم about Fatimah daughter of Abu Hubaish, who had bleeding for a period and did not pray. The Prophet صلى الله عليه وسلم said this was from the devil, then gave practical guidance. She should sit in a tub, and when she sees yellowness on top of the water, she should take one bath for Zuhr and Asr, one bath for Maghrib and Isha, and one bath for Fajr. Between those times, she should perform ablution. This narration is important for searches about istihadah ghusl and wudu because both are mentioned clearly in one text. It also shows prayer was to resume with purification steps."},"teachings":["Fatimah’s prolonged bleeding had led her to stop praying.","The Prophet صلى الله عليه وسلم gave a plan involving baths for paired prayers.","A separate bath is mentioned for Fajr.","Ablution is mentioned between those bath times."],"related_hadiths":[{"id":"361","book_id":"3","label":"Sunan an-Nasai"},{"id":"362","book_id":"3","label":"Sunan an-Nasai"},{"id":"333a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ghusl and Wudu Between Prayers","description":"$book_name$ $hadith_number$ - $chapter_name$. Fatimah was guided to bathe for paired prayers and perform ablution between them."},"heading":{"title":"Istihadah Hadith: Bathing for Paired Prayers and Wudu Between Them","description":"This hadith reports that Asma daughter of Umays spoke to the Messenger of Allah صلى الله عليه وسلم about Fatimah daughter of Abu Hubaish, who had bleeding for a period and did not pray. The Prophet صلى الله عليه وسلم said this was from the devil, then gave practical guidance. She should sit in a tub, and when she sees yellowness on top of the water, she should take one bath for Zuhr and Asr, one bath for Maghrib and Isha, and one bath for Fajr. Between those times, she should perform ablution. This narration is important for searches about istihadah ghusl and wudu because both are mentioned clearly in one text. It also shows prayer was to resume with purification steps."},"teachings":["Fatimah’s prolonged bleeding had led her to stop praying.","The Prophet صلى الله عليه وسلم gave a plan involving baths for paired prayers.","A separate bath is mentioned for Fajr.","Ablution is mentioned between those bath times."],"related_hadiths":[{"id":"361","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"362","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"333a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E611" s="4" t="n"/>
@@ -14566,7 +14570,7 @@
       </c>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu for Every Prayer in Istihadah","description":"$book_name$ $hadith_number$ - $chapter_name$. A woman with prolonged bleeding leaves prayer during menses, bathes, prays, and makes wudu for every prayer."},"heading":{"title":"Wudu for Every Prayer Hadith: Istihadah and Menstrual Days","description":"This hadith gives a compact ruling about a woman with prolonged bleeding. The Prophet صلى الله عليه وسلم said that she should abandon prayer during her menstrual period. Then she should take a bath and pray. The narration also says that she should perform ablution for every prayer. Abu Dawud adds that Uthman’s version includes that she should fast and pray. The focus is clear: the menstrual period has its own ruling, and after that, worship continues with purification. For readers searching for wudu for every prayer during istihadah, this narration gives the exact phrase they are looking for. It also keeps the order simple: menses, bath, prayer, and ablution for each prayer."},"teachings":["Prayer is left during the menstrual period.","After the menstrual period, taking a bath and praying are mentioned.","Ablution for every prayer is stated in this narration.","One version also mentions fasting and praying."],"related_hadiths":[{"id":"362","book_id":"3","label":"Sunan an-Nasai"},{"id":"333a","book_id":"2","label":"Sahih Muslim"},{"id":"320","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu for Every Prayer in Istihadah","description":"$book_name$ $hadith_number$ - $chapter_name$. A woman with prolonged bleeding leaves prayer during menses, bathes, prays, and makes wudu for every prayer."},"heading":{"title":"Wudu for Every Prayer Hadith: Istihadah and Menstrual Days","description":"This hadith gives a compact ruling about a woman with prolonged bleeding. The Prophet صلى الله عليه وسلم said that she should abandon prayer during her menstrual period. Then she should take a bath and pray. The narration also says that she should perform ablution for every prayer. Abu Dawud adds that Uthman’s version includes that she should fast and pray. The focus is clear: the menstrual period has its own ruling, and after that, worship continues with purification. For readers searching for wudu for every prayer during istihadah, this narration gives the exact phrase they are looking for. It also keeps the order simple: menses, bath, prayer, and ablution for each prayer."},"teachings":["Prayer is left during the menstrual period.","After the menstrual period, taking a bath and praying are mentioned.","Ablution for every prayer is stated in this narration.","One version also mentions fasting and praying."],"related_hadiths":[{"id":"362","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"333a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"320","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E612" s="4" t="n"/>
@@ -14589,7 +14593,7 @@
       </c>
       <c r="D613" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ablution for Every Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Fatimah was told to bathe, perform ablution for every prayer, and pray."},"heading":{"title":"Fatimah bint Abi Hubaish Hadith: Bathe, Make Wudu, and Pray","description":"This narration from Aishah says that Fatimah daughter of Abu Hubaish came to the Prophet صلى الله عليه وسلم and mentioned her situation. He told her to take a bath, then perform ablution for every prayer and pray. The hadith is short, but it speaks directly to the issue of istihadah and prayer. It is especially useful for people searching for wudu for every salah during prolonged bleeding. The wording does not include a long discussion of menstrual days in this report, so the explanation should stay close to what is stated. The main teaching is that after bathing, ablution is made for each prayer, and prayer continues."},"teachings":["Fatimah brought her condition to the Prophet صلى الله عليه وسلم.","Taking a bath is mentioned first.","Ablution for every prayer is then mentioned.","The instruction ends with prayer, showing worship continues."],"related_hadiths":[{"id":"362","book_id":"3","label":"Sunan an-Nasai"},{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ablution for Every Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Fatimah was told to bathe, perform ablution for every prayer, and pray."},"heading":{"title":"Fatimah bint Abi Hubaish Hadith: Bathe, Make Wudu, and Pray","description":"This narration from Aishah says that Fatimah daughter of Abu Hubaish came to the Prophet صلى الله عليه وسلم and mentioned her situation. He told her to take a bath, then perform ablution for every prayer and pray. The hadith is short, but it speaks directly to the issue of istihadah and prayer. It is especially useful for people searching for wudu for every salah during prolonged bleeding. The wording does not include a long discussion of menstrual days in this report, so the explanation should stay close to what is stated. The main teaching is that after bathing, ablution is made for each prayer, and prayer continues."},"teachings":["Fatimah brought her condition to the Prophet صلى الله عليه وسلم.","Taking a bath is mentioned first.","Ablution for every prayer is then mentioned.","The instruction ends with prayer, showing worship continues."],"related_hadiths":[{"id":"362","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"333a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E613" s="4" t="n"/>
@@ -14612,7 +14616,7 @@
       </c>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Bath Then Ablution","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah said a woman with prolonged bleeding bathes once, then performs ablution until the next menses."},"heading":{"title":"Istihadah Hadith: One Bath and Wudu Until the Next Period","description":"This report is a statement from Aishah about the woman who has prolonged bleeding. She said that such a woman should take a bath, meaning one time, then perform ablution until the days of her next menstrual period. The narration is concise and focuses on purification during istihadah. It does not discuss every possible case, so it should be explained only within its wording. The practical point is that one bath is mentioned, followed by ablution until the next menses. For searchers asking whether istihadah requires ghusl every time or wudu, this report is relevant because it mentions both bath and ablution, with a clear order."},"teachings":["Aishah mentions one bath for the woman with prolonged bleeding.","After that, ablution is mentioned until the next menstrual days.","The report connects istihadah with ongoing purification for prayer.","The wording is brief and should not be expanded beyond its statement."],"related_hadiths":[{"id":"333a","book_id":"2","label":"Sahih Muslim"},{"id":"354","book_id":"3","label":"Sunan an-Nasai"},{"id":"355","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Bath Then Ablution","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah said a woman with prolonged bleeding bathes once, then performs ablution until the next menses."},"heading":{"title":"Istihadah Hadith: One Bath and Wudu Until the Next Period","description":"This report is a statement from Aishah about the woman who has prolonged bleeding. She said that such a woman should take a bath, meaning one time, then perform ablution until the days of her next menstrual period. The narration is concise and focuses on purification during istihadah. It does not discuss every possible case, so it should be explained only within its wording. The practical point is that one bath is mentioned, followed by ablution until the next menses. For searchers asking whether istihadah requires ghusl every time or wudu, this report is relevant because it mentions both bath and ablution, with a clear order."},"teachings":["Aishah mentions one bath for the woman with prolonged bleeding.","After that, ablution is mentioned until the next menstrual days.","The report connects istihadah with ongoing purification for prayer.","The wording is brief and should not be expanded beyond its statement."],"related_hadiths":[{"id":"333a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"354","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"},{"id":"355","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E614" s="4" t="n"/>
@@ -14635,7 +14639,7 @@
       </c>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Choosing a Proper Place to Urinate","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم chose soft ground and told believers to look for a suitable place before urinating."},"heading":{"title":"Hadith About Choosing a Proper Place to Urinate","description":"This hadith focuses on choosing a suitable place before urinating. Abu Musa wrote that the Prophet صلى الله عليه وسلم came to soft ground at the foot of a wall and urinated there. He then said that when one of you wants to urinate, he should look for a place for his urination. The teaching is practical and easy to understand. A person should not be careless about where urine falls. The phrase hadith about urinating place fits this narration well because the Prophet صلى الله عليه وسلم directly told people to look for a place. The text does not give a long list of reasons, so we should not add claims beyond it. The safe lesson is care, planning, and cleanliness."},"teachings":["A person should look for a suitable place before urinating.","Carelessness in urination is not encouraged by this narration.","Cleanliness begins with choosing the right place."],"related_hadiths":[{"id":"20","book_id":"4","label":"Sunan Abu Dawud"},{"id":"217","book_id":"1","label":"Sahih Bukhari"},{"id":"1","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Choosing a Proper Place to Urinate","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم chose soft ground and told believers to look for a suitable place before urinating."},"heading":{"title":"Hadith About Choosing a Proper Place to Urinate","description":"This hadith focuses on choosing a suitable place before urinating. Abu Musa wrote that the Prophet صلى الله عليه وسلم came to soft ground at the foot of a wall and urinated there. He then said that when one of you wants to urinate, he should look for a place for his urination. The teaching is practical and easy to understand. A person should not be careless about where urine falls. The phrase hadith about urinating place fits this narration well because the Prophet صلى الله عليه وسلم directly told people to look for a place. The text does not give a long list of reasons, so we should not add claims beyond it. The safe lesson is care, planning, and cleanliness."},"teachings":["A person should look for a suitable place before urinating.","Carelessness in urination is not encouraged by this narration.","Cleanliness begins with choosing the right place."],"related_hadiths":[{"id":"20","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"217","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"1","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E615" s="4" t="n"/>
@@ -14658,7 +14662,7 @@
       </c>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ghufranaka After Leaving the Toilet","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم would say “Ghufranaka” after leaving the privy, teaching remembrance after a private need."},"heading":{"title":"Hadith About Ghufranaka After Leaving the Toilet","description":"This hadith about Ghufranaka after leaving the toilet teaches a short daily supplication. Aishah, the Mother of the Believers, reports that when the Prophet صلى الله عليه وسلم came out of the privy, he used to say: “Grant me Thy forgiveness.” The Arabic word is “Ghufranaka.” The report is brief, so the explanation should be brief in meaning too. It does not give a long reason in the text. It simply teaches what the Prophet صلى الله عليه وسلم used to say after leaving the place of relief. Many people search for “dua after toilet Ghufranaka” or “Ghufranaka meaning in English.” The key lesson is that even after an ordinary private need, a Muslim can return to Allah with a simple request for forgiveness."},"teachings":["Say “Ghufranaka” after leaving the toilet.","Short daily duas keep a person connected to Allah.","The hadith teaches a simple Sunnah phrase for a common moment."],"related_hadiths":[{"id":"7","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"300","book_id":"6","label":"Sunan Ibn Majah"},{"id":"5376","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ghufranaka After Leaving the Toilet","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم would say “Ghufranaka” after leaving the privy, teaching remembrance after a private need."},"heading":{"title":"Hadith About Ghufranaka After Leaving the Toilet","description":"This hadith about Ghufranaka after leaving the toilet teaches a short daily supplication. Aishah, the Mother of the Believers, reports that when the Prophet صلى الله عليه وسلم came out of the privy, he used to say: “Grant me Thy forgiveness.” The Arabic word is “Ghufranaka.” The report is brief, so the explanation should be brief in meaning too. It does not give a long reason in the text. It simply teaches what the Prophet صلى الله عليه وسلم used to say after leaving the place of relief. Many people search for “dua after toilet Ghufranaka” or “Ghufranaka meaning in English.” The key lesson is that even after an ordinary private need, a Muslim can return to Allah with a simple request for forgiveness."},"teachings":["Say “Ghufranaka” after leaving the toilet.","Short daily duas keep a person connected to Allah.","The hadith teaches a simple Sunnah phrase for a common moment."],"related_hadiths":[{"id":"7","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"300","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"5376","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E616" s="4" t="n"/>
@@ -14681,7 +14685,7 @@
       </c>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Weak Reports on Istihadah Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Dawud discusses weak reports on ablution for every prayer and compares stronger related narrations."},"heading":{"title":"Istihadah Hadith Grading: Abu Dawud on Wudu and Weak Reports","description":"This narration is mainly about hadith criticism on the topic of istihadah and purification. It says the tradition was also narrated through another chain from Aishah. Abu Dawud then explains that several reports on this subject, including reports through Adi ibn Thabit, al-Amash from Habib, and Ayyub Abu al-Ala, are weak and not sound. He points out how some versions are reported as a statement of Aishah rather than directly from the Prophet صلى الله عليه وسلم. He also compares reports that mention ablution for every prayer with reports that mention bathing. The key value of this hadith for readers is not a new ruling alone, but seeing how carefully Abu Dawud checked chains, wording, and whether a statement was raised to the Prophet صلى الله عليه وسلم or stopped at a Companion."},"teachings":["Abu Dawud identifies several reports on this issue as weak.","The narration shows the difference between a Prophetic report and a Companion statement.","Different wordings mention ablution for every prayer or bathing.","Hadith scholars checked chains and wording before relying on reports."],"related_hadiths":[{"id":"333a","book_id":"2","label":"Sahih Muslim"},{"id":"334a","book_id":"2","label":"Sahih Muslim"},{"id":"362","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Weak Reports on Istihadah Wudu","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Dawud discusses weak reports on ablution for every prayer and compares stronger related narrations."},"heading":{"title":"Istihadah Hadith Grading: Abu Dawud on Wudu and Weak Reports","description":"This narration is mainly about hadith criticism on the topic of istihadah and purification. It says the tradition was also narrated through another chain from Aishah. Abu Dawud then explains that several reports on this subject, including reports through Adi ibn Thabit, al-Amash from Habib, and Ayyub Abu al-Ala, are weak and not sound. He points out how some versions are reported as a statement of Aishah rather than directly from the Prophet صلى الله عليه وسلم. He also compares reports that mention ablution for every prayer with reports that mention bathing. The key value of this hadith for readers is not a new ruling alone, but seeing how carefully Abu Dawud checked chains, wording, and whether a statement was raised to the Prophet صلى الله عليه وسلم or stopped at a Companion."},"teachings":["Abu Dawud identifies several reports on this issue as weak.","The narration shows the difference between a Prophetic report and a Companion statement.","Different wordings mention ablution for every prayer or bathing.","Hadith scholars checked chains and wording before relying on reports."],"related_hadiths":[{"id":"333a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"334a","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"362","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E617" s="4" t="n"/>
@@ -14704,7 +14708,7 @@
       </c>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istihadah Purification and Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how prolonged bleeding is handled with washing, wudu for prayer, and practical care when the flow becomes heavy."},"heading":{"title":"Hadith About Istihadah: Washing and Wudu for Prayer","description":"This Hadith focuses on istihadah, or prolonged bleeding, and how prayer is kept connected to purification. Sa'id b. al-Musayyab was asked how a woman with continuous bleeding should wash. His answer gives a practical routine: washing at the time of Zuhr, making wudu for every prayer, and using a cloth if the bleeding is heavy. The report also records that Abu Dawud mentioned other narrations and scholarly views about the wording, especially whether it should be read as one Zuhr to the next or one purification to the next. So the main lesson is careful purity during prolonged bleeding, while still treating prayer as something to maintain with the steps mentioned in the text."},"teachings":["A woman with prolonged bleeding is directed to keep a clear routine of washing and prayer.","Wudu is mentioned for every prayer in this report.","When bleeding is heavy, using a cloth is given as a practical way to manage it."],"related_hadiths":[{"id":"282","book_id":"4","label":"Sunan Abu Dawud"},{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"216","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Istihadah Purification and Prayer","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how prolonged bleeding is handled with washing, wudu for prayer, and practical care when the flow becomes heavy."},"heading":{"title":"Hadith About Istihadah: Washing and Wudu for Prayer","description":"This Hadith focuses on istihadah, or prolonged bleeding, and how prayer is kept connected to purification. Sa'id b. al-Musayyab was asked how a woman with continuous bleeding should wash. His answer gives a practical routine: washing at the time of Zuhr, making wudu for every prayer, and using a cloth if the bleeding is heavy. The report also records that Abu Dawud mentioned other narrations and scholarly views about the wording, especially whether it should be read as one Zuhr to the next or one purification to the next. So the main lesson is careful purity during prolonged bleeding, while still treating prayer as something to maintain with the steps mentioned in the text."},"teachings":["A woman with prolonged bleeding is directed to keep a clear routine of washing and prayer.","Wudu is mentioned for every prayer in this report.","When bleeding is heavy, using a cloth is given as a practical way to manage it."],"related_hadiths":[{"id":"282","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"216","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E618" s="4" t="n"/>
@@ -14727,7 +14731,7 @@
       </c>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Daily Washing After Menstrual Period","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali reports that a woman with prolonged bleeding should wash after her period ends and use a prepared woollen cloth."},"heading":{"title":"Hadith About Prolonged Bleeding: Daily Washing After Menses","description":"This Hadith speaks about a woman who has prolonged bleeding after the normal menstrual period. The report from Ali ibn Abi Talib says that when her menstrual period is over, she should wash herself every day. It also mentions taking a woollen cloth with fat or oil to tie over the private area. The focus is simple and practical: distinguish the menstrual period from the bleeding that continues after it, then return to purification and prayer care. The Hadith does not give a long ruling list, so the explanation should stay close to the words given. It teaches personal cleanliness, care, and a steady routine during istihadah."},"teachings":["The normal menstrual period is treated separately from bleeding that continues afterward.","Washing is mentioned after the menstrual period is over.","The woollen cloth shows practical care for managing continued flow."],"related_hadiths":[{"id":"282","book_id":"4","label":"Sunan Abu Dawud"},{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"216","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Daily Washing After Menstrual Period","description":"$book_name$ $hadith_number$ - $chapter_name$. Ali reports that a woman with prolonged bleeding should wash after her period ends and use a prepared woollen cloth."},"heading":{"title":"Hadith About Prolonged Bleeding: Daily Washing After Menses","description":"This Hadith speaks about a woman who has prolonged bleeding after the normal menstrual period. The report from Ali ibn Abi Talib says that when her menstrual period is over, she should wash herself every day. It also mentions taking a woollen cloth with fat or oil to tie over the private area. The focus is simple and practical: distinguish the menstrual period from the bleeding that continues after it, then return to purification and prayer care. The Hadith does not give a long ruling list, so the explanation should stay close to the words given. It teaches personal cleanliness, care, and a steady routine during istihadah."},"teachings":["The normal menstrual period is treated separately from bleeding that continues afterward.","Washing is mentioned after the menstrual period is over.","The woollen cloth shows practical care for managing continued flow."],"related_hadiths":[{"id":"282","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"216","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E619" s="4" t="n"/>
@@ -14750,7 +14754,7 @@
       </c>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Recognizing Menstrual Blood","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet teaches Fatimah bint Abi Hubaish to recognize menstrual blood, stop prayer then, and pray after wudu when it differs."},"heading":{"title":"Hadith About Istihadah: Recognizing Menstrual Blood","description":"This Hadith is one of the clearest reports about distinguishing menses from istihadah. Fatimah bint Abi Hubaish had prolonged bleeding, and the Prophet صلى الله عليه وسلم told her that menstrual blood is black and recognizable. When that blood appears, she should refrain from prayer. When the blood is of another type, she should perform wudu and pray. The Hadith does not speak in general guesses; it gives a sign mentioned in the report and then links it to prayer. It helps readers searching for hadith about istihadah, menstrual blood, and wudu understand that the text separates recognized menses from other bleeding. The answer is short, but it gives a clear action for each kind of blood."},"teachings":["Recognizable menstrual blood is treated differently from other bleeding.","Prayer is left when the menstrual blood mentioned in the report appears.","When the bleeding is different, the instruction is to make wudu and pray."],"related_hadiths":[{"id":"282","book_id":"4","label":"Sunan Abu Dawud"},{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"362","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Recognizing Menstrual Blood","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet teaches Fatimah bint Abi Hubaish to recognize menstrual blood, stop prayer then, and pray after wudu when it differs."},"heading":{"title":"Hadith About Istihadah: Recognizing Menstrual Blood","description":"This Hadith is one of the clearest reports about distinguishing menses from istihadah. Fatimah bint Abi Hubaish had prolonged bleeding, and the Prophet صلى الله عليه وسلم told her that menstrual blood is black and recognizable. When that blood appears, she should refrain from prayer. When the blood is of another type, she should perform wudu and pray. The Hadith does not speak in general guesses; it gives a sign mentioned in the report and then links it to prayer. It helps readers searching for hadith about istihadah, menstrual blood, and wudu understand that the text separates recognized menses from other bleeding. The answer is short, but it gives a clear action for each kind of blood."},"teachings":["Recognizable menstrual blood is treated differently from other bleeding.","Prayer is left when the menstrual blood mentioned in the report appears.","When the bleeding is different, the instruction is to make wudu and pray."],"related_hadiths":[{"id":"282","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"362","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E620" s="4" t="n"/>
@@ -14773,7 +14777,7 @@
       </c>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Waiting for Menstrual Days","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Habibah was told to wait through her menstrual days, then wash and pray, making wudu if something occurs."},"heading":{"title":"Hadith About Istihadah: Wait, Wash, and Pray","description":"This Hadith reports the case of Umm Habibah daughter of Jahsh, who had prolonged bleeding. The Prophet صلى الله عليه وسلم commanded her to wait during the days of her menstrual period. After that, she should wash and pray. The report then says that if she sees anything that affects ablution, she should make wudu and pray. This is a clear and gentle answer for people searching for istihadah prayer rules. The Hadith keeps the matter tied to her menstrual days, then to ghusl, wudu, and prayer. It does not turn prolonged bleeding into a reason to leave prayer beyond the time named in the report."},"teachings":["The menstrual days are observed before resuming prayer.","After that period, washing and prayer are mentioned together.","If something occurs that affects ablution, wudu is made before prayer."],"related_hadiths":[{"id":"282","book_id":"4","label":"Sunan Abu Dawud"},{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"216","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Waiting for Menstrual Days","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Habibah was told to wait through her menstrual days, then wash and pray, making wudu if something occurs."},"heading":{"title":"Hadith About Istihadah: Wait, Wash, and Pray","description":"This Hadith reports the case of Umm Habibah daughter of Jahsh, who had prolonged bleeding. The Prophet صلى الله عليه وسلم commanded her to wait during the days of her menstrual period. After that, she should wash and pray. The report then says that if she sees anything that affects ablution, she should make wudu and pray. This is a clear and gentle answer for people searching for istihadah prayer rules. The Hadith keeps the matter tied to her menstrual days, then to ghusl, wudu, and prayer. It does not turn prolonged bleeding into a reason to leave prayer beyond the time named in the report."},"teachings":["The menstrual days are observed before resuming prayer.","After that period, washing and prayer are mentioned together.","If something occurs that affects ablution, wudu is made before prayer."],"related_hadiths":[{"id":"282","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"216","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E621" s="4" t="n"/>
@@ -14796,7 +14800,7 @@
       </c>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu When Something Occurs","description":"$book_name$ $hadith_number$ - $chapter_name$. Rabi'ah held that a woman with prolonged bleeding makes wudu when something besides blood affects ablution."},"heading":{"title":"Hadith About Istihadah: Wudu When Ablution Is Affected","description":"This report records the view of Rabi'ah about a woman with istihadah. He did not see wudu as required at every prayer unless something besides the blood affected her ablution. Abu Dawud adds that this was the view held by Malik b. Anas. Since the text is a report of a view, the safest explanation is to keep it as stated. It shows that scholars discussed how wudu applies when prolonged bleeding is present. The main point for readers is not to confuse this report with other narrations that mention wudu for every prayer. Here, the wording highlights wudu when a separate event affects ablution."},"teachings":["This report records a view about wudu during prolonged bleeding.","It links wudu to something besides the blood that affects ablution.","Abu Dawud notes that Malik b. Anas held this view."],"related_hadiths":[{"id":"282","book_id":"4","label":"Sunan Abu Dawud"},{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"216","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wudu When Something Occurs","description":"$book_name$ $hadith_number$ - $chapter_name$. Rabi'ah held that a woman with prolonged bleeding makes wudu when something besides blood affects ablution."},"heading":{"title":"Hadith About Istihadah: Wudu When Ablution Is Affected","description":"This report records the view of Rabi'ah about a woman with istihadah. He did not see wudu as required at every prayer unless something besides the blood affected her ablution. Abu Dawud adds that this was the view held by Malik b. Anas. Since the text is a report of a view, the safest explanation is to keep it as stated. It shows that scholars discussed how wudu applies when prolonged bleeding is present. The main point for readers is not to confuse this report with other narrations that mention wudu for every prayer. Here, the wording highlights wudu when a separate event affects ablution."},"teachings":["This report records a view about wudu during prolonged bleeding.","It links wudu to something besides the blood that affects ablution.","Abu Dawud notes that Malik b. Anas held this view."],"related_hadiths":[{"id":"282","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"216","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E622" s="4" t="n"/>
@@ -14819,7 +14823,7 @@
       </c>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Brown and Yellow Discharge After Purification","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Atiyyah says brown and yellow discharge after purification was not treated as something to count."},"heading":{"title":"Hadith About Discharge After Purity: Brown and Yellow Fluid","description":"This Hadith is short, but very helpful for a common search: yellow discharge after period in Islam. Umm Atiyyah, who had pledged allegiance to the Prophet صلى الله عليه وسلم, said that they did not count brown and yellow fluid after purification as anything. The wording is tied to after purification, so the explanation should not stretch it to every case or every time. The Hadith gives a clear point about what comes after purity has been reached. It helps a reader see that the timing matters. The report is about purity after menses, brown discharge, yellow discharge, and how those fluids were treated by the women mentioned in the narration."},"teachings":["The report is about brown and yellow fluid after purification.","Timing matters because the wording says after purity.","The narration keeps the matter simple and does not add extra conditions."],"related_hadiths":[{"id":"326","book_id":"1","label":"Sahih Bukhari"},{"id":"307","book_id":"1","label":"Sahih Bukhari"},{"id":"269","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Brown and Yellow Discharge After Purification","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Atiyyah says brown and yellow discharge after purification was not treated as something to count."},"heading":{"title":"Hadith About Discharge After Purity: Brown and Yellow Fluid","description":"This Hadith is short, but very helpful for a common search: yellow discharge after period in Islam. Umm Atiyyah, who had pledged allegiance to the Prophet صلى الله عليه وسلم, said that they did not count brown and yellow fluid after purification as anything. The wording is tied to after purification, so the explanation should not stretch it to every case or every time. The Hadith gives a clear point about what comes after purity has been reached. It helps a reader see that the timing matters. The report is about purity after menses, brown discharge, yellow discharge, and how those fluids were treated by the women mentioned in the narration."},"teachings":["The report is about brown and yellow fluid after purification.","Timing matters because the wording says after purity.","The narration keeps the matter simple and does not add extra conditions."],"related_hadiths":[{"id":"326","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"307","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"269","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E623" s="4" t="n"/>
@@ -14842,7 +14846,7 @@
       </c>
       <c r="D624" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Marital Relations During Prolonged Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Ikrimah reports that Umm Habibah had prolonged bleeding and her husband used to cohabit with her."},"heading":{"title":"Hadith About Istihadah and Marital Relations","description":"This Hadith reports a brief point about Umm Habibah, who had istihadah. Ikrimah said that she had prolonged bleeding and that her husband used to cohabit with her. The report does not give a long explanation or list conditions, so the content should not add more than what is said. Its main value is that it separates this ongoing bleeding from the normal menstrual period discussed in nearby narrations. It also shows why people search for istihadah and marital relations hadith. Abu Dawud then mentions comments about one of the narrators, including Yahya b. Ma'in calling him trustworthy and Ahmad b. Hanbal not reporting from him."},"teachings":["The report speaks about cohabitation while Umm Habibah had prolonged bleeding.","It does not give extra details beyond the case mentioned.","Abu Dawud includes notes about a narrator connected to the report."],"related_hadiths":[{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"282","book_id":"4","label":"Sunan Abu Dawud"},{"id":"216","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Marital Relations During Prolonged Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Ikrimah reports that Umm Habibah had prolonged bleeding and her husband used to cohabit with her."},"heading":{"title":"Hadith About Istihadah and Marital Relations","description":"This Hadith reports a brief point about Umm Habibah, who had istihadah. Ikrimah said that she had prolonged bleeding and that her husband used to cohabit with her. The report does not give a long explanation or list conditions, so the content should not add more than what is said. Its main value is that it separates this ongoing bleeding from the normal menstrual period discussed in nearby narrations. It also shows why people search for istihadah and marital relations hadith. Abu Dawud then mentions comments about one of the narrators, including Yahya b. Ma'in calling him trustworthy and Ahmad b. Hanbal not reporting from him."},"teachings":["The report speaks about cohabitation while Umm Habibah had prolonged bleeding.","It does not give extra details beyond the case mentioned.","Abu Dawud includes notes about a narrator connected to the report."],"related_hadiths":[{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"282","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"216","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E624" s="4" t="n"/>
@@ -14865,7 +14869,7 @@
       </c>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Use the Right Hand for Cleaning","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught not to touch or wipe private parts with the right hand and not to drink in one breath."},"heading":{"title":"Hadith About Right Hand Etiquette in Purification","description":"This hadith about right hand etiquette in purification teaches respect for the right hand and care in daily habits. Abu Qatadah reports that the Prophet صلى الله عليه وسلم said when one urinates, he must not touch his private part with his right hand. When he relieves himself, he must not wipe with his right hand. When he drinks, he must not drink in one breath. The hadith covers three actions, but the core topic is clean and respectful use of the hands. It separates the right hand from private cleaning. It also mentions a drinking habit, warning against drinking in one breath. Searchers often look for “do not clean with right hand hadith.” The meaning is direct, practical, and tied to everyday manners."},"teachings":["Do not touch the private part with the right hand while urinating.","Do not wipe after relieving oneself with the right hand.","Drinking should not be done in one breath according to this report."],"related_hadiths":[{"id":"153","book_id":"1","label":"Sahih Bukhari"},{"id":"154","book_id":"1","label":"Sahih Bukhari"},{"id":"262a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Do Not Use the Right Hand for Cleaning","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم taught not to touch or wipe private parts with the right hand and not to drink in one breath."},"heading":{"title":"Hadith About Right Hand Etiquette in Purification","description":"This hadith about right hand etiquette in purification teaches respect for the right hand and care in daily habits. Abu Qatadah reports that the Prophet صلى الله عليه وسلم said when one urinates, he must not touch his private part with his right hand. When he relieves himself, he must not wipe with his right hand. When he drinks, he must not drink in one breath. The hadith covers three actions, but the core topic is clean and respectful use of the hands. It separates the right hand from private cleaning. It also mentions a drinking habit, warning against drinking in one breath. Searchers often look for “do not clean with right hand hadith.” The meaning is direct, practical, and tied to everyday manners."},"teachings":["Do not touch the private part with the right hand while urinating.","Do not wipe after relieving oneself with the right hand.","Drinking should not be done in one breath according to this report."],"related_hadiths":[{"id":"153","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"154","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"262a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E625" s="4" t="n"/>
@@ -14888,7 +14892,7 @@
       </c>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hamnah During Prolonged Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Hamnah bint Jahsh is reported to have had prolonged bleeding while her husband had intercourse with her."},"heading":{"title":"Hadith About Hamnah bint Jahsh and Istihadah","description":"This Hadith is another short report about istihadah and marital relations. Ikrimah reported from Hamnah daughter of Jahsh that she was a woman with prolonged bleeding, and her husband would have intercourse with her during that period. The wording is brief, so it should be handled with care and not mixed with the separate rulings of menses unless the text says so. The Hadith is useful for readers searching for Hamnah bint Jahsh, prolonged bleeding, and istihadah in Islam. The core point is that the report describes a state of ongoing blood flow called istihadah, not a new story with many added details."},"teachings":["Hamnah bint Jahsh is described as having prolonged bleeding.","The report mentions marital relations during that prolonged bleeding.","The narration is brief and should not be made to say more than it states."],"related_hadiths":[{"id":"306","book_id":"1","label":"Sahih Bukhari"},{"id":"282","book_id":"4","label":"Sunan Abu Dawud"},{"id":"362","book_id":"3","label":"Sunan an-Nasai"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Hamnah During Prolonged Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Hamnah bint Jahsh is reported to have had prolonged bleeding while her husband had intercourse with her."},"heading":{"title":"Hadith About Hamnah bint Jahsh and Istihadah","description":"This Hadith is another short report about istihadah and marital relations. Ikrimah reported from Hamnah daughter of Jahsh that she was a woman with prolonged bleeding, and her husband would have intercourse with her during that period. The wording is brief, so it should be handled with care and not mixed with the separate rulings of menses unless the text says so. The Hadith is useful for readers searching for Hamnah bint Jahsh, prolonged bleeding, and istihadah in Islam. The core point is that the report describes a state of ongoing blood flow called istihadah, not a new story with many added details."},"teachings":["Hamnah bint Jahsh is described as having prolonged bleeding.","The report mentions marital relations during that prolonged bleeding.","The narration is brief and should not be made to say more than it states."],"related_hadiths":[{"id":"306","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"282","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"362","book_id":"3","slug":"nasai","label":"Sunan an-Nasai"}]}</t>
         </is>
       </c>
       <c r="E626" s="4" t="n"/>
@@ -14911,7 +14915,7 @@
       </c>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forty Days of Postnatal Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Salamah reports that women with postnatal bleeding would refrain for forty days or nights and used wars for dark spots."},"heading":{"title":"Hadith About Nifas: Forty Days After Childbirth","description":"This Hadith speaks about nifas, the bleeding after childbirth. Umm Salamah, the Mother of the Believers, said that the woman with bleeding after delivery would sit out for forty days or forty nights. The report also mentions that they would anoint their faces with wars, an aromatic herb, for dark spots. The main lesson stays close to the words: postnatal bleeding had a known period mentioned in the narration, and women refrained during that time. It is a common search topic because people look for hadith about nifas, forty days after childbirth, and prayer after delivery. The text gives that point simply and directly."},"teachings":["Postnatal bleeding is linked here with forty days or forty nights.","Women refrained during the period mentioned in the report.","The narration also notes the use of wars for dark spots."],"related_hadiths":[{"id":"648","book_id":"6","label":"Sunan Ibn Majah"},{"id":"139","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"310","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Forty Days of Postnatal Bleeding","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Salamah reports that women with postnatal bleeding would refrain for forty days or nights and used wars for dark spots."},"heading":{"title":"Hadith About Nifas: Forty Days After Childbirth","description":"This Hadith speaks about nifas, the bleeding after childbirth. Umm Salamah, the Mother of the Believers, said that the woman with bleeding after delivery would sit out for forty days or forty nights. The report also mentions that they would anoint their faces with wars, an aromatic herb, for dark spots. The main lesson stays close to the words: postnatal bleeding had a known period mentioned in the narration, and women refrained during that time. It is a common search topic because people look for hadith about nifas, forty days after childbirth, and prayer after delivery. The text gives that point simply and directly."},"teachings":["Postnatal bleeding is linked here with forty days or forty nights.","Women refrained during the period mentioned in the report.","The narration also notes the use of wars for dark spots."],"related_hadiths":[{"id":"648","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"139","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"310","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E627" s="4" t="n"/>
@@ -14934,7 +14938,7 @@
       </c>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Makeup Prayer for Nifas","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Salamah says women in postnatal bleeding refrained for forty nights and were not told to make up missed prayers."},"heading":{"title":"Hadith About Nifas: No Makeup Prayer After Postnatal Bleeding","description":"This Hadith answers a direct question about making up prayers connected to bleeding. Mussah came to Umm Salamah and said that Samurah b. Jundub commanded women to make up prayers left during menstruation. Umm Salamah replied that they should not do so. She then mentioned that the wives of the Prophet صلى الله عليه وسلم would refrain for forty nights during postnatal bleeding, and the Prophet صلى الله عليه وسلم did not command them to make up those prayers. The Hadith is often searched under nifas prayer, missed prayers after childbirth, and menstruation prayer makeup. The safest reading is to keep the answer tied to the exact report and its wording."},"teachings":["Umm Salamah rejected making up the prayers in the case discussed.","The report mentions forty nights during postnatal bleeding.","The Prophet صلى الله عليه وسلم did not command makeup prayers for the prayers missed in that period."],"related_hadiths":[{"id":"648","book_id":"6","label":"Sunan Ibn Majah"},{"id":"139","book_id":"5","label":"Jami at-Tirmidhi"},{"id":"321","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | No Makeup Prayer for Nifas","description":"$book_name$ $hadith_number$ - $chapter_name$. Umm Salamah says women in postnatal bleeding refrained for forty nights and were not told to make up missed prayers."},"heading":{"title":"Hadith About Nifas: No Makeup Prayer After Postnatal Bleeding","description":"This Hadith answers a direct question about making up prayers connected to bleeding. Mussah came to Umm Salamah and said that Samurah b. Jundub commanded women to make up prayers left during menstruation. Umm Salamah replied that they should not do so. She then mentioned that the wives of the Prophet صلى الله عليه وسلم would refrain for forty nights during postnatal bleeding, and the Prophet صلى الله عليه وسلم did not command them to make up those prayers. The Hadith is often searched under nifas prayer, missed prayers after childbirth, and menstruation prayer makeup. The safest reading is to keep the answer tied to the exact report and its wording."},"teachings":["Umm Salamah rejected making up the prayers in the case discussed.","The report mentions forty nights during postnatal bleeding.","The Prophet صلى الله عليه وسلم did not command makeup prayers for the prayers missed in that period."],"related_hadiths":[{"id":"648","book_id":"6","slug":"majah","label":"Sunan Ibn Majah"},{"id":"139","book_id":"5","slug":"tirmidhi","label":"Jami at-Tirmidhi"},{"id":"321","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E628" s="4" t="n"/>
@@ -14957,7 +14961,7 @@
       </c>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Washing Menstrual Blood With Water and Salt","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet guided a woman of Banu Ghifar to care for herself and wash menstrual blood from the saddle with salted water."},"heading":{"title":"Hadith About Menstrual Blood: Washing With Salted Water","description":"This Hadith describes a personal moment for a woman of Banu Ghifar during her first menstruation. She noticed blood on the rear of the saddle and felt ashamed. The Messenger of Allah صلى الله عليه وسلم saw what happened and asked if she was menstruating. When she said yes, he told her to set herself right, take water, put salt in it, wash the blood from the saddle, and return to her mount. The Hadith is often found through searches like washing menstrual blood in Islam and hadith about menstrual blood on clothes. Its message is practical and kind: deal with the blood, clean the affected place, and continue the journey."},"teachings":["Menstruation is handled with practical care, not shame in the report.","The blood on the saddle was washed with water mixed with salt.","The woman was told to return to her mount after cleaning the affected place."],"related_hadiths":[{"id":"307","book_id":"1","label":"Sahih Bukhari"},{"id":"308","book_id":"1","label":"Sahih Bukhari"},{"id":"269","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Washing Menstrual Blood With Water and Salt","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet guided a woman of Banu Ghifar to care for herself and wash menstrual blood from the saddle with salted water."},"heading":{"title":"Hadith About Menstrual Blood: Washing With Salted Water","description":"This Hadith describes a personal moment for a woman of Banu Ghifar during her first menstruation. She noticed blood on the rear of the saddle and felt ashamed. The Messenger of Allah صلى الله عليه وسلم saw what happened and asked if she was menstruating. When she said yes, he told her to set herself right, take water, put salt in it, wash the blood from the saddle, and return to her mount. The Hadith is often found through searches like washing menstrual blood in Islam and hadith about menstrual blood on clothes. Its message is practical and kind: deal with the blood, clean the affected place, and continue the journey."},"teachings":["Menstruation is handled with practical care, not shame in the report.","The blood on the saddle was washed with water mixed with salt.","The woman was told to return to her mount after cleaning the affected place."],"related_hadiths":[{"id":"307","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"308","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"269","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E629" s="4" t="n"/>
@@ -14980,7 +14984,7 @@
       </c>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ghusl After Menstruation","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Asma to wash after menses with water and lote leaves, rub the hair roots, pour water, and remove blood marks."},"heading":{"title":"Hadith About Ghusl After Menstruation","description":"This Hadith gives clear steps for ghusl after menstruation. Asma asked the Messenger of Allah صلى الله عليه وسلم how a woman should bathe when she becomes pure from menses. He told her to use water mixed with lote-tree leaves, perform ablution, wash and rub her head until the water reaches the roots of her hair, pour water over her body, then take a piece of cloth, cotton, or wool and purify with it. Aishah understood the indirect wording and explained that it meant removing the marks of blood. For readers searching how to perform ghusl after period, this Hadith gives a simple and careful description."},"teachings":["A woman may ask clearly about purification after menses.","The report mentions washing the head until water reaches the hair roots.","Aishah explained that the cloth was used to remove traces of blood."],"related_hadiths":[{"id":"332c","book_id":"2","label":"Sahih Muslim"},{"id":"314","book_id":"1","label":"Sahih Bukhari"},{"id":"315","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Ghusl After Menstruation","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet taught Asma to wash after menses with water and lote leaves, rub the hair roots, pour water, and remove blood marks."},"heading":{"title":"Hadith About Ghusl After Menstruation","description":"This Hadith gives clear steps for ghusl after menstruation. Asma asked the Messenger of Allah صلى الله عليه وسلم how a woman should bathe when she becomes pure from menses. He told her to use water mixed with lote-tree leaves, perform ablution, wash and rub her head until the water reaches the roots of her hair, pour water over her body, then take a piece of cloth, cotton, or wool and purify with it. Aishah understood the indirect wording and explained that it meant removing the marks of blood. For readers searching how to perform ghusl after period, this Hadith gives a simple and careful description."},"teachings":["A woman may ask clearly about purification after menses.","The report mentions washing the head until water reaches the hair roots.","Aishah explained that the cloth was used to remove traces of blood."],"related_hadiths":[{"id":"332c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"314","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"315","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E630" s="4" t="n"/>
@@ -15003,7 +15007,7 @@
       </c>
       <c r="D631" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Musk-Scented Cloth After Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah praised the Ansari women, and this version mentions using a musk-scented piece of cloth after purification."},"heading":{"title":"Hadith About Ghusl: Musk-Scented Cloth After Menses","description":"This Hadith continues the same meaning about ghusl after menstruation. Aishah mentioned the women of the Ansar and praised them. Then she reported that one of their women came to the Messenger of Allah صلى الله عليه وسلم and asked about the matter. This version includes the words “a musk-scented piece of cloth.” Musaddad also notes wording differences from narrators, whether the word was firsah or qasrah. The useful point for readers is direct and modest: after purification from menses, a woman was guided to use a scented piece of cloth as part of cleaning. The report also shows that asking about religious cleanliness was not treated as wrong."},"teachings":["Aishah praised the women of the Ansar in this report.","This version mentions a musk-scented piece of cloth.","The narration preserves wording details from different transmitters."],"related_hadiths":[{"id":"332c","book_id":"2","label":"Sahih Muslim"},{"id":"314","book_id":"1","label":"Sahih Bukhari"},{"id":"315","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Musk-Scented Cloth After Menses","description":"$book_name$ $hadith_number$ - $chapter_name$. Aishah praised the Ansari women, and this version mentions using a musk-scented piece of cloth after purification."},"heading":{"title":"Hadith About Ghusl: Musk-Scented Cloth After Menses","description":"This Hadith continues the same meaning about ghusl after menstruation. Aishah mentioned the women of the Ansar and praised them. Then she reported that one of their women came to the Messenger of Allah صلى الله عليه وسلم and asked about the matter. This version includes the words “a musk-scented piece of cloth.” Musaddad also notes wording differences from narrators, whether the word was firsah or qasrah. The useful point for readers is direct and modest: after purification from menses, a woman was guided to use a scented piece of cloth as part of cleaning. The report also shows that asking about religious cleanliness was not treated as wrong."},"teachings":["Aishah praised the women of the Ansar in this report.","This version mentions a musk-scented piece of cloth.","The narration preserves wording details from different transmitters."],"related_hadiths":[{"id":"332c","book_id":"2","slug":"muslim","label":"Sahih Muslim"},{"id":"314","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"315","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E631" s="4" t="n"/>
@@ -15026,7 +15030,7 @@
       </c>
       <c r="D632" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Revelation of Tayammum","description":"$book_name$ $hadith_number$ - $chapter_name$. A lost necklace led to prayer without water, then the verse of tayammum was revealed as relief for the Muslims."},"heading":{"title":"Hadith About Tayammum: The Lost Necklace of Aishah","description":"This Hadith explains the event connected to the verse of tayammum. The Messenger of Allah صلى الله عليه وسلم sent Usayd ibn Hudayr and others to search for Aishah's lost necklace. The time of prayer came, and they prayed without ablution. When they returned and told the Prophet صلى الله عليه وسلم, the verse concerning tayammum was revealed. Usayd then said that whenever Aishah faced an unpleasant matter, Allah made a way out for her and for the Muslims through it. The report is a key result for searches like hadith about tayammum, tayammum verse revealed, and Aishah necklace hadith. It shows ease after a difficult moment, without adding details beyond the narration."},"teachings":["The prayer time came while the group had no ablution.","The verse concerning tayammum was revealed after the event was reported.","Usayd noted that relief came through a difficult situation."],"related_hadiths":[{"id":"334","book_id":"1","label":"Sahih Bukhari"},{"id":"4607","book_id":"1","label":"Sahih Bukhari"},{"id":"336","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Revelation of Tayammum","description":"$book_name$ $hadith_number$ - $chapter_name$. A lost necklace led to prayer without water, then the verse of tayammum was revealed as relief for the Muslims."},"heading":{"title":"Hadith About Tayammum: The Lost Necklace of Aishah","description":"This Hadith explains the event connected to the verse of tayammum. The Messenger of Allah صلى الله عليه وسلم sent Usayd ibn Hudayr and others to search for Aishah's lost necklace. The time of prayer came, and they prayed without ablution. When they returned and told the Prophet صلى الله عليه وسلم, the verse concerning tayammum was revealed. Usayd then said that whenever Aishah faced an unpleasant matter, Allah made a way out for her and for the Muslims through it. The report is a key result for searches like hadith about tayammum, tayammum verse revealed, and Aishah necklace hadith. It shows ease after a difficult moment, without adding details beyond the narration."},"teachings":["The prayer time came while the group had no ablution.","The verse concerning tayammum was revealed after the event was reported.","Usayd noted that relief came through a difficult situation."],"related_hadiths":[{"id":"334","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"4607","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"336","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E632" s="4" t="n"/>
@@ -15049,7 +15053,7 @@
       </c>
       <c r="D633" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping With Pure Earth","description":"$book_name$ $hadith_number$ - $chapter_name$. Ammar reports that the Companions used pure earth for Fajr, wiping the face once and then the arms after another strike."},"heading":{"title":"Hadith About Tayammum: Wiping Face and Arms With Earth","description":"This Hadith reports a method of tayammum narrated by Ammar ibn Yasir. The Companions were with the Messenger of Allah صلى الله عليه وسلم and wiped with pure earth for the dawn prayer. They struck the ground with their palms and wiped their faces once. Then they struck the ground again and wiped their arms completely up to the shoulders and armpits with the inner side of their hands. The narration is detailed, and Abu Dawud records other reports nearby with wording differences. For readers searching how to perform tayammum hadith, the safe way to explain this report is to describe exactly what it says and not turn it into a wider claim."},"teachings":["The Companions used pure earth for purification before Fajr.","The face was wiped once after striking the ground.","The report mentions a second strike and wiping the arms up to the shoulders and armpits."],"related_hadiths":[{"id":"338","book_id":"1","label":"Sahih Bukhari"},{"id":"339","book_id":"1","label":"Sahih Bukhari"},{"id":"368b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping With Pure Earth","description":"$book_name$ $hadith_number$ - $chapter_name$. Ammar reports that the Companions used pure earth for Fajr, wiping the face once and then the arms after another strike."},"heading":{"title":"Hadith About Tayammum: Wiping Face and Arms With Earth","description":"This Hadith reports a method of tayammum narrated by Ammar ibn Yasir. The Companions were with the Messenger of Allah صلى الله عليه وسلم and wiped with pure earth for the dawn prayer. They struck the ground with their palms and wiped their faces once. Then they struck the ground again and wiped their arms completely up to the shoulders and armpits with the inner side of their hands. The narration is detailed, and Abu Dawud records other reports nearby with wording differences. For readers searching how to perform tayammum hadith, the safe way to explain this report is to describe exactly what it says and not turn it into a wider claim."},"teachings":["The Companions used pure earth for purification before Fajr.","The face was wiped once after striking the ground.","The report mentions a second strike and wiping the arms up to the shoulders and armpits."],"related_hadiths":[{"id":"338","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"339","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"368b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E633" s="4" t="n"/>
@@ -15072,7 +15076,7 @@
       </c>
       <c r="D634" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tayammum Without Holding Dust","description":"$book_name$ $hadith_number$ - $chapter_name$. This version says the Muslims struck the earth with their palms, did not take dust in their hands, and wiped above the elbows."},"heading":{"title":"Hadith About Tayammum: Striking Earth Without Holding Dust","description":"This report gives another chain for the tayammum narration. It says the Muslims stood and struck the earth with their palms, but did not take any earth in their hands. The rest of the meaning is similar to the previous report, though this version does not mention shoulders and armpits. Ibn al-Laith's wording says they wiped above the elbows. This matters because the report is about wording details in the method of tayammum. People searching tayammum without dust or tayammum hands and face hadith should notice how carefully the narration records what was included and what was not included in this version."},"teachings":["The Muslims struck the earth but did not hold dust in their hands.","This version omits the wording about shoulders and armpits.","Ibn al-Laith's wording mentions wiping above the elbows."],"related_hadiths":[{"id":"338","book_id":"1","label":"Sahih Bukhari"},{"id":"339","book_id":"1","label":"Sahih Bukhari"},{"id":"368b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tayammum Without Holding Dust","description":"$book_name$ $hadith_number$ - $chapter_name$. This version says the Muslims struck the earth with their palms, did not take dust in their hands, and wiped above the elbows."},"heading":{"title":"Hadith About Tayammum: Striking Earth Without Holding Dust","description":"This report gives another chain for the tayammum narration. It says the Muslims stood and struck the earth with their palms, but did not take any earth in their hands. The rest of the meaning is similar to the previous report, though this version does not mention shoulders and armpits. Ibn al-Laith's wording says they wiped above the elbows. This matters because the report is about wording details in the method of tayammum. People searching tayammum without dust or tayammum hands and face hadith should notice how carefully the narration records what was included and what was not included in this version."},"teachings":["The Muslims struck the earth but did not hold dust in their hands.","This version omits the wording about shoulders and armpits.","Ibn al-Laith's wording mentions wiping above the elbows."],"related_hadiths":[{"id":"338","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"339","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"368b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E634" s="4" t="n"/>
@@ -15095,7 +15099,7 @@
       </c>
       <c r="D635" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Right Hand for Food and Drink","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used his right hand for food and drink and his left hand for other purposes."},"heading":{"title":"Hadith About Using the Right Hand for Food and Drink","description":"This hadith about using the right hand for food and drink teaches daily manners through the Prophet’s صلى الله عليه وسلم own practice. Hafsah, the Mother of the Believers, reports that the Prophet صلى الله عليه وسلم used his right hand for taking food and drink, and his left hand for other purposes. The wording is short, but the teaching is clear. The right hand is honored in eating and drinking. The left hand is used for other needs. This is why many people search “hadith eat with right hand” or “right hand for food and drink hadith.” The report is not hard to apply. It turns an ordinary meal or drink into a moment of Sunnah manners. It also matches the broader theme of cleanliness and ordered daily conduct."},"teachings":["Use the right hand for food.","Use the right hand for drink.","Daily manners can reflect the Prophet’s صلى الله عليه وسلم practice."],"related_hadiths":[{"id":"5376","book_id":"1","label":"Sahih Bukhari"},{"id":"5380","book_id":"1","label":"Sahih Bukhari"},{"id":"2020a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Right Hand for Food and Drink","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used his right hand for food and drink and his left hand for other purposes."},"heading":{"title":"Hadith About Using the Right Hand for Food and Drink","description":"This hadith about using the right hand for food and drink teaches daily manners through the Prophet’s صلى الله عليه وسلم own practice. Hafsah, the Mother of the Believers, reports that the Prophet صلى الله عليه وسلم used his right hand for taking food and drink, and his left hand for other purposes. The wording is short, but the teaching is clear. The right hand is honored in eating and drinking. The left hand is used for other needs. This is why many people search “hadith eat with right hand” or “right hand for food and drink hadith.” The report is not hard to apply. It turns an ordinary meal or drink into a moment of Sunnah manners. It also matches the broader theme of cleanliness and ordered daily conduct."},"teachings":["Use the right hand for food.","Use the right hand for drink.","Daily manners can reflect the Prophet’s صلى الله عليه وسلم practice."],"related_hadiths":[{"id":"5376","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5380","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"2020a","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E635" s="4" t="n"/>
@@ -15118,7 +15122,7 @@
       </c>
       <c r="D636" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Concession of Pure Earth","description":"$book_name$ $hadith_number$ - $chapter_name$. Ammar reports the necklace event, lack of water, and the revelation allowing purification with pure earth."},"heading":{"title":"Hadith About Tayammum: Purification With Pure Earth","description":"This Hadith gives a fuller account of the event at Ulat al-Jaysh. Aishah was with the Messenger of Allah صلى الله عليه وسلم, and her necklace broke. The people stayed to search for it until dawn, and they had no water. Abu Bakr became upset because the people were delayed without water. Then Allah sent revelation to His Messenger صلى الله عليه وسلم granting the concession of purification with pure earth. The Muslims stood with the Prophet صلى الله عليه وسلم, struck the ground with their hands, raised their hands without taking dust, and wiped their faces and hands as described in the report. Abu Dawud then adds notes about chains and wording, including the mention of two strikes in some routes."},"teachings":["The Muslims faced prayer time while they had no water.","The concession of purification with pure earth was revealed in this event.","The report describes striking the ground and wiping the face and hands."],"related_hadiths":[{"id":"334","book_id":"1","label":"Sahih Bukhari"},{"id":"338","book_id":"1","label":"Sahih Bukhari"},{"id":"368b","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Concession of Pure Earth","description":"$book_name$ $hadith_number$ - $chapter_name$. Ammar reports the necklace event, lack of water, and the revelation allowing purification with pure earth."},"heading":{"title":"Hadith About Tayammum: Purification With Pure Earth","description":"This Hadith gives a fuller account of the event at Ulat al-Jaysh. Aishah was with the Messenger of Allah صلى الله عليه وسلم, and her necklace broke. The people stayed to search for it until dawn, and they had no water. Abu Bakr became upset because the people were delayed without water. Then Allah sent revelation to His Messenger صلى الله عليه وسلم granting the concession of purification with pure earth. The Muslims stood with the Prophet صلى الله عليه وسلم, struck the ground with their hands, raised their hands without taking dust, and wiped their faces and hands as described in the report. Abu Dawud then adds notes about chains and wording, including the mention of two strikes in some routes."},"teachings":["The Muslims faced prayer time while they had no water.","The concession of purification with pure earth was revealed in this event.","The report describes striking the ground and wiping the face and hands."],"related_hadiths":[{"id":"334","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"338","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"368b","book_id":"2","slug":"muslim","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
       <c r="E636" s="4" t="n"/>
@@ -15141,7 +15145,7 @@
       </c>
       <c r="D637" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tayammum When Water Is Missing","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how tayammum is shown when water is unavailable and how the Prophet صلى الله عليه وسلم corrected Ammar’s method."},"heading":{"title":"How to Perform Tayammum When Water Is Not Found","description":"This Hadith focuses on tayammum when a person is in a state of major impurity and cannot find water. Abu Musa asks a direct question about a man who has no water for a long time. The discussion then turns to the Qur’anic wording about clean earth and the report of Ammar. Ammar had rolled on the ground because he did not know the correct way. The Prophet صلى الله عليه وسلم corrected him with a simple method: strike the ground, shake off the hands, wipe the hands, and wipe the face. The main message is that tayammum is not meant to be hard or confusing. It is a clean and simple way to prepare for prayer when water is not available."},"teachings":["Tayammum is connected to the situation where water cannot be found.","The Prophet صلى الله عليه وسلم corrected Ammar with a simple practical method.","Religious questions should be answered with evidence, not only personal concern.","A person should learn the proper way of purification instead of guessing."],"related_hadiths":[{"id":"322","book_id":"4","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","label":"Sunan Abu Dawud"},{"id":"327","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tayammum When Water Is Missing","description":"$book_name$ $hadith_number$ - $chapter_name$. Learn how tayammum is shown when water is unavailable and how the Prophet صلى الله عليه وسلم corrected Ammar’s method."},"heading":{"title":"How to Perform Tayammum When Water Is Not Found","description":"This Hadith focuses on tayammum when a person is in a state of major impurity and cannot find water. Abu Musa asks a direct question about a man who has no water for a long time. The discussion then turns to the Qur’anic wording about clean earth and the report of Ammar. Ammar had rolled on the ground because he did not know the correct way. The Prophet صلى الله عليه وسلم corrected him with a simple method: strike the ground, shake off the hands, wipe the hands, and wipe the face. The main message is that tayammum is not meant to be hard or confusing. It is a clean and simple way to prepare for prayer when water is not available."},"teachings":["Tayammum is connected to the situation where water cannot be found.","The Prophet صلى الله عليه وسلم corrected Ammar with a simple practical method.","Religious questions should be answered with evidence, not only personal concern.","A person should learn the proper way of purification instead of guessing."],"related_hadiths":[{"id":"322","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"327","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E637" s="4" t="n"/>
@@ -15164,7 +15168,7 @@
       </c>
       <c r="D638" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tayammum in Long Absence of Water","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows Ammar recalling the Prophet’s صلى الله عليه وسلم guidance on tayammum when water was not available."},"heading":{"title":"Tayammum for Janabah When Water Is Far Away","description":"This Hadith explains tayammum for janabah when people live in a place where water may be absent for a month or two. A man asks Umar what to do, and Umar gives his own view. Ammar then reminds him of an earlier event when they had become sexually defiled and Ammar had rolled on the ground. When they came to the Prophet صلى الله عليه وسلم, he showed that a much easier action was enough. He struck the earth with his hands, blew over them, then wiped his face and hands. The key lesson is that tayammum is a valid form of purification in hardship, and the Prophet’s صلى الله عليه وسلم teaching made the method clear and lighter than Ammar first thought."},"teachings":["Tayammum is mentioned in the context of having no access to water.","The Prophet صلى الله عليه وسلم showed a simple way instead of a harsh or mistaken one.","Ammar carefully recalled what he heard and saw from the Prophet صلى الله عليه وسلم.","Scholarly discussion can include different memories and views."],"related_hadiths":[{"id":"321","book_id":"4","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","label":"Sunan Abu Dawud"},{"id":"327","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tayammum in Long Absence of Water","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration shows Ammar recalling the Prophet’s صلى الله عليه وسلم guidance on tayammum when water was not available."},"heading":{"title":"Tayammum for Janabah When Water Is Far Away","description":"This Hadith explains tayammum for janabah when people live in a place where water may be absent for a month or two. A man asks Umar what to do, and Umar gives his own view. Ammar then reminds him of an earlier event when they had become sexually defiled and Ammar had rolled on the ground. When they came to the Prophet صلى الله عليه وسلم, he showed that a much easier action was enough. He struck the earth with his hands, blew over them, then wiped his face and hands. The key lesson is that tayammum is a valid form of purification in hardship, and the Prophet’s صلى الله عليه وسلم teaching made the method clear and lighter than Ammar first thought."},"teachings":["Tayammum is mentioned in the context of having no access to water.","The Prophet صلى الله عليه وسلم showed a simple way instead of a harsh or mistaken one.","Ammar carefully recalled what he heard and saw from the Prophet صلى الله عليه وسلم.","Scholarly discussion can include different memories and views."],"related_hadiths":[{"id":"321","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"327","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E638" s="4" t="n"/>
@@ -15187,7 +15191,7 @@
       </c>
       <c r="D639" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Strike for Tayammum","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith reports the Prophet’s صلى الله عليه وسلم instruction to Ammar about one strike and wiping the face and arms."},"heading":{"title":"One Strike in Tayammum: The Hadith of Ammar","description":"This Hadith gives another wording of the tayammum report from Ammar ibn Yasir. The Prophet صلى الله عليه وسلم said that it would have been enough for Ammar to do it in this way. The narration mentions one strike on the ground with both hands, then one hand being struck against the other, followed by wiping the face and the arms up to half the forearms, without reaching the elbows. The report is focused on the action itself, so the explanation should stay close to that. It teaches that the Prophet صلى الله عليه وسلم made tayammum practical and limited. The Hadith also includes Abu Dawud’s note about different chains, showing that the wording was carefully transmitted."},"teachings":["The Prophet صلى الله عليه وسلم taught Ammar a shorter method than rolling on the ground.","This narration mentions one strike for tayammum.","The report describes wiping the face and arms without reaching the elbows.","Hadith transmitters carefully preserved different chains and wordings."],"related_hadiths":[{"id":"324","book_id":"4","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","label":"Sunan Abu Dawud"},{"id":"327","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Strike for Tayammum","description":"$book_name$ $hadith_number$ - $chapter_name$. The Hadith reports the Prophet’s صلى الله عليه وسلم instruction to Ammar about one strike and wiping the face and arms."},"heading":{"title":"One Strike in Tayammum: The Hadith of Ammar","description":"This Hadith gives another wording of the tayammum report from Ammar ibn Yasir. The Prophet صلى الله عليه وسلم said that it would have been enough for Ammar to do it in this way. The narration mentions one strike on the ground with both hands, then one hand being struck against the other, followed by wiping the face and the arms up to half the forearms, without reaching the elbows. The report is focused on the action itself, so the explanation should stay close to that. It teaches that the Prophet صلى الله عليه وسلم made tayammum practical and limited. The Hadith also includes Abu Dawud’s note about different chains, showing that the wording was carefully transmitted."},"teachings":["The Prophet صلى الله عليه وسلم taught Ammar a shorter method than rolling on the ground.","This narration mentions one strike for tayammum.","The report describes wiping the face and arms without reaching the elbows.","Hadith transmitters carefully preserved different chains and wordings."],"related_hadiths":[{"id":"324","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"327","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E639" s="4" t="n"/>
@@ -15210,7 +15214,7 @@
       </c>
       <c r="D640" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Face and Hands in Tayammum","description":"$book_name$ $hadith_number$ - $chapter_name$. This report describes the Prophet صلى الله عليه وسلم striking the earth, blowing, and wiping the face and hands."},"heading":{"title":"Tayammum Method: Wiping the Face and Hands","description":"This Hadith repeats the incident of Ammar and tayammum with a short and clear wording. The Prophet صلى الله عليه وسلم said that this action would have been enough, then struck the earth with his hand, blew into it, and wiped his face and hands. The narrator Salamah is unsure whether the wiping reached the elbows or only the wrists. That doubt is part of the narration and should be respected. The Hadith is useful for people searching for the method of tayammum because it shows the main actions: touch the earth, reduce the dust by blowing, and wipe. It also teaches care in narration, because uncertainty is mentioned honestly instead of being hidden."},"teachings":["The Prophet صلى الله عليه وسلم showed tayammum as a simple act of purification.","Blowing after touching the earth is mentioned in this wording.","The narrator openly stated his doubt about the exact extent of wiping.","Careful reporting includes what is known and what is uncertain."],"related_hadiths":[{"id":"323","book_id":"4","label":"Sunan Abu Dawud"},{"id":"325","book_id":"4","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Face and Hands in Tayammum","description":"$book_name$ $hadith_number$ - $chapter_name$. This report describes the Prophet صلى الله عليه وسلم striking the earth, blowing, and wiping the face and hands."},"heading":{"title":"Tayammum Method: Wiping the Face and Hands","description":"This Hadith repeats the incident of Ammar and tayammum with a short and clear wording. The Prophet صلى الله عليه وسلم said that this action would have been enough, then struck the earth with his hand, blew into it, and wiped his face and hands. The narrator Salamah is unsure whether the wiping reached the elbows or only the wrists. That doubt is part of the narration and should be respected. The Hadith is useful for people searching for the method of tayammum because it shows the main actions: touch the earth, reduce the dust by blowing, and wipe. It also teaches care in narration, because uncertainty is mentioned honestly instead of being hidden."},"teachings":["The Prophet صلى الله عليه وسلم showed tayammum as a simple act of purification.","Blowing after touching the earth is mentioned in this wording.","The narrator openly stated his doubt about the exact extent of wiping.","Careful reporting includes what is known and what is uncertain."],"related_hadiths":[{"id":"323","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"325","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E640" s="4" t="n"/>
@@ -15233,7 +15237,7 @@
       </c>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Different Wording on Tayammum","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration records wording about wiping the face and hands, with a note on the mention of forearms."},"heading":{"title":"Tayammum Hadith and the Wording About Forearms","description":"This Hadith gives another chain for the same tayammum report. It says that the Prophet صلى الله عليه وسلم blew into his hands and wiped his face and hands up to the elbows or forearms. Then Shu'bah explains that Salamah used to narrate the words “the hands, the face, and the forearms.” Mansur warned him to be careful, because no one else mentioned the forearms in that way. This report is not just about the method of tayammum. It also shows how precise Hadith scholars were with wording. For a reader, the safe lesson is to notice what the narration actually says and also notice the caution raised about one wording."},"teachings":["The narration mentions wiping the face and hands in tayammum.","There is a reported difference about the wording related to forearms.","Mansur advised care in repeating a wording that others did not mention.","Hadith transmission includes checks on exact words."],"related_hadiths":[{"id":"323","book_id":"4","label":"Sunan Abu Dawud"},{"id":"324","book_id":"4","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Different Wording on Tayammum","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration records wording about wiping the face and hands, with a note on the mention of forearms."},"heading":{"title":"Tayammum Hadith and the Wording About Forearms","description":"This Hadith gives another chain for the same tayammum report. It says that the Prophet صلى الله عليه وسلم blew into his hands and wiped his face and hands up to the elbows or forearms. Then Shu'bah explains that Salamah used to narrate the words “the hands, the face, and the forearms.” Mansur warned him to be careful, because no one else mentioned the forearms in that way. This report is not just about the method of tayammum. It also shows how precise Hadith scholars were with wording. For a reader, the safe lesson is to notice what the narration actually says and also notice the caution raised about one wording."},"teachings":["The narration mentions wiping the face and hands in tayammum.","There is a reported difference about the wording related to forearms.","Mansur advised care in repeating a wording that others did not mention.","Hadith transmission includes checks on exact words."],"related_hadiths":[{"id":"323","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"324","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E641" s="4" t="n"/>
@@ -15256,7 +15260,7 @@
       </c>
       <c r="D642" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Stroke for Face and Hands","description":"$book_name$ $hadith_number$ - $chapter_name$. Ammar asked about tayammum, and the Prophet صلى الله عليه وسلم commanded one stroke for the face and hands."},"heading":{"title":"One Stroke Tayammum for the Face and Hands","description":"This Hadith is one of the shortest and clearest reports about tayammum. Ammar ibn Yasir says that he asked the Prophet صلى الله عليه وسلم about tayammum. The Prophet صلى الله عليه وسلم commanded him to make one stroke for the face and the hands. The narration does not add a long story here. It gives the main instruction in a direct way. For anyone searching “tayammum hadith” or “one stroke tayammum,” this text is easy to understand. It shows that the Prophet صلى الله عليه وسلم answered the question with a simple action. The Hadith also helps readers avoid making tayammum harder than what is stated in this report."},"teachings":["Ammar asked the Prophet صلى الله عليه وسلم directly about tayammum.","The Prophet صلى الله عليه وسلم commanded one stroke for the face and hands.","The Hadith gives a short and direct method.","Asking about purification can lead to clear guidance."],"related_hadiths":[{"id":"323","book_id":"4","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","label":"Sunan Abu Dawud"},{"id":"328","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | One Stroke for Face and Hands","description":"$book_name$ $hadith_number$ - $chapter_name$. Ammar asked about tayammum, and the Prophet صلى الله عليه وسلم commanded one stroke for the face and hands."},"heading":{"title":"One Stroke Tayammum for the Face and Hands","description":"This Hadith is one of the shortest and clearest reports about tayammum. Ammar ibn Yasir says that he asked the Prophet صلى الله عليه وسلم about tayammum. The Prophet صلى الله عليه وسلم commanded him to make one stroke for the face and the hands. The narration does not add a long story here. It gives the main instruction in a direct way. For anyone searching “tayammum hadith” or “one stroke tayammum,” this text is easy to understand. It shows that the Prophet صلى الله عليه وسلم answered the question with a simple action. The Hadith also helps readers avoid making tayammum harder than what is stated in this report."},"teachings":["Ammar asked the Prophet صلى الله عليه وسلم directly about tayammum.","The Prophet صلى الله عليه وسلم commanded one stroke for the face and hands.","The Hadith gives a short and direct method.","Asking about purification can lead to clear guidance."],"related_hadiths":[{"id":"323","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"328","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E642" s="4" t="n"/>
@@ -15279,7 +15283,7 @@
       </c>
       <c r="D643" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tayammum During Travel","description":"$book_name$ $hadith_number$ - $chapter_name$. Qatadah was asked about tayammum in travel and reported wording about wiping up to the elbows."},"heading":{"title":"Tayammum During Travel and Wiping Up to the Elbows","description":"This Hadith is about tayammum during a journey. Qatadah was asked about the issue, and he reported a narration through al-Sha'bi from Abd al-Rahman ibn Abza, from Ammar ibn Yasir, from the Messenger of Allah صلى الله عليه وسلم. The wording here says “up to the elbows.” The narration is brief, so we should not add more than it gives. Its core value is that it records a specific wording related to the extent of wiping in tayammum while traveling. For readers searching “tayammum during travel,” this Hadith shows that the topic was asked about by early Muslims and that reports were passed on with their exact wording."},"teachings":["Tayammum was discussed in the setting of travel.","This wording mentions wiping up to the elbows.","The report is linked through Ammar ibn Yasir.","Short narrations can preserve specific legal wording."],"related_hadiths":[{"id":"323","book_id":"4","label":"Sunan Abu Dawud"},{"id":"325","book_id":"4","label":"Sunan Abu Dawud"},{"id":"327","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Tayammum During Travel","description":"$book_name$ $hadith_number$ - $chapter_name$. Qatadah was asked about tayammum in travel and reported wording about wiping up to the elbows."},"heading":{"title":"Tayammum During Travel and Wiping Up to the Elbows","description":"This Hadith is about tayammum during a journey. Qatadah was asked about the issue, and he reported a narration through al-Sha'bi from Abd al-Rahman ibn Abza, from Ammar ibn Yasir, from the Messenger of Allah صلى الله عليه وسلم. The wording here says “up to the elbows.” The narration is brief, so we should not add more than it gives. Its core value is that it records a specific wording related to the extent of wiping in tayammum while traveling. For readers searching “tayammum during travel,” this Hadith shows that the topic was asked about by early Muslims and that reports were passed on with their exact wording."},"teachings":["Tayammum was discussed in the setting of travel.","This wording mentions wiping up to the elbows.","The report is linked through Ammar ibn Yasir.","Short narrations can preserve specific legal wording."],"related_hadiths":[{"id":"323","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"325","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"327","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E643" s="4" t="n"/>
@@ -15302,7 +15306,7 @@
       </c>
       <c r="D644" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Right Hand for Purity and Food","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used his right hand for ablution water and food, and his left for evacuation and repugnant matters."},"heading":{"title":"Hadith About Right Hand for Purity and Food","description":"This hadith about right hand for purity and food explains the Prophet’s صلى الله عليه وسلم daily hand etiquette. Aishah reports that his right hand was for getting water for ablution and for taking food. His left hand was for evacuation and for anything repugnant. The message is clear and balanced. The right hand is used for clean and honored actions, such as food and water connected to purification. The left hand is used for cleaning after private needs and similar matters. Searchers often type “right hand for wudu and food hadith” or “left hand for toilet hadith.” The hadith helps Muslims organize ordinary habits with cleanliness and respect. It is a small daily practice, but it appears in very personal parts of life."},"teachings":["Use the right hand for clean and honored actions.","Use the left hand for evacuation and disliked matters.","The hadith teaches order and cleanliness in private habits."],"related_hadiths":[{"id":"153","book_id":"1","label":"Sahih Bukhari"},{"id":"154","book_id":"1","label":"Sahih Bukhari"},{"id":"5376","book_id":"1","label":"Sahih Bukhari"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Right Hand for Purity and Food","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم used his right hand for ablution water and food, and his left for evacuation and repugnant matters."},"heading":{"title":"Hadith About Right Hand for Purity and Food","description":"This hadith about right hand for purity and food explains the Prophet’s صلى الله عليه وسلم daily hand etiquette. Aishah reports that his right hand was for getting water for ablution and for taking food. His left hand was for evacuation and for anything repugnant. The message is clear and balanced. The right hand is used for clean and honored actions, such as food and water connected to purification. The left hand is used for cleaning after private needs and similar matters. Searchers often type “right hand for wudu and food hadith” or “left hand for toilet hadith.” The hadith helps Muslims organize ordinary habits with cleanliness and respect. It is a small daily practice, but it appears in very personal parts of life."},"teachings":["Use the right hand for clean and honored actions.","Use the left hand for evacuation and disliked matters.","The hadith teaches order and cleanliness in private habits."],"related_hadiths":[{"id":"153","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"154","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"},{"id":"5376","book_id":"1","slug":"bukhari","label":"Sahih Bukhari"}]}</t>
         </is>
       </c>
       <c r="E644" s="4" t="n"/>
@@ -15325,7 +15329,7 @@
       </c>
       <c r="D645" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Purification Before Returning Salam","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports the Prophet صلى الله عليه وسلم delaying salam until he performed wiping after leaving the toilet."},"heading":{"title":"Purification Before Replying to Salam After Toilet","description":"This Hadith reports that a man passed by the Messenger of Allah صلى الله عليه وسلم in a street after he had returned from the toilet or urinated. The man gave salam, but the Prophet صلى الله عليه وسلم did not reply immediately. When the man was almost out of sight, the Prophet صلى الله عليه وسلم struck the wall with his hands, wiped his face, then struck again and wiped his arms. He then returned the salam and explained that he had not replied because he was not in a state of purification. The narration also includes Abu Dawud’s note that this wording with two strikes from the Prophet صلى الله عليه وسلم was not supported in the same way by others. So the explanation should keep both the action and the hadith note in view."},"teachings":["The Prophet صلى الله عليه وسلم gave a reason for delaying the reply to salam.","The report links the delay to not being in a state of purification.","The narration mentions wiping from a wall in this event.","Abu Dawud records a caution about the two-strike wording."],"related_hadiths":[{"id":"329","book_id":"4","label":"Sunan Abu Dawud"},{"id":"331","book_id":"4","label":"Sunan Abu Dawud"},{"id":"338","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Purification Before Returning Salam","description":"$book_name$ $hadith_number$ - $chapter_name$. This narration reports the Prophet صلى الله عليه وسلم delaying salam until he performed wiping after leaving the toilet."},"heading":{"title":"Purification Before Replying to Salam After Toilet","description":"This Hadith reports that a man passed by the Messenger of Allah صلى الله عليه وسلم in a street after he had returned from the toilet or urinated. The man gave salam, but the Prophet صلى الله عليه وسلم did not reply immediately. When the man was almost out of sight, the Prophet صلى الله عليه وسلم struck the wall with his hands, wiped his face, then struck again and wiped his arms. He then returned the salam and explained that he had not replied because he was not in a state of purification. The narration also includes Abu Dawud’s note that this wording with two strikes from the Prophet صلى الله عليه وسلم was not supported in the same way by others. So the explanation should keep both the action and the hadith note in view."},"teachings":["The Prophet صلى الله عليه وسلم gave a reason for delaying the reply to salam.","The report links the delay to not being in a state of purification.","The narration mentions wiping from a wall in this event.","Abu Dawud records a caution about the two-strike wording."],"related_hadiths":[{"id":"329","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"331","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"338","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E645" s="4" t="n"/>
@@ -15348,7 +15352,7 @@
       </c>
       <c r="D646" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Before Returning Salam","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم wiped his face and hands at a wall, then returned the man’s salam."},"heading":{"title":"Wiping the Face and Hands Before Replying to Salam","description":"This Hadith is another report about the Prophet صلى الله عليه وسلم coming from the privy and meeting a man near Bir Jamal. The man gave salam, but the Messenger of Allah صلى الله عليه وسلم did not return it until he came to a wall. He placed his hands on the wall, wiped his face and hands, and then returned the salam. The narration is short and focused. It does not give a long ruling or many details. Its main lesson is tied to purification before replying in that moment. For people searching “tayammum before returning salam,” this Hadith gives a direct report with the key actions: wall, hands, face, hands, then salam."},"teachings":["The Prophet صلى الله عليه وسلم returned the salam after wiping his face and hands.","The narration mentions a wall as the surface used.","The report connects purification and respect for the greeting.","The action is described in a simple and direct way."],"related_hadiths":[{"id":"329","book_id":"4","label":"Sunan Abu Dawud"},{"id":"330","book_id":"4","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Wiping Before Returning Salam","description":"$book_name$ $hadith_number$ - $chapter_name$. The Prophet صلى الله عليه وسلم wiped his face and hands at a wall, then returned the man’s salam."},"heading":{"title":"Wiping the Face and Hands Before Replying to Salam","description":"This Hadith is another report about the Prophet صلى الله عليه وسلم coming from the privy and meeting a man near Bir Jamal. The man gave salam, but the Messenger of Allah صلى الله عليه وسلم did not return it until he came to a wall. He placed his hands on the wall, wiped his face and hands, and then returned the salam. The narration is short and focused. It does not give a long ruling or many details. Its main lesson is tied to purification before replying in that moment. For people searching “tayammum before returning salam,” this Hadith gives a direct report with the key actions: wall, hands, face, hands, then salam."},"teachings":["The Prophet صلى الله عليه وسلم returned the salam after wiping his face and hands.","The narration mentions a wall as the surface used.","The report connects purification and respect for the greeting.","The action is described in a simple and direct way."],"related_hadiths":[{"id":"329","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"330","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"326","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E646" s="4" t="n"/>
@@ -15371,7 +15375,7 @@
       </c>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Clean Earth as Tahur","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Dharr was taught that clean earth purifies when water is absent, but water should be used when found."},"heading":{"title":"Clean Earth as Tahur When Water Cannot Be Found","description":"This Hadith gives another version of Abu Dharr’s story. He explains that he was away from the watering place with his family, became sexually defiled, and prayed without purification. When he came to the Prophet صلى الله عليه وسلم, he admitted that he felt ruined. The Prophet صلى الله عليه وسلم asked what had ruined him, then commanded water to be brought. Abu Dharr bathed behind a camel and came back. The Prophet صلى الله عليه وسلم then said that clean earth is a means of purification even if water is not found for ten years. When water is found, it should touch the skin. This Hadith directly teaches that lack of water does not leave a person without a path to purification."},"teachings":["Abu Dharr openly admitted his concern about praying without purification.","The Prophet صلى الله عليه وسلم taught that clean earth can purify when water is absent.","When water becomes available, it should be used on the skin.","The narration shows that asking about a mistake can lead to guidance."],"related_hadiths":[{"id":"332","book_id":"4","label":"Sunan Abu Dawud"},{"id":"334","book_id":"4","label":"Sunan Abu Dawud"},{"id":"338","book_id":"4","label":"Sunan Abu Dawud"}]}</t>
+          <t>{"meta":{"title":"$book_name$ - $hadith_number$ ($publication$) | Clean Earth as Tahur","description":"$book_name$ $hadith_number$ - $chapter_name$. Abu Dharr was taught that clean earth purifies when water is absent, but water should be used when found."},"heading":{"title":"Clean Earth as Tahur When Water Cannot Be Found","description":"This Hadith gives another version of Abu Dharr’s story. He explains that he was away from the watering place with his family, became sexually defiled, and prayed without purification. When he came to the Prophet صلى الله عليه وسلم, he admitted that he felt ruined. The Prophet صلى الله عليه وسلم asked what had ruined him, then commanded water to be brought. Abu Dharr bathed behind a camel and came back. The Prophet صلى الله عليه وسلم then said that clean earth is a means of purification even if water is not found for ten years. When water is found, it should touch the skin. This Hadith directly teaches that lack of water does not leave a person without a path to purification."},"teachings":["Abu Dharr openly admitted his concern about praying without purification.","The Prophet صلى الله عليه وسلم taught that clean earth can purify when water is absent.","When water becomes available, it should be used on the skin.","The narration shows that asking about a mistake can lead to guidance."],"related_hadiths":[{"id":"332","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"334","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"},{"id":"338","book_id":"4","slug":"dawud","label":"Sunan Abu Dawud"}]}</t>
         </is>
       </c>
       <c r="E647" s="4" t="n"/>
@@ -15394,7 +15398